--- a/data/berita_2026-08-07.xlsx
+++ b/data/berita_2026-08-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$86</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,18 +419,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="33" customWidth="1" min="3" max="3"/>
-    <col width="43" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4475,8 +4475,3721 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Transformasi PAM Jaya dinilai jadi fondasi akses air minum perpipaan</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:58:13 +0700</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Peneliti Jakarta Public Service (JPS) Rahmat Hidayat mengatakan transformasi layanan yang dilakukan PAM Jaya merupakan ...</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683567/transformasi-pam-jaya-dinilai-jadi-fondasi-akses-air-minum-perpipaan</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_20260807_084236.jpg</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Jumat, cuaca di sebagian besar wilayah Indonesia berawan tebal</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:57:35 +0700</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Badan Meteorologi, Klimatologi, dan Geofisika (BMKG) memprakirakan cuaca hari ini, Jumat, di sebagian besar wilayah ...</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683565/jumat-cuaca-di-sebagian-besar-wilayah-indonesia-berawan-tebal</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/08/07/IMG_20250415_110015.jpg</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>PIHPS: Harga cabai rawit Rp58.750/kg, telur ayam Rp29.500/kg</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:53:08 +0700</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Pusat Informasi Harga Pangan Strategis (PIHPS) Nasional, yang dikelola Bank Indonesia, mencatat harga komoditas cabai ...</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683561/pihps-harga-cabai-rawit-rp58750-kg-telur-ayam-rp29500-kg</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/27EE2ECB-317D-4C0C-8627-5B3B9FB5C1C9.jpeg</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Strategi baru senjata nuklir AS dinilai tingkatkan risiko perang</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:49:34 +0700</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Rencana Amerika Serikat untuk memperluas penggunaan senjata nuklir taktis dalam konflik yang mungkin terjadi dapat ...</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683559/strategi-baru-senjata-nuklir-as-dinilai-tingkatkan-risiko-perang</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/04/kapal-selam.jpg</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Duel ulang juara WBO Dubois melawan Wardley digelar Oktober</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:48:48 +0700</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Promotor Queensberry Promotions menyatakan duel ulang juara dunia kelas berat (di atas 90,7kg) World Boxing ...</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683557/duel-ulang-juara-wbo-dubois-melawan-wardley-digelar-oktober</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/a0f228b1-2335-4048-a457-f7491c080a2d.jpeg</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Rekomendasi drama Korea dengan genre komedi romantis</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:45:41 +0700</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Bila sedang mencari rekomendasi drama Korea dengan genre komedi romantis, beberapa judul berikut barangkali bisa ...</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683553/rekomendasi-drama-korea-dengan-genre-komedi-romantis</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2021/02/11/What-s-Wrong-With-Secretary-Kim-Start-Up.jpg</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Pertamina: Terminal LPG Tanjung Sekong raih sertifikasi terminal hijau</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:44:36 +0700</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>PT Pertamina (Persero) kembali mencatatkan Terminal LPG Tanjung Sekong resmi meraih Green Terminal Label Certification ...</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683551/pertamina-terminal-lpg-tanjung-sekong-raih-sertifikasi-terminal-hijau</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/11/pertamina-hadirkan-terminal-hijau-di-kota-cilegon-2726870.jpg</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Parlemen Iran kaji RUU larang AS-Israel lewat Selat Hormuz</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:38:55 +0700</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Parlemen Iran sedang menyusun rancangan undang-undang (RUU) mengenai langkah-langkah strategis untuk menjamin keamanan ...</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683548/parlemen-iran-kaji-ruu-larang-as-israel-lewat-selat-hormuz</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/thumbs_b_c_09e6784a909d202910770244ef3eea07.jpg</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Gelombang panas berkaitan dengan kesehatan mental anak-anak</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:30:25 +0700</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Kenaikan suhu dan gelombang panas berkaitan dengan memburuknya kesehatan mental pada anak-anak dan remaja, ungkap ...</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683547/gelombang-panas-berkaitan-dengan-kesehatan-mental-anak-anak</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/CjkinzN000027_20260806_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Penjualan Nintendo Switch 2 turun jelang kenaikan harga</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:29:52 +0700</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Konsol Nintendo Switch 2 tercatat telah terjual sebanyak 3,82 juta unit pada kuartal terbaru atau turun 34,4 persen ...</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683545/penjualan-nintendo-switch-2-turun-jelang-kenaikan-harga</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/images-7.jpg</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Kemenekraf dan ABPEDNAS perkuat sinergi kembangkan potensi ekraf desa</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:27:31 +0700</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Kementerian Ekonomi Kreatif memperkuat sinergi dengan Asosiasi Badan Permusyawaratan Desa Nasional (ABPEDNAS) untuk ...</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683543/kemenekraf-dan-abpednas-perkuat-sinergi-kembangkan-potensi-ekraf-desa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000455131.jpg</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Air yang menguji kepemimpinan</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:23:31 +0700</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Setetes air yang mengalir dari keran rumah mungkin tampak sederhana. Padahal, di balik aliran itu terdapat rangkaian ...</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683541/air-yang-menguji-kepemimpinan</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/pipa.jpg</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Menko IPK: WTP standar moral wujudkan tata kelola keuangan negara</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:21:22 +0700</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Infrastruktur dan Pembangunan Kewilayahan (Menko IPK) Agus Harimurti Yudhoyono (AHY) ...</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683540/menko-ipk-wtp-standar-moral-wujudkan-tata-kelola-keuangan-negara</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-00.46.45.jpg</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Kamboja rilis peringatan perjalanan laut saat hadapi dampak 3 siklon</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:13:13 +0700</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Kementerian Sumber Daya Air dan Meteorologi Kamboja pada Kamis (6/8) mengeluarkan peringatan cuaca yang mengimbau para ...</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683539/kamboja-rilis-peringatan-perjalanan-laut-saat-hadapi-dampak-3-siklon</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/CjkinzN000030_20260806_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Trailer baru GTA VI akan tayang perdana di Netflix pada 27 Agustus</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:53:25 +0700</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Gim Grand Theft Auto VI (GTA VI) akan menampilkan trailer cuplikan permainan terlebih dahulu di layanan pemutaran film ...</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683536/trailer-baru-gta-vi-akan-tayang-perdana-di-netflix-pada-27-agustus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/intro-1786019336.jpg</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Janice Tjen terhenti pada babak pertama ganda WTA 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:51:55 +0700</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Petenis Indonesia Janice Tjen terhenti pada babak pertama sektor ganda WTA 1000 National Bank Open 2026 di Toronto, ...</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683535/janice-tjen-terhenti-pada-babak-pertama-ganda-wta-1000-toronto</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/2026-01-22T015230Z_1942350582_UP1EM1M057GHL_RTRMADP_3_TENNIS-AUSOPEN.jpg</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Vivo S2 debut dengan layar AMOLED melengkung dan baterai 7.050mAh</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:49:28 +0700</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Vivo meluncurkan ponsel pintar Vivo S2 yang menandai kembalinya seri S setelah terakhir kali menghadirkan Vivo S1 pada ...</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683532/vivo-s2-debut-dengan-layar-amoled-melengkung-dan-baterai-7050mah</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/image-768x1393.jpg</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Agus Fatoni: Alumni Kepamongprajaan wajib dukung program pemerintah</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:42:45 +0700</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Ketua Umum Dewan Pengurus Nasional (DPN) Ikatan Keluarga Alumni Pendidikan Tinggi Kepamongprajaan (IKAPTK) Agus Fatoni ...</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683529/agus-fatoni-alumni-kepamongprajaan-wajib-dukung-program-pemerintah</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001099664.jpg</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Samsat Keliling tersedia di 14 titik wilayah Jadetabek pada Jumat</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:28:09 +0700</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya menyediakan layanan Sistem Administrasi Manunggal Satu Atap (Samsat) Keliling di 14 titik wilayah yang ...</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683525/samsat-keliling-tersedia-di-14-titik-wilayah-jadetabek-pada-jumat</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/24/program-pemutihan-pajak-kendaraan-di-jakarta-2665333.jpg</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SIM Keliling tersedia di lima lokasi Jakarta pada Jumat</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:20:02 +0700</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Direktorat Lalu Lintas Polda Metro Jaya menyediakan layanan surat izin mengemudi (SIM) Keliling di lima lokasi di ...</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683523/sim-keliling-tersedia-di-lima-lokasi-jakarta-pada-jumat</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/07/10/IMG_20240710_063125.jpg</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Politik kemarin, Investasi bidang pendidikan hingga komentar nakes</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 06:59:06 +0700</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Beragam peristiwa politik telah terjadi pada Kamis (6/8), mulai Presiden ingin investasi besar di bidang pendidikan ...</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683520/politik-kemarin-investasi-bidang-pendidikan-hingga-komentar-nakes</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/27d03785-b673-4948-938e-08b30202c584.jpeg</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Jumat pagi, kualitas udara Jakarta masuk 10 besar terburuk di dunia</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 06:58:37 +0700</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Kualitas udara di Jakarta pada Jumat pagi menduduki posisi 10 besar sebagai kota dengan udara terburuk di dunia dan ...</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683516/jumat-pagi-kualitas-udara-jakarta-masuk-10-besar-terburuk-di-dunia</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/12/Kasus-COVID-19-Indonesia-111220-hma-3.jpg</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Hasil Liga Conference: Paes starter, Ajax menang 3-1 atas Shelbourne</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 06:48:29 +0700</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Kiper timnas Indonesia Maarten Paes menjadi pemain pemula (starter) saat Ajax Amsterdam meraih kemenangan 3-1 atas ...</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683515/hasil-liga-conference-paes-starter-ajax-menang-3-1-atas-shelbourne</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000042755.jpg</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>25 Siswa dan Guru di Bogor Keracunan Usai Diduga Santap Menu MBG</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:56:44 +0700</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Sebanyak 25 orang, termasuk siswa dan guru, mengalami keracunan di Desa Ciherang, Bogor. Keracunan diduga terjadi usai menyantap menu MBG.</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607976/25-siswa-dan-guru-di-bogor-keracunan-usai-diduga-santap-menu-mbg</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/09/30/ilustrasi-makan-siang-gratis-1759218011364_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Kemensos Bentuk Tim Khusus Percepat Pembangunan Sekolah Rakyat Permanen</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:56:42 +0700</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Rahmat Khairurizqi</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Kemensos bentuk Tim Percepatan Pembangunan Sekolah Rakyat untuk kawal pembangunan 61 titik sekolah permanen.</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607975/kemensos-bentuk-tim-khusus-percepat-pembangunan-sekolah-rakyat-permanen</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kemensos-1786067747846_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Berkat Bantuan Kewirausahaan Kemensos, Oneng Setop Mengemis</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:46:06 +0700</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Moch. Prima Fauzi</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Setelah hampir 10 tahun mengemis, Oneng kini berjualan berkat bantuan modal usaha dari Kementerian Sosial. Dia bertekad untuk meningkatkan taraf hidup.</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607968/berkat-bantuan-kewirausahaan-kemensos-oneng-setop-mengemis</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/mantan-pengemis-yang-dapat-bantuan-kemensos-1786067134426_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Kemdikti Sebut Penulis Paper 'Nobel MBG' Cantumkan Nama Tanpa Persetujuan</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:32:44 +0700</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Isal Mawardi</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Kemendiktisaintek menyelidiki makalah Makan Bergizi Gratis yang mencatut nama Prabowo Subianto untuk Nobel Perdamaian 2026. Investigasi masih berlangsung.</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607956/kemdikti-sebut-penulis-paper-nobel-mbg-cantumkan-nama-tanpa-persetujuan</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/09/mendiktisaintek-brian-yuliarto-1778331069187_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Tim 9 Kejagung Periksa Febrie Adriansyah Tersangka TPPU Hari Ini</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:24:51 +0700</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Tim 9 Kejaksaan Agung (Kejagung) akan memeriksa mantan Jampidsus Febrie Adriansyah (FA) hari ini.</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607950/tim-9-kejagung-periksa-febrie-adriansyah-tersangka-tppu-hari-ini</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/24/febrie-adriansyah-1784909849250_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Rebutan Warisan, Petani di Tapsel Tewas Ditikam Adik Kandung</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:21:10 +0700</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Mhd Ilham Pradilla</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Petani berinisial SS (58) tewas usai ditikam adik kandungnya sendiri, GS (53), di Tapanuli Selatan (Tapsel). Peristiwa itu dipicu perebutan harta warisan.</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607946/rebutan-warisan-petani-di-tapsel-tewas-ditikam-adik-kandung</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/12/ilustrasi-pembunuhan-1754995633475_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Viral Wanita ASN Bandung Barat Live TikTok di Jam Kerja, Singgung Fee Proyek</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:59:02 +0700</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Whisnu Pradana</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Viral wanita ASN di lingkungan kantor Pemerintahan Daerah (Pemda) Kabupaten Bandung Barat (KBB) live TikTok saat jam kerja.</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607932/viral-wanita-asn-bandung-barat-live-tiktok-di-jam-kerja-singgung-fee-proyek</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/02/asn-di-mataram-1770022558231_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Satelit Lampung-1 Diluncurkan dari China, BRIN Pastikan Keamanan Data</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:44:23 +0700</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Satelit hiperspektral Lampung-1 yang mendukung pembangunan berbasis AI diluncurkan dari China. BRIN memastikan keamanan data meski diluncurkan di luar RI.</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607904/satelit-lampung-1-diluncurkan-dari-china-brin-pastikan-keamanan-data</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/24/kepala-badan-riset-inovasi-nasional-brin-arif-satria-1763992717436_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Teka-teki Temuan Nyaris Seribu Senjata hingga Narkoba di Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:43:04 +0700</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Temuan mengejutkan di sekolah swasta Jakarta: hampir seribu pucuk senjata, narkoba, dan CD porno ditemukan. Polisi selidiki asal-usulnya.</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607903/teka-teki-temuan-nyaris-seribu-senjata-hingga-narkoba-di-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temuan-ratusan-pucuk-senjata-di-sekolah-swasta-di-pondok-pinang-jakarta-selatan-1786014363566_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Serangan Tiba-tiba Rampok di Bekasi Gondol Duit Puluhan Juta</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:34:57 +0700</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Seorang nasabah di Cibitung jadi korban perampokan bersenjata tajam usai mengambil uang dari bank. Polisi masih menyelidiki dan memburu pelaku.</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607901/serangan-tiba-tiba-rampok-di-bekasi-gondol-duit-puluhan-juta</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2019/04/23/77c24ba3-a62d-47b7-8fed-4c85235df13b_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Api di Gudang Buku SD Jaksel Berujung Siswa Dievakuasi</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:29:38 +0700</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani, Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Gudang penyimpanan buku di SDN 04 Srengseng Sawah kebakaran akibat masalah kelistrikan. Para pelajar dipulangkan lebih cepat akibat kebakaran siang tadi.</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607899/api-di-gudang-buku-sd-jaksel-berujung-siswa-dievakuasi</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/gudang-penyimpanan-buku-di-sdn-04-srengseng-sawah-kebakaran-akibat-masalah-kelistrikan-para-pelajar-dipulangkan-lebih-cepat-ak-1786015666076_169.webp?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Dukung MBG, BRIN Buat Alat Sensor Cegah Pembusukan di Ompreng</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:29:27 +0700</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Kepala BRIN Arif Satria memaparkan inovasi riset untuk mendukung program Prabowo. Salah satunya alat deteksi untuk mencegah gas pembusukan di dalam ompreng MBG.</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607898/dukung-mbg-brin-buat-alat-sensor-cegah-pembusukan-di-ompreng</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kepala-brin-arif-satria-saat-memaparkan-laporan-di-depan-presiden-di-istana-jakarta-kamis-682026-1786062524518_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Perawat Nyinyir Pasien BPJS Viral Curhat Nunggu 8 Jam, RSA UGM Siapkan Sanksi</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:24:32 +0700</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Adji G Rinepta</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Perawat RSA UGM, Dika Purnomo Aji, terancam sanksi etik setelah mengomentari keluhan pasien BPJS. Investigasi sedang dilakukan oleh tim etik rumah sakit.</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607895/perawat-nyinyir-pasien-bpjs-viral-curhat-nunggu-8-jam-rsa-ugm-siapkan-sanksi</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/01/15/ilustrasi-kamar-rumah-sakit_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Pasien BPJS Dihina, Legislator Ingatkan Nakes Jangan Hilang Empati</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 06:43:56 +0700</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Kadek Melda Luxiana</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Asep Rommy Romaya mengecam hinaan nakes terhadap pasien BPJS di media sosial. Ia menegaskan pentingnya empati dan etika dalam pelayanan kesehatan.</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607883/pasien-bpjs-dihina-legislator-ingatkan-nakes-jangan-hilang-empati</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/09/20/ilustrasi-pasien-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Cek Rekomendasi Saham Saat IHSG Melemah</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:46:22 +0700</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Redaksi Detik</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>IHSG turun 0,12% ke 6.343,71. CTRA mulai proyek Senja Beach Club, OKAS tambah kontrak US$60 juta, sementara HAJJ fokus meningkatkan margin.</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8607969/cek-rekomendasi-saham-saat-ihsg-melemah</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/bursa-dan-valas-1786065953-1786065953999.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Investasi Pabrik Tekstil Baru Berpotensi Serap 9.000 Tenaga Kerja</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:45:38 +0700</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Ribuan lapangan kerja terbuka karena hadirnya gelombang investasi baru di industri tekstil dan pakaian jadi.</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/industri/d-8607942/investasi-pabrik-tekstil-baru-berpotensi-serap-9-000-tenaga-kerja</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/14/kenaikan-harga-tekan-industri-garmen-biaya-produksi-ikut-membengkak-1776151719650_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Trump Pasang Tarif 15% untuk Bahan Baku Panel Surya, China Jadi Sasaran</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:30:45 +0700</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Polisilikon menjadi bahan baku untuk membuat semikonduktor dan panel surya yang sebagian besar diproduksi oleh China.</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607929/trump-pasang-tarif-15-untuk-bahan-baku-panel-surya-china-jadi-sasaran</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/presiden-as-donald-trump-saat-memimpin-rapat-kabinet-di-camp-david-maryland-pada-jumat-317-waktu-setempat-1785566125849_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Rencana Iran Perketat Selat Hormuz Bikin Harga Minyak Mendidih</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:15:37 +0700</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Rencana pemerintah Iran memperketat syarat untuk lalu lintas kapal di Selat Hormuz mengerek harga minyak.</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8607917/rencana-iran-perketat-selat-hormuz-bikin-harga-minyak-mendidih</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/06/13/emas-minyak-membara-usai-israel-serang-iran-1749816526884_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Pajak Toko Online Baru Berlaku 1 November, Telanjur Bayar Gimana Nasibnya?</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan (Kemenkeu) memutuskan menunda penerapan pemungutan Pajak Penghasilan (PPh) Pasal 22 oleh marketplace hingga 31 Oktober 2026.</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607694/pajak-toko-online-baru-berlaku-1-november-telanjur-bayar-gimana-nasibnya</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2019/03/04/5394c5b5-e2e8-4cc6-b022-29b973e633f2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Jumlah Penerima MBG Berpotensi Turun 6 Juta</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Pemerintah menemukan 6 juta data ganda penerima manfaat program makan bergizi gratis (MBG). Hal ini membuat jumlah penerima MBG bakal dievaluasi.</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607759/jumlah-penerima-mbg-berpotensi-turun-6-juta</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/dapur-mbg-dikejar-sertifikasi-higiene-sanitasi-1785988097868_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>RI Terancam Kehilangan Ekspor Nikel 5 Juta Ton</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Kadin Indonesia memperkirakan ekspor nikel akan berkurang 3,5-5 juta ton akibat pemangkasan kuota produksi nikel dalam RKAB 2026.</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8607699/ri-terancam-kehilangan-ekspor-nikel-5-juta-ton</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/10/22/mengintip-pengelolaan-tambang-nikel-di-sulawesi-selatan-1761100742633_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Kronologi Temuan Hampir 1.000 Pucuk Senjata di Sekolah Swasta di Jaksel, Saksi Mengaku Heran</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:50:15 +0700</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Saksi Untung Sangaji mengaku  merasa heran, mengapa ada senjata dengan jumlah hampir 1.000 pucuk yang disimpan di lingkungan sekolah.</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7865078/kronologi-temuan-hampir-1000-pucuk-senjata-di-sekolah-swasta-di-jaksel-saksi-mengaku-heran</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/C0lT2Y0zI_MxSjs7s2qkRNylM8s=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Benda-berbentuk-senjata-yang-ditemukan-di-sebuah-ruangan-321.jpg</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Putuskan Calon Gubernur Bank Indonesia Pekan Ini, Berikut Nama yang Mencuat</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:48:20 +0700</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Destry saat ini menjadi Pejabat Gubernur Sementara (PGS) Bank Indonesia setelah mundurnya Perry Warjiyo.</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7865077/presiden-prabowo-putuskan-calon-gubernur-bank-indonesia-pekan-ini-berikut-nama-yang-mencuat</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/wsAZsOfs9valaqSWEXMzqToStdY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/prabowo-di-sidang-kabinet-paripurna-123.jpg</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Menyebut Nama Sendiri Saat Stres Bisa Bantu Tetap Tenang? Ini Temuan Riset Psikolog</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:47:36 +0700</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Riset Universitas Michigan menemukan bahwa menyebut nama sendiri saat menghadapi tekanan dapat membantu menciptakan jarak psikologis</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/lifestyle/7865076/menyebut-nama-sendiri-saat-stres-bisa-bantu-tetap-tenang-ini-temuan-riset-psikolog</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/xxxt4LswqJgzMOWvod4vSetS9vY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/KORTISOL-TINGGI-Foto-ilustrasi-orang-mengalami-stress.jpg</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Saepul Curi dan Jual Motor Kunaefi Korban Mutilasi, Polisi Kini Buru Sang Penadah Motor</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:47:07 +0700</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Penyidik mencari barang bukti berupa pisau yang diduga digunakan pelaku untuk menghabisi nyawa korban sekaligus memutilasi jasadnya.</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7865075/saepul-curi-jual-motor-kunaefi-korban-mutilasi-polisi-kini-buru-sang-penadah-motor</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/4XppmMwLuiWmzR-TlJ_3p75y4Nc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Saepul-26-pelaku-mutilasi-Kusnaefi-51-di-Depok-ditangkap-polisi-setelah-kabur-ke-Pandeglang.jpg</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Nasib Ipda MA, Perwira Polisi yang Tabrak Balita hingga Tewas di Bone</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:44:07 +0700</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Ipda MA diamankan Propam Polres Bone usai mobil yang dikemudikannya menabrak motor dan tewaskan balita 4 tahun akibat diduga alami rem blong.</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865074/nasib-ipda-ma-perwira-polisi-yang-tabrak-balita-hingga-tewas-di-bone</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/FjaohxO3fAoVVJJuCxm1_cfkeDY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/balita-tewas-ditabrak-perwira-polisi.jpg</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Riwayat Pendidikan Ade Darmawan yang Prediksinya 100 Persen Akurat soal Praperadilan ke-4 Roy Suryo</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:43:38 +0700</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Berikut ini adalah riwayat pendidikan Ade Darmawan yang prediksinya 100 persen akurat soal Roy Suryo mengajukan praperadilan keempat.</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865073/riwayat-pendidikan-ade-darmawan-yang-prediksinya-100-persen-akurat-soal-praperadilan-ke-4-roy-suryo</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/iepAQOTFqUD4cjifSfoHNzqAHmg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ade-darmawan-dan-roy-suryo.jpg</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Bersyukur Perankan Ustaz di Film Munafik, Arya Saloka Kembali Belajar Iqra, Perbaiki Bacaan AlQuran</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:43:01 +0700</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Arya Saloka menjalani persiapan panjang untuk perankan Ustaz Adam dalam film horor Munafik: Melawan Iblis.</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865072/bersyukur-perankan-ustaz-di-film-munafik-arya-saloka-kembali-belajar-iqra-perbaiki-bacaan-alquran</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/HQig47UghfflyBr1U314ZTPyFMc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/arya-saloka-munafik-film.jpg</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Kode Redeem FC Mobile Terbaru 7 Agustus 2026 Klaim Reward 1,000 Gems dan 100 Rankup Tokens Gratis</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:42:49 +0700</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Kode redeem FC Mobile terbaru 7 Agustus 2026 yang tersedia reward menarik gratis, segera klaim 1,000 Gems, 100 Rankup Tokens, hingga pemain MLS.</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/techno/7865071/kode-redeem-fc-mobile-terbaru-7-agustus-2026-klaim-reward-1000-gems-100-rankup-tokens-gratis</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/K79AqXTM4a6pvpYwfh3RiDVLRjI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/bermain-gim-FC-Mobile-baru-nih.jpg</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Lesti Kejora Minta Anaknya Panggil Ruben Onsu dengan Sebutan Ayah, sang Presenter Ngaku Baper</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:39:07 +0700</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Presenter Ruben Onsu ngaku baper usai anak pedangdut Lesti Kejora panggil dirinya dengan sebutan Ayah.</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865070/lesti-kejora-minta-anaknya-panggil-ruben-onsu-dengan-sebutan-ayah-sang-presenter-ngaku-baper</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vepR-Pgt5UYY2gZZ6i1yabBOu9s=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ruben-Onsu-resmi-mualaf-pastikan-keputusannya-tak-ada-kaitan-dengan-masalah-rumah-tangganya.jpg</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>7 Cara Tetap Rajin Bersih-Bersih Meski Lelah, Menurut Pakar Kebersihan</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:38:24 +0700</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Pakar kebersihan menyarankan membagi pekerjaan rumah menjadi tugas-tugas kecil agar tidak menguras energi.</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/lifestyle/7865069/7-cara-tetap-rajin-bersih-bersih-meski-lelah-menurut-pakar-kebersihan</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/pIhQ9IemYHy_UJDUO-Eo9vfOrHw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/LIFESTYLE-Foto-ilustrasi-seseorang-membersihkan-rumah.jpg</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>AS Beda Suara soal Iran, Vance Sebut Teheran Sulit Diajak Negosiasi, Trump Klaim Deal Sudah Dekat</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:35:52 +0700</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Wakil Presiden JD Vance menilai pembicaraan dengan Teheran akan berlangsung rumit karena perpecahan politik di dalam kepemimpinan Iran</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7865068/as-beda-suara-soal-iran-vance-sebut-teheran-sulit-diajak-negosiasi-trump-klaim-deal-sudah-dekat</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/f6UC76RegI-5Nr7f0hdGhGs5bNA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Donald-Trump-dan-JD-Vance-sdtg34yh.jpg</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Lionel Messi Mending Liburan Saja, Pelatih Monterrey Pasrah Lawan Inter Miami</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:34:51 +0700</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Pelatih Monterrey bercanda meminta Messi untuk berlibur lebih lama agar tak bermain di Leagues Cup bersama Inter Miami</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7865067/lionel-messi-mending-liburan-saja-pelatih-monterrey-pasrah-lawan-inter-miami</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/yZU9C4kdiVDlBtgSF4ARQy0YF0E=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Perayaan-Gol-Lionel-Messi-Inter-Miami-vs-DC-United.jpg</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Hari Terakhir War Undangan Upacara HUT ke-81 RI di Istana Merdeka, Klik Link dan Semoga Beruntung</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:32:36 +0700</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Hari ini Jumat, 7 Agustus 2026 adalah hari terakhir bagi masyarakat untuk mengikuti war tiket undangan Upacara HUT ke-81 Kemerdekaan RI.</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865066/hari-terakhir-war-undangan-upacara-hut-ke-81-ri-di-istana-merdeka-klik-link-semoga-beruntung</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/LMu_-t0Ne-W0VbRATPhbubx62QY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Prabowo-Apresiasi-Petugas-dan-Peserta-Upacara-HUT-ke-80-RI-Saya-Bangga.jpg</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ChatGPT, Claude, dan Gemini Sepakat: Ini Kebiasaan Pagi Terbaik untuk Energi dan Tidur Berkualitas</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:26:04 +0700</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>ChatGPT, Claude, dan Gemini sama-sama merekomendasikan paparan sinar matahari pagi sebagai kebiasaan terbaik setelah bangun tidur.</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/lifestyle/7865065/chatgpt-claude-dan-gemini-sepakat-ini-kebiasaan-pagi-terbaik-untuk-energi-dan-tidur-berkualitas</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/01IuhYG0pK59xTw5zxLXl1jKtCM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/LIFESTYLE-Foto-ilustrasi-bangun-tidur.jpg</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Cerita Acha Septriasa Harus Lakoni Adegan Merayap di Tembok saat Kerasukan di Film Munafik</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:24:41 +0700</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Acha Septriasa mempersiapkan fisik secara serius demi memerankan Fitri dalam film horor Munafik: Melawan Iblis.</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865064/cerita-acha-septriasa-harus-lakoni-adegan-merayap-di-tembok-saat-kerasukan-di-film-munafik</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/RPsthg0vFVhwax1UNUammZMviP4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/acha-septriasa-munafik.jpg</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Polisi Singapura Tangkap Pria yang Injak-injak Al Qur'an di Dalam Bus</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:21:42 +0700</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Polisi Singapura menangkap seorang pria berusia 27 tahun yang sengaja menginjak Al-Quran di dalam bus umum.</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7865063/polisi-singapura-tangkap-pria-yang-injak-injak-al-quran-di-dalam-bus</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/hOPOxIMFfNkKLVSa3jVV25yC3-w=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/pelaku-injak-k.jpg</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Kasus Minyakita Berbau Solar dan Minyak Tanah di Wonogiri, 1 Orang Jadi Tersangka</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:17:39 +0700</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Sosok J pria 50 tahun tersangka di balik kasus Minyakita berbau solar dan minyak tanah di Wonogiri, Jateng.</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865062/kasus-minyakita-berbau-solar-dan-minyak-tanah-di-wonogiri-1-orang-jadi-tersangka</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/2egThdpLeDwRDG8Z5SjvUK_l7IQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/minyakita-bau-minyak-tanah-di-Wonogiri.jpg</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>3 Drama Korea Romantis Terbaru Tayang Agustus 2026, dari Kisah Cinta Kantor hingga Musisi Muda</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:15:15 +0700</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Tiga drama romantis Korea siap tayang sepanjang Agustus 2026. Dari romansa kantor hingga kisah cinta penuh misteri dan musik</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865061/3-drama-korea-romantis-terbaru-tayang-agustus-2026-dari-kisah-cinta-kantor-hingga-musisi-muda</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/92tPO-ZJW7eu75LMBlPwRyxjWCM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/drakorbaruagustus11111.jpg</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Bicara soal Mualaf, Ruben Onsu Sebut Lesti Kejora Ikut Andil di Perjalanan Dirinya Menentukan Arah</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:13:29 +0700</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Presenter Ruben Onsu sebut Lesti Kejora salah satu orang yang ikut andil dalam perjalanan spiritualnya.</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865060/bicara-soal-mualaf-ruben-onsu-sebut-lesti-kejora-ikut-andil-di-perjalanan-dirinya-menentukan-arah</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/W7gmLCzQlwXnp_c6UbnBU9p_jj4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ruben-onsu-puasa-2621.jpg</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Di Bawah Kesepakatan dengan Oman, Iran Akan Larang Kapal-kapal AS dan Israel Lewati Selat Hormuz</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:13:14 +0700</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Parlemen Iran mengkaji usulan melarang kapal yang terkait AS dan Israel melintasi Selat Hormuz hingga Iran menerima kompensasi perang.</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7865059/di-bawah-kesepakatan-dengan-oman-iran-akan-larang-kapal-kapal-as-dan-israel-lewati-selat-hormuz</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vm-7ifiH7ApHry7X5wP6lkf2RCc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/PERANG-IRAN-Tangkap-layar-Google-Maps-memperlihatkan-peta-Selat-Hormuzdf.jpg</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Pemilik FIFA Dikuasai Arab Saudi, Dibeli Nyaris Rp 1.000 Triliun</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:31:57 +0700</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Electronic Arts kini dimiliki oleh Arab Saudi setelah akuisisi senilai US$55 miliar oleh PIF.</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807082804-37-757304/pemilik-fifa-dikuasai-arab-saudi-dibeli-nyaris-rp-1000-triliun</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2023/05/31/1246159554_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Kayu 300 Juta Tahun Ungkap Sejarah Panjang Geologi Bumi</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Penelitian baru mengungkap sejarah geologi jutaan tahun dari kayu fosil di Jerman.</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807071138-37-757283/kayu-300-juta-tahun-ungkap-sejarah-panjang-geologi-bumi</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/04/16/hutan-dok-freepik-1744794147032_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Seluruh Dunia Pakai, Ternyata Teknologi Ini Dapat Subsidi Amerika</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:10:27 +0700</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>GPS adalah teknologi navigasi penting yang didanai AS dengan US$2 miliar.</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807070614-37-757281/seluruh-dunia-pakai-ternyata-teknologi-ini-dapat-subsidi-amerika</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/06/11/sebuah-monitor-menunjukkan-pelacakan-gps-pada-balon-yang-dibuat-oleh-kelompok-aktivis-yang-berbasis-di-seoul-yang-dirancang-un-1_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Isu PHK Buruh Garmen di Cimahi, Ini Penjelasan Menperin</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:30:50 +0700</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Ahmad Fikri Noor</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Menteri Perindustrian (Menperin) Agus Gumiwang Kartasasmita memberikan penjelasan terkait isu pemutusan hubungan kerja (PHK) terhadap 178 buruh PT Namnam Fashion Industries di Kota Cimahi, Jawa Barat. Agus...</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjdlje490/isu-phk-buruh-garmen-di-cimahi-ini-penjelasan-menperin</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/015921500-1729087578-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Cek Progres Kampung Haji di Saudi, Rosan Ungkap Danantara Ditawari Investasi Bandara Madinah</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:21:08 +0700</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Ahmad Fikri Noor</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Presiden Prabowo Subianto menerima laporan dari CEO Danantara Rosan Perkasa Roeslani yang juga menjabat Menteri Investasi dan Hilirisasi/Kepala Badan Koordinasi Penanaman Modal (BKPM) mengenai perkembangan terbaru pembangunan...</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjdl38490/cek-progres-kampung-haji-di-saudi-rosan-ungkap-danantara-ditawari-investasi-bandara-madinah</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/060396500-1784253244-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Pemerintah Masih Rahasiakan Besaran Defisit APBN 2026, Makin Besar atau Kecil?</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:53:40 +0700</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA — Pemerintah masih merahasiakan besaran target defisit anggaran dalam Rancangan Anggaran Pendapatan dan Belanja Negara (RAPBN) 2027. Besaran defisit tersebut baru akan diumumkan Presiden Prabowo Subianto saat...</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjdjtg370/pemerintah-masih-rahasiakan-besaran-defisit-apbn-2026-makin-besar-atau-kecil</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/065092500-1785818145-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Otomotif</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Mitsubishi Fuso Perkuat Standar Karoseri untuk Tingkatkan Keselamatan Kendaraan Niaga</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 06:41:43 +0700</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Israr Itah</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, TANGERANG -- PT Krama Yudha Tiga Berlian Motors (KTB) memperkuat standardisasi pembangunan karoseri kendaraan niaga sebagai bagian dari upaya meningkatkan aspek keselamatan dan kualitas kendaraan yang digunakan di berbagai...</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjdghj348/mitsubishi-fuso-perkuat-standar-karoseri-untuk-tingkatkan-keselamatan-kendaraan-niaga</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/perwakilan-perusahaan-karoseri-penerima-sertifikasi-dari-pt-krama-yudha_260807064025-864.jpg</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Timsus Kejagung Periksa Febrie Adriansyah Soal TPPU Hari Ini</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:58:46 +0700</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Kapuspenkum Kejagung Anang Supriatna mengaku belum mengetahui lokasi pemeriksaan Febrie. Lokasi pemeriksaan Febrie itu bergantung tim sembilan.</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263973/timsus-kejagung-periksa-febrie-adriansyah-soal-tppu-hari-ini</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/A02PfRJ2y22nBz-jXAXGn_wIYFI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9306887/original/065864800_1784913814-jam8.jpg</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Isi Pesan Terakhir Tersangka Mutilasi di Depok, Sempat Minta Maaf ke Bos</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:47:36 +0700</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Percakapan terakhir pelaku itu diungkap bos umkm tempat tersangka bekerja sebelum ditangkap polisi.</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263966/isi-pesan-terakhir-tersangka-mutilasi-di-depok-sempat-minta-maaf-ke-bos</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/jk0mg0oz_NYTomVposjWMV7bOa4=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317152/original/097817700_1786004215-email-attachment_2026_08_06_dicky-agung-prihanto_polisi-lakukan-pencarian-potongan-tubuh-korban-mutilasi-disepanjang-kali-licin-depok_IMG-20260806-WA0016.jpg</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Pendaftaran Upacara HUT ke-81 RI di Istana Merdeka Tembus 128.331</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:23:43 +0700</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Kuota pendaftaran upacara HUT ke-81 RI hari pertama ludes, registrasi kembali dibuka pada hari berikutnya.</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263963/pendaftaran-upacara-hut-ke-81-ri-di-istana-merdeka-tembus-128331</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/xd05yL1gtFEzgEEMh1AEfsGlgYk=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5318121/original/001265800_1755424797-WhatsApp_Image_2025-08-17_at_13.20.59_dea7c4b9.jpg</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Situasi Terkini Sekolah di Jaksel Usai Temuan 995 Senpi</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:52:28 +0700</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Tak ada penjagaan khusus meski polisi masih menyelidiki temuan di sekolah.</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263950/situasi-terkini-sekolah-di-jaksel-usai-temuan-995-senpi</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/olx8bnfoyQ106ljJRWcgY6uIXEg=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317703/original/035554900_1786063935-IMG_20260807_065229_814.jpg</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Tak Cukup Minta Maaf, Sanksi Menanti Para Nakes Nirempati</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:10:20 +0700</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Kasus yang viral di media sosial itu memicu gelombang kritik terhadap profesionalisme pelayanan kesehatan.</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263933/tak-cukup-minta-maaf-sanksi-menanti-para-nakes-nirempati</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/IiOsgxGbLOMN1ZXS3TxNv_P2qTk=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9315744/original/019758300_1785885131-yurizal.webp</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Tekno</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Temuan Baru AI "Kabur" dari Lab dan Retas Hugging Face, Kronologinya di Luar Dugaan</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:04:53 +0700</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Menurut OpenAI, agen AI buatannya membuat semacam 'forum' sendiri untuk berbagi celah keamanan, kredensial login, hingga membagi tugas satu sama lain.</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://tekno.kompas.com/read/2026/08/07/09020027/temuan-baru-ai-kabur-dari-lab-dan-retas-hugging-face-kronologinya-di-luar</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/Kpca2iLM5ciYQpZAqr3rjd0BsC4=/0x0:1080x720/1200x675/filters:watermark(data/photo/2026/01/30/697c816a7af9e.png,0,-0,1)/data/photo/2025/09/17/68caa77f3eabb.png</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Mobil Perwira Polisi Tabrak Balita hingga Tewas di Bone Sulsel, Ini Penyebabnya</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:04:53 +0700</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Polres Bone ungkap dugaan penyebab mobil perwira polisi menabrak balita hingga tewas.</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/07/084959278/mobil-perwira-polisi-tabrak-balita-hingga-tewas-di-bone-sulsel-ini</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/e0vduDi0DHLOT7FDQyitYA3XA88=/120x80:1080x720/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/07/07/6a4c439d0a060.jpg</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Dugaan Penyelewengan Bansos PKH, Kejari Wonosobo Geledah Dinsos dan Dua Rumah Saksi</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:04:53 +0700</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Dugaan penyelewengan bansos PKH di Wonosobo, Kejari geledah Dinsos dan dua rumah saksi. Kartu ATM penerima manfaat diduga dikuasai.</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/07/083441678/dugaan-penyelewengan-bansos-pkh-kejari-wonosobo-geledah-dinsos-dan-dua</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/_4Bnb-8BJB3SuIgTYt9Az9FxLlI=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/07/6a752251297bc.jpg</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I86"/>
+  <autoFilter ref="A1:I165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-07.xlsx
+++ b/data/berita_2026-08-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$370</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I165"/>
+  <dimension ref="A1:I370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -8188,8 +8188,9643 @@
         </is>
       </c>
     </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Pemkot Jaktim sosialisasi penataan ruang demi wujudkan kota tertib</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:20:24 +0700</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota (Pemkot) Jakarta Timur (Jaktim) menggencarkan sosialisasi perencanaan penataan ruang, informasi rencana ...</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683737/pemkot-jaktim-sosialisasi-penataan-ruang-demi-wujudkan-kota-tertib</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/InShot_20260807_110916885.jpg</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Manchester United umumkan rekap transfer sementara 2026</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:18:55 +0700</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Klub peringkat ketiga Liga Inggris 2025/2026, Manchester United (MU), mengumumkan rekap transfer sementara mereka pada ...</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683736/manchester-united-umumkan-rekap-transfer-sementara-2026</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/14/media_114048746_113657801_compressed.jpg</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>PBB: Revisi UU Pemilu momentum hadirkan pemilu yang lebih baik</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:18:13 +0700</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Penjabat Ketua Umum Dewan Pimpinan Pusat Partai Bulan Bintang (PBB) Yuri Kemal Fadlullah menegaskan revisi ...</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683732/pbb-revisi-uu-pemilu-momentum-hadirkan-pemilu-yang-lebih-baik</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000581793.jpg</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Investigasi SSRN, Kemdiktisaintek: Para penulis tak pernah terlibat</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:17:57 +0700</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Kementerian Pendidikan Tinggi, Sains, dan Teknologi (Kemdiktisaintek) mengungkapkan bahwa sejumlah pihak yang ...</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683729/investigasi-ssrn-kemdiktisaintek-para-penulis-tak-pernah-terlibat</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/WhatsApp-Image-2026-07-27-at-20.44.49-1.jpeg</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>BI: Cadangan devisa akhir Juli stabil sebesar 145,3 miliar dolar AS</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:14:16 +0700</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Bank Indonesia (BI) melaporkan posisi cadangan devisa Indonesia pada akhir Juli 2026 sebesar 145,3 miliar dolar AS ...</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683725/bi-cadangan-devisa-akhir-juli-stabil-sebesar-1453-miliar-dolar-as</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/06/29/antarafoto-dolar-melemah-tipis-230622-adm-5.jpg</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Wamenkomdigi ungkap urgensi tata kelola hadapi AI yang makin dinamis</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:09:58 +0700</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Komunikasi dan Digital (Wamenkomdigi) Nezar Patria mengungkapkan pentingnya menciptakan tata kelola yang ...</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683721/wamenkomdigi-ungkap-urgensi-tata-kelola-hadapi-ai-yang-makin-dinamis</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG-20260806-WA0084.jpg</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Kejagung limpahkan enam tersangka kasus Petral ke Kejari Jakarta Pusat</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:08:33 +0700</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Kejaksaan Agung melimpahkan enam tersangka dan barang bukti kasus dugaan korupsi tata kelola minyak mentah dan produk ...</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683717/kejagung-limpahkan-enam-tersangka-kasus-petral-ke-kejari-jakarta-pusat</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000087383.jpg</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Kanadevia Inova Mengadakan Perjanjian Konsesi untuk Pembangkit Listrik Tenaga Sampah Pertamanya di Afrika</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:05:56 +0700</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>- Kanadevia Inova AG (Swiss; selanjutnya disebut “Inova”), suatu anak perusahaan yang sepenuhnya dimiliki ...</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683715/kanadevia-inova-mengadakan-perjanjian-konsesi-untuk-pembangkit-listrik-tenaga-sampah-pertamanya-di-afrika</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-10.54.44.jpeg</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Warga lansia di China main gim untuk pererat hubungan sosial</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:01:17 +0700</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Bagi Zhou Zhihong (67), ajakan bermain dari cucu perempuannya yang berusia 14 tahun terdengar tak biasa. Usai ...</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683711/warga-lansia-di-china-main-gim-untuk-pererat-hubungan-sosial</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/CjkinzN000026_20260806_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>DPR desak aparat usut tuntas temuan ratusan senjata api di sekolah</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:00:46 +0700</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Anggota Komisi I DPR RI TB Hasanuddin meminta aparat penegak hukum mengusut tuntas kasus temuan 995 pucuk senjata api, ...</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683709/dpr-desak-aparat-usut-tuntas-temuan-ratusan-senjata-api-di-sekolah</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/1001014922.jpg</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Irak laporkan 313 kasus demam berdarah Krimea-Kongo, 24 meninggal</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:00:34 +0700</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Dalam rekapitulasi mingguan terbaru, Irak melaporkan 14 kasus terkonfirmasi demam berdarah Krimea-Kongo dengan ...</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683707/irak-laporkan-313-kasus-demam-berdarah-krimea-kongo-24-meninggal</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/28/1001052311.jpg</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>PSIM boyong striker asal Paraguay Mauro Caballero</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:00:24 +0700</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>PSIM Yogyakarta resmi memboyong striker baru asal Paraguay bernama Mauro Caballero untuk mempertajam lini serang tim di ...</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683705/psim-boyong-striker-asal-paraguay-mauro-caballero</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_7466.jpeg</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Perkuat ketahanan pangan, Pemkot Jaktim panen 10 ton padi</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:58:23 +0700</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota (Pemkot) Jakarta Timur (Jaktim) memanen padi varietas Ciherang di Kawasan Urban Farming Bali Lestari, ...</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683703/perkuat-ketahanan-pangan-pemkot-jaktim-panen-10-ton-padi</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/InShot_20260807_104031141.jpg</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Wakil Ketua DPR minta pekerja migran Lombok tetap tempuh jalur resmi</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:53:56 +0700</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Dewan Perwakilan Rakyat (DPR) RI Hj Sari Yuliati meminta pekerja migran Indonesia (PMI) di wilayah Lombok, ...</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683699/wakil-ketua-dpr-minta-pekerja-migran-lombok-tetap-tempuh-jalur-resmi</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1005741723.jpg</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>KSP siap kawal penyelesaian RUU Pembinaan Ideologi Pancasila</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:51:40 +0700</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Kantor Staf Presiden (KSP) siap memberikan dukungan penuh terhadap langkah Badan Pembinaan Ideologi Pancasila (BPIP) ...</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683696/ksp-siap-kawal-penyelesaian-ruu-pembinaan-ideologi-pancasila</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/20f41d54-92f7-4e69-872b-68f68b419dd6.jpeg</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Persiapan Bandara Husein Sastranegara Bandung jelang pengoperasian 14 Agustus mendatang</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:49:45 +0700</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Petugas membersihkan kaca ruang tunggu di Bandara Husein Sastranegara, Bandung, Jawa Barat, Jumat (7/8/2025). PT. ...</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5683695/persiapan-bandara-husein-sastranegara-bandung-jelang-pengoperasian-14-agustus-mendatang</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Persiapan-Bandara-Husein-Sastranegara-Jelang-Pengoperasian-070826-rai-3.jpg</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>PBB kecam sanksi AS terhadap Kuba</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:45:18 +0700</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Sejumlah pakar di Perserikatan Bangsa-Bangsa (PBB) mengecam sanksi yang dijatuhkan Amerika Serikat terhadap Kuba dan ...</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683691/pbb-kecam-sanksi-as-terhadap-kuba</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/20/thumbs_b_c_e79bec0669c6a009c1fb0d83f4f0f2eb.jpg</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Brimob Polda Metro Jaya sita motor saat bubarkan balap liar di Jaktim</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:44:07 +0700</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Brimob Polda Metro Jaya bersama Tim Perintis Presisi Polres Metro Jakarta Timur menyita sembilan unit sepeda motor saat ...</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683687/brimob-polda-metro-jaya-sita-motor-saat-bubarkan-balap-liar-di-jaktim</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG-20260807-WA0005_1.jpg</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Asal-usul senjata di sekolah swasta Jaksel terungkap, diklaim untuk ekskul menembak</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:44:05 +0700</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Ratusan senjata di sekolah swasta kawasan Pondok Pinang, Kebayoran Lama, Jakarta Selatan terungkap untuk ...</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683684/asal-usul-senjata-di-sekolah-swasta-jaksel-terungkap-diklaim-untuk-ekskul-menembak</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001015950.jpg</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Rupiah diprediksi menguat seiring fundamental ekonomi RI tetap terjaga</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:43:19 +0700</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Research and Development Indonesia Commodity &amp; Derivatives Exchange (ICDX) Muhammad Amru Syifa memperkirakan rupiah ...</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683683/rupiah-diprediksi-menguat-seiring-fundamental-ekonomi-ri-tetap-terjaga</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/08/20/rupiah.jpg</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>RI-Korea bangun Indonesia Forest and Land Fire Management Center</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:41:06 +0700</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Indonesia dan Korea Selatan memperkuat kerja sama dalam pengendalian kebakaran hutan dan lahan (karhutla) melalui ...</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683680/ri-korea-bangun-indonesia-forest-and-land-fire-management-center</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/a869abe5-d08d-4a46-9419-3f894705062d.jpeg</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Mengantar kepergian Cak Sholeh; Keadilan tak boleh menunggu viral</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:39:46 +0700</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>Tidak semua orang meninggalkan warisan berupa gedung, jabatan, atau kekayaan. Ada yang dikenang karena sebuah kalimat ...</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683679/mengantar-kepergian-cak-sholeh-keadilan-tak-boleh-menunggu-viral</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-09.35.49.jpeg</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Harga emas tiga jenama di Pegadaian pada Jumat serempak turun</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:38:49 +0700</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>Harga emas di laman Pegadaian, yang dikutip di Jakarta, Jumat, pukul 10.32 WIB, menunjukkan harga emas jenama Galeri24, ...</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683677/harga-emas-tiga-jenama-di-pegadaian-pada-jumat-serempak-turun</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/03/inflasi-kalimantan-tengah-mei-2026-2798829.jpg</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Kemnaker sesuaikan aturan ketenagakerjaan hadapi dinamika dunia kerja</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:35:48 +0700</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>Kementerian Ketenagakerjaan (Kemnaker) menyesuaikan regulasi ketenagakerjaan agar mampu menjawab dinamika dunia ...</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683675/kemnaker-sesuaikan-aturan-ketenagakerjaan-hadapi-dinamika-dunia-kerja</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/5e740592-0118-417d-8980-4bc396b08671.jpeg</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>KSP ajak masyarakat jaga persatuan dan stabilitas nasional</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:32:19 +0700</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>Kepala Staf Kepresidenan Jenderal TNI (Purn.) Dudung Abdurachman menyampaikan pesan kebangsaan yang mengajak seluruh ...</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683673/ksp-ajak-masyarakat-jaga-persatuan-dan-stabilitas-nasional</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_0984.jpeg</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Menhut pastikan negara hadir untuk mencegah karhutla</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:27:37 +0700</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>Menteri Kehutanan (Menhut) Raja Juli Antoni menegaskan Presiden Prabowo Subianto menginstruksikan seluruh jajaran ...</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683671/menhut-pastikan-negara-hadir-untuk-mencegah-karhutla</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/9b7ed762-7343-4ff4-9a55-3a1455f1b400.jpeg</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Bapanas tegaskan produsen wajib penuhi klaim gizi beras fortifikasi</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:27:30 +0700</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Badan Pangan Nasional (Bapanas) menegaskan produsen beras fortifikasi wajib memastikan kandungan gizi sesuai klaim pada ...</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683667/bapanas-tegaskan-produsen-wajib-penuhi-klaim-gizi-beras-fortifikasi</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/C4C16A0B-DAC2-4259-89A3-113CEF3AACB7.jpeg</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Cahaya di Pulau Dudepo di Hari Kemerdekaan</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:26:34 +0700</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Mungkin tidak ada yang menyangka kalau Dudepo itu sebenarnya adalah nama satu pohon yang daunnya sering dimasak sebagai ...</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683665/cahaya-di-pulau-dudepo-di-hari-kemerdekaan</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/784505.jpg</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>KP2MI jajaki peluang penempatan pekerja migran terampil ke Ceko</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:24:38 +0700</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Pelindungan Pekerja Migran Indonesia (P2MI) Christina Aryani menjajaki peluang perluasan penempatan ...</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683664/kp2mi-jajaki-peluang-penempatan-pekerja-migran-terampil-ke-ceko</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000678861.jpg</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Nasabah Mekaar studi banding gratis, PNM buka jalan inovasi usaha ultra mikro</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:21:08 +0700</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA) – Melalui pendekatan pemberdayaan yang berkelanjutan, PT Permodalan Nasional Madani (Persero) ...</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683660/nasabah-mekaar-studi-banding-gratis-pnm-buka-jalan-inovasi-usaha-ultra-mikro</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-09.30.07.jpeg</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Menko Pangan: MBG diprioritaskan untuk ibu hamil-balita dan daerah 3T</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:21:02 +0700</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Menteri Koordinator Bidang Pangan Zulkifli Hasan (Zulhas) mengatakan pemerintah melakukan penajaman sasaran program ...</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683659/menko-pangan-mbg-diprioritaskan-untuk-ibu-hamil-balita-dan-daerah-3t</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/C68C1E6C-32A6-4310-82E9-29A2BE83E4DF.jpeg</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Huawei Jadi Mitra bagi Ajang GSMA M360 ASEAN 2026</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:11:50 +0700</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>Huawei berpartisipasi sebagai Mitra dalam ajang M360 ASEAN 2026 yang berlangsung di Kuala Lumpur, Malaysia, ...</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683657/huawei-jadi-mitra-bagi-ajang-gsma-m360-asean-2026</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Huawei-GSMA-M360-ASEAN.jpg</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>KBPBI betkomitmen kawal RUU Ketenagakerjaan perjuangkan hak pekerja</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:06:31 +0700</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Koalisi Besar Perjuangan Buruh Indonesia (KBPBI) menyatakan tetap berkomitmen mengawal pembahasan Rancangan ...</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683653/kbpbi-betkomitmen-kawal-ruu-ketenagakerjaan-perjuangkan-hak-pekerja</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-06-at-7.15.28-PM_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Cision Raih MarTech Breakthrough Awards 2026 untuk Pemantauan dan Analisis Media Sosial, Distribusi Siaran Pers, dan AEO</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:05:56 +0700</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Cision, pemimpin global dalam kecerdasan konsumen dan media, hari ini mengumumkan bahwakedua mereknya, ...</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683649/cision-raih-martech-breakthrough-awards-2026-untuk-pemantauan-dan-analisis-media-sosial-distribusi-siaran-pers-dan-aeo</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/MarTech-Breakthrough-Awards.jpg</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>AS sebut jalur sementara Hormuz tak akan dipungut biaya</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:04:09 +0700</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Pemerintah Amerika Serikat menyatakan setiap jalur pelayaran sementara di Selat Hormuz akan dibuka tanpa ...</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683648/as-sebut-jalur-sementara-hormuz-tak-akan-dipungut-biaya</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/1001014481.jpg</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>DiCaprio-Jeff Bezos himpun dana buat pulihkan spesies terancam punah</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:03:30 +0700</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Yayasan milik Leonardo DiCaprio yakni Re:wild bersama Yayasan milik Jeff Bezos yakni Bezos Earth Fund meluncurkan ...</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683644/dicaprio-jeff-bezos-himpun-dana-buat-pulihkan-spesies-terancam-punah</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/24/Leonardo.jpg</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Shueisha Perluas Jangkauan Global melalui MANGA MILLION, Platform Manga yang Tersedia dalam 100 Bahasa</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:58:04 +0700</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Shueisha Inc., salah satu penerbit manga terkemuka di dunia, hari ini mengumumkan peluncuran MANGA MILLION, platform ...</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683640/shueisha-perluas-jangkauan-global-melalui-manga-million-platform-manga-yang-tersedia-dalam-100-bahasa</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/MANGA-MILLION-KV.jpg</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>KBRI Beijing hadirkan festival kuliner Indonesia</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:55:31 +0700</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Kedutaan Besar Republik Indonesia (KBRI) Beijing menyelenggarakan acara Indonesian Culinary Festival yang ...</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683637/kbri-beijing-hadirkan-festival-kuliner-indonesia</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-06-at-8.21.48-PM.jpeg</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>IHSG menguat di tengah investor cermati sentimen global dan domestik</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:55:25 +0700</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Jumat bergerak menguat di tengah pelaku pasar ...</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683633/ihsg-menguat-di-tengah-investor-cermati-sentimen-global-dan-domestik</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/18/ihsg-ditutup-turun-488-persen-ke-level-7.92273-2720490.jpg</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Fair Finance Asia Desak Perbankan Hentikan Pendanaan untuk Sektor Batu Bara di ASEAN</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:46:51 +0700</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Fair Finance Asia (FFA) bersama Influencing Just Energy Transition in ASEAN (I-JET) mendesak perbankan dan investor ...</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683629/fair-finance-asia-desak-perbankan-hentikan-pendanaan-untuk-sektor-batu-bara-di-asean</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Fair-Finance-Asia.jpg</t>
+        </is>
+      </c>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>DPR minta polisi ungkap bandar di balik peredaran 46 juta pil koplo</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:44:22 +0700</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi III DPR RI Ahmad Sahroni meminta aparat penegak hukum mengusut tuntas jaringan peredaran pil koplo ...</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683627/dpr-minta-polisi-ungkap-bandar-di-balik-peredaran-46-juta-pil-koplo</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000084060.jpg</t>
+        </is>
+      </c>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>AS pantau medsos pemohon visa bisnis dan jurnalis asal Meksiko, Kanada</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:41:35 +0700</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Departemen Luar Negeri (Deplu) Amerika Serikat akan menerapkan peraturan untuk memeriksa akun media sosial milik ...</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683625/as-pantau-medsos-pemohon-visa-bisnis-dan-jurnalis-asal-meksiko-kanada</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/03/23/2021-01-20T140129Z_1525162880_RC2PBL911UCD_RTRMADP_3_USA-BIDEN-INAUGURATION.jpg</t>
+        </is>
+      </c>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Menaker: Penguatan kompetensi penting guna jawab kebutuhan dunia kerja</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:40:25 +0700</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>Menteri Ketenagakerjaan (Menaker) Yassierli menegaskan penguatan kompetensi lulusan perguruan tinggi menjadi bagian ...</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683624/menaker-penguatan-kompetensi-penting-guna-jawab-kebutuhan-dunia-kerja</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/kuliah-umum-menaker-di-universitas-muhammadiyah-kendari-2834817.jpg</t>
+        </is>
+      </c>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Kemenhub audit sistem manajemen keselamatan pascainsiden KMP Mutiara</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:39:07 +0700</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan (Kemenhub) segera mengaudit sistem manajemen keselamatan operator KMP Mutiara Sentosa II ...</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683623/kemenhub-audit-sistem-manajemen-keselamatan-pascainsiden-kmp-mutiara</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/51036762-3110-49E0-8782-E633AE63E8BA.jpeg</t>
+        </is>
+      </c>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>SUS ENVIRONMENT Raih Dua Proyek WtE di Indonesia, Percepat Ekspansi Global</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:39:06 +0700</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>SUS ENVIRONMENT (SUS Indonesia Holding Limited) terpilih sebagai mitra untuk mengembangkan dua proyek Pengolahan ...</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683620/sus-environment-raih-dua-proyek-wte-di-indonesia-percepat-ekspansi-global</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/01/23/sus.jpg</t>
+        </is>
+      </c>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Haier Gandeng AO 1 Point Slam, Buka Peluang bagi Petenis Komunitas Tampil di Ajang Grand Slam</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:37:10 +0700</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Haier, merek peralatan rumah tangga nomor satu di dunia, resmi berkolaborasi dengan AO 1 Point Slam, program tenis ...</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683616/haier-gandeng-ao-1-point-slam-buka-peluang-bagi-petenis-komunitas-tampil-di-ajang-grand-slam</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/01/26/Logo-cision.jpg</t>
+        </is>
+      </c>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya gagalkan peredaran 3,4 kilogram ganja ke Jakarta</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:37:08 +0700</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>Direktorat Reserse Narkoba Polda Metro Jaya kembali menggagalkan upaya distribusi narkotika jenis ganja seberat 3,4 ...</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683612/polda-metro-jaya-gagalkan-peredaran-34-kilogram-ganja-ke-jakarta</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000755848.jpg</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>BP Tapera prediksi peminat rumah subsidi semester II pekerja swasta</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:34:50 +0700</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Badan Pengelola Tabungan Perumahan Rakyat (BP Tapera) memprediksikan peminat terbesar rumah subsidi pada semester II ...</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683608/bp-tapera-prediksi-peminat-rumah-subsidi-semester-ii-pekerja-swasta</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-09.22.35.jpeg</t>
+        </is>
+      </c>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>KuCoin Pay Perluas Pemanfaatan Stablecoin melalui Solusi Gift Card untuk Pelaku Usaha</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:34:38 +0700</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>KuCoin Pay, layanan pembayaran berbasis aset kripto milik KuCoin, meluncurkan KuCoin Gift Card, solusi distribusi aset ...</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683607/kucoin-pay-perluas-pemanfaatan-stablecoin-melalui-solusi-gift-card-untuk-pelaku-usaha</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/KuCoin-Gift-Card.jpg</t>
+        </is>
+      </c>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Jumat ini harga emas Antam turun Rp29.000 ke angka Rp2,650 juta/gr</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:31:28 +0700</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Harga emas Antam, yang dipantau dari laman Logam Mulia, di Jakarta, Jumat pukul 09.11 WIB turun Rp29.000 menjadi ...</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683603/jumat-ini-harga-emas-antam-turun-rp29000-ke-angka-rp2650-juta-gr</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/harga-emas-antam-turun-2829983.jpg</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Raja Felipe VI akan kunjungi Ceuta di tengah krisis migrasi</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:21:01 +0700</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Raja Spanyol Felipe VI akan melakukan kunjungan resmi ke Ceuta setelah krisis migrasi terjadi di kota ...</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683583/raja-felipe-vi-akan-kunjungi-ceuta-di-tengah-krisis-migrasi</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/AA-20260728-42087980-42087979-PRESIDENTELECT_KEIKO_FUJIMORI_ARRIVES_AHEAD_OF_SWEARINGIN_CEREMONY.jpg</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>IHSG Jumat dibuka menguat 8,67 poin ke posisi 6.352</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:18:56 +0700</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) Bursa Efek Indonesia (BEI) pada Jumat pagi dibuka menguat 8,67 poin atau 0,14 persen ...</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683581/ihsg-jumat-dibuka-menguat-867-poin-ke-posisi-6352</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/25/pembukaan-ihsg-usai-libur-lebaran-2760778.jpg</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Diduga Lecehkan Bocah Perempuan, Pegawai Wi-Fi di Bogor Nyaris Diamuk Massa</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:21:42 +0700</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>M Solihin</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>Seorang pegawai Wi-Fi di Bogor Barat hampir diamuk warga karena diduga melakukan pelecehan verbal terhadap anak. Kasus ini viral di media sosial.</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608198/diduga-lecehkan-bocah-perempuan-pegawai-wi-fi-di-bogor-nyaris-diamuk-massa</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/11/ilustrasi-pelecehan-dan-penelantaran-anak-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Polda Metro Tangkap 2 Kurir 3,4 Kg Ganja, Ada yang Masih Usia 15 Tahun</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:20:55 +0700</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>Direktorat Reserse Narkoba Polda Metro Jaya menggagalkan upaya peredaran narkotika jenis ganja yang dikirim dari Sumatera Utara menuju Jakarta.</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608196/polda-metro-tangkap-2-kurir-3-4-kg-ganja-ada-yang-masih-usia-15-tahun</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/polisi-tangkap-pengedar-ganja-di-tangerang-wildandetikcom-1786076316964_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Marbut di Purwakarta Tewas Dibacok Tetangga, Samurai dan Celurit Disita</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:13:13 +0700</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>Dian Firmansyah</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>Dia tewas dibacok tetangga sendiri saat hendak mengumandangkan azan. Polisi pun menyita celurit dan samurai yang dipakai pelaku.</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608179/marbut-di-purwakarta-tewas-dibacok-tetangga-samurai-dan-celurit-disita</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/pelaku-pembunuhan-marbot-masjid-di-purwakarta-1786073065642_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Bocah di Masjid Bone Ditendang Pria hingga Kepala Dijahit, Ibu Lapor Polisi</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:11:29 +0700</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>Tim detikSulsel</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>Bocah berinisial MAA (8) mengalami luka hingga kepalanya dijahit usai ditendang pria inisial SF di masjid di Kabupaten Bone, Sulawesi Selatan (Sulsel).</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608175/bocah-di-masjid-bone-ditendang-pria-hingga-kepala-dijahit-ibu-lapor-polisi</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/pria-di-bone-tendang-bocah-di-masjid-hingga-kepala-dijahit-1785998989641_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Baleg DPR Garap RUU Sistem Perbukuan, Soroti Fenomena Penerbit Gulung Tikar</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:57:18 +0700</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>Willy Aditya mengatakan RUU Sistem Perbukuan akan segera dibahas di Baleg DPR. Willy menilai regulasi itu penting untuk memperbaiki ekosistem literasi nasional.</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608146/baleg-dpr-garap-ruu-sistem-perbukuan-soroti-fenomena-penerbit-gulung-tikar</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/08/28/anggota-mpr-ri-willy-aditya-1756360486103_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Hari Kedua, Polisi Lanjut Cari Kaki Korban Mutilasi di Kali Licin Depok</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:56:36 +0700</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>Tim Subdit Resmob Ditreskrimum Polda Metro Jaya kembali melakukan penyisiran di Kali Licin, Cipayung, Depok, untuk mencari potongan kaki K (51).</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608145/hari-kedua-polisi-lanjut-cari-kaki-korban-mutilasi-di-kali-licin-depok</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/polisi-lanjut-cari-potongan-kaki-korban-mutilasi-di-kali-licin-depok-devidetikcom-1786074971703_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Detik-detik Maling Kabel di Jakut Kesetrum: Terpental hingga Diseret Warga</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:56:20 +0700</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>Seorang pria berinisial SD tersengat listrik saat mencoba mencuri kabel di gardu PLN, mengalami luka bakar 70% dan dirawat intensif di RS Polri.</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608144/detik-detik-maling-kabel-di-jakut-kesetrum-terpental-hingga-diseret-warga</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/maling-kabel-listrik-di-gardu-pln-sunter-agung-jakut-kesetrum-hingga-badan-melepuh-1786074935209_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Ini Penyebab Tanggul Laut Rembes hingga Bikin Becek Jalan Muara Baru</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:45:19 +0700</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>Tanggul laut di Muara Baru, Penjaringan, Jakut rembes hingga membuat jalan becek. Tanggul itu rembes akibat tekanan air laut serta penurunan permukaan tanah.</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608126/ini-penyebab-tanggul-laut-rembes-hingga-bikin-becek-jalan-muara-baru</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/05/tanggul-muara-baru-yang-bocor-mulai-ditambal-taufiqdetikcom-1764921981327_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Waka Komisi X DPR: Pencatutan Nama di Paper 'Nobel MBG' Pelanggaran Serius</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:42:59 +0700</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi X DPR Lalu Hadrian mengatakan pencatutan nama dalam paper terkait MBG tersebut sebagai pelanggaran serius.</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608117/waka-komisi-x-dpr-pencatutan-nama-di-paper-nobel-mbg-pelanggaran-serius</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/05/11/lalu-hadrian-irfani-1778488546595_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Dirjen SDA KemenPU Miris Sungai Cibanten Penuh Sampah: Dulu Bersih Sekali</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:41:55 +0700</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>Dirjen SDA KemenPU, Arnold Ritiauw, menyoroti kondisi Sungai Cibanten yang kini dipenuhi sampah. Ia dorong Gerakan Irigasi Bersih untuk kesehatan masyarakat.</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608115/dirjen-sda-kemenpu-miris-sungai-cibanten-penuh-sampah-dulu-bersih-sekali</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/dirjen-sda-kementerian-pu-arnold-aristoteles-paplapna-ritiauw-saat-membuka-acara-gerakan-irigasi-bersih-di-sungai-cibanten-kot-1786073966278_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Eks Sekda Konawe Selatan Pakai Pelat Palsu Saat Digerebek Bareng Selingkuhan</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:41:00 +0700</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Nadhir Attamimi</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>Pelaku ternyata menggunakan mobil kendaraan dinas Pemkab Konsel serta pelat palsu pada kendaraannya tersebut.</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608113/eks-sekda-konawe-selatan-pakai-pelat-palsu-saat-digerebek-bareng-selingkuhan</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/mobil-dinas-pemkab-konsel-dipakai-mantan-sekda-1786070622434_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Awas Keliru, Ini Penulisan HUT ke-81 RI yang Benar</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:34:27 +0700</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Kanya Anindita Mutiarasari</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>Pelajari penulisan yang benar untuk HUT ke-81 RI. Temukan aturan dan contoh ucapan yang tepat untuk merayakan kemerdekaan Indonesia pada 17 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608102/awas-keliru-ini-penulisan-hut-ke-81-ri-yang-benar</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/ilustrasi-upacara-hut-ri-di-istana-1785898929673_169.webp?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Kera Ekor Panjang Serbu Rumah Warga Inhil, 18 Warga Jadi Korban</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:34:18 +0700</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>Kera ekor panjang menyerang permukiman di Tembilahan, Riau, melukai 18 warga. Pemerintah setempat meningkatkan kewaspadaan dan penanganan.</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608101/kera-ekor-panjang-serbu-rumah-warga-inhil-18-warga-jadi-korban</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/10/05/kera-ekor-panjang-di-kabupaten-gunungkidul-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>BMKG: Gempa Dangkal M 3,5 di Bogor Dipicu Sesar Aktif</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:23:42 +0700</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Wilda Hayatun Nufus</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>Gempa bumi dengan magnitudo (M) 3,5 terjadi di Bogor, Jawa Barat, dini hari tadi. BMKG menyebut gempa Bogor terjadi akibat aktivitas sesar aktif.</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608083/bmkg-gempa-dangkal-m-3-5-di-bogor-dipicu-sesar-aktif</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/08/ilustrasi-gempa-1780909642348_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Bupati Bogor Minta SPPG Ciherang Disetop Sementara Usai Dugaan Keracunan MBG</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:07:49 +0700</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>Bupati Bogor Rudy Susmanto meminta pengoperasian SPPG di Desa Ciherang, Bogor, disetop sementara setelah 25 orang diduga keracunan usai menyantap MBG.</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608065/bupati-bogor-minta-sppg-ciherang-disetop-sementara-usai-dugaan-keracunan-mbg</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/15/bupati-bogor-rudy-susmanto-1768460853421_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Bos Konter HP Ambarawa Tewas di Bagasi Mobil, Diduga Korban Perampokan</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:06:40 +0700</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Ardian Dwi Kurnia</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>Polisi memastikan mayat pria yang ditemukan di dalam bagasi mobil di Gubug, Grobogan, adalah bos konter telepon seluler. Korban diduga tewas karena dirampok.</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608064/bos-konter-hp-ambarawa-tewas-di-bagasi-mobil-diduga-korban-perampokan</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/konter-hp-di-ambarawa-1786026181459_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Pihak Eks Ketua Yayasan Buka Suara soal Ratusan Senjata di Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:02:59 +0700</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>PT Lokta Karya Perbakin mengonfirmasi ratusan airsoft gun yang ditemukan di sekolah di Jakarta Selatan adalah milik mereka dan berizin resmi.</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608060/pihak-eks-ketua-yayasan-buka-suara-soal-ratusan-senjata-di-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temuan-ratusan-pucuk-senjata-di-sekolah-swasta-di-pondok-pinang-jakarta-selatan-1786014363566_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Pria di Jakut Alami Luka Bakar 70% Usai Tersengat Listrik Saat Mau Curi Kabel</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:01:21 +0700</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>Pria berinisial SD (25) tersengat listrik saat hendak mencuri kabel di gardu PLN di Jalan Agung Karya, Kelurahan Sunter Agung, Kecamatan Tanjung Priok, Jakut.</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608056/pria-di-jakut-alami-luka-bakar-70-usai-tersengat-listrik-saat-mau-curi-kabel</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/05/07/tangan-tersengat-listrik-1746608472561_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Ketua Komisi III DPR Desak Polda Sumut Usut Tuntas Meninggalnya WL Eks Istri Polisi</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:47:24 +0700</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Wilda Hayatun Nufus</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>Ketua Komisi III DPR Habiburokhman mendesak Polda Sumatera Utara mengusut tuntas meninggalnya WL, mantan istri polisi di Sumatera Utara.</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608047/ketua-komisi-iii-dpr-desak-polda-sumut-usut-tuntas-meninggalnya-wl-eks-istri-polisi</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/27/komisi-iii-dpr-terima-469-aduan-sepanjang-2024-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Kebakaran Bromo Makin Meluas hingga 120 Hektare, Heli Water Bombing Disiapkan</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:30:41 +0700</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Muhammad Aminudin</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>Kebakaran yang melanda kawasan kaldera Bromo terus meluas. Hingga kini, area yang terdampak kobaran api diperkirakan telah mencapai sekitar 120 hektare.</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608028/kebakaran-bromo-makin-meluas-hingga-120-hektare-heli-water-bombing-disiapkan</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kebakaran-di-gunung-bromo-1786068097105_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>MenPAN-RB Sebut Kolaborasi Kunci Mewujudkan Layanan Publik Terintegrasi</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:23:34 +0700</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>Menteri Rini Widyantini menekankan pentingnya kolaborasi dalam transformasi digital untuk layanan publik yang inklusif, aman, dan terintegrasi.</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608019/menpan-rb-sebut-kolaborasi-kunci-mewujudkan-layanan-publik-terintegrasi</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/menpan-rb-sebut-kolaborasi-kunci-mewujudkan-layanan-publik-terintegrasi-1786069395773.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Menko Pangan Tegaskan MBG Diprioritaskan untuk Ibu Hamil, Balita, &amp;amp; Daerah 3T</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:20:44 +0700</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Mega Putra Ratya</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>Pemerintah fokus pada Program Makan Bergizi Gratis untuk ibu hamil, menyusui, dan balita. Penajaman sasaran dan pengawasan ketat untuk manfaat maksimal.</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608016/menko-pangan-tegaskan-mbg-diprioritaskan-untuk-ibu-hamil-balita-daerah-3t</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/menteri-koordinator-bidang-pangan-zulkifli-hasan-1786068803843.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Alun-alun Suryakencana Gunung Gede Sempat Terbakar, Kini Api Padam</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:14:25 +0700</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Ikbal Selamet</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda Alun-alun Suryakencana, Gunung Gede Pangrango, Cianjur. Pemadaman melibatkan relawan dan warga, api bisa dipadamkan setelah 3 jam.</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608011/alun-alun-suryakencana-gunung-gede-sempat-terbakar-kini-api-padam</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/gunung-gede-pangrango-kebakaran-1786025219821_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Dirgakkum Korlantas: Informasi Viral Belum Tentu Fakta, Jangan Mudah Percaya Hoaks</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:09:06 +0700</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Herianto Batubara</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>Dirgakkum Korlantas Polri Korlantas Polri Brigjen I Made Agus Prasatya mengingatkan jajaran penegakan hukum untuk waspada terhadap hoaks di era post-truth.</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8607991/dirgakkum-korlantas-informasi-viral-belum-tentu-fakta-jangan-mudah-percaya-hoaks</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/dirgakkum-korlantas-polri-brigjen-i-made-agus-prasatya-1786068462632_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>274 BUMN Sudah Dipangkas, Target Akhir Tinggal 250 Perusahaan</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:23:56 +0700</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>Sebanyak 274 BUMN telah dipangkas dalam program transformasi untuk efisiensi. Targetnya, 652 perusahaan disederhanakan, menyisakan 250 BUMN.</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8608200/274-bumn-sudah-dipangkas-target-akhir-tinggal-250-perusahaan</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/16/ilustrasi-kantor-danantara-1784212600266_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Cadangan Devisa RI Turun Tipis Jadi US$ 145,3 Miliar</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:02:16 +0700</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>Bank Indonesia (BI) mencatat posisi cadangan devisa Indonesia pada akhir Juli 2026 tetap terjaga sebesar US$ 145,3 miliar.</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8608150/cadangan-devisa-ri-turun-tipis-jadi-us-145-3-miliar</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/10/29/ilustrasi-bank-indonesia-6_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Makin Banyak Orang RI Kerja Paruh Waktu, Kini Tembus 38,41 Juta</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:39:23 +0700</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>BPS mencatat jumlah pekerja di Indonesia mencapai 148,19 juta pada Mei 2026, dengan 66,80% di antaranya bekerja penuh. Pengangguran turun menjadi 7,22 juta.</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8608109/makin-banyak-orang-ri-kerja-paruh-waktu-kini-tembus-38-41-juta</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/10/24/kelakuan-kocak-netizen-saat-pesan-makanan-via-ojol-ini-bikin-ngakak-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Semen Kujang Dijual Lagi, Bidik Pasar Jawa Barat</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:32:31 +0700</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>PT Semen Indonesia (Persero) Tbk (SIG) menghadirkan kembali merek legendaris yang sempat menjadi ikon industri semen di Jawa Barat, Semen Kujang.</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/industri/d-8608097/semen-kujang-dijual-lagi-bidik-pasar-jawa-barat</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/sig-hidupkan-lagi-merek-semen-kujang-bidik-pasar-jawa-barat-1786073500869_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Konglomerat China Panik! Pajak Baru Bikin Taipan Ramai-ramai Jual Aset</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:29:22 +0700</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Pemerintah China mulai mengenakan pajak 20% pada aset dalam trust offshore, memicu kepanikan di kalangan konglomerat yang berlomba menghitung kewajiban pajak.</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8608093/konglomerat-china-panik-pajak-baru-bikin-taipan-ramai-ramai-jual-aset</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/01/04/jelang-libur-imlek-china-desak-warganya-tidak-mudik-6_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Pemerintah Bidik Pajak dari Rumah Kontrakan Tahun Depan</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:24:30 +0700</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Kementerian Keuangan (Kemenkeu) akan memperluas basis perpajakan pada 2027 untuk meningkatkan penerimaan negara.</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8608084/pemerintah-bidik-pajak-dari-rumah-kontrakan-tahun-depan</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/31/ilustrasi-rumah-1767168982348_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Dolar AS Masih Betah di Level Rp 17.900</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:53:48 +0700</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>Nilai tukar dolar Amerika Serikat (AS) menguat terhadap rupiah pada pembukaan perdagangan hari ini. Mata uang Paman Sam betah di level Rp 17.900.</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8608051/dolar-as-masih-betah-di-level-rp-17-900</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/10/rupiah-masih-tertekan-dolar-as-betah-di-level-rp18000-1783662450657_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Terminal LPG Tanjung Sekong Pertamina Raih Sertifikasi Terminal Hijau</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:38:26 +0700</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Terminal LPG Tanjung Sekong menjadi yang pertama di dunia meraih Green Terminal Label bintang 2. Pertamina berkomitmen pada keberlanjutan dan transisi energi.</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/ekonomi-hijau/d-8608037/terminal-lpg-tanjung-sekong-pertamina-raih-sertifikasi-terminal-hijau</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/terminal-lpg-tanjung-sekong-banten-1786070292539_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Harga Emas Antam Hari Ini Ambruk!</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:29:34 +0700</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Harga emas Antam hari ini turun Rp 29.000 per gram menjadi Rp 2.650.000. Rincian harga untuk berbagai ukuran juga disajikan. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8608027/harga-emas-antam-hari-ini-ambruk</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/11/13/harga-emas-hari-ini-1763003232311_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Zulhas Minta KDKMP Malut Perkuat Hilirisasi Sektor Perikanan dan Perkebunan</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:23:58 +0700</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Rahmat Khairurizqi</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Menko Pangan Zulkifli Hasan dorong Koperasi Desa Merah Putih di Maluku Utara untuk hilirisasi perikanan dan perkebunan, tingkatkan nilai tambah komoditas lokal.</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8608020/zulhas-minta-kdkmp-malut-perkuat-hilirisasi-sektor-perikanan-dan-perkebunan</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/zulhas-dan-sherly-tjoanda-1786069403181_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Traktor Listrik Mulai Dipakai Petani di Bali, Pengolahan Lahan Lebih Cepat</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:22:55 +0700</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>Petani di Subak Sembung, Denpasar, kini menggunakan traktor listrik dari Pertamina untuk efisiensi pertanian. Bantuan ini mendukung pengolahan lahan dan biaya.</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8608081/traktor-listrik-mulai-dipakai-petani-di-bali-pengolahan-lahan-lebih-cepat</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/petani-1786072967685_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>IHSG Dibuka Menguat ke 6.352 Jelang Akhir Pekan</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:22:40 +0700</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) pagi ini kembali dibuka menguat. IHSG langsung meroket ke zona hijau saat pembukaan di level 6.300-an.</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8608018/ihsg-dibuka-menguat-ke-6-352-jelang-akhir-pekan</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/11/19/ihsg-ditutup-menguat-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Menko Pangan Nilai KNMP Jadi Motor Ekonomi Baru bagi Nelayan Makassar</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:01:25 +0700</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Mega Putra Ratya</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Pemerintah percepat transformasi ekonomi pesisir melalui Kampung Nelayan Merah Putih, menciptakan pusat pertumbuhan dan meningkatkan kesejahteraan nelayan.</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8607984/menko-pangan-nilai-knmp-jadi-motor-ekonomi-baru-bagi-nelayan-makassar</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/menko-pangan-nilai-knmp-jadi-motor-ekonomi-baru-bagi-nelayan-makassar-1786068056961.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Sulap Sampah Jadi Cuan, Wayang Botol Bekas Ini Tembus Pasar Nasional</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:00:33 +0700</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Rengga Sancaya</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>Botol plastik bekas di Yogyakarta disulap menjadi wayang upcycle bernilai seni tinggi. Ramah lingkungan, karya ini sukses menembus pasar nasional.</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8607214/sulap-sampah-jadi-cuan-wayang-botol-bekas-ini-tembus-pasar-nasional</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/sulap-sampah-jadi-cuan-wayang-botol-bekas-ini-tembus-pasar-nasional-1786007721771_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Randy Pangalila Kalungi 3 Medali Silver Kejuaraan Renang, Definisi Artis Atlet</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:06:39 +0700</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Randy Pangalila kembali menunjukkan prestasinya di bidang olahraga. Kali ini, dia mengikuti GBK Fun Swimm 2026 dan meraih 3 medali silver.</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608000/randy-pangalila-kalungi-3-medali-silver-kejuaraan-renang-definisi-artis-atlet</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/randy-pangalila-1786068239344_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Melly Lee Berduka</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:30:30 +0700</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Kabar duka datang dari penyanyi Melly Lee. Juara 1 D'Academy Asia 6 itu ditinggal ayah untuk selamanya.</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608085/melly-lee-berduka</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/melly-lee-1786073021869_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Saksi Dinilai Berbelit, Richard Lee Sebut Banyak Kebohongan di Sidang</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:10:58 +0700</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Persidangan kasus Richard Lee di Tangerang berlanjut. Kuasa hukum temukan kejanggalan saksi dan bukti alibi yang menguntungkan kliennya.</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608029/saksi-dinilai-berbelit-richard-lee-sebut-banyak-kebohongan-di-sidang</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/02/richard-lee-1782969208992_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Kemampuan Mengaji Indra Priawan, Suami Nikita Willy Disebut Bukan Kaleng-kaleng</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:14:49 +0700</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>Indra Priawan yang gak lain suami Nikita Willy mendapatkan sorotan. Kemampuan mengajinya disebut bukan kaleng-kaleng.</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8607999/kemampuan-mengaji-indra-priawan-suami-nikita-willy-disebut-bukan-kaleng-kaleng</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/indra-priawan-1786068660512_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Komentar Raisa di Unggahan Mathis Molinie Bikin Heboh</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:09:33 +0700</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>Penyanyi Raisa, bikin heboh usai memberikan komentar dalam unggahan Tiktok chef asal Prancis, Mathis Molinie.</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8607887/komentar-raisa-di-unggahan-mathis-molinie-bikin-heboh</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/raisa-1786060869113_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Momen Ghea Indrawari Nyanyi Bareng Perdana Menteri Thailand di Istana Negara</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:05:51 +0700</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>wes</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>Penyanyi Ghea Indrawari mengaku bangga nyanyi bareng Perdana Menteri Thailand, Anutin Charnvirakul, di Istana Negara.</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606841/momen-ghea-indrawari-nyanyi-bareng-perdana-menteri-thailand-di-istana-negara</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/ghea-indrawari-1785992569228_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Cadangan Devisa RI Turun Tipis Jadi US$145,3 M per Akhir Juli 2026</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:13:13 +0700</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>Bank Indonesia mencatat posisi cadangan devisa RI per akhir Juli 2026 sebesar US$145,3 miliar, turun tipis dibandingkan posisi akhir Juni 2026, US$145,6 miliar.</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807110759-78-1389638/cadangan-devisa-ri-turun-tipis-jadi-us-1453-m-per-akhir-juli-2026</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2020/06/02/c10ab6bf-3457-4b33-9f9a-4ba5a4adb2ac_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Terminal LPG Pertamina Kantongi Sertifikasi Hijau Pertama di Dunia</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:11:25 +0700</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>Pertamina raih Green Terminal Label Certification bintang 2 pertama di dunia untuk Terminal LPG Tanjung Sekong, dukung energi berkelanjutan.</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807092540-625-1389590/terminal-lpg-pertamina-kantongi-sertifikasi-hijau-pertama-di-dunia</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/pertamina-1786068024160_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Kemenhub Audit Sistem Manajemen Keselamatan usai Kebakaran KMP Mutiara</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:45:18 +0700</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>Kementerian Perhubungan (Kemenhub) segera mengaudit sistem manajemen keselamatan operator KMP Mutiara Sentosa II.</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807103424-92-1389623/kemenhub-audit-sistem-manajemen-keselamatan-usai-kebakaran-kmp-mutiara</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/03/evakuasi-korban-kebakaran-km-mutiara-sentosa-ii-1785712804674_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Tembus 3,6 Juta Pengguna, 24% Nasabah Bank Jago Aktif Berinvestasi</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:40:54 +0700</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>Kolaborasi Bank Jago dengan Bibit dan Stockbit mendorong pertumbuhan investasi digital. Kini, 3,6 juta pengguna terhubung, dominasi saham 48,4 persen.</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807093429-78-1389593/tembus-36-juta-pengguna-24-nasabah-bank-jago-aktif-berinvestasi</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/07/23/ilustrasi-bank-jago-4_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>FOTO: El Nino Bawa Berkah, Produksi Garam Cirebon Tembus 600 Ton</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:05:28 +0700</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>Para petani garam di Provinsi Jawa Barat, Indonesia, menikmati keuntungan dari kekeringan yang dipicu fenomena El Nino.</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806095642-94-1389189/foto-el-nino-bawa-berkah-produksi-garam-cirebon-tembus-600-ton</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/panen-melimpah-petani-garam-efek-kemarau-el-nino-1785985490799_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Rupiah Dibuka Melemah Tipis ke Rp17.935 per Dolar AS</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:47:00 +0700</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah dibuka melemah 0,07 persen ke Rp17.935 per dolar AS pada perdagangan Jumat (7/8) pagi.</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807094134-78-1389596/rupiah-dibuka-melemah-tipis-ke-rp17935-per-dolar-as</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/12/24/kurs-rupiah-menguat-meski-bertengger-di-16-ribu-rupiah-6_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Harga Emas Antam Merosot Rp29 Ribu ke Rp2,650 Juta per Gram Pagi Ini</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:28:27 +0700</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Harga emas batangan produksi PT Aneka Tambang Tbk (Antam) turun ke Rp2,65 juta per gram pada perdagangan Jumat (7/8).</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807092023-92-1389588/harga-emas-antam-merosot-rp29-ribu-ke-rp2650-juta-per-gram-pagi-ini</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/01/07/kondisi-geopolitik-bikin-harga-emas-makin-bersinar-1767771424093_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Harga Minyak Dunia Naik ke US$83,48 per Barel</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:05:27 +0700</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Harga minyak dunia kembali menguat pada perdagangan Jumat (7/8), setelah muncul kekhawatiran baru terkait rencana pembukaan Selat Hormuz.</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807085833-85-1389583/harga-minyak-dunia-naik-ke-us-8348-per-barel</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/02/04/ilustrasi-kilang-minyak_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Pemerintah Bakal Gabung Insentif Rp20 M Kota Terbersih dengan Adipura</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:25:50 +0700</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Pemerintah akan integrasikan insentif Rp20 miliar untuk kota terbersih dengan program Adipura. Ini bertujuan mendukung pengelolaan kebersihan dan lingkungan.</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806113404-532-1389227/pemerintah-bakal-gabung-insentif-rp20-m-kota-terbersih-dengan-adipura</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2022/11/01/ilustrasi-mata-uang-rupiah-5_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Indonesia Penjajakan Bareng China-Rusia Garap Trans Kalimantan Railway</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:59:52 +0700</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Menteri Perhubungan Dudy Purwagandhi menyebut telah memulai penjajakan dengan investor asal China dan Rusia dalam membangun Trans Kalimantan Railway.</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807075400-92-1389572/indonesia-penjajakan-bareng-china-rusia-garap-trans-kalimantan-railway</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/04/28/menteri-perhubungan-dudy-purwagandhi-memantau-evakuasi-kecelakaan-krl-commuterline-dengan-ka-argo-bromo-anggrek-1777347266623_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>INFOGRAFIS: Data Ekonomi Terbaru RI Kuartal II 2026</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:25:34 +0700</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Badan Pusat Statistik (BPS) baru saja mengumumkan data perekonomian terbaru untuk Kuartal II 2026.</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807070834-535-1389550/infografis-data-ekonomi-terbaru-ri-kuartal-ii-2026</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/infografis-data-ekonomi-terbaru-ri-kuartal-ii-2026-1786058626362_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Kenapa Banyak Lulusan SMK Nganggur?</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 06:52:01 +0700</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Pengamat menilai tingginya pengangguran lulusan SMK mencerminkan persoalan struktural di pasar tenaga kerja Indonesia.</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807062735-92-1389538/kenapa-banyak-lulusan-smk-nganggur</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/05/19/bursa-kerja-upaya-menekan-laju-angka-pengangguran-1747633655678_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>BPS: Sawit hingga Kopi Jadi Andalan Ekspor RI ke Arab Saudi</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 06:25:34 +0700</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>BPS mengungkap minyak sawit, kopi, hingga produk kayu menjadi komoditas unggulan Indonesia yang memiliki pangsa pasar kuat di Arab Saudi.</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806133845-92-1389289/bps-sawit-hingga-kopi-jadi-andalan-ekspor-ri-ke-arab-saudi</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2022/08/28/ilustrasi-biji-kopi_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>IHSG Diproyeksi Cerah Jelang Akhir Pekan</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 06:16:12 +0700</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Indeks Harga Saham Gabungan (IHSG) diperkirakan menguat pada perdagangan Jumat (7/8).</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807061018-92-1389533/ihsg-diproyeksi-cerah-jelang-akhir-pekan</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2016/09/16/78f83416-b1e3-4ea0-9350-069be15789d3_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Airlangga Sebut 60 Persen Alumni Magang Nasional Direkrut Karyawan</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 04:30:46 +0700</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Menko Airlangga menyebut sebanyak 60 persen alumni program magang nasional berhasil direkrut kembali menjadi karyawan oleh perusahaan tempat mereka magang.</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260806102913-532-1389212/airlangga-sebut-60-persen-alumni-magang-nasional-direkrut-karyawan</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/03/31/konferensi-pers-tentang-kebijakan-pemerintah-dalam-mitigasi-risiko-dan-antisipasi-dinamika-global-1774959255627_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Digosipkan Cekcok soal Iran, Trump Ngaku Sangat Happy dengan Menhan AS</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat Donald Trump mengatakan dirinya "sangat bahagia" dengan Menteri Pertahanan Pete Hegseth pada Kamis (6/8).</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807092207-134-1389629/digosipkan-cekcok-soal-iran-trump-ngaku-sangat-happy-dengan-menhan-as</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/07/08/netanyahu-trump-rapat-rencana-jahat-mau-usir-warga-gaza-1751943457945_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Pulau Kecil Ini Berani Tantang AS Tolak Eksploitasi Laut Dalam</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Salah satu kepulauan kecil di Pasifik milik Amerika Serikat, Kepulauan Marina Utara, menolak rencana Washington yang ingin mengeksploitasi laut dalam mereka.</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806195334-113-1389479/pulau-kecil-ini-berani-tantang-as-tolak-eksploitasi-laut-dalam</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/07/21/bf416e30-ff90-42d3-b32c-d6e2c4dc2a6e_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Iran Sindir Gaya Diplomasi Trump Bak 'Aktor Teater'</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Iran menuduh Presiden Amerika Serikat Donald Trump bak aktor yang melakukan "diplomasi teater berulang-ulang".</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807081121-120-1389576/iran-sindir-gaya-diplomasi-trump-bak-aktor-teater</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/04/30/ketua-parlemen-iran-mohammad-bagher-ghalibaf-1777530561438_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Pria India Ditangkap usai Buka Paksa Pintu Darurat Pesawat di Udara</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Seorang pria India ditangkap usai diduga mencoba membuka pintu darurat pesawat Batik Air OD231 dalam penerbangan dari Kuala Lumpur ke Kochi India.</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807085907-113-1389584/pria-india-ditangkap-usai-buka-paksa-pintu-darurat-pesawat-di-udara</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/01/28/ilustrasi-cabin-pesawat-1769570838252_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Ratusan Warga di 27 Bagian AS Mencret-mencret Gegara Makan Jalapeno</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:15:41 +0700</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>AS selidiki sebaran wabah Salmonella penyebab diare 345 warga di 27 negara bagian, diduga gara-gara konsumsi jalapeno asal Meksiko.</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807071310-134-1389552/ratusan-warga-di-27-bagian-as-mencret-mencret-gegara-makan-jalapeno</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2017/08/29/8182eed9-e9fb-40bf-8254-1756dc91ef1a_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Trump Teken Aturan Batasi Kewarganegaraan Berdasarkan Tempat Kelahiran</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>Trump teken perintah eksekutif batasi pemberian kewarganegaraan berdasarkan tempat kelahiran.</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807063355-134-1389545/trump-teken-aturan-batasi-kewarganegaraan-berdasarkan-tempat-kelahiran</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/08/08/donald-trump-di-oval-office-1754653005688_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Trump Ngamuk soal Bocor Stok Amunisi AS, Akui Ada Pasokan yang Menipis</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>Presiden AS Donald Trump dilaporkan mengamuk soal kebocoran informasi terkait stok amunisi, membantah Washington kekurangan pasokan  gegara perang melawan Iran.</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807071554-134-1389567/trump-ngamuk-soal-bocor-stok-amunisi-as-akui-ada-pasokan-yang-menipis</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/09/donald-trump-1783564606984_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Bos Mossad Israel Pecat 2 Pejabat Gegara Gagal Gulingkan Rezim Iran</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>Kepala badan intelijen Mossad Israel, Roman Gofman, memecat dua pejabat senior lembaga tersebut menyusul kegagalan rencana untuk menggulingkan pemerintahan Iran</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807064656-120-1389546/bos-mossad-israel-pecat-2-pejabat-gegara-gagal-gulingkan-rezim-iran</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/05/10/mojtaba-khamenei-1778379361297_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Trump: Saya Lebih Pilih Bersepakat dengan Iran daripada Membunuh</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat Donald Trump menyatakan ia lebih memilih mencapai kesepakatan dengan Iran daripada mengambil langkah militer dan membunuh.</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807063021-134-1389542/trump-saya-lebih-pilih-bersepakat-dengan-iran-daripada-membunuh</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/09/donald-trump-1783564606904_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Susunan Upacara Hari Pramuka 2026 Lengkap dari Awal sampai Akhir</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:07:37 +0700</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>Inilah susunan upacara Hari Pramuka 2026 lengkap dari awal sampai akhir yang jatuh pada Jumat, 14 Agustus 2026 sebagai referensi.</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865141/susunan-upacara-hari-pramuka-2026-lengkap-dari-awal-sampai-akhir</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/iO-LWYoS7Ckq9P62uo37sEXUIUU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Peringatan-hari-pramuka.jpg</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Konsil Kesehatan Indonesia Selidiki Perundungan Pasien, Pegawai RS di Tasikmalaya Mengundurkan Diri</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:06:46 +0700</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>Konsil Kesehatan Indonesia selidiki perundungan nakes terhadap pasien BPJS yang viral di media sosial setelah korban meninggal dunia.</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865140/konsil-kesehatan-indonesia-selidiki-perundungan-pasien-pegawai-rs-di-tasikmalaya-mengundurkan-diri</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/aGrIOKQltBbKHE_h49x38Xaczhg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Perundungan-Pasien-BPJS.jpg</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Mengapa Biaya Kepemilikan Lebih Penting daripada Harga Mobil? Berikut Penjelasannya</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:03:23 +0700</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>VinFast memanfaatkan ajang GIIAS 2026 untuk mengubah cara pandang masyarakat terhadap kendaraan listrik.</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/otomotif/7865139/mengapa-biaya-kepemilikan-lebih-penting-daripada-harga-mobil-berikut-penjelasannya</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/2ecl_gZdPAB_v3dxayVcVl655Jw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Liputan-VinFast-GIIAS-2907202.jpg</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Isi Doa Lesti Kejora untuk Ruben Onsu yang Tengah Konflik dengan Sarwendah</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:59:36 +0700</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>Ruben Onsu tengah berkonflik dengan Ruben, Lesti Kejora nampak ikut beri doa terbaik.</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865138/isi-doa-lesti-kejora-untuk-ruben-onsu-yang-tengah-konflik-dengan-sarwendah</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/mswu3JMtpd8DCkded6DfYgvxH7I=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Lesti-Kejora-ASI.jpg</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Demi Dalami Karakter Melodi di Film Operasi Pesta Copet, Kawai Labiba Rutin Datangi Festival Musik</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:59:11 +0700</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>Aktris Kawai Labiba ngaku rutin datangi festival musik demi dalami karakter Melodi dalam film Operasi Pesta Copet.</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865137/demi-dalami-karakter-melodi-di-film-operasi-pesta-copet-kawai-labiba-rutin-datangi-festival-musik</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/0IwwLaCAMZD1vnN-uWFtmecN5gI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Kawai-Labiba.jpg</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Dari Lampung hingga NTT: Apakah Safari Politik Jokowi Mampu Mendongkrak PSI?</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:57:22 +0700</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>Safari politik Jokowi bersama PSI di Lampung dan NTT diuji: karisma pasca-presiden tak otomatis berbuah suara elektoral.</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/tribunners/7865136/dari-lampung-hingga-ntt-apakah-safari-politik-jokowi-mampu-mendongkrak-psi</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/RSk9JN-9JdvEb7CpYzKzisldsoI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/jokowi-safari-politik-di-kupang-ntt.jpg</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Isu 'Agustus Kelabu' Diduga Sengaja Dihembuskan Guna Ciptakan Kepanikan Publik</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:56:46 +0700</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>Evident Institute menemukan indikasi isu "Agustus Kelabu" di media sosial didorong secara terkoordinasi untuk memicu kepanikan publik</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865135/isu-agustus-kelabu-diduga-sengaja-dihembuskan-guna-ciptakan-kepanikan-publik</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/WWOAv1mLhQ9viocyCo4aBqE3uPk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/dr-algooth-putranto-1.jpg</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Terduga Pencuri Kabel Tersengat Listrik di Sunter, Alami Luka Bakar 70 Persen</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:56:27 +0700</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>Seorang pria berinisial SD (25) mengalami luka bakar akibat tersengat listrik saat diduga hendak mencuri kabel gardu.</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7865134/terduga-pencuri-kabel-tersengat-listrik-di-sunter-alami-luka-bakar-70-persen</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/UPqCkQzSO1Ty69W5EtgdkfDaCYQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ng-Kecamatan-Tanjung-Priok-Jak.jpg</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>iPhone 18 Pro Dikabarkan Terancam Langka, Krisis DRAM Hambat Produksi Apple</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:54:03 +0700</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>Laporan terbaru menyebut produksi iPhone 18 Pro terhambat akibat kelangkaan memori DRAM.</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/techno/7865133/iphone-18-pro-dikabarkan-terancam-langka-krisis-dram-hambat-produksi-apple</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/EkaKJmACYZLOgeDv2PpgKh8CKQ4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Apple-terbaru-iPhone-18-Pro.jpg</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>5 Kasus Oknum Polisi Terjerat Narkoba di 2026: Jadi Beking hingga Tersangka Kepemilikan Sabu-Ekstasi</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:50:33 +0700</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>Ada oknum polisi yang turut ditangkap terkait dugaan peredaran gelap narkotika, ada yang diduga membekingi kampung narkoba.</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865132/5-kasus-oknum-polisi-terjerat-narkoba-di-2026-jadi-beking-hingga-tersangka-kepemilikan-sabu-ekstasi</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/JcvH2nwSB1Z6Wu8sY2maAE0sJtw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Bripka-Dedy-Wiratama-1.jpg</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Tema dan Logo Hari Pramuka 2026, Dilengkapi Link Download</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:49:07 +0700</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>Inilah tema dan logo peringatan Hari Pramuka yang jatuh pada Jumat, 14 Agustus 2026, dilengkapi link download.</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865131/tema-dan-logo-hari-pramuka-2026-dilengkapi-link-download</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Anbh98FNk4CAGrKXCe1buHCDKaU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Logo-Hari-Pramuka-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Daftar 4 Kabareskrim yang Jadi Kapolri, Ada Sutarman hingga Idham Azis</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:47:16 +0700</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>Berikut ini adalah daftar 4 mantan Kabareskrim Polri yang berhasil menjadi Kepala Kepolisian Negara Republik Indonesia atau Kapolri.</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865130/daftar-4-kabareskrim-yang-jadi-kapolri-ada-sutarman-hingga-idham-azis</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/9ttWprNPwERtKBCtTy1tJbXVYso=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kapolri-umumkan-irjen-ferdy-sambo-tersangka_20220809_201757.jpg</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Diduga Korban Pencurian dan Penculikan, Bos Konter HP Ambarawa Ditemukan Tewas di Grobogan</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:46:25 +0700</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>Pemilik usaha konter Royal Phone di Ambarawa ditemukan tewas di Grobogan. Diduga jadi korban pencurian dan penculikan.</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865129/diduga-korban-pencurian-dan-penculikan-bos-konter-hp-ambarawa-ditemukan-tewas-di-grobogan</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/uSFJBKkI99SpecMW9nKrYmjZaqs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Pembunuhan-bos-konter-Ambarawa.jpg</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Kapan Apple Umumkan iPhone 18 Pro? Ini Prediksi Jadwal Peluncurannya</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:45:15 +0700</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>Apple diperkirakan menggelar acara peluncuran iPhone 18 Pro pada 9 September 2026 dan mengumumkan tanggal resminya sekitar 26 Agustus.</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/techno/7865128/kapan-apple-umumkan-iphone-18-pro-ini-prediksi-jadwal-peluncurannya</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/6C8NF8PCo8MqAuHlP3Xq0bvsBaw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/TEKNOLOGI-Foto-ilustrasi-logo-Apple.jpg</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Sekda Ichsan Porosi Tersangka Usai Tabrak Adik, Siapa Pejabat Konsel yang Ajukan Restorative Justice</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:44:21 +0700</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>Pejabat di Konawe Selatan mengajukan permohonan Restorative Justice terkait kasus dugaan penganiayaan yang menjadikan Ichsan Porosi tersangka.</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865127/sekda-ichsan-porosi-tersangka-usai-tabrak-adik-siapa-pejabat-konsel-yang-ajukan-restorative-justice</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/sKNAfNlhuLC-vPAh2KE0q2US-gQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Kolase-Sekda-Konawe-Selatan-Ichsan-Porosi-Tersangka_1.jpg</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>995 Senjata Api dan Narkoba Ditemukan di Sekolah, Anggota DPR: Tak Sesuai Fungsi Sekolah</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:40:03 +0700</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>995 senpi beserta amunisi ditemukan tersimpan rapi di sebuah ruangan sekolah swasta di Pondok Pinang.</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7865126/995-senjata-api-dan-narkoba-ditemukan-di-sekolah-anggota-dpr-tak-sesuai-fungsi-sekolah</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/C0lT2Y0zI_MxSjs7s2qkRNylM8s=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Benda-berbentuk-senjata-yang-ditemukan-di-sebuah-ruangan-321.jpg</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Dinilai Gagal Jalankan Operasi Rahasia Israel, Bos Mossad Pecat Dua Pejabat Senior Terkait Misi Iran</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:38:23 +0700</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>Israel dikabarkan evaluasi besar-besaran di tubuh Mossad. Dua pejabat senior dipecat setelah misi intelijen terkait Iran diduga gagal dijalankan.</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7865125/dinilai-gagal-jalankan-operasi-rahasia-israel-bos-mossad-pecat-dua-pejabat-senior-terkait-misi-iran</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/KsQEV9SVlfZKspurjFvEyuqzTFE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-mossad-israel.jpg</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>AI Bukan Pengganti Guru, tapi Dinilai Jadi Alat Pendukung Pembelajaran di Sekolah</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:34:26 +0700</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>Pemanfaatan kecerdasan buatan (AI) dapat dimanfaatkan di dunia pendidikan, tapi perannya dinilai bukan menggantikan guru.</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865124/ai-bukan-pengganti-guru-tapi-dinilai-jadi-alat-pendukung-pembelajaran-di-sekolah</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/CGTY-WJIdOvSl0MJpTOIJNN-E1s=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ilustrasi-kecerdasan-buatan-atau-Artificial-Intelligence-AI-dalam-dunia-kerja.jpg</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Berkali-kali Gagal Seleksi PTN, Anak Pedagang Asal Jakarta Akhirnya Lolos UNY dengan Laptop Sewaan</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:32:10 +0700</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>Perjuangan Abimanyu, anak pedagang, lolos UNY meski harus menyewa laptop demi ikut ujian Seleksi Mandiri CBT Domisili.</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865123/berkali-kali-gagal-seleksi-ptn-anak-pedagang-asal-jakarta-akhirnya-lolos-uny-dengan-laptop-sewaan</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/D4JNe2u5sPCE17XeOR_CLl28Zzw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Muhammad-Abimanyu-Ramadhan-kanan-saat-berfoto-bersama-ibunya.jpg</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Cara Denny Sumargo Ajarkan Kesederhanaan ke Anaknya, Rayakan Ulang Tahun Tanpa Pesta Meriah</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:29:15 +0700</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>Sukses di panggung hiburan namun Denny Sumargo menerapkan hidup mewah pada anak dan istrinya.</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865122/cara-denny-sumargo-ajarkan-kesederhanaan-ke-anaknya-rayakan-ulang-tahun-tanpa-pesta-meriah</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/-H5KCOgZbRXFSqtubnZCGd5nBOE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/olivia-allan-dan-denny-sumargo.jpg</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Prabowo Pesan Sepatu Karet Lokal Buatan BRIN, Harganya Tak Terduga</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:20:11 +0700</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto memesan sepatu sekolah berbahan karet lokal dari BRIN. Ini sebagai dukungan terhadap riset dan inovasi dalam negeri.</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807103857-4-757351/prabowo-pesan-sepatu-karet-lokal-buatan-brin-harganya-tak-terduga</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/pertemuan-presiden-ri-dengan-150-periset-dari-badan-riset-dan-inovasi-nasional-6-agustus-2026-1786004780568_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>BRIN Kembangkan Teknologi ANG Pengganti LPG, RI Bisa Hemat Rp26 T</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:10:00 +0700</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>BRIN sedang mengembangkan teknologi ANG pengganti LPG, RI bisa hemat subsidi Rp26 triliun</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807104625-4-757357/brin-kembangkan-teknologi-ang-pengganti-lpg-ri-bisa-hemat-rp26-t</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/prabowo-panggil-pimpinan-brin-bahas-riset-program-prioritas-1786069775435_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Duduk Perkara Utang Whoosh Hingga Akhirnya Dibereskan Purbaya</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:05:33 +0700</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa memastikan bahwa Kementerian Keuangan akan mengambil alih utang Kereta Cepat Jakarta-Bandung.</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807104333-4-757356/duduk-perkara-utang-whoosh-hingga-akhirnya-dibereskan-purbaya</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/03/menteri-keuangan-purbaya-yudhi-sadewa-saat-konferensi-pers-hasil-rapat-berskla-kssk-iii-tahun-2016-di-jakarta-senin-382026-1785748274051_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Pemerintah Genjot Investasi dan Pariwisata Demi Pertumbuhan Ekonomi</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>Pemerintah akan memfokuskan penguatan investasi dan sektor pariwisata pada kuartal tiga 2026.</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807093606-8-757325/pemerintah-genjot-investasi-pariwisata-demi-pertumbuhan-ekonomi</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/pemerintah-genjot-investasi-pariwisata-demi-pertumbuhan-ekonomi-1786071042461_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Berubah Total! Penampakan Terbaru Lembah Anai Bak di Luar Negeri</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>Jalur Lembah Anai dan Malalak di Sumatra Barat kembali beroperasi usai penanganan longsor dan banjir rampung. Penampakannya tak terduga.</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806121255-7-757074/berubah-total-penampakan-terbaru-lembah-anai-bak-di-luar-negeri</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/jalur-lembah-anai-resmi-dibuka-untuk-seluruh-jenis-kendaraan-mulai-senin-277-setelah-sebelumnya-mobilitas-di-kawasan-tersebut--1785993169886_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Permintaan Susu Melonjak, Industri Pengolahan Susu Segar Tumbuh 17,3%</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:45:41 +0700</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>Permintaan susu pada kuartal II 2026 meningkat tajam. Kenaikan ini ikut mendorong lonjakan pertumbuhan industrinya.</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807093941-8-757328/permintaan-susu-melonjak-industri-pengolahan-susu-segar-tumbuh-173</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/permintaan-susu-melonjak-industri-pengolahan-susu-segar-tumbuh-173-1786070439262_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Proyek 100 Giga Watt PLTS Tahap Awal Bakal Diresmikan di Tol Bali</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>Peresmian PLTS 100 Giga Watt tahap awal akan diresmikan di Tol Bali</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807102333-4-757347/proyek-100-giga-watt-plts-tahap-awal-bakal-diresmikan-di-tol-bali</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/10/25/plts-tol-bali-mandara_169.mpo?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Genjot Penerimaan, Ditjen Pajak Bakal Sasar Pemilik Rumah Kontrakan</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:40:31 +0700</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>Perluasan basis perpajakan terus dilakukan oleh pemerintah guna menyasar kelompok wajib pajak yang dinilai belum memenuhi kewajiban secara optimal.</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807102231-4-757348/genjot-penerimaan-ditjen-pajak-bakal-sasar-pemilik-rumah-kontrakan</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2023/12/05/format-baru-pajak-karyawan-bakal-berlaku-di-2024_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Video: Industri Susu Jadi Bintang Baru Ekonomi RI</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:30:03 +0700</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>Terkait kinerja produksi susu nasional, langsung saja kita simak paparan dari Commodity Expert CNBC Indonesia Research</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807094103-8-757329/video-industri-susu-jadi-bintang-baru-ekonomi-ri</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/industri-susu-jadi-bintang-baru-ekonomi-ri-1786070528927_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Potret Kapal Dicegat Diduga Bawa Virus Mematikan, 300 Orang Diperiksa</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>Otoritas kesehatan Kongo memeriksa lebih dari 300 penumpang kapal usai seorang penumpang diduga meninggal akibat Ebola, untuk mencegah penyebaran wabah.</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807074426-7-757288/potret-kapal-dicegat-diduga-bawa-virus-mematikan-300-orang-diperiksa</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/para-penumpang-menunggu-pemeriksaan-di-atas-sebuah-kapal-setelah-otoritas-kesehatan-mencegat-kapal-tersebut-menyusul-kematian--1786063460667_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Video:Prabowo Akan Serahkan Nama Calon Gubernur BI Sebelum Akhir Pekan</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:20:31 +0700</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>Prabowo akan mengajukan nama calon Gubernur BI baru kepada Dewan Perwakilan Rakyat RI sebelum akhir pekan ini.</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807093327-8-757319/videoprabowo-akan-serahkan-nama-calon-gubernur-bi-sebelum-akhir-pekan</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/prabowo-akan-serahkan-nama-calon-gubernur-bi-sebelum-akhir-pekan-1786070336637_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Penuhi 100 Giga Watt, RI Akan Bangun PLTS di Sepanjang Jalan Tol</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>Pemerintah mengkaji pembangunan PLTS 100 Giga Watt (GW) di sepanjang jalan tol</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807094523-4-757332/penuhi-100-giga-watt-ri-akan-bangun-plts-di-sepanjang-jalan-tol</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/03/05/groundbreaking-plts-bali-mandara_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Tuntas! Ekspor Nikel-Timah Cs Imbas LTJ Resmi Dibuka Lagi Hari Ini</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>Ekspor mineral yakni nikel hingga timah cs resmi dibuka lagi</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807093101-4-757326/tuntas-ekspor-nikel-timah-cs-imbas-ltj-resmi-dibuka-lagi-hari-ini</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/06/12/area-penambangan-biji-nikel-pt-vale-indonesia-persero-tbk-inco-area-hasan-koro-tempat-stock-pile-limonite-igp-sorowako-limonit-1749726174463_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Video: Sejumlah Negara Kutuk Serangan Israel di Gaza</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:43:30 +0700</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>Para menteri luar negeri sejumlah negara mengecam apa yang mereka sebut sebagai pelanggaran berkelanjutan oleh Israel di Jalur Gaza.</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807092330-8-757315/video-sejumlah-negara-kutuk-serangan-israel-di-gaza</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/sejumlah-negara-kutuk-serangan-israel-di-gaza-1786069543962_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Video: Trump Bantah AS Kekurangan Amunisi Dalam Perang Iran</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:31:46 +0700</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>Trump membantah laporan yang menyebut militer AS mengalami kekurangan amunisi dalam konflik dengan Iran.</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807092146-8-757314/video-trump-bantah-as-kekurangan-amunisi-dalam-perang-iran</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/trump-bantah-as-kekurangan-amunisi-dalam-perang-iran-1786069390912_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Video: Iran Mengkaji RUU Perketat Pelayaran di Selat Hormuz</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:21:34 +0700</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>Parlemen Iran tengah membahas rancangan aturan baru yang akan memperketat pengendalian pelayaran di Selat Hormuz dan Teluk Persia.</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807091907-8-757313/video-iran-mengkaji-ruu-perketat-pelayaran-di-selat-hormuz</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/iran-mengkaji-ruu-perketat-pelayaran-di-selat-hormuz-1786069268091_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Genjot Hilirasasi, Negara Ini Setop Ekspor Konsentrat Tembaga dan Kobalt</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:15:11 +0700</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>Republik Demokratik Kongo melarang ekspor konsentrat tembaga dan kobalt untuk meningkatkan pemrosesan domestik. Harga tembaga melonjak</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807075758-4-757295/genjot-hilirasasi-negara-ini-setop-ekspor-konsentrat-tembaga-kobalt</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/seorang-pekerja-sedang-bekerja-di-fasilitas-konsentrator-tembaga-milik-perusahaan-pertambangan-negara-kongo-gecamines-di-lokas-1786069064462_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Ada 'Harta Karun Langka' Buat 'Nuklir' di RI, Segini Potensinya</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>BRIN menyampaikan Indonesia memiliki potensi 89.000 ton uranium untuk bahan baku pembangkit listrik tenaga nuklir</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807083101-4-757305/ada-harta-karun-langka-buat-nuklir-di-ri-segini-potensinya</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/06/29/uranium-dok-pixabay-1751201210729_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Pertama di Dunia, Terminal LPG Tanjung Sekong Raih Sertifikasi Hijau</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:56:27 +0700</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Pertamina raih Green Terminal Label Certification bintang 2 untuk Terminal LPG Tanjung Sekong, jadi yang pertama di dunia. Langkah penting menuju keberlanjutan.</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807085132-4-757307/pertama-di-dunia-terminal-lpg-tanjung-sekong-raih-sertifikasi-hijau</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/dok-pertamina-1786067716813_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Prabowo Minta BRIN Uji Penggunaan BBM Campur Etanol Hingga 100%</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Presiden RI Prabowo Subianto meminta BRIN mengkaji implementasi BBM campur etanol hingga 100%</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807082255-4-757302/prabowo-minta-brin-uji-penggunaan-bbm-campur-etanol-hingga-100</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/pertemuan-presiden-ri-dengan-150-periset-dari-badan-riset-dan-inovasi-nasional-6-agustus-2026-1786010089825_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>PNS dan PPPK Daerah Bernafas Lega, Gaji Ditransfer Purbaya Pekan Depan</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:15:56 +0700</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>ASN daerah akhirnya bisa bernafas lega setelah keputusan Menteri Keuangan Purbaya Yudhi Sadewa menambah anggaran Rp 20,5 triliun.</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807074356-4-757286/pns-pppk-daerah-bernafas-lega-gaji-ditransfer-purbaya-pekan-depan</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/03/menteri-keuangan-purbaya-yudhi-sadewa-saat-konferensi-pers-hasil-rapat-berskla-kssk-iii-tahun-2016-di-jakarta-senin-382026-1785746448068_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Resmi! Daftar Tarif Listrik PLN per kWh, Berlaku Juli-September 2026</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Daftar tarif listrik pelanggan PLN per kWh, berlaku Juli hingga September 2026</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807074417-4-757287/resmi-daftar-tarif-listrik-pln-per-kwh-berlaku-juli-september-2026</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/ilustrasi-petugas-pln-melakukan-pengecekan-kwh-meter-untuk-home-charging-kendaraan-listrik-meningkatnya-jumlah-pengguna-kendar-1786011138627_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Proyek Pertama Board of Peace di Gaza Siap Dibangun: Markas Militer</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Dewan Perdamaian AS menerbitkan kontrak pertama untuk pembangunan pos militer di Gaza, menandai langkah awal rekonstruksi setelah perang.</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807065015-4-757280/proyek-pertama-board-of-peace-di-gaza-siap-dibangun-markas-militer</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/03/26/seorang-pemuda-palestina-yang-mengungsi-berlindung-di-sebuah-kamp-tenda-pada-hari-hujan-di-kota-gaza-26-maret-2026-1774531955872_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Ada Retakan di Badan Pesawat, Ratusan Boeing 737 Max Kena Inspeksi</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>luc</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>FAA perintahkan inspeksi 471 pesawat Boeing 737 Max setelah ditemukan retakan pada struktur. Inspeksi wajib mulai 10 September untuk menjaga keselamatan.</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807063748-4-757277/ada-retakan-di-badan-pesawat-ratusan-boeing-737-max-kena-inspeksi</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2019/03/28/0b96c430-6a26-4866-a865-2ef25091e5d0_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Cek Iuran BPJS Kesehatan Kelas 1,2,3 Berlaku 7 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 06:55:56 +0700</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Peserta BPJS Kesehatan diwajibkan membayar iuran setiap bulan sesuai dengan kelas yang dipilih.</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807064356-4-757278/cek-iuran-bpjs-kesehatan-kelas-123-berlaku-7-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/08/22/bpjs-kesehatan-1755866819340_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Penampakan Danau Raksasa Mengering, Tanda Petaka Kian Nyata</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 06:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>Foto udara menujukkan menurunnya permukaan air di Danau Velence, Hungaria. Permukaan air di Danau diprediksi akan turun ke level terendah sepanjang masa.</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806191606-7-757255/penampakan-danau-raksasa-mengering-tanda-petaka-kian-nyata</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/foto-udara-menujukkan-menurunnya-permukaan-air-di-danau-velence-hungaria-kamis-682026-permukaan-air-di-danau-velence-diprediks-1786018517641_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Trump Membangkang dari Putusan Mahkamah Agung, Nekat Teken Aturan Baru</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 06:05:47 +0700</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>luc</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>Presiden Trump menandatangani perintah eksekutif baru untuk membatasi birthright citizenship dan praktik birth tourism.</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807060204-4-757275/trump-membangkang-dari-putusan-mahkamah-agung-nekat-teken-aturan-baru</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/09/06/trump-teken-perintah-eksekutif-ancam-negara-penahan-warga-as-1757153804587_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>AS Kehilangan Pegangan di Perang Iran, Trump Maju Kena-Mundur Kena</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 05:39:03 +0700</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>Presiden Trump menghadapi dilema sulit dalam konflik dengan Iran. Dua pilihan utama: kesepakatan sementara atau serangan lebih lanjut.</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807053601-4-757274/as-kehilangan-pegangan-di-perang-iran-trump-maju-kena-mundur-kena</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/02/presiden-as-donald-trump-reutersnathan-howard-1777683758032_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Momen Militer Mulai Bergerak, Siaga Invasi Negara Tetangga</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 05:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>Latihan militer terbesar Taiwan tahun ini dimulai seiring pulau itu berupaya mempersiapkan penduduknya untuk menghadapi kemungkinan invasi China.</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806174817-7-757235/momen-militer-mulai-bergerak-siaga-invasi-negara-tetangga</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/06/latihan-militer-terbesar-taiwan-tahun-ini-dimulai-pada-hari-rabu-582026-seiring-pulau-itu-berupaya-mempersiapkan-penduduknya-u-1786013238616_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Telkom (TLKM) Pangkas 34 Entitas Usaha, Bos Danantara Ungkap Ini</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:25:43 +0700</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>PT Telkom Indonesia (Persero) Tbk. (TLKM) akan mempercepat perampingan entitas usaha dengan memangkas 34 perusahaan.</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807104943-17-757359/telkom--tlkm--pangkas-34-entitas-usaha-bos-danantara-ungkap-ini</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/06/05/grapari-telkom-group-cnbc-indonesiafaisal-rahman-1749113200923_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Video: Harga Minyak Ambruk 5% - Harga Emas Tertekan Sentimen The Fed</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:15:01 +0700</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>Harga Minyak Dunia Ambruk 5% hingga Harga Emas Tertekan Sentimen The Fed</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807103920-19-757354/video-harga-minyak-ambruk-5--harga-emas-tertekan-sentimen-the-fed</t>
+        </is>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/harga-minyak-dunia-ambruk-5-hingga-harga-emas-tertekan-sentimen-the-fed-1786074938503_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Video: RUU Larangan Kapal AS dan Israel Lewat Hormuz - IHSG Lanjut Reli</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:52:30 +0700</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>RUU Larangan Kapal AS-Israel Lewat Selat Hormuz hingga IHSG Lanjutkan Reli</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807103910-19-757352/video-ruu-larangan-kapal-as-israel-lewat-hormuz--ihsg-lanjut-reli</t>
+        </is>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/ruu-larangan-kapal-as-israel-lewat-selat-hormuz-hingga-ihsg-lanjutkan-reli-1786074684031_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Harga Saham Meroket Ratusan Persen, BEI Pelototi Dua Emiten Ini</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:35:18 +0700</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>BEI memantau ketat pola pergerakan Unusual Market Activity (UMA) atas PT Citra Buana Prasida Tbk. (CBPE) dan PT Karya Pacific Energy Tbk. (IATA).</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807100618-17-757337/harga-saham-meroket-ratusan-persen-bei-pelototi-dua-emiten-ini</t>
+        </is>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019885_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>BI: Cadangan Devisa RI Turun Tipis ke US$145,3 M Akhir Juli 2026</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:21:02 +0700</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>Bank Indonesia (BI) melaporkan cadangan devisa Indonesia pada akhir Juli 2026 sebesar US$145,3 miliar.</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807101632-17-757338/bi-cadangan-devisa-ri-turun-tipis-ke-us-1453-m-akhir-juli-2026</t>
+        </is>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/07/04/ilustrasi-dolar-amerika-serikat-as-1_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Seminggu Melesat 124,8%, BEI Auto Gembok Saham BAJA</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:20:59 +0700</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>Romys Binekasri</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>Bursa Efek Indonesia (BEI) menghentikan sementara perdagangan (suspensi) saham PT Saranacentral Bajatama Tbk (BAJA).</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807095359-17-757335/seminggu-melesat-1248-bei-auto-gembok-saham-baja</t>
+        </is>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2021/08/13/dok-saranacentral-bajatama_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Video: IHSG Dibuka Menguat hingga Rupiah Bertahan di Rp 17.900/USD</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:06:56 +0700</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>IHSG Dibuka Menguat hingga Rupiah Pertahankan Level Rp 17.900 per Dolar AS</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807095545-19-757336/video-ihsg-dibuka-menguat-hingga-rupiah-bertahan-di-rp-17900-usd</t>
+        </is>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/ihsg-dibuka-menguat-hingga-rupiah-pertahankan-level-rp-17900-per-dolar-as-1786071899371_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Penjualan Naik, Rugi SIPD Malah Bengkak 240,67%, Ini Penyebabnya</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:05:07 +0700</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>Emiten produsen olahan ayam, PT Sreeya Sewu Indonesia Tbk (SIPD) kembali mengemas rugi bersih di semester I-2026.</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807094655-17-757331/penjualan-naik-rugi-sipd-malah-bengkak-24067-ini-penyebabnya</t>
+        </is>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2020/06/17/doksieradproduce_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Digugat Mantan Direktur, Emiten RI Ini Balik Menggugat, Ini Alasannya</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:00:09 +0700</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>Emiten manufaktur bahan kimia, PT Duta Pertiwi Nusantara Tbk. (DPNS) menjelaskan aksi gugatan balik atau rekonvensi yang diajukannya terhadap mantan direktur.</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807094109-17-757330/digugat-mantan-direktur-emiten-ri-ini-balik-menggugat-ini-alasannya</t>
+        </is>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/07/21/pt-duta-pertiwi-nusantara-1753069534804_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Video; PDB RI Q2-2026 Lampaui Ekspektasi, IHSG Bertahan di Atas 6.300</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:58:40 +0700</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>Ekonomi RI Q2-2026 Tumbuh Lampaui Ekspektasi, IHSG Bertahan di Atas Level 6.300</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807091827-19-757312/video-pdb-ri-q2-2026-lampaui-ekspektasi-ihsg-bertahan-di-atas-6300</t>
+        </is>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/ekonomi-ri-q2-2026-tumbuh-lampaui-ekspektasi-ihsg-bertahan-di-atas-level-6300-1786071215045_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Saham MDIA Melesat 274% Sebulan, Emiten Ini Diam-Diam Ketiban Cuan</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:55:10 +0700</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>Saham emiten media, PT Intermedia Capital Tbk (MDIA) melonjak sekitar 274% dalam satu bulan terakhir, dan menjadi salah satu saham dengan penguatan tertinggi.</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807093108-17-757327/saham-mdia-melesat-274-sebulan-emiten-ini-diam-diam-ketiban-cuan</t>
+        </is>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2019/03/20/bfb3754e-3b5e-4974-ab36-c173cb47d48b_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Minyak Mulai Memanas, Brent Tembus US$83</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:30:01 +0700</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>Harga minyak dunia menguat seiring kekhawatiran di Selat Hormuz. Brent mencapai US$83,21 per barel, didorong ketegangan geopolitik dan rencana pungutan baru.</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807091311-17-757311/minyak-mulai-memanas-brent-tembus-us-83</t>
+        </is>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2018/02/09/531a9a76-df7c-4fd0-8bec-7c9741ea2cb0_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Ada Update Baru Soal Konsolidasi Asuransi BUMN</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:20:52 +0700</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>Asuransi Tugu Pratama Indonesia (TUGU) mengumumkan rencana konsolidasi asuransi BUMN. Proses masih dalam kajian, ditargetkan rampung pada September 2026.</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807085614-17-757308/ada-update-baru-soal-konsolidasi-asuransi-bumn</t>
+        </is>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/06/dok-tugu-insurance-1778063657513_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>Rupiah Dibuka Menguat Pagi Ini, Dolar AS Turun Tipis ke Rp17.905</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:04:29 +0700</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah kembali menguat terhadap dolar Amerika Serikat (AS) saat mengawali perdagangan terakhir pekan ini.</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807084420-17-757310/rupiah-dibuka-menguat-pagi-ini-dolar-as-turun-tipis-ke-rp17905</t>
+        </is>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/08/petugas-menjunjukkan-uang-pecahan-dolar-amerika-serikat-as-dan-rupiah-di-dolar-asia-money-changer-jakarta-rabu-872026-1783496342089_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Bursa RI Dibuka Positif, IHSG Bertahan di Atas 6.350</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:01:28 +0700</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>IHSG dibuka menguat di level 6.352,38 pada 7 Agustus 2026. Sentimen pasar beragam, dengan perhatian pada cadangan devisa dan wacana IPO BUMN.</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807083215-17-757306/bursa-ri-dibuka-positif-ihsg-bertahan-di-atas-6350</t>
+        </is>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/19/indeks-harga-saham-gabungan-ihsg-kembali-anjlok-signifikan-pada-perdagangan-hari-ini-selasa-1952026-1779182443779_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Rekomendasi Saham Hari Ini: DSSA, BKSL, hingga SMGR</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:50:48 +0700</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>Rekomendasi saham hari ini ada DSSA, BKSL, GTSI, CDIA, dan SMGR. Cek area antry dan target harganya.</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807082426-17-757301/rekomendasi-saham-hari-ini-dssa-bksl-hingga-smgr</t>
+        </is>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/market-1786065865-1786065866065_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Chandra Asri (TPIA) Tingkatkan Free Float Saham Jadi 25,7%</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:40:44 +0700</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>Romys Binekasri</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>Chandra Asri Pacific (TPIA) meningkatkan free float saham menjadi 25,7% untuk meningkatkan likuiditas dan akses investor, tanpa mengubah kendali perusahaan.</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807081643-17-757299/chandra-asri--tpia--tingkatkan-free-float-saham-jadi-257</t>
+        </is>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/19/ilustrasi-orang-berdoa-dengan-latar-belakang-bursa-saham-indonesia-di-bursa-efek-indonesia-jakarta-selasa-1952026-1779182674008_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Jelang Akhir Pekan, Bursa Asia Kompak Menguat</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:35:48 +0700</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>Pasar Asia-Pasifik menguat menjelang akhir pekan, dipicu harapan data perdagangan Tiongkok dan kesepakatan Selat Hormuz.</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807081448-17-757297/jelang-akhir-pekan-bursa-asia-kompak-menguat</t>
+        </is>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/04/07/usa-trumptariffs-taiwan-markets-1743996013585_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Ada Apa dengan Saham Energi? Asing Kompak Serok</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>Investor asing mencatatkan net buy signifikan di sektor energi dan petrokimia, meski secara keseluruhan masih net sell. Temukan saham-saham unggulan di sini.</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807045559-17-757272/ada-apa-dengan-saham-energi-asing-kompak-serok</t>
+        </is>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2021/07/28/ilustrasi-bursa-efek-indonesia-cnbc-indonesiaandrean-kristianto-17_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Pelindo Buka Suara Soal Rencana IPO, Begini Kata Manajemen</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:30:43 +0700</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>Pelindo belum memutuskan rencana IPO. Fokus saat ini adalah penguatan fundamental bisnis dan peningkatan layanan, sesuai arahan Danantara Indonesia.</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807050843-17-757273/pelindo-buka-suara-soal-rencana-ipo-begini-kata-manajemen</t>
+        </is>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/29/dok-pelindo-1780032056538_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Begini Sosok yang Diharapkan Jadi Gubernur BI, Pengganti Perry Warjiyo</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:25:02 +0700</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>Nama calon Gubernur Bank Indonesia masih menjadi tanda tanya. Meski sejak pengunduran diri Perry Warjiyo sudah bermunculan beberapa nama ke publik.</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807063328-17-757276/begini-sosok-yang-diharapkan-jadi-gubernur-bi-pengganti-perry-warjiyo</t>
+        </is>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2018/02/01/c7497f38-96f1-4782-95bb-e9ac05a8c8b5_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Sinyal Baru Asing, Borong Saham Bank BUMN</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:05:40 +0700</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>Investor asing mencatatkan net sell Rp273,5 miliar pada perdagangan kemarin.</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807044750-17-757271/sinyal-baru-asing-borong-saham-bank-bumn</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/07/15/ilustrasi-bursa-cnbc-indonesiaandrean-kristianto-4_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Tokenisasi ETF Permudah Akses Investor Ritel ke Pasar Saham AS</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:50:35 +0700</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA — Perkembangan teknologi blockchain mulai mengubah cara investor mengakses pasar modal global. Melalui tokenisasi aset (tokenized exchange traded fund/ETF), investor kini dapat berinvestasi pada indeks saham Amerika...</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjds0b370/tokenisasi-etf-permudah-akses-investor-ritel-ke-pasar-saham-as</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260223210508-736.png</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>ESG Didorong Menjadi Standar Baru Daya Saing Bisnis Indonesia</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:27:00 +0700</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Muhammad Hafil</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – Di tengah meningkatnya tuntutan dunia terhadap praktik bisnis yang berkelanjutan, penerapan prinsip Environmental, Social, and Governance (ESG) tidak lagi dipandang sebagai pelengkap strategi perusahaan, melainkan menjadi...</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjdqqc430/esg-didorong-menjadi-standar-baru-daya-saing-bisnis-indonesia</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/yayasan-kehati-kembali-menyelenggarakan-esg-award_260807102213-437.jpg</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>PTPN Catat Penjualan Rp 29,1 Triliun, Transformasi Bisnis Mulai Berhasil</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:24:04 +0700</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA — Transformasi bisnis yang dijalankan Holding Perkebunan Nusantara PTPN III (Persero) mulai tercermin pada kinerja operasional dan keuangan perusahaan. Sepanjang semester I 2026, PTPN Group mencatat pertumbuhan...</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjdqs4370/ptpn-catat-penjualan-rp-291-triliun-transformasi-bisnis-mulai-berhasil</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/pt-perkebunan-nusantara-ptpn-iv-palmco-mempercepat-langkah-hilirisasi_260327080727-621.jpeg</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Insentif EV Diprioritaskan untuk Kendaraan Bernilai Tambah Tinggi</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA — Menteri Perindustrian (Menperin) Agus Gumiwang Kartasasmita menyatakan penerima insentif kendaraan listrik atau electric vehicle (EV) diarahkan untuk produk yang memberikan nilai tambah tinggi, serta merupakan program...</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjdko2370/insentif-ev-diprioritaskan-untuk-kendaraan-bernilai-tambah-tinggi</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/pengguna-mobil-listrik-saat-melakukan-pengisian-daya-di-spklu_260314132157-549.jpeg</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Reaksi Gubernur DKI  Ada 995 Senjata dan Narkoba di Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:14:41 +0700</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>Gubernur DKI meminta aparat menindak tegas kasus di sekolah swasta tersebut.</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264055/reaksi-gubernur-dki-ada-995-senjata-dan-narkoba-di-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/iqJioQdqGErs86EZlEySMcKBnAo=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317872/original/081819100_1786075991-IMG_3355.jpg</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Diduga Curi Kabel, Pria Terbakar Akibat Sengatan Listrik</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:21:12 +0700</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>Aksi pria masuk gardu PLN berakhir tragis setelah tubuhnya tersengat listrik.</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264016/diduga-curi-kabel-pria-terbakar-akibat-sengatan-listrik</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/NSAGsWSFTLiM4Uz88v9cjH6KcZ0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317800/original/040315000_1786072809-eb766691-3248-4d67-813c-6c080ce10842.jpg</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Febrie Adriansyah Diperiksa Sebagai Tersangka Hari Ini</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:26:14 +0700</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>Pemeriksaan terhadap Febrie akan berlangsung di Komisi Pemberantasan Korupsi (KPK), Jakarta Selatan.</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264019/febrie-adriansyah-diperiksa-sebagai-tersangka-hari-ini</t>
+        </is>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/5H9OrKrKfqk4sxzMhRXDJocJZzs=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9306884/original/012167500_1784913813-jam4.jpg</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Kapolresta Banda Aceh Diperiksa Propam Mabes Polri</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:37:53 +0700</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>Kapolresta Banda Aceh, Kapolda Aceh Irjen Pol. Ruddi Setiawan menunjuk Kabid TIK Polda Aceh Kombes Pol. Teguh Priyambodo sebagai pelaksana tugas.</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263991/kapolresta-banda-aceh-diperiksa-propam-mabes-polri</t>
+        </is>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/j9nfrzZ0jUlq996vXe1u8X7JlJo=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317761/original/078167100_1786070270-SnapInsta.to_681964350_17906790624404359_4518614206507391175_n.jpg</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Cuaca Didominasi Awan Tebal, BMKG Beri Peringatan untuk Papua</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:35:45 +0700</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>BMKG memprakirakan cuaca berawan mendominasi sebagian besar wilayah Indonesia.</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263990/cuaca-didominasi-awan-tebal-bmkg-beri-peringatan-untuk-papua</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/2A3BhpyIxGizJRRMdURur9U2mRc=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317759/original/069833200_1786070133-IMG_20250415_110015.jpg</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Penyelundupan 3,4 Kg Ganja Digagalkan, Pelaku 15 Tahun Ditangkap</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:19:43 +0700</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Pengiriman ganja dari Sumatera Utara ke Jakarta digagalkan di Daan Mogot.</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263981/penyelundupan-34-kg-ganja-digagalkan-pelaku-15-tahun-ditangkap</t>
+        </is>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/5-sVcdXGjGphQTeCNJW6t61cBL8=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317748/original/049178700_1786068996-21831b60-e297-43d5-b0cb-925cc9ed76d4.jpg</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Kronologi Penangkapan Warga Cimahi Pembuat Video AI Manipulasi Prabowo</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:32:16 +0700</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>Perbuatan tersangka diduga memenuhi unsur tindak pidana manipulasi data elektronik atau identity theft.</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8263980/kronologi-penangkapan-warga-cimahi-pembuat-video-ai-manipulasi-prabowo</t>
+        </is>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/QmH9aMAq9zkNXbdgLzySVuzykWo=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317822/original/063947900_1786073515-Rilis_penangkapan_penyebar_manipulasi_AI_Prabowo.jpg</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Lifestyle</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Sering ke Museum dan Bioskop Bisa Bikin Kamu Panjang Umur</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:29:13 +0700</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>Kegiatan budaya seperti ke museum dan bioskop ternyata dapat memperlambat penuaan. Begini penjelasannya.</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>https://lifestyle.kompas.com/read/2026/08/07/112700420/sering-ke-museum-dan-bioskop-bisa-bikin-kamu-panjang-umur</t>
+        </is>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/Mj1GIg6tRPqgcR150KqI0oOYYng=/145x0:1765x1080/1200x675/filters:watermark(data/photo/2026/01/30/697c817ed68bb.png,0,-0,1)/data/photo/2026/08/01/6a6d3588db8b8.jpg</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Ekonom Soroti Dominasi Pekerja Informal Meski Ekonomi Tumbuh 5,29 Persen</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:29:13 +0700</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>Ekonom menilai pertumbuhan ekonomi 5,29 persen belum berkualitas karena lapangan kerja formal dan pendapatan pekerja belum meningkat signifikan.</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/07/110730426/ekonom-soroti-dominasi-pekerja-informal-meski-ekonomi-tumbuh-529-persen</t>
+        </is>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/ssCzepmGtYzHmbt0aesZ-IPTMPI=/0x0:5000x3333/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/05/24/6a122b256b39f.jpg</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>Ilmuwan BRIN Lapor ke Prabowo soal Nuklir, Lalu Mikrofon Dimatikan</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:29:13 +0700</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>Kepala riset nuklir BRIN melaporkan soal kemampuan mengolah uranium ke Prabowo. Lantas Prabowo meminta mikrofon dimatikan dulu.</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/07/10503491/ilmuwan-brin-lapor-ke-prabowo-soal-nuklir-lalu-mikrofon-dimatikan</t>
+        </is>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/u6zE-eYIioyhf0wM5lFHM5iVLl8=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/07/6a75415297fed.jpg</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I165"/>
+  <autoFilter ref="A1:I370"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-07.xlsx
+++ b/data/berita_2026-08-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$370</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$462</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I370"/>
+  <dimension ref="A1:I462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -17823,8 +17823,4332 @@
         </is>
       </c>
     </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>PPAL aktif berikan rekomendasi untuk kepentingan TNI AL</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:03:57 +0700</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>Ketua Umum Persatuan Purnawirawan Angkatan Laut (PPAL) Laksamana TNI (Purn) Yudo Margono mengatakan jajarannya selalu ...</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683853/ppal-aktif-berikan-rekomendasi-untuk-kepentingan-tni-al</t>
+        </is>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001562012.jpg</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Bandara Soetta layani 25,9 juta penumpang pada semester I 2026</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:59:44 +0700</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>PT Angkasa Pura Indonesia (Persero) atau InJourneyAirports melalui Kantor Cabang Bandara Soekarno-Hatta (Soetta), ...</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683849/bandara-soetta-layani-259-juta-penumpang-pada-semester-i-2026</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000290609.jpg</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Tumpukan sampah di Kedaung Kaliangke Jakbar kembali dikeluhkan warga</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:59:35 +0700</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>Warga kembalimengeluhkan sampah yang menumpuk di kawasan RT 04/RW 03, Kelurahan Kedaung Kaliangke, Kecamatan ...</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683848/tumpukan-sampah-di-kedaung-kaliangke-jakbar-kembali-dikeluhkan-warga</t>
+        </is>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Sampah-Kedaung-Kaliangke-Jakbar.jpg</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Pembalap melakukan sesi latihan ARRC 2026 di Sirkuit Mandalika</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:58:22 +0700</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>Pembalap JDT Racing Team Joshua Waters memacu motornya saat sesi free practice 1 balapan Asia Road Racing Championship ...</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5683844/pembalap-melakukan-sesi-latihan-arrc-2026-di-sirkuit-mandalika</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Arrc-2026-di-mandalika-070826-AS-7.jpg</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Ilmuwan AS ciptakan bakteriofag AI untuk pertama kali</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:58:08 +0700</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>Sejumlah ilmuwan Amerika Serikat, untuk pertama kalinya, berhasil menggunakan model kecerdasan buatan (AI) untuk ...</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683840/ilmuwan-as-ciptakan-bakteriofag-ai-untuk-pertama-kali</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/12/16/Illustration_Gen-AI-by-Freepik.jpg</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>RSCM lakukan implantasi LVAD paling kecil di dunia</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:55:30 +0700</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>Rumah Sakit Umum Pusat Nasional Dr. Cipto Mangunkusumo (RSCM) mengklaim telah sukses melakukan implantasi Left ...</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683837/rscm-lakukan-implantasi-lvad-paling-kecil-di-dunia</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-08.08.25.jpeg</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Bareskrim bongkar dugaan peredaran narkoba di THM Five Star, Bali</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:54:23 +0700</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>Direktorat Tindak Pidana Narkoba (Dittipidnarkoba) Bareskrim Polri membongkar dugaan peredaran narkoba di tempat ...</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683835/bareskrim-bongkar-dugaan-peredaran-narkoba-di-thm-five-star-bali</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/27/1000080547.jpg</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Trump perintahkan investigasi atas kebocoran informasi stok amunisi AS</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:53:14 +0700</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat Donald Trump telah memerintahkan penyelidikan baru terkait pengungkapan informasi mengenai ...</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683832/trump-perintahkan-investigasi-atas-kebocoran-informasi-stok-amunisi-as</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/AA-20260802-42124703-42124695-TRUMPTARGETING_BANNER_DISPLAYED_IN_TEHRANS_AZADI_SQUARE.jpg</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Permohonan imigrasi AS "menumpuk" sampai 7,5 juta</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:52:38 +0700</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>Lambatnya proses imigrasi Amerika Serikat telah menyebabkan penumpukan permohonan hingga mencapai rekor tertinggi, ...</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683829/permohonan-imigrasi-as-menumpuk-sampai-75-juta</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/07/CjkinzN000022_20251107_CBMFN0A001a.jpg</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>KPK terima permintaan Kejagung untuk periksa Febrie Adriansyah</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:52:37 +0700</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>Komisi Pemberantasan Korupsi (KPK) menerima permintaan Kejaksaan Agung untuk memeriksa mantan Jaksa Agung Muda Bidang ...</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683828/kpk-terima-permintaan-kejagung-untuk-periksa-febrie-adriansyah</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/05/1001013665.jpg</t>
+        </is>
+      </c>
+      <c r="I380" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>Banyak Hipertensi, pelajar dilibatkan jadi agen penggerak hidup sehat</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:50:45 +0700</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota (Pemkot) Kediri, Jawa Timur, melibatkan pelajar Sekolah Menengah Atas (SMA) sebagai peer educator atau ...</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683825/banyak-hipertensi-pelajar-dilibatkan-jadi-agen-penggerak-hidup-sehat</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000897304.jpg</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>Redmi Note 17 masuk ke pasar India, spesifikasinya mirip versi China</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:48:51 +0700</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>Redmi telah meluncurkan Redmi Note 17 di pasar India, menawarkan ponsel yang spesifikasinya hampir ...</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683824/redmi-note-17-masuk-ke-pasar-india-spesifikasinya-mirip-versi-china</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/InShot_20260807_120221131.jpg</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>PPAL kenang jasa para pahlawan dengan berziarah ke TMP Kalibata</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:43:56 +0700</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E383" t="inlineStr">
+        <is>
+          <t>Persatuan Purnawirawan Angkatan Laut (PPAL) mengenang jasa para pahlawan bangsa dengan menggelar ziarah di Taman Makam ...</t>
+        </is>
+      </c>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683823/ppal-kenang-jasa-para-pahlawan-dengan-berziarah-ke-tmp-kalibata</t>
+        </is>
+      </c>
+      <c r="H383" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001561814.jpg</t>
+        </is>
+      </c>
+      <c r="I383" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>Kementerian PU gelar Gerakan Irigasi Bersih dukung ketahanan pangan</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:41:58 +0700</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E384" t="inlineStr">
+        <is>
+          <t>Kementerian Pekerjaan Umum (PU) melalui Direktorat Jenderal Sumber Daya Air (SDA) menggelar Gerakan Irigasi ...</t>
+        </is>
+      </c>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683820/kementerian-pu-gelar-gerakan-irigasi-bersih-dukung-ketahanan-pangan</t>
+        </is>
+      </c>
+      <c r="H384" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000878502.jpg</t>
+        </is>
+      </c>
+      <c r="I384" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>DKI akui ada tumpang tindih jalur mikrolet 44 dan Mikrotrans JAK 48A</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:38:31 +0700</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E385" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi DKI Jakarta mengakui ada tumpang tindih jalur antara mikrolet 44 yang melayani trayek Kampung ...</t>
+        </is>
+      </c>
+      <c r="F385" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683817/dki-akui-ada-tumpang-tindih-jalur-mikrolet-44-dan-mikrotrans-jak-48a</t>
+        </is>
+      </c>
+      <c r="H385" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_2478.jpeg</t>
+        </is>
+      </c>
+      <c r="I385" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>Bandara Soetta genjot peningkatan infrastruktur dan layanan digital</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:30:20 +0700</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E386" t="inlineStr">
+        <is>
+          <t>PT Angkasa Pura Indonesia (Persero) atau InJourney Airports melalui Kantor Cabang Bandara Internasional Soekarno-Hatta, ...</t>
+        </is>
+      </c>
+      <c r="F386" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683815/bandara-soetta-genjot-peningkatan-infrastruktur-dan-layanan-digital</t>
+        </is>
+      </c>
+      <c r="H386" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000453452.jpg</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>Presiden Polandia tegaskan tak akan legalkan pernikahan sesama jenis</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:29:44 +0700</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>Presiden Polandia Karol Nawrocki mengatakan dirinya terbuka untuk membahas peraturan yang memungkinkan untuk melegalkan ...</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683813/presiden-polandia-tegaskan-tak-akan-legalkan-pernikahan-sesama-jenis</t>
+        </is>
+      </c>
+      <c r="H387" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/09/21/ring-2407552_960_720.jpg</t>
+        </is>
+      </c>
+      <c r="I387" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>KemenPPPA gelar Kemudi Anak, sarana penyampaian aspirasi ke pemerintah</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:28:02 +0700</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>Kementerian Pemberdayaan Perempuan dan Perlindungan Anak (PPPA) menggelar kegiatan Kemudi Anak (Kepemimpinan Muda ...</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683811/kemenpppa-gelar-kemudi-anak-sarana-penyampaian-aspirasi-ke-pemerintah</t>
+        </is>
+      </c>
+      <c r="H388" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-05-at-15.30.43.jpg</t>
+        </is>
+      </c>
+      <c r="I388" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Polres Jakpus sita 132 kilogram ganja, dua DPO masih diburu</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:20:23 +0700</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>Polres Metro Jakarta Pusat menyita sekitar 132 kilogram ganja dari pengungkapan tiga kasus peredaran narkotika ...</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683807/polres-jakpus-sita-132-kilogram-ganja-dua-dpo-masih-diburu</t>
+        </is>
+      </c>
+      <c r="H389" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/20260807_103050.jpg</t>
+        </is>
+      </c>
+      <c r="I389" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>DPP Perbasi gandeng Nico Widmer untuk kembangkan 3x3 di Indonesia</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:15:15 +0700</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>Badan 3x3 Dewan Pengurus Pusat Persatuan Bola Basket Seluruh Indonesia (DPP Perbasi) menggandeng Nico Widmer untuk ...</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683805/dpp-perbasi-gandeng-nico-widmer-untuk-kembangkan-3x3-di-indonesia</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000475111.jpg</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Pramono angkat bicara soal temuan senjata di sekolah</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:12:42 +0700</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta Pramono Anung mengatakan temuan berupa 995 pucuk senjata dan narkoba di salah satu sekolah ...</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683803/pramono-angkat-bicara-soal-temuan-senjata-di-sekolah</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_2465.jpeg</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Gubernur prioritaskan pembangunan jalan puluhan tahun dinanti di Nias</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:10:50 +0700</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Gubernur Sumatera Utara (Sumut) Bobby Nasution memprioritaskan pembangunan infrastruktur jalan yang telah dinantikan ...</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683799/gubernur-prioritaskan-pembangunan-jalan-puluhan-tahun-dinanti-di-nias</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001034262.jpg</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Daftar juara Piala Presiden 2015-2026, Persebaya juara terbaru</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:09:30 +0700</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Persebaya Surabaya berhasil mencatatkan sejarah baru dengan keluar sebagai juara Piala Presiden 2026. Gelar tersebut ...</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683796/daftar-juara-piala-presiden-2015-2026-persebaya-juara-terbaru</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/persebaya-juara-piala-presiden-2026-2836164.jpg</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Kalbar perkuat kesiapsiagaan hadapi puncak karhutla</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:07:30 +0700</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi Kalimantan Barat (Pemprov Kalbar) memperkuat kesiapsiagaan menghadapi puncak ancaman kebakaran ...</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683792/kalbar-perkuat-kesiapsiagaan-hadapi-puncak-karhutla</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-09.02.55.jpeg</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Kepala BNPB perkuat antisipasi karhutla di lahan gambut di Kubu Raya</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:06:38 +0700</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Kepala Badan Nasional Penanggulangan Bencana (BNPB) Suharyanto mengatakan kebakaran hutan dan lahan (karhutla) di ...</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683788/kepala-bnpb-perkuat-antisipasi-karhutla-di-lahan-gambut-di-kubu-raya</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/767101496_1372423328362643_3390602255780147155_n.jpeg</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Terkait 995 senjata, Yayasan sekolah tegaskan tak ada ekskul menembak</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:05:58 +0700</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Pengurus yayasan sekolah swasta di kawasan Pondok Pinang, Kebayoran Lama, Jakarta Selatan, menegaskan tidak ada ...</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683785/terkait-995-senjata-yayasan-sekolah-tegaskan-tak-ada-ekskul-menembak</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001016071.jpg</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Telkom pangkas 34 entitas dalam proses transformasi BUMN</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:05:29 +0700</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>PT Telkom Indonesia memangkas 34 entitas dari 67 entitas usaha dalam proses transformasi BUMN untuk membangun ...</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683781/telkom-pangkas-34-entitas-dalam-proses-transformasi-bumn</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-10.05.33.jpeg</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>KPPPA: Kepemimpinan ASN perempuan harus ditopang kemampuan komunikasi</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:04:45 +0700</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Kementerian Pemberdayaan Perempuan dan Perlindungan Anak (KPPPA) menekankan pentingnya kemampuan komunikasi sebagai ...</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683779/kpppa-kepemimpinan-asn-perempuan-harus-ditopang-kemampuan-komunikasi</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-06-at-15.46.49.jpeg</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>CAF sampaikan dukungan penuh untuk Gianni Infantino</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:01:11 +0700</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Konfederasi Sepak Bola Afrika (CAF) menyampaikan dukungan penuh kepada Presiden FIFA Gianni Infantino dan ...</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683775/caf-sampaikan-dukungan-penuh-untuk-gianni-infantino</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/thumbs_b_c_669e9774d8942ff9475105617b428127.jpg</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>BSKDN kembangkan SINTESIS hadirkan kebijakan tepat sasaran</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:58:33 +0700</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>Badan Strategi Kebijakan Dalam Negeri (BSKDN) Kementerian Dalam Negeri terus memperkuat pengembangan platform SINTESIS ...</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683772/bskdn-kembangkan-sintesis-hadirkan-kebijakan-tepat-sasaran</t>
+        </is>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000581661.jpg</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Yayasan tegaskan belajar mengajar tetap normal usai temuan 995 senjata</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:56:18 +0700</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr">
+        <is>
+          <t>Pengurus yayasan sekolah swasta di Pondok Pinang, Kebayoran Lama, menegaskan kegiatan belajar mengajar tetap berjalan ...</t>
+        </is>
+      </c>
+      <c r="F401" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683769/yayasan-tegaskan-belajar-mengajar-tetap-normal-usai-temuan-995-senjata</t>
+        </is>
+      </c>
+      <c r="H401" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001016025.jpg</t>
+        </is>
+      </c>
+      <c r="I401" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Mantan PM Malaysia Ismail Sabri dirawat di RS di tengah kasus hukum</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:56:13 +0700</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>Mantan perdana menteri Malaysia, Ismail Sabri Yaakob (66), dikabarkan dirawat di Rumah Sakit Institut Jantung ...</t>
+        </is>
+      </c>
+      <c r="F402" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683767/mantan-pm-malaysia-ismail-sabri-dirawat-di-rs-di-tengah-kasus-hukum</t>
+        </is>
+      </c>
+      <c r="H402" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2021/08/20/reuters_ismail_sabri2.jpg</t>
+        </is>
+      </c>
+      <c r="I402" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Pemerintah akan kirim tim untuk kaji langkah pemulihan Montara</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:52:04 +0700</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa menyatakan Pemerintah akan mengirim tim riset untuk mengkaji secara komprehensif ...</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683765/pemerintah-akan-kirim-tim-untuk-kaji-langkah-pemulihan-montara</t>
+        </is>
+      </c>
+      <c r="H403" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-08.12.49.jpeg</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Kemenkes: Pasien BPJS yang viral tunggu 8 jam karena HCU RSCM terbatas</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:51:26 +0700</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan (Kemenkes) mengatakan pasien BPJS Kesehatan yang viral di media sosial harus menunggu selama ...</t>
+        </is>
+      </c>
+      <c r="F404" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683764/kemenkes-pasien-bpjs-yang-viral-tunggu-8-jam-karena-hcu-rscm-terbatas</t>
+        </is>
+      </c>
+      <c r="H404" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/27/WhatsApp-Image-2025-11-27-at-17.49.15_831c9c5c.jpg</t>
+        </is>
+      </c>
+      <c r="I404" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>OpenAI akan rilis "speaker donat" pintar pada 2027</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:49:48 +0700</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr">
+        <is>
+          <t>Perusahaan kecerdasan buatan (AI) asal Amerika Serikat, OpenAI, sedang mengembangkan perangkat rumah tangga berbasis AI ...</t>
+        </is>
+      </c>
+      <c r="F405" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683760/openai-akan-rilis-speaker-donat-pintar-pada-2027</t>
+        </is>
+      </c>
+      <c r="H405" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/22/thumbs_b_c_c48eb58d9c1e7c83fd91f3633ecd20ec.jpg</t>
+        </is>
+      </c>
+      <c r="I405" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Iran kecam "diplomasi sandiwara" oleh AS</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:49:35 +0700</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr">
+        <is>
+          <t>Mohammad Bagher Ghalibaf, ketua parlemen Iran sekaligus ketua tim negosiator Iran dalam pembicaraan dengan ...</t>
+        </is>
+      </c>
+      <c r="F406" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683759/iran-kecam-diplomasi-sandiwara-oleh-as</t>
+        </is>
+      </c>
+      <c r="H406" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/02/AA-20260802-42124703-42124695-TRUMPTARGETING_BANNER_DISPLAYED_IN_TEHRANS_AZADI_SQUARE.jpg</t>
+        </is>
+      </c>
+      <c r="I406" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Kemenperin perkuat pengelolaan kemasan untuk pacu industri hijau</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:45:49 +0700</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr">
+        <is>
+          <t>Kementerian Perindustrian (Kemenperin) memperkuat pengelolaan kemasan pascakonsumsi sebagai bagian dari upaya ...</t>
+        </is>
+      </c>
+      <c r="F407" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683757/kemenperin-perkuat-pengelolaan-kemasan-untuk-pacu-industri-hijau</t>
+        </is>
+      </c>
+      <c r="H407" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/3-1.jpeg</t>
+        </is>
+      </c>
+      <c r="I407" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Penyanyi Ghea Indrawari hadirkan "Rasi Bintang" sebagai album kedua</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:44:06 +0700</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>Penyanyi Ghea Indrawari merilis album studio keduanya bertajuk "Rasi Bintang" di seluruh platform musik ...</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683755/penyanyi-ghea-indrawari-hadirkan-rasi-bintang-sebagai-album-kedua</t>
+        </is>
+      </c>
+      <c r="H408" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Ghea-Indrawari-05.JPG.jpeg</t>
+        </is>
+      </c>
+      <c r="I408" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Presiden FA Yordania tegaskan tak akan dukung Gianni Infantino</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:32:53 +0700</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>Presiden Asosiasi Sepak Bola (FA) Yordania Ali Al Hussein menegaskan tak akan memberikan dukungan kepada Gianni ...</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683753/presiden-fa-yordania-tegaskan-tak-akan-dukung-gianni-infantino</t>
+        </is>
+      </c>
+      <c r="H409" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/thumbs_b_c_4b35583a6a2b064678bf5739a06f4ada.jpg</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Warisan "fair play" dari stadion para pejuang</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:32:53 +0700</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>Peluit panjang mengakhiri adu penalti di Stadion Kapten I Wayan Dipta, Gianyar, Kamis (6/8) malam. Para pemain ...</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683752/warisan-fair-play-dari-stadion-para-pejuang</t>
+        </is>
+      </c>
+      <c r="H410" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/279254.jpg</t>
+        </is>
+      </c>
+      <c r="I410" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Maroko siap bekerja sama pulangkan imigran anak</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:29:45 +0700</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr">
+        <is>
+          <t>Pemerintah Maroko menyatakan siap bekerja sama dengan Spanyol dan Uni Eropa untuk memulangkan anak-anak di bawah umur ...</t>
+        </is>
+      </c>
+      <c r="F411" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683749/maroko-siap-bekerja-sama-pulangkan-imigran-anak</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/thumbs_b_c_163e90d67c855177fcf9553fd9012181.jpg</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>AFA berikan dukungan untuk Gianni Infantino</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:27:34 +0700</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr">
+        <is>
+          <t>Federasi Sepak Bola Argentina (AFA) memberikan dukungan untuk Presiden FIFA Gianni Infantino yang pada beberapa waktu ...</t>
+        </is>
+      </c>
+      <c r="F412" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683747/afa-berikan-dukungan-untuk-gianni-infantino</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/timnas-spanyol-juara-piala-dunia-2026-2824232.jpg</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>BBTNKS luncurkan program penghijauan di kaki Gunung Kerinci</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:27:19 +0700</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr">
+        <is>
+          <t>Balai Besar Taman Nasional Kerinci Seblat (BBTNKS) meluncurkan program penghijauan (greenline) di kaki Gunung Kerinci ...</t>
+        </is>
+      </c>
+      <c r="F413" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683743/bbtnks-luncurkan-program-penghijauan-di-kaki-gunung-kerinci</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/566130.jpg</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Arab Saudi yakini kelompok bersenjata asing siapkan serangan</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:26:13 +0700</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr">
+        <is>
+          <t>Arab Saudi memperoleh informasi intelijen yang mengindikasikan adanya persiapan serangan terhadap kerajaan ...</t>
+        </is>
+      </c>
+      <c r="F414" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683740/arab-saudi-yakini-kelompok-bersenjata-asing-siapkan-serangan</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/01/23/CjkinzN007037_20220123_CBPFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Pramono Sindir ASN 'Curi-curi' Tak Naik Transportasi Umum Saat Rabu: Saya Tahu</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:44:52 +0700</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>Pramono menyoroti ASN yang masih menggunakan mobil pribadi meski diwajibkan menggunakan transportasi umum setiap Rabu. Dia tahu ada ASN yang tak patuh.</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608326/pramono-sindir-asn-curi-curi-tak-naik-transportasi-umum-saat-rabu-saya-tahu</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/gubernur-dki-jakarta-pramono-anung-brigittadetik-1786081467940_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Kera yang Menyerang di Inhil Sudah Ditangkap, Warga Diminta Tetap Waspada</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:31:34 +0700</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr">
+        <is>
+          <t>Kera ekor panjang yang menyerang 17 warga di Tembilahan, Riau, telah ditangkap. Polisi imbau warga tetap waspada meski serangan sudah berhenti.</t>
+        </is>
+      </c>
+      <c r="F416" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608316/kera-yang-menyerang-di-inhil-sudah-ditangkap-warga-diminta-tetap-waspada</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kera-ekor-panjang-yang-menyerang-warga-sudah-diamankan-pada-kamis-682026-1786080546645_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Melihat Lebih Dekat Stasiun Gunung Putri di Bogor yang Terbengkalai</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:31:14 +0700</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr">
+        <is>
+          <t>Kereta melintas setiap hari, tapi tak satu pun penumpang naik atau turun di Stasiun Gunung Putri. Bangunan stasiun itu kini terbengkalai dipenuhi ilalang.</t>
+        </is>
+      </c>
+      <c r="F417" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608315/melihat-lebih-dekat-stasiun-gunung-putri-di-bogor-yang-terbengkalai</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kondisi-stasiun-gunung-putri-bogor-yang-kini-terbengkalai-1786080454648_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>2 Pelaku Demo Anarkis Minta Jatah Limbah Perusahaan di Tangerang Ditangkap</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:28:20 +0700</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>Polda Banten menangkap dua pria yang diduga menjadi otak demonstrasi anarkis di PT EDS. Mereka dituduh merusak fasilitas dan menuntut pengelolaan limbah.</t>
+        </is>
+      </c>
+      <c r="F418" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608304/2-pelaku-demo-anarkis-minta-jatah-limbah-perusahaan-di-tangerang-ditangkap</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/07/25/ilustrasi-penangkapan_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Pramono Pastikan Gaji ASN DKI Aman Meski DBH Dipangkas: Semuanya Terpenuhi</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:25:13 +0700</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr">
+        <is>
+          <t>Pramono menegaskan kewajiban Pemprov DKI kepada ASN tetap dapat dipenuhi. Pembayaran gaji maupun hak-hak pegawai tidak terdampak oleh kebijakan pemangkasan DBH.</t>
+        </is>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608303/pramono-pastikan-gaji-asn-dki-aman-meski-dbh-dipangkas-semuanya-terpenuhi</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/gubernur-dki-jakarta-pramono-anung-beliadetikcom-1786080281071_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Balap Liar di Taman Mini Dibubarkan, Pelaku Kocar-kacir Dikejar Polisi</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:19:38 +0700</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr">
+        <is>
+          <t>Tim Patroli Brimob membubarkan aksi balap liar di Jakarta Timur, mengamankan 11 pemuda dan sepeda motor. Patroli rutin untuk mencegah gangguan keamanan.</t>
+        </is>
+      </c>
+      <c r="F420" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608298/balap-liar-di-taman-mini-dibubarkan-pelaku-kocar-kacir-dikejar-polisi</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/patroli-gabungan-brimob-polda-metro-jaya-dan-tim-perintis-polres-jakarta-timur-membubarkan-balap-liar-di-kawasan-taman-mini-ja-1786079956709_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Pramono Perintahkan DLH Bersihkan Gunungan Sampah Dekat SD Kedaung Kali Angke</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:17:36 +0700</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr">
+        <is>
+          <t>Pramono Anung memerintahkan Dinas Lingkungan Hidup (DLH) DKI Jakarta segera membersihkan gunungan sampah di dekat SDN Kedaung Kali Angke 12, Jakarta Barat.</t>
+        </is>
+      </c>
+      <c r="F421" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608290/pramono-perintahkan-dlh-bersihkan-gunungan-sampah-dekat-sd-kedaung-kali-angke</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/gubernur-dki-jakarta-pramono-anung-beliadetikcom-1786079771132_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Bareskrim Bongkar Peredaran Narkoba di Five Stars Bali, 53 Orang Diamankan</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:13:00 +0700</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr">
+        <is>
+          <t>Dittipidnarkoba Bareskrim Polri mengungkap peredaran narkoba di kelab malam Five Stars Bali, mengamankan 53 orang sebagai tersangka dan saksi.</t>
+        </is>
+      </c>
+      <c r="F422" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608288/bareskrim-bongkar-peredaran-narkoba-di-five-stars-bali-53-orang-diamankan</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/bareskrim-polri-mengungkap-peredaran-di-five-stars-denpasar-bali-dan-mengamankan-53-orang-1786079431797_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Legislator Soroti Nakes Hina Pasien BPJS, Minta Evaluasi Total Manajemen RS</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:06:25 +0700</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr">
+        <is>
+          <t>Ia memandang harus ada evaluasi total terkait durasi masa tunggu bagi pasien rawat inap untuk mendapatkan perawatan.</t>
+        </is>
+      </c>
+      <c r="F423" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608270/legislator-soroti-nakes-hina-pasien-bpjs-minta-evaluasi-total-manajemen-rs</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/04/16/ilustrasi-dokter-dengan-pasien-1744783009967_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Ada Konflik Internal di Balik Temuan Ratusan Senjata di Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:58:43 +0700</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>Taufiq Syarifudin, Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr">
+        <is>
+          <t>Pihak sekolah mengungkap temuan ratusan senjata di ruang mantan ketua yayasan, terkait sengketa internal. Polisi selidiki kasus ini lebih lanjut.</t>
+        </is>
+      </c>
+      <c r="F424" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608255/ada-konflik-internal-di-balik-temuan-ratusan-senjata-di-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temuan-ratusan-pucuk-senjata-di-sekolah-swasta-di-pondok-pinang-jakarta-selatan-1786014363648_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Ketua DPD Sambangi Kediaman Boediono, Sampaikan Undangan Sidang Bersama</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:57:56 +0700</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>Anggi Muliawati</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr">
+        <is>
+          <t>Ketua DPD RI Sultan Najamudin mengunjungi kediaman Boediono. Kunjungan itu dalam rangka menyampaikan undangan Sidang Bersama DPR-DPD RI 2026.</t>
+        </is>
+      </c>
+      <c r="F425" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608253/ketua-dpd-sambangi-kediaman-boediono-sampaikan-undangan-sidang-bersama</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/ketua-dpd-ri-sultan-baktiar-najamudin-menyambangi-kediaman-wakil-presiden-ke-11-ri-boediono-1786078635188_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Dinkes Pastikan Nakes Viral Cibir Pasien BPJS Bukan Pegawai Pemprov DKI</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:53:23 +0700</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr">
+        <is>
+          <t>Dinkes DKI Jakarta menegaskan nakes yang mencibir pasien BPJS bukan pegawai Pemprov. Nakes tersebut tidak bekerja di RSUD milik Pemprov Jakarta.</t>
+        </is>
+      </c>
+      <c r="F426" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608241/dinkes-pastikan-nakes-viral-cibir-pasien-bpjs-bukan-pegawai-pemprov-dki</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kepala-dinas-kesehatan-dki-jakarta-ani-ruspitawati-brigittadetik-1786078386930_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Pemprov DKI Kaji Rute Angkot JakLingko dan M44 Agar Tak Tumpang Tindih</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:30:07 +0700</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr">
+        <is>
+          <t>Dinas Perhubungan (Dishub) DKI Jakarta akan mengkaji ulang rute Mikrotrans atau angkot JakLingko 48 dengan angkot M44 jurusan Karet-Kampung Melayu.</t>
+        </is>
+      </c>
+      <c r="F427" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608209/pemprov-dki-kaji-rute-angkot-jaklingko-dan-m44-agar-tak-tumpang-tindih</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/angkot-kosong-ditinggal-oleh-sopirnya-yang-sedang-berdemo-di-balai-kota-adhfar-aulia-syuhadadetikcom-1785990400876_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Anggota DPR Minta Usut Tuntas Temuan Ratusan Senjata di Sekolah Swasta Jaksel</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:27:00 +0700</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr">
+        <is>
+          <t>Sejumlah anggota DPR RI turut menanggapi perihal temuan ratusan senjata di salah satu sekolah swasta di Kebayoran Lama. Mereka meminta temuan itu diusut tuntas.</t>
+        </is>
+      </c>
+      <c r="F428" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608205/anggota-dpr-minta-usut-tuntas-temuan-ratusan-senjata-di-sekolah-swasta-jaksel</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temuan-ratusan-pucuk-senjata-di-sekolah-swasta-di-pondok-pinang-jakarta-selatan-1786014363566_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Pramono Dukung Polisi Usut Temuan Senjata-Narkoba di Sekolah Swasta Jaksel</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:25:11 +0700</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr">
+        <is>
+          <t>Gubernur Jakarta Pramono Anung mendukung aparat mengusut tuntas temuan ratusan senjata, narkoba, hingga film dewasa di sebuah sekolah swasta di Jaksel.</t>
+        </is>
+      </c>
+      <c r="F429" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608201/pramono-dukung-polisi-usut-temuan-senjata-narkoba-di-sekolah-swasta-jaksel</t>
+        </is>
+      </c>
+      <c r="H429" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temuan-ratusan-pucuk-senjata-di-sekolah-swasta-di-pondok-pinang-jakarta-selatan-1786014363566_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I429" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Kera Ekor Panjang Serang Warga Inhil, 18 Orang Jadi Korban</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:34:18 +0700</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr">
+        <is>
+          <t>Kera ekor panjang menyerang permukiman di Tembilahan, Riau, melukai 18 warga. Pemerintah setempat meningkatkan kewaspadaan dan penanganan.</t>
+        </is>
+      </c>
+      <c r="F430" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608101/kera-ekor-panjang-serang-warga-inhil-18-orang-jadi-korban</t>
+        </is>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/10/05/kera-ekor-panjang-di-kabupaten-gunungkidul-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Mail Syahputra, Asisten Nikita Mirzani Ajukan PK Dugaan TTPU dan Pemerasan</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:24:54 +0700</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr">
+        <is>
+          <t>Ismail Marzuki, asisten Nikita Mirzani, ajukan PK atas dugaan pemerasan dan TPPU. Kuasa hukum kritik kekhilafan hakim dalam penerapan UU ITE.</t>
+        </is>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608269/mail-syahputra-asisten-nikita-mirzani-ajukan-pk-dugaan-ttpu-dan-pemerasan</t>
+        </is>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/07/24/nikita-mirzani-jalani-sidang-ttpu-1753328999013_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>Fakta Lain soal Anak Vicky Prasetyo dengan Fangfang</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:03:13 +0700</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr">
+        <is>
+          <t>Fangfang mengungkap ketidakterbukaan Vicky Prasetyo tentang jumlah anaknya. Dia terkejut mengetahui anak yang dikandungnya adalah anak kesembilan.</t>
+        </is>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608140/fakta-lain-soal-anak-vicky-prasetyo-dengan-fangfang</t>
+        </is>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/17/fangfang-1784271583661_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Pawzia Bikin Heboh Lewat Selain Donatur Dilarang Ngatur</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:37:41 +0700</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Pawzia merilis lagu terbaru Selain Donatur Dilarang Ngatur yang viral. Meski bahagia, ia menghadapi perbandingan dengan Veni Nur yang menyakitkan.</t>
+        </is>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/music/d-8608098/pawzia-bikin-heboh-lewat-selain-donatur-dilarang-ngatur</t>
+        </is>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/pawzia-1786073508427_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Tantang Titi Kamal hingga Sarah Tumiwa Bintangi Perumahan Laddaland</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:25:58 +0700</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Titi Kamal bintangi film horor psikologis Perumahan Laddaland. Titi Kamal hingga Sarah Tumiw amenceritakan tantangan membintangi film tersebut.</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/movie/d-8607954/tantang-titi-kamal-hingga-sarah-tumiwa-bintangi-perumahan-laddaland</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/film-perumahan-laddaland-1786066142597_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Simulasi Ranking FIFA Indonesia vs Singapura di Piala AFF 2026, Menang Jadi Harga Mati</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:49:28 +0700</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>Simulasi hitungan ranking FIFA Timnas Indonesia vs Singapura di Piala AFF 2026, Garuda wajib menang jika tak ingin lengser.</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7865194/simulasi-ranking-fifa-indonesia-vs-singapura-di-piala-aff-2026-menang-jadi-harga-mati</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/yNQRBwgJz2YPPsUobmy3fY0wL6Y=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Piala-AFF-2026-Timnas-Indonesia-Tekuk-Timor-Leste-3-0_20260731_231927.jpg</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Penemuan 995 Senpi di Sekolah Jaksel, Ketua Komisi X DPR RI: 'Ini Persoalan Serius'</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:49:23 +0700</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>Ketua Komisi X DPR meminta polisi mengusut temuan 995 senjata di sekolah Jaksel. Perbakin menyebutnya airsoft gun untuk olahraga</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7865193/penemuan-995-senpi-di-sekolah-jaksel-ketua-komisi-x-dpr-ri-ini-persoalan-serius</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/c23bmk4PHY76ZCmOECtNP5j3wK4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ratusan-senjata-api-di-sekolah-swasta-Pondok-Pinang-Kebayoran-Lama-Jakarta-Selatan.jpg</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Kode Redeem FF Terbaru Hari Ini, Jumat 7 Agustus 2026: Klaim Hadiahnya Secara Gratis</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:48:10 +0700</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>Kumpulan kode redeem Free Fire terbaru pada hari ini, Jumat (7/8/2026) di laman reward.ff.garena.com, klaim kodenya dan dapat hadiah gratisnya.</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/techno/7865192/kode-redeem-ff-terbaru-hari-ini-jumat-7-agustus-2026-klaim-hadiahnya-secara-gratis</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/8I9GRYZwCbjGkKc3Ukw81342xcw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/bermain-gim-Garena-Free-Fire-FF-baru-saja.jpg</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Kementerian Luar Negeri Himpun Masukan Multipihak, Perkuat Diplomasi Dekarbonisasi</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:42:24 +0700</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>Masukan peserta akan menjadi bahan pendalaman dalam pertemuan dengan tenant dan kunjungan lapangan ke KEK Batang.</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865191/kementerian-luar-negeri-himpun-masukan-multipihak-perkuat-diplomasi-dekarbonisasi</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/3-KA1NYO2DeLd13wC1FvminrfdU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/iplomasi-dekarbonisasi-qw.jpg</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Timnas Voli Putra Indonesia Genjot Fisik Jelang Asian Games 2026, Dony Haryono: Latihan Semi Militer</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:42:11 +0700</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>Timnas voli putra Indonesia menggenjot fisik jelang Asian Games 2026, Dony Haryono ikutan nimbrung dan sampai menyebutnya "latihan semi militer".</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7865190/timnas-voli-putra-indonesia-genjot-fisik-jelang-asian-games-2026-dony-haryono-latihan-semi-militer</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/8n95cKP3vY7IbrPEMcOvww5MSpU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/GAGAL-KE-FINAL-Asa-Timnas-voli-putra-Indonesia.jpg</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Mahfud MD Setuju Kabinet Bayangan Dibentuk: Pemerintahan Prabowo Menteri-menterinya Agak Lemah</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:42:09 +0700</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>Eks Menkopolhukam RI Mahfud MD menilai, dibentuknya Kabinet Bayangan oleh Koalisi Masyarakat Sipil pada 27 Juli 2026 tidak jadi masalah.</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865189/mahfud-md-setuju-kabinet-bayangan-dibentuk-pemerintahan-prabowo-menteri-menterinya-agak-lemah</t>
+        </is>
+      </c>
+      <c r="H440" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/m1cHCktOUEc2P8dLa7Hi6MrNrcc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Mahfud-MD-Bicara-soal-Kasus-Saiful-Mujani_1.jpg</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Sosok Pelaku Pembunuhan Marbot Masjid di Purwakarta, Sakit Hati dengan Ucapan Korban</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:40:40 +0700</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr">
+        <is>
+          <t>Marbut masjid di Purwakarta tewas dibacok tetangganya akibat sakit hati sering dihina pengangguran. Pelaku ditangkap dengan ancaman 15 tahun penjara.</t>
+        </is>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865188/sosok-pelaku-pembunuhan-marbot-masjid-di-purwakarta-sakit-hati-dengan-ucapan-korban</t>
+        </is>
+      </c>
+      <c r="H441" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/iVQoFd00f4I54X3zKDiHAJJIyGM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Marbot-Masjid-Tewas.jpg</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Harga Emas Antam Hari Ini, Jumat 7 Agustus 2026: Terjun di Level Rp2.650.000 per Gram</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:38:19 +0700</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr">
+        <is>
+          <t>Harga emas pada hari ini, Jumat (7/8/2026), terjun drastis di level Rp 2.650.000, simak rincian harga emas terbarunya.</t>
+        </is>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7865187/harga-emas-antam-hari-ini-jumat-7-agustus-2026-terjun-di-level-rp2650000-per-gram</t>
+        </is>
+      </c>
+      <c r="H442" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/J5yz2H6KghKOYYUDkxXa0zEptx0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Harga-Emas-Antam-Naik_20251007_212034.jpg</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Persiapan India sebagai Tuan Rumah Kejuaraan Dunia BWF 2026, Cegah Burung dan Monyet Masuk Arena</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:37:29 +0700</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr">
+        <is>
+          <t>India selaku tuan rumah menyiapkan langkah antisipasi guna mencegah burung dan monyet masuk arena jelang Kejuaraan Dunia BWF 2026.</t>
+        </is>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7865186/persiapan-india-sebagai-tuan-rumah-kejuaraan-dunia-bwf-2026-cegah-burung-dan-monyet-masuk-arena</t>
+        </is>
+      </c>
+      <c r="H443" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/SKgoLpkjtyOCGf319vgkqeLC20M=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/India-Open-kotoran-Burung-Loh-Kean-Yae.jpg</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban IPAS Kelas 6 SD Kurikulum Merdeka Hal 161 Edisi Revisi: Ayo, Simpulkan</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:37:02 +0700</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr">
+        <is>
+          <t>Simak berikut merupakan kunci jawaban buku pelajaran IPAS kelas 6 SD/MI Kurikulum Merdeka (Edisi Revisi) halaman 161 bab 6: Ayo, Simpulkan</t>
+        </is>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7865185/kunci-jawaban-ipas-kelas-6-sd-kurikulum-merdeka-hal-161-edisi-revisi-ayo-simpulkan</t>
+        </is>
+      </c>
+      <c r="H444" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/O6GemeIcgrqlBjxOSV1OQuh-qRw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Siswa-Tetap-Semangat-Masuk-Sekolah-Setelah-Libur-Lebaran-2026_20260330_123016.jpg</t>
+        </is>
+      </c>
+      <c r="I444" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Banyak Ibu Kejar Stok ASI sampai Freezer Penuh, Dokter Ingatkan Risiko Mastitis karena Oversupply</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:34:49 +0700</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr">
+        <is>
+          <t>Banyak ibu berlomba memperlihatkan freezer penuh Tren menyimpan stok ASI dalam jumlah besar semakin sering terlihat di media sosial.</t>
+        </is>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7865184/banyak-ibu-kejar-stok-asi-sampai-freezer-penuh-dokter-ingatkan-risiko-mastitis-karena-oversupply</t>
+        </is>
+      </c>
+      <c r="H445" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/deqyqX9iXfkTNmFZ7ai7E69o1T8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/asi-eksklusif-2-0313.jpg</t>
+        </is>
+      </c>
+      <c r="I445" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Bareskrim Bongkar Sarang Narkoba di Kelab Malam Bali, Dikendalikan Manajemen, 53 Orang Diamankan</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:33:31 +0700</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr">
+        <is>
+          <t>Bareskrim bongkar sarang narkoba yang beroperasi di kelab malam bernama Five Star di Kota Denpasar, Bali pada Jumat (7/8/2026) dini hari</t>
+        </is>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865183/bareskrim-bongkar-sarang-narkoba-di-kelab-malam-bali-dikendalikan-manajemen-53-orang-diamankan</t>
+        </is>
+      </c>
+      <c r="H446" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/c3WhMmS7ZqVfAXc7O59KV7fKwsI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/peredaran-narkoba-di-Five-Star-di-Denpasar-Bali.jpg</t>
+        </is>
+      </c>
+      <c r="I446" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>RB Leipzig Sindir Fabrizio Romano saat Resmikan Transfer Yan Diomande ke Real Madrid</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:28:07 +0700</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr">
+        <is>
+          <t>RB Leipzig sindir Fabrizio Romano saat umumkan transfer Yann Diomande ke Real Madrid dengan kalimat "HERE WE ACTUALLY GO".</t>
+        </is>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7865182/rb-leipzig-sindir-fabrizio-romano-saat-resmikan-transfer-yan-diomande-ke-real-madrid</t>
+        </is>
+      </c>
+      <c r="H447" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/E54RA_I8M15KG7G9nmg6eXOU94s=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Logo-klub-Real-Madrid.jpg</t>
+        </is>
+      </c>
+      <c r="I447" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Terungkap Lokasi Rumah Sakit dan Alasan Yurizal Pasien BPJS yang Menunggu 8 Jam Sebelum Meninggal</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:27:50 +0700</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr">
+        <is>
+          <t>Kasus komentar niremapti nakes dan dokter pada pasien BPJS viral.Hebohnya kasus ini mengungkap fakta lokasi rumah sakit yang dimaksud.</t>
+        </is>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7865181/terungkap-lokasi-rumah-sakit-dan-alasan-yurizal-pasien-bpjs-yang-menunggu-8-jam-sebelum-meninggal</t>
+        </is>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/JpmCUL7yNHEkxI9Hn17BoXEHfGw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ramli-di-rscm.jpg</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>Ketua KPU Kotawaringin Timur Beserta 4 Komisioner Tersangka Dugaan Korupsi Dana Hibah Pilkada 2024</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:27:39 +0700</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>Lima Komisioner KPU Kotawaringin Timur ditetapkan sebagai tersangka dugaan korupsi dana hibah Pilkada 2024.</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865180/ketua-kpu-kotawaringin-timur-beserta-4-komisioner-tersangka-dugaan-korupsi-dana-hibah-pilkada-2024</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/_CftJ4Pu8xm_7GEGubhbQ5d30Xs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Komisioner-KPU-Kotim-Tersangka_1.jpg</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Mantan Manajer Sarwendah Ungkap Kondisi Kesehatan Ruben Onsu di Tengah Isu Penyakit Kronis</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:20:14 +0700</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>Mantan manajer Sarwendah, Nanda Persada mengungkap kondisi kesehatan Ruben Onsu setelah muncul isu penyakit kronis.</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865179/mantan-manajer-sarwendah-ungkap-kondisi-kesehatan-ruben-onsu-di-tengah-isu-penyakit-kronis</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ZG3_PDED1CjlCCKn-J5WB8tswOA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ruben-Onsu-KPAI.jpg</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban Bahasa Indonesia Kelas 9 Halaman 56, 57, 58 Edisi Revisi Latihan 1</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:20:09 +0700</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr">
+        <is>
+          <t>Kunci jawaban Bahasa Indonesia kelas 9 halaman 56, 57, 58 Kurikulum Merdeka Edisi Revisi, Latihan 1 Bab 2 Belajar Berpantun.</t>
+        </is>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7865178/kunci-jawaban-bahasa-indonesia-kelas-9-halaman-56-57-58-edisi-revisi-latihan-1</t>
+        </is>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/FBmkDqYmlx5UM0pD7_3NuyX3Hwc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/SISWA-SMP-BELAJAR-10.jpg</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Tim 9 Kejagung Jemput Eks Jampidsus Febrie Adriansyah di KPK Siang Ini</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:19:56 +0700</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr">
+        <is>
+          <t>Tim 9 Kejagung bersiap melakukan pemeriksaan lanjutan terhadap mantan Jampidsus Febrie Adriansyah terkait kasus dugaan TPPU.</t>
+        </is>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865177/tim-9-kejagung-jemput-eks-jampidsus-febrie-adriansyah-di-kpk-siang-ini</t>
+        </is>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/gNaM9P5dS5GBE26SM6ozbYNMZJE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/mobil-siap-jemput-febrie-adriansyah-diperiksa-tim-9.jpg</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban IPAS 6 SD Kurikulum Merdeka Hal 167 Edisi Revisi: Satelit dan Teknologi Antariksa</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:19:31 +0700</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr">
+        <is>
+          <t>Berikut merupakan kunci jawaban buku pelajaran IPAS kelas 6 SD/MI Kurikulum Merdeka (Edisi Revisi) halaman 167 bab 6: Satelit dan Teknologi Antariksa</t>
+        </is>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7865176/kunci-jawaban-ipas-6-sd-kurikulum-merdeka-hal-167-edisi-revisi-satelit-dan-teknologi-antariksa</t>
+        </is>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Q5yW0uMJfi6M5C8kylsmRdOWTcs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Siswa-Tetap-Semangat-Masuk-Sekolah-Setelah-Libur-Lebaran-2026_20260330_123000.jpg</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>SPK: Pernyataan Kampus soal Gaji Dosen Rp20-50 Juta Malah Timbulkan Polemik Baru</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:15:16 +0700</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr">
+        <is>
+          <t>SPK menilai klaim gaji dosen Rp20 juta-Rp50 juta memicu polemik. Mereka menegaskan angka itu bukan gaji pokok, melainkan termasuk tunjangan</t>
+        </is>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865175/spk-pernyataan-kampus-soal-gaji-dosen-rp20-50-juta-malah-timbulkan-polemik-baru</t>
+        </is>
+      </c>
+      <c r="H454" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/0GLE2g4P6afy-H0qs5aPIaR9ZVQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Sidang-gaji-dosen-di-MK.jpg</t>
+        </is>
+      </c>
+      <c r="I454" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Pertanian</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>Pupuk Kaltim Kembangkan Agrowisata Berbasis Pertanian di Gowa</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:05:26 +0700</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – PT Pupuk Kalimantan Timur (Pupuk Kaltim) meresmikan Kampung Sawah Abadi (KSA) Bulutana di Kabupaten Gowa, Sulawesi Selatan, sebagai kawasan yang mengintegrasikan pertanian berkelanjutan dengan agrowisata. Program tersebut...</t>
+        </is>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjdxzl416/pupuk-kaltim-kembangkan-agrowisata-berbasis-pertanian-di-gowa</t>
+        </is>
+      </c>
+      <c r="H455" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260807130500-912.png</t>
+        </is>
+      </c>
+      <c r="I455" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Braze Perkuat Customer Engagement Berbasis AI di Indonesia</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:42:11 +0700</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA — Braze, platform customer engagement global terkemuka, mengumumkan bahwa PT Pertamina Patra Niaga, unit usaha ritel dan distribusi dari perusahaan energi milik negara Indonesia, serta PT Telkomsel,...</t>
+        </is>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjdx6b370/braze-perkuat-customer-engagement-berbasis-ai-di-indonesia</t>
+        </is>
+      </c>
+      <c r="H456" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260807124137-824.png</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Pertanian</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Amran Perintahkan Bulog Segera Kirim Beras SPHP ke Alor Untuk Netralisir Harga</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:44:01 +0700</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Kepala Badan Pangan Nasional (Bapanas) Andi Amran Sulaiman memerintahkan Perum Bulog segera mengirimkan beras program Stabilisasi Pasokan dan Harga Pangan (SPHP) ke Kabupaten Alor, Nusa Tenggara...</t>
+        </is>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjduhd370/amran-perintahkan-bulog-segera-kirim-beras-sphp-ke-alor-untuk-netralisir-harga</t>
+        </is>
+      </c>
+      <c r="H457" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/057218600-1771936201-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Kejagung Jemput Febrie Adriansyah di Rutan KPK</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:57:59 +0700</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr">
+        <is>
+          <t>Febrie akan menjalani pemeriksaan lanjutan terkait kasus TPPU.</t>
+        </is>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264134/kejagung-jemput-febrie-adriansyah-di-rutan-kpk</t>
+        </is>
+      </c>
+      <c r="H458" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/KHyKZj-hqnufk-4rOxO_1qVv9P8=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317957/original/009574100_1786082243-IMG_20260807_113438_2.jpg</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Profil Muhammad Soleh Pengacara No Viral No Justice, Warisannya Mengubah Sistem Pemilu</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:14:38 +0700</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr">
+        <is>
+          <t>Gugatan yang diajukan pada 2008 bukan sekadar memenangkan sengketa, melainkan mengubah cara rakyat memilih wakilnya di parlemen.</t>
+        </is>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264111/profil-muhammad-soleh-pengacara-no-viral-no-justice-warisannya-mengubah-sistem-pemilu</t>
+        </is>
+      </c>
+      <c r="H459" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/_n4mLUYf1d8_RgZK65k5kyBXjT4=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317874/original/090240100_1786076097-079028200_1786075648-IMG-20260807-WA0005.webp</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Hype</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Oasis Dikabarkan Reuni Akhir Tahun 2026</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:08:29 +0700</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr">
+        <is>
+          <t>Oasis dikabarkan akan gelar reuni akhir tahun 2026, berniat kumpulkan semua anggota</t>
+        </is>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/hype/read/2026/08/07/130702166/oasis-dikabarkan-reuni-akhir-tahun-2026</t>
+        </is>
+      </c>
+      <c r="H460" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/yDZlmZp-eGtEdBECat7fnJnH2ns=/0x0:660x440/1200x675/filters:watermark(data/photo/2026/01/30/697c8191ee571.png,0,-0,1)/data/photo/2022/03/19/62358c5f714ec.jpg</t>
+        </is>
+      </c>
+      <c r="I460" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>Dinkes DKI Pastikan Nakes yang Diduga Cibir Pasien BPJS Tak Bekerja di Faskes Pemprov</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:08:29 +0700</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr">
+        <is>
+          <t>Kadinkes DKI Ani Ruspitawati mengatakan, salah satu dari nakes yang diduga mencibir pasien BPJS Kesehatan memang bekerja di salah satu RS di Jakarta.</t>
+        </is>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/07/12401801/dinkes-dki-pastikan-nakes-yang-diduga-cibir-pasien-bpjs-tak-bekerja-di</t>
+        </is>
+      </c>
+      <c r="H461" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/_9yh_0xHF8tK9nA7GDO3b_Ou0Sc=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/05/11/6a01c0d6bef91.jpg</t>
+        </is>
+      </c>
+      <c r="I461" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Jelang Pemeriksaan Febrie, Mobil Tahanan Kejagung Parkir di Rutan KPK</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:08:29 +0700</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr">
+        <is>
+          <t>Eks Jampidsus Febrie Adriansyah diperiksa KPK terkait dugaan TPPU. Mobil tahanan Jaksa Agung Muda Bidang Pidana Khusus tiba di Rutan KPK hari ini.</t>
+        </is>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/07/12132031/jelang-pemeriksaan-febrie-mobil-tahanan-kejagung-parkir-di-rutan-kpk</t>
+        </is>
+      </c>
+      <c r="H462" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/teM9JptxduI7Gzwj_RBDnH-LtyY=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/07/6a75652fe9a0b.jpeg</t>
+        </is>
+      </c>
+      <c r="I462" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I370"/>
+  <autoFilter ref="A1:I462"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-07.xlsx
+++ b/data/berita_2026-08-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$462</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$542</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I462"/>
+  <dimension ref="A1:I542"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -22147,8 +22147,3768 @@
         </is>
       </c>
     </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Zverev susul Sinner lolos ke ATP Finals 2026</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:48:57 +0700</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr">
+        <is>
+          <t>Petenis Jerman Alexander Zverev menjadi petenis kedua yang memastikan tiket ke turnamen penutup musim ATP Finals 2026 ...</t>
+        </is>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683944/zverev-susul-sinner-lolos-ke-atp-finals-2026</t>
+        </is>
+      </c>
+      <c r="H463" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/09/IMG_0011.jpeg</t>
+        </is>
+      </c>
+      <c r="I463" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>Korban tewas penembakan sekolah dekat Bangkok jadi 7 orang</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:45:04 +0700</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr">
+        <is>
+          <t>Korban tewas dalam insiden penembakan di sebuah sekolah dekat Bangkok, Thailand, dikonfirmasi bertambah menjadi ...</t>
+        </is>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683939/korban-tewas-penembakan-sekolah-dekat-bangkok-jadi-7-orang</t>
+        </is>
+      </c>
+      <c r="H464" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/XxjpbeE000054_20260807_PEPFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I464" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>API: Pertumbuhan industri TPT cerminkan pemulihan yang makin kuat</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:38:57 +0700</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Umum Asosiasi Pertekstilan Indonesia (API) Ian Syarif mengatakan pertumbuhan industri tekstil dan pakaian ...</t>
+        </is>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683929/api-pertumbuhan-industri-tpt-cerminkan-pemulihan-yang-makin-kuat</t>
+        </is>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/07/17/daya-saing-produk-manufaktur-domestik-di-pasar-ekspor-2576249.jpg</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Kementan: Panen padi program PM-AAS di Sidrap tembus 11,2 ton/hektare</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:37:35 +0700</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian menyatakan panen padi perdana program Pertanian Modern–Advanced Agricultural System ...</t>
+        </is>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683919/kementan-panen-padi-program-pm-aas-di-sidrap-tembus-112-ton-hektare</t>
+        </is>
+      </c>
+      <c r="H466" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/174A08BF-EF84-4444-84DC-7D039EC7FFC4_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I466" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Penembakan sekolah dekat Bangkok tewaskan 2 orang, 20 terluka</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:34:20 +0700</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr">
+        <is>
+          <t>Insiden penembakan di sebuah sekolah di Provinsi Nonthaburi, Thailand, menyebabkan sedikitnya dua orang meninggal ...</t>
+        </is>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683908/penembakan-sekolah-dekat-bangkok-tewaskan-2-orang-20-terluka</t>
+        </is>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/XxjpbeE000055_20260807_PEPFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Bolehkah satu rumah punya 2 meteran listrik? Ini penjelasannya</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:01:42 +0700</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr">
+        <is>
+          <t>Memiliki dua meteran listrik dalam satu rumah ternyata bukan hal yang mustahil. Kondisi ini dapat dilakukan apabila ...</t>
+        </is>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684100/bolehkah-satu-rumah-punya-2-meteran-listrik-ini-penjelasannya</t>
+        </is>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/16/1000214974.jpg</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Politik</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Berapa gaji Paskibraka Nasional 2026? Ini uang saku dan bonusnya</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:04:14 +0700</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr">
+        <is>
+          <t>Paskibraka Nasional menjadi salah satu bagian penting dalam upacara peringatan Hari Ulang Tahun (HUT) Kemerdekaan ...</t>
+        </is>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5683855/berapa-gaji-paskibraka-nasional-2026-ini-uang-saku-dan-bonusnya</t>
+        </is>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/latihan-paskibraka-nasional-tingkat-pusat-2832963.jpg</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Isu Reshuffle Agustus, Mensesneg: Kalaupun Ada untuk Isi Wamen Kosong</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:47:50 +0700</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara (Mensesneg) Prasetyo Hadi merespons isu mengenai bakal adanya perombakan kabinet atau reshuffle di bulan Agustus.</t>
+        </is>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608556/isu-reshuffle-agustus-mensesneg-kalaupun-ada-untuk-isi-wamen-kosong</t>
+        </is>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/18/menteri-sekretaris-negara-mensesneg-prasetyo-hadi-anggi-mdetikcom-1771412206075_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>2 Anjing K9 Polri Cari Kaki Korban Mutilasi di Depok: Roby dan Dasa</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:43:46 +0700</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr">
+        <is>
+          <t>Dua ekor anjing pelacak dikerahkan mencari kaki pria berinisial K (51), korban mutilasi di Cipayung, Depok. Kedua anjing itu punya spesialisasi masing-masing.</t>
+        </is>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608541/2-anjing-k9-polri-cari-kaki-korban-mutilasi-di-depok-roby-dan-dasa</t>
+        </is>
+      </c>
+      <c r="H471" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/dua-ekor-anjing-pelacak-dikerahkan-mencari-kaki-pria-berinisial-k-51-korban-mutilasi-di-cipayung-depok-kedua-anjing-itu-punya--1786088465464_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I471" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Polisi Pastikan Kegiatan Belajar di Sekolah Jaksel Normal Usai Temuan Senpi</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:40:03 +0700</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>Taufiq Syarifudin</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr">
+        <is>
+          <t>Polisi menyelidiki temuan 995 airsoft gun dan senjata api di sekolah Jakarta Selatan. Polisi memastikan kegiatan belajar tetap normal.</t>
+        </is>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608536/polisi-pastikan-kegiatan-belajar-di-sekolah-jaksel-normal-usai-temuan-senpi</t>
+        </is>
+      </c>
+      <c r="H472" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temuan-ratusan-pucuk-senjata-di-sekolah-swasta-di-pondok-pinang-jakarta-selatan-1786014363566_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I472" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Sahroni Minta Temuan 995 Senjata di Sekolah Swasta Jaksel Diusut hingga Akar</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:37:58 +0700</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t>Ahmad Sahroni meminta temuan 995 senjata di sekolah Kebayoran Lama, Jakarta Selatan (Jaksel), diusut hingga akar. Sahroni menilai temuan tersebut tidak wajar.</t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608534/sahroni-minta-temuan-995-senjata-di-sekolah-swasta-jaksel-diusut-hingga-akar</t>
+        </is>
+      </c>
+      <c r="H473" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/wakil-ketua-komisi-iii-dpr-ahmad-sahroni-1785822730689_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I473" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Kurang Optimal, Kawasan Industri Serang Barat Bakal Ditata Ulang</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:31:45 +0700</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr">
+        <is>
+          <t>Gubernur Banten Andra Soni menyebut penataan kawasan industri di Serang Barat masih kurang optimal.</t>
+        </is>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608521/kurang-optimal-kawasan-industri-serang-barat-bakal-ditata-ulang</t>
+        </is>
+      </c>
+      <c r="H474" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/10/gubernur-banten-andra-soni-1775807404673_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I474" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Polisi Tangkap Pelaku Penyayat Leher Warga di Depok</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:30:58 +0700</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr">
+        <is>
+          <t>Pelaku ditangkap di Jalan Margonda Raya, Depok pada Kamis (6/8). Pelaku terancam Pasal 467 KUHP dengan pidana penjara maksimal tujuh tahun penjara.</t>
+        </is>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608519/polisi-tangkap-pelaku-penyayat-leher-warga-di-depok</t>
+        </is>
+      </c>
+      <c r="H475" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/polisi-tangkap-pelaku-penyerangan-terhadap-warga-di-depok-dokistimewa-1786087228399_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I475" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>Karhutla 100 Hektare Lahan di Banggai Diduga Gegara Puntung Rokok Pemotor</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:28:06 +0700</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>Rangga Musabar</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>Sekitar 100 hektare lahan terbakar di Desa Toipan, Kecamatan Pagimana, Kabupaten Banggai, Sulawesi Tengah (Sulteng). Kebakaran itu diduga dipicu puntung rokok.</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608514/karhutla-100-hektare-lahan-di-banggai-diduga-gegara-puntung-rokok-pemotor</t>
+        </is>
+      </c>
+      <c r="H476" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kebakaran-hutan-dan-lahan-karhutla-melanda-desa-toipan-1786076194618_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I476" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Warga Harap Stasiun Gunung Putri Diaktifkan Lagi: Supaya Nggak Jauh ke Nambo</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:14:47 +0700</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t>Warga sekitar Stasiun Gunung Putri, Bogor, berharap stasiun nonaktif ini segera beroperasi kembali untuk akses transportasi yang lebih dekat ke Jakarta.</t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608488/warga-harap-stasiun-gunung-putri-diaktifkan-lagi-supaya-nggak-jauh-ke-nambo</t>
+        </is>
+      </c>
+      <c r="H477" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kondisi-stasiun-gunung-putri-bogor-yang-kini-terbengkalai-1786080454648_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I477" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>BRIN Pamerkan Teknologi Nuklir ke Prabowo, Mensesneg: untuk Energi dan Medis</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:09:41 +0700</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr">
+        <is>
+          <t>BRIN menampilkan hasil riset terkait teknologi nuklir di depan Prabowo. Mensesneg mengatakan teknologi nuklir yang dipamerkan itu untuk energi dan medis.</t>
+        </is>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608476/brin-pamerkan-teknologi-nuklir-ke-prabowo-mensesneg-untuk-energi-dan-medis</t>
+        </is>
+      </c>
+      <c r="H478" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/mensesneg-prasetyo-hadi-1784627991720_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I478" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>2 Turis India Bawa Ganja Pasta Rp 1,5 M ke Bali Modus Kotak Mainan</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:59:02 +0700</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>Fabiola Dianira</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr">
+        <is>
+          <t>Dua turis India ditangkap di Bandara Ngurah Rai, Bali, membawa ganja pasta senilai Rp 1,5 miliar. Narkotika disamarkan dalam kotak mainan anak.</t>
+        </is>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608464/2-turis-india-bawa-ganja-pasta-rp-1-5-m-ke-bali-modus-kotak-mainan</t>
+        </is>
+      </c>
+      <c r="H479" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/wn-india-bawa-ganja-1786082807295_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I479" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Pejalan Kaki di Bogor Tewas Usai Tersenggol Motor lalu Tertabrak Truk</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:57:59 +0700</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr">
+        <is>
+          <t>Seorang pejalan kaki berinisial Y tewas dalam kecelakaan di Jalan Raya Klapanunggal, Bogor. Korban meninggal dunia usai tersenggol motor lalu tertabrak truk.</t>
+        </is>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608456/pejalan-kaki-di-bogor-tewas-usai-tersenggol-motor-lalu-tertabrak-truk</t>
+        </is>
+      </c>
+      <c r="H480" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2016/10/31/e530c053-3487-4654-a642-b6d7fb610779_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I480" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Pakai Rompi Tahanan dan Diborgol, Febrie Tiba di Kejagung untuk Diperiksa Tim 9</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:46:27 +0700</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr">
+        <is>
+          <t>Mantan Jaksa Agung Muda bidang Tindak Pidana Khusus (Jampidsus) Kejagung, Febrie Adriansyah (FA), tiba di Kejagung untuk diperiksa.</t>
+        </is>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608435/pakai-rompi-tahanan-dan-diborgol-febrie-tiba-di-kejagung-untuk-diperiksa-tim-9</t>
+        </is>
+      </c>
+      <c r="H481" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/febrie-adriansyah-tiba-di-kejagung-kurniawandetikcom-1786085169134_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I481" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Perawat RSUD Cicalengka Cibir Pasien BPJS 'Tidur di Kamar Mandi' Dinonaktifkan</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:43:32 +0700</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>Yuga Hassani</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr">
+        <is>
+          <t>RSUD Cicalengka, Kabupaten Bandung, menonaktifkan Nieke Adelia Marlina dari tugas pelayanan.</t>
+        </is>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608432/perawat-rsud-cicalengka-cibir-pasien-bpjs-tidur-di-kamar-mandi-dinonaktifkan</t>
+        </is>
+      </c>
+      <c r="H482" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/01/05/rsud-cicalengka-bandung_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I482" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Kata Petinggi Parpol soal Isu Reshuffle, Kabarnya Usai 17 Agustus</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:36:09 +0700</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr">
+        <is>
+          <t>Isu adanya reshuffle kabinet Presiden Prabowo Subianto setelah 17 Agustus mencuat ke publik. Sejumlah petinggi parpol merespons isu tersebut.</t>
+        </is>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608408/kata-petinggi-parpol-soal-isu-reshuffle-kabarnya-usai-17-agustus</t>
+        </is>
+      </c>
+      <c r="H483" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/presiden-prabowo-menggelar-sidang-kabinet-paripurna-di-istana-negara-jakarta-selasa-2172026-1784625687891_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I483" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Polisi Cek Izin Ratusan Senjata yang Ditemukan di Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:26:13 +0700</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>Taufiq Syarifudin</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr">
+        <is>
+          <t>Penyelidikan polisi terkait temuan 995 senjata di yayasan sekolah Pondok Pinang, Jakarta Selatan, meliputi kepemilikan dan perizinan senjata.</t>
+        </is>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608399/polisi-cek-izin-ratusan-senjata-yang-ditemukan-di-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H484" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kasie-humas-polres-metro-jakarta-selatan-akp-joko-adiwibowo-1786083942095_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I484" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>Alun-alun Suryakencana Terbakar, Pendakian Gunung Gede Ditutup 4 Hari</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:24:39 +0700</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>Muchamad Sholihin</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr">
+        <is>
+          <t>Aktivitas pendakian Taman Nasional Gunung Gede-Pangrango (TNGGP) ditutup 4 hari pasca-kebakaran Alun-alun Suryakencana Gunung Gede.</t>
+        </is>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608395/alun-alun-suryakencana-terbakar-pendakian-gunung-gede-ditutup-4-hari</t>
+        </is>
+      </c>
+      <c r="H485" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/gunung-gede-pangrango-kebakaran-1786025219821_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I485" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Jelang Porprov, Waka DPRD Surabaya Dorong Konsep Sportainment</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:18:53 +0700</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>Dea Duta Aulia</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr">
+        <is>
+          <t>Wakil Ketua DPRD Surabaya, Arif Fathoni, menilai persiapan Porprov 2027 belum signifikan. Ia dorong konsep sportainment untuk sukseskan acara.</t>
+        </is>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608383/jelang-porprov-waka-dprd-surabaya-dorong-konsep-sportainment</t>
+        </is>
+      </c>
+      <c r="H486" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/wakil-ketua-dprd-surabaya-arif-fathoni-1786083449440_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I486" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Bakal Diperiksa Tim 9, Febrie Adriansyah Pakai Rompi Tahanan dan Diborgol</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:16:44 +0700</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>Mulia Budi</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr">
+        <is>
+          <t>Tim 9 Kejaksaan Agung akan memeriksa mantan Jampidsus Febrie Adriansyah (FA) sebagai tersangka kasus korupsi dan dugaan tindak pidana pencucian uang (TPPU).</t>
+        </is>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608382/bakal-diperiksa-tim-9-febrie-adriansyah-pakai-rompi-tahanan-dan-diborgol</t>
+        </is>
+      </c>
+      <c r="H487" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/febrie-adriansyah-muliadetikcom-1786083384950_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I487" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Ombudsman Minta OPD DKI Gercep Respons Keluhan Warga: Jangan Keduluan Gubernur</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:06:43 +0700</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t>Ombudsman meminta jajaran OPD harus lebih dahulu mengetahui persoalan di lapangan dibandingkan seorang gubernur.</t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608377/ombudsman-minta-opd-dki-gercep-respons-keluhan-warga-jangan-keduluan-gubernur</t>
+        </is>
+      </c>
+      <c r="H488" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/anggota-ombudsman-ri-fikri-yasin-beliadetikcom-1786082685594_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I488" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Pengelola Ungkap Kebakaran 120 Ha Lahan di Gunung Bromo Dipicu Ulah Manusia</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:06:09 +0700</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>Muhammad Aminudin</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr">
+        <is>
+          <t>Kebakaran di kawasan Gunung Bromo mencapai 120 hektare. Kebakaran itu disebut bukan karena faktor cuaca, melainkan karena ulah manusia.</t>
+        </is>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608372/pengelola-ungkap-kebakaran-120-ha-lahan-di-gunung-bromo-dipicu-ulah-manusia</t>
+        </is>
+      </c>
+      <c r="H489" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/kebakaran-bromo-1786017621738_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Ngeri! Pria di Depok Tiba-tiba Diserang OTK, Leher Disabet Cutter</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:05:26 +0700</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr">
+        <is>
+          <t>Seorang pria diserang OTK saat menutup warung di Depok. Pelaku menyayat lehernya dengan cutter dan berhasil ditangkap dua hari setelah kejadian.</t>
+        </is>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608371/ngeri-pria-di-depok-tiba-tiba-diserang-otk-leher-disabet-cutter</t>
+        </is>
+      </c>
+      <c r="H490" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2019/10/11/cb064125-cf9b-4c42-9d95-af2459273f8f_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Puncak Musim Kemarau 2026 Tak Serempak di Agustus, Cek Wilayahmu</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:03:32 +0700</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>Widhia Arum Wibawana</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr">
+        <is>
+          <t>BMKG mengungkap puncak musim kemarau 2026 tidak serempak di Agustus. Setiap wilayah Indonesia memiliki waktu puncak berbeda. Cek informasi lengkapnya!</t>
+        </is>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608242/puncak-musim-kemarau-2026-tak-serempak-di-agustus-cek-wilayahmu</t>
+        </is>
+      </c>
+      <c r="H491" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/07/ilustrasi-musim-kemarau-1775529251407_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Mensesneg Sebut Prabowo Sudah Panggil Calon-calon Gubernur BI</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:56:29 +0700</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto disebut sudah mengagendakan pertemuan dengan beberapa nama calon Gubernur Bank Indonesia.</t>
+        </is>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8608573/mensesneg-sebut-prabowo-sudah-panggil-calon-calon-gubernur-bi</t>
+        </is>
+      </c>
+      <c r="H492" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/21/mensesneg-prasetyo-hadi-1784627991720_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Dana Asing Rp 17 T Mengalir ke Pinjol RI, Naik 34%</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:33:03 +0700</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>Otoritas Jasa Keuangan (OJK) mencatat pertumbuhan pembiayaan bagi industri pinjaman daring (pindar) di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8608525/dana-asing-rp-17-t-mengalir-ke-pinjol-ri-naik-34</t>
+        </is>
+      </c>
+      <c r="H493" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2020/02/04/0612942f-44fc-44b9-9d95-15801009ae90_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Kredit Macet 16 Pinjol di Atas 5%, OJK Perketat Pengawasan</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:14:29 +0700</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>Angka tersebut turun dibanding periode bulan sebelumnya, yakni sebanyak 18 penyelenggara pindar.</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8608487/kredit-macet-16-pinjol-di-atas-5-ojk-perketat-pengawasan</t>
+        </is>
+      </c>
+      <c r="H494" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/11/24/ilustrasi-pinjol_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I494" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Istana Pastikan Destry Damayanti Masuk Bursa Calon Gubernur BI</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:09:04 +0700</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>Herdi Alif Al Hikam</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr">
+        <is>
+          <t>Hal ini dikonfirmasi langsung oleh Menteri Sekretaris Negara Prasetyo Hadi.</t>
+        </is>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8608474/istana-pastikan-destry-damayanti-masuk-bursa-calon-gubernur-bi</t>
+        </is>
+      </c>
+      <c r="H495" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/menteri-sekretaris-negara-prasetyo-hadi-1786086397243_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I495" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Husein Sastranegara Bersolek Sambut Kembali Penerbangan Pesawat</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:56:49 +0700</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>Grandyos Zafna</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>Bandara Husein Sastranegara, Bandung, berbenah menjelang kembali melayani penerbangan komersial menggunakan pesawat jet berbadan sedang pada 14 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8608229/husein-sastranegara-bersolek-sambut-kembali-penerbangan-pesawat</t>
+        </is>
+      </c>
+      <c r="H496" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/persiapan-bandara-husein-sastranegara-jelang-pengoperasian-1786077660151.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I496" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Perhatian! MSCI Umumkan Rebalancing Saham Pekan Depan</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:02:06 +0700</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr">
+        <is>
+          <t>Hasil tinjauan tersebut mencakup sejumlah indeks saham global yang menjadi acuan investor institusi di seluruh dunia.</t>
+        </is>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/bursa-dan-valas/d-8608365/perhatian-msci-umumkan-rebalancing-saham-pekan-depan</t>
+        </is>
+      </c>
+      <c r="H497" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/01/30/ihsg-rebound-usai-dua-hari-anjlok-seiring-pengunduran-diri-dirut-bei-1769748663323_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I497" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Laporan Keuangan Semua K/L Dapat Opini WTP BPK, Tapi Ada Catatan</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:52:10 +0700</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>Seluruh Kementerian dan Lembaga meraih opini WTP dari BPK untuk laporan keuangan 2025. BPK menekankan pentingnya perbaikan berkelanjutan dalam tata kelola.</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8608239/laporan-keuangan-semua-k-l-dapat-opini-wtp-bpk-tapi-ada-catatan</t>
+        </is>
+      </c>
+      <c r="H498" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2017/05/26/0dadd724-78e9-4380-9aed-8a12fc2c4c57_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I498" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Jepang Pangkas Pajak Makanan Jadi 1% Mulai Tahun Depan</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:34:15 +0700</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr">
+        <is>
+          <t>Pemerintah Jepang menurunkan pajak konsumsi atas makanan menjadi 1% selama dua tahun mulai April 2027. Saat ini, tarif pajak konsumsi untuk makanan sebesar 8%.</t>
+        </is>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8608217/jepang-pangkas-pajak-makanan-jadi-1-mulai-tahun-depan</t>
+        </is>
+      </c>
+      <c r="H499" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/09/pm-jepang-sanae-takaichi-1770601688780_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I499" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>228 Pedagang Kripto Ilegal Disetop</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:30:32 +0700</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>Langkah ini dianggap sebagai upaya otoritas dalam memperkuat pengawasan dan mendukung pertumbuhan industri aset digital.</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/fintech/d-8608214/228-pedagang-kripto-ilegal-disetop</t>
+        </is>
+      </c>
+      <c r="H500" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/01/26/ilustrasi-cryptocurrency-atau-kripto_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I500" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Momen Haru Audellya Ambara Harsono Tampil di IWF</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:59:08 +0700</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>prih febriani</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t>Audellya Ambara Harsono, model muda dan Puteri Anak Indonesia Pendidikan, berbagi pengalaman berharga di Indonesia Fashion Week 2026.</t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608579/momen-haru-audellya-ambara-harsono-tampil-di-iwf</t>
+        </is>
+      </c>
+      <c r="H501" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/audellya-ambara-harsono-1786083385128_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I501" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>Abdel Achrian Bahagia Anak Jadi Mahasiswa ITB, Titip Pesan Ini</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:20:53 +0700</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr">
+        <is>
+          <t>Artis Abdel Achrian lagi berbahagia. Sebab anaknya telah resmi berkuliah di ITB (Institut Teknik Bandung).</t>
+        </is>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608490/abdel-achrian-bahagia-anak-jadi-mahasiswa-itb-titip-pesan-ini</t>
+        </is>
+      </c>
+      <c r="H502" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/abdel-achrian-1786086433729_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I502" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Bubah Alfian: Indonesia Kaya dan Banyak Talenta, tapi Kurang Kesempatan</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:11:03 +0700</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>MUA Bubah Alfian bahagia Jember Fashion Carnaval (JFC) 2026 sukses. Bubah punya pesan, Indonesia itu kaya dan punya banyak talenta, tapi kurang kesempatan.</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8607919/bubah-alfian-indonesia-kaya-dan-banyak-talenta-tapi-kurang-kesempatan</t>
+        </is>
+      </c>
+      <c r="H503" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/12/14/bubah-alfian-1765726534361_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I503" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>Uhuy! Daehoon Kasih Kejutan Ultah ke Diva Azzura</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:24:44 +0700</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t>Selebgram asal Korea, Daehoon, bikin netizen heboh. Hal itu terjadi setelah ia memberi kejutan ulang tahun ke Diva Azzura.</t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608384/uhuy-daehoon-kasih-kejutan-ultah-ke-diva-azzura</t>
+        </is>
+      </c>
+      <c r="H504" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/diva-azzura-1786083446351_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Vicky Prasetyo Dilaporkan Terkait Dugaan Penelantaran Anak</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:13:11 +0700</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr">
+        <is>
+          <t>Presenter Vicky Prasetyo dilaporkan oleh istrinya, Fangfang, ke Bareskrim Polri atas dugaan penelantaran anak dan tidak memenuhi kewajiban sebagai ayah.</t>
+        </is>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608378/vicky-prasetyo-dilaporkan-terkait-dugaan-penelantaran-anak</t>
+        </is>
+      </c>
+      <c r="H505" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/01/07/vicky-prasetyo_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Pelaku Penembakan di Sekolah Thailand Sempat Bunuh Kakek-Neneknya Sebelum Beraksi, 9 Orang Tewas</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:53:24 +0700</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr">
+        <is>
+          <t>Pelaku penembakan massal di sekolah Nonthaburi, Thailand sempat melakukan pembunuhan terhadap kakek dan neneknya sebelum beraksi.</t>
+        </is>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7865279/pelaku-penembakan-di-sekolah-thailand-sempat-bunuh-kakek-neneknya-sebelum-beraksi-9-orang-tewas</t>
+        </is>
+      </c>
+      <c r="H506" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/DPRMXn9cJ1FlXAvBpOd0cgVCYnY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/PENEMBAKAN-MASSAL-DI-THAILAND-07082026.jpg</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Peluang Marco Bezzecchi di MotoGP Inggris 2026, Cedera Jadi Tantangan sang Juara Bertahan</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:52:46 +0700</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr">
+        <is>
+          <t>Marco Bezzecchi belum berada dalam kondisi fisik terbaik menjelang MotoGP Inggris 2026 meski pengamat tetap menaruhnya sebagai favorit.</t>
+        </is>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7865278/peluang-marco-bezzecchi-di-motogp-inggris-2026-cedera-jadi-tantangan-sang-juara-bertahan</t>
+        </is>
+      </c>
+      <c r="H507" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/fu3etsNOkXyYw_TylwItxIcJTUA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Marco-Bezzecchi-Pole-Position-MotoGP-Mandalika-2025.jpg</t>
+        </is>
+      </c>
+      <c r="I507" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Indra Wargadalem Kaitkan Kasus Temuan 995 Senjata dengan Sengketa Yayasan</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:52:05 +0700</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>Indra Wargadalem mengaitkan temuan 995 senjata di sebuah sekolah di Jaksel dengan sengketa yayasan. Dia menduga hal ini adalah jebakan.</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865277/indra-wargadalem-kaitkan-kasus-temuan-995-senjata-dengan-sengketa-yayasan</t>
+        </is>
+      </c>
+      <c r="H508" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vW0d_IgDKBzXm1gs4Ywv9pSzyic=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Sosok-Indra-Wargadalem.jpg</t>
+        </is>
+      </c>
+      <c r="I508" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>Kejagung Geledah Rumah Nurman Herin di Bandung dan Periksa 8 Saksi Kasus TPPU Febrie Adriansyah</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:51:12 +0700</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>Tim 9 Penyidik Kejaksaan Agung menggeledah kediaman tersangka Nurman Herin yang terletak di Bandung, Jawa Barat pada Kamis (6/8/2026).</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865276/kejagung-geledah-rumah-nurman-herin-di-bandung-dan-periksa-8-saksi-kasus-tppu-febrie-adriansyah</t>
+        </is>
+      </c>
+      <c r="H509" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/YzygyICaBCRCYhnCiHD_EU03RNs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Nurman-Herin-NH-saat-digiring-menuju-mobil-tahanan-231.jpg</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Ikuti Jejak Indonesia, Argentina Dukung Gianni Infantino Bertahan Jadi Presiden FIFA</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:50:25 +0700</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>Dukungan Gianni Infantino bertambah, Argentina bergabung bersama Indonesia dukung kembali menjabat sebagai Presiden FIFA pada periode berikutnya.</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7865275/ikuti-jejak-indonesia-argentina-dukung-gianni-infantino-bertahan-jadi-presiden-fifa</t>
+        </is>
+      </c>
+      <c r="H510" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vDuyLgptgdOb7AvgksZeqb-NEgM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/KERJA-SAMA-PSSI-DAN-FIFA-Ketua-Umum-PSSI-Erick-Thohir-bersama-Presiden-FIFA-Gianni-Infantino.jpg</t>
+        </is>
+      </c>
+      <c r="I510" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Truk Kopdes Dipakai Angkut Tebu di Sragen, Anggota DPR: Itu Penyalahgunaan</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:50:01 +0700</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>Truk Kopdes Merah Putih dipakai mengangkut tebu saat melintas di Desa Srawung, Kecamatan Gesi, Kabupaten Sragen, Jawa Tengah.</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/otomotif/7865274/truk-kopdes-dipakai-angkut-tebu-di-sragen-anggota-dpr-itu-penyalahgunaan</t>
+        </is>
+      </c>
+      <c r="H511" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/XK8ieBZCcKqnq67dFjcH9G7oZ7w=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Truk-Kopdes-angkut-tebu-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Asal-Usul 995 Senjata di Sekolah Jaksel Masih Misterius, Pengurus Baru Yayasan Angkat Bicara</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:49:51 +0700</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>Misteri 995 senjata api di sekolah swasta Jaksel, pengurus baru yayasan akui tak tahu asal-usul temuan.</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7865273/asal-usul-995-senjata-di-sekolah-jaksel-masih-misterius-pengurus-baru-yayasan-angkat-bicara</t>
+        </is>
+      </c>
+      <c r="H512" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/c23bmk4PHY76ZCmOECtNP5j3wK4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ratusan-senjata-api-di-sekolah-swasta-Pondok-Pinang-Kebayoran-Lama-Jakarta-Selatan.jpg</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Prediksi Line-up Timnas Indonesia vs Singapura: Sandy Walsh dan Cahya Supriadi Berpeluang Starter</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:49:04 +0700</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia wajib menang atas Singapura demi tiket semifinal Piala AFF 2026. John Herdman diprediksi merotasi lini belakang dan posisi kiper.</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7865272/prediksi-line-up-timnas-indonesia-vs-singapura-sandy-walsh-dan-cahya-supriadi-berpeluang-starter</t>
+        </is>
+      </c>
+      <c r="H513" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/yNQRBwgJz2YPPsUobmy3fY0wL6Y=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Piala-AFF-2026-Timnas-Indonesia-Tekuk-Timor-Leste-3-0_20260731_231927.jpg</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Iran Siapkan Strategi 'Mata Ganti Mata'! Negara Teluk Terancam Gelap Jika AS Serang Lebih Dulu</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:48:25 +0700</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>Iran ancam "matikan" listrik negara-negara Teluk jika AS menyerang lebih dulu. Strategi balasan Teheran memicu kekhawatiran baru di Timur Tengah.</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7865271/iran-siapkan-strategi-mata-ganti-mata-negara-teluk-terancam-gelap-jika-as-serang-lebih-dulu</t>
+        </is>
+      </c>
+      <c r="H514" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/hhokL3jdRBzLyIRFusGQGcIw9a8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/minyak-Iran-Amerika-Serikat-menerapkan-embargo.jpg</t>
+        </is>
+      </c>
+      <c r="I514" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Cirebon Sabtu, 8 Agustus 2026: Awas Terik Matahari Tembus 34 Derajat</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:46:56 +0700</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>Menurut pantauan BMKG Jawa Barat prakiraan cuaca untuk wilayah Cirebon pada Sabtu (8/8/2026) cerah dengan potensi terik matahari yang menyengat.</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865270/prakiraan-cuaca-cirebon-sabtu-8-agustus-2026-awas-terik-matahari-tembus-34-derajat</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/5NsvRAfKVVqlNUGVnYRGovtF7v4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/cuaca-cerah-berawan-8.jpg</t>
+        </is>
+      </c>
+      <c r="I515" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Viral Truk Kopdes di Sragen Dipakai Angkut Tebu, Anggota DPR Minta Pengurusnya Ditegur</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:46:19 +0700</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr">
+        <is>
+          <t>Dugaan penyalahgunaan truk KDMP Desa Srawung ini mencuat setelah videonya beredar luas di media sosial.</t>
+        </is>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865269/viral-truk-kopdes-di-sragen-dipakai-angkut-tebu-anggota-dpr-minta-pengurusnya-ditegur</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/eO7zDCEBs_y-UmpBCpEH0MCzuaI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/tebu-Dokumentasi-akun-TikTok-KOP.jpg</t>
+        </is>
+      </c>
+      <c r="I516" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Kecelakaan Misterius, Mobil Masuk Jurang di Bolaang Mongondow Sulut, Satu Polisi Tewas</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:42:43 +0700</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>Mobil brio kecelakaan masuk jurang, satu korban tewas diketahui seorang polisi di Polres Bolaang Mongondow Sulut</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865268/kecelakaan-misterius-mobil-masuk-jurang-di-bolaang-mongondow-sulut-satu-polisi-tewas</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/toKuA705N6Gasr6g57OLfbRBPxs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/mobil-masuk-jurang-di-Bolaang-Mongondow-satu-polisi-tewas.jpg</t>
+        </is>
+      </c>
+      <c r="I517" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>Kumpulan Pidato untuk Malam Tirakatan HUT Kemerdekaan RI 2026 dalam Beberapa Versi</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:39:50 +0700</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr">
+        <is>
+          <t>Jelang HUT ke-81 Kemerdekaan RI, panitia mulai mempersiapkan pidato malam tirakatan, berikut kumpulan teks pidato yang cocok dijadikan referensi.</t>
+        </is>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865267/kumpulan-pidato-untuk-malam-tirakatan-hut-kemerdekaan-ri-2026-dalam-beberapa-versi</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/44V96-LBP6C0LMPZ1m22SHpdXCk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/sambut-hut-kemerdekaan-ri-warga-cilenggang-hias-kampung_20220810_194413.jpg</t>
+        </is>
+      </c>
+      <c r="I518" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Istana Bantah Telah Kirimkan Surpres Pergantian Kapolri</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:37:22 +0700</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr">
+        <is>
+          <t>Prasetyo Hadi meluruskan kabar yang menyebutkan bahwa Presiden Prabowo Subianto telah mengirimkan Surat Presiden terkait pergantian Kapolri.</t>
+        </is>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865266/istana-bantah-telah-kirimkan-surpres-pergantian-kapolri</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/yTBm4IYvYt8Ta9Tu3Z6r7wQU-_U=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Prasetyo-Hadi-di-Istana-Kepresidenan07082026.jpg</t>
+        </is>
+      </c>
+      <c r="I519" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Beli Mobil Cara Cicilan Jangan FOMO, Hitung Dulu Total Owning Cost-nya</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:34:00 +0700</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr">
+        <is>
+          <t>Mencicil kendaraan dengan tenor panjang membuat total owning cost (TOC) menjadi lebih tinggi mengingat komponen lain seperti bunga jadi lebih mahal.</t>
+        </is>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/otomotif/7865265/beli-mobil-cara-cicilan-jangan-fomo-hitung-dulu-total-owning-cost-nya</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Nap0e1aFY5P1HKBV7G7o5y5WbsQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Diskusi-Astra-Financial-GIIS-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I520" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Alasan Ruben Onsu Tak Terpikir untuk Menikah Lagi, Tunggu Anak-anak Dewasa</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:32:54 +0700</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr">
+        <is>
+          <t>Penjelasan Ruben Onsu soal tidak kepikiran menikah lagi, ingin fokus lihat dan temani anak-anak dewasa.</t>
+        </is>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865264/alasan-ruben-onsu-tak-terpikir-untuk-menikah-lagi-tunggu-anak-anak-dewasa</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/B0PjO6TU4zWsvX1GGG1dLTB_lgA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/mediasi-ruben-onsu.jpg</t>
+        </is>
+      </c>
+      <c r="I521" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Terjemahan Lirik Lagu Waterfall - The Stone Roses: Chimes Sing Sunday Morn</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:32:30 +0700</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>Berikut ini merupakan terjemahan lirik lagu Waterfall yang dipopulerkan oleh grup band The Stone Roses.</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7865263/terjemahan-lirik-lagu-waterfall-the-stone-roses-chimes-sing-sunday-morn</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/zLN77GXG_MWcQ27NDqNvGgp-QJs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-musik-ilustrasi-lirik-ilustrasi-terjemahan-lirik-lagu.jpg</t>
+        </is>
+      </c>
+      <c r="I522" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Jessica Iskandar Klarifikasi usai Posting Foto Bareng Sarwendah: Saya Tidak Bermaksud Memihak</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:31:32 +0700</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr">
+        <is>
+          <t>Artis Jessica Iskandar klarifikasi setelah mengunggah foto kebersamaan dengan Sarwendah di media sosial. Ia mengaku berada di posisi netral.</t>
+        </is>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865262/jessica-iskandar-klarifikasi-usai-posting-foto-bareng-sarwendah-saya-tidak-bermaksud-memihak</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/yUEI0CAXSwNuRYvWOQ_aT_q189A=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Sarwendah-1-15072026.jpg</t>
+        </is>
+      </c>
+      <c r="I523" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>Magang Kemdiktisaintek Batch 3 Dibuka 7-18 Agustus 2026, Ada 9 Bidang Humas</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:31:30 +0700</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>Magang Kemdiktisaintek Batch 3 dibuka 7-18 Agustus 2026. Ada 9 bidang Humas dan Kerja Sama yang dibuka. Peserta mendaftar melalui link tautan resmi.</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7865261/magang-kemdiktisaintek-batch-3-dibuka-7-18-agustus-2026-ada-9-bidang-humas</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/5WirZN787OAGacJViCmJ8XVde8E=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/MAGANG-KEMDIKTISAINTEK-3453443.jpg</t>
+        </is>
+      </c>
+      <c r="I524" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>ESG AWARD 2026 BY KEHATI Digelar, Dorong ESG Menjadi Standar Baru Daya Saing Bisnis Indonesia</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:30:49 +0700</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>Yayasan KEHATI kembali menyelenggarakan ajang penghargaan  ESG Award 2026 by KEHATI pada 6 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/lestari/7865260/esg-award-2026-by-kehati-digelar-dorong-esg-menjadi-standar-baru-daya-saing-bisnis-indonesia</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/JxeP0i0bN6E92MeHyM4epgL-iPI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/esg_award_ongki-k.jpg</t>
+        </is>
+      </c>
+      <c r="I525" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Bandara Husein Sastranegara Kembali Layani Penerbangan Pesawat Jet Mulai 14 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:56:25 +0700</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>Ahmad Fikri Noor</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- PT Angkasa Pura Indonesia (Persero) atau InJourney Airports mendapat persetujuan dari Kementerian Perhubungan (Kemenhub) untuk melayani penerbangan pesawat jet berbadan sedang (narrow body) di Bandara Husein Sastranegara,...</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tje3e1490/bandara-husein-sastranegara-kembali-layani-penerbangan-pesawat-jet-mulai-14-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/034793900-1786083194-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I526" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Hana Bank Cetak Laba Rp360,76 Miliar</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – PT Bank KEB Hana Indonesia (Hana Bank) membukukan laba bersih sebesar Rp360,76 miliar pada semester I 2026 atau tumbuh 9,21 persen secara tahunan (year on year/yoy). Pertumbuhan...</t>
+        </is>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjdw6y416/hana-bank-cetak-laba-rp36076-miliar</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260807122317-698.png</t>
+        </is>
+      </c>
+      <c r="I527" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Cadangan Devisa pada Juli 2026 Turun, Bank Indonesia Beberkan Penyebabnya</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:59:16 +0700</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>Ahmad Fikri Noor</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Bank Indonesia (BI) menyampaikan posisi cadangan devisa Indonesia kembali menurun. Pada akhir Juli 2026, cadangan devisa tercatat sebesar 145,3 miliar dolar AS, turun 0,3 miliar dolar...</t>
+        </is>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tje0qs490/cadangan-devisa-pada-juli-2026-turun-bank-indonesia-beberkan-penyebabnya</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/041906600-1713342441-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I528" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Pertamina Marine Buka Peluang Kerja Pelaut Indonesia ke China</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:48:20 +0700</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- PT Pertamina Marine Solutions (PMSol) menjalin kerja sama dengan perusahaan pelayaran asal China, Xingtong Group, untuk membuka peluang penempatan pelaut Indonesia di armada tanker internasional. Kolaborasi tersebut...</t>
+        </is>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tje08k416/pertamina-marine-buka-peluang-kerja-pelaut-indonesia-ke-china</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/pt-pertamina-marine-solutions-pmsol-dan-xingtong-group-menandatangani_260807134713-634.jpeg</t>
+        </is>
+      </c>
+      <c r="I529" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>Otomotif</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>BAIC Tawarkan Kesempatan Menangkan T1 bagi Konsumen di GIIAS 2026</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:12:26 +0700</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>Israr Itah</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, TANGERANG -- BAIC Indonesia mencatat lebih dari 12 ribu pengunjung mendatangi booth perusahaan hingga hari kelima penyelenggaraan Gaikindo Indonesia International Auto Show (GIIAS) 2026. Selama periode tersebut, BAIC juga...</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjdykq348/baic-tawarkan-kesempatan-menangkan-t1-bagi-konsumen-di-giias-2026</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/baict1-dipamerkan-di-booth-baic-di-giias_260807131216-555.JPG</t>
+        </is>
+      </c>
+      <c r="I530" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Isu Reshuffle Kabinet Menguat, Istana Ungkap Dua Jabatan Kosong</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:06:45 +0700</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara Prasetyo Hadi mengatakan isu reshuffle memang kerap mencuat.</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264319/isu-reshuffle-kabinet-menguat-istana-ungkap-dua-jabatan-kosong</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/a_OlaD9VdfFL0AWqKLYT8v9Rcfc=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/4993028/original/025379800_1730884437-IMG-20241106-WA0032.jpg</t>
+        </is>
+      </c>
+      <c r="I531" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Sosok Hakim Tunggal yang Sidangkan Praperadilan Lodewyk Pusung Pekan Depan</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:51:32 +0700</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr">
+        <is>
+          <t>Sebelumnya, PN Jaksel menolak menangani praperadilan Lodewyk karena merasa tidak berwenang mengadili perkara tersebut.</t>
+        </is>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264304/sosok-hakim-tunggal-yang-sidangkan-praperadilan-lodewyk-pusung-pekan-depan</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/abGHhJmMYj4T4hf0esK651NWkKg=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318206/original/026758800_1786089090-kejagung-tahan-mantan-pimpinan-bgn-2799051.jpg</t>
+        </is>
+      </c>
+      <c r="I532" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Bandara Husein Sastranegara Siap Layani Penerbangan Jet Reguler</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:54:05 +0700</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t>PT Angkasa Pura Indonesia (Persero) atau InJourney Airports memastikan kesiapan fasilitas Bandara Husein Sastranegara, Bandung, menjelang kembali beroperasinya penerbangan pesawat jet berbadan sedang (narrow body) secara reguler pada 14 Agustus 2026. Persetujuan dari Kementerian Perhubungan diperoleh setelah seluruh persyaratan operasional, keamanan, keselamatan, pelayanan, dan kepatuhan regulasi dipenuhi. Fasilitas yang disiapkan meliputi 26 konter check-in, mesin self check-in, area pemeriksaan keamanan, serta ruang tunggu yang dilengkapi area komersial untuk mendukung kenyamanan penumpang.</t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/photo/read/8264296/bandara-husein-sastranegara-siap-layani-penerbangan-jet-reguler</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/NpPOBggvrFZq14Wx-VtXIIW1BHo=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318184/original/015332000_1786088834-bdg.jpg</t>
+        </is>
+      </c>
+      <c r="I533" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Foto</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Menelusuri Lebih Dekat Jejak Kampung Somang Saat Kemarau</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:19:56 +0700</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>Musim kemarau membuat debit air Bendungan Karian di Kabupaten Lebak, Banten, terus menyusut sehingga bangunan-bangunan bekas permukiman Kampung Somang kembali muncul ke permukaan. Atap rumah, dinding, hingga bangunan masjid yang selama ini terendam kini terlihat lebih jelas dan menarik perhatian warga yang datang menggunakan perahu untuk menyaksikan jejak kampung yang telah ditinggalkan sejak pembangunan bendungan. Warga sebelumnya direlokasi ketika kawasan tersebut digenangi air. Bendungan Karian menjadi salah satu infrastruktur strategis penyedia air baku dengan kapasitas 14,6 meter kubik per detik untuk memenuhi kebutuhan rumah tangga dan industri di sejumlah wilayah Jakarta dan Banten.</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/photo/read/8264251/menelusuri-lebih-dekat-jejak-kampung-somang-saat-kemarau</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/U1WfkmTU2Asp_GbTpja6na6xLP8=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318094/original/061387500_1786086580-mun1.jpg</t>
+        </is>
+      </c>
+      <c r="I534" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Temuan 995 Senjata, Polisi Panggil Eks Ketua Yayasan Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:30:59 +0700</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t>Pemanggilan dilakukan setelah pihak yayasan menyebut barang-barang tersebut diduga berkaitan dengan kepengurusan lama.</t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264281/temuan-995-senjata-polisi-panggil-eks-ketua-yayasan-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/u15x1w9N_6-9iVpP-LBJokwIdVo=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317533/original/004362800_1786019652-WhatsApp_Image_2026-08-06_at_19.28.11.jpeg</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Penampakan Febrie Adriansyah, Perdana Pakai Rompi Pink dan Tangan Diborgol</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:58:40 +0700</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr">
+        <is>
+          <t>Ini momen perdana Febrie kembali muncul sejak ditahan 24 Juli 2026 lalu.</t>
+        </is>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264230/penampakan-febrie-adriansyah-perdana-pakai-rompi-pink-dan-tangan-diborgol</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/GrhlK2VMDgFLtLhcSMGdYzQHFTs=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318066/original/045657600_1786085809-IMG_20260807_131251_051.jpg</t>
+        </is>
+      </c>
+      <c r="I536" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Polisi Bicara Legalitas 995 Senjata di Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:48:21 +0700</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr">
+        <is>
+          <t>Polisi masih meneliti dokumen kepemilikan yang turut diamankan bersama barang bukti.</t>
+        </is>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264226/polisi-bicara-legalitas-995-senjata-di-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/ETTDU2qEXOzAfRQOJ_Mo1H87TaE=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317518/original/012310700_1786017988-Bungker.webp</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Dinkes DKI: Nakes Cibir Pasien BPJS Bukan Pegawai Faskes Pemprov Jakarta</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:42:47 +0700</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr">
+        <is>
+          <t>Hasil penelusuran sementara menemukan lima tenaga kesehatan maupun tenaga medis yang diduga terlibat dalam unggahan tersebut.</t>
+        </is>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264217/dinkes-dki-nakes-cibir-pasien-bpjs-bukan-pegawai-faskes-pemprov-jakarta</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/IiOsgxGbLOMN1ZXS3TxNv_P2qTk=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9315744/original/019758300_1785885131-yurizal.webp</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Daftar Senjata yang Ditemukan Polisi di Sekolah Swasta Jaksel</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:04:12 +0700</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>Polisi Rinci Temuan 995 Airsoft Gun, Ada Senpi Francisca hingga Empat Laras Senapan</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264177/daftar-senjata-yang-ditemukan-polisi-di-sekolah-swasta-jaksel</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/u15x1w9N_6-9iVpP-LBJokwIdVo=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317533/original/004362800_1786019652-WhatsApp_Image_2026-08-06_at_19.28.11.jpeg</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Food</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>6 Promo Makan Spesial HUT RI ke-81, Ada Hokben hingga Lawson</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:09:04 +0700</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>Promo makan spesial HUT RI ke-81 ini kembali hadir. Ada berbagai promo restoran dan minimarket yang sayang untuk dilewatkan.</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/food/read/2026/08/07/150835175/6-promo-makan-spesial-hut-ri-ke-81-ada-hokben-hingga-lawson</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/vvMCSE3kxyE4UEt7LFZPNaeUrF8=/149x0:1769x1080/1200x675/filters:watermark(data/photo/2026/01/30/697c81a417f45.png,0,-0,1)/data/photo/2026/08/07/6a759235bb258.jpg</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Prabowo Sudah Panggil Sejumlah Calon Gubernur BI untuk Diajak Diskusi</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:09:04 +0700</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t>Prabowo Subianto telah berdiskusi dengan sejumlah calon gubernur Bank Indonesia. Pjs Gubernur BI Destry Damayanti masuk daftar pertimbangan.</t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/07/14542341/prabowo-sudah-panggil-sejumlah-calon-gubernur-bi-untuk-diajak-diskusi</t>
+        </is>
+      </c>
+      <c r="H541" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/oXyBAST46TU9HDJW7FDqWtrsfF8=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/06/6a747754344fc.jpg</t>
+        </is>
+      </c>
+      <c r="I541" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>PSN Blok Masela Berdenyut, Pemkab Tanimbar Minta Tambahan Kuota BBM</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:09:04 +0700</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>Pemkab Kepulauan Tanimbar minta tambahan kuota BBM karena pengerjaan PSN Blok Masela, sehingga ada peningkatan kegiatan pengakutan material...</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/07/143707778/psn-blok-masela-berdenyut-pemkab-tanimbar-minta-tambahan-kuota-bbm</t>
+        </is>
+      </c>
+      <c r="H542" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/oupL1K1axDG6Uj9ftvATZuiwz9c=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/07/6a7577a369e49.jpg</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I462"/>
+  <autoFilter ref="A1:I542"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-07.xlsx
+++ b/data/berita_2026-08-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$542</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$716</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I542"/>
+  <dimension ref="A1:I716"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -25907,8 +25907,8186 @@
         </is>
       </c>
     </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Muzani sebut progam Kopdes Prabowo berangkat dari pemikiran Bung Hatta</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:47:30 +0700</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>Ketua MPR RI Ahmad Muzani menyebut program Koperasi Desa Merah Putih yang dicanangkan Presiden Prabowo Subianto ...</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684363/muzani-sebut-progam-kopdes-prabowo-berangkat-dari-pemikiran-bung-hatta</t>
+        </is>
+      </c>
+      <c r="H543" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/tempImagesUX1sa.jpg</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Sengketa kepengurusan yayasan awal ditemukannya senjata di sekolah</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:47:22 +0700</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>Sengketa kepengurusan yayasan sekolah swasta di Pondok Pinang, Kebayoran Lama, Jakarta Selatan, disebut menjadi awal ...</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684359/sengketa-kepengurusan-yayasan-awal-ditemukannya-senjata-di-sekolah</t>
+        </is>
+      </c>
+      <c r="H544" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001016438.jpg</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Cole Palmer dan skuad Chelsea FC resmi tiba di Indonesia, duel kontra AC Milan di SUGBK jadi magnet pecinta sepak bola</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:47:14 +0700</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>Pesepak bola Chelsea FC Cole Palmer (kiri) dan Olutayo Subuloye (kedua kiri) berjalan menuju bus setibanya di kawasan ...</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5684355/cole-palmer-dan-skuad-chelsea-fc-resmi-tiba-di-indonesia-duel-kontra-ac-milan-di-sugbk-jadi-magnet-pecinta-sepak-bola</t>
+        </is>
+      </c>
+      <c r="H545" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Tim-sepak-bola-Chelsea-tiba-di-Indonesia-782026-pma-1.jpg</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Polisi segera panggil mantan pengurus yayasan soal temuan 995 senpi</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:46:48 +0700</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr">
+        <is>
+          <t>ANTARA - Polres Metro Jakarta Selatan segera memanggil mantan Ketua Pengurus Yayasan Harapan Ibu berinisial ...</t>
+        </is>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5684285/polisi-segera-panggil-mantan-pengurus-yayasan-soal-temuan-995-senpi</t>
+        </is>
+      </c>
+      <c r="H546" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/POLISI-SEGERA-PANGGIL-MANTAN-PENGURUS-YAYASAN-SOAL-TEMUAN-995-SENPI.jpg</t>
+        </is>
+      </c>
+      <c r="I546" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Prabowo resmikan acara peluncuran 10 buku karya Bahlil Lahadalia</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:45:42 +0700</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto meresmikan acara peluncuran 10 buku karya Menteri ESDM Bahlil Lahadalia di Jakarta, Jumat, ...</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684351/prabowo-resmikan-acara-peluncuran-10-buku-karya-bahlil-lahadalia</t>
+        </is>
+      </c>
+      <c r="H547" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/f10c8f10-1f6b-478f-99f7-17eab49201d6.jpeg</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>ChatGPT hapus batas percakapan teks untuk semua pengguna</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:44:53 +0700</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>OpenAI mengumumkan akan menghapus batas percakapan teks di ChatGPT untuk seluruh pengguna, menyusul pencapaian chatbot ...</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684348/chatgpt-hapus-batas-percakapan-teks-untuk-semua-pengguna</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/09/26/chat-gpt.jpg</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Taruna Akpol-Akmil bentuk kedisiplinan siswa Sekolah Rakyat di Kalsel</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:44:15 +0700</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Sebanyak 10 taruna Akademi Kepolisian (Akpol) dan lima taruna Akademi Angkatan Laut melaksanakan pengabdian di tiga ...</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684344/taruna-akpol-akmil-bentuk-kedisiplinan-siswa-sekolah-rakyat-di-kalsel</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_20260807_151310.jpg</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Barry Sheene masuk dalam MotoGP Hall of Fame</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:44:11 +0700</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Pembalap legendaris Inggris Barry Sheene yang menjadi jawara MotoGP pada 1976 dan 1977 akan masuk dalam MotoGP ...</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684341/barry-sheene-masuk-dalam-motogp-hall-of-fame</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/08/08/2025-motogp-01.jpg</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Cara makan gorengan dengan sehat dan terlepas dari rasa khawatir</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:43:29 +0700</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Gorengan menjadi salah satu camilan favorit masyarakat Indonesia. Mulai dari bakwan, tempe goreng, tahu isi, pisang ...</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684337/cara-makan-gorengan-dengan-sehat-dan-terlepas-dari-rasa-khawatir</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2018/10/GORENGAN1.jpg</t>
+        </is>
+      </c>
+      <c r="I551" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Rantis Polres Gunungkidul jadi harapan baru warga di tengah kemarau</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:42:19 +0700</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>ANTARA - Polres Gunungkidul menerjunkan kendaraan Air Water Cannon guna menyalurkan air bersih ke wilayah yang ...</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5684256/rantis-polres-gunungkidul-jadi-harapan-baru-warga-di-tengah-kemarau</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/RANTIS-POLRES-GUNUNGKIDUL-JADI-HARAPAN-BARU-WARGA-DI-TENGAH-KEMARAU.jpg</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Bicara Udara dukung DPRD DKI revisi perda tentang pencemaran udara</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:40:49 +0700</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Organisasi nirlaba Bicara Udara mendukung DPRD DKI Jakarta memprioritaskan revisi Peraturan Daerah (Raperda) Pengganti ...</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684336/bicara-udara-dukung-dprd-dki-revisi-perda-tentang-pencemaran-udara</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/20/polusi-debu-di-kabupaten-bandung-barat-2824725.jpg</t>
+        </is>
+      </c>
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Polisi buru tiga DPO pemilik narkotika di Penjaringan</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:40:34 +0700</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Polsek Metro Penjaringan, Jakarta Utara masih mengejar tiga pelaku yang masuk dalam daftar pencarian orang (DPO) karena ...</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684332/polisi-buru-tiga-dpo-pemilik-narkotika-di-penjaringan</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-13.10.54_1.jpeg</t>
+        </is>
+      </c>
+      <c r="I554" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Menkomdigi: Kehadiran AI Factory memperkuat posisi Indonesia</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:40:10 +0700</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Menteri Komunikasi dan Digital (Menkomdigi) Meutya Hafid mengatakan bahwa kehadiran infrastruktur komputasi ...</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684331/menkomdigi-kehadiran-ai-factory-memperkuat-posisi-indonesia</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG-20260807-WA0196.jpg</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Fiona Sari Utami Corporate Secretary PTP Nonpetikemas Mendapat Pengakuan Popular PR Person Awards 2026</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:38:28 +0700</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA) – Senior Manager Sekretaris Perusahaan PT Pelabuhan Tanjung Priok (PTP Nonpetikemas), Fiona Sari ...</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684328/fiona-sari-utami-corporate-secretary-ptp-nonpetikemas-mendapat-pengakuan-popular-pr-person-awards-2026</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/PTP-Nonpetikemas-Fiona-Sari-Utami.jpg</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Ratusan siswa PAUD antusias ikuti Festival Kreatif di Manokwari, cara unik tanamkan cinta tanah air sejak dini</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:37:32 +0700</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Siswa PAUD mewarnai gambar saat mengikuti Festival PAUD Kreatif di Borarsi, Manokwari, Papua Barat, Jumat (7/8/2026). ...</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5684325/ratusan-siswa-paud-antusias-ikuti-festival-kreatif-di-manokwari-cara-unik-tanamkan-cinta-tanah-air-sejak-dini</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Festival-PAUD-Kreatif-di-Manokwari-782026-ci-4.jpg</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Tagana Tasikmalaya salurkan 84 ribu liter air bantu daerah kekeringan</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:35:41 +0700</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Taruna Siaga Bencana (Tagana) Kabupaten Tasikmalaya, Jawa Barat bekerja sama dengan sejumlah instansi telah menyalurkan ...</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684321/tagana-tasikmalaya-salurkan-84-ribu-liter-air-bantu-daerah-kekeringan</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_20260807_161332.jpg</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>Ada kebakaran, BB TNGGP tutup jalur pendakian hingga 11 Agustus</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:35:35 +0700</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Balai Besar Taman Nasional Gunung Gede Pangrango (BB TNGGP) menutup sementara pendakian selama lima hari karena ...</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684320/ada-kebakaran-bb-tnggp-tutup-jalur-pendakian-hingga-11-agustus</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/alun-bakar.jpg</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>PTP Nonpetikemas Raih PR Popular Companies Awards 2026 Kategori Port Operation</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:35:22 +0700</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA) – PT Pelabuhan Tanjung Priok (PTP Nonpetikemas) meraih PR Popular Companies Awards 2026 kategori ...</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684316/ptp-nonpetikemas-raih-pr-popular-companies-awards-2026-kategori-port-operation</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/PTP-Nonpetikemas-raih-PR-Popular.jpg</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>Kemenag resmi terbitkan struktur Direktorat Jenderal Pesantren</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:34:42 +0700</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Kementerian Agama telah menerbitkan regulasi baru, yaitu Peraturan Menteri Agama (PMA) No 16 tahun 2026 tentang ...</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684315/kemenag-resmi-terbitkan-struktur-direktorat-jenderal-pesantren</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_20260807_162502.jpg</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>DPRD DKI sebut penerapan pajak kendaraan listrik optimalkan PAD</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:34:00 +0700</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>DPRD DKI Jakarta mendukung usulan terkait penerapan Pajak Kendaraan Bermotor (PKB) dan Bea Balik Nama Kendaraan ...</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684313/dprd-dki-sebut-penerapan-pajak-kendaraan-listrik-optimalkan-pad</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/25/realisasi-pembangunan-spklu-di-indonesia-2794159.jpg</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Dispar Sleman optimistis target 8 juta wisatawan pada 2026 terealisasi</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:32:36 +0700</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Dinas Pariwisata (Dinpar) Kabupaten Sleman, Daerah Istimewa Yogyakarta, optimistis mampu mengawal pencapaian target ...</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684309/dispar-sleman-optimistis-target-8-juta-wisatawan-pada-2026-terealisasi</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000038972.jpg</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>KY akan umumkan hasil seleksi calon hakim agung petang ini</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:31:55 +0700</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Komisi Yudisial (KY) akan mengumumkan hasil akhir seleksi calon hakim agung, calon hakim ad hoc HAM, dan calon hakim ad ...</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684303/ky-akan-umumkan-hasil-seleksi-calon-hakim-agung-petang-ini</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_4555.jpeg</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Pemprov Jateng dan Otorita IKN jajaki potensi kolaborasi dan investasi</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:28:39 +0700</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi Jawa Tengah menjajaki potensi kolaborasi dan investasi dengan Otorita Ibu Kota Nusantara (IKN), ...</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684299/pemprov-jateng-dan-otorita-ikn-jajaki-potensi-kolaborasi-dan-investasi</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1002086439.jpg</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>OJK: Laba industri pindar naik 10,14 persen pada Juni 2026</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:28:30 +0700</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Otoritas Jasa Keuangan (OJK) mengungkapkan bahwa laba industri pinjaman daring (pindar) pada Juni 2026 meningkat ...</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684296/ojk-laba-industri-pindar-naik-1014-persen-pada-juni-2026</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/30/IMG_0468.jpeg</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Luhut nilai manfaat hilirisasi harus lebih adil bagi daerah penghasil</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:27:46 +0700</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Ketua Dewan Ekonomi Nasional (DEN) Luhut Binsar Pandjaitan menilai manfaat kebijakan hilirisasi harus semakin dirasakan ...</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684295/luhut-nilai-manfaat-hilirisasi-harus-lebih-adil-bagi-daerah-penghasil</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-4.01.21-PM.jpeg</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>Dishut Kalteng perkuat penanganankarhutla melalui normalisasi kanal</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:27:37 +0700</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Dinas Kehutanan (Dishut) Kalimantan Tengah memperkuat upaya pencegahan serta penanganan kebakaran hutan dan lahan ...</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684293/dishut-kalteng-perkuat-penanganankarhutla-melalui-normalisasi-kanal</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001729976.jpg</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Pramono: Penilaian Ombudsman jadi acuan DKI untuk tertib administrasi</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:27:31 +0700</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta, Pramono Anung mengatakan penilaian Ombudsman tentang opini maladminstrasi penyelenggaraan ...</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684289/pramono-penilaian-ombudsman-jadi-acuan-dki-untuk-tertib-administrasi</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000316233.jpg</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Burnout dapat picu perilaku impulsif di media sosial</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:25:04 +0700</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Psikolog klinis lulusan Universitas Indonesia Ratih Ibrahim, M.M., Psikolog mengatakan burnout atau kelelahan ...</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684283/burnout-dapat-picu-perilaku-impulsif-di-media-sosial</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2022/03/08/pexels-nataliya-vaitkevich-6837793.jpg</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Bea Cukai Bali gagalkan dua WNA selundupkan 10,1 kg ganja</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:23:18 +0700</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Bea Cukai Ngurah Rai menggagalkan dugaan penyelundupan 10,1 kilogram ganja yang dibawa dua warga negara asing (WNA) ...</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684280/bea-cukai-bali-gagalkan-dua-wna-selundupkan-101-kg-ganja</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_5111.jpg</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Leao, Modric, hingga Goncalo dipastikan tampil lawan Chelsea di SUGBK</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:22:31 +0700</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Sejumlah bintang AC Milan seperti Rafael Leao, Luka Modric, hingga Goncalo Ramos dipastikan tampil pada laga pramusim ...</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684273/leao-modric-hingga-goncalo-dipastikan-tampil-lawan-chelsea-di-sugbk</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/09/MilanGenoa-SerieA-32.jpg</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Bappenas: Penguatan SDM jadi fondasi transformasi kawasan transmigrasi</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:18:45 +0700</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Menteri Perencanaan Pembangunan Nasional/Kepala Badan Perencanaan Pembangunan Nasional (PPN/Bappenas) Rachmat Pambudy ...</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684272/bappenas-penguatan-sdm-jadi-fondasi-transformasi-kawasan-transmigrasi</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Bappenas-Transmigrasi.jpeg</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Kementerian HAM minta layanan pasien BPJS bebas diskriminasi</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:18:32 +0700</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Kementerian Hak Asasi Manusia meminta pelayanan kesehatan bagi peserta Badan Penyelenggara Jaminan Sosial (BPJS) ...</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684271/kementerian-ham-minta-layanan-pasien-bpjs-bebas-diskriminasi</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/04/02/Gambar-02-04-26-di-12.01.jpeg</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>8 manfaat daun katuk dan kandungan gizinya</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:17:01 +0700</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Daun katuk (Sauropus androgynus) merupakan salah satu sayuran hijau yang telah lama dikonsumsi masyarakat Indonesia. ...</t>
+        </is>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684268/8-manfaat-daun-katuk-dan-kandungan-gizinya</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2018/10/katuk.jpg</t>
+        </is>
+      </c>
+      <c r="I575" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Wapres tinjau renovasi sekolah, kelancaran belajar pascabencana Aceh</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:15:43 +0700</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Wakil Presiden (Wapres) RI Gibran Rakabuming memastikan progres renovasi infrastruktur sekolah di Aceh terus dilakukan ...</t>
+        </is>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684264/wapres-tinjau-renovasi-sekolah-kelancaran-belajar-pascabencana-aceh</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/f935ad7f-1f57-4e36-833b-896f4b676704.jpeg</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Bezzecchi dalam kondisi fit untuk GP Inggris</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:12:52 +0700</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Pembalap Aprilia Racing Marco Bezzecchi dalam kondisi fit jelang berlangsungnya MotoGP Inggris di Sirkuit Silverstone, ...</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684261/bezzecchi-dalam-kondisi-fit-untuk-gp-inggris</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/01/XxjpbeE000208_20260601_PEPFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Polisi ungkap peredaran narkotika jenis etomidate di Jakut</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:09:49 +0700</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Polisi mengungkap peredaran narkotika jenis etomidate dan sabu yang diedarkan pelaku berinisial B di kawasan ...</t>
+        </is>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684255/polisi-ungkap-peredaran-narkotika-jenis-etomidate-di-jakut</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-13.10.54.jpeg</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Kementerian PU sebut empat Sekolah Rakyat di Sulsel beroperasi</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:09:29 +0700</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Kementerian Pekerjaan Umum (PU) memastikan empat Sekolah Rakyat Terintegrasi (SRT) di Provinsi Sulawesi Selatan ...</t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684252/kementerian-pu-sebut-empat-sekolah-rakyat-di-sulsel-beroperasi</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-05-at-16.12.53.jpg</t>
+        </is>
+      </c>
+      <c r="I579" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Libur musim panas picu lonjakan wisata di Shapotou, pengunjung rela datang demi menikmati sensasi naik unta di gurun</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:07:03 +0700</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Foto udara wisatawan naik unta saat berkunjung ke kawasan wisata Shapotou di Zhongwei, Daerah Otonom Ningxia Hui, ...</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5684251/libur-musim-panas-picu-lonjakan-wisata-di-shapotou-pengunjung-rela-datang-demi-menikmati-sensasi-naik-unta-di-gurun</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Wisata-Shapotou-Di-Zhongwei-070826-YZ-1.jpg</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Pejabat di Cilacap pakai uang pribadi untuk iuran THR forkopimda</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:06:41 +0700</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Sejumlah pejabat di Pemerintah Kabupaten Cilacap, Jawa Tengah, harus mengeluarkan uang pribadinya untuk memenuhi iuran ...</t>
+        </is>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684248/pejabat-di-cilacap-pakai-uang-pribadi-untuk-iuran-thr-forkopimda</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_20260807_144428.jpg</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>PLN nyatakan kelistrikan di Kalselteng masih siaga</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:05:55 +0700</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Senior Manager Komunikasi, Keuangan, dan Umum (KKU), PLN Unit Induk Distribusi Kalimantan Selatan dan Kalimantan Tengah ...</t>
+        </is>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684247/pln-nyatakan-kelistrikan-di-kalselteng-masih-siaga</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/PLN-UID-Kalselteng.jpeg</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>Hak pekerja PT Kalrez terpenuhi setelah intervensi Kementerian ESDM</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:05:22 +0700</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Sebanyak 94 pekerja dan tenaga outsourcing di lingkungan PT Kalrez Petroleum Ltd kini sudah mendapatkan haknya setelah ...</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684244/hak-pekerja-pt-kalrez-terpenuhi-setelah-intervensi-kementerian-esdm</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_20260807_133125.jpg</t>
+        </is>
+      </c>
+      <c r="I583" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Kasus flu burung meningkat, Australia wajibkan karantina unggas</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:04:10 +0700</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Negara bagian Victoria, Australia, akan mewajibkan para peternak unggas untuk menempatkan burung dalam kandang ...</t>
+        </is>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684237/kasus-flu-burung-meningkat-australia-wajibkan-karantina-unggas</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2019/12/10/Australia-Bushfires-SmokeHaze-101219.jpg</t>
+        </is>
+      </c>
+      <c r="I584" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Inilah 7 cara ampuh untuk membasmi kecoa di rumah</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:03:20 +0700</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Kecoa merupakan salah satu hama rumah tangga yang paling sering membuat penghuni rumah merasa tidak nyaman. Selain ...</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684233/inilah-7-cara-ampuh-untuk-membasmi-kecoa-di-rumah</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/01/11/shutterstock_631419989.jpg</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Kalimantan tawarkan 15 proyek strategis Rp62,13 triliun ke 20 investor</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:01:14 +0700</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Bank Indonesia mempertemukan 15 proyek strategis senilai Rp62,13 triliun dari berbagai provinsi di Kalimantan dengan 20 ...</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684231/kalimantan-tawarkan-15-proyek-strategis-rp6213-triliun-ke-20-investor</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_1750.jpeg</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Pakar UI: Kerja sama ekonomi RI-Thailand topang stabilitas kawasan</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:00:40 +0700</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Pengamat Hubungan Internasional Universitas Indonesia (UI) Shofwan Al-Banna Choiruzzad menilai penguatan kerja sama ...</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684228/pakar-ui-kerja-sama-ekonomi-ri-thailand-topang-stabilitas-kawasan</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/presiden-prabowo-terima-PM-Thailand-030226-gp-4.jpg</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Opsi mobil listrik berharga Rp200 jutaan di ajang GIIAS 2026</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:59:46 +0700</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Mobil-mobil listrik dengan harga Rp200 jutaan ada di antara model-model kendaraan yang dipamerkan di ...</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5684227/opsi-mobil-listrik-berharga-rp200-jutaan-di-ajang-giias-2026</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_1966.jpeg</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Temuan senjata di sekolah Jaksel, polisi panggil mantan ketua yayasan</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:59:39 +0700</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Kepolisian memanggil mantan ketua yayasan berinisial IW terkait temuan ratusan pucuk senjata di dalam salah satu ...</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684224/temuan-senjata-di-sekolah-jaksel-polisi-panggil-mantan-ketua-yayasan</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_20260807_154049.jpg</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>Tol Prosiwangi Seksi 1 dan 2 sepanjang 24 km siap beroperasi</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:58:39 +0700</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Kementerian Pekerjaan Umum (PU) menyiapkan pengoperasian Jalan Tol Probolinggo–Situbondo–Banyuwangi ...</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684220/tol-prosiwangi-seksi-1-dan-2-sepanjang-24-km-siap-beroperasi</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Tol-Prosiwngi-Dibuka-Fungsional-Lumajang-160326-IS-3A.jpg</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Kemendagri: SP2D daring permudah pencairan anggaran daerah</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:58:20 +0700</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Kementerian Dalam Negeri (Kemendagri) menyebut penerapan Surat Perintah Pencairan Dana (SP2D) secara daring yang ...</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684217/kemendagri-sp2d-daring-permudah-pencairan-anggaran-daerah</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001100450.jpg</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Pascatemuan 995 senpi di sekolah Jaksel, kegiatan belajar kondusif</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:57:51 +0700</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>ANTARA - Kuasa Hukum Yayasan Harapan Ibu, Hermawanto pada Jumat (7/8) menyebut temuan 995 senjata api, kaset video ...</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5684153/pascatemuan-995-senpi-di-sekolah-jaksel-kegiatan-belajar-kondusif</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PASCATEMUAN-995-SENPI-DI-SEKOLAH-JAKSEL-KEGIATAN-BELAJAR-KONDUSIF.jpg</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Top News</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Polisi temukan satu "combat shotgun" dari ratusan pucuk senjata di sekolah</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:14:07 +0700</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya mengungkapkan satu dari 996 pucuk senjata yang ditemukan bersama narkoba dan VCD porno di sebuah ...</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684128/polisi-temukan-satu-combat-shotgun-dari-ratusan-pucuk-senjata-di-sekolah</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001016156.jpg</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Walkot Farhan Bekukan Izin Videotron SixNine Padel Buntut Penebangan 10 Pohon</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:39:54 +0700</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>Rifat Alhamidi</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Izin usaha videotron dibekukan buntut penebangan 10 pohon secara ilegal di depan SixNine Padel, Bandung. Pengelola videotron terbukti telah memotong pohon.</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608789/walkot-farhan-bekukan-izin-videotron-sixnine-padel-buntut-penebangan-10-pohon</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/penyegelan-videotron-sixnine-padel-buntut-penebangan-10-pohon-secara-ilegal-1785907225233_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Ketua MPR Pastikan Naskah PPHN Dibuka ke Publik Setelah 17 Agustus</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:39:33 +0700</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Ketua MPR RI Ahmad Muzani akan membuka naskah Pokok-Pokok Haluan Negara (PPHN) ke publik setelah 17 Agustus 2026, melibatkan masyarakat dan akademisi.</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608788/ketua-mpr-pastikan-naskah-pphn-dibuka-ke-publik-setelah-17-agustus</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/12/ketua-mpr-ri-ahmad-muzani-1781266209667_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Dindikbud Kebut Pendataan 3 Ribu Potensi Cagar Budaya di Kota Serang</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:29:56 +0700</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Salah satu wilayah yang memiliki potensi cagar budaya adalah Kecamatan Kasemen. Kasemen merupakan kawasan Banten Lama.</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608774/dindikbud-kebut-pendataan-3-ribu-potensi-cagar-budaya-di-kota-serang</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kepala-dinas-pendidikan-dan-kebudayaan-dindikbud-kota-serang-ahmad-nuri-ariefdetikcom-1786094924878_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Kemenkes Minta TEP Petakan Persoalan Kesehatan di Kawasan Transmigrasi</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:21:03 +0700</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan minta Tim Ekspedisi Patriot 2026 fokus pada kesehatan masyarakat di kawasan transmigrasi. Angka harapan hidup Indonesia perlu ditingkatkan</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608732/kemenkes-minta-tep-petakan-persoalan-kesehatan-di-kawasan-transmigrasi</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kemenkes-minta-tim-ekspedisi-patriot-petakan-persoalan-kesehatan-di-kawasan-transmigrasi-1786094354769.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Polres Malang Tangkap Komplotan Pencuri 17 Baterai Tower Bikin Rugi Rp 432 Juta</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:18:54 +0700</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Haris Fadhil</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Polres Malang menangkap komplotan pencuri baterai litium tower telekomunikasi yang beraksi di sejumlah wilayah Kabupaten Malang.</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608730/polres-malang-tangkap-komplotan-pencuri-17-baterai-tower-bikin-rugi-rp-432-juta</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/konferensi-pers-polres-malang-dok-istimewa-1786094214521_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Soal Kopdes Merah Putih, Muzani Sebut Prabowo Banyak Geluti Pemikiran Hatta</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:18:30 +0700</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Ketua MPR RI Ahmad Muzani menyebut program Koperasi Desa Merah Putih terinspirasi pemikiran Bung Hatta, Bapak Koperasi Indonesia.</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608728/soal-kopdes-merah-putih-muzani-sebut-prabowo-banyak-geluti-pemikiran-hatta</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/12/ketua-mpr-ahmad-muzani-anggidetikcom-1773253269222_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Serba-serbi Satelit Lampung-1 Berbasis AI, Ini Fungsi dan Manfaatnya</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:16:05 +0700</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Widhia Arum Wibawana</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Satelit Lampung-1, hasil kolaborasi Pemprov Lampung dan STAR.VISION, diluncurkan untuk mendukung pembangunan berbasis data dan teknologi AI.</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608623/serba-serbi-satelit-lampung-1-berbasis-ai-ini-fungsi-dan-manfaatnya</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/satelit-hiperspektral-lampung-1-berbasis-kecerdasan-artifisial-ai-diluncurkan-dari-perairan-haiyang-provinsi-shandong-china-ra-1785933152789_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Muzani Respons Kabar Reshuffle Kabinet Setelah 17 Agustus</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:06:25 +0700</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Ketua MPR RI Ahmad Muzani menanggapi isu reshuffle kabinet. Sekjen Partai Gerindra itu menegaskan reshuffle merupakan hak prerogatif Presiden Prabowo.</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608711/muzani-respons-kabar-reshuffle-kabinet-setelah-17-agustus</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/03/12/ketua-mpr-ahmad-muzani-anggidetikcom-1773253269222_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Surabaya Buktikan Satu Data NIK Pacu Pertumbuhan Ekonomi Daerah</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:02:55 +0700</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Pemkot Surabaya berhasil membangun sistem Satu Data berbasis NIK, meningkatkan pelayanan publik dan ekonomi, serta meraih dua penghargaan nasional.</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608709/surabaya-buktikan-satu-data-nik-pacu-pertumbuhan-ekonomi-daerah</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/surabaya-buktikan-satu-data-nik-pacu-pertumbuhan-ekonomi-daerah-1786093335889.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Wamendagri Ribka Puji Penanganan Korban Dugaan Keracunan MBG di Jayapura</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:57:17 +0700</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Chayyara Zulghifary</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Wamendagri Ribka Haluk apresiasi penanganan cepat korban keracunan MBG di Papua. Ia mendorong pengawasan lebih ketat untuk mencegah kejadian serupa.</t>
+        </is>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608700/wamendagri-ribka-puji-penanganan-korban-dugaan-keracunan-mbg-di-jayapura</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/ribka-haluk-apresiasi-penanganan-korban-keracunan-mbg-papua-1786093016651.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I603" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Canda Prabowo ke Kepala BGN: Rambut Putih Tambah, Baru Seminggu Menjabat</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:54:24 +0700</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto melempar candaan ke Kepala Badan Gizi Nasional (BGN) Sudaryono yang menurutnya mulai berambut putih.</t>
+        </is>
+      </c>
+      <c r="F604" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608694/canda-prabowo-ke-kepala-bgn-rambut-putih-tambah-baru-seminggu-menjabat</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/prabowo-subianto-evadetikcom-1786092746487_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I604" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Polisi Dalami Temuan Narkoba dan 30 CD Porno di Sekolah Swasta Jaksel</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:43:17 +0700</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Polisi mendalami temuan 996 senjata di ruangan mantan ketua yayasan sekolah di Jaksel. Polisi juga akan mendalami temuan narkoba hingga CD porno di ruangan itu.</t>
+        </is>
+      </c>
+      <c r="F605" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608662/polisi-dalami-temuan-narkoba-dan-30-cd-porno-di-sekolah-swasta-jaksel</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temuan-ratusan-pucuk-senjata-di-sekolah-swasta-di-pondok-pinang-jakarta-selatan-1786014363566_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I605" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>TPA Cipayung Ditutup 3 Hari Imbas Hajatan Anggota DPRD Depok, Ini Kata DLH</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:37:12 +0700</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Surat edaran berisi imbauan truk sampah berpelat hitam untuk tak buang sampah ke TPS Cipayung Depok viral di medsos. Ini kata DLH Depok.</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608646/tpa-cipayung-ditutup-3-hari-imbas-hajatan-anggota-dprd-depok-ini-kata-dlh</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/17/kebakaran-padam-aktivitas-di-tpa-cipayung-depok-kembali-normal-1784256726866_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I606" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Viral Tumpukan Sampah Bikin Akses Siswa SD di Cengkareng Tertutup</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:34:56 +0700</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Tumpukan sampah seberat sekitar 140 ton menumpuk di wilayah RW 03, Kelurahan Kedaung Kali Angke. Sudin LH Jakbar menargetkan seluruh sampah terangkut hari ini.</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608637/viral-tumpukan-sampah-bikin-akses-siswa-sd-di-cengkareng-tertutup</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/sampah-seberat-140-ton-menumpuk-di-wilayah-rw-03-kelurahan-kedaung-kali-angke-jakarta-barat-1786091599551_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I607" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Polisi Periksa YouTuber Bigmo pada 10 Agustus Buntut Ajak Anak Promosi Vape</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:31:51 +0700</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya akan memanggil YouTuber Bigmo terkait dugaan pelibatan anak dalam promosi liquid vape. Klarifikasi dijadwalkan pada 10 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608633/polisi-periksa-youtuber-bigmo-pada-10-agustus-buntut-ajak-anak-promosi-vape</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/01/youtuber-bigmo-diadukan-ke-polisi-karena-diduga-mengeksploitasi-anak-dalam-siaran-langsung-doktangkapan-layar-medsos-1785590766503_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I608" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Terungkap Motif Asmara Cinta Segitiga di Balik Pria Depok Disayat OTK</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:30:30 +0700</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Devi Puspitasari</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Polisi mengungkap motif penyerangan pemuda di Depok akibat cemburu dalam cinta segitiga. Pelaku, remaja 16 tahun, menyerang korban dengan pisau cutter.</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608629/terungkap-motif-asmara-cinta-segitiga-di-balik-pria-depok-disayat-otk</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/07/25/ilustrasi-penangkapan_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I609" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Polisi Panggil Eks Ketua Yayasan soal Temuan Ratusan Senjata di Sekolah</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:28:26 +0700</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Taufiq Syarifudin</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Polres Metro Jakarta Selatan akan memeriksa mantan pengurus yayasan sekolah swasta terkait temuan 995 senjata. Ada dugaan keterlibatan dalam sengketa internal.</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608705/polisi-panggil-eks-ketua-yayasan-soal-temuan-ratusan-senjata-di-sekolah</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kasie-humas-polres-metro-jakarta-selatan-akp-joko-adiwibowo-1786083942095_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I610" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Suami Dokter Ngaku Pakai Medsos Istri Hina Pasien BPJS 'Triase Merah Dulu'</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:28:23 +0700</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Muhammad Aminudin</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Dokter di Malang, dr Herdiana, menuai kontroversi setelah komentar tidak pantas tentang pasien BPJS. Suaminya meminta maaf dan menjelaskan insiden tersebut.</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608626/suami-dokter-ngaku-pakai-medsos-istri-hina-pasien-bpjs-triase-merah-dulu</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/komentar-sinis-akun-dr-herdiana-di-kiriman-pasien-bpjs-yang-mengeluhkan-8-jam-tak-dapat-kamar-1786077312993_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Mensesneg Sebut Prabowo Ingin Hasil Riset BRIN Bisa Diproduksi Massal</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:24:41 +0700</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Mensesneg menyebutkan Presiden Prabowo ingin berbagai hasil riset Badan Riset dan Inovasi Nasional (BRIN) dikaji nilai ekonomi dan kemungkinan produksi massal.</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608616/mensesneg-sebut-prabowo-ingin-hasil-riset-brin-bisa-diproduksi-massal</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/presiden-prabowo-melihat-hasil-riset-brin-cahyo-biro-pers-media-dan-informasi-sekretariat-presiden-1786030862950.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I612" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Polisi Sebut Ratusan Senjata di Sekolah Swasta Jaksel Diimpor, untuk Apa?</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:21:39 +0700</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Polisi menyelidiki temuan 995 pucuk airsoft gun di yayasan sekolah Jakarta. Penyelidikan berfokus pada dokumen impor dan penyimpanan senjata tersebut.</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608612/polisi-sebut-ratusan-senjata-di-sekolah-swasta-jaksel-diimpor-untuk-apa</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kabid-humas-polda-metro-jaya-kombes-budi-hermanto-1786089469736_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Wamendagri Ajak Aparatur Pemerintah Maknai HUT RI dengan Semangat Juang</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:20:41 +0700</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Inkana Izatifiqa R. Putri</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Wamendagri Akhmad Wiyagus mengajak aparatur pemerintah memaknai HUT ke-81 RI dengan semangat perjuangan dan sportivitas melalui olahraga.</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608608/wamendagri-ajak-aparatur-pemerintah-maknai-hut-ri-dengan-semangat-juang</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/wamendagri-akhmad-wiyagus-1786090805461_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>6 Penjual Obat Keras Ilegal di Bogor Diringkus, Ratusan Tramadol-Hexymer Disita</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:18:20 +0700</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Polisi menangkap penjual obat keras tanpa izin edar atau ilegal di wilayah Kecamatan Parungpanjang, Bogor, Jawa Barat. Sebanyak enam orang ditangkap polisi.</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608604/6-penjual-obat-keras-ilegal-di-bogor-diringkus-ratusan-tramadol-hexymer-disita</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2015/11/06/6da17d61-730f-4c82-8d3a-363b30d553a8_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Jelang HUT ke-81 RI, Pimpinan MPR Ziarah ke Makam Bung Hatta</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:16:47 +0700</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Matius Alfons Hutajulu</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Ketua MPR RI Ahmad Muzani berziarah ke makam Bung Hatta jelang HUT RI ke-81. Muzani mengenang jasa Bung Hatta dalam pendirian dan kedaulatan RI.</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608603/jelang-hut-ke-81-ri-pimpinan-mpr-ziarah-ke-makam-bung-hatta</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/pimpinan-mpr-berziarah-ke-makam-bung-hatta-di-tpu-tanah-kusir-1786090565999_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Polisi Tangkap 8 Penganiaya dan Paksa Onani Pria di Tangerang</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:11:40 +0700</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Polisi menangkap delapan pelaku penganiayaan di Tangerang yang memaksa korban melakukan onani. Kasus ini melibatkan kekerasan dan penyebaran video.</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608595/polisi-tangkap-8-penganiaya-dan-paksa-onani-pria-di-tangerang</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/07/25/ilustrasi-penangkapan_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Sakit Stroke, Pak Awan Berharap Punya Gerobak untuk Mempermudah Jualan Balon</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:09:43 +0700</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Tim berbuatbaik.id</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Awan, 64 tahun, menjual balon untuk memenuhi kebutuhan hidup keluarganya. Mari bantu wujudkan harapannya memiliki gerobak untuk berjualan.</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608591/sakit-stroke-pak-awan-berharap-punya-gerobak-untuk-mempermudah-jualan-balon</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/02/awan-berbuatbaikid-1782991073958_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>Hari Internasional Masyarakat Adat Sedunia 2026: Sejarah hingga Tema</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Kanya Anindita Mutiarasari</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Hari Internasional Masyarakat Adat Sedunia 2026 diperingati pada 9 Agustus. Peringatan tahun ini mengangkat tema Honouring Indigenous Midwives.</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608299/hari-internasional-masyarakat-adat-sedunia-2026-sejarah-hingga-tema</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/02/padi-bergoyang-di-atas-bambu-ritual-ngarengkong-jadi-wujud-syukur-warga-citorek-1785667017795_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>Polisi Ungkap Pemilik Senpi di Sekolah Swasta Jaksel Sudah Meninggal</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:58:36 +0700</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Polisi menemukan 995 senjata airsoft gun di yayasan sekolah swasta Jakarta. Satu senjata api milik pria DS yang telah meninggal. Penyelidikan berlanjut.</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608578/polisi-ungkap-pemilik-senpi-di-sekolah-swasta-jaksel-sudah-meninggal</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kabid-humas-polda-metro-jaya-kombes-budi-hermanto-1786089469648_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Polisi Pastikan Kegiatan Belajar di Sekolah Jaksel Normal Usai Temuan Senjata</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:40:03 +0700</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Taufiq Syarifudin</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Polisi menyelidiki temuan 995 airsoft gun dan senjata api di sekolah Jakarta Selatan. Polisi memastikan kegiatan belajar tetap normal.</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608536/polisi-pastikan-kegiatan-belajar-di-sekolah-jaksel-normal-usai-temuan-senjata</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temuan-ratusan-pucuk-senjata-di-sekolah-swasta-di-pondok-pinang-jakarta-selatan-1786014363566_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Devy Anastasia Cantik Maksimal Saat Prewed</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:34:04 +0700</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Devy Anastasia menghitung hari jelang menikah. Kreator konten memasak itu membagikan penampilan menawan di momen prewedding.</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608767/devy-anastasia-cantik-maksimal-saat-prewed</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/devy-anastasia-1786094840057_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Kata Tengku Dewi Ketika Andrew Andika Rayakan Ultah Anak Bareng Istri</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:12:05 +0700</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Andrew Andika merayakan ulang tahun anak kedua dari pernikahannya dengan Tengku Dewi Putri, Zeya. Tengku menghargai apa yang dilakukan Andrew.</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8607281/kata-tengku-dewi-ketika-andrew-andika-rayakan-ultah-anak-bareng-istri</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/tengku-dewi-putri-1786008915226_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>Daus Mini Lapor Polisi Gak Terima Nama dan Foto Dicatut Konten Ujaran Kebencian</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:28:51 +0700</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Komedian Daus Mini melapor ke Polda Metro Jaya terkait pencemaran nama baik. Ia gak terima identitasnya dicatut dan dimanfaatkan untuk menyebarkan kebencian.</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608628/daus-mini-lapor-polisi-gak-terima-nama-dan-foto-dicatut-konten-ujaran-kebencian</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/daus-mini-1786090106353_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>3 Pesan Penting Rieke Diah Pitaloka ke 3 Anak Cowok</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:12:44 +0700</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Rieke Diah Pitaloka mengungkap kekhawatirannya sebagai ibu saat anak-anak remajanya mulai mandiri. Ia berbagi pengalaman panik saat anaknya tak bisa dihubungi.</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8606403/3-pesan-penting-rieke-diah-pitaloka-ke-3-anak-cowok</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/20/anggota-komisi-xiii-dpr-ri-rieke-diah-pitaloka-1784539374041_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Momen Haru Audellya Ambara Harsono Tampil di IFW</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:59:08 +0700</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>prih febriani</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Audellya Ambara Harsono, model muda dan Puteri Anak Indonesia Pendidikan, berbagi pengalaman berharga di Indonesia Fashion Week 2026.</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608579/momen-haru-audellya-ambara-harsono-tampil-di-ifw</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/audellya-ambara-harsono-1786083385128_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Mail Syahputra, Asisten Nikita Mirzani Ajukan PK Dugaan TPPU dan Pemerasan</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:24:54 +0700</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Ismail Marzuki, asisten Nikita Mirzani, ajukan PK atas dugaan pemerasan dan TPPU. Kuasa hukum kritik kekhilafan hakim dalam penerapan UU ITE.</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608269/mail-syahputra-asisten-nikita-mirzani-ajukan-pk-dugaan-tppu-dan-pemerasan</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/07/24/nikita-mirzani-jalani-sidang-ttpu-1753328999013_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Istana Buka Suara Respons Isu Reshuffle Kabinet Agustus</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:40:57 +0700</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Menteri Prasetyo Hadi menegaskan belum ada rencana reshuffle Kabinet Merah Putih, hanya untuk mengisi posisi kosong. Isu reshuffle awal Agustus juga dibantah.</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807161156-32-1389804/istana-buka-suara-respons-isu-reshuffle-kabinet-agustus</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/istana-buka-suara-soal-pengambilalihan-saham-kereta-cepat-oleh-kemenkeu-1785997652333_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Wamen Wiyagus Ajak ASN Maknai HUT RI dengan Semangat Sportivitas</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:55:18 +0700</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>TIM</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Akhmad Wiyagus mengatakan peringatan kemerdekaan tidak semestinya hanya diisi dengan kegiatan seremonial semata.</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807155208-20-1389797/wamen-wiyagus-ajak-asn-maknai-hut-ri-dengan-semangat-sportivitas</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/wamendagri-wiyagus-ajak-aparatur-pemerintah-maknai-hut-ke-81-ri-dengan-semangat-juang-dan-sportivitas-1786092634854_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Pegawai RSUD di Tasikmalaya yang Cibir Pasien BPJS Pilih &lt;i&gt;Resign&lt;/i&gt;</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:46:11 +0700</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Seorang pegawai RSUD dr Soekardjo mengundurkan diri setelah kritik publik terkait komentar tidak empati terhadap pasien BPJS.</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807150259-20-1389776/pegawai-rsud-di-tasikmalaya-yang-cibir-pasien-bpjs-pilih-resign</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/05/24/ilustrasi-konsultasi-dengan-dokter_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Paper Mob ala Siswa Sekolah Rakyat Sulsel</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:44:51 +0700</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Ratusan siswa menyambut kedatangan Mensos Saifullah Yusuf (Gus Ipul) dengan penampilan paper mob di Sekolah Rakyat Provinsi Sulawesi Selatan.</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807154113-20-1389796/paper-mob-ala-siswa-sekolah-rakyat-sulsel</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/paper-mob-ala-siswa-sekolah-rakyat-sulsel-1786092120239_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>Ratusan Senjata di Yayasan Sekolah Jaksel Diduga Impor</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:43:14 +0700</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Ratusan senjata ditemukan di yayasan sekolah swasta di Pondok Pinang, Jaksel, diduga hasil impor. Polisi mendalami alasan penyimpanan dan legalitasnya.</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807152226-12-1389782/ratusan-senjata-di-yayasan-sekolah-jaksel-diduga-impor</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/995-senjata-yang-ditemukan-di-ruang-mantan-ketua-yayasan-sekolah-jaksel-1786011308099_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Wacana Pilkada Tanpa Wakil, Ganjar Minta DPR Bentuk Pansus RUU Pemilu</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:26:42 +0700</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Politikus PDIP Ganjar Pranowo dorong DPR bentuk pansus untuk bahas revisi UU Pemilu. Tujuh isu penting perlu dibahas komprehensif terkait pilkada.</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807074904-32-1389570/wacana-pilkada-tanpa-wakil-ganjar-minta-dpr-bentuk-pansus-ruu-pemilu</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/08/14/ganjar-pranowo-di-dpp-pdip-1755170077862_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>Leher Remaja Depok Disayat Cutter, Pelaku Ditangkap di Margonda</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:04:02 +0700</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Polisi menangkap RA (19) setelah menyerang MAN (16) di Depok. Pelaku terpaksa ditembak saat melawan. Korban mengalami luka serius di leher.</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807144436-12-1389760/leher-remaja-depok-disayat-cutter-pelaku-ditangkap-di-margonda</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/05/30/ilustrasi-penangkapan-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Polisi: Ratusan Senjata di Sekolah Jaksel Tak Terkait Kegiatan Ekskul</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:00:44 +0700</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>Polisi menyelidiki temuan ratusan senjata di sekolah swasta Jakarta. Pemilik menyatakan senjata airsoft gun tersebut legal dan untuk kegiatan ekstrakurikuler.</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807142154-12-1389742/polisi-ratusan-senjata-di-sekolah-jaksel-tak-terkait-kegiatan-ekskul</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/995-senjata-yang-ditemukan-di-ruang-mantan-ketua-yayasan-sekolah-jaksel-1786011308187_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Rekomendasi RSA UGM ke Nakes Cibir Pasien BPJS: Sanksi Berat</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:56:40 +0700</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Rumah Sakit Akademik UGM merekomendasikan sanksi berat untuk perawat yang melontarkan komentar nirempati di media sosial terkait pasien BPJS yang meninggal.</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807142333-12-1389741/rekomendasi-rsa-ugm-ke-nakes-cibir-pasien-bpjs-sanksi-berat</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/06/28/ilustrasi-tenaga-kesehatan-di-masa-pandemi_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Polda Metro: Pemilik Senpi di Yayasan Sekolah Jaksel Sudah Meninggal</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:51:20 +0700</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Polisi mengungkap senjata api Franchi SPAS-15 yang ditemukan di yayasan sekolah swasta di Jakarta, pemiliknya sudah meninggal sejak 2020.</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807143658-12-1389757/polda-metro-pemilik-senpi-di-yayasan-sekolah-jaksel-sudah-meninggal</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/995-senjata-yang-ditemukan-di-ruang-mantan-ketua-yayasan-sekolah-jaksel-1786011308187_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>PO Bus Klarifikasi Viral Klakson Suara Jokowi 'Saya Akan Lawan'</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:30:43 +0700</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>PO MTrans bantah armada busnya gunakan klakson suara Jokowi 'saya akan lawan'. Humas MTrans sebut video yang beredar viral itu diduga hasil editan.</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807140236-20-1389739/po-bus-klarifikasi-viral-klakson-suara-jokowi-saya-akan-lawan</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/05/13/ilustrasi-sopir-bus-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Kata Mabes TNI soal Sertifikat Pramuka Bisa Daftar TNI-Polri Tanpa Tes</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:25:07 +0700</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Mabes TNI menjelaskan sertifikat Pramuka Garuda dapat menjadi nilai tambah dalam pendaftaran TNI dan Polri, namun tidak menggantikan proses seleksi resmi.</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807141058-20-1389722/kata-mabes-tni-soal-sertifikat-pramuka-bisa-daftar-tni-polri-tanpa-tes</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/08/14/pramuka-gelar-perkemahan-nasional-untuk-anak-berkebutuhan-khususpramuka-gelar-perkemahan-nasional-untuk-anak-berkebutuhan-khus-1755177247887_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Berompi Tahanan dan Tangan Diborgol, Febrie Diperiksa di Kejagung</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:23:46 +0700</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Mantan Jaksa Agung Muda Pidana Khusus, Febrie Adriansyah, menjalani pemeriksaan sebagai tersangka kasus dugaan pencucian uang pada Jumat (7/8).</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807135121-16-1389704/berompi-tahanan-dan-tangan-diborgol-febrie-diperiksa-di-kejagung</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/febrie-jalani-pemeriksaan-sebagai-tersangka-di-kejagung-1786086472671_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Teror Monyet di Inhil Riau: Ada 18 Korban, Sekolah Terapkan PJJ</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:20:24 +0700</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Serangan monyet ekor panjang di Inhil, Riau, menyebabkan 18 korban. Sekolah terpaksa belajar daring untuk mengantisipasi serangan lebih lanjut.</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807100227-20-1389718/teror-monyet-di-inhil-riau-ada-18-korban-sekolah-terapkan-pjj</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2014/09/25/ecb70abf-f34b-4842-b204-861a21ef2098_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I641" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Istana Bantah Isu Prabowo Terbitkan Surpres Ganti Kapolri Listyo</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:19:08 +0700</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara menegaskan tidak ada surat presiden untuk pergantian Kapolri. Isu reshuffle kabinet juga dibantah.</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807140859-32-1389720/istana-bantah-isu-prabowo-terbitkan-surpres-ganti-kapolri-listyo</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/22/presiden-prabowo-menerbitkan-keppres-pergantian-pejabat-di-kejagung-1784701099943_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I642" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Polisi Dalami Legalitas Ratusan Senjata di Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:47:35 +0700</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Polisi menyelidiki legalitas ratusan senjata yang ditemukan di yayasan sekolah swasta di Jakarta. Temuan mencakup airsoft gun dan senjata api.</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807132254-12-1389691/polisi-dalami-legalitas-ratusan-senjata-di-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/995-senjata-yang-ditemukan-di-ruang-mantan-ketua-yayasan-sekolah-jaksel-1786011308099_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I643" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Bripda IH Dilaporkan Terkait Dugaan Pembunuhan Mantan Istri di Medan</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:40:05 +0700</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Orang tua L melaporkan Bripda IH ke Polda Sumut terkait dugaan pembunuhan anaknya. Keluarga curiga ada kejanggalan pada jenazah L yang diduga bunuh diri.</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807131306-12-1389696/bripda-ih-dilaporkan-terkait-dugaan-pembunuhan-mantan-istri-di-medan</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/08/24/8a7149c5-8060-403e-9fba-e91b1608a9fb_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I644" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Pakai Rompi Pink-Tangan Diborgol, Febrie Adriansyah Dibawa ke Kejagung</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:32:30 +0700</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Mobil tahanan menjemput Eks Jampidsus Febrie Adriansyah, tersangka TPPU, untuk pemeriksaan di Kejaksaan Agung.</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807132224-12-1389692/pakai-rompi-pink-tangan-diborgol-febrie-adriansyah-dibawa-ke-kejagung</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/febrie-adriansyah-berangkat-untuk-diperiksa-di-kejagung-1786087913716_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I645" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>FOTO: Merawat Sumber Air di Kedalaman Gua Keceme Gunungkidul</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:23:21 +0700</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Kegiatan ini dilakukan untuk menjaga pasokan air bersih tetap tersedia bagi warga yang bergantung pada sumber air tersebut selama musim kemarau.</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807101309-22-1389613/foto-merawat-sumber-air-di-kedalaman-gua-keceme-gunungkidul</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/perawatan-sumber-air-di-gua-keceme-gunungkidul-1786072364916_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I646" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Kapolresta Banda Aceh dan Kasat Narkoba Diperiksa Propam Mabes Polri</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:21:34 +0700</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Kapolresta Banda Aceh Kombes Pol Andi Kirana dan Kasat Narkoba AKP Muhammad Jabir diperiksa di Mabes Polri.</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807125630-12-1389683/kapolresta-banda-aceh-dan-kasat-narkoba-diperiksa-propam-mabes-polri</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/08/09/ilustrasi-anggota-polisi-berseragam-dinas-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I647" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Daftar Senjata yang Ditemukan di Ruang Ketua Yayasan Sekolah di Jaksel</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:09:12 +0700</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Polisi menemukan 995 senjata, termasuk airsoft gun dan senjata api, di yayasan sekolah swasta di Pondok Pinang. Berikut rinciannya.</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807124727-12-1389680/daftar-senjata-yang-ditemukan-di-ruang-ketua-yayasan-sekolah-di-jaksel</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/995-senjata-yang-ditemukan-di-ruang-mantan-ketua-yayasan-sekolah-jaksel-1786011308187_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I648" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Bareskrim Bongkar Narkoba di Klub Five Star Bali, 53 Orang Ditangkap</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:52:23 +0700</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Bareskrim Polri menggerebek kelab malam Five Star di Denpasar, Bali, mengamankan 53 orang terkait peredaran narkoba. Informasi lebih lanjut menyusul.</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807124343-12-1389675/bareskrim-bongkar-narkoba-di-klub-five-star-bali-53-orang-ditangkap</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/bareskrim-ungkap-peredaran-narkoba-di-klub-five-star-bali-1786081508003_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I649" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Dugaan Sengketa Yayasan di Balik Temuan Senjata di Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:09:46 +0700</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>Alhadid Endar Putra selaku kuasa hukum eks ketua yayasan sebuah sekolah swasta di Jakarta Selatan menyebut ada sengketa yayasan di balik temuan ratusan senjata.</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807120425-12-1389665/dugaan-sengketa-yayasan-di-balik-temuan-senjata-di-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/995-senjata-yang-ditemukan-di-ruang-mantan-ketua-yayasan-sekolah-jaksel-1786011308187_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I650" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Pihak Sekolah Bantah Temuan Ratusan Senjata untuk Ekskul Menembak</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:59:00 +0700</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Sekolah swasta di Pondok Pinang bantah ratusan senjata terkait ekstrakurikuler menembak. Kuasa hukum ungkap penyimpanan senjata akibat sengketa yayasan.</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807114932-12-1389657/pihak-sekolah-bantah-temuan-ratusan-senjata-untuk-ekskul-menembak</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/995-senjata-yang-ditemukan-di-ruang-mantan-ketua-yayasan-sekolah-jaksel-1786011308187_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I651" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>FOTO: Sang Saka Merah Putih Raksasa Mulai Berkibar Sambut HUT ke-81 RI</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:47:40 +0700</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>ANTARA</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Bendera Merah Putih berukuran besar mulai dikibarkan di sejumlah wilayah menyambut Hari Kemerdekaan RI.</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807095908-22-1389600/foto-sang-saka-merah-putih-raksasa-mulai-berkibar-sambut-hut-ke-81-ri</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/pengibaran-merah-putih-raksasa-di-stadion-pakansari-1786071476423_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I652" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Diperiksa Hari Ini, Kuasa Hukum Pastikan Febrie Adriansyah Kooperatif</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:43:47 +0700</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Kuasa hukum Febrie Adriansyah mengonfirmasi pemeriksaan kliennya oleh Tim 9 Kejaksaan Agung. Febrie akan kooperatif terkait dugaan pencucian uang.</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807113256-12-1389649/diperiksa-hari-ini-kuasa-hukum-pastikan-febrie-adriansyah-kooperatif</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/04/eks-jampidsus-febrie-bakal-ajukan-praperadilan-soal-status-tersangka-hingga-penyitaan-1785831420810_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I653" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Kemensos Bentuk TP2SR, Kebut Pembangunan Sekolah Rakyat Permanen</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:41:41 +0700</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Kementerian Sosial membentuk Tim Percepatan Pembangunan Sekolah Rakyat (TP2SR) sebagai tim ad hoc untuk mengawal percepatan pembangunan Sekolah Rakyat permanen.</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807113821-20-1389652/kemensos-bentuk-tp2sr-kebut-pembangunan-sekolah-rakyat-permanen</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/kemensos-bentuk-tp2sr-kebut-pembangunan-sekolah-rakyat-permanen-1786077616526_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I654" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Menghadap Wamensos, 4 Bupati Siap  Bangun Sekolah Rakyat Permanen</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:37:42 +0700</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Empat kepala daerah dari Agam, Buton Selatan, Kutai Kertanegara, dan Buru datang siap selengarakan Sekolah Rakyat.</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807113508-20-1389650/menghadap-wamensos-4-bupati-siap-bangun-sekolah-rakyat-permanen</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/menghadap-wamensos-4-bupati-siap-bangun-sekolah-rakyat-permanen-1786077382642_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I655" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Kemenkes Ungkap Alasan Yurizal Harus Tunggu 8 Jam di IGD RSCM</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:33:08 +0700</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Kemenkes menjelaskan kasus pasien BPJS yang menunggu 8 jam di IGD RSCM sebelum meninggal. Kapasitas HCU terbatas jadi penyebab lamanya penanganan.</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807111255-20-1389642/kemenkes-ungkap-alasan-yurizal-harus-tunggu-8-jam-di-igd-rscm</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/02/12/rscm-tetap-berikan-pelayanan-meski-polemik-bjps-pbi-1770892443037_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I656" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Ipda MA, Polisi Penabrak Motor Hingga Tewaskan Balita di Bone Ditahan</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:13:54 +0700</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Ipda MA (49) menjalani penahanan di sel Seksi Profesi dan Pengamanan (Propam) Polres Bone, Sulawesi Selatan, setelah diduga menabrak pengendara sepeda motor.</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807110907-12-1389639/ipda-ma-polisi-penabrak-motor-hingga-tewaskan-balita-di-bone-ditahan</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/05/30/ilustrasi-penangkapan-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I657" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Pihak Eks Ketua Yayasan Buka Suara soal Temuan Narkoba dan CD Porno</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:07:32 +0700</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Pihak mantan ketua yayasan sekolah di Pondok Pinang buka suara kepemilikan narkoba dan CD porno.</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807105746-12-1389628/pihak-eks-ketua-yayasan-buka-suara-soal-temuan-narkoba-dan-cd-porno</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/995-senjata-yang-ditemukan-di-ruang-mantan-ketua-yayasan-sekolah-jaksel-1786011308099_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I658" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Kegiatan Belajar Sekolah di Jaksel Normal Usai Temuan Ratusan Senjata</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:58:23 +0700</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Kegiatan belajar di sekolah swasta Pondok Pinang Jakarta tetap normal setelah penemuan 995 senjata.</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807104841-20-1389625/kegiatan-belajar-sekolah-di-jaksel-normal-usai-temuan-ratusan-senjata</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/995-senjata-yang-ditemukan-di-ruang-mantan-ketua-yayasan-sekolah-jaksel-1786011308187_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I659" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Daftar Nakes Minta Maaf Usai Cibir Pasien BPJS di Medsos</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:39:54 +0700</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Sejumlah tenaga kesehatan meminta maaf setelah komentar tidak empati terhadap pasien BPJS yang meninggal.</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807101153-20-1389612/daftar-nakes-minta-maaf-usai-cibir-pasien-bpjs-di-medsos</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/08/08/ilustrasi-logo-threads_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I660" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Lodewyk Pusung Kembali Ajukan Praperadilan, Kali Ini ke PN Jakpus</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 10:07:21 +0700</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Mantan Wakil Kepala Badan Gizi Nasional (BGN), Lodewyk Pusung, kembali mengajukan Praperadilan ke pengadilan.</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807100253-12-1389610/lodewyk-pusung-kembali-ajukan-praperadilan-kali-ini-ke-pn-jakpus</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/27/sidang-praperadilan-eks-waka-bgn-minta-hakim-nyatakan-penyidikan-kejaksaan-tidak-sah-1785123700284_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I661" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Kemdikti Buka Suara soal Paper 'Nobel MBG'</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:48:37 +0700</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Kementerian Pendidikan Tinggi, Sains, dan Teknologi RI (Kemendiktisaintek) mengungkap hasil investigasi awal terkait makalah MBG masuk nobel.</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807094147-20-1389597/kemdikti-buka-suara-soal-paper-nobel-mbg</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/06/02/raker-komisi-x-dpr-dengan-mendiktisaintek-1780382685859_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I662" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>RS Pusri Palembang Pecat Dokter Hina Pasien BPJS 'Banyakin Duit Halal'</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 09:16:53 +0700</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>RS Pusri Palembang akhiri kerja sama dengan dr Tamara Dewi Jasmine setelah komentar nirempati dalam utas pasien BPJS.</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807090510-20-1389586/rs-pusri-palembang-pecat-dokter-hina-pasien-bpjs-banyakin-duit-halal</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/07/14/ilustrasi-dokter-alat-medis-4_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I663" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Tim 9 Kejagung Bakal Periksa Febrie Adriansyah di KPK Hari Ini</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:56:49 +0700</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Kejaksaan Agung jadwalkan pemeriksaan mantan Jaksa Agung Muda, Febrie Adriansyah, sebagai tersangka TPPU.</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807082926-12-1389581/tim-9-kejagung-bakal-periksa-febrie-adriansyah-di-kpk-hari-ini</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/25/febrie-adriansyah-ditahan-kejagung-1784914764925_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I664" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Respons TNI AD soal Pramuka Garuda Bisa Daftar TNI-Polri Tanpa Tes</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:35:16 +0700</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>TNI Angkatan Darat (AD) menegaskan proses seleksi tetap dilakukan sekalipun seseorang memegang sertifikat Pramuka Garuda.</t>
+        </is>
+      </c>
+      <c r="F665" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807062252-20-1389537/respons-tni-ad-soal-pramuka-garuda-bisa-daftar-tni-polri-tanpa-tes</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/08/01/pramuka-indonesia_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I665" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Kejagung Periksa Don Ritto dan 8 Pihak Swasta di Kasus TPPU Febrie</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:16:19 +0700</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Kejagung kembali memeriksa Don Ritto (DR) selaku tersangka di kasus TPPU emas 74 kilogram dan uang Rp543 miliar di rumah Sentul milik Febrie Adriansyah.</t>
+        </is>
+      </c>
+      <c r="F666" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807081201-12-1389577/kejagung-periksa-don-ritto-dan-8-pihak-swasta-di-kasus-tppu-febrie</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/17/don-ritto-di-kejaksaan-1784284326917_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I666" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>Cibir Pasien BPJS 'Ruang Jenazah Kosong', Dokter di NTT Minta Maaf</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 08:10:42 +0700</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>Kasus dugaan penghinaan pasien BPJS viral setelah keluhan Yurizal. Komentar dokter Beni memicu kritik, ia minta maaf dan siap terima konsekuensi.</t>
+        </is>
+      </c>
+      <c r="F667" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807073823-20-1389569/cibir-pasien-bpjs-ruang-jenazah-kosong-dokter-di-ntt-minta-maaf</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/07/14/ilustrasi-dokter-alat-medis-2_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I667" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Hasan Nasbi Bicara Dunia Simulakra, Algoritma, dan Statecraft RI</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:30:05 +0700</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>Saksikan obrolan seru di Podcast What The Fact! Politics bersama Penasihat Khusus Presiden Bidang Komunikasi, Hasan Nasbi.</t>
+        </is>
+      </c>
+      <c r="F668" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806183507-32-1389436/hasan-nasbi-bicara-dunia-simulakra-algoritma-dan-statecraft-ri</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/podcast-what-the-fact-politics-1786015927457_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I668" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>10 Nakes yang Cibir Pasien BPJS Masuk Radar KKI: Dokter Gigi-Perawat</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:29:54 +0700</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Konsil Kesehatan Indonesia menyelidiki dugaan penghinaan pasien BPJS oleh sejumlah tenaga kesehatan di media sosial.</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807071519-20-1389554/10-nakes-yang-cibir-pasien-bpjs-masuk-radar-kki-dokter-gigi-perawat</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2020/03/11/2d153fdc-4635-4139-88b4-aafe5f017ac9_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I669" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Ikut Cibir Pasien BPJS, Dokter Puskesmas Pakisaji Malang Dinonaktifkan</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:10:53 +0700</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr">
+        <is>
+          <t>Dokter Herdiana di Puskesmas Pakisaji dinonaktifkan setelah komentar menghina pasien BPJS yang meninggal.</t>
+        </is>
+      </c>
+      <c r="F670" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G670" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807065836-20-1389549/ikut-cibir-pasien-bpjs-dokter-puskesmas-pakisaji-malang-dinonaktifkan</t>
+        </is>
+      </c>
+      <c r="H670" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/07/14/ilustrasi-dokter-alat-medis_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I670" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>KPK Bakal Panggil Kakanim Jaksel Usai Temuan Uang Sin$8.500</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 07:01:56 +0700</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr">
+        <is>
+          <t>KPK akan memanggil Kakanim Jakarta Selatan, Winarko, terkait temuan Sin$8.500 di ruang kerjanya.</t>
+        </is>
+      </c>
+      <c r="F671" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G671" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807062830-12-1389544/kpk-bakal-panggil-kakanim-jaksel-usai-temuan-uang-sin-8500</t>
+        </is>
+      </c>
+      <c r="H671" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2020/02/17/e5d4d7af-456f-414f-9e2e-bcebe2fa6000_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I671" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Fakta-fakta Temuan Ratusan Senjata di Yayasan Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 06:37:21 +0700</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr">
+        <is>
+          <t>Ratusan senjata ditemukan di sebuah ruangan mantan ketua yayasan sebuah sekolah swasta yang berlokasi di Pondok Pinang, Kebayoran Lama, Jakarta Selatan.</t>
+        </is>
+      </c>
+      <c r="F672" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G672" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807062936-12-1389541/fakta-fakta-temuan-ratusan-senjata-di-yayasan-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H672" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/04/13/polri-tangkap-ki-bedil-terkait-penjualan-senjata-api-ilegal-di-jabar-1776055302711_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I672" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Polda Tetapkan 4 Tersangka Penampung 52,5 ton Timah Ilegal Belitung</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 05:58:39 +0700</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>Direktorat Reskrimsus Polda Babel menetapkan 4 tersangka dalam kasus penampungan 52,5 ton bijih timah ilegal. Penindakan ini untuk pemberantasan tambang ilegal.</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G673" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807000021-12-1389523/polda-tetapkan-4-tersangka-penampung-525-ton-timah-ilegal-belitung</t>
+        </is>
+      </c>
+      <c r="H673" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/09/08/ilustrasi-tindakan-kriminal-5_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I673" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Bareskrim Turun Tangan Selidiki Tambang Pasir Timah Ilegal di Belitung</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 05:45:31 +0700</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr">
+        <is>
+          <t>Bareskrim menyelidiki kasus penyelundupan 50 ton pasir timah ilegal di Belitung. Tiga tersangka ditangkap, penyidikan berlanjut untuk mengungkap aktor utama.</t>
+        </is>
+      </c>
+      <c r="F674" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G674" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806220113-12-1389514/bareskrim-turun-tangan-selidiki-tambang-pasir-timah-ilegal-di-belitung</t>
+        </is>
+      </c>
+      <c r="H674" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/pasir-timah-ilegal-belitung-1786033949870_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I674" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Kematian Eks Istri Polisi Medan, Dokter Jelaskan Asal-usul Luka Lebam</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 05:15:22 +0700</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>Kematian L, mantan istri personel Polsek, jadi sorotan. Dokter forensik ungkap luka tembak tempel, dan bantah dugaan penganiayaan dari keluarga.</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807005711-12-1389525/kematian-eks-istri-polisi-medan-dokter-jelaskan-asal-usul-luka-lebam</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/eks-istri-polisi-di-medan-bunuh-diri-dokter-forensik-jelaskan-asal-usul-luka-lebam-1786023343953_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Kematian Eks Istri Polisi di Medan, Polisi Ungkap Posisi Jasad-Senpi</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 05:00:12 +0700</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>Seorang perempuan berusia 30 tahun ditemukan tewas diduga bunuh diri dengan senjata mantan suaminya. Polisi menyelidiki kasus ini dan menemukan jejak tembakan.</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807004511-12-1389524/kematian-eks-istri-polisi-di-medan-polisi-ungkap-posisi-jasad-senpi</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/polisi-tangkap-pria-di-medan-produksi-konten-pornografi-gay-dijual-rp50-ribu-1785927191482_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Wacana Pilkada Tanpa Wakil, Golkar Ingatkan Pengganti Kepala Daerah</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 03:36:18 +0700</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>Anggota DPR dari Fraksi Golkar mengingatkan pengganti kepala daerah bila berhalangan saat merespons wacana Pilkada tanpa Wakil Kepala Daerah.</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807012510-32-1389526/wacana-pilkada-tanpa-wakil-golkar-ingatkan-pengganti-kepala-daerah</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/12/01/rekapitulasi-berjenjang-pilkada-jakarta-11_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Karhutla di Alun-alun Suryakancana Gunung Gede Pangrango</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 02:06:25 +0700</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Kebakaran lahan terjadi di Alun-alun Suryakancana, Gunung Gede Pangrango. Relawan dan warga berhasil padamkan api setelah tiga jam.</t>
+        </is>
+      </c>
+      <c r="F678" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807002236-20-1389522/karhutla-di-alun-alun-suryakancana-gunung-gede-pangrango</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/09/28/dc18c612-acc3-4853-a1d0-5242d64e70fb_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I678" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Eks Ketua DPRD Ponorogo Jadi Tersangka Korupsi Tunjangan Perumahan</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 00:17:55 +0700</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Kejari Ponorogo menetapkan mantan Ketua DPRD SN sebagai tersangka korupsi tunjangan anggota DPRD, merugikan negara Rp3,6 miliar.</t>
+        </is>
+      </c>
+      <c r="F679" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260806234043-12-1389520/eks-ketua-dprd-ponorogo-jadi-tersangka-korupsi-tunjangan-perumahan</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/07/24/0676200f-0af8-4c87-a754-bff6467e55d7_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I679" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Jadwal Dewata Challenge Series 2026: Persib Bandung Kembali Tempur di Bali, Jadi Modal Jelang ACL 2</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:31:35 +0700</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>Jadwal lengkap Dewata Challenge Series 2026, turnamen pramusim segitiga yang diikuti Bali United, Persib Bandung, dan klub Malaysia, Sabah FC.</t>
+        </is>
+      </c>
+      <c r="F680" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7865350/jadwal-dewata-challenge-series-2026-persib-bandung-kembali-tempur-di-bali-jadi-modal-jelang-acl-2</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/XmIlLyqYi2qEIe0XEOOcu_Tc6gY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Pemain-Persib-Bandung-melakukan-selebrasi-bersama-setelah-mencetak-gol-ke-gawang-Persija-Jakarta.jpg</t>
+        </is>
+      </c>
+      <c r="I680" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Geger Temuan 995 Senpi di Sekolah Swasta Jaksel, Pramono Anung: Yayasan Beri Contoh yang Tidak Baik</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:30:48 +0700</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Gubernur DKI Jakarta, Pramono Anung menilai insiden penemuan senpi di sekolah swasta ini menunjukkan bahwa yayasan memberikan contoh yang tidak baik.</t>
+        </is>
+      </c>
+      <c r="F681" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7865349/geger-temuan-995-senpi-di-sekolah-swasta-jaksel-pramono-anung-yayasan-beri-contoh-yang-tidak-baik</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/8oKD7KedTktuPKYPY4PG1DiYiQI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/GUBERNUR-DKI-JAKARTA-PRAMONO-ANUNG.jpg</t>
+        </is>
+      </c>
+      <c r="I681" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>Kasus 995 Senjata di Sekolah Jaksel, Kemendikdasmen Siap Beri Pendampingan Guru dan Siswa</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:26:34 +0700</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Kemendikdasmen menyiapkan langkah antisipasi usai temuan 995 senjata di sekolah, sementara polisi masih mengusut asal-usulnya.</t>
+        </is>
+      </c>
+      <c r="F682" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865348/kasus-995-senjata-di-sekolah-jaksel-kemendikdasmen-siap-beri-pendampingan-guru-dan-siswa</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/TtOpqja35eI2BWeOx6VbqBObjg8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/abdul-muti-kenaaaang-soeharto.jpg</t>
+        </is>
+      </c>
+      <c r="I682" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Ikut Komentar Nirempati kepada Pasien BPJS, Perawat RSUD Cicalengka Bandung Dinonaktifkan</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:24:45 +0700</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Nieke Adelia Marlina dinonaktifkan sebagai perawat di RSUD Cicalengka, Kabupaten Bandung, Jawa Barat buntut komentar nirempati kepada pasien BPJS</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865347/ikut-komentar-nirempati-kepada-pasien-bpjs-perawat-rsud-cicalengka-bandung-dinonaktifkan</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/p0kXUyCR8fnZZnvbSAImBeiibE4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/KOMENTAR-PASIEN-BPJS-1.jpg</t>
+        </is>
+      </c>
+      <c r="I683" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Bahlil Luncurkan 10 Buku, Rosan Meramal Akan Jadi Tokoh Besar dari Timur</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:23:56 +0700</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>CEO Danantara Rosan Roeslani meramal, sahabat dekatnya, Menteri ESDM Bahlil Lahadalia, akan menjadi tokoh besar dari Timur di masa datang.</t>
+        </is>
+      </c>
+      <c r="F684" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865346/bahlil-luncurkan-10-buku-rosan-meramal-akan-jadi-tokoh-besar-dari-timur</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/oU_EXyxCAS_Ns7afpZeyNbTJTGM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Rosan-Roeslani-dan-Bahlil-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I684" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Percepat Transformasi Digital, Kemenperin Perkuat Ekosistem Startup Nasional</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:23:20 +0700</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Menurut Agus, Indonesia memiliki modal yang sangat besar untuk menjadi pusat pertumbuhan startup di kawasan.</t>
+        </is>
+      </c>
+      <c r="F685" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7865345/percepat-transformasi-digital-kemenperin-perkuat-ekosistem-startup-nasional</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/HSY_UBp_adO0cRM0LMVXwIviSiY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Agus-Gumiwang-saat-Peluncuran-Resmi-Indo-Startup-Expo-and-Forum.jpg</t>
+        </is>
+      </c>
+      <c r="I685" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Wamendagri Wiyagus Ajak Aparatur Maknai HUT RI dengan Semangat Juang dan Sportivitas</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:20:36 +0700</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Wamendagri Akhmad Wiyagus mengajak aparatur memaknai HUT ke-81 RI dengan semangat perjuangan, sportivitas, dan nasionalisme.</t>
+        </is>
+      </c>
+      <c r="F686" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kilas-kementerian/7865344/wamendagri-wiyagus-ajak-aparatur-maknai-hut-ri-dengan-semangat-juang-sportivitas</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/UdytLN2_c8jd5JZYx6NheVAJgxQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Wamendagri-Wiyagus-0608.jpg</t>
+        </is>
+      </c>
+      <c r="I686" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>Febri Diansyah Ungkap Alasan Bersedia Jadi Pengacara Eks Jampidsus Febrie Adriansyah</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:19:55 +0700</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Mantan Juru Bicara KPK Febrie Diansyah mengungkap alasan dia bersedia menjadi kuasa hukum yang mendampingi eks Jampidsus Febrie Adriansyah.</t>
+        </is>
+      </c>
+      <c r="F687" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865343/febri-diansyah-ungkap-alasan-bersedia-jadi-pengacara-eks-jampidsus-febrie-adriansyah</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/JtDGfgLMfqLaDv2EqREy2aMlyMQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Mantan-Jubir-KPK-Febri-Diansyah-kiri-dan-mantan-Jampidsus-Febrie-Adriansyah-kanan.jpg</t>
+        </is>
+      </c>
+      <c r="I687" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Lomba Artikel dan Video Kreatif untuk Umum, Total Hadiah Rp50 Juta</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:19:00 +0700</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Kemkomdigi dan genbestid buka lomba artikel dan video kreatif bertema kesehatan. Total hadiah mencapai Rp50 Juta berdasarkan pembagian pemenang.</t>
+        </is>
+      </c>
+      <c r="F688" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7865342/lomba-artikel-dan-video-kreatif-untuk-umum-total-hadiah-rp50-juta</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/cRDtU_7fzVKrKX2Mf-VQ4LivE5w=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/LOMBA-ARTIKEL-VIDEO-45345345435t43.jpg</t>
+        </is>
+      </c>
+      <c r="I688" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Bantah Dipecat Imbas Selewengkan Uang, Pengacara Indra Wargadalem: Sekolah Justru Punya Utang Rp7 M</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:17:12 +0700</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>Kuasa hukum Indra Wargadalem membantah bahwa kliennya dipecat dari sekolah karena menggelapkan uang. Pihak sekolah justru berutang kepadanya.</t>
+        </is>
+      </c>
+      <c r="F689" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865341/bantah-dipecat-imbas-selewengkan-uang-pengacara-indra-wargadalem-sekolah-justru-punya-utang-rp7-m</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vW0d_IgDKBzXm1gs4Ywv9pSzyic=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Sosok-Indra-Wargadalem.jpg</t>
+        </is>
+      </c>
+      <c r="I689" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>PDIP Tolak Usulan Pilkada Tanpa Wakil Kepala Daerah, Minta Sistem Berpasangan Dipertahankan</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:13:05 +0700</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>Menurut Giri, figur wakil kepala daerah tetap mutlak diperlukan dalam roda pemerintahan.</t>
+        </is>
+      </c>
+      <c r="F690" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865340/pdip-tolak-usulan-pilkada-tanpa-wakil-kepala-daerah-minta-sistem-berpasangan-dipertahankan</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/LZRWwfA97lebPe-PeKLkaZM5gIA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Giri-Ramanda-Kiemas-4321.jpg</t>
+        </is>
+      </c>
+      <c r="I690" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Pihak Sarwendah Bantah Membuka Isu Penyakit Tiga Huruf Ruben Onsu</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:12:03 +0700</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>Konflik yang bermula dari persoalan komunikasi terkait anak antara Ruben dan Sarwendah merembet ke gosip liar yang tak terkendali.</t>
+        </is>
+      </c>
+      <c r="F691" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865339/pihak-sarwendah-bantah-membuka-isu-penyakit-tiga-huruf-ruben-onsu</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/17MeeNABlB64uNZ5bi9H-74-Xeg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/SIDANG-SARWENDAH-RUBEN-onsu.jpg</t>
+        </is>
+      </c>
+      <c r="I691" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Adam Alis Bangga Meski Persib Gagal Juara Piala Presiden 2026, Fokus Tatap ACL 2 dan Super League</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:08:45 +0700</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Adam Alis tetap bangga meski Persib gagal juara Piala Presiden 2026. Kini Maung Bandung mengalihkan fokus untuk menghadapi ACL 2 dan Super League.</t>
+        </is>
+      </c>
+      <c r="F692" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7865338/adam-alis-bangga-meski-persib-gagal-juara-piala-presiden-2026-fokus-tatap-acl-2-dan-super-league</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/lWO-q-Yki1SPFUulomJwYpI8JFs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Gelandang-Persib-Bandung-Adam-Alis-merayakan-gol-saat-melawan-Persib-Bandung-di-Super-League.jpg</t>
+        </is>
+      </c>
+      <c r="I692" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Klasemen SEA V Cup 2026 Leg 2: Timnas Voli Putri Indonesia di Puncak, Thailand Jadi Musuh Utama</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:07:27 +0700</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>Timnas Voli Putri Indonesia sementara puncaki klasemen Leg 2 SEA V Cup 2026 seusai kalahkan Vietnam 3-2 di Chiang Mai, Thailand.</t>
+        </is>
+      </c>
+      <c r="F693" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7865337/klasemen-sea-v-cup-2026-leg-2-timnas-voli-putri-indonesia-di-puncak-thailand-jadi-musuh-utama</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ji5jh_awPmeoo7bKdWFIChFnymU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Pemain-Timnas-Voli-Putri-Indonesia-melakukan-perayaan-setelah-mencetak-poin-saat.jpg</t>
+        </is>
+      </c>
+      <c r="I693" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Dobrak Stagnasi 5 Persen, PKS Dorong Ekonomi Syariah Jadi Mesin Baru Pertumbuhan Nasional</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:06:50 +0700</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>PKS menilai potensi ekonomi syariah di Indonesia masih tersimpan besar dan belum digarap secara maksimal.</t>
+        </is>
+      </c>
+      <c r="F694" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865336/dobrak-stagnasi-5-persen-pks-dorong-ekonomi-syariah-jadi-mesin-baru-pertumbuhan-nasional</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/96vE_LtiB38ke-lAe2zizXgQIwc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Presiden-PKS-Almuzzammil-Yusuf-saat-membuka-diskusi.jpg</t>
+        </is>
+      </c>
+      <c r="I694" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Mabes Polri dan Polda Aceh Saling Lempar Ditanya soal Pemeriksaan Kapolresta Banda Aceh oleh Propam</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:05:59 +0700</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>Mabes Polri dan Polda Aceh saling lempar dalam memberikan keterangan terkait pemeriksaan Kapolresta Banda Aceh beserta Kasat Reserse Narkoba.</t>
+        </is>
+      </c>
+      <c r="F695" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865335/mabes-polri-polda-aceh-saling-lempar-ditanya-soal-pemeriksaan-kapolresta-banda-aceh-oleh-propam</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Z4tnr6hxQmy4OB4eYA1X0XB29uE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Irjen-Pol-Johnny-Eddizon-Isir-Kepala-Divisi-Humas-Polri-jumpa-pers-di-Mabes-Polri-Jakarta.jpg</t>
+        </is>
+      </c>
+      <c r="I695" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Zelenskyy Desak AS untuk Beri Bantuan Militer Tambahan, Trump Balas Dingin: Kami juga Butuh Rudal</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:05:40 +0700</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>Presiden Amerika Serikat (AS) Donald Trump menanggapi dingin permintaan Presiden Ukraina, Volodymyr Zelenskyy yang meminta bantuan militer tambahan.</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7865334/zelenskyy-desak-as-untuk-beri-bantuan-militer-tambahan-trump-balas-dingin-kami-juga-butuh-rudal</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/F9Vku9YqBsRvreE70DK_jTb1Z54=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ukraina-Volodymyr-Zelenskyy-Presiden-AS-Donald-Trump-berpartisipasi.jpg</t>
+        </is>
+      </c>
+      <c r="I696" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>Polisi Periksa YouTuber Bigmo Terkait Dugaan Eksploitasi Anak Senin Depan</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:05:10 +0700</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Polisi menjadwalkan pemeriksaan Bigmo setelah mengantongi bukti digital dan memeriksa empat anak dalam kasus promosi vape.</t>
+        </is>
+      </c>
+      <c r="F697" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865333/polisi-periksa-youtuber-bigmo-terkait-dugaan-eksploitasi-anak-senin-depan</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/X2Ez5cydYJLGk6ZfG2_CP0wJ8wM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Kabid-Humas-Polda-Metro-Jaya-Kombes-Pol-Budi-Hermanto-soal-pemeriksaan-Bigmo.jpg</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Terpergok Selingkuh Pakai Mobil Dinas, Sekda Konawe Selatan jadi Tersangka Penganiayaan</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:04:42 +0700</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Sekda Konawe Selatan berinisial IP (56) ditetapkan sebagai tersangka usai melindas adiknya demi melarikan diri saat tertangkap basah selingkuh.</t>
+        </is>
+      </c>
+      <c r="F698" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865332/terpergok-selingkuh-pakai-mobil-dinas-sekda-konawe-selatan-jadi-tersangka-penganiayaan</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/W2tWwMEfjia1nN8oHx3iWzxqNRA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Sekda-Konawe-Selatan-Ichsan-Porosi_3.jpg</t>
+        </is>
+      </c>
+      <c r="I698" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Rupiah Kembali Menguat di Akhir Pekan, Cadangan Devisa Jadi Pendorong</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:03:31 +0700</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Rupiah sore ini ditutup menguat 25 point sebelumnya sempat melemah 20 point di level Rp 17.897 dari penutupan sebelumnya di level Rp 17.923.</t>
+        </is>
+      </c>
+      <c r="F699" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7865331/rupiah-kembali-menguat-di-akhir-pekan-cadangan-devisa-jadi-pendorong</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/jgK8bURB73bgjHQYkMP7V4xVAm8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Penukaran-Uang-Rupiah-di-Bank-Muamalat_20260312_142254.jpg</t>
+        </is>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>Energi</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Bahlil: Transformasi Ekonomi Indonesia tak akan Terjadi Tanpa Hilirisasi</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:37:08 +0700</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menegaskan transformasi ekonomi Indonesia tidak akan pernah terwujud tanpa kebijakan hilirisasi sumber daya alam. Menurut dia, Indonesia harus...</t>
+        </is>
+      </c>
+      <c r="F700" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tje81w423/bahlil-transformasi-ekonomi-indonesia-tak-akan-terjadi-tanpa-hilirisasi</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260108151559-263.png</t>
+        </is>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Adidaya Institute Dorong Pembenahan Tata Kelola MBG di Era Sudaryono</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Adidaya Institute mendorong pembenahan tata kelola Program Makan Bergizi Gratis (MBG) pada masa kepemimpinan Sudaryono di Badan Gizi Nasional (BGN). Lembaga tersebut menilai pergantian kepemimpinan menjadi momentum...</t>
+        </is>
+      </c>
+      <c r="F701" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tje5ne416/adidaya-institute-dorong-pembenahan-tata-kelola-mbg-di-era-sudaryono</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/096462300-1785818101-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>Pertanian</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>Kementan dan Pemerintah Aceh Percepat Pemulihan Sektor Pertanian Pascabencana</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:51:30 +0700</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Ferry kisihandi</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Kepala Biro Komunikasi dan Layanan Informasi Kementerian Pertanian (Kementan), Moch Arief Cahyono, menyambut baik penjelasan juru bicara Pemerintah Aceh, Nurlis Effendi mengenai mekanisme dukungan Kementan untuk...</t>
+        </is>
+      </c>
+      <c r="F702" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tje5xu472/kementan-dan-pemerintah-aceh-percepat-pemulihan-sektor-pertanian-pascabencana</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/kementan-berkomitmen-untuk-terus-bersinergi-dengan-pemerintah-aceh-dan_260807155005-162.jpeg</t>
+        </is>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>PTPN Ubah Strategi Bisnis Karet, tak Lagi Kejar Volume Produksi</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:22:07 +0700</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Perubahan lanskap industri karet global mendorong pelaku usaha mengubah strategi bisnis untuk menjaga daya saing. Selain meningkatkan produktivitas, perusahaan mulai mengedepankan pengelolaan aset biologis yang berkelanjutan, pengambilan...</t>
+        </is>
+      </c>
+      <c r="F703" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tje4kv416/ptpn-ubah-strategi-bisnis-karet-tak-lagi-kejar-volume-produksi</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/pt-perkebunan-nusantara-iv-anak-perusahaan-holding-perkebunan-nusantara_240710091042-114.jpeg</t>
+        </is>
+      </c>
+      <c r="I703" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Polisi Telusuri Temuan Dokumen Impor Senjata Tahun 2008 di Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:42:07 +0700</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Dokumen impor tersebut ditemukan bersama 996 senjata ragam jenis.</t>
+        </is>
+      </c>
+      <c r="F704" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264456/polisi-telusuri-temuan-dokumen-impor-senjata-tahun-2008-di-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/CtM5XDTHJfKJmDzpcb6YMTVMeWI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317273/original/093250400_1786008225-1001014569.jpg</t>
+        </is>
+      </c>
+      <c r="I704" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Pengelolaan Sampah dari Sumber Diperkuat di Kepulauan Seribu</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Pengelolaan Sampah dari Sumber didorong di Kepulauan Seribu melalui pemilahan dan pengolahan sampah sejak awal untuk menjaga kebersihan pulau.</t>
+        </is>
+      </c>
+      <c r="F705" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264280/pengelolaan-sampah-dari-sumber-diperkuat-di-kepulauan-seribu</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/1MzRQxAgwaSOgaB0GWI7goknfM0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9297664/original/086562900_1784102286-ChatGPT_Image_15_Jul_2026__14.51.08.jpg</t>
+        </is>
+      </c>
+      <c r="I705" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Wisuda IMDE ke-XIX, Lulusan Diingatkan Tak Berhenti Belajar di Era AI</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:46:08 +0700</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>Wisudawan IMDE diingatkan membekali diri dengan karakter, kreativitas, kemampuan adaptasi, dan kesiapan menghadapi perubahan teknologi.</t>
+        </is>
+      </c>
+      <c r="F706" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264462/wisuda-imde-ke-xix-lulusan-diingatkan-tak-berhenti-belajar-di-era-ai</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/J6pu6XSyODsM8kelUtCuF_4P-7E=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318431/original/080523300_1786095949-WhatsApp_Image_2026-08-07_at_14.47.46.jpeg</t>
+        </is>
+      </c>
+      <c r="I706" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>Harmoni Energi Terbarukan dan Dampak Sosial Berkelanjutan di Lereng Dieng</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:35:31 +0700</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>PLTA Garung tak hanya memasok listrik, tetapi juga memberdayakan warga Wonosobo.</t>
+        </is>
+      </c>
+      <c r="F707" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264450/harmoni-energi-terbarukan-dan-dampak-sosial-berkelanjutan-di-lereng-dieng</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/abnn_1XKbWUQ4jgt2sDvIVkkjp4=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318414/original/080502700_1786095317-WhatsApp_Image_2026-08-06_at_4.50.30_PM.jpeg</t>
+        </is>
+      </c>
+      <c r="I707" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>Sopir M44 Demo, Dishub DKI Buka Opsi Penataan Rute</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:00:55 +0700</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>Dishub DKI akan membahas penataan rute Mikrotrans 48 setelah sopir M44 mengeluhkan adanya tumpang tindih trayek yang berdampak pada pendapatan mereka.</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264400/sopir-m44-demo-dishub-dki-buka-opsi-penataan-rute</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/0DjyWv8HMo7744NWCOverkkIa90=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318356/original/020909000_1786093175-IMG_3361.jpg</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>Rincian 996 Senjata Temuan di Sekolah Jaksel, Ada Senpi</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:53:25 +0700</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>Seluruhnya diamankan di gudang Subdit Wasendak Direktorat Intelkam Polda Metro Jaya.</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264392/rincian-996-senjata-temuan-di-sekolah-jaksel-ada-senpi</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/-eUS8GJMRLt2IW4qc-LAL6kQZjI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318350/original/039310200_1786092787-IMG_2896.jpg</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Pemilik Senjata Api di Sekolah Jaksel Sudah Meninggal Sejak 2020</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:30:16 +0700</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>Pemilik Senjata Api di Gudang Yayasan Ternyata Sudah Meninggal Sejak 2020</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264355/pemilik-senjata-api-di-sekolah-jaksel-sudah-meninggal-sejak-2020</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/O7xkstsu9c4li17XKW9ryOnHB60=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318320/original/097951300_1786091410-1001016132.jpg</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Polisi Ungkap Fakta Berbeda soal Asal Usul 995 Senjata di Sekolah Jaksel</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:15:16 +0700</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>Kubu mantan ketua yayasan menyebut airsoft gun bekas kegiatan ekskul sekolah di tahun 2020.</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264326/polisi-ungkap-fakta-berbeda-soal-asal-usul-995-senjata-di-sekolah-jaksel</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/u15x1w9N_6-9iVpP-LBJokwIdVo=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9317533/original/004362800_1786019652-WhatsApp_Image_2026-08-06_at_19.28.11.jpeg</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Penampakan Eks Jampidsus Febrie Jalani Pemeriksaan di Kejagung</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:10:11 +0700</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>Mantan Jampidsus Febrie Adriansyah kembali diperiksa Tim 9 Kejagung sebagai tersangka dalam kasus dugaan TPPU.</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264325/penampakan-eks-jampidsus-febrie-jalani-pemeriksaan-di-kejagung</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/ppK6odVd8ibr_wjmN8mAvC60TU8=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318263/original/022204500_1786090210-54a2666a-b300-4f62-9003-288cc548be72.jpg</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Istana Buka Suara soal Reshuffle, Dua Jabatan Ini Jadi Prioritas</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:10:01 +0700</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara Prasetyo Hadi mengatakan isu reshuffle memang kerap mencuat.</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264319/istana-buka-suara-soal-reshuffle-dua-jabatan-ini-jadi-prioritas</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/a_OlaD9VdfFL0AWqKLYT8v9Rcfc=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/4993028/original/025379800_1730884437-IMG-20241106-WA0032.jpg</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>Bola</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Hasil SEA V Cup 2026: Timnas Voli Putri Indonesia Tekuk Vietnam Usai Comeback Dramatis</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:53:51 +0700</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>Timnas voli putri Indonesia berhasil menundukkan Vietnam secara dramatis di laga leg 2 SEA V Cup 2026.</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/sports/read/2026/08/07/16533908/hasil-sea-v-cup-2026-timnas-voli-putri-indonesia-tekuk-vietnam-usai</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/QxAAVKHSPlPj5yuJde35vjKLcfg=/31x78:1540x1085/1200x675/filters:watermark(data/photo/2026/01/30/697c8163c3944.png,0,-0,1)/data/photo/2026/06/14/6a2e689970b36.jpeg</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>Hype</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Tak Berniat Ganti Lagi, Cerita Sule Bayar Rp 4 Juta untuk Daftarkan Nama Prikitiew Land</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:53:51 +0700</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>Sule ungkap proses ganti nama tempat wisata miliknya, dari Taman Anggur menjadi Prikitiew Land</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>https://entertainment.kompas.com/read/2026/08/07/163514666/tak-berniat-ganti-lagi-cerita-sule-bayar-rp-4-juta-untuk-daftarkan</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/RC3HS1wckqZDz9XbKMmLPqLuylM=/67x0:731x443/1200x675/filters:watermark(data/photo/2026/01/30/697c81706c5a3.png,0,-0,1)/data/photo/2026/02/18/69955a977eeff.png</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>Bola</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Kelebihan Yan Diomande, Winger Pantai Gading yang Baru Ditebus Real Madrid</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:53:51 +0700</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>Yan Diomande punya sejumlah kelebihan yang bisa berdampak untuk permainan Real Madrid asuhan Jose Mourinho musim depan.</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>https://bola.kompas.com/read/2026/08/07/16235698/kelebihan-yan-diomande-winger-pantai-gading-yang-baru-ditebus-real-madrid</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/_-jO8AmEr30BwtHAy60nl2vU7lM=/0x0:1200x800/1200x675/filters:watermark(data/photo/2026/01/30/697c8163c3944.png,0,-0,1)/data/photo/2026/06/15/6a2f859ce0b7b.jpg</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I542"/>
+  <autoFilter ref="A1:I716"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-07.xlsx
+++ b/data/berita_2026-08-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$716</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$832</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I716"/>
+  <dimension ref="A1:I832"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -34085,8 +34085,5460 @@
         </is>
       </c>
     </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>DJ Resty Novita Siap Dobrak Panggung Miss Grand Indonesia 2026 Wakili NTB</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:19:02 +0700</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>Resty Novita, DJ profesional, melangkah ke Miss Grand Indonesia 2026. Ia buktikan bahwa latar belakang tak batasi perempuan untuk bersinar dan berkontribusi.</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608843/dj-resty-novita-siap-dobrak-panggung-miss-grand-indonesia-2026-wakili-ntb</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/resty-novita-1786097526270_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Doktif Sebut Rilis BPOM Jadi Bukti Kuat Pelanggaran Richard Lee</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:12:02 +0700</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>Muhammad Ahsan Nurrijal</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr">
+        <is>
+          <t>Sidang kasus dokter Richard Lee berlanjut di Tangerang. Saksi Dokter Samira menegaskan pelaporan berdasarkan temuan BPOM terkait praktik penipuan konsumen.</t>
+        </is>
+      </c>
+      <c r="F718" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G718" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608151/doktif-sebut-rilis-bpom-jadi-bukti-kuat-pelanggaran-richard-lee</t>
+        </is>
+      </c>
+      <c r="H718" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/14/doktif-1784036897055_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I718" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Canda Prabowo ke Bahlil: Dia Bisa Bikin Jokowi Tertawa</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:32:42 +0700</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto memuji Menteri ESDM Bahlil Lahadalia dalam peluncuran buku, menyoroti kemampuannya membuat Jokowi tertawa.</t>
+        </is>
+      </c>
+      <c r="F719" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G719" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807170044-32-1389836/canda-prabowo-ke-bahlil-dia-bisa-bikin-jokowi-tertawa</t>
+        </is>
+      </c>
+      <c r="H719" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/31/pertemuan-presiden-prabowo-dengan-pengusaha-kadin-1785484949393_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I719" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Prabowo Hadiri Peluncuran Buku Bahlil, Pidato soal Kepemimpinan</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:28:29 +0700</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo menekankan bahwa pemimpin harus memiliki keberanian, kebajikan, dan empati. Kepemimpinan diperoleh melalui kerja keras dan nilai-nilai.</t>
+        </is>
+      </c>
+      <c r="F720" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G720" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807165608-32-1389833/prabowo-hadiri-peluncuran-buku-bahlil-pidato-soal-kepemimpinan</t>
+        </is>
+      </c>
+      <c r="H720" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/presiden-undang-150-periset-dan-peneliti-brin-ke-istana-1786016567897_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I720" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Insiden Jalan Raya, Direskrimum Polda Sumbar Diduga Aniaya Pengendara</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:06:23 +0700</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr">
+        <is>
+          <t>Seorang pria diduga Kombes Teddy Fanani, Direskrimum Polda Sumbar, memukuli pengendara di jalan menuju bandara. Kasus ini sedang diselidiki Polda Sumbar.</t>
+        </is>
+      </c>
+      <c r="F721" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G721" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807165331-12-1389830/insiden-jalan-raya-direskrimum-polda-sumbar-diduga-aniaya-pengendara</t>
+        </is>
+      </c>
+      <c r="H721" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/oknum-direskrimum-polda-sumbar-pukuli-dan-aniaya-pengendara-1786095989361_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I721" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Konglomerat China Panik Imbas Kebijakan Xi Jinping, Ini Pemicunya</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:33:11 +0700</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr">
+        <is>
+          <t>Konglomerat China panik setelah pemerintah Negeri Tirai Bambu mendadak memberlakukan pajak 20 persen atas perwalian luar negeri (offshore trust).</t>
+        </is>
+      </c>
+      <c r="F722" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G722" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807140904-92-1389721/konglomerat-china-panik-imbas-kebijakan-xi-jinping-ini-pemicunya</t>
+        </is>
+      </c>
+      <c r="H722" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/03/09/bendera-vietnam_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I722" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Dana Asing Masuk ke Pinjol RI Tembus Rp17,28 T per Juni 2026</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:18:24 +0700</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr">
+        <is>
+          <t>OJK mencatat pendanaan asing ke industri pinjol RI mencapai Rp17,28 triliun per Juni 2026, naik 34 persen dibandingkan periode yang sama tahun lalu (yoy).</t>
+        </is>
+      </c>
+      <c r="F723" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G723" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807165819-78-1389834/dana-asing-masuk-ke-pinjol-ri-tembus-rp1728-t-per-juni-2026</t>
+        </is>
+      </c>
+      <c r="H723" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2022/11/01/ilustrasi-mata-uang-rupiah-5_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I723" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>ParagonCorp Perluas Riset Kecantikan dengan Pendekatan Multi-Omics</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:16:00 +0700</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr">
+        <is>
+          <t>ParagonCorp bekerja sama dengan Corpora Science dalam pengembangan pendekatan multi-omics untuk riset kecantikan berbasis sains di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F724" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G724" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807165216-625-1389829/paragoncorp-perluas-riset-kecantikan-dengan-pendekatan-multi-omics</t>
+        </is>
+      </c>
+      <c r="H724" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/paragoncorp-1786095555388_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I724" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Istana Sebut Nama Destry Damayanti Masuk Bursa Calon Gubernur BI</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:54:16 +0700</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>Mensesneg Prasetyo Hadi menyebut nama Destry Damayanti masuk dalam bursa calon gubernur Bank Indonesia (BI). Saat ini Desty menjabat Pjs Gubernur BI.</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G725" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807164827-532-1389828/istana-sebut-nama-destry-damayanti-masuk-bursa-calon-gubernur-bi</t>
+        </is>
+      </c>
+      <c r="H725" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/27/rapat-pelibatan-danantara-dalam-kssk-1785158540398_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I725" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Kementan-Pemda Percepat Pemulihan Sektor Pertanian Pascabencana Aceh</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:50:07 +0700</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr">
+        <is>
+          <t>Kementan menyatakan akan terus bersinergi dengan Pemerintah Aceh, agar percepatan pemulihan pascabencana benar-benar dirasakan manfaatnya oleh petani Aceh.</t>
+        </is>
+      </c>
+      <c r="F726" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G726" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807163927-97-1389817/kementan-pemda-percepat-pemulihan-sektor-pertanian-pascabencana-aceh</t>
+        </is>
+      </c>
+      <c r="H726" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/kementan-1786095647587_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I726" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>IHSG Berotot ke 6.409 Akhiri Pekan Ini, 355 Saham Hijau</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:38:23 +0700</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr">
+        <is>
+          <t>IHSG ditutup di level 6.409 pada perdagangan Jumat (7/8) sore usai menguat 65,94 poin atau naik 1,04 persen dari perdagangan sebelumnya.</t>
+        </is>
+      </c>
+      <c r="F727" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G727" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807163538-92-1389815/ihsg-berotot-ke-6409-akhiri-pekan-ini-355-saham-hijau</t>
+        </is>
+      </c>
+      <c r="H727" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2020/05/11/132ca13c-ddd3-46ee-8bdd-0853886d9e66_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I727" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Rupiah Ditutup Bangkit ke Rp17.896 per Dolar AS Sore Ini</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:53:22 +0700</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah ditutup di level Rp17.896 per dolar AS pada perdagangan Jumat (7/8), menguat 26 poin atau 0,15 persen dibandingkan penutupan sebelumnya.</t>
+        </is>
+      </c>
+      <c r="F728" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G728" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807152847-78-1389793/rupiah-ditutup-bangkit-ke-rp17896-per-dolar-as-sore-ini</t>
+        </is>
+      </c>
+      <c r="H728" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/01/20/rupiah-melemah-dolar-as-sentuh-rp16965-1768896982720_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I728" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Istana Akui Masih Godok Beberapa Nama Calon Gubernur Baru BI</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:03:58 +0700</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara (Mensesneg) RI Prasetyo Hadi mengakui ada sejumlah nama yang masuk bursa gubernur Bank Indonesia usai mundurnya Perry Warjiyo.</t>
+        </is>
+      </c>
+      <c r="F729" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G729" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807145255-85-1389764/istana-akui-masih-godok-beberapa-nama-calon-gubernur-baru-bi</t>
+        </is>
+      </c>
+      <c r="H729" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/21/mensesneg-prasetyo-hadi-1784621820806_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I729" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>MIND ID Setor Dividen Rp12,6 T ke Negara Sepanjang 2025</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:31:10 +0700</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr">
+        <is>
+          <t>Holding Industri Pertambangan atau MIND ID menyetorkan dividen sebesar Rp12,6 triliun kepada negara sepanjang 2025.</t>
+        </is>
+      </c>
+      <c r="F730" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G730" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807133343-85-1389700/mind-id-setor-dividen-rp126-t-ke-negara-sepanjang-2025</t>
+        </is>
+      </c>
+      <c r="H730" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/11/26/mind-id_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I730" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>BGN Ungkap Dugaan Penyebab Ratusan Siswa Keracunan MBG di Jayapura</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:55:58 +0700</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr">
+        <is>
+          <t>BGN mengungkap dugaan awal penyebab ratusan siswa keracunan usai menyantap menu Makan Bergizi Gratis (MBG) di Distrik Depapre, Jayapura, Papua.</t>
+        </is>
+      </c>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807131813-92-1389690/bgn-ungkap-dugaan-penyebab-ratusan-siswa-keracunan-mbg-di-jayapura</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/10/16/426-siswa-sman-1-yogya-alami-sakit-perut-diare-diduga-keracunan-mbg-1760595677670_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I731" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Telkom Pangkas 34 Entitas Usaha Demi Percepat Transformasi</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:32:09 +0700</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr">
+        <is>
+          <t>Saat ini Telkom Indonesia mengelola 67 entitas yang terdiri atas 58 anak perusahaan dan 9 investasi minoritas.</t>
+        </is>
+      </c>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807122116-92-1389669/telkom-pangkas-34-entitas-usaha-demi-percepat-transformasi</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/03/05/ab8d8228-c8af-406a-b694-b580827ccf9f_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I732" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>Survei BI: Harga Properti Residensial Naik Tipis Kuartal II 2026</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:30:31 +0700</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr">
+        <is>
+          <t>Bank Indonesia (BI) mencatat harga properti residensial di pasar primer masih mencatat kenaikan terbatas pada kuartal II 2026.</t>
+        </is>
+      </c>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807120831-92-1389667/survei-bi-harga-properti-residensial-naik-tipis-kuartal-ii-2026</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/09/17/pemerintah-siapkan-plafon-kur-perumahan-rp130-t-tahun-ini-1758088926193_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I733" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Menhub Beber Rute yang Bakal Dilayani KA Nusantara Explorer</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:59:07 +0700</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr">
+        <is>
+          <t>Menhub Dudy Purwagandhi membeberkan sejumlah rute yang akan dilayani Kereta Api (KA) Nusantara Explorer.</t>
+        </is>
+      </c>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807114608-92-1389654/menhub-beber-rute-yang-bakal-dilayani-ka-nusantara-explorer</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/04/10/menhub-ungkap-usaha-patungan-garudasaudia-bisa-tekan-biaya-penerbangan-haji-1775776373835_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I734" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Malaysia Airlines Wajibkan 1.260 Pilot Tes Narkoba Buntut Kasus di RI</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:35:35 +0700</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>Malaysia Aviation Group memberlakukan tes narkoba wajib bagi seluruh pilot usai pilot mereka ditangkap di RI karena menyelundupkan narkoba.</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807171102-106-1389841/malaysia-airlines-wajibkan-1260-pilot-tes-narkoba-buntut-kasus-di-ri</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/31/pilot-maskapai-asing-ditangkap-di-bandara-soetta-usai-kedapatan-bawa-sabu-dan-ekstasi-25-kg-1785461146712_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I735" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Aktivis Sayap Kiri Israel Serbu Kantor Partai Peneror Warga Palestina</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:05:58 +0700</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr">
+        <is>
+          <t>Sejumlah aktivis sayap kiri Israel, mendemo dan menggeruduk kantor Partai Zionisme Religius sayap kanan di Shoham, sebelah timur Tel Aviv, Rabu (5/8).</t>
+        </is>
+      </c>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807164551-120-1389827/aktivis-sayap-kiri-israel-serbu-kantor-partai-peneror-warga-palestina</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/09/30/warga-israel-demo-kedubes-as-di-tel-aviv-1759169250014_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I736" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Aviasi Malaysia Beber Pilot Cuti 2 Hari saat Bawa Narkoba ke RI</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:35:35 +0700</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>Malaysia Aviation Group menyatakan pilot Malaysia Airlines yang ditangkap di Bandara Soekarno-Hatta, RI, karena menyelundupkan narkoba tidak sedang bertugas.</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807161344-106-1389805/aviasi-malaysia-beber-pilot-cuti-2-hari-saat-bawa-narkoba-ke-ri</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/03/detik-detik-pilot-maskapai-malaysia-ditangkap-bawa-sabu-1785750021111_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I737" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Pelaku Diduga Bunuh Kakek-Nenek Sebelum Menembak di Sekolah Thailand</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:02:36 +0700</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr">
+        <is>
+          <t>Pelaku penembakan di sekolah elite Debsirin, Thailand, diduga membunuh kakek dan neneknya di rumah sebelum melancarkan penembakan pada Jumat (7/8).</t>
+        </is>
+      </c>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807155319-106-1389799/pelaku-diduga-bunuh-kakek-nenek-sebelum-menembak-di-sekolah-thailand</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/penembakan-sekolah-di-thailand-1786075452918_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I738" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Detik-detik Horor Murid Sekolah Thailand Sembunyi saat Penembakan</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:32:14 +0700</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr">
+        <is>
+          <t>Rekaman memperlihatkan momen para siswa berlindung di dalam ruang kelas saat penembakan massal terjadi di sekolah Debsirin Nonthaburi, Thailand, Jumat (7/8).</t>
+        </is>
+      </c>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807150934-110-1389778/detik-detik-horor-murid-sekolah-thailand-sembunyi-saat-penembakan</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/thumbnail-video-1786090246627_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I739" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Iran Ancam Bikin Negara-negara Teluk Gelap Gulita</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:21:05 +0700</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr">
+        <is>
+          <t>Iran mengancam akan membuat negara-negara Teluk gelap gulita jika Amerika Serikat atau Israel menyerang pembangkit listrik Teheran.</t>
+        </is>
+      </c>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807145816-120-1389773/iran-ancam-bikin-negara-negara-teluk-gelap-gulita</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/15/iran-luncurkan-drone-ke-pangkalan-jet-tempur-f-18-as-di-azraq-yordania-1784084253646_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I740" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Korban Tewas Penembakan di Sekolah Thailand: 3 Murid dan 3 Guru</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:49:21 +0700</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>Sebanyak tujuh orang tewas akibat insiden penembakan di salah satu sekolah elite Debsirin, Distrik Bang Kruai, Provinsi Nonthaburi, pada Jumat (7/8).</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807144419-106-1389759/korban-tewas-penembakan-di-sekolah-thailand-3-murid-3-guru</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/penembakan-sekolah-di-thailand-1786075379384_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I741" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Kronologi Penembakan di Sekolah Thailand, 7 Tewas dan Pelaku Bunuh Diri</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:09:27 +0700</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr">
+        <is>
+          <t>Berikut kronologi penembakan di sebuah sekolah di Provinsi Nonthaburi, Thailand, pada Jumat (7/8) yang menewaskan tujuh orang.</t>
+        </is>
+      </c>
+      <c r="F742" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807135550-106-1389715/kronologi-penembakan-di-sekolah-thailand-7-tewas-pelaku-bunuh-diri</t>
+        </is>
+      </c>
+      <c r="H742" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/penembakan-sekolah-di-thailand-1786075452831_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I742" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Pelaku Penembakan Sekolah Thailand Merupakan Remaja, Tewas Bunuh Diri</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:36:22 +0700</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr">
+        <is>
+          <t>Pelaku penembakan di sekolah Distrik Bang Kruai, Provinsi Nonthaburi, Thailand, merupakan seorang remaja.</t>
+        </is>
+      </c>
+      <c r="F743" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G743" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807133130-106-1389699/pelaku-penembakan-sekolah-thailand-merupakan-remaja-tewas-bunuh-diri</t>
+        </is>
+      </c>
+      <c r="H743" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/penembakan-sekolah-di-thailand-1786076745948_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I743" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Aksi Boikot-Bentrokan Warnai Pemilu di Kashmir yang Dikelola Pakistan</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:30:57 +0700</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr">
+        <is>
+          <t>Pemilu Majelis Legislatif 2026 di Jammu dan Kashmir yang dikelola Pakistan (PoJK) diwarnai aksi boikot hingga tuduhan kecurangan.</t>
+        </is>
+      </c>
+      <c r="F744" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G744" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807115816-113-1389663/aksi-boikot-bentrokan-warnai-pemilu-di-kashmir-yang-dikelola-pakistan</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/04/11/f2c94c55-b4f0-4d8d-80aa-551e82eca5c0_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I744" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Bom Meledak di Dalam Minibus di Suriah, 2 Tewas Belasan Luka</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:55:09 +0700</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr">
+        <is>
+          <t>Sebuah bom yang dipasang di dalam minibus meledak dan menewaskan dua orang di pinggiran ibu kota Damaskus, Suriah pada Kamis (7/8) malam.</t>
+        </is>
+      </c>
+      <c r="F745" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G745" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807113449-120-1389648/bom-meledak-di-dalam-minibus-di-suriah-2-tewas-belasan-luka</t>
+        </is>
+      </c>
+      <c r="H745" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2022/12/07/ilustrasi-bom-atau-ledakan_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I745" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>FOTO: Penembakan Sekolah di Thailand, Korban Jiwa Berjatuhan</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:20:15 +0700</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr">
+        <is>
+          <t>Penembakan sekolah di Thailand, seorang guru tewas dan empat orang lainnya terluka.</t>
+        </is>
+      </c>
+      <c r="F746" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G746" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807110454-108-1389630/foto-penembakan-sekolah-di-thailand-korban-jiwa-berjatuhan</t>
+        </is>
+      </c>
+      <c r="H746" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/penembakan-sekolah-di-thailand-1786075452831_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I746" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Penembakan di Sekolah Thailand, 2 Tewas dan 15 Luka Diyakini Siswa</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:42:23 +0700</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>Sebanyak 2 orang dilaporkan tewas dan 15 orang lainnya terluka dalam penembakan di sebuah sekolah di provinsi di utara ibu kota Thailand, Bangkok.</t>
+        </is>
+      </c>
+      <c r="F747" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807113233-106-1389651/penembakan-di-sekolah-thailand-2-tewas-15-luka-diyakini-siswa</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/penembakan-sekolah-di-thailand-1786075452918_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>Ibu Tak Perlu Hentikan ASI Saat Mastitis, Dokter Ungkap Manfaat Direct Breastfeeding untuk Pemulihan</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:30:04 +0700</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>Banyak ibu menyusui memilih menghentikan pemberian ASI ketika mengalami mastitis karena khawatir membuat bayi ikut sakit. Anggapan itu keliru.</t>
+        </is>
+      </c>
+      <c r="F748" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865388/ibu-tak-perlu-hentikan-asi-saat-mastitis-dokter-ungkap-manfaat-direct-breastfeeding-untuk-pemulihan</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/hZXoQ3Hju0FQ_VmyG1eAYKWT4UY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-ibu-menyusui-pake-baju-putih.jpg</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Ketua MPR: Pemikiran Bung Hatta soal Ekonomi dan Pemerintahan Masih Relevan</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:27:37 +0700</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>Muzani menilai Bung Karno dan Bung Hatta merupakan dua tokoh yang sejak awal menginspirasi perjuangan rakyat Indonesia.</t>
+        </is>
+      </c>
+      <c r="F749" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865387/ketua-mpr-pemikiran-bung-hatta-soal-ekonomi-dan-pemerintahan-masih-relevan</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/SFKEedJk53fHviX2wwYJD8IVS-g=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ziearah-ke-makam-Bung-hatta-07082026.jpg</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Awal Mula Polemik Gerbang SD di Bandung Digembok Ahli Waris, Farhan Minta Diberi Waktu Relokasi</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:26:29 +0700</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>Sengketa lahan memicu penggembokan gerbang SDN 026 Bojongloa Bandung hingga siswa terpaksa pulang, sementara Pemkot masih mengupayakan lahan pengganti</t>
+        </is>
+      </c>
+      <c r="F750" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865386/awal-mula-polemik-gerbang-sd-di-bandung-digembok-ahli-waris-farhan-minta-diberi-waktu-relokasi</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/l1P32TLy3X8cEM76a_dW_v3Vqg4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/SD-Negeri-026-Bojongloa-disegel-asdf.jpg</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Bahlil Curhat Awal Mula Larangan Ekspor Nikel, Akui Sempat Bingung Saat Diperintah Jokowi</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:26:17 +0700</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia mengungkap cerita di balik kebijakan larangan ekspor bijih nikel oleh Pemerintah.</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7865385/bahlil-curhat-awal-mula-larangan-ekspor-nikel-akui-sempat-bingung-saat-diperintah-jokowi</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/qb1ldK2O3ajMm7TWecRFfhW354Q=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Peluncuran-buku-Bahlil-Lahadalia-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Mantan Ketua DPRD Ponorogo Jatim Jadi Tersangka Korupsi Tunjangan Perumahan</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:24:24 +0700</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>Kepala Kejari Ponorogo, Zulmar Adhy Surya, mengonfirmasi peningkatan status SN yang sebelumnya diperiksa sebagai saksi kini resmi menjadi tersangka</t>
+        </is>
+      </c>
+      <c r="F752" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865384/mantan-ketua-dprd-ponorogo-jatim-jadi-tersangka-korupsi-tunjangan-perumahan</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/9iBPkz-OjcF5Wqdlpipaysb1KzM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/DITAHAN-SN-Ketua-DPRD-Ponorogo.jpg</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Banyumas, Sabtu 8 Agustus 2026: Seluruh Kecamatan Berawan</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:22:47 +0700</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>Pada hari Sabtu, 8 Agustus 2026, seluruh daerah Kabupaten Banyumas, Jawa Tengah, diprediksi akan berawan.</t>
+        </is>
+      </c>
+      <c r="F753" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865383/prakiraan-cuaca-banyumas-sabtu-8-agustus-2026-seluruh-kecamatan-berawan</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/wThwclW1QgdbBunn-f09irjnfzA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Potret-Cuaca-Berawan-ya.jpg</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>Kuasa Hukum Indra Wargadalem: Ekskul Menembak di Sekolah Jaksel Baru Rencana, Belum Ada Kegiatan</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:21:56 +0700</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>Kuasa hukum Indra Wargadalem menegaskan ekstrakulikuler menembak di sekolah di Jaksel baru rencana. Sehingga belum ada kegiatan.</t>
+        </is>
+      </c>
+      <c r="F754" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865382/kuasa-hukum-indra-wargadalem-ekskul-menembak-di-sekolah-jaksel-baru-rencana-belum-ada-kegiatan</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Am_oSUTg_ePo_whmlt5KtBDaTf4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Senpi-di-sekolah-12.jpg</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>BREAKING NEWS: Polisi Sebut Pemilik Senjata Api di Sekolah Jaksel Meninggal</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:19:48 +0700</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>Polisi mengungkap pemilik satu-satunya senjata api yang ditemukan di sekolah Jaksel telah meninggal. Dokumen impor kini didalami.</t>
+        </is>
+      </c>
+      <c r="F755" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865381/breaking-news-polisi-sebut-pemilik-senjata-api-di-sekolah-jaksel-meninggal</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/c23bmk4PHY76ZCmOECtNP5j3wK4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ratusan-senjata-api-di-sekolah-swasta-Pondok-Pinang-Kebayoran-Lama-Jakarta-Selatan.jpg</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban IPS Kelas 7 Halaman 42 Kurikulum Merdeka Edisi Revisi: Aktivitas 8</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:19:46 +0700</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>Berikut ini kunci jawaban mata pelajaran IPS Kelas 7 Halaman 42 Kurikulum Merdeka terdapat tugas Aktivitas 8 pada Tema 1.</t>
+        </is>
+      </c>
+      <c r="F756" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7865380/kunci-jawaban-ips-kelas-7-halaman-42-kurikulum-merdeka-edisi-revisi-aktivitas-8</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Nj0pDBHbMVc2FfzH_Vier8Az45c=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/SISWA-SMP-UJIAN-01.jpg</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Momen Muzani Pimpin Rombongan MPR Ziarah ke Makam Bung Hatta di Tanah Kusir</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:18:35 +0700</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>Pimpinan MPR RI dipimpin Ahmad Muzani melakukan ziarah ke makam Wakil Presiden Pertama RI Mohammad Hatta di Tanah Kusir, jakarta Selatan.</t>
+        </is>
+      </c>
+      <c r="F757" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865379/momen-muzani-pimpin-rombongan-mpr-ziarah-ke-makam-bung-hatta-di-tanah-kusir</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/SFKEedJk53fHviX2wwYJD8IVS-g=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ziearah-ke-makam-Bung-hatta-07082026.jpg</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Komitmen pada Pendidikan Berkualitas, CITA Raih Penghargaan</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:17:53 +0700</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>Program ini diharapkan tidak hanya di wilayah lingkar tambang CITA Site Air Upas, namun bisa diperluas ke wilayah lainnya.</t>
+        </is>
+      </c>
+      <c r="F758" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7865378/komitmen-pada-pendidikan-berkualitas-cita-raih-penghargaan</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/3Zvg-nlQ8A4gOnwo99Lrbg8xD2M=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/PT-Cita-Mineral-Investindo-Tbk-CITA-v2333.jpg</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Tiga Dekade APJII, Dorong Konektivitas Inklusif hingga Wilayah 3T</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:15:31 +0700</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>Internet telah berkembang menjadi infrastruktur strategis yang menentukan daya saing bangsa.</t>
+        </is>
+      </c>
+      <c r="F759" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7865377/tiga-dekade-apjii-dorong-konektivitas-inklusif-hingga-wilayah-3t</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/dbWXaThnVJJR2S3PY4_hWcY-o7o=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Rakernas-APJII-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Doa Mengendalikan Hawa Nafsu agar Tak Terjerumus Dalam Dosa</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:15:04 +0700</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>Allah memberikan nafsu kepada manusia, yaitu dorongan yang bisa menjadi baik/buruk. Muslim dianjurkan untuk menahan hawa nafsu buruk. Berikut doanya.</t>
+        </is>
+      </c>
+      <c r="F760" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/lifestyle/7865376/doa-mengendalikan-hawa-nafsu-agar-tak-terjerumus-dalam-dosa</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/mCB_Mk0hcxA9UCRGc722xnSNqfU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/DOA-MENGENDALIKAN-NAFSU-34532R3R3R.jpg</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>ISESS Soroti Baintelkam Polri, Temuan 995 Senjata di Sekolah Dinilai Bukti Pengawasan Belum Efektif</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:13:30 +0700</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>Temuan 995 senjata di sekolah dinilai membuka celah lemahnya pengawasan Baintelkam. ISESS mendesak legalitas senjata</t>
+        </is>
+      </c>
+      <c r="F761" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865375/isess-soroti-baintelkam-polri-temuan-995-senjata-di-sekolah-dinilai-bukti-pengawasan-belum-efektif</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/C0lT2Y0zI_MxSjs7s2qkRNylM8s=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Benda-berbentuk-senjata-yang-ditemukan-di-sebuah-ruangan-321.jpg</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Kapolda NTT Perkuat Kerja Sama dengan Australia dan Timor Leste, Fokus Awasi Kejahatan Transnasional</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:10:10 +0700</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>Kerja sama diharapkan memperkuat deteksi dini dan respons aparat terhadap kejahatan transnasional.</t>
+        </is>
+      </c>
+      <c r="F762" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865374/kapolda-ntt-perkuat-kerja-sama-dengan-australia-dan-timor-leste-fokus-awasi-kejahatan-transnasional</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/IqvUEcHN9ddUQ452YbSBDw-qWUQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kejahatannnnnn-transnasional.jpg</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Benjamin Sesko Diincar Raksasa Eropa, Manchester United Tegaskan Tidak Dijual!</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:09:21 +0700</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>Benjamin Sesko diincar Bayern Munchen, Barcelona, dan Tottenham. Namun Manchester United menegaskan sang striker tak tersentuh di bursa transfer.</t>
+        </is>
+      </c>
+      <c r="F763" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7865373/benjamin-sesko-diincar-raksasa-eropa-manchester-united-tegaskan-tidak-dijual</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/fIg_jemLA3DBmKAhlZO7Pixl8ZI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Selebrasi-penyerang-Manchester-United-Benjamin-Sesko-saat-lawan-Brentford.jpg</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Shin Tae-yong: Persija Juara Tiga Piala Presiden 2026, Prestasi Oke di Tengah Persiapan yang Kurang</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:08:33 +0700</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>Macan Kemayoran memastikan kemenangan lewat gol yang dicetak Witan Sulaeman, Arlyansyah Abdulmanan, dan Victor Dethan.</t>
+        </is>
+      </c>
+      <c r="F764" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7865372/shin-tae-yong-persija-juara-tiga-piala-presiden-2026-prestasi-oke-di-tengah-persiapan-yang-kurang</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/K8StLKJY9udjTiZomPhbZQLK31M=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/LAKUKAN-SELEBRASI-Pemain-muda-Persija-Arlyansyah-Abdulmanan.jpg</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Definisi Gejala Keputihan yang Normal dan Tidak Normal, Simak Faktor Penyebab dan Cara Mengatasinya</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:07:03 +0700</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>Keputihan sering membuat khawatir karena dianggap sebagai tanda adanya gangguan kesehatan, berikut penjelasan mengenai gejala dan penyebabnya.</t>
+        </is>
+      </c>
+      <c r="F765" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/kesehatan/7865371/definisi-gejala-keputihan-yang-normal-dan-tidak-normal-simak-faktor-penyebab-dan-cara-mengatasinya</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ci1QkFGMUSIztNem_oGbI_2GISE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/warga-ngobrol-dan-main-handphone-menunggu-giliran-cek-kesehatan-gratis.jpg</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Prakiraan Cuaca Kota Surabaya, Kediri, Madiun, Blitar, Sabtu 8 Agustus 2026: Cerah Berawan</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:03:27 +0700</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>Simak prakiraan cuaca di Kota Surabaya, Kediri, Madiun, dan Blitar pada Sabtu (8/8/2026). Seluruh wilayah tersebut diprediksi cerah berawan.</t>
+        </is>
+      </c>
+      <c r="F766" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865370/prakiraan-cuaca-kota-surabaya-kediri-madiun-blitar-sabtu-8-agustus-2026-cerah-berawan</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/XghfMEZWjztiwTR5MRc64jAE4gI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/hujan-deras-guyur-yonif-raider-700wyc454.jpg</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Fakta Baru Temuan 996 Senapan di Sekolah Swasta Jaksel: Sosok DS Pemilik Senpi, tapi Sudah Meninggal</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:01:57 +0700</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya mengungkap fakta baru terkait temuan ratusan senapan di sekolah swasta di Jakarta Selatan.</t>
+        </is>
+      </c>
+      <c r="F767" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7865369/fakta-baru-temuan-996-senapan-di-sekolah-swasta-jaksel-sosok-ds-pemilik-senpi-tapi-sudah-meninggal</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/c23bmk4PHY76ZCmOECtNP5j3wK4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ratusan-senjata-api-di-sekolah-swasta-Pondok-Pinang-Kebayoran-Lama-Jakarta-Selatan.jpg</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Video:Hippindo Gelar IRS 2026, Targetkan Transaksi Capai Rp 25 Triliun</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:40:38 +0700</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>Hippindo Gelar Retail Summit Expo 2026, Targetkan Transaksi Capai Rp 25 Triliun</t>
+        </is>
+      </c>
+      <c r="F768" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260806155333-8-757178/videohippindo-gelar-irs-2026-targetkan-transaksi-capai-rp-25-triliun</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/hippindo-gelar-retail-summit-expo-2026-targetkan-transaksi-capai-rp-25-triliun-1786091368729_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Jepang Siaga! 260.000 Warga Dievakuasi, 500 Penerbangan Batal</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr">
+        <is>
+          <t>Jepang evakuasi 260.000 penduduk saat Topan Dolphin mendekat. Badai kategori 1 ini batalkan 500 penerbangan dan ancam pemulihan pasca-gempa.</t>
+        </is>
+      </c>
+      <c r="F769" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G769" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807154857-4-757472/jepang-siaga-260000-warga-dievakuasi-500-penerbangan-batal</t>
+        </is>
+      </c>
+      <c r="H769" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2018/04/11/477085d3-efda-4893-a507-97ae7d85a42e_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I769" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>IMF Sarankan RI Lepas Kecanduan "Duit Panas", Bikin Ekonomi Rentan</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:35:02 +0700</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr">
+        <is>
+          <t>Dana Moneter Internasional (International Monetary Fund/IMF) mengungkapkan Indonesia masih bergantung dari investasi portofolio</t>
+        </is>
+      </c>
+      <c r="F770" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G770" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807161930-4-757490/imf-sarankan-ri-lepas-kecanduan-duit-panas-bikin-ekonomi-rentan</t>
+        </is>
+      </c>
+      <c r="H770" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/07/29/logo-dana-moneter-internasional-imf-reutersyuri-gripasfile-photo-1753790541518_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I770" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Tetangga RI Hadapi Krisis, Ekonomi Tumbuh Terendah 5 Tahun</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr">
+        <is>
+          <t>Ekonomi Filipina melambat tajam dengan pertumbuhan PDB hanya 2,3% pada kuartal II-2026. Sektor konstruksi tertekan, sementara inflasi mencapai 5%.</t>
+        </is>
+      </c>
+      <c r="F771" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G771" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807145940-4-757457/tetangga-ri-hadapi-krisis-ekonomi-tumbuh-terendah-5-tahun</t>
+        </is>
+      </c>
+      <c r="H771" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/05/12/warga-filipina-memberikan-suara-dalam-pemilihan-paruh-waktu-di-taguig-city-metro-manila-filipina-senin-1252025-reuterslisa-mar-1747030332380_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I771" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Bahlil Luncurkan Buku 10 Karya Nyata untuk Negeri, Ini Isinya</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:22:25 +0700</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr">
+        <is>
+          <t>Menteri ESDM Bahlil Lahadalia resmi meluncurkan buku 10 karya nyata negeri, berikut isi lengkapnya</t>
+        </is>
+      </c>
+      <c r="F772" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G772" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807171614-4-757519/bahlil-luncurkan-buku-10-karya-nyata-untuk-negeri-ini-isinya</t>
+        </is>
+      </c>
+      <c r="H772" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/menteri-esdm-bahlil-lahadalia-ddalam-peluncuran-dan-bedah-buku-10-karya-nyata-untuk-negeri-setengah-abad-bahlil-lahadalia-di-d-1786088945805_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I772" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Mobil Listrik Ini Dijual Rp 119 Juta, Mau Kredit? DP Cuma Segini</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:20:10 +0700</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>Ferry Sandi</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr">
+        <is>
+          <t>Mobil listrik ini hadir di GIIAS 2026 dengan harga Rp119 juta. Mau kredit? DPnya cuma segini.</t>
+        </is>
+      </c>
+      <c r="F773" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G773" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807163110-4-757495/mobil-listrik-ini-dijual-rp-119-juta-mau-kredit-dp-cuma-segini</t>
+        </is>
+      </c>
+      <c r="H773" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/mobil-listrik-mungil-dfsk-seres-s5-menjadi-salah-satu-kendaraan-yang-menarik-perhatian-pengunjung-giias-2026-1786092059687_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I773" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Penampakan Sepatu Karet Lokal BRIN Rp 80 Ribuan yang Dipesan Prabowo</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>Emir Yanwardhana</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto memesan sepatu sekolah berbahan karet lokal dari BRIN seharga di bawah Rp80 ribu. Ini penampakannya.</t>
+        </is>
+      </c>
+      <c r="F774" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G774" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807161950-4-757489/penampakan-sepatu-karet-lokal-brin-rp-80-ribuan-yang-dipesan-prabowo</t>
+        </is>
+      </c>
+      <c r="H774" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/penampakan-sepatu-sekolah-berbahan-karet-lokal-hasil-inovasi-badan-riset-dan-inovasi-nasional-brin-yang-dibanderol-dengan-harg-1786093839277_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I774" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Prabowo Kasih Rapor Kinerja Bahlil : Memuaskan!</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:56:57 +0700</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr">
+        <is>
+          <t>Presiden RI Prabowo Subianto memberikan penilaian kinerja ke Menteri ESDM Bahlil Lahadalia</t>
+        </is>
+      </c>
+      <c r="F775" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G775" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807165317-4-757509/prabowo-kasih-rapor-kinerja-bahlil-memuaskan</t>
+        </is>
+      </c>
+      <c r="H775" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/presiden-prabowo-subianto-menandatangani-giant-book-bahlil-lahadalia-jumat-782026-1786092905091_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I775" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Catatan Kritis Ekonom Soal Capaian Ekonomi RI 5,29% di Kuartal II-2026</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:55:05 +0700</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr">
+        <is>
+          <t>Indef menilai pertumbuhan ekonomi Indonesia pada kuartal II-2026 lebih rapuh dibandingkan kuartal I-2026 atau kuartal II-2025.</t>
+        </is>
+      </c>
+      <c r="F776" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G776" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807161205-4-757485/catatan-kritis-ekonom-soal-capaian-ekonomi-ri-529-di-kuartal-ii-2026</t>
+        </is>
+      </c>
+      <c r="H776" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/02/22/ilustrasi-perkantoran-jakarta_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I776" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Pemerintah Tahan Tarif Listrik - Ratusan Boeing 737 Max Kena Inspeksi</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:50:50 +0700</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr">
+        <is>
+          <t>Pemerintah Tahan Tarif Listrik - Ratusan Boeing 737 Max Kena Inspeksi</t>
+        </is>
+      </c>
+      <c r="F777" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G777" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807151027-8-757486/pemerintah-tahan-tarif-listrik--ratusan-boeing-737-max-kena-inspeksi</t>
+        </is>
+      </c>
+      <c r="H777" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/pemerintah-tahan-tarif-listrik-ratusan-boeing-737-max-kena-inspeksi-1786094987239_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I777" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Setahun Beroperasi, Prabowo Sebut Pendapatan Danantara Melejit 400%</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:44:17 +0700</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>Presiden RI Prabowo Subianto menyampaikan pendapatan Danantara melesat 400% dalam setahun beroperasi</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G778" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807164134-4-757497/setahun-beroperasi-prabowo-sebut-pendapatan-danantara-melejit-400</t>
+        </is>
+      </c>
+      <c r="H778" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/presiden-prabowo-subianto-memberikan-sambutan-pada-acara-peluncuran-dan-beda-buku-bahlil-lahadalia-di-djakarta-theatre-jakarta-1786091462751_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I778" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Detik-Detik Maut Siswa 14 Tahun Tembak Sekolah, Anak-Anak Berlarian</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr">
+        <is>
+          <t>Penembakan massal terjadi di Sekolah Debsirin Nonthaburi, Distrik Bang Kruai, Provinsi Nonthaburi, di Bangkok, Thailand Jumat. Pelakunya siswa berusia 14 tahun.</t>
+        </is>
+      </c>
+      <c r="F779" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G779" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807132859-7-757419/detik-detik-maut-siswa-14-tahun-tembak-sekolah-anak-anak-berlarian</t>
+        </is>
+      </c>
+      <c r="H779" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/para-siswa-berlari-saat-mengevakuasi-diri-dari-sekolah-debsirin-nonthaburilokasi-terjadinya-insiden-penembakandi-distrik-bang--1786084015262_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I779" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Cetak Sejarah, RI Teguhkan Kemerdekaan dengan Ketahanan Pangan</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:36:45 +0700</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr">
+        <is>
+          <t>Indonesia mencatat lompatan bersejarah dalam swasembada pangan, menghentikan impor beras, dan mencapai cadangan beras tertinggi. Kedaulatan pangan semakin kuat.</t>
+        </is>
+      </c>
+      <c r="F780" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G780" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807162827-4-757492/cetak-sejarah-ri-teguhkan-kemerdekaan-dengan-ketahanan-pangan</t>
+        </is>
+      </c>
+      <c r="H780" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/kementan-1786095304242_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I780" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Kebakaran Hanguskan Pasar Populer, Sumber Api belum Diketahui</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda Pasar Feria Barrio Lindo di Santa Cruz, Bolivia. Tidak ada korban jiwa, sementara penyebab kebakaran masih diselidiki pihak berwenang.</t>
+        </is>
+      </c>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807093234-7-757318/kebakaran-hanguskan-pasar-populer-sumber-api-belum-diketahui</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/tampilan-dari-drone-yang-memperlihatkan-petugas-darurat-sedang-menangani-kebakaran-di-pasar-feria-barrio-lindo-santa-cruz-boli-1786069284704_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I781" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Istana Ungkap Daftar Bursa Calon Gubernur BI: Ada Destry-Muliaman?</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:10:17 +0700</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>Emir Yanwardhana</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr">
+        <is>
+          <t>Istana Kepresidenan membuka sedikit informasi tentang bursa nama calon Gubernur Bank Indonesia (BI) definitif</t>
+        </is>
+      </c>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807153710-4-757467/istana-ungkap-daftar-bursa-calon-gubernur-bi-ada-destry-muliaman</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/22/menteri-sekretais-negara-prasetyo-hadi-menyampaika-keterangan-pers-terkait-pengunduran-diri-kepala-bgn-naniek-s-deyang-di-jaka-1784696978881_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I782" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>Penampakan Mobil Listrik Termurah di GIIAS, Harganya Cuma Rp 119 Juta</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>Ferry Sandi</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr">
+        <is>
+          <t>Mobil listrik mungil menarik perhatian di GIIAS 2026 dengan harga promo Rp119 juta. Ini dia mobilnya.</t>
+        </is>
+      </c>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807154830-4-757471/penampakan-mobil-listrik-termurah-di-giias-harganya-cuma-rp-119-juta</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/mobil-listrik-mungil-dfsk-seres-s5-menjadi-salah-satu-kendaraan-yang-menarik-perhatian-pengunjung-giias-2026-1786092059687_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I783" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>Dianggap Hina Presiden di Medsos, 3 Influencer Ini Masuk Penjara</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr">
+        <is>
+          <t>Tiga influencer TikTok di Senegal dijatuhi hukuman penjara dan denda karena menghina presiden. Kritikus menyebut ini serangan terhadap kebebasan berpendapat.</t>
+        </is>
+      </c>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807151446-4-757462/dianggap-hina-presiden-di-medsos-3-influencer-ini-masuk-penjara</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/12/23/ilustrasi-tiktok-reutersmike-blakefile-photo_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I784" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Bea Cukai Gagalkan Penyelundupan 10 Kg Ganja oleh Guru India ke Bali</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:50:25 +0700</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr">
+        <is>
+          <t>Direktorat Jenderal Bea dan Cukai Kementerian Keuangan (DJBC Kemenkeu) menggagalkan upaya penyelundupan narkoba jenis ganja ke Bali</t>
+        </is>
+      </c>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807151425-4-757461/bea-cukai-gagalkan-penyelundupan-10-kg-ganja-oleh-guru-india-ke-bali</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/05/27/penumpang-menunggu-kedatangan-pesawat-di-bandara-i-gusti-ngurah-rai-denpasar-bali-senin-2752024-selama-momen-libur-panjang-wai_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I785" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Kementan Percepat Pencairan Dana Pemulihan Sektor Pertanian Aceh</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:45:22 +0700</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>Martyasari Rizky</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr">
+        <is>
+          <t>Kementan dukung pemulihan sektor pertanian Aceh pascabencana dengan alokasi Rp1,7 triliun. Percepatan realisasi anggaran jadi kunci manfaat bagi petani.</t>
+        </is>
+      </c>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807153356-4-757466/kementan-percepat-pencairan-dana-pemulihan-sektor-pertanian-aceh</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/kukungan-kementerian-pertanian-untuk-pemulihan-sektor-pertanian-dan-perkebunan-pascabencana-hidrometeorologi-di-aceh-1786091674298_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I786" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Video: Peringatan Pelaku "The Big Short", Waspada "Market Crash"!</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:45:15 +0700</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>Peringatan Pelaku "The Big Short", Waspada "Market Crash"!</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807132034-8-757411/video-peringatan-pelaku-the-big-short-waspada-market-crash</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/peringatan-pelaku-the-big-short-waspada-market-crash-1786087265723_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I787" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Pengumuman! Coretax DJP Tak Bisa Diakses Selama Akhir Pekan</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:45:02 +0700</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>Chandra Dwi Pranata</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr">
+        <is>
+          <t>Ditjen Pajak akan melakukan pemeliharaan sistem pada akhir pekan ini teknologi informasi dan komunikasi (TIK)</t>
+        </is>
+      </c>
+      <c r="F788" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G788" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807145702-4-757456/pengumuman-coretax-djp-tak-bisa-diakses-selama-akhir-pekan</t>
+        </is>
+      </c>
+      <c r="H788" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/12/16/kantor-pelayanan-pajak-kpp-pratama-mampang-prapatan-membuka-layanan-pojok-pajak-di-lobi-gedung-bank-mega-tendean-jakarta-selat-1765881261158_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I788" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>Video: China Pajaki Trust Offshore, Konglomerat Panik</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:30:36 +0700</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr">
+        <is>
+          <t>China Pajaki Trust Offshore, Konglomerat Panik</t>
+        </is>
+      </c>
+      <c r="F789" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G789" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807132021-8-757410/video-china-pajaki-trust-offshore-konglomerat-panik</t>
+        </is>
+      </c>
+      <c r="H789" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/china-pajaki-trust-offshore-konglomerat-panik-1786087189235_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I789" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>ESDM Beberkan Penyebab Sektor Tambang Terkontraksi di Kuartal II-2026</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr">
+        <is>
+          <t>Ini penyebab sektor pertambangan alami kontraksi di kuartal II-2026</t>
+        </is>
+      </c>
+      <c r="F790" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G790" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807141055-4-757443/esdm-beberkan-penyebab-sektor-tambang-terkontraksi-di-kuartal-ii-2026</t>
+        </is>
+      </c>
+      <c r="H790" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/04/12/area-tambang-terbuka-grasberg-dan-tambang-bawah-tanah-deep-mill-level-zone-dmlz-pt-freeport-indonesia-ptfi-pt-freeport-indones-1775944307191_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I790" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Trump Hajar China, Ekspor "Harta Karun" Ini Diblokir Habis</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>tfa</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr">
+        <is>
+          <t>Pemerintah AS memperketat kebijakan ekspor limbah tungsten dan baterai litium untuk mendukung industri daur ulang.</t>
+        </is>
+      </c>
+      <c r="F791" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G791" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807141025-4-757442/trump-hajar-china-ekspor-harta-karun-ini-diblokir-habis</t>
+        </is>
+      </c>
+      <c r="H791" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/01/11/bendera-as-china-1768108640745_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I791" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Video: Uang Primer Adjusted Juli 2026 Tumbuh 17,1% (YoY)</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:00:49 +0700</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr">
+        <is>
+          <t>Uang Primer Adjusted Juli 2026 Tumbuh 17,1% (YoY)</t>
+        </is>
+      </c>
+      <c r="F792" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G792" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807132004-8-757409/video-uang-primer-adjusted-juli-2026-tumbuh-171--yoy-</t>
+        </is>
+      </c>
+      <c r="H792" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/uang-primer-adjusted-juli-2026-tumbuh-171-yoy-1786087113619_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I792" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Prabowo, Luhut Hingga Dasco Hadiri Peluncuran Buku Bahlil Lahadalia</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:45:46 +0700</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr">
+        <is>
+          <t>Menteri ESDM Bahlil Lahadalia terbitkan buku bertajuk 10 Karya Nyata untuk Negeri</t>
+        </is>
+      </c>
+      <c r="F793" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G793" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807144103-4-757454/prabowo-luhut-hingga-dasco-hadiri-peluncuran-buku-bahlil-lahadalia</t>
+        </is>
+      </c>
+      <c r="H793" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/prabowo-subianto-hadir-dalam-peluncuran-buku-bahlil-lahadalia-di-jakarta-jumat-782026-1786088057188_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I793" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Juli 2026, Cadev RI Tembus USD 145,3 Miliar</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:45:13 +0700</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr">
+        <is>
+          <t>Juli 2026, Cadev RI Tembus USD 145,3 Miliar, Susut USD 300 Juta Dalam Sebulan</t>
+        </is>
+      </c>
+      <c r="F794" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G794" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807131922-8-757407/juli-2026-cadev-ri-tembus-usd-1453-miliar</t>
+        </is>
+      </c>
+      <c r="H794" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/juli-2026-cadev-ri-tembus-usd-1453-miliar-1786087022386_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I794" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Momen Prabowo Lempar dan Injak-injak Genteng Buatan BRIN</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:45:08 +0700</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menguji langsung ketahanan genteng hasil inovasi Badan Riset dan Inovasi Nasional (BRIN) di Istana Merdeka, Jakarta, Jumat (7/8/2026).</t>
+        </is>
+      </c>
+      <c r="F795" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G795" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807135052-7-757435/momen-prabowo-lempar-dan-injak-injak-genteng-buatan-brin</t>
+        </is>
+      </c>
+      <c r="H795" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/presiden-prabowo-subianto-menguji-langsung-ketahanan-genteng-hasil-inovasi-badan-riset-dan-inovasi-nasional-brin-saat-bertemu--1786085449394_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I795" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>Kisi-kisi RAPBN 2027: Defisit Melebar Karena Tambahan Belanja KL</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:40:48 +0700</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr">
+        <is>
+          <t>Pemerintah akan mengajukan RAPBN 2027 kepada DPR.</t>
+        </is>
+      </c>
+      <c r="F796" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G796" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807135120-4-757433/kisi-kisi-rapbn-2027-defisit-melebar-karena-tambahan-belanja-kl</t>
+        </is>
+      </c>
+      <c r="H796" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/20/layar-menampilkan-presiden-prabowo-subianto-menyampaikan-pidato-saat-menghadiri-rapat-paripurna-dpr-ri-ke-19-terkait-kem-dan-p-1779249146792_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I796" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Perang Kelar Langsung Bikin Harga BBM Turun? Tak Semudah Itu</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>tps</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr">
+        <is>
+          <t>Serangan Ukraina ke Rusia dan ketegangan di Teluk Persia memicu krisis penyulingan minyak global, menyebabkan lonjakan harga bensin.</t>
+        </is>
+      </c>
+      <c r="F797" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G797" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807080528-4-757296/perang-kelar-langsung-bikin-harga-bbm-turun-tak-semudah-itu</t>
+        </is>
+      </c>
+      <c r="H797" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/06/sebuah-tayangan-drone-menunjukkan-kilang-minyak-stanlow-milik-essar-energy-kilang-terbesar-kedua-di-inggris-yang-memproduksi-s-1778060006858_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I797" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>100 Kapal Nikel Cs Sudah Resmi Ekspor, Rp2,2 Triliun Terselamatkan</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>pgr</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr">
+        <is>
+          <t>Kegiatan ekspor nikel-timah cs resmi dibuka lagi</t>
+        </is>
+      </c>
+      <c r="F798" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G798" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807133542-4-757420/100-kapal-nikel-cs-sudah-resmi-ekspor-rp22-triliun-terselamatkan</t>
+        </is>
+      </c>
+      <c r="H798" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2023/06/16/eksor-perdana-nikel-sulphate_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I798" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>Penampakan Febrie Adriansyah Pakai Rompi Tahanan Pink dan Diborgol</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:22:40 +0700</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr">
+        <is>
+          <t>Tim 9 Kejagung periksa mantan Jaksa Agung Muda Febrie Adriansyah sebagai tersangka korupsi dan TPPU. Febrie dibawa dari Rutan KPK dengan rompi tahanan.</t>
+        </is>
+      </c>
+      <c r="F799" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G799" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807141349-4-757446/penampakan-febrie-adriansyah-pakai-rompi-tahanan-pink-diborgol</t>
+        </is>
+      </c>
+      <c r="H799" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/tim-9-kejaksaan-agung-kejagung-akan-memeriksa-mantan-jampidsus-febrie-adriansyah-fa-sebagai-tersangka-kasus-korupsi-dan-dugaan-1786087084645_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I799" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Mobil Terbang X2 di GIIAS Bikin Heboh, Pabrikan China Ini yang Bikin</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:20:01 +0700</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr">
+        <is>
+          <t>Mobil terbang X2 diperkenalkan di Indonesia, namun regulasi masih belum siap. Perusahaan asal China ini ternyata yang produksi.</t>
+        </is>
+      </c>
+      <c r="F800" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G800" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807134403-4-757431/mobil-terbang-x2-di-giias-bikin-heboh-pabrikan-china-ini-yang-bikin</t>
+        </is>
+      </c>
+      <c r="H800" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/x-peng-mobil-terbang-x2-di-giias-2026-1786084985992_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I800" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Prabowo Masih Cari Calon Gubernur BI Baru, Banyak Nama Masuk Daftar</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:18:24 +0700</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto belum mengirimkan Surat Presiden (Surpres) kepada DPR RI, terkait calon definitif Gubernur Bank Indonesia</t>
+        </is>
+      </c>
+      <c r="F801" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G801" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807141228-4-757445/prabowo-masih-cari-calon-gubernur-bi-baru-banyak-nama-masuk-daftar</t>
+        </is>
+      </c>
+      <c r="H801" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/27/menteri-sekretaris-negara-prasetyo-hadi-saat-menyampaikan-konferensi-pers-di-bank-indonesia-jakarta-senin-2772026-1785117094422_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I801" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>Orang Miskin Kota dan Desa Sama Saja: Duit Habis Buat Beras, Rokok-Kopi</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:15:28 +0700</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr">
+        <is>
+          <t>Garis kemiskinan di Indonesia kembali naik, berdasarkan catatan terbaru Badan Pusat Statistik (BPS).</t>
+        </is>
+      </c>
+      <c r="F802" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G802" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807131928-4-757408/orang-miskin-kota-desa-sama-saja-duit-habis-buat-beras-rokok-kopi</t>
+        </is>
+      </c>
+      <c r="H802" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2018/11/13/70164ddf-8308-4ebc-834d-14ac21785575_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I802" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Video: Harga Properti Residensial Naik Tipis</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:15:25 +0700</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr">
+        <is>
+          <t>Harga Properti Residensial Naik Tipis</t>
+        </is>
+      </c>
+      <c r="F803" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G803" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807131910-8-757406/video-harga-properti-residensial-naik-tipis</t>
+        </is>
+      </c>
+      <c r="H803" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/harga-properti-residensial-naik-tipis-1786086910446_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I803" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Ada Apa India, Pemerintah Tiba-Tiba "Sale" Besar-besaran BUMN?</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr">
+        <is>
+          <t>Pemerintah India melakukan divestasi besar-besaran saham BUMN. Target penghimpunan dana tahun ini mencapai US$8,4 miliar.</t>
+        </is>
+      </c>
+      <c r="F804" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G804" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807125244-4-757402/ada-apa-india-pemerintah-tiba-tiba-sale-besar-besaran-bumn</t>
+        </is>
+      </c>
+      <c r="H804" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/11/bendera-india-dok-pixabay-1778482382486_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I804" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Top! Tingkat Kepuasan Stakeholder Terhadap Pertamina NRE Meningkat</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:55:50 +0700</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr">
+        <is>
+          <t>Pertamina NRE mencatat peningkatan kepuasan stakeholder dengan skor 4,30. Kepercayaan dan kolaborasi jadi kunci dalam transisi energi baru dan terbarukan.</t>
+        </is>
+      </c>
+      <c r="F805" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G805" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807135018-4-757432/top-tingkat-kepuasan-stakeholder-terhadap-pertamina-nre-meningkat</t>
+        </is>
+      </c>
+      <c r="H805" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/pertamina-nre-1786085722621_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I805" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Masalah LTJ Tuntas! 100 Kapal Nikel Cs Kembali Berlayar Ekspor</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr">
+        <is>
+          <t>KSP mencatat sebanyak 100 kapal sudah bisa kembali berlayar ekspor</t>
+        </is>
+      </c>
+      <c r="F806" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G806" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807132737-4-757417/masalah-ltj-tuntas-100-kapal-nikel-cs-kembali-berlayar-ekspor</t>
+        </is>
+      </c>
+      <c r="H806" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/28/kepala-staf-kepresidenan-ri-dudung-abdurachman-saat-menyampaikan-keterangan-usai-rapat-koordinasi-tata-kelola-ekspor-mineral-k-1785199707509_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I806" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Jurang Si Kaya dan Miskin di Jakarta, Jawa Barat hingga Maluku Melebar</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:35:15 +0700</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>Ketimpangan di Indonesia kembali melebar, baik di perkotaan maupun perdesaan, menurut catatan terbaru Badan Pusat Statistik (BPS).</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G807" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807095346-4-757334/jurang-si-kaya-miskin-di-jakarta-jawa-barat-hingga-maluku-melebar</t>
+        </is>
+      </c>
+      <c r="H807" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/01/18/infografis-tingkat-ketimpangan-pengeluaran-penduduk-ri_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I807" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Ketua Gapensi: Sudah Rp1.000 T Digelontorkan di Konstruksi Era Prabowo</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:30:43 +0700</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto bertemu pengusaha Kadin, membahas capaian infrastruktur dan pentingnya sinergi elite nasional untuk pembangunan bangsa.</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G808" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807131437-4-757413/ketua-gapensi-sudah-rp1000-t-digelontorkan-di-konstruksi-era-prabowo</t>
+        </is>
+      </c>
+      <c r="H808" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/07/22/andi-rukman-nurdin-karumpa-ketua-umum-gapensi_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I808" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Perang Saudara Arab Membara Lagi, Pemerintah Diserang-30 Tewas</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>tps</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr">
+        <is>
+          <t>Serangan Houthi di Yaman menewaskan 30 tentara pemerintah dan melukai 15 lainnya. Ini adalah eskalasi terburuk sejak 2022</t>
+        </is>
+      </c>
+      <c r="F809" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G809" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807082330-4-757303/perang-saudara-arab-membara-lagi-pemerintah-diserang-30-tewas</t>
+        </is>
+      </c>
+      <c r="H809" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/04/06/para-pengikut-houthi-memegang-senjata-granat-berpeluncur-roket-rpg-selama-demonstrasi-pro-iran-saat-konflik-as-israel-dengan-i-1775474286731_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I809" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Soal Listrik di Kalimantan, Ini Penjelasan Kementerian ESDM</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr">
+        <is>
+          <t>Kementerian ESDM ungkap alasan kondisi listrik di Kalimantan</t>
+        </is>
+      </c>
+      <c r="F810" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G810" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807125807-4-757404/soal-listrik-di-kalimantan-ini-penjelasan-kementerian-esdm</t>
+        </is>
+      </c>
+      <c r="H810" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/10/17/direktur-jenderal-minerba-kementerian-esdm-tri-winarno-menyampaikan-paparan-dalam-program-cnbc-indonesia-road-to-hari-tambang--1760700772244_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I810" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>Video: Daftar Negara Penguasa Senjata Nuklir, Iran Masuk?</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:20:34 +0700</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>Daftar Negara Penguasa Senjata Nuklir, Iran Masuk?</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G811" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807102051-8-757346/video-daftar-negara-penguasa-senjata-nuklir-iran-masuk</t>
+        </is>
+      </c>
+      <c r="H811" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/daftar-negara-penguasa-senjata-nuklir-iran-masuk-1786081813863_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I811" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>Thailand Geger! Siswa 14 Tahun Bawa Senjata Tembak Sekolah, 7 Tewas</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr">
+        <is>
+          <t>Insiden penembakan di Sekolah Debsirin Nonthaburi, Thailand, menewaskan tujuh orang, termasuk pelaku. Empat lainnya terluka.</t>
+        </is>
+      </c>
+      <c r="F812" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G812" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807121808-4-757397/thailand-geger-siswa-14-tahun-bawa-senjata-tembak-sekolah-7-tewas</t>
+        </is>
+      </c>
+      <c r="H812" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/sebuah-ambulans-yang-diduga-membawa-pelaku-penembakan-bermanuver-di-sekolah-debsirin-nonthaburilokasi-terjadinya-insiden-penem-1786078717442_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I812" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Suhu "Neraka" 40 Derajat Terjang Italia, 27 Kota Siaga Merah</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:51:40 +0700</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>Reuters</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr">
+        <is>
+          <t>Italia menetapkan siaga merah di 27 kota akibat gelombang panas ekstrem. Suhu mendekati 40 Derajat Celsius.</t>
+        </is>
+      </c>
+      <c r="F813" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G813" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807101452-7-757339/suhu-neraka-40-derajat-terjang-italia-27-kota-siaga-merah</t>
+        </is>
+      </c>
+      <c r="H813" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/warga-mengangkat-tangan-sembari-menyejukkan-diri-di-tengah-semburan-kabut-air-di-luar-basilika-santa-maria-degli-angeli-saat-b-1786071864797_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I813" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>Saat Prabowo Tinjau Alutsista Canggih BRIN, Drone hingga Satelit</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo meninjau inovasi BRIN di Istana, mulai dari teknologi air minum hingga pesawat nirawak, untuk mendukung percepatan pembangunan nasional.</t>
+        </is>
+      </c>
+      <c r="F814" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G814" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807115401-7-757383/saat-prabowo-tinjau-alutsista-canggih-brin-drone-hingga-satelit</t>
+        </is>
+      </c>
+      <c r="H814" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/presiden-prabowo-subianto-meninjau-hasil-riset-dan-inovasi-badan-riset-dan-inovasi-nasional-brin-di-istana-kepresidenan-jakart-1786078429219_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I814" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Video: Kebutuhan Susu Melonjak Imbas MBG, Tapi Sayang 75% Masih Impor</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:27:00 +0700</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr">
+        <is>
+          <t>Kebutuhan Susu Melonjak Imbas MBG, Tapi Sayang 75% Masih Harus Impor</t>
+        </is>
+      </c>
+      <c r="F815" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G815" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807114639-8-757382/video-kebutuhan-susu-melonjak-imbas-mbg-tapi-sayang-75-masih-impor</t>
+        </is>
+      </c>
+      <c r="H815" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/kebutuhan-susu-melonjak-imbas-mbg-tapi-sayang-75-masih-harus-impor-1786079202399_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I815" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Video: Prabowo Panggil Pimpinan BRIN, Bahas Riset Program Prioritas</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:15:46 +0700</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto memanggil jajaran pimpinan Badan Riset dan Inovasi Nasional ke Istana Kepresidenan Kamis kemarin.</t>
+        </is>
+      </c>
+      <c r="F816" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G816" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807092722-8-757316/video-prabowo-panggil-pimpinan-brin-bahas-riset-program-prioritas</t>
+        </is>
+      </c>
+      <c r="H816" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/prabowo-panggil-pimpinan-brin-bahas-riset-program-prioritas-1786069775435_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I816" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Pemerintah Siapkan Revisi Aturan Ketentuan Logam Tanah Jarang</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:15:00 +0700</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr">
+        <is>
+          <t>Pemerintah siapkan revisi aturan untuk ketentuan logam tanah jarang</t>
+        </is>
+      </c>
+      <c r="F817" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G817" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807112107-4-757371/pemerintah-siapkan-revisi-aturan-ketentuan-logam-tanah-jarang</t>
+        </is>
+      </c>
+      <c r="H817" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/11/03/mineral-berharga-mengandung-thorium-dan-logam-tanah-jarang-ltj-1762142199363_169.webp?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I817" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Siapa Abdul El-Sayed, Muslim Calon Kuat Senat AS yang Dibenci Trump?</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:05:21 +0700</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr">
+        <is>
+          <t>Kemenangan Abdul El-Sayed dalam pemilihan pendahuluan Partai Demokrat di Michigan AS mengejutkan. Kemenangannya juga membuat reaksi keras dari Trump.</t>
+        </is>
+      </c>
+      <c r="F818" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G818" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807115752-4-757391/siapa-abdul-el-sayed-muslim-calon-kuat-senat-as-yang-dibenci-trump</t>
+        </is>
+      </c>
+      <c r="H818" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/abdul-el-sayed-pemenang-pemilihan-pendahuluan-partai-demokrat-di-michigan-as-berbicara-dalam-sebuah-konferensi-pers-di-detroit-1786076585200_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I818" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Video: RI Jawara Pertumbuhan di G20, China dan AS Kalah Telak</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:00:07 +0700</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr">
+        <is>
+          <t>Ekonomi Indonesia kembali menunjukkan kinerja positif.</t>
+        </is>
+      </c>
+      <c r="F819" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G819" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807095305-8-757333/video-ri-jawara-pertumbuhan-di-g20-china-as-kalah-telak</t>
+        </is>
+      </c>
+      <c r="H819" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/ri-jawara-pertumbuhan-di-g20-china-as-kalah-telak-1786075519821_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I819" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Gempa M 5,8 Guncang Filipina, Warga Panik-Gedung Goyang</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr">
+        <is>
+          <t>Gempa magnitudo 5,8 mengguncang lepas pantai Filipina, terasa hingga Manila.</t>
+        </is>
+      </c>
+      <c r="F820" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G820" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807113104-4-757373/gempa-m-58-guncang-filipina-warga-panik-gedung-goyang</t>
+        </is>
+      </c>
+      <c r="H820" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/15/gempa-filipina-tangkapan-layar-1781517767490_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I820" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr">
+        <is>
+          <t>Taiwan Siaga Hadapi Ancaman China - Kriteria Calon Gubernur BI</t>
+        </is>
+      </c>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:40:42 +0700</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>Taiwan Siaga Hadapi Ancaman China - Kriteria Calon Gubernur BI</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G821" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807102049-8-757340/taiwan-siaga-hadapi-ancaman-china--kriteria-calon-gubernur-bi</t>
+        </is>
+      </c>
+      <c r="H821" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/taiwan-siaga-hadapi-ancaman-china-kriteria-calon-gubernur-bi-1786076749926_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I821" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>BRIN Sudah Kembangkan Reaktor Nuklir Mini, Segini Kapasitasnya</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:35:00 +0700</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr">
+        <is>
+          <t>BRIN sudah kembangkan small modular reactor (SMR)</t>
+        </is>
+      </c>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807105448-4-757361/brin-sudah-kembangkan-reaktor-nuklir-mini-segini-kapasitasnya</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/prabowo-panggil-pimpinan-brin-bahas-riset-program-prioritas-1786069775435_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I822" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>Energi</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>Regulasi yang Stabil Dinilai Perkuat Industri Pertambangan Nasional</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>Intan Pratiwi</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Wakil Ketua Komisi XII DPR RI Eddy Soeparno menilai regulasi yang stabil dan konsisten menjadi faktor penting untuk memperkuat industri pertambangan nasional. Menurutnya, Kepastian hukum mampu...</t>
+        </is>
+      </c>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tje38q522/regulasi-yang-stabil-dinilai-perkuat-industri-pertambangan-nasional</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/pimpinan-mpr-dari-fraksi-pan-eddy_260124153206-732.jpeg</t>
+        </is>
+      </c>
+      <c r="I823" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>Krom Bank Bidik Pertumbuhan Industri Pergadaian yang Melonjak 50 Persen</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:09:19 +0700</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- PT Krom Bank Indonesia Tbk (BBSI) membidik peluang pertumbuhan industri pergadaian yang dalam setahun terakhir mencatat kenaikan outstanding pembiayaan lebih dari 50 persen. Prospek tersebut mendorong...</t>
+        </is>
+      </c>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tje9jj416/krom-bank-bidik-pertumbuhan-industri-pergadaian-yang-melonjak-50-persen</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/027994100-1758191471-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I824" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>Pertanian</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>Mentan Pastikan Kekeringan Belum Ganggu Ketersediaan Pangan Nasional</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:01:00 +0700</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Menteri Pertanian (Mentan) Andi Amran Sulaiman menegaskan pemerintah telah menyiapkan langkah antisipasi kekeringan jauh sebelum dampaknya meluas di berbagai daerah. Kementerian Pertanian (Kementan) mengandalkan pompanisasi, rehabilitasi irigasi,...</t>
+        </is>
+      </c>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tje8l6423/mentan-pastikan-kekeringan-belum-ganggu-ketersediaan-pangan-nasional</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/002805300-1781098591-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I825" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>Infografis 5 BUMN Gulung Tikar Akibat Pailit</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:45:59 +0700</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr">
+        <is>
+          <t>Lima BUMN ini pernah berjaya, tetapi akhirnya harus berhadapan dengan kepailitan.</t>
+        </is>
+      </c>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264513/infografis-5-bumn-gulung-tikar-akibat-pailit</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/J4tkXvgTtmtTo98Cief-x6TI7IA=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318489/original/097178200_1786099314-6b7cf5d9-c05d-4873-ad74-fd590a0d78ea.jpg</t>
+        </is>
+      </c>
+      <c r="I826" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>Viral Gunungan Sampah di Kedaung Kaliangke, DLH Turunkan Belasan Truk</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:29:09 +0700</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr">
+        <is>
+          <t>DLH DKI mengerahkan belasan truk dan alat berat untuk mengangkut 140 ton sampah di Kedaung Kaliangke.</t>
+        </is>
+      </c>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264509/viral-gunungan-sampah-di-kedaung-kaliangke-dlh-turunkan-belasan-truk</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/QyRnoPyFSyBaO2dfpO8kVvYCRn4=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318486/original/097663500_1786098544-059233fe-17c9-493d-b7ac-8a55a02561f5.jpg</t>
+        </is>
+      </c>
+      <c r="I827" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>Wamendagri Ribka Puji Kerja Sigap Pemkab Jayapura Bantu Korban Dugaan Keracunan MBG</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:18:13 +0700</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>Ribka mengatakan pemerintah akan terus memperkuat fungsi pengawasan agar kejadian serupa tidak terulang.</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264500/wamendagri-ribka-puji-kerja-sigap-pemkab-jayapura-bantu-korban-dugaan-keracunan-mbg</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/sU2FRaFlgXYHolPFszrnq6a49mM=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318471/original/079750300_1786097889-WhatsApp_Image_2026-08-07_at_16.42.12__1_.jpeg</t>
+        </is>
+      </c>
+      <c r="I828" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>Wamendagri Ungkap Bekal Penting Aparatur Hadapi Tantangan</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:56:33 +0700</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr">
+        <is>
+          <t>Wamendagri Akhmad Wiyagus mengajak aparatur meneladani semangat juang dan sportivitas dalam menjalankan tugas pemerintahan.</t>
+        </is>
+      </c>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264473/wamendagri-ungkap-bekal-penting-aparatur-hadapi-tantangan</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/QFJRpJD6KzTB4Ti76qUoYdPDva0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318446/original/056086600_1786096589-WhatsApp_Image_2026-08-07_at_16.42.11.jpeg</t>
+        </is>
+      </c>
+      <c r="I829" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>Ring Road GBK Ditutup Sementara 7-8 Agustus karena Chelsea vs AC Milan, Cek Penyesuaiannya</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:50:26 +0700</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr">
+        <is>
+          <t>Ring Road Stadion Utama GBK ditutup sementara pada 7-8 Agustus 2026 untuk Indonesia Super Cup Chelsea FC vs AC Milan.</t>
+        </is>
+      </c>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/07/17491311/ring-road-gbk-ditutup-sementara-7-8-agustus-karena-chelsea-vs-ac-milan</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/f6cBw_PiOyMiPwxHoPo9kWoUCps=/0x0:780x390/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2016/08/25/135819920160824KP40-KCM1780x390.JPG</t>
+        </is>
+      </c>
+      <c r="I830" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>Dari Liverpool ke Trabzonspor, Kekayaan Mohamed Salah Tembus Rp 2,5 Triliun</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:50:26 +0700</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr">
+        <is>
+          <t>Selama membela Liverpool, Salah mengantongi gaji lebih dari Rp 6 miliar per pekan atau Rp 483,3 miliar per tahun.</t>
+        </is>
+      </c>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/07/173200426/dari-liverpool-ke-trabzonspor-kekayaan-mohamed-salah-tembus-rp-2-5-triliun</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/0JsZSytlCoFE2kyXmxzhAPG5y0Q=/48x0:1830x1188/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/07/04/6a4858596cda4.jpg</t>
+        </is>
+      </c>
+      <c r="I831" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>Penebangan Pohon di Cihapit Disorot, MasHuKo Dorong Audit Pohon Perkotaan</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:50:26 +0700</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr">
+        <is>
+          <t>Kasus penebangan pohon di Jalan Riau Bandung dinilai menjadi momentum membenahi tata kelola pohon perkotaan, termasuk inventarisvdan audit pohon.</t>
+        </is>
+      </c>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>https://bandung.kompas.com/read/2026/08/07/171548478/penebangan-pohon-di-cihapit-disorot-mashuko-dorong-audit-pohon-perkotaan</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/t4WKeq7qUBfZVE9isMV8ELMCgmw=/188x0:1200x675/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/03/6a7073762c500.webp</t>
+        </is>
+      </c>
+      <c r="I832" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I716"/>
+  <autoFilter ref="A1:I832"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-07.xlsx
+++ b/data/berita_2026-08-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$832</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$987</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I832"/>
+  <dimension ref="A1:I987"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -39537,8 +39537,7293 @@
         </is>
       </c>
     </row>
+    <row r="833">
+      <c r="A833" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>Menhut sampaikan Salam ASRI dari Presiden Prabowo untuk rakyat Sumsel</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:36:06 +0700</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr">
+        <is>
+          <t>Menteri Kehutanan (Menhut) Raja Juli Antoni menyampaikan salam Presiden Prabowo Subianto kepada masyarakat Sumatera ...</t>
+        </is>
+      </c>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684591/menhut-sampaikan-salam-asri-dari-presiden-prabowo-untuk-rakyat-sumsel</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/09f9780a-eb82-421c-8595-dd90e81a1b27.jpg</t>
+        </is>
+      </c>
+      <c r="I833" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="834">
+      <c r="A834" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>AdaKami terapkan prinsip "human oversight" dalam adopsi AI</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:33:57 +0700</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr">
+        <is>
+          <t>PT Pembiayaan Digital Indonesia (AdaKami) menyatakan bahwa perusahaan menerapkan prinsip human oversight atau ...</t>
+        </is>
+      </c>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684589/adakami-terapkan-prinsip-human-oversight-dalam-adopsi-ai</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Foto-2-AdaKami-at-AI-Cyber-Forum.jpg</t>
+        </is>
+      </c>
+      <c r="I834" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="835">
+      <c r="A835" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>PASI alihkan pelatnas mandiri untuk persiapan Asian Games 2026</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:33:53 +0700</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr">
+        <is>
+          <t>Pengurus Besar Persatuan Atletik Seluruh Indonesia (PB PASI) mengalihkan program pelatnas mandiri yang sebelumnya ...</t>
+        </is>
+      </c>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684587/pasi-alihkan-pelatnas-mandiri-untuk-persiapan-asian-games-2026</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/12/26/foto-terbaik-2025-2696653.jpg</t>
+        </is>
+      </c>
+      <c r="I835" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="836">
+      <c r="A836" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>Sebelum ganti gula ke stevia, ketahui dulu efek sampingnya</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:32:46 +0700</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>Stevia semakin populer sebagai pengganti gula, terutama bagi orang yang ingin mengurangi asupan gula atau menjaga kadar ...</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684584/sebelum-ganti-gula-ke-stevia-ketahui-dulu-efek-sampingnya</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/28/IMG_3358.jpg</t>
+        </is>
+      </c>
+      <c r="I836" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="837">
+      <c r="A837" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B837" t="inlineStr">
+        <is>
+          <t>Pendaftaran upacara HUT ke-81 RI di Istana diperpanjang 8-9 Agustus</t>
+        </is>
+      </c>
+      <c r="C837" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:32:29 +0700</t>
+        </is>
+      </c>
+      <c r="D837" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E837" t="inlineStr">
+        <is>
+          <t>Pemerintah memperpanjang pendaftaran dan menambah kuota undangan Upacara Peringatan HUT ke-81 Kemerdekaan Republik ...</t>
+        </is>
+      </c>
+      <c r="F837" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G837" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684581/pendaftaran-upacara-hut-ke-81-ri-di-istana-diperpanjang-8-9-agustus</t>
+        </is>
+      </c>
+      <c r="H837" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/28/upacara-penurunan-bendera-di-istana-merdeka-1jrq1.jpg</t>
+        </is>
+      </c>
+      <c r="I837" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B838" t="inlineStr">
+        <is>
+          <t>Polres Jakpus perkuat kolaborasi berantas tramadol di Tanah Abang</t>
+        </is>
+      </c>
+      <c r="C838" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:31:04 +0700</t>
+        </is>
+      </c>
+      <c r="D838" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E838" t="inlineStr">
+        <is>
+          <t>Polres Metro Jakarta Pusat memperkuat kolaborasi dengan pemerintah daerah dan masyarakat untuk memberantas peredaran ...</t>
+        </is>
+      </c>
+      <c r="F838" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G838" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684579/polres-jakpus-perkuat-kolaborasi-berantas-tramadol-di-tanah-abang</t>
+        </is>
+      </c>
+      <c r="H838" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000833884.jpg</t>
+        </is>
+      </c>
+      <c r="I838" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B839" t="inlineStr">
+        <is>
+          <t>BGN pastikan penerima manfaat MBG dapat pelayanan kesehatan optimal</t>
+        </is>
+      </c>
+      <c r="C839" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:29:05 +0700</t>
+        </is>
+      </c>
+      <c r="D839" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E839" t="inlineStr">
+        <is>
+          <t>Badan Gizi Nasional (BGN) memastikan seluruh penerima manfaat dalam pelaksanaan program Makan Bergizi Gratis (MBG) di ...</t>
+        </is>
+      </c>
+      <c r="F839" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G839" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684572/bgn-pastikan-penerima-manfaat-mbg-dapat-pelayanan-kesehatan-optimal</t>
+        </is>
+      </c>
+      <c r="H839" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000905543.jpg</t>
+        </is>
+      </c>
+      <c r="I839" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B840" t="inlineStr">
+        <is>
+          <t>Bandara Husein Bandung siap layani penerbangan jet pada 14 Agustus</t>
+        </is>
+      </c>
+      <c r="C840" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:28:11 +0700</t>
+        </is>
+      </c>
+      <c r="D840" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E840" t="inlineStr">
+        <is>
+          <t>PT Angkasa Pura Indonesia (Persero) atau InJourney Airports menyatakan Bandara Husein Sastranegara Bandung telah siap ...</t>
+        </is>
+      </c>
+      <c r="F840" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G840" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684568/bandara-husein-bandung-siap-layani-penerbangan-jet-pada-14-agustus</t>
+        </is>
+      </c>
+      <c r="H840" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_9221.jpeg</t>
+        </is>
+      </c>
+      <c r="I840" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B841" t="inlineStr">
+        <is>
+          <t>DPRD DKI dukung nama perusahaan pembuang sampah ilegal diumumkan</t>
+        </is>
+      </c>
+      <c r="C841" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:26:56 +0700</t>
+        </is>
+      </c>
+      <c r="D841" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E841" t="inlineStr">
+        <is>
+          <t>Komisi D DPRD DKI Jakarta mendukung langkah tegas Gubernur DKI Jakarta Pramono Anung yang akan menindak tegas ...</t>
+        </is>
+      </c>
+      <c r="F841" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684565/dprd-dki-dukung-nama-perusahaan-pembuang-sampah-ilegal-diumumkan</t>
+        </is>
+      </c>
+      <c r="H841" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/1001005066.jpg</t>
+        </is>
+      </c>
+      <c r="I841" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B842" t="inlineStr">
+        <is>
+          <t>Tebang 10 pohon, Pemkot Bandung denda pengelola videotron Rp100 juta</t>
+        </is>
+      </c>
+      <c r="C842" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:26:28 +0700</t>
+        </is>
+      </c>
+      <c r="D842" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E842" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota (Pemkot) Bandung, Jawa Barat, menjatuhkan denda administratif sebesar Rp100 juta kepada pengelola ...</t>
+        </is>
+      </c>
+      <c r="F842" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G842" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684564/tebang-10-pohon-pemkot-bandung-denda-pengelola-videotron-rp100-juta</t>
+        </is>
+      </c>
+      <c r="H842" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/d51015a7-78dd-43fd-957f-7cf0a8720adc.jpeg</t>
+        </is>
+      </c>
+      <c r="I842" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B843" t="inlineStr">
+        <is>
+          <t>Prabowo: Bahlil Lahadalia tidak hanya menteri tapi juga mitra politik</t>
+        </is>
+      </c>
+      <c r="C843" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:26:11 +0700</t>
+        </is>
+      </c>
+      <c r="D843" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E843" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menyebut Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia tidak hanya sebagai ...</t>
+        </is>
+      </c>
+      <c r="F843" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G843" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684560/prabowo-bahlil-lahadalia-tidak-hanya-menteri-tapi-juga-mitra-politik</t>
+        </is>
+      </c>
+      <c r="H843" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/19308ac9-e06c-4451-9835-757ab1cfb7d3.jpeg</t>
+        </is>
+      </c>
+      <c r="I843" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B844" t="inlineStr">
+        <is>
+          <t>Istana jelaskan pengembangan riset nuklir untuk energi dan medis</t>
+        </is>
+      </c>
+      <c r="C844" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:25:31 +0700</t>
+        </is>
+      </c>
+      <c r="D844" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E844" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara Prasetyo Hadi mengatakan pengembangan riset nuklir oleh BRIN dan lembaga pemerintah lainnya ...</t>
+        </is>
+      </c>
+      <c r="F844" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G844" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684559/istana-jelaskan-pengembangan-riset-nuklir-untuk-energi-dan-medis</t>
+        </is>
+      </c>
+      <c r="H844" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Image-07-08-26-at-18.16.jpeg</t>
+        </is>
+      </c>
+      <c r="I844" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B845" t="inlineStr">
+        <is>
+          <t>DPMG: Penyaluran dana desa di Aceh sudah capai 81,88 persen</t>
+        </is>
+      </c>
+      <c r="C845" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:22:43 +0700</t>
+        </is>
+      </c>
+      <c r="D845" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E845" t="inlineStr">
+        <is>
+          <t>Dinas Pemberdayaan Masyarakat dan Gampong (DPMG) Aceh mencatat realisasi penyaluran dana desa reguler di Aceh telah ...</t>
+        </is>
+      </c>
+      <c r="F845" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G845" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684555/dpmg-penyaluran-dana-desa-di-aceh-sudah-capai-8188-persen</t>
+        </is>
+      </c>
+      <c r="H845" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG-20260608-WA0028.jpg</t>
+        </is>
+      </c>
+      <c r="I845" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B846" t="inlineStr">
+        <is>
+          <t>PPAL gelar upacara ziarah dan tabur bunga peringati HUT ke-40</t>
+        </is>
+      </c>
+      <c r="C846" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:19:41 +0700</t>
+        </is>
+      </c>
+      <c r="D846" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E846" t="inlineStr">
+        <is>
+          <t>ANTARA - Persatuan Purnawirawan Angkatan Laut (PPAL) menggelar upacara ziarah dan tabur bunga di Taman Makam Pahlawan ...</t>
+        </is>
+      </c>
+      <c r="F846" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G846" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5684307/ppal-gelar-upacara-ziarah-dan-tabur-bunga-peringati-hut-ke-40</t>
+        </is>
+      </c>
+      <c r="H846" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SANS_PPAL-GELAR-UPACARA-ZIARAH-DAN-TABUR-BUNGA-PERINGATI-HUT-KE-40.jpg</t>
+        </is>
+      </c>
+      <c r="I846" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B847" t="inlineStr">
+        <is>
+          <t>Ormas di Tanah Abang dukung deklarasi pemberantasan tramadol ilegal</t>
+        </is>
+      </c>
+      <c r="C847" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:19:17 +0700</t>
+        </is>
+      </c>
+      <c r="D847" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E847" t="inlineStr">
+        <is>
+          <t>Organisasi kemasyarakatan (ormas) di Kecamatan Tanah Abang, mendukung deklarasi pemberantasan peredaran tramadol ilegal ...</t>
+        </is>
+      </c>
+      <c r="F847" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G847" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684553/ormas-di-tanah-abang-dukung-deklarasi-pemberantasan-tramadol-ilegal</t>
+        </is>
+      </c>
+      <c r="H847" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000833694.jpg</t>
+        </is>
+      </c>
+      <c r="I847" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B848" t="inlineStr">
+        <is>
+          <t>Prabowo: Pemerintah percepat pembangunan jembatan desa</t>
+        </is>
+      </c>
+      <c r="C848" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:19:06 +0700</t>
+        </is>
+      </c>
+      <c r="D848" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E848" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menegaskan pemerintah mempercepat pembangunan jembatan rusak di berbagai desa untuk memenuhi ...</t>
+        </is>
+      </c>
+      <c r="F848" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G848" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684551/prabowo-pemerintah-percepat-pembangunan-jembatan-desa</t>
+        </is>
+      </c>
+      <c r="H848" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000401376.jpg</t>
+        </is>
+      </c>
+      <c r="I848" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B849" t="inlineStr">
+        <is>
+          <t>Indonesia mulai bangun kapal selam Scorpene pertama di dalam negeri</t>
+        </is>
+      </c>
+      <c r="C849" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:18:16 +0700</t>
+        </is>
+      </c>
+      <c r="D849" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E849" t="inlineStr">
+        <is>
+          <t>ANTARA - Indonesia resmi memulai pembangunan kapal selam Scorpene Evolved pertama yang diproduksi sepenuhnya di dalam ...</t>
+        </is>
+      </c>
+      <c r="F849" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5684259/indonesia-mulai-bangun-kapal-selam-scorpene-pertama-di-dalam-negeri</t>
+        </is>
+      </c>
+      <c r="H849" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_INDONESIA-MULAI-BANGUN-KAPAL-SELAM-SCORPENE-PERTAMA-DI-DALAM-NEGERI.jpg</t>
+        </is>
+      </c>
+      <c r="I849" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B850" t="inlineStr">
+        <is>
+          <t>CIMB Niaga-Ajaib bawa layanan perbankan dan investasi terintegrasi</t>
+        </is>
+      </c>
+      <c r="C850" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:15:39 +0700</t>
+        </is>
+      </c>
+      <c r="D850" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E850" t="inlineStr">
+        <is>
+          <t>PT Bank CIMB Niaga Tbk (CIMB Niaga) dan Ajaib Group berkolaborasi menghadirkan layanan perbankan dan investasi digital ...</t>
+        </is>
+      </c>
+      <c r="F850" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G850" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684548/cimb-niaga-ajaib-bawa-layanan-perbankan-dan-investasi-terintegrasi</t>
+        </is>
+      </c>
+      <c r="H850" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_0465.jpeg</t>
+        </is>
+      </c>
+      <c r="I850" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B851" t="inlineStr">
+        <is>
+          <t>Pemkot gerakkan ekonomi rakyat lewat peringatan HUT Ke-270 Yogyakarta</t>
+        </is>
+      </c>
+      <c r="C851" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:14:19 +0700</t>
+        </is>
+      </c>
+      <c r="D851" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E851" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota (Pemkot) Yogyakarta menggelar serangkaian kegiatan dalam peringatan Hari Ulang Tahun (HUT) Ke-270 Kota ...</t>
+        </is>
+      </c>
+      <c r="F851" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G851" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684545/pemkot-gerakkan-ekonomi-rakyat-lewat-peringatan-hut-ke-270-yogyakarta</t>
+        </is>
+      </c>
+      <c r="H851" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_20260807_164325.jpg</t>
+        </is>
+      </c>
+      <c r="I851" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B852" t="inlineStr">
+        <is>
+          <t>Legislator minta audit layanan usai kejadian pasien JKN menunggu 8 jam</t>
+        </is>
+      </c>
+      <c r="C852" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:14:17 +0700</t>
+        </is>
+      </c>
+      <c r="D852" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E852" t="inlineStr">
+        <is>
+          <t>Anggota Komisi IX DPR RI Edy Wuryanto mengatakan kejadian pasien BPJS Kesehatan, Yurizal, yang mengeluh lewat media ...</t>
+        </is>
+      </c>
+      <c r="F852" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G852" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684543/legislator-minta-audit-layanan-usai-kejadian-pasien-jkn-menunggu-8-jam</t>
+        </is>
+      </c>
+      <c r="H852" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/05/11/Anggota_Komisi_IX_DPR_RI_Edy_Wuryanto_Foto_Dok_Alma20260511121938.jpeg</t>
+        </is>
+      </c>
+      <c r="I852" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B853" t="inlineStr">
+        <is>
+          <t>Akademisi UI kembangkan bisnis baterai bekas dukung transisi energi</t>
+        </is>
+      </c>
+      <c r="C853" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:11:47 +0700</t>
+        </is>
+      </c>
+      <c r="D853" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E853" t="inlineStr">
+        <is>
+          <t>Akademisi Fakultas Teknik Universitas Indonesia (FTUI) Ellia Kristiningrum mengembangkan bisnis baterai bekas pakai ...</t>
+        </is>
+      </c>
+      <c r="F853" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G853" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684541/akademisi-ui-kembangkan-bisnis-baterai-bekas-dukung-transisi-energi</t>
+        </is>
+      </c>
+      <c r="H853" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG-20260807-WA0027.jpg</t>
+        </is>
+      </c>
+      <c r="I853" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B854" t="inlineStr">
+        <is>
+          <t>Foto udara ungkap kemacetan mengular di Jalintim Palembang-Jambi, pengendara diminta waspadai titik ini</t>
+        </is>
+      </c>
+      <c r="C854" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:08:15 +0700</t>
+        </is>
+      </c>
+      <c r="D854" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E854" t="inlineStr">
+        <is>
+          <t>Foto udara sejumlah kendaraan terjebak kemacetan di Jalan Lintas Timur (Jalintim) Palembang-Jambi di Air Batu, ...</t>
+        </is>
+      </c>
+      <c r="F854" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G854" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5684540/foto-udara-ungkap-kemacetan-mengular-di-jalintim-palembang-jambi-pengendara-diminta-waspadai-titik-ini</t>
+        </is>
+      </c>
+      <c r="H854" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Kemacetan-di-jalan-lintas-Palembang-Jambi-070826-Lmo-4.jpg</t>
+        </is>
+      </c>
+      <c r="I854" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B855" t="inlineStr">
+        <is>
+          <t>Daftar mobil hybrid yang mejeng di GIIAS 2026 dan harganya</t>
+        </is>
+      </c>
+      <c r="C855" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:08:01 +0700</t>
+        </is>
+      </c>
+      <c r="D855" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E855" t="inlineStr">
+        <is>
+          <t>Gaikindo Indonesia International Auto Show (GIIAS) 2026 yang digelar di ICE BSD, Tangerang, hingga 9 Agustus mendatang ...</t>
+        </is>
+      </c>
+      <c r="F855" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G855" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5684536/daftar-mobil-hybrid-yang-mejeng-di-giias-2026-dan-harganya</t>
+        </is>
+      </c>
+      <c r="H855" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_1961.jpeg</t>
+        </is>
+      </c>
+      <c r="I855" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B856" t="inlineStr">
+        <is>
+          <t>Objek Wisata Oro-oro Kesongo Blora kembali semburkan lumpur</t>
+        </is>
+      </c>
+      <c r="C856" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:07:53 +0700</t>
+        </is>
+      </c>
+      <c r="D856" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E856" t="inlineStr">
+        <is>
+          <t>Objek Wisata Geologi Oro-oro Kesongo di Dukuh Sucen, Desa Gabusan, Kecamatan Jati, Kabupaten Blora, Jawa Tengah, ...</t>
+        </is>
+      </c>
+      <c r="F856" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G856" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684532/objek-wisata-oro-oro-kesongo-blora-kembali-semburkan-lumpur</t>
+        </is>
+      </c>
+      <c r="H856" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/lumpur-jpg.jpg</t>
+        </is>
+      </c>
+      <c r="I856" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B857" t="inlineStr">
+        <is>
+          <t>APPBI targetkan transaksi Rp38 triliun lebih selama ISF 2026</t>
+        </is>
+      </c>
+      <c r="C857" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:06:46 +0700</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E857" t="inlineStr">
+        <is>
+          <t>Asosiasi Pengelola Pusat Belanja Indonesia (APPBI) menargetkan transaksi hingga Rp38,93 triliun ...</t>
+        </is>
+      </c>
+      <c r="F857" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G857" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684531/appbi-targetkan-transaksi-rp38-triliun-lebih-selama-isf-2026</t>
+        </is>
+      </c>
+      <c r="H857" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-17.21.22.jpeg</t>
+        </is>
+      </c>
+      <c r="I857" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B858" t="inlineStr">
+        <is>
+          <t>Menkeu Purbaya minta LPDP biayai riset lingkungan di Laut Timor</t>
+        </is>
+      </c>
+      <c r="C858" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:06:09 +0700</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E858" t="inlineStr">
+        <is>
+          <t>Menteri Keuangan Purbaya Yudhi Sadewa meminta Lembaga Pengelola Dana Pendidikan (LPDP) untuk membiayai riset lingkungan ...</t>
+        </is>
+      </c>
+      <c r="F858" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G858" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684529/menkeu-purbaya-minta-lpdp-biayai-riset-lingkungan-di-laut-timor</t>
+        </is>
+      </c>
+      <c r="H858" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-08.12.48.jpeg</t>
+        </is>
+      </c>
+      <c r="I858" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B859" t="inlineStr">
+        <is>
+          <t>PKM Unib bangun model pengelolaan sampah desa berbasis partisipatif</t>
+        </is>
+      </c>
+      <c r="C859" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:04:40 +0700</t>
+        </is>
+      </c>
+      <c r="D859" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E859" t="inlineStr">
+        <is>
+          <t>Tim Pengabdian kepada Masyarakat (PKM) Universitas Bengkulu (Unib) membangun model pengelolaan sampah desa berbasis ...</t>
+        </is>
+      </c>
+      <c r="F859" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G859" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684528/pkm-unib-bangun-model-pengelolaan-sampah-desa-berbasis-partisipatif</t>
+        </is>
+      </c>
+      <c r="H859" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000839286.jpg</t>
+        </is>
+      </c>
+      <c r="I859" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>Menag: Dana umat tak sekedar bantuan, tapi harus memberdayakan</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:04:34 +0700</t>
+        </is>
+      </c>
+      <c r="D860" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>Menteri Agama Nasaruddin Umar menegaskan dana umat tidak semestinya hanya dimanfaatkan untuk memberikan bantuan yang ...</t>
+        </is>
+      </c>
+      <c r="F860" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684524/menag-dana-umat-tak-sekedar-bantuan-tapi-harus-memberdayakan</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG-20260807-WA0003_1.jpg</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>Penelitian Polinela dukung tata kelola Program Makan Bergizi Gratis</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:04:17 +0700</t>
+        </is>
+      </c>
+      <c r="D861" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>Tim peneliti Politeknik Negeri Lampung (Polinela) mengembangkan model evaluasi keberlanjutan Program Makan Bergizi ...</t>
+        </is>
+      </c>
+      <c r="F861" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684523/penelitian-polinela-dukung-tata-kelola-program-makan-bergizi-gratis</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/0f933b73-d656-4d95-9ddc-c879d7e9ea94.jpeg</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>BI DKI ingatkan Pemprov kelola risiko penerbitan obligasi daerah</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:02:36 +0700</t>
+        </is>
+      </c>
+      <c r="D862" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>Kantor Perwakilan Bank Indonesia (BI) DKI Jakarta mengingatkan Pemerintah Provinsi (Pemprov) DKI Jakarta agar mengelola ...</t>
+        </is>
+      </c>
+      <c r="F862" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684521/bi-dki-ingatkan-pemprov-kelola-risiko-penerbitan-obligasi-daerah</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/50016df8-c542-46c1-a2d4-0b9080d9190d.jpeg</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>Kementan dan Pemerintah Aceh percepat pemulihan pertanian pascabencana</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:02:22 +0700</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>Kementerian Pertanian (Kementan) dan Pemerintah Aceh bersinergi mempercepat pemulihan sektor pertanian ...</t>
+        </is>
+      </c>
+      <c r="F863" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684517/kementan-dan-pemerintah-aceh-percepat-pemulihan-pertanian-pascabencana</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1C9FD7BA-F0FF-4096-9125-236366FA5033.jpeg</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>ngaben massal Balinuraga perkuat pelestarian budaya dan pariwisata</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:01:39 +0700</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>Pemerintah Kabupaten Lampung Selatan berkomitmen memperkuat pelestarian budaya sekaligus mengembangkan sektor ...</t>
+        </is>
+      </c>
+      <c r="F864" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684513/ngaben-massal-balinuraga-perkuat-pelestarian-budaya-dan-pariwisata</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_1660.jpeg</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>Peluncuran sepuluh buku karya nyata untuk negeri Bahlil Lahadalia</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:00:48 +0700</t>
+        </is>
+      </c>
+      <c r="D865" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto (kanan) bersama Menteri ESDM Bahlil Lahadalia (kiri) meluncurkan 10 buku karya nyata untuk ...</t>
+        </is>
+      </c>
+      <c r="F865" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5684511/peluncuran-sepuluh-buku-karya-nyata-untuk-negeri-bahlil-lahadalia</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Peluncuran-10-buku-karya-nyata-untuk-negeri-Bahlil-Lahadalia-070826-Ada-1.jpg</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>160 ribu sambungan baru jaringan gas 2026</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D866" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>Pemerintah menargetkan pembangunan 160 ribu sambungan rumah (SR) jaringan gas bumi (jargas) di berbagai daerah di ...</t>
+        </is>
+      </c>
+      <c r="F866" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/infografik/5684504/160-ribu-sambungan-baru-jaringan-gas-2026</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/20260807-160-ribu-sambungan-baru-jaringan-gas-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>Kemenpar: FBLB ke-34 masuk top Karisama Event Nusantara 2026</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:59:24 +0700</t>
+        </is>
+      </c>
+      <c r="D867" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>Kementerian Pariwisata (Kemenpar) RI menyatakan Festival Budaya Lembah Baliem atau FBLB ke-34 masuk top Karisma Event ...</t>
+        </is>
+      </c>
+      <c r="F867" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684509/kemenpar-fblb-ke-34-masuk-top-karisama-event-nusantara-2026</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-15.18.40.jpeg</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>Prabowo: Perjalanan hidup Bahlil bisa jadi inspirasi generasi muda</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:58:42 +0700</t>
+        </is>
+      </c>
+      <c r="D868" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menilai perjalanan hidup Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia dapat ...</t>
+        </is>
+      </c>
+      <c r="F868" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684508/prabowo-perjalanan-hidup-bahlil-bisa-jadi-inspirasi-generasi-muda</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_0992.jpeg</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>Wamen Dikdasmen dorong transformasi digital sektor pendidikan</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:55:29 +0700</t>
+        </is>
+      </c>
+      <c r="D869" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Pendidikan Dasar dan Menengah (Dikdasmen) Republik Indonesia Fajar Riza Ul Haq mendorong transformasi ...</t>
+        </is>
+      </c>
+      <c r="F869" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684503/wamen-dikdasmen-dorong-transformasi-digital-sektor-pendidikan</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/566899.jpg</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B870" t="inlineStr">
+        <is>
+          <t>Jakpus deklarasikan pemberantasan peredaran tramadol ilegal</t>
+        </is>
+      </c>
+      <c r="C870" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:54:58 +0700</t>
+        </is>
+      </c>
+      <c r="D870" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E870" t="inlineStr">
+        <is>
+          <t>Forum Koordinasi Pimpinan Kota (Forkopimko) Jakarta Pusat dan masyarakat mendeklarasikan komitmen memberantas peredaran ...</t>
+        </is>
+      </c>
+      <c r="F870" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G870" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684501/jakpus-deklarasikan-pemberantasan-peredaran-tramadol-ilegal</t>
+        </is>
+      </c>
+      <c r="H870" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000833726.jpg</t>
+        </is>
+      </c>
+      <c r="I870" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B871" t="inlineStr">
+        <is>
+          <t>Suno tambahkan "watermark" pada lagu buatan AI mudah dikenali</t>
+        </is>
+      </c>
+      <c r="C871" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:54:29 +0700</t>
+        </is>
+      </c>
+      <c r="D871" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E871" t="inlineStr">
+        <is>
+          <t>Layanan AI pembuat musik, Suno, mengumumkan bahwa pihaknya bakal mulai memberikan watermark pada lagu-lagu yang dibuat ...</t>
+        </is>
+      </c>
+      <c r="F871" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G871" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684500/suno-tambahkan-watermark-pada-lagu-buatan-ai-mudah-dikenali</t>
+        </is>
+      </c>
+      <c r="H871" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG-20260807-WA0255.jpg</t>
+        </is>
+      </c>
+      <c r="I871" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B872" t="inlineStr">
+        <is>
+          <t>Tim golf Indonesia jalani pelatnas desentralisasi untuk Asian Games</t>
+        </is>
+      </c>
+      <c r="C872" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:53:40 +0700</t>
+        </is>
+      </c>
+      <c r="D872" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E872" t="inlineStr">
+        <is>
+          <t>Tim golf Indonesia menjalani pemusatan latihan nasional (pelatnas) secara desentralisasi sebagai bagian dari persiapan ...</t>
+        </is>
+      </c>
+      <c r="F872" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G872" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684497/tim-golf-indonesia-jalani-pelatnas-desentralisasi-untuk-asian-games</t>
+        </is>
+      </c>
+      <c r="H872" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/05/13/antarafoto-golf-beregu-putra-gagal-ke-final-120523-adm-11.jpg</t>
+        </is>
+      </c>
+      <c r="I872" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B873" t="inlineStr">
+        <is>
+          <t>Bappenas: Pembangunan hunian vertikal dukung transportasi massal</t>
+        </is>
+      </c>
+      <c r="C873" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:52:52 +0700</t>
+        </is>
+      </c>
+      <c r="D873" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E873" t="inlineStr">
+        <is>
+          <t>Menteri Perencanaan Pembangunan Nasional/Kepala Badan Perencanaan Pembangunan Nasional (PPN/Bappenas) Rachmat Pambudy ...</t>
+        </is>
+      </c>
+      <c r="F873" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G873" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684495/bappenas-pembangunan-hunian-vertikal-dukung-transportasi-massal</t>
+        </is>
+      </c>
+      <c r="H873" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/RP-PKP.jpeg</t>
+        </is>
+      </c>
+      <c r="I873" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B874" t="inlineStr">
+        <is>
+          <t>OJK: Piutang multifinance akhir 2026 tetap positif meski bias ke bawah</t>
+        </is>
+      </c>
+      <c r="C874" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:52:18 +0700</t>
+        </is>
+      </c>
+      <c r="D874" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E874" t="inlineStr">
+        <is>
+          <t>Otoritas Jasa Keuangan (OJK) meyakini piutang pembiayaan oleh perusahaan pembiayaan atau multifinance oleh pada akhir ...</t>
+        </is>
+      </c>
+      <c r="F874" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G874" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684493/ojk-piutang-multifinance-akhir-2026-tetap-positif-meski-bias-ke-bawah</t>
+        </is>
+      </c>
+      <c r="H874" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/07/WhatsApp-Image-2026-03-03-at-18.40.25.jpeg</t>
+        </is>
+      </c>
+      <c r="I874" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B875" t="inlineStr">
+        <is>
+          <t>Masjid Istiqlal luncurkan program Jumat Berkah, sediakan makan gratis</t>
+        </is>
+      </c>
+      <c r="C875" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:51:40 +0700</t>
+        </is>
+      </c>
+      <c r="D875" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E875" t="inlineStr">
+        <is>
+          <t>Badan Pengelola Masjid Istiqlal Jakarta meluncurkan program "Jumat Berkah" yang mencakup penyediaan makan ...</t>
+        </is>
+      </c>
+      <c r="F875" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G875" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684492/masjid-istiqlal-luncurkan-program-jumat-berkah-sediakan-makan-gratis</t>
+        </is>
+      </c>
+      <c r="H875" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG-20260807-WA0001_1.jpg</t>
+        </is>
+      </c>
+      <c r="I875" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B876" t="inlineStr">
+        <is>
+          <t>Bupati Karawang pimpin penertiban puluhan bangunan liar di akses tol</t>
+        </is>
+      </c>
+      <c r="C876" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:50:52 +0700</t>
+        </is>
+      </c>
+      <c r="D876" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E876" t="inlineStr">
+        <is>
+          <t>Bupati Karawang Aep Syaepuloh memimpin langsung penertiban puluhan bangunan liar di sepanjang jalan akses Tol Karawang ...</t>
+        </is>
+      </c>
+      <c r="F876" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G876" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684489/bupati-karawang-pimpin-penertiban-puluhan-bangunan-liar-di-akses-tol</t>
+        </is>
+      </c>
+      <c r="H876" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_20260807_174438.jpg</t>
+        </is>
+      </c>
+      <c r="I876" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B877" t="inlineStr">
+        <is>
+          <t>BPK ingatkan WTP langkah awal penguatan tata kelola yang transparan</t>
+        </is>
+      </c>
+      <c r="C877" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:49:36 +0700</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E877" t="inlineStr">
+        <is>
+          <t>Badan Pemeriksa Keuangan (BPK) mengingatkan capaian kementerian/lembaga (K/L) meraih opini wajar tanpa pengecualian ...</t>
+        </is>
+      </c>
+      <c r="F877" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G877" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684487/bpk-ingatkan-wtp-langkah-awal-penguatan-tata-kelola-yang-transparan</t>
+        </is>
+      </c>
+      <c r="H877" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/25/WhatsApp-Image-2026-02-21-at-15.04.31.jpeg</t>
+        </is>
+      </c>
+      <c r="I877" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B878" t="inlineStr">
+        <is>
+          <t>Imigrasi hadirkan layanan pembuatan paspor di Pulau Panggang</t>
+        </is>
+      </c>
+      <c r="C878" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:48:57 +0700</t>
+        </is>
+      </c>
+      <c r="D878" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E878" t="inlineStr">
+        <is>
+          <t>Kantor Imigrasi Kelas I TPI Tanjung Priok menghadirkan layanan keimigrasian kepada masyarakat di Pulau Panggang, ...</t>
+        </is>
+      </c>
+      <c r="F878" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G878" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684483/imigrasi-hadirkan-layanan-pembuatan-paspor-di-pulau-panggang</t>
+        </is>
+      </c>
+      <c r="H878" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_4391.jpeg</t>
+        </is>
+      </c>
+      <c r="I878" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B879" t="inlineStr">
+        <is>
+          <t>OJK Sumut terima 1.878 pengaduan dari konsumen hingga Juni 2026</t>
+        </is>
+      </c>
+      <c r="C879" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:48:21 +0700</t>
+        </is>
+      </c>
+      <c r="D879" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E879" t="inlineStr">
+        <is>
+          <t>Otoritas Jasa Keuangan (OJK) Provinsi Sumatera Utara menerima sebanyak 1.878 pengaduan dari konsumen di provinsi ...</t>
+        </is>
+      </c>
+      <c r="F879" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G879" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684481/ojk-sumut-terima-1878-pengaduan-dari-konsumen-hingga-juni-2026</t>
+        </is>
+      </c>
+      <c r="H879" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG-20260807-WA0100.jpg</t>
+        </is>
+      </c>
+      <c r="I879" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B880" t="inlineStr">
+        <is>
+          <t>Konsul RI: PNG pindahkan ABK dan kapal ke Port Moresby</t>
+        </is>
+      </c>
+      <c r="C880" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:47:48 +0700</t>
+        </is>
+      </c>
+      <c r="D880" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E880" t="inlineStr">
+        <is>
+          <t>Konsul RI di Vanimo Alexander Tangkuman mengatakan otoritas Papua Nugini (PNG) telah memindahkan anak buah kapal (ABK) ...</t>
+        </is>
+      </c>
+      <c r="F880" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G880" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684480/konsul-ri-png-pindahkan-abk-dan-kapal-ke-port-moresby</t>
+        </is>
+      </c>
+      <c r="H880" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1002602625.jpg</t>
+        </is>
+      </c>
+      <c r="I880" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B881" t="inlineStr">
+        <is>
+          <t>Wamendagri: Pemkab Jayapura bergerak cepat tangani keracunan makanan</t>
+        </is>
+      </c>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:46:24 +0700</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Dalam Negeri (Wamendagri) Ribka Haluk mengapresiasi peran aktif masyarakat dan langkah cepat Pemerintah ...</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G881" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684479/wamendagri-pemkab-jayapura-bergerak-cepat-tangani-keracunan-makanan</t>
+        </is>
+      </c>
+      <c r="H881" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000582107.jpg</t>
+        </is>
+      </c>
+      <c r="I881" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B882" t="inlineStr">
+        <is>
+          <t>Kemendag dorong festival belanja terintegrasi dengan pariwisata</t>
+        </is>
+      </c>
+      <c r="C882" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D882" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E882" t="inlineStr">
+        <is>
+          <t>Direktur Jenderal Perdagangan Dalam Negeri Kementerian Perdagangan (Kemendag) Iqbal Shoffan Shofwan mengatakan ...</t>
+        </is>
+      </c>
+      <c r="F882" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G882" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684476/kemendag-dorong-festival-belanja-terintegrasi-dengan-pariwisata</t>
+        </is>
+      </c>
+      <c r="H882" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000593011.jpg</t>
+        </is>
+      </c>
+      <c r="I882" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B883" t="inlineStr">
+        <is>
+          <t>Lintasarta Dorong Transformasi Digital BPD Lewat Intelligent Core</t>
+        </is>
+      </c>
+      <c r="C883" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:30:49 +0700</t>
+        </is>
+      </c>
+      <c r="D883" t="inlineStr">
+        <is>
+          <t>Hana Nushratu Uzma</t>
+        </is>
+      </c>
+      <c r="E883" t="inlineStr">
+        <is>
+          <t>Lintasarta luncurkan Intelligent Core untuk BPD, mengintegrasikan 4C: Connectivity, Cloud, Cybersecurity, dan Collaboration-AI.</t>
+        </is>
+      </c>
+      <c r="F883" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G883" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608974/lintasarta-dorong-transformasi-digital-bpd-lewat-intelligent-core</t>
+        </is>
+      </c>
+      <c r="H883" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/24/lintasarta-perkuat-transformasi-digital-bpd-untuk-dukung-ekonomi-nasional-1784863989503_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I883" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B884" t="inlineStr">
+        <is>
+          <t>950 SPPG Diduga Tak Layak Sanitasi dan Higiene, Terancam Ditutup Permanen</t>
+        </is>
+      </c>
+      <c r="C884" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:23:56 +0700</t>
+        </is>
+      </c>
+      <c r="D884" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E884" t="inlineStr">
+        <is>
+          <t>BGN mengungkap ada 950 dapur MBG yang diduga tidak layak higiene dan sanitasi. Dapur-dapur tersebut terancam ditutup secara permanen.</t>
+        </is>
+      </c>
+      <c r="F884" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G884" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608969/950-sppg-diduga-tak-layak-sanitasi-dan-higiene-terancam-ditutup-permanen</t>
+        </is>
+      </c>
+      <c r="H884" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kepala-bgn-sudaryono-brigittadetikcom-1786101809094_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I884" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B885" t="inlineStr">
+        <is>
+          <t>Sosok Saepul Pemutilasi Pria di Depok, Pernah Ikut Ajang Pencarian Bakat</t>
+        </is>
+      </c>
+      <c r="C885" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:17:25 +0700</t>
+        </is>
+      </c>
+      <c r="D885" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E885" t="inlineStr">
+        <is>
+          <t>Rekaman video Saepul, pelaku mutilasi pria K, viral saat ikut ajang bakat untuk membantu ibunya. Kasusnya masih dalam penyelidikan.</t>
+        </is>
+      </c>
+      <c r="F885" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G885" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608962/sosok-saepul-pemutilasi-pria-di-depok-pernah-ikut-ajang-pencarian-bakat</t>
+        </is>
+      </c>
+      <c r="H885" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/05/saepul-pelaku-pembunuhan-dan-mutilasi-pria-di-pancoran-mas-depok-ditangkap-subdit-resmob-polda-metro-jaya-1785915706525_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I885" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B886" t="inlineStr">
+        <is>
+          <t>Air Sumur Warga di Bogor Mendadak Keruh, Ternyata Kemasukan 2 Biawak</t>
+        </is>
+      </c>
+      <c r="C886" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:15:37 +0700</t>
+        </is>
+      </c>
+      <c r="D886" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E886" t="inlineStr">
+        <is>
+          <t>Warga di Desa Cibinong, Kecamatan Gunung Sindur, Bogor, Jawa Barat, kaget melihat air sumur yang keruh. Ternyata ada biawak di dalam sumurnya.</t>
+        </is>
+      </c>
+      <c r="F886" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G886" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608946/air-sumur-warga-di-bogor-mendadak-keruh-ternyata-kemasukan-2-biawak</t>
+        </is>
+      </c>
+      <c r="H886" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/biawak-dok-ist-1786101305861_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I886" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B887" t="inlineStr">
+        <is>
+          <t>Prabowo Sebut Ben Mboi hingga Cak Noer Mentor Kepemimpinannya</t>
+        </is>
+      </c>
+      <c r="C887" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:14:30 +0700</t>
+        </is>
+      </c>
+      <c r="D887" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E887" t="inlineStr">
+        <is>
+          <t>Prabowo Subianto mengungkapkan Ben Mboi dan Cak Noer sebagai mentor kepemimpinannya, menekankan cinta rakyat dan akal sehat dalam kebijakan.</t>
+        </is>
+      </c>
+      <c r="F887" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G887" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608944/prabowo-sebut-ben-mboi-hingga-cak-noer-mentor-kepemimpinannya</t>
+        </is>
+      </c>
+      <c r="H887" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/presiden-prabowo-subianto-1786098762245_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I887" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B888" t="inlineStr">
+        <is>
+          <t>Kapolri Siap Kawal Perjuangan Buruh, Titip Pesan Tetap Jaga Ketertiban</t>
+        </is>
+      </c>
+      <c r="C888" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:11:53 +0700</t>
+        </is>
+      </c>
+      <c r="D888" t="inlineStr">
+        <is>
+          <t>Adrial akbar</t>
+        </is>
+      </c>
+      <c r="E888" t="inlineStr">
+        <is>
+          <t>Kapolri Jenderal Listyo Sigit Prabowo berdialog dengan Koalisi Besar Perjuangan Buruh Indonesia, berkomitmen mengawal perjuangan buruh.</t>
+        </is>
+      </c>
+      <c r="F888" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G888" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608943/kapolri-siap-kawal-perjuangan-buruh-titip-pesan-tetap-jaga-ketertiban</t>
+        </is>
+      </c>
+      <c r="H888" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kapolri-jenderal-listyo-sigit-prabowo-berdialog-dengan-koalisi-besar-perjuangan-buruh-indonesia-kbpbi-1786101048249_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I888" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B889" t="inlineStr">
+        <is>
+          <t>Polri Kunjungi Universitas Palangka Raya, Bahas Pusat Studi Kepolisian</t>
+        </is>
+      </c>
+      <c r="C889" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:08:02 +0700</t>
+        </is>
+      </c>
+      <c r="D889" t="inlineStr">
+        <is>
+          <t>Audrey Santoso</t>
+        </is>
+      </c>
+      <c r="E889" t="inlineStr">
+        <is>
+          <t>Polri operasionalkan Pusat Studi Kepolisian di Universitas Palangka Raya. Ini jadi ruang kolaborasi riset dan inovasi untuk meningkatkan pelayanan kepolisian.</t>
+        </is>
+      </c>
+      <c r="F889" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G889" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608938/polri-kunjungi-universitas-palangka-raya-bahas-pusat-studi-kepolisian</t>
+        </is>
+      </c>
+      <c r="H889" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/polri-kunjungi-universitas-palangka-raya-1786100854269_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I889" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B890" t="inlineStr">
+        <is>
+          <t>Polda Metro Pastikan Agustus Aman, Minta Masyarakat Tak Khawatir</t>
+        </is>
+      </c>
+      <c r="C890" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:06:36 +0700</t>
+        </is>
+      </c>
+      <c r="D890" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E890" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya memastikan keamanan dan ketertiban di tengah isu demo Agustus 2026. Polri siap memberikan rasa aman dan nyaman untuk masyarakat.</t>
+        </is>
+      </c>
+      <c r="F890" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G890" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608936/polda-metro-pastikan-agustus-aman-minta-masyarakat-tak-khawatir</t>
+        </is>
+      </c>
+      <c r="H890" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/konferensi-pers-penanganan-kasus-siber-hingga-kriminalitas-di-polda-metro-jaya-1786096229886_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I890" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B891" t="inlineStr">
+        <is>
+          <t>Bripda Putra Ciptakan Pupuk Ramah Lingkungan, Wakapolri: Harus Diberi Ruang Berkembang</t>
+        </is>
+      </c>
+      <c r="C891" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:04:52 +0700</t>
+        </is>
+      </c>
+      <c r="D891" t="inlineStr">
+        <is>
+          <t>Audrey Santoso</t>
+        </is>
+      </c>
+      <c r="E891" t="inlineStr">
+        <is>
+          <t>Wakapolri Dedi Prasetyo mengapresiasi Bripda Putra dari Polda Riau yang inovatif dalam ketahanan pangan dan green policing dengan pupuk ramah lingkungan.</t>
+        </is>
+      </c>
+      <c r="F891" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G891" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608933/bripda-putra-ciptakan-pupuk-ramah-lingkungan-wakapolri-harus-diberi-ruang-berkembang</t>
+        </is>
+      </c>
+      <c r="H891" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/bripda-putra-ciptakan-pupuk-ramah-lingkungan-1786100660102_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I891" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B892" t="inlineStr">
+        <is>
+          <t>Polda Metro Ungkap 4 Modus Penyebar Provokasi dan Hoaks di Medsos</t>
+        </is>
+      </c>
+      <c r="C892" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:59:02 +0700</t>
+        </is>
+      </c>
+      <c r="D892" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E892" t="inlineStr">
+        <is>
+          <t>Sejumlah orang ditetapkan sebagai tersangka penyebaran konten provokasi hingga hoaks di medsos. Polisi mengungkap 4 modus operandi para pelaku. Apa saja?</t>
+        </is>
+      </c>
+      <c r="F892" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G892" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608923/polda-metro-ungkap-4-modus-penyebar-provokasi-dan-hoaks-di-medsos</t>
+        </is>
+      </c>
+      <c r="H892" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/konferensi-pers-penanganan-kasus-siber-hingga-kriminalitas-di-polda-metro-jaya-1786096229886_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I892" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B893" t="inlineStr">
+        <is>
+          <t>Maling di Bogor Ditangkap Usai Pemilik Rumah Dapat Notifikasi dari CCTV</t>
+        </is>
+      </c>
+      <c r="C893" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:56:53 +0700</t>
+        </is>
+      </c>
+      <c r="D893" t="inlineStr">
+        <is>
+          <t>Rizky Adha Mahendra</t>
+        </is>
+      </c>
+      <c r="E893" t="inlineStr">
+        <is>
+          <t>Polisi menangkap pria berinisial E karena melakukan pencurian di salah satu rumah kontrakan di Desa Cicadas.</t>
+        </is>
+      </c>
+      <c r="F893" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G893" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608920/maling-di-bogor-ditangkap-usai-pemilik-rumah-dapat-notifikasi-dari-cctv</t>
+        </is>
+      </c>
+      <c r="H893" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/08/28/ilustrasi-pencuri-ilustrasi-maling-ilustrasi-kriminal-freepik_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I893" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B894" t="inlineStr">
+        <is>
+          <t>Kapolri Dialog dengan Pimpinan Buruh, Ini yang Dibahas</t>
+        </is>
+      </c>
+      <c r="C894" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:48:09 +0700</t>
+        </is>
+      </c>
+      <c r="D894" t="inlineStr">
+        <is>
+          <t>Adrial akbar</t>
+        </is>
+      </c>
+      <c r="E894" t="inlineStr">
+        <is>
+          <t>Kapolri Jenderal Listyo Sigit Prabowo berdialog dengan Koalisi Besar Perjuangan Buruh Indonesia, membahas isu-isu buruh dan revisi UU Ketenagakerjaan.</t>
+        </is>
+      </c>
+      <c r="F894" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G894" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608911/kapolri-dialog-dengan-pimpinan-buruh-ini-yang-dibahas</t>
+        </is>
+      </c>
+      <c r="H894" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kapolri-jenderal-listyo-sigit-prabowo-berdialog-dengan-bos-bos-buruh-dalam-koalisi-besar-perjuangan-buruh-indonesia-kbpbi-1786099593774_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I894" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B895" t="inlineStr">
+        <is>
+          <t>Resmi! Pendaftaran Upacara HUT RI di Istana Diperpanjang Sampai 9 Agustus</t>
+        </is>
+      </c>
+      <c r="C895" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:47:10 +0700</t>
+        </is>
+      </c>
+      <c r="D895" t="inlineStr">
+        <is>
+          <t>Kanya Anindita Mutiarasari</t>
+        </is>
+      </c>
+      <c r="E895" t="inlineStr">
+        <is>
+          <t>Pendaftaran upacara HUT ke-81 RI diperpanjang hingga 9 Agustus 2026. Masyarakat dapat mendaftar online melalui laman Pandang Istana Presiden.</t>
+        </is>
+      </c>
+      <c r="F895" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G895" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608910/resmi-pendaftaran-upacara-hut-ri-di-istana-diperpanjang-sampai-9-agustus</t>
+        </is>
+      </c>
+      <c r="H895" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/08/03/link-daftar-upacara-17-agustus-2023-di-istana-negara-cek-di-sini_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I895" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B896" t="inlineStr">
+        <is>
+          <t>Canda Prabowo: Bahlil Bisa Bikin Jokowi Ketawa, Orang Solo Itu Susah Ketawa</t>
+        </is>
+      </c>
+      <c r="C896" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:42:04 +0700</t>
+        </is>
+      </c>
+      <c r="D896" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E896" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo bercanda tentang karakter Bahlil yang bisa membuat orang ketawa, termasuk Jokowi.</t>
+        </is>
+      </c>
+      <c r="F896" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G896" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608897/canda-prabowo-bahlil-bisa-bikin-jokowi-ketawa-orang-solo-itu-susah-ketawa</t>
+        </is>
+      </c>
+      <c r="H896" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/presiden-prabowo-subianto-1786098762245_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I896" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B897" t="inlineStr">
+        <is>
+          <t>Kunjungi Sekolah Rakyat Sulsel, Gus Ipul Disambut Aksi Paper Mob</t>
+        </is>
+      </c>
+      <c r="C897" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:41:35 +0700</t>
+        </is>
+      </c>
+      <c r="D897" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E897" t="inlineStr">
+        <is>
+          <t>Ratusan siswa sambut Menteri Sosial Gus Ipul di Makassar dengan atraksi Paper Mob. Mereka menunjukkan bakat dan percaya diri yang berkembang di Sekolah Rakyat.</t>
+        </is>
+      </c>
+      <c r="F897" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G897" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608895/kunjungi-sekolah-rakyat-sulsel-gus-ipul-disambut-aksi-paper-mob</t>
+        </is>
+      </c>
+      <c r="H897" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kemensos-1786099264831_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I897" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B898" t="inlineStr">
+        <is>
+          <t>Lintasarta Gandeng ASBANDA Perkuat Transformasi Digital Bank Daerah</t>
+        </is>
+      </c>
+      <c r="C898" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:40:52 +0700</t>
+        </is>
+      </c>
+      <c r="D898" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E898" t="inlineStr">
+        <is>
+          <t>Lintasarta dan ASBANDA tandatangani MoU di BPD Summit 2026 untuk dukung transformasi digital bank daerah. Fokus pada AI dan penguatan SDM.</t>
+        </is>
+      </c>
+      <c r="F898" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G898" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608864/lintasarta-gandeng-asbanda-perkuat-transformasi-digital-bank-daerah</t>
+        </is>
+      </c>
+      <c r="H898" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/lintasarta-cxo-bpd-summit-2026-1786016739700.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I898" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B899" t="inlineStr">
+        <is>
+          <t>Waka MPR Dorong Revisi UU TPPO untuk Tangani Perbudakan Modern</t>
+        </is>
+      </c>
+      <c r="C899" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:40:15 +0700</t>
+        </is>
+      </c>
+      <c r="D899" t="inlineStr">
+        <is>
+          <t>Alfi Kholisdinuka</t>
+        </is>
+      </c>
+      <c r="E899" t="inlineStr">
+        <is>
+          <t>Wakil Ketua MPR Lestari Moerdijat dorong revisi UU TPPO untuk tangani kejahatan modern. Data menunjukkan korban dari kalangan terdidik, perlu perlindungan lebih</t>
+        </is>
+      </c>
+      <c r="F899" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G899" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608890/waka-mpr-dorong-revisi-uu-tppo-untuk-tangani-perbudakan-modern</t>
+        </is>
+      </c>
+      <c r="H899" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/03/07/wakil-ketua-mpr-ri-lestari-moerdijat-1741358117025.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I899" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B900" t="inlineStr">
+        <is>
+          <t>Video Lama Demo Diviralkan Lagi, Polda Metro Peringatkan Setop Sebar Hoaks</t>
+        </is>
+      </c>
+      <c r="C900" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:38:20 +0700</t>
+        </is>
+      </c>
+      <c r="D900" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E900" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya merespons fenomena konten video lama terkait demo yang sempat diviralkan lagi di media sosial. Polisi meminta menghentikan menyebar hoaks.</t>
+        </is>
+      </c>
+      <c r="F900" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G900" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608889/video-lama-demo-diviralkan-lagi-polda-metro-peringatkan-setop-sebar-hoaks</t>
+        </is>
+      </c>
+      <c r="H900" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/dirkrimum-polda-metro-jaya-kombes-iman-imanuddin-1786096322096_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I900" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B901" t="inlineStr">
+        <is>
+          <t>Ini Kera 'Codet' yang Serang Belasan Warga Inhil, Ganas dan Bertaring</t>
+        </is>
+      </c>
+      <c r="C901" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:33:52 +0700</t>
+        </is>
+      </c>
+      <c r="D901" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E901" t="inlineStr">
+        <is>
+          <t>Kera ekor panjang yang menyerang 17 warga di Inhil bisa ditangkap setelah dijebak. Kapolres mengimbau masyarakat untuk tetap waspada pasca-penangkapan.</t>
+        </is>
+      </c>
+      <c r="F901" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G901" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608888/ini-kera-codet-yang-serang-belasan-warga-inhil-ganas-dan-bertaring</t>
+        </is>
+      </c>
+      <c r="H901" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kera-ekor-panjang-yang-diduga-pelaku-penyerangan-terhadap-belasan-warga-di-tembilahan-inhil-diamankan-setelah-masuk-jebakan-1786098478708_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I901" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B902" t="inlineStr">
+        <is>
+          <t>Bahtra Peduli Beri Bantuan Beras ke 3 Ponpes Tahfiz Al-Qur'an di Kolaka</t>
+        </is>
+      </c>
+      <c r="C902" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:33:48 +0700</t>
+        </is>
+      </c>
+      <c r="D902" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E902" t="inlineStr">
+        <is>
+          <t>Anggota DPR Bahtra Banong salurkan bantuan beras ke tiga pondok pesantren di Kolaka. Ia harap dukungan ini bantu santri fokus menghafal Al-Qur'an.</t>
+        </is>
+      </c>
+      <c r="F902" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G902" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608887/bahtra-peduli-beri-bantuan-beras-ke-3-ponpes-tahfiz-al-quran-di-kolaka</t>
+        </is>
+      </c>
+      <c r="H902" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/bahtra-peduli-1786098800820_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I902" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B903" t="inlineStr">
+        <is>
+          <t>Polda Metro Tindak 28 Pegiat Medsos Terkait Provokasi-Hoax, 10 Diproses Hukum</t>
+        </is>
+      </c>
+      <c r="C903" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:30:17 +0700</t>
+        </is>
+      </c>
+      <c r="D903" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E903" t="inlineStr">
+        <is>
+          <t>Dalam 3 bulan, polisi mendalami dugaan penyebaran konten-konten provokasi hingga hoax dari sejumlah pegiat medsos. Sepuluh orang diproses hukum.</t>
+        </is>
+      </c>
+      <c r="F903" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G903" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608880/polda-metro-tindak-28-pegiat-medsos-terkait-provokasi-hoax-10-diproses-hukum</t>
+        </is>
+      </c>
+      <c r="H903" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/konferensi-pers-penanganan-kasus-siber-hingga-kriminalitas-di-polda-metro-jaya-1786096229797_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I903" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B904" t="inlineStr">
+        <is>
+          <t>Menkop Bawa Semangat Koperasi ke Festival Lembah Baliem Wamena</t>
+        </is>
+      </c>
+      <c r="C904" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:29:30 +0700</t>
+        </is>
+      </c>
+      <c r="D904" t="inlineStr">
+        <is>
+          <t>Hana Nushratu Uzma</t>
+        </is>
+      </c>
+      <c r="E904" t="inlineStr">
+        <is>
+          <t>Menkop Ferry Juliantono menekankan peran koperasi meningkatkan kesejahteraan masyarakat Papua. Festival Budaya Lembah Baliem jadi ajang promosi produk lokal.</t>
+        </is>
+      </c>
+      <c r="F904" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G904" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608878/menkop-bawa-semangat-koperasi-ke-festival-lembah-baliem-wamena</t>
+        </is>
+      </c>
+      <c r="H904" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kemenkop-1786098532810.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I904" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B905" t="inlineStr">
+        <is>
+          <t>Prabowo Kasih Rapor 'Memuaskan' ke Bahlil Saat Hadiri Acara Peluncuran Buku</t>
+        </is>
+      </c>
+      <c r="C905" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:17:08 +0700</t>
+        </is>
+      </c>
+      <c r="D905" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E905" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto memberikan rapor 'memuaskan' kepada Menteri ESDM Bahlil Lahadalia. Dia memuji pengalaman dan dedikasi Bahlil kepada bangsa.</t>
+        </is>
+      </c>
+      <c r="F905" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G905" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608851/prabowo-kasih-rapor-memuaskan-ke-bahlil-saat-hadiri-acara-peluncuran-buku</t>
+        </is>
+      </c>
+      <c r="H905" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/prabowo-hadiri-peluncuran-buku-berjudul-10-karya-nyata-untuk-negeri-setengah-abad-bahlil-lahadalia-evadetik-1786097755145_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I905" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B906" t="inlineStr">
+        <is>
+          <t>Lintasarta Dorong Kedaulatan Digital Bank Daerah Lewat BPD Summit 2026</t>
+        </is>
+      </c>
+      <c r="C906" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:10:45 +0700</t>
+        </is>
+      </c>
+      <c r="D906" t="inlineStr">
+        <is>
+          <t>Hana Nushratu Uzma</t>
+        </is>
+      </c>
+      <c r="E906" t="inlineStr">
+        <is>
+          <t>Lintasarta percepat transformasi digital BPD di RI melalui Lintasarta Intelligent Core. Fokus pada keamanan siber, AI, dan kolaborasi untuk pertumbuhan ekonomi.</t>
+        </is>
+      </c>
+      <c r="F906" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G906" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608841/lintasarta-dorong-kedaulatan-digital-bank-daerah-lewat-bpd-summit-2026</t>
+        </is>
+      </c>
+      <c r="H906" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/lintasarta-1786097425626_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I906" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B907" t="inlineStr">
+        <is>
+          <t>Pulihkan 15 Ribu Hektare Tambak di Aceh, Bantuan Perikanan Mulai Disalurkan</t>
+        </is>
+      </c>
+      <c r="C907" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:55:42 +0700</t>
+        </is>
+      </c>
+      <c r="D907" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E907" t="inlineStr">
+        <is>
+          <t>Satgas PRR salurkan bantuan sektor kelautan di Aceh untuk pemulihan ekonomi masyarakat terdampak bencana. Bantuan meliputi peralatan dan dukungan produksi.</t>
+        </is>
+      </c>
+      <c r="F907" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G907" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608813/pulihkan-15-ribu-hektare-tambak-di-aceh-bantuan-perikanan-mulai-disalurkan</t>
+        </is>
+      </c>
+      <c r="H907" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/satgas-prr-salurkan-bantuan-perikanan-kkp-ke-warga-terdampak-aceh-1786096496499.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I907" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B908" t="inlineStr">
+        <is>
+          <t>Kebakaran Bromo Mulai Menjalar ke Wisata Puncak B29</t>
+        </is>
+      </c>
+      <c r="C908" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:51:24 +0700</t>
+        </is>
+      </c>
+      <c r="D908" t="inlineStr">
+        <is>
+          <t>Nur Hadi Wicaksono</t>
+        </is>
+      </c>
+      <c r="E908" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan di Taman Nasional Bromo mendekati Puncak B29. Petugas gabungan dan helikopter dikerahkan untuk mencegah api menjalar ke kawasan wisata.</t>
+        </is>
+      </c>
+      <c r="F908" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G908" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608807/kebakaran-bromo-mulai-menjalar-ke-wisata-puncak-b29</t>
+        </is>
+      </c>
+      <c r="H908" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/helikopter-water-bombing-mengambil-air-di-ranupani-untuk-memadamkan-kebakaran-bromo-1786093774126_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I908" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B909" t="inlineStr">
+        <is>
+          <t>Eks Napi Luncurkan Sepatu Merek 'Arprize', Berbekal Keterampilan Saat Masa Pidana</t>
+        </is>
+      </c>
+      <c r="C909" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:50:18 +0700</t>
+        </is>
+      </c>
+      <c r="D909" t="inlineStr">
+        <is>
+          <t>Audrey Santoso</t>
+        </is>
+      </c>
+      <c r="E909" t="inlineStr">
+        <is>
+          <t>Bakti Kurniawan, mantan napi, membangun merek sepatu lokal Arprize. Ia berfokus pada produk berkualitas dan berharap memberi kesempatan kerja.</t>
+        </is>
+      </c>
+      <c r="F909" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G909" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608803/eks-napi-luncurkan-sepatu-merek-arprize-berbekal-keterampilan-saat-masa-pidana</t>
+        </is>
+      </c>
+      <c r="H909" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/eks-napi-luncurkan-sepatu-merk-arprize-1786096198690_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I909" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B910" t="inlineStr">
+        <is>
+          <t>Gus Ipul Sambut Baik Usulan Tambah Sekolah Rakyat di Makassar</t>
+        </is>
+      </c>
+      <c r="C910" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:49:03 +0700</t>
+        </is>
+      </c>
+      <c r="D910" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E910" t="inlineStr">
+        <is>
+          <t>Gus Ipul dukung penambahan Sekolah Rakyat di Makassar untuk tampung lebih banyak siswa. Pemprov Sulsel siapkan lahan 20 hektare untuk pembangunan.</t>
+        </is>
+      </c>
+      <c r="F910" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G910" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608798/gus-ipul-sambut-baik-usulan-tambah-sekolah-rakyat-di-makassar</t>
+        </is>
+      </c>
+      <c r="H910" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/menteri-sosial-saifullah-yusuf-gus-ipul-menyambut-usulan-penambahan-satu-sekolah-rakyat-permanen-di-kota-makassar-yang-disampa-1786096119115.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I910" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B911" t="inlineStr">
+        <is>
+          <t>Polisi Tangkap Wanita Pencuri Motor Pria di Jakbar Saat First Meet</t>
+        </is>
+      </c>
+      <c r="C911" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:49:02 +0700</t>
+        </is>
+      </c>
+      <c r="D911" t="inlineStr">
+        <is>
+          <t>Jabbar Ramdhani</t>
+        </is>
+      </c>
+      <c r="E911" t="inlineStr">
+        <is>
+          <t>Polisi menangkap wanita yang mencuri sepeda motor pria saat pertemuan pertama (first meet) mereka setelah kenal di medsos.</t>
+        </is>
+      </c>
+      <c r="F911" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G911" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608799/polisi-tangkap-wanita-pencuri-motor-pria-di-jakbar-saat-first-meet</t>
+        </is>
+      </c>
+      <c r="H911" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/seorang-pria-menjadi-korban-curanmor-di-kembangan-jakbar-sepeda-motor-pria-itu-diduga-dibawa-wanita-saat-pertemuan-pertama-fir-1785999460503_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I911" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>Dindikbud Kebut Pendataan 3.000 Potensi Cagar Budaya di Kota Serang</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:29:56 +0700</t>
+        </is>
+      </c>
+      <c r="D912" t="inlineStr">
+        <is>
+          <t>Arief Ikhsanudin</t>
+        </is>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>Salah satu wilayah yang memiliki potensi cagar budaya adalah Kecamatan Kasemen. Kasemen merupakan kawasan Banten Lama.</t>
+        </is>
+      </c>
+      <c r="F912" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608774/dindikbud-kebut-pendataan-3-000-potensi-cagar-budaya-di-kota-serang</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kepala-dinas-pendidikan-dan-kebudayaan-dindikbud-kota-serang-ahmad-nuri-ariefdetikcom-1786094924878_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>950 Dapur MBG Terindikasi Tak Sesuai Standar</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:30:32 +0700</t>
+        </is>
+      </c>
+      <c r="D913" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono menduga adanya sekitar 950 SPPG yang beroperasi, tapi tak memenuhi standar laik higiene sanitasi.</t>
+        </is>
+      </c>
+      <c r="F913" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8608971/950-dapur-mbg-terindikasi-tak-sesuai-standar</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kepala-badan-gizi-nasional-bgn-sudaryono-1786101835426_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>66 Kepala Dapur MBG Dipecat!</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:53:35 +0700</t>
+        </is>
+      </c>
+      <c r="D914" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono menyampaikan sebanyak 66 Kepala Satuan Pelayanan Pemenuhan Gizi (SPPG) dalam proses pemberhentian secara tidak hormat</t>
+        </is>
+      </c>
+      <c r="F914" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8608917/66-kepala-dapur-mbg-dipecat</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/29/kepala-badan-gizi-nasional-bgn-sudaryono-1785314871601_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>Prabowo Puji Kinerja Bahlil: Saya Kasih Rapor Memuaskan!</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:40:22 +0700</t>
+        </is>
+      </c>
+      <c r="D915" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto memberikan penilaian memuaskan terhadap kinerja Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia.</t>
+        </is>
+      </c>
+      <c r="F915" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8608893/prabowo-puji-kinerja-bahlil-saya-kasih-rapor-memuaskan</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/presiden-prabowo-subianto-1786098762245_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>Waka MPR Dorong Transformasi BUMN Jadi Agen Perubahan dan Keadilan Sosial</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:32:33 +0700</t>
+        </is>
+      </c>
+      <c r="D916" t="inlineStr">
+        <is>
+          <t>Alfi Kholisdinuka</t>
+        </is>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>Wakil Ketua MPR Eddy Soeparno dorong transformasi BUMN untuk menciptakan nilai bagi masyarakat dan lingkungan, bukan hanya pemegang saham.</t>
+        </is>
+      </c>
+      <c r="F916" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8608882/waka-mpr-dorong-transformasi-bumn-jadi-agen-perubahan-dan-keadilan-sosial</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/wakil-ketua-mpr-ri-dari-fraksi-pan-eddy-soeparno-1786098698037.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>Smelter Freeport di Gresik Kembali Operasi Bertahap Mulai September 2026</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:16:03 +0700</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>Smelter Manyar PT Freeport di Gresik dijadwalkan beroperasi bertahap mulai September 2026 setelah terhenti akibat longsor.</t>
+        </is>
+      </c>
+      <c r="F917" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8608849/smelter-freeport-di-gresik-kembali-operasi-bertahap-mulai-september-2026</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/12/13/pernah-lihat-konsentrat-ini-bentuknya-sebelum-masuk-smelter-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>Prabowo Sebut Banyak Negara Panik soal Gejolak Energi: RI Masih Cool!</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:05:39 +0700</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E918" t="inlineStr">
+        <is>
+          <t>Walaupun banyak negara lain sudah agak panik, Indonesia masih cool masih tenang, kata Prabowo.</t>
+        </is>
+      </c>
+      <c r="F918" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G918" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8608834/prabowo-sebut-banyak-negara-panik-soal-gejolak-energi-ri-masih-cool</t>
+        </is>
+      </c>
+      <c r="H918" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/prabowo-subianto-evadetikcom-1786092746269_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>Prabowo Dapat Laporan Pendapatan Danantara Melesat 400%</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:51:25 +0700</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E919" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto mendapat laporan bahwa pendapatan Badan Pengelola Investasi Daya Anagata Nusantara (BPI Danantara) berhasil naik 400%.</t>
+        </is>
+      </c>
+      <c r="F919" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G919" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8608806/prabowo-dapat-laporan-pendapatan-danantara-melesat-400</t>
+        </is>
+      </c>
+      <c r="H919" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/prabowo-subianto-evadetikcom-1786092746269_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>Industri Tekstil Tarik Investasi Rp 11,4 T</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:40:26 +0700</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>Secara kumulatif sampai dengan kuartal II 2026, investasi industri tekstil dan pakaian jadi mencapai Rp 11,40 triliun.</t>
+        </is>
+      </c>
+      <c r="F920" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G920" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/industri/d-8608800/industri-tekstil-tarik-investasi-rp-11-4-t</t>
+        </is>
+      </c>
+      <c r="H920" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/04/14/kenaikan-harga-tekan-industri-garmen-biaya-produksi-ikut-membengkak-1776151719528_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>Konsumsi Listrik SPKLU Melonjak, PLN Perluas Infrastruktur Pengisian EV</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:33:59 +0700</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>Penggunaan kendaraan listrik di Indonesia meningkat, dengan konsumsi listrik SPKLU mencapai 62,4 juta kWh hingga Juni 2026.</t>
+        </is>
+      </c>
+      <c r="F921" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G921" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8608778/konsumsi-listrik-spklu-melonjak-pln-perluas-infrastruktur-pengisian-ev</t>
+        </is>
+      </c>
+      <c r="H921" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/konsumsi-listrik-spklu-melonjak-pln-perluas-infrastruktur-pengisian-kendaraan-listrik-1786095205941.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>Rosan: Orang Biasanya Luncurkan 1 Buku, Bahlil Langsung 10!</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:10:50 +0700</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>CEO Danantara, Rosan Roeslani, menghadiri peluncuran 10 buku Bahlil Lahadalia. Ia menilai buku ini inspiratif bagi generasi muda untuk meraih kesuksesan.</t>
+        </is>
+      </c>
+      <c r="F922" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G922" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8608717/rosan-orang-biasanya-luncurkan-1-buku-bahlil-langsung-10</t>
+        </is>
+      </c>
+      <c r="H922" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/rosan-p-roeslani-1786093590837_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>Kelolaan Bank Emas Kini Tembus 150 Ton</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:46:44 +0700</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E923" t="inlineStr">
+        <is>
+          <t>Otoritas Jasa Keuangan (OJK) mencatat kinerja positif usaha bulion atau bank emas.</t>
+        </is>
+      </c>
+      <c r="F923" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G923" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/moneter/d-8608675/kelolaan-bank-emas-kini-tembus-150-ton</t>
+        </is>
+      </c>
+      <c r="H923" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/18/ilustrasi-emas-batangan-1784354557947_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>BRImo Hadir di Code.Strt 2026, Bikin Transaksi Makin Praktis</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:45:15 +0700</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E924" t="inlineStr">
+        <is>
+          <t>Code.Strt 2026 hadir dengan pengalaman transaksi digital praktis melalui BRImo. Nikmati festival streetwear, musik, dan promo menarik dari 30 Juli-9 Agustus!</t>
+        </is>
+      </c>
+      <c r="F924" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G924" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8608665/brimo-hadir-di-code-strt-2026-bikin-transaksi-makin-praktis</t>
+        </is>
+      </c>
+      <c r="H924" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/brimo-hadir-di-codestrt-2026-bikin-transaksi-makin-praktis-1786092260562.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>PT PAL Mulai Bangun Kapal Selam Pertama Scorpene</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:15:57 +0700</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E925" t="inlineStr">
+        <is>
+          <t>PT PAL Indonesia resmi memulai pembangunan fisik kapal selam pertama Scorpène Republik Indonesia (SRI).</t>
+        </is>
+      </c>
+      <c r="F925" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G925" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/infrastruktur/d-8608599/pt-pal-mulai-bangun-kapal-selam-pertama-scorpene</t>
+        </is>
+      </c>
+      <c r="H925" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/pt-pal-mulai-bangun-kapal-selam-sri-1786090294723_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>Daus Mini Juga Berencana Laporkan Adanya Ancaman Pembunuhan</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:09:28 +0700</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E926" t="inlineStr">
+        <is>
+          <t>Komedian Daus Mini melaporkan pencatutan identitasnya ke polisi. Dia juga berencana melaporkan adanya dugaan ancaman pembunuhan.</t>
+        </is>
+      </c>
+      <c r="F926" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G926" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608833/daus-mini-juga-berencana-laporkan-adanya-ancaman-pembunuhan</t>
+        </is>
+      </c>
+      <c r="H926" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/daus-mini-1786090106434_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>Eks Ketua Yayasan Sekolah Jaksel Bakal Diperiksa soal Ratusan Senjata</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:17:15 +0700</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E927" t="inlineStr">
+        <is>
+          <t>Polisi akan memeriksa eks ketua yayasan sekolah swasta di Jakarta terkait temuan ratusan senjata. Penyelidikan mencakup asal-usul dan perizinan senjata.</t>
+        </is>
+      </c>
+      <c r="F927" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G927" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807174815-12-1389854/eks-ketua-yayasan-sekolah-jaksel-bakal-diperiksa-soal-ratusan-senjata</t>
+        </is>
+      </c>
+      <c r="H927" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/ratusan-senjata-di-yayasan-sekolah-jaksel-1786100090384_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>Guru Asal India Jadi Kurir Ganja Thailand Rp1,5 M, Ditangkap di Bali</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:05:23 +0700</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E928" t="inlineStr">
+        <is>
+          <t>Dua WN India ditangkap di Bali saat menyelundupkan 10 kg ganja senilai Rp1,5 miliar. Satu WNA pria berprofesi manajer, satu lainnya perempuan berprofesi guru.</t>
+        </is>
+      </c>
+      <c r="F928" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G928" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807135353-12-1389774/guru-asal-india-jadi-kurir-ganja-thailand-rp15-m-ditangkap-di-bali</t>
+        </is>
+      </c>
+      <c r="H928" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/09/08/ilustrasi-tindakan-kriminal-7_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>Luhut Kenang Perjuangan Hilirisasi Nikel dengan Bahlil: Kami Dicibir</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:16:12 +0700</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr">
+        <is>
+          <t>Luhut mengenang masa-masa awal kebijakan larangan ekspor bijih nikel yang ia kawal bersama Menteri ESDM Bahlil Lahadalia. Banyak cibiran dan tekanan.</t>
+        </is>
+      </c>
+      <c r="F929" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G929" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807175924-92-1389857/luhut-kenang-perjuangan-hilirisasi-nikel-dengan-bahlil-kami-dicibir</t>
+        </is>
+      </c>
+      <c r="H929" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/luhut-kenang-awal-larangan-ekspor-bijih-nikel-bareng-bahlil-1786097382105_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>Prabowo Puji Bahlil Tak Naikkan Harga BBM: Negara Lain Panik, RI Cool</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:52:45 +0700</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E930" t="inlineStr">
+        <is>
+          <t>Prabowo memuji kinerja Menteri ESDM Bahlil Lahadalia yang dinilai berhasil dalam menghadapi gejolak geopolitik yang berimbas pada harga minyak dunia.</t>
+        </is>
+      </c>
+      <c r="F930" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G930" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807173851-532-1389847/prabowo-puji-bahlil-tak-naikkan-harga-bbm-negara-lain-panik-ri-cool</t>
+        </is>
+      </c>
+      <c r="H930" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/peluncuran-sepuluh-buku-karya-nyata-untuk-negeri-bahlil-lahadalia-1786099773572_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>Pemerintah Bidik Pajak dari Juragan Kontrakan Tahun Depan</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:43:36 +0700</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E931" t="inlineStr">
+        <is>
+          <t>Pemerintah bakal memperluas basis perpajakan pada 2027. Salah satu kelompok yang dibidik adalah pungutan pajak dari juragan kontrakan.</t>
+        </is>
+      </c>
+      <c r="F931" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G931" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807172442-532-1389844/pemerintah-bidik-pajak-dari-juragan-kontrakan-tahun-depan</t>
+        </is>
+      </c>
+      <c r="H931" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2015/02/02/fce19f4d-dac6-476e-9328-28d6b44c1990_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>Mengapa Oknum Polisi Mudah Tergiur Bisnis Narkoba? IPW Ungkap 3 Alasannya: Praktis, Bernilai Mahal</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:31:43 +0700</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>Ketua IPW Sugeng Teguh Santoso mengungkap alasan mendasar di balik rentannya oknum anggota Polri terjerumus dalam lingkaran setan kasus narkoba.</t>
+        </is>
+      </c>
+      <c r="F932" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G932" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865426/mengapa-oknum-polisi-mudah-tergiur-bisnis-narkoba-ipw-ungkap-3-alasannya-praktis-bernilai-mahal</t>
+        </is>
+      </c>
+      <c r="H932" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/xciAegZliJ6QT5L0umnF1kmk6C4=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/wawancara-khusus-dengan-ketua-ipw-sugeng-teguh-santoso_20240710_213751.jpg</t>
+        </is>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>Imbas Ulah Akun Palsu, Daus Mini Alami Pembunuhan Karakter hingga Penurunan Penghasilan</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:31:31 +0700</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>Komedian Daus Mini mengaku mengalami kerugian nama baik hingga materi akibat ulah akun media sosial yang diduga mencatut identitasnya.</t>
+        </is>
+      </c>
+      <c r="F933" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G933" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865425/imbas-ulah-akun-palsu-daus-mini-alami-pembunuhan-karakter-hingga-penurunan-penghasilan</t>
+        </is>
+      </c>
+      <c r="H933" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/l76qTHtg7DcHWjQKmILAohIPsr8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Daus-Mini-2-07082026.jpg</t>
+        </is>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>Potongan Kaki Korban Mutilasi di Depok Belum Ditemukan, Polisi Telusuri Aliran Sungai</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:30:36 +0700</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>derasnya aliran sungai diduga menyebabkan potongan tubuh tersebut terbawa arus, sehingga tim penyidik harus menelusuri aliran sungai</t>
+        </is>
+      </c>
+      <c r="F934" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G934" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7865424/potongan-kaki-korban-mutilasi-di-depok-belum-ditemukan-polisi-telusuri-aliran-sungai</t>
+        </is>
+      </c>
+      <c r="H934" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/OjMG3FJ-39duihokZY4K15I_9Os=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Pelaku-Mutilasi-di-Depok-Saepullah-12.jpg</t>
+        </is>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>Terjemahan Lirik Lagu The Time Of My Life - Benson Boone: I Wish You Came Along</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:29:59 +0700</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>Inilah lirik lagu dan terjemahan The Time Of My Life yang dipopulerkan oleh penyanyi Benson Boone. Lagu ini dirilis pada 26 Juni 2026.</t>
+        </is>
+      </c>
+      <c r="F935" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G935" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/musik/7865423/terjemahan-lirik-lagu-the-time-of-my-life-benson-boone-i-wish-you-came-along</t>
+        </is>
+      </c>
+      <c r="H935" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/zLN77GXG_MWcQ27NDqNvGgp-QJs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-musik-ilustrasi-lirik-ilustrasi-terjemahan-lirik-lagu.jpg</t>
+        </is>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>950 Dapur MBG Terancam Ditutup Permanen, Kepala BGN: SLHS Syarat Mutlak, Bukan Formalitas!</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:26:20 +0700</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E936" t="inlineStr">
+        <is>
+          <t>Mengingat risiko keracunan makanan mengintai keselamatan dan jiwa para siswa penerima manfaat, BGN berikan batas waktu singkat hingga 10 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F936" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G936" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865422/950-dapur-mbg-terancam-ditutup-permanen-kepala-bgn-slhs-syarat-mutlak-bukan-formalitas</t>
+        </is>
+      </c>
+      <c r="H936" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/4q4UMH5Yz2QKnWL_YM976-I3kGM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Budi-Gunadi-Sadikin-dan-Sudaryono.jpg</t>
+        </is>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>Kepala BGN Sudaryono Cerita Kisah Haru Temui Siswa Bawa Pulang Burger MBG untuk Ibu</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:26:17 +0700</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono membagikan temuan mengharukan terkait perilaku sejumlah siswa penerima Program MBG di lapangan</t>
+        </is>
+      </c>
+      <c r="F937" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G937" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865421/kepala-bgn-sudaryono-cerita-kisah-haru-temui-siswa-bawa-pulang-burger-mbg-untuk-ibu</t>
+        </is>
+      </c>
+      <c r="H937" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/pZTamHkyu0hU4b-z_jCK-qzQ_3Q=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/sudaryono-BGN-020.jpg</t>
+        </is>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>Ukraina Kekurangan Rudal Antipesawat, NATO Percepat Pengiriman Sistem Pertahanan</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:25:41 +0700</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E938" t="inlineStr">
+        <is>
+          <t>Sekretaris Jenderal NATO Mark Rutte mengatakan penguatan pertahanan udara menjadi kebutuhan mendesak bagi Ukraina.</t>
+        </is>
+      </c>
+      <c r="F938" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G938" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7865420/ukraina-kekurangan-rudal-antipesawat-nato-percepat-pengiriman-sistem-pertahanan</t>
+        </is>
+      </c>
+      <c r="H938" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/7ulSBLITUtHqmnqUerYpwM4_CZc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Foto-ilustrasi-bendera-NATO-dan-bendera-Ukraina-yang-diambil.jpg</t>
+        </is>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>Jelang Kejuaraan Dunia BWF 2026, Rexy Mainaky Tak Cemas soal Chemistry Ganda Putra</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:24:11 +0700</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E939" t="inlineStr">
+        <is>
+          <t>Chemistry ganda putra utama Malaysia yang sempat dirombak diyakini tak memudar jelang Kejuaraan Dunia BWF 2026 oleh Rexy Mainaky.</t>
+        </is>
+      </c>
+      <c r="F939" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G939" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7865419/jelang-kejuaraan-dunia-bwf-2026-rexy-mainaky-tak-cemas-soal-chemistry-ganda-putra</t>
+        </is>
+      </c>
+      <c r="H939" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/yoV87cuvFbibknPtbgk8pRanBAQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/aaron-chiasoh-wooi-yik-kalah_20240608_210449.jpg</t>
+        </is>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>YouTuber Bigmo Diperiksa atas Dugaan Eksploitasi Anak pada 10 Agustus, Polisi Amankan 3 Barang Bukti</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:21:21 +0700</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E940" t="inlineStr">
+        <is>
+          <t>YouTuber Muhammad Jannah alias Bigmo diperiksa polisi terkait dugaan eksploitasi anak pada Senin (10/8/2026), tiga barang bukti diamankan.</t>
+        </is>
+      </c>
+      <c r="F940" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G940" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865418/youtuber-bigmo-diperiksa-atas-dugaan-eksploitasi-anak-pada-10-agustus-polisi-amankan-3-barang-bukti</t>
+        </is>
+      </c>
+      <c r="H940" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/kVJ1JVg63OmX06VPzX6uBJAdK7g=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/bigmo-apa.jpg</t>
+        </is>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>Komisi III DPR Minta Bandar 46 Juta Pil Koplo Senilai Rp230 Miliar Diburu hingga Tuntas</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:20:16 +0700</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E941" t="inlineStr">
+        <is>
+          <t>Sahroni meminta aparat penegak hukum mengusut tuntas jaringan di balik pengungkapan peredaran sekitar 46 juta butir obat keras.</t>
+        </is>
+      </c>
+      <c r="F941" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G941" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865417/komisi-iii-dpr-minta-bandar-46-juta-pil-koplo-senilai-rp230-miliar-diburu-hingga-tuntas</t>
+        </is>
+      </c>
+      <c r="H941" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/QSkn5JciYogy4ltZ2THQlltcGVk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/sinergi-3-kantor-bea-cukai-gagalkan-pengiriman-seribu-butir-pil-koplo-y.jpg</t>
+        </is>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>Kunci Jawaban IPS Kelas 10 SMA Kurikulum Merdeka Halaman 130 Edisi Revisi: Pengayaan</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:17:16 +0700</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E942" t="inlineStr">
+        <is>
+          <t>Berikut ini kunci jawaban kelas 10 SMA Kurikulum Merdeka Halaman 130 Edisi Revisi: Pengayaan.</t>
+        </is>
+      </c>
+      <c r="F942" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G942" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7865416/kunci-jawaban-ips-kelas-10-sma-kurikulum-merdeka-halaman-130-edisi-revisi-pengayaan</t>
+        </is>
+      </c>
+      <c r="H942" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/nFsQMFTJWnTiWRz4kEeN-T0dFBk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/pembelajaran-tatap-muka-pelajar-di-bandar-lampung_20210913_163413.jpg</t>
+        </is>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>Kasus Kapolresta Banda Aceh hingga Diperiksa Propam Masih Misteri, Kompolnas Desak Polri Transparan</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:17:12 +0700</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E943" t="inlineStr">
+        <is>
+          <t>Beredar informasi keduanya terjerat kasus penyalahgunaan narkoba. Namun hingga kini Mabes Polri masih belum mengonfirmasi.</t>
+        </is>
+      </c>
+      <c r="F943" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G943" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865415/kasus-kapolresta-banda-aceh-hingga-diperiksa-propam-masih-misteri-kompolnas-desak-polri-transparan</t>
+        </is>
+      </c>
+      <c r="H943" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/-x6OZX7zgEAtmwNMMW-J7x43Ig8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Profil-Kombes-Pol-Andi-Kirana-Kapolresta-Banda-Aceh-yang-Diperiksa-Mabes-Polri-Hartanya-Rp369-Juta.jpg</t>
+        </is>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>Pelaku UMKM Solo Bertahan di Tengah Gempuran Produk Impor Murah, Utamakan Kualitas Handmade</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:14:03 +0700</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr">
+        <is>
+          <t>Pelaku UMKM kerajinan di Solo menghadapi persaingan ketat dengan produk impor murah di marketplace.</t>
+        </is>
+      </c>
+      <c r="F944" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G944" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865414/pelaku-umkm-solo-bertahan-di-tengah-gempuran-produk-impor-murah-utamakan-kualitas-handmade</t>
+        </is>
+      </c>
+      <c r="H944" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/yMa58OZlUI8xwZIC_F9jmm6cvhs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/UMKM-Flanelisa.jpg</t>
+        </is>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>Ketua MPR Ungkap Naskah PPHN Akan Dibuka ke Publik Setelah 17 Agustus 2026</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:14:01 +0700</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>Ketua MPR RI Ahmad Muzani mengatakan naskah PPHN akan dibuka kepada publik setelah peringatan Hari Kemerdekaan 17 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F945" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G945" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865413/ketua-mpr-ungkap-naskah-pphn-akan-dibuka-ke-publik-setelah-17-agustus-2026</t>
+        </is>
+      </c>
+      <c r="H945" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/J6vP3PVyKjqpjjpqfaGoWehjxp8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ketua-MPR-RI-Ahmad-Muzani-07082026.jpg</t>
+        </is>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>Harta Kekayaan Eks Ketua DPRD Ponorogo SN Capai Rp2,2 Miliar, Kini Jadi Tersangka Korupsi</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:12:24 +0700</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E946" t="inlineStr">
+        <is>
+          <t>Kejari Ponorogo resmi menetapkan eks Ketua DPRD Ponorogo periode 2019-2024 Fraksi Nasdem, SN, sebagai tersangka baru dalam kasus dugaan korupsi.</t>
+        </is>
+      </c>
+      <c r="F946" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G946" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865412/harta-kekayaan-eks-ketua-dprd-ponorogo-sn-capai-rp22-miliar-kini-jadi-tersangka-korupsi</t>
+        </is>
+      </c>
+      <c r="H946" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/9iBPkz-OjcF5Wqdlpipaysb1KzM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/DITAHAN-SN-Ketua-DPRD-Ponorogo.jpg</t>
+        </is>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>Kasus Yurizal Jadi Sorotan, Anggota DPR Abduh Dorong Kemenkes Benahi Komunikasi Tenaga Kesehatan</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:11:17 +0700</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>Anggota Komisi III DPR Abdullah meminta kasus Yurizal menjadi momentum bagi Kemenkes memperbaiki standar komunikasi tenaga kesehatan.</t>
+        </is>
+      </c>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865411/kasus-yurizal-jadi-sorotan-anggota-dpr-abduh-dorong-kemenkes-benahi-komunikasi-tenaga-kesehatan</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/UJjrCL0UKtG65Dc1hl7MXz2F_8k=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/FOTO-Anggota-Komisi-III-dari-Fraksi-Partai-Kebangkitan-Bangsa-PKB-Abdullah.jpg</t>
+        </is>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>Igor Tolic Akui Persebaya Layak Juara, Optimistis Persib Tatap Musim Baru dengan Modal Positif</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:08:20 +0700</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr">
+        <is>
+          <t>Pelatih asal Kroasia itu justru melihat banyak sisi positif yang bisa menjadi bekal Persib menghadapi musim kompetisi 2026/2027.</t>
+        </is>
+      </c>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7865410/igor-tolic-akui-persebaya-layak-juara-optimistis-persib-tatap-musim-baru-dengan-modal-positif</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/nCgC2_gpFoMvUGfECfJIq3D6imA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Final-Piala-Presiden-2026-antara-Persib-Bandung-vs-Persebaya.jpg</t>
+        </is>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>Daus Mini Resmi Lapor Polisi, Tiga Akun Diduga Catut Identitasnya Kini Diburu Ditreskrimsus Siber</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:08:03 +0700</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr">
+        <is>
+          <t>Daus Mini dan kuasa hukumnya melaporkan dugaan pelanggaran Pasal 51 ayat (1) juncto Pasal 35 ayat (1) UU ITE.</t>
+        </is>
+      </c>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865409/daus-mini-resmi-lapor-polisi-tiga-akun-diduga-catut-identitasnya-kini-diburu-ditreskrimsus-siber</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/l76qTHtg7DcHWjQKmILAohIPsr8=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Daus-Mini-2-07082026.jpg</t>
+        </is>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>Istana Soal Kasus Unggahan Konten Nuklir Iran: Tanyakan ke Kepolisian</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:02:32 +0700</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr">
+        <is>
+          <t>Prasetyo Hadi enggan mengomentari proses penegakan hukum yang dilakukan polisi terhadap dua orang yang dinilai menimbulkan keresahan.</t>
+        </is>
+      </c>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865408/istana-soal-kasus-unggahan-konten-nuklir-iran-tanyakan-ke-kepolisian</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/hH7V60ix95CcR0SInm1prH87c_M=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Prasetyo-Hadi-di-Wisma-Negara-Komplek-Istana-07082026.jpg</t>
+        </is>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya Proses Hukum 10 Orang Diduga Sebarkan Konten Provokatif dan Hoaks Kericuhan Demo</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:01:59 +0700</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr">
+        <is>
+          <t>Konten tersebut berkaitan dengan salah satunya kericuhan demo yang dapat mengganggu stabilitas keamanan.</t>
+        </is>
+      </c>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7865407/polda-metro-jaya-proses-hukum-10-orang-diduga-sebarkan-konten-provokatif-dan-hoaks-kericuhan-demo</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/SJlDphYZb8erWpHv8P8tsSvKMZA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/KONTEN-PROVOKATIF-demo.jpg</t>
+        </is>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>Video: Pemerintah Perkuat dan Bangun Ekosistem Kekayaan Intelektual</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:30:26 +0700</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr">
+        <is>
+          <t>Pemerintah Perkuat Kolaborasi dan Bangun Ekosistem Kekayaan Intelektual</t>
+        </is>
+      </c>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807141316-8-757458/video-pemerintah-perkuat-bangun-ekosistem-kekayaan-intelektual</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/medcov-forum-koordinasi-nasional-1786086851202_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>Bos BGN Pecat 66 Kepala Dapur MBG: Secara Tidak Hormat!</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:22:04 +0700</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr">
+        <is>
+          <t>Badan Gizi Nasional (BGN) sedang memproses pemberhentian tidak hormat atas 66 kepala dapur program Makan Bergizi Gratis (MBG)</t>
+        </is>
+      </c>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807182005-4-757529/bos-bgn-pecat-66-kepala-dapur-mbg-secara-tidak-hormat</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/22/kepala-badan-gizi-nasional-bgn-sudaryono-saat-ditemui-di-kantor-pusat-bgn-jakarta-rabu-2272026-1784722137132_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>Prabowo Sebut Bahlil Pintar: Bisa Bikin Jokowi Ketawa</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>Verda Nano Setiawan</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr">
+        <is>
+          <t>Presiden RI Prabowo Subianto memuji Menteri ESDM Bahlil Lahadalia</t>
+        </is>
+      </c>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807172440-4-757521/prabowo-sebut-bahlil-pintar-bisa-bikin-jokowi-ketawa</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/presiden-prabowo-subianto-memberikan-sambutan-pada-acara-peluncuran-dan-beda-buku-bahlil-lahadalia-di-djakarta-theatre-jakarta-1786091462835_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Sinyal Merah Pelayaran: Laut Bergejolak, Laba Emiten Kapal RI Karam</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:55:32 +0700</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>Sinyal Merah Pelayaran: Laut Bergejolak, Laba Emiten Kapal RI Karam</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807151030-8-757488/sinyal-merah-pelayaran-laut-bergejolak-laba-emiten-kapal-ri-karam</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/sinyal-merah-pelayaran-laut-bergejolak-laba-emiten-kapal-ri-karam-1786097273618_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>IMF Akui Utang Luar Negeri RI Aman, Terhindar dari Risiko Gagal Bayar</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:55:08 +0700</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>IMF mengungkapkan risiko utang luar negeri Indonesia masih cukup aman</t>
+        </is>
+      </c>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807165208-4-757508/imf-akui-utang-luar-negeri-ri-aman-terhindar-dari-risiko-gagal-bayar</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2023/10/06/logo-imf-reutersyuri-gripasfile-photo_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>Unilever Sabet ESG Award 2026 dari Yayasan KEHATI</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:43:26 +0700</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>PT Unilever Indonesia meraih penghargaan Best Emiten di ajang ESG Award 2026, menegaskan komitmen keberlanjutan dalam bisnis dan rantai nilai.</t>
+        </is>
+      </c>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807173348-17-757523/unilever-sabet-esg-award-2026-dari-yayasan-kehati</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/dok-unilever-indonesia-1786099377501_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>Video: Iran Tuding Trump Lakukan "Diplomasi Teater" - Rupiah Perkasa</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:23:26 +0700</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>Iran Tuding Trump Lakukan "Diplomasi Teater" hingga Rupiah Perkasa di Rp17.800 per USD</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807170854-19-757516/video-iran-tuding-trump-lakukan-diplomasi-teater--rupiah-perkasa</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/iran-tuding-trump-lakukan-diplomasi-teater-hingga-rupiah-perkasa-di-rp17800-per-usd-1786097912404_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>Video: Sentimen Ini Bikin IHSG Akhir Pekan Melesat Tembus Level 6.400</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:17:41 +0700</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>Sentimen Ini Bikin IHSG Akhir Pekan Melesat Tembus Level 6.400</t>
+        </is>
+      </c>
+      <c r="F959" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807170054-19-757511/video-sentimen-ini-bikin-ihsg-akhir-pekan-melesat-tembus-level-6400</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/sentimen-ini-bikin-ihsg-akhir-pekan-melesat-tembus-level-6400-1786097593161_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>Ini Bukti Warga RI Makin Doyan Beli Barang Pakai Pay Later</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:07:29 +0700</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr">
+        <is>
+          <t>Mentari Puspadini</t>
+        </is>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>Minat masyarakat terhadap pembiayaan Buy Now Pay Later (BNPL) terus meningkat, dengan pertumbuhan 57,02% yoy di Juni 2026.</t>
+        </is>
+      </c>
+      <c r="F960" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807161359-17-757513/ini-bukti-warga-ri-makin-doyan-beli-barang-pakai-pay-later</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/01/17/wajib-tahu-ini-perbedaan-kartu-kredit-paylater-pinjol_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>Istana Ungkap Sosok Ini Dipertimbangkan Prabowo Jadi Calon Gubernur BI</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:25:26 +0700</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto tengah dalam proses seleksi calon Gubernur Bank Indonesia (BI).</t>
+        </is>
+      </c>
+      <c r="F961" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807155425-17-757474/istana-ungkap-sosok-ini-dipertimbangkan-prabowo-jadi-calon-gubernur-bi</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/27/menteri-sekretaris-negara-prasetyo-hadi-saat-menyampaikan-konferensi-pers-di-bank-indonesia-jakarta-senin-2772026-1785117094500_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>IHSG Happy Weekend! Melesat 1% dan Tembus Level Psikologis 6.400</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:21:19 +0700</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr">
+        <is>
+          <t>Redaksi</t>
+        </is>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>IHSG menguat 1,04% di level 6.409,65 pada 7 Agustus 2026. Sektor teknologi dan properti mendominasi penguatan, meski pelaku pasar waspada sentimen global.</t>
+        </is>
+      </c>
+      <c r="F962" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807161625-17-757487/ihsg-happy-weekend-melesat-1-tembus-level-psikologis-6400</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/08/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-gedung-bursa-efek-indonesia-bei-jakarta-senin-862026-cnbc-ind-1780893013553_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>Bank Kasikorn (BMAS) Galang Rights Issue Jumbo, Duitnya Buat Ini</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:00:58 +0700</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>PT Bank Kasikorn Indonesia Tbk. (BMAS) berencana menggelar aksi korporasi melalui Penambahan Modal dengan Memberikan Hak Memesan Efek Terlebih Dahulu (PMHMETD).</t>
+        </is>
+      </c>
+      <c r="F963" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807151358-17-757460/bank-kasikorn--bmas--galang-rights-issue-jumbo-duitnya-buat-ini</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/10/18/kbank-cnbc-indonesiasefti-oktarianisa-4_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>BEI Lelang 11 Saham, Ini Syarat Belinya</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:35:15 +0700</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr">
+        <is>
+          <t>Romys Binekasri</t>
+        </is>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>PT Bursa Efek Indonesia (BEI) berencana akan menyelenggarakan lelang atas 11 saham bursa yang belum dikeluarkan atau telah dibeli kembali (buyback) oleh Bursa.</t>
+        </is>
+      </c>
+      <c r="F964" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807143214-17-757448/bei-lelang-11-saham-ini-syarat-belinya</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019885_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>Pilih Calon Gubernur BI, Prabowo Sudah Panggil Banyak Nama ke Istana</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:25:49 +0700</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara (Mensesneg) Prasetyo Hadi mengungkapkan calon Gubernur Bank Indonesia (BI) belum diputuskan oleh Presiden Prabowo Subianto.</t>
+        </is>
+      </c>
+      <c r="F965" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807150549-17-757459/pilih-calon-gubernur-bi-prabowo-sudah-panggil-banyak-nama-ke-istana</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2018/02/01/b11fce91-e359-452f-9764-7ad833927e18_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>Rupiah Melaju Jelang Akhir Pekan, Dolar Turun ke Rp17.885</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:04:23 +0700</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr">
+        <is>
+          <t>Elvan Widyatama</t>
+        </is>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>Nilai tukar rupiah menutup perdagangan terakhir pekan ini dengan penguatan terhadap dolar Amerika Serikat (AS).</t>
+        </is>
+      </c>
+      <c r="F966" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807144816-17-757455/rupiah-melaju-jelang-akhir-pekan-dolar-turun-ke-rp17885</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/08/petugas-menjunjukkan-uang-pecahan-dolar-amerika-serikat-as-dan-rupiah-di-dolar-asia-money-changer-jakarta-rabu-872026-1783496342241_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>Bos OJK: Analisa Kredit Pindar Bisa Pakai AI</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:00:12 +0700</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr">
+        <is>
+          <t>Romys Binekasri</t>
+        </is>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>Otoritas Jasa Keuangan (OJK) menyampaikan, perusahaan pinjaman daring dapat menggunakan teknologi kecerdasan buatan (Artificial Intelegence/AI).</t>
+        </is>
+      </c>
+      <c r="F967" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807135955-17-757441/bos-ojk-analisa-kredit-pindar-bisa-pakai-ai</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/02/11/kepala-eksekutif-pengawas-lembaga-pembiayaan-perusahaan-modal-ventura-lembaga-keuangan-mikro-dan-lembaga-jasa-keuangan-lainnya-6_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>Pegadaian dan BSI Kelola 150 Ton Emas di Usaha Bulion</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:41:30 +0700</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr">
+        <is>
+          <t>Mentari Puspadini</t>
+        </is>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>Total kelolaan ekosistem emas di Indonesia mencapai 150 ton di paruh pertama 2026. Dua lembaga keuangan telah memperoleh izin untuk usaha bulion.</t>
+        </is>
+      </c>
+      <c r="F968" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807144032-17-757453/pegadaian-bsi-kelola-150-ton-emas-di-usaha-bulion</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/04/21/pegadaian-1776770280304_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>Video: Akhir Pekan, IHSG Reli dan Rupiah Menguat ke Rp 17.800-an per USD</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:06:07 +0700</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia TV</t>
+        </is>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>Akhir Pekan Ceria, IHSG Reli dan Rupiah Menguat ke Rp 17.800-an per USD</t>
+        </is>
+      </c>
+      <c r="F969" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807135454-19-757440/video-akhir-pekan-ihsg-reli-rupiah-menguat-ke-rp-17800-an-per-usd</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/akhir-pekan-ceria-ihsg-reli-rupiah-menguat-ke-rp-17800-an-per-usd-1786086220781_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>Asing Net Buy Rp343 Miliar di Sesi I, Terciduk Kompak Serok BBRI</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:40:34 +0700</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>IHSG menguat di sesi I, mendekati level 6.400. Investor asing mencatat net buy terbesar pada BBRI. Sektor teknologi dan properti jadi pendorong utama.</t>
+        </is>
+      </c>
+      <c r="F970" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807132040-17-757415/asing-net-buy-rp343-miliar-di-sesi-i-terciduk-kompak-serok-bbri</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/08/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-gedung-bursa-efek-indonesia-bei-jakarta-senin-862026-cnbc-ind-1780893110993_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>WOM Finance (WOMF) Ungkap Strategi Pembiayaan Kala BI Rate Naik</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:00:26 +0700</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>WOM Finance optimis capai target pembiayaan Rp6,3 triliun pada 2026 meski suku bunga tinggi. Strategi diversifikasi pendanaan jadi kunci keberhasilan.</t>
+        </is>
+      </c>
+      <c r="F971" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807125226-17-757403/wom-finance--womf--ungkap-strategi-pembiayaan-kala-bi-rate-naik</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/02/23/wom-finance-2_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>Lanjutkan Tren Penguatan, IHSG Selangkah Lagi Tembus Level 6.400</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:30:42 +0700</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>IHSG menguat 0,71% pada perdagangan Jumat, mencapai 6.388,48. Sektor teknologi dan properti mendominasi penguatan, meski pelaku pasar waspada sentimen global.</t>
+        </is>
+      </c>
+      <c r="F972" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807122037-17-757399/lanjutkan-tren-penguatan-ihsg-selangkah-lagi-tembus-level-6400</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/06/30/layar-menampilkan-pergerakan-indeks-harga-saham-gabungan-ihsg-di-bursa-efek-indonesia-bei-jakarta-selasa-3062026-1782797019138_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>Penjualan Rumah Masih Seret, Harga Cuma Naik Tipis</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:30:30 +0700</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>Robertus Andrianto</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr">
+        <is>
+          <t>SHPR BI menunjukkan harga properti residensial di pasar primer pada triwulan II 2026 secara tahunan meningkat terbatas.</t>
+        </is>
+      </c>
+      <c r="F973" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G973" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807115218-17-757390/penjualan-rumah-masih-seret-harga-cuma-naik-tipis</t>
+        </is>
+      </c>
+      <c r="H973" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/01/14/pekerja-beraktivitas-pada-salah-satu-proyek-pembangunan-rumah-bersubsidi-di-kawasan-kemang-bogor-jawa-barat-minggu-1212025-3_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>Kupas Tuntas Strategi Industri Pembiayaan di Tengah Berbagai Tantangan</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:26:36 +0700</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E974" t="inlineStr">
+        <is>
+          <t>Industri pembiayaan menghadapi tantangan ekonomi global. CNBC Indonesia menggelar CEO Gathering memperkuat kolaborasi dan kinerja sektor multifinance.</t>
+        </is>
+      </c>
+      <c r="F974" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G974" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807114231-17-757396/kupas-tuntas-strategi-industri-pembiayaan-di-tengah-berbagai-tantangan</t>
+        </is>
+      </c>
+      <c r="H974" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/multifinance-ceo-gathering-2026-1786080104210_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>BI: Uang Primer Tumbuh 17,1% Juli 2026, Tembus Rp2.254 T</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:45:44 +0700</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E975" t="inlineStr">
+        <is>
+          <t>Bank Indonesia (BI) mengumumkan Uang Primer (M0) pada Juli 2026 tumbuh 17,1% (yoy)</t>
+        </is>
+      </c>
+      <c r="F975" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G975" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807113444-17-757376/bi-uang-primer-tumbuh-171-juli-2026-tembus-rp2254-t</t>
+        </is>
+      </c>
+      <c r="H975" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/03/10/ilustrasi-tunjangan-hari-raya-1773120003268_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>Bos Danantara: 652 Perusahaan BUMN Akan Hilang</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:40:58 +0700</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E976" t="inlineStr">
+        <is>
+          <t>BP BUMN bersama BPI Danantara terus melanjutkan program transformasi BUMN melalui percepatan streamlining perusahaan.</t>
+        </is>
+      </c>
+      <c r="F976" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G976" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807105358-17-757360/bos-danantara-652-perusahaan-bumn-akan-hilang</t>
+        </is>
+      </c>
+      <c r="H976" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/23/kepala-bp-bumn-sekaligus-coo-danantara-indonesia-dony-oskaria-menggelar-pertemuan-bersama-direktur-utama-pt-sucofindo-rabu-227-1784802379806_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>Asprindo Dorong KDMP Berkolaborasi dengan Kampung Industri</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E977" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Asosiasi Pengusaha Bumiputera Nusantara Indonesia (Asprindo) menilai Koperasi Desa Merah Putih (KDMP) perlu dikolaborasikan dengan Program Kampung Industri agar desa tidak hanya menjadi pusat distribusi, tetapi juga...</t>
+        </is>
+      </c>
+      <c r="F977" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G977" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tje63l416/asprindo-dorong-kdmp-berkolaborasi-dengan-kampung-industri</t>
+        </is>
+      </c>
+      <c r="H977" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/058550200-1783858320-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>DJKI Sita 9.609 Sepatu Pakai Merek Ilegal, Omzet Usaha Capai Rp 1 Miliar</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:28:36 +0700</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>Friska Yolandha</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA — Direktorat Jenderal Kekayaan Intelektual (DJKI) Kementerian Hukum melalui Direktorat Penegakan Hukum Kekayaan Intelektual menyita 9.609 pasang sepatu dan 49 kotak atau kemasan sepatu yang diduga menggunakan...</t>
+        </is>
+      </c>
+      <c r="F978" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G978" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjed7o370/djki-sita-9609-sepatu-pakai-merek-ilegal-omzet-usaha-capai-rp-1-miliar</t>
+        </is>
+      </c>
+      <c r="H978" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/ilustrasi-sepatu-direktorat-jenderal-kekayaan-intelektual-djki-kementerian-hukum_260807182808-524.jpg</t>
+        </is>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>Industri IVD Perkuat Ekspansi, Indonesia Dibidik Jadi Basis Manufaktur Asia Tenggara</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E979" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA – Industri alat diagnostik atau in vitro diagnostics (IVD) mulai mengubah strategi bisnis di tengah melambatnya belanja pemerintah untuk alat kesehatan dan ketidakpastian ekonomi global. Pelaku industri kini...</t>
+        </is>
+      </c>
+      <c r="F979" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G979" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjecht416/industri-ivd-perkuat-ekspansi-indonesia-dibidik-jadi-basis-manufaktur-asia-tenggara</t>
+        </is>
+      </c>
+      <c r="H979" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260807181714-475.png</t>
+        </is>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>BP BUMN Targetkan Jumlah Entitas BUMN Tinggal 250</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E980" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Kepala BP BUMN sekaligus COO Danantara Dony Oskaria mengatakan program transformasi BUMN terus berjalan melalui percepatan streamlining perusahaan sebagai upaya membangun struktur yang lebih ramping, efektif, dan...</t>
+        </is>
+      </c>
+      <c r="F980" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G980" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjebly423/bp-bumn-targetkan-jumlah-entitas-bumn-tinggal-250</t>
+        </is>
+      </c>
+      <c r="H980" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/096024300-1593678876-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>Finansial</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>KNEKS Dorong Indonesia Miliki PDB Syariah Pertama di Dunia</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:01:00 +0700</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Komite Nasional Ekonomi dan Keuangan Syariah (KNEKS) mendorong percepatan penyusunan produk domestik bruto (PDB) syariah sebagai alat ukur kontribusi ekonomi dan keuangan syariah terhadap perekonomian nasional. Jika...</t>
+        </is>
+      </c>
+      <c r="F981" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G981" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjeb60423/kneks-dorong-indonesia-miliki-pdb-syariah-pertama-di-dunia</t>
+        </is>
+      </c>
+      <c r="H981" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/iaei-dan-kneks-mendorong-agar-indonesia-mempercepat-tata-kelola_260807161037-134.png</t>
+        </is>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>Energi</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>Akademisi Usulkan Roadmap Bertahap untuk Target PLTS 100 GW</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:53:00 +0700</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>Intan Pratiwi</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Akademisi Institut Teknologi PLN (ITPLN) Zulfikar Manggau mengusulkan roadmap bertahap untuk mewujudkan target pembangunan Pembangkit Listrik Tenaga Surya (PLTS) berkapasitas 100 gigawatt (GW) di Indonesia. Menurut dia, pendekatan...</t>
+        </is>
+      </c>
+      <c r="F982" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G982" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tje3bu522/akademisi-usulkan-roadmap-bertahap-untuk-target-plts-100-gw</t>
+        </is>
+      </c>
+      <c r="H982" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/025561300-1781799326-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>Semburan Lumpur Muncul di Oro-oro Kesongo Blora, Tingginya Capai 15 Meter</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:23:36 +0700</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr">
+        <is>
+          <t>Semburan lumpur pertama terjadi pada Jumat (7/8)</t>
+        </is>
+      </c>
+      <c r="F983" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G983" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264545/semburan-lumpur-muncul-di-oro-oro-kesongo-blora-tingginya-capai-15-meter</t>
+        </is>
+      </c>
+      <c r="H983" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/4f9af-MrpStT_8zlS_DoF-FL91w=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318534/original/023454400_1786101814-Screenshot_2026-08-07_181022.jpg</t>
+        </is>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>Kronologi Penumpang Batik Air Coba Buka Paksa Pintu Darurat di Udara</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:18:16 +0700</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr">
+        <is>
+          <t>Penumpang asal India itu sudah diserahkan ke polisi setelah pesawat mendarat.</t>
+        </is>
+      </c>
+      <c r="F984" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G984" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264514/kronologi-penumpang-batik-air-coba-buka-paksa-pintu-darurat-di-udara</t>
+        </is>
+      </c>
+      <c r="H984" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/Egh8Wx8nsUhNSNnKsHDdkpmm0k0=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318492/original/096117900_1786099339-WhatsApp_Image_2026-08-07_at_17.21.36.jpeg</t>
+        </is>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>Advertorial</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>Ngaben Massal Balinuraga, Daya Tarik Pelestarian Budaya Lampung Selatan yang Harus Dijaga</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:47:52 +0700</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr">
+        <is>
+          <t>Tradisi Ngaben Massal Balinuraga di Lampung Selatan disambut antusiasme tinggi para tamu dari berbagai daerah.</t>
+        </is>
+      </c>
+      <c r="F985" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G985" t="inlineStr">
+        <is>
+          <t>https://biz.kompas.com/read/2026/08/07/184730028/ngaben-massal-balinuraga-daya-tarik-pelestarian-budaya-lampung-selatan-yang</t>
+        </is>
+      </c>
+      <c r="H985" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/iDePvJEjt-CaraRXGbhP5oxo3is=/0x0:1200x800/1200x675/data/photo/2026/08/07/6a75c527688d4.jpg</t>
+        </is>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>Serangan Rudal Balistik dan Drone Houthi Tewaskan 17 Tentara Yaman</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:47:52 +0700</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>Sebanyak 17 tentara dan perwira Yaman tewas dan sejumlah lainnya terluka dalam serangan kelompok Houthi.</t>
+        </is>
+      </c>
+      <c r="F986" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G986" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/global/read/2026/08/07/182300770/serangan-rudal-balistik-dan-drone-houthi-tewaskan-17-tentara-yaman</t>
+        </is>
+      </c>
+      <c r="H986" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/XbVxYC5VqvTWAQjpCiz_063ZMV8=/0x0:2000x1333/1200x675/filters:watermark(data/photo/2026/01/30/697c81ac46b81.png,0,-0,1)/data/photo/2025/05/20/682c90e85896c.jpg</t>
+        </is>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>Otomotif</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>Lihat Deretan Mobil Klasik di GIIAS 2026, Ada Mobil Pertama di Dunia</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:47:52 +0700</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E987" t="inlineStr">
+        <is>
+          <t>Di tengah gempuran mobil berdesain futuristis, kehadiran sejumlah mobil klasik dan bersejarah justru sukses menyedot perhatian pengunjung</t>
+        </is>
+      </c>
+      <c r="F987" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G987" t="inlineStr">
+        <is>
+          <t>https://otomotif.kompas.com/read/2026/08/07/180100015/lihat-deretan-mobil-klasik-di-giias-2026-ada-mobil-pertama-di-dunia</t>
+        </is>
+      </c>
+      <c r="H987" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/yt9Rx26DLe74xPVQUU7XO7bjYyc=/21x14:1361x684/1200x675/filters:watermark(data/photo/2026/01/30/697c81750a668.png,0,-0,1)/data/photo/2026/08/07/6a759752e1ce2.png</t>
+        </is>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I832"/>
+  <autoFilter ref="A1:I987"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-07.xlsx
+++ b/data/berita_2026-08-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$987</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1067</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I987"/>
+  <dimension ref="A1:I1067"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -46822,8 +46822,3768 @@
         </is>
       </c>
     </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>Polri pastikan pemeriksaan anggota Polresta Banda Aceh transparan</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:35:08 +0700</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr">
+        <is>
+          <t>Polri memastikan pemeriksaan dua anggota Polresta Banda Aceh oleh Divisi Profesi dan Pengamanan (Divpropam) Polri ...</t>
+        </is>
+      </c>
+      <c r="F988" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G988" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684707/polri-pastikan-pemeriksaan-anggota-polresta-banda-aceh-transparan</t>
+        </is>
+      </c>
+      <c r="H988" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/1000086556.jpg</t>
+        </is>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>Bahlil tegaskan ekspor bauksit dan tembaga dilarang demi hilirisasi</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:34:54 +0700</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr">
+        <is>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia menegaskan pemerintah akan mempertahankan larangan ...</t>
+        </is>
+      </c>
+      <c r="F989" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G989" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684703/bahlil-tegaskan-ekspor-bauksit-dan-tembaga-dilarang-demi-hilirisasi</t>
+        </is>
+      </c>
+      <c r="H989" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_7687.jpg</t>
+        </is>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>BPOM: Apoteker perlu kuasai ATMP &amp; living therapy, dukung ketahanan RI</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:30:20 +0700</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr">
+        <is>
+          <t>Badan Pengawas Obat dan Makanan (BPOM) mengatakan seiring perkembangan teknologi peran apoteker juga semakin ...</t>
+        </is>
+      </c>
+      <c r="F990" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G990" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684700/bpom-apoteker-perlu-kuasai-atmp-living-therapy-dukung-ketahanan-ri</t>
+        </is>
+      </c>
+      <c r="H990" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1786099467196.jpg</t>
+        </is>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Analis BEI lihat peluang kinerja LQ45 tumbuh pada semester II 2026</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:30:09 +0700</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E991" t="inlineStr">
+        <is>
+          <t>Analis Senior Divisi Riset Bursa Efek Indonesia (BEI) Fikrian Naufal Hardiatmojo melihat peluang kinerja 45 saham ...</t>
+        </is>
+      </c>
+      <c r="F991" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G991" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684696/analis-bei-lihat-peluang-kinerja-lq45-tumbuh-pada-semester-ii-2026</t>
+        </is>
+      </c>
+      <c r="H991" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000178311.jpg</t>
+        </is>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>Danantara dan JBS Group kolaborasi pengembangan ekosistem protein RI</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:23:55 +0700</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr">
+        <is>
+          <t>Danantara Indonesia melalui Danantara Investment Management (DIM) menjalin kemitraan strategis jangka panjang ...</t>
+        </is>
+      </c>
+      <c r="F992" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G992" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684692/danantara-dan-jbs-group-kolaborasi-pengembangan-ekosistem-protein-ri</t>
+        </is>
+      </c>
+      <c r="H992" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/19/WhatsApp-Image-2025-11-19-at-14.11.00_83e2c60d_1.jpg</t>
+        </is>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>ESDM: Implementasi B50 hasil pengembangan yang panjang</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:23:49 +0700</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E993" t="inlineStr">
+        <is>
+          <t>Kementerian Energi dan Sumber Daya Mineral (ESDM) mengatakan bahwa implementasi biodiesel B50 merupakan hasil ...</t>
+        </is>
+      </c>
+      <c r="F993" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G993" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5684688/esdm-implementasi-b50-hasil-pengembangan-yang-panjang</t>
+        </is>
+      </c>
+      <c r="H993" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/10/penggunaan-b50-mobil-industri-semarang-100726-aaa-116.jpg</t>
+        </is>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>Pemkot Bandung: Pembelajaran siswa SDN 026 Bojongloa tetap berjalan</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:23:12 +0700</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E994" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Bandung memastikan proses kegiatan belajar sekitar 900 siswa SDN 026 Bojongloa harus tetap berjalan ...</t>
+        </is>
+      </c>
+      <c r="F994" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G994" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684684/pemkot-bandung-pembelajaran-siswa-sdn-026-bojongloa-tetap-berjalan</t>
+        </is>
+      </c>
+      <c r="H994" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_9198.jpeg</t>
+        </is>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>Temuan senjata api, Yayasan minta polisi lakukan sterilisasi sekolah</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:20:51 +0700</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E995" t="inlineStr">
+        <is>
+          <t>Kuasa hukum yayasan sekolah swasta di kawasan Pondok Pinang, Kebayoran Lama, Jakarta Selatan meminta kepolisian ...</t>
+        </is>
+      </c>
+      <c r="F995" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G995" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684675/temuan-senjata-api-yayasan-minta-polisi-lakukan-sterilisasi-sekolah</t>
+        </is>
+      </c>
+      <c r="H995" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001016766.jpg</t>
+        </is>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>FAA perintahkan inspeksi pesawat Boeing 737 MAX terkait retakan</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:15:31 +0700</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E996" t="inlineStr">
+        <is>
+          <t>Administrasi Penerbangan Federal (Federal Aviation Administration/FAA) Amerika Serikat (AS) telah memerintahkan ...</t>
+        </is>
+      </c>
+      <c r="F996" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G996" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684672/faa-perintahkan-inspeksi-pesawat-boeing-737-max-terkait-retakan</t>
+        </is>
+      </c>
+      <c r="H996" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2021/12/19/Xinhua-News-Agency.jpg</t>
+        </is>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>Amartha komitmen dukung gaya hidup sehat lewat Amartha 10X Run 2026</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:13:45 +0700</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>Senior Vice President (SVP) Growth &amp; Marketing Amartha Financial Sheldon Chuan mengatakan perusahaan tersebut ...</t>
+        </is>
+      </c>
+      <c r="F997" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G997" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684668/amartha-komitmen-dukung-gaya-hidup-sehat-lewat-amartha-10x-run-2026</t>
+        </is>
+      </c>
+      <c r="H997" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000475673.jpg</t>
+        </is>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>Legislator DKI dukung deklarasi perangi peredaran tramadol ilegal</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:12:20 +0700</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E998" t="inlineStr">
+        <is>
+          <t>Anggota Komisi B DPRD DKI Jakarta, Wa Ode Herlina mendukung deklarasi yang dilakukan Forum Koordinasi Pimpinan Kota ...</t>
+        </is>
+      </c>
+      <c r="F998" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G998" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684664/legislator-dki-dukung-deklarasi-perangi-peredaran-tramadol-ilegal</t>
+        </is>
+      </c>
+      <c r="H998" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000833694.jpg</t>
+        </is>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>Isuzu mu-X terbaru dipamerkan di GIIAS 2026</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:11:33 +0700</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E999" t="inlineStr">
+        <is>
+          <t>PT Isuzu Astra Motor Indonesia memamerkan Isuzu mu-X terbaru di ajang Gaikindo Indonesia International Auto Show ...</t>
+        </is>
+      </c>
+      <c r="F999" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G999" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5684663/isuzu-mu-x-terbaru-dipamerkan-di-giias-2026</t>
+        </is>
+      </c>
+      <c r="H999" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Photo-2-New-Isuzu-mu-X.jpg</t>
+        </is>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>Sedikitnya tujuh tewas dalam penembakan di sekolah Thailand</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:11:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr">
+        <is>
+          <t>ANTARA - Sedikitnya tujuh orang tewas dalam insiden penembakan di Sekolah Debsirin, Provinsi Nonthaburi, Thailand, ...</t>
+        </is>
+      </c>
+      <c r="F1000" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1000" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5684575/sedikitnya-tujuh-tewas-dalam-penembakan-di-sekolah-thailand</t>
+        </is>
+      </c>
+      <c r="H1000" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SEDIKITNYA-TUJUH-TEWAS-DALAM-PENEMBAKAN-DI-SEKOLAH-THAILAND.jpg</t>
+        </is>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>Perdagangan luar negeri China tumbuh 19,2 persen pada Juli 2026</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:10:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1001" t="inlineStr">
+        <is>
+          <t>Data Administrasi Umum Kepabeanan (General Administration of Customs/GAC) China yang dirilis pada Jumat (7/8) ...</t>
+        </is>
+      </c>
+      <c r="F1001" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1001" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684659/perdagangan-luar-negeri-china-tumbuh-192-persen-pada-juli-2026</t>
+        </is>
+      </c>
+      <c r="H1001" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/CjkinzN000016_20260807_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>Apakah gula aren lebih baik dari gula putih? Ini faktanya</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:09:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1002" t="inlineStr">
+        <is>
+          <t>Belakangan ini, gula aren semakin populer sebagai pemanis alami untuk berbagai makanan dan minuman. Mulai dari kopi ...</t>
+        </is>
+      </c>
+      <c r="F1002" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1002" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684656/apakah-gula-aren-lebih-baik-dari-gula-putih-ini-faktanya</t>
+        </is>
+      </c>
+      <c r="H1002" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/04/gula-merah-ppu.jpeg</t>
+        </is>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Ideatax sebut penundaan PPh lokapasar beri ruang penyempurnaan</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:07:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>Praktisi perpajakan yang juga Managing Partner Ideatax Jonathan Nainggolan mengatakan keputusan pemerintah menunda ...</t>
+        </is>
+      </c>
+      <c r="F1003" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1003" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684653/ideatax-sebut-penundaan-pph-lokapasar-beri-ruang-penyempurnaan</t>
+        </is>
+      </c>
+      <c r="H1003" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/Pemerintah-Tunda-Penerapan-Pajak-Lokapasar-060826-DAN-03.jpg</t>
+        </is>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>Bupati Bogor-KSAD tanda tangani pengolahan sampah jadi BBM</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:07:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1004" t="inlineStr">
+        <is>
+          <t>Bupati Bogor Rudy Susmanto dan Kepala Staf Angkatan Darat (KSAD) Jenderal TNI Maruli Simanjuntak menandatangani kerja ...</t>
+        </is>
+      </c>
+      <c r="F1004" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1004" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684651/bupati-bogor-ksad-tanda-tangani-pengolahan-sampah-jadi-bbm</t>
+        </is>
+      </c>
+      <c r="H1004" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1003321321.jpg</t>
+        </is>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>Bank BSN Catat Tingkat Keterhunian Rumah Subsidi Capai 92,58 Persen</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:05:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1005" t="inlineStr">
+        <is>
+          <t>Jakarta (ANTARA) – PT Bank Syariah Nasional (Bank BSN) mencatat tingkat validasi elektronik monitoring dan ...</t>
+        </is>
+      </c>
+      <c r="F1005" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1005" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684645/bank-bsn-catat-tingkat-keterhunian-rumah-subsidi-capai-9258-persen</t>
+        </is>
+      </c>
+      <c r="H1005" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-18.48.57-1.jpeg</t>
+        </is>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>Angkutan Retail KAI Capai 146.617 Ton, Naik 19,59 Persen dalam Dua Tahun</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:00:13 +0700</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1006" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia (Persero) mencatat volume angkutan retail sebesar 146.617 ton sepanjang Januari–Juli ...</t>
+        </is>
+      </c>
+      <c r="F1006" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1006" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684641/angkutan-retail-kai-capai-146617-ton-naik-1959-persen-dalam-dua-tahun</t>
+        </is>
+      </c>
+      <c r="H1006" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-18.07.58.jpeg</t>
+        </is>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>DPR minta usut tuntas kasus temuan senjata demi keamanan pendidikan</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:59:44 +0700</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1007" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi X DPR RI Lalu Hadrian Irfani meminta kepada aparat untuk mengusut tuntas kasus temuan ratusan ...</t>
+        </is>
+      </c>
+      <c r="F1007" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1007" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684639/dpr-minta-usut-tuntas-kasus-temuan-senjata-demi-keamanan-pendidikan</t>
+        </is>
+      </c>
+      <c r="H1007" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/656463b7-bd6c-46b6-9ad6-409fe8b6dcb2.jpg</t>
+        </is>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>Pelanggan KA Lokal Bandung Raya Tembus 11,87 Juta, KAI Dorong Infrastruktur Berbasis Kebutuhan</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:57:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia (Persero) mencatat kebutuhan masyarakat terhadap layanan kereta api di kawasan Bandung Raya ...</t>
+        </is>
+      </c>
+      <c r="F1008" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1008" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684637/pelanggan-ka-lokal-bandung-raya-tembus-1187-juta-kai-dorong-infrastruktur-berbasis-kebutuhan</t>
+        </is>
+      </c>
+      <c r="H1008" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/KA-LOKAL-BANDUNG-RAYA.jpg</t>
+        </is>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>PLN perluas infrastruktur pengisian daya kendaraan listrik</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:56:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1009" t="inlineStr">
+        <is>
+          <t>PT Perusahaan Listrik Negara (Persero) atau PLN memperluas infrastruktur pengisian daya kendaraan listrik sebagai upaya ...</t>
+        </is>
+      </c>
+      <c r="F1009" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1009" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684635/pln-perluas-infrastruktur-pengisian-daya-kendaraan-listrik</t>
+        </is>
+      </c>
+      <c r="H1009" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/SPKLUGIIAS.jpg</t>
+        </is>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>Prabowo minta Bahlil Lahadalia teruskan pengabdian terbaik bagi negara</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:52:44 +0700</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1010" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto meminta Ketua Umum Partai Golkar sekaligus Menteri ESDM Bahlil Lahadalia untuk terus ...</t>
+        </is>
+      </c>
+      <c r="F1010" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1010" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684632/prabowo-minta-bahlil-lahadalia-teruskan-pengabdian-terbaik-bagi-negara</t>
+        </is>
+      </c>
+      <c r="H1010" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Peluncuran-10-buku-karya-nyata-untuk-negeri-Bahlil-Lahadalia-070826-Ada-1.jpg</t>
+        </is>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>Airlangga: Indonesia miliki KEK siap dimanfaatkan sektor industri</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:52:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>Menteri Kordinator Bidang Perekonomian Airlangga Hartarto menegaskan bahwa pemerintah Indonesia memiliki Kawasan ...</t>
+        </is>
+      </c>
+      <c r="F1011" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1011" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5684629/airlangga-indonesia-miliki-kek-siap-dimanfaatkan-sektor-industri</t>
+        </is>
+      </c>
+      <c r="H1011" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_1374.jpeg</t>
+        </is>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>Otto tekankan pentingnya kewenangan dan harmonisasi dalam regulasi</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:51:08 +0700</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Koordinator Bidang Hukum, HAM, Imigrasi, dan Pemasyarakatan Otto Hasibuan menekankan pentingnya ...</t>
+        </is>
+      </c>
+      <c r="F1012" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1012" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684627/otto-tekankan-pentingnya-kewenangan-dan-harmonisasi-dalam-regulasi</t>
+        </is>
+      </c>
+      <c r="H1012" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000474664.jpg</t>
+        </is>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>Pemkot Cirebon lanjutkan GPM hingga akhir 2026 jaga daya beli warga</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:50:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>Pemerintah Kota Cirebon, Jawa Barat, memastikan program Gerakan Pangan Murah (GPM) terus dilaksanakan hingga akhir 2026 ...</t>
+        </is>
+      </c>
+      <c r="F1013" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1013" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684624/pemkot-cirebon-lanjutkan-gpm-hingga-akhir-2026-jaga-daya-beli-warga</t>
+        </is>
+      </c>
+      <c r="H1013" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001522792.jpg</t>
+        </is>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>12.957 Pelamar Ikuti Rekrutmen PJL KAI, Perkuat Keselamatan sekaligus Buka Kesempatan Kerja</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:49:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>PT Kereta Api Indonesia (Persero) melanjutkan penguatan keselamatan perlintasan sebidang melalui pemenuhan kebutuhan ...</t>
+        </is>
+      </c>
+      <c r="F1014" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1014" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684620/12957-pelamar-ikuti-rekrutmen-pjl-kai-perkuat-keselamatan-sekaligus-buka-kesempatan-kerja</t>
+        </is>
+      </c>
+      <c r="H1014" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-18.07.56.jpeg</t>
+        </is>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>SP Palu dampingi pekerja migran Sigi terkait pelanggaran hak</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:49:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>Solidaritas Perempuan (SP) Palu mendampingi seorang pekerja migran perempuan asal Kabupaten Sigi, Sulawesi Tengah, ...</t>
+        </is>
+      </c>
+      <c r="F1015" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1015" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684619/sp-palu-dampingi-pekerja-migran-sigi-terkait-pelanggaran-hak</t>
+        </is>
+      </c>
+      <c r="H1015" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/ec28b584-1895-4c8c-a977-f88d6f01abfd.jpeg</t>
+        </is>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>Prabowo ungkap rumus bernegara dari mantan Gubernur NTT Ben Mboi</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:45:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto membagikan dua rumus penting bernegara yang diperoleh dari tokoh senior Ben Mboi untuk ...</t>
+        </is>
+      </c>
+      <c r="F1016" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1016" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684617/prabowo-ungkap-rumus-bernegara-dari-mantan-gubernur-ntt-ben-mboi</t>
+        </is>
+      </c>
+      <c r="H1016" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Peluncuran-10-buku-karya-nyata-untuk-negeri-Bahlil-Lahadalia-070826-Ada-6_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>Berkas tersangka anak kasus santri terbakar dilimpahkan ke jaksa</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:45:53 +0700</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>Penyidik Direktorat Reserse Perlindungan Perempuan dan Anak serta Pemberantasan Perdagangan Orang Polda Nusa Tenggara ...</t>
+        </is>
+      </c>
+      <c r="F1017" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1017" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684616/berkas-tersangka-anak-kasus-santri-terbakar-dilimpahkan-ke-jaksa</t>
+        </is>
+      </c>
+      <c r="H1017" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/MG_3083.jpg</t>
+        </is>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>Bupati Manokwari: Festival Kopi Manokwari akselerasi pengembangan UMKM</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:45:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1018" t="inlineStr">
+        <is>
+          <t>Bupati Manokwari Hermus Indou mengatakan penyelenggaraan Festival Kopi Manokwari 2026 merupakan salah satu strategi ...</t>
+        </is>
+      </c>
+      <c r="F1018" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1018" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684615/bupati-manokwari-festival-kopi-manokwari-akselerasi-pengembangan-umkm</t>
+        </is>
+      </c>
+      <c r="H1018" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/FotoJet-2.jpg</t>
+        </is>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>Kenapa bantal tidur cepat menguning? Ini penyebabnya</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:44:08 +0700</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>Bantal tidur yang awalnya berwarna putih sering berubah menjadi kuning setelah digunakan dalam waktu tertentu. ...</t>
+        </is>
+      </c>
+      <c r="F1019" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1019" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684611/kenapa-bantal-tidur-cepat-menguning-ini-penyebabnya</t>
+        </is>
+      </c>
+      <c r="H1019" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/03/16/tidur_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>Operasi gabungan Polda Jabar ungkap ratusan kejahatan jalanan, kendaraan dan senjata disita dari para pelaku</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:41:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr">
+        <is>
+          <t>Sejumlah pelaku kejahatan jalanan dihadirkan saat rilis pengungkapan kasus kejahatan jalanan di Mapolda Jabar, Bandung, ...</t>
+        </is>
+      </c>
+      <c r="F1020" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1020" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5684607/operasi-gabungan-polda-jabar-ungkap-ratusan-kejahatan-jalanan-kendaraan-dan-senjata-disita-dari-para-pelaku</t>
+        </is>
+      </c>
+      <c r="H1020" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Rilis-pengungkapan-kasus-kejahatan-jalanan-di-Polda-Jabar-070826-NA-4.jpg</t>
+        </is>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>BGN berhentikan 66 kepala dapur MBG atas tindakan tidak disiplin</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:40:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1021" t="inlineStr">
+        <is>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono menyatakan pihaknya telah memberhentikan 66 Sarjana Penggerak Pembangunan ...</t>
+        </is>
+      </c>
+      <c r="F1021" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1021" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684604/bgn-berhentikan-66-kepala-dapur-mbg-atas-tindakan-tidak-disiplin</t>
+        </is>
+      </c>
+      <c r="H1021" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/20260807_161317.jpg</t>
+        </is>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>Bappenas dukung Papeda Summit 2026 di Sorong</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:40:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr">
+        <is>
+          <t>Kementerian Perencanaan Pembangunan Nasional/Badan Perencanaan Pembangunan Nasional (PPN/Bappenas) menyatakan dukungan ...</t>
+        </is>
+      </c>
+      <c r="F1022" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1022" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684601/bappenas-dukung-papeda-summit-2026-di-sorong</t>
+        </is>
+      </c>
+      <c r="H1022" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-3.54.43-PM.jpeg</t>
+        </is>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>IHSG ditutup menguat ke level tertinggi tiga bulan, sinyal positif pasar saham kian menguat</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:38:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr">
+        <is>
+          <t>Pengunjung memotret layar pergerakan Indeks Harga Saham Gabungan (IHSG) di Bursa Efek Indonesia (BEI), Jakarta, ...</t>
+        </is>
+      </c>
+      <c r="F1023" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1023" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5684599/ihsg-ditutup-menguat-ke-level-tertinggi-tiga-bulan-sinyal-positif-pasar-saham-kian-menguat</t>
+        </is>
+      </c>
+      <c r="H1023" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IHSG-ditutup-menguat-65-94-poin-070826-Fah-1.jpg</t>
+        </is>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>Menpora dukung promotor hadirkan laga pramusim di Indonesia</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:38:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr">
+        <is>
+          <t>Menteri Pemuda dan Olahraga Erick Thohir mendukung pihak perusahaan-perusahaan promotor swasta untuk menghadirkan laga ...</t>
+        </is>
+      </c>
+      <c r="F1024" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1024" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684596/menpora-dukung-promotor-hadirkan-laga-pramusim-di-indonesia</t>
+        </is>
+      </c>
+      <c r="H1024" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/01/aston-villa-menang-atas-indonesia-all-stars-2832201.jpg</t>
+        </is>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>Pemprov dorong SBI optimalkan produksi semen penuhi kebutuhan Aceh</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:37:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr">
+        <is>
+          <t>Pemerintah Aceh mendorong PT Solusi Bangun Indonesia (SBI) melalui anak perusahaannya PT Solusi Bangun Andalas (SBA) ...</t>
+        </is>
+      </c>
+      <c r="F1025" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1025" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684593/pemprov-dorong-sbi-optimalkan-produksi-semen-penuhi-kebutuhan-aceh</t>
+        </is>
+      </c>
+      <c r="H1025" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG-20260807-WA0022.jpg</t>
+        </is>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>114 Dapur MBG di Papua hingga NTT Akan Beroperasi Pekan Depan</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:27:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E1026" t="inlineStr">
+        <is>
+          <t>BGN akan mengaktifkan 114 dapur MBG pekan depan. Dapur tersebut tersebar di sejumlah wilayah, termasuk Papua, Nusa Tenggara Timur (NTT), dan Maluku.</t>
+        </is>
+      </c>
+      <c r="F1026" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1026" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609046/114-dapur-mbg-di-papua-hingga-ntt-akan-beroperasi-pekan-depan</t>
+        </is>
+      </c>
+      <c r="H1026" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kepala-bgn-sudaryono-brigittadetikcom-1786101809094_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>Bima Arya Dorong Penghijauan Jadi Gerakan Berkelanjutan di Daerah</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:09:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E1027" t="inlineStr">
+        <is>
+          <t>Wamendagri Bima Arya dorong Pemda untuk penghijauan berkelanjutan. Kolaborasi lintas sektor penting untuk keberhasilan rehabilitasi hutan dan lahan.</t>
+        </is>
+      </c>
+      <c r="F1027" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1027" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609032/bima-arya-dorong-penghijauan-jadi-gerakan-berkelanjutan-di-daerah</t>
+        </is>
+      </c>
+      <c r="H1027" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/wakil-menteri-dalam-negeri-wamendagri-bima-arya-sugiarto-1786104463489.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>Menilik Ruangan Ditemukan Senjata di Sekolah Swasta Jaksel, Kini Digaris Polisi</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:09:08 +0700</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr">
+        <is>
+          <t>Taufiq Syarifudin</t>
+        </is>
+      </c>
+      <c r="E1028" t="inlineStr">
+        <is>
+          <t>Sekolah swasta di Pondok Pinang, Jakarta Selatan dihebohkan karena ditemukan 995 senjata. Kini ruangan tersebut digaris polisi.</t>
+        </is>
+      </c>
+      <c r="F1028" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1028" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609029/menilik-ruangan-ditemukan-senjata-di-sekolah-swasta-jaksel-kini-digaris-polisi</t>
+        </is>
+      </c>
+      <c r="H1028" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/ruangan-mantan-kepala-yayasan-ditemukannya-senjata-di-sekolah-swasta-jaksel-taufiqdetikcom-1786104460641_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>Solusi 4C Lintasarta Bantu Bank Daerah Kebut Transformasi Digital</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:07:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>Bank Pembangunan Daerah didorong untuk percepat transformasi digital guna tingkatkan layanan dan peran ekonomi.</t>
+        </is>
+      </c>
+      <c r="F1029" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1029" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609026/solusi-4c-lintasarta-bantu-bank-daerah-kebut-transformasi-digital</t>
+        </is>
+      </c>
+      <c r="H1029" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/lintasarta-cxo-bpd-summit-2026-1786016739700_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>Kebakaran di Suryakencana Gunung Gede Capai 1 Hektar, 5 Meter dari Taman Edelweiss</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:57:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr">
+        <is>
+          <t>Muchamad Sholihin</t>
+        </is>
+      </c>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>Kebakaran di alun-alun Suryakencana Gunung Gede melanda area seluas 1 hektar. Lokasi kebakaran hanya berjarak 5 meter dari Taman Edelweiss.</t>
+        </is>
+      </c>
+      <c r="F1030" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1030" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609008/kebakaran-di-suryakencana-gunung-gede-capai-1-hektar-5-meter-dari-taman-edelweiss</t>
+        </is>
+      </c>
+      <c r="H1030" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/gunung-gede-pangrango-kebakaran-1786025219821_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>Lintasarta Dorong Bank Daerah Tingkatkan Ketahanan Siber dan AI</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:57:13 +0700</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E1031" t="inlineStr">
+        <is>
+          <t>Lintasarta dan ASBANDA tandatangani MoU di CxO BPD Summit 2026 untuk transformasi digital BPD, fokus pada ketahanan siber dan pemanfaatan AI.</t>
+        </is>
+      </c>
+      <c r="F1031" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1031" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609007/lintasarta-dorong-bank-daerah-tingkatkan-ketahanan-siber-dan-ai</t>
+        </is>
+      </c>
+      <c r="H1031" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/lintasarta-cxo-bpd-summit-2026-1786016739700.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>Polisi Sebut Ada Pihak Sengaja Pesan Konten Hoax: Berpotensi Gaduh!</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:53:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E1032" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya ungkap kasus penyebaran konten hoax di medsos. 28 orang diamankan, 10 diproses hukum. Polisi imbau masyarakat bijak menggunakan medsos.</t>
+        </is>
+      </c>
+      <c r="F1032" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1032" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609004/polisi-sebut-ada-pihak-sengaja-pesan-konten-hoax-berpotensi-gaduh</t>
+        </is>
+      </c>
+      <c r="H1032" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/dirkrimum-polda-metro-jaya-kombes-iman-imanuddin-1786096322096_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>BGN Pecat 66 Kepala Dapur MBG, Terlibat Judol hingga 'Hengki Pengki'</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:49:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>BGN memproses pemecatan 66 kepala dapur MBG yang melakukan pelanggaran. Pelanggarannya ada yang terlibat judi online hingga 'hengki pengki'.</t>
+        </is>
+      </c>
+      <c r="F1033" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1033" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609001/bgn-pecat-66-kepala-dapur-mbg-terlibat-judol-hingga-hengki-pengki</t>
+        </is>
+      </c>
+      <c r="H1033" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/tancap-gas-kepala-bgn-sudaryono-pecat-261-pegawai-bermasalah-1785138053252_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>Prabowo Ultimatum Kepala Daerah: Tak Bisa Penuhi Teriakan Rakyat, Presiden Turun Tangan</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:42:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo memberi ultimatum kepada kepala daerah untuk memenuhi kebutuhan rakyat. Jika tidak, pemerintah pusat akan turun tangan membangun infrastruktur.</t>
+        </is>
+      </c>
+      <c r="F1034" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1034" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8608989/prabowo-ultimatum-kepala-daerah-tak-bisa-penuhi-teriakan-rakyat-presiden-turun-tangan</t>
+        </is>
+      </c>
+      <c r="H1034" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/prabowo-subianto-evadetikcom-1786092746269_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>Luhut Cerita Dulu RI Ditertawakan soal Nikel, Kini Dunia Datang Investasi</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:30:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr">
+        <is>
+          <t>Heri Purnomo</t>
+        </is>
+      </c>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>Luhut Binsar Pandjaitan membahas larangan ekspor biji nikel yang menuai kritik.</t>
+        </is>
+      </c>
+      <c r="F1035" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1035" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8608990/luhut-cerita-dulu-ri-ditertawakan-soal-nikel-kini-dunia-datang-investasi</t>
+        </is>
+      </c>
+      <c r="H1035" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/06/24/ketua-dewan-ekonomi-nasional-den-luhut-binsar-pandjaitan-1782274037708_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>Freeport Mundurkan Produksi Tambang Kucing Liar ke 2029</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:00:44 +0700</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E1036" t="inlineStr">
+        <is>
+          <t>PT Freeport Indonesia memastikan produksi tambang Kucing Liar di Grasberg mundur ke 2029. Perpanjangan izin usaha juga diajukan untuk kelangsungan operasional.</t>
+        </is>
+      </c>
+      <c r="F1036" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1036" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8608967/freeport-mundurkan-produksi-tambang-kucing-liar-ke-2029</t>
+        </is>
+      </c>
+      <c r="H1036" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/presiden-direktur-pt-freeport-indonesia-ptfi-tony-wenas-1786101675207_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>Kekecewaan Pihak Asisten Nikita Mirzani, Sidang PK TPPU Ditunda</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:08:48 +0700</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E1037" t="inlineStr">
+        <is>
+          <t>Ismail Marzuki, asisten Nikita Mirzani, ajukan Peninjauan Kembali atas dugaan pemerasan dan TPPU. Sidang perdana digelar di Jakarta Selatan.</t>
+        </is>
+      </c>
+      <c r="F1037" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1037" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608627/kekecewaan-pihak-asisten-nikita-mirzani-sidang-pk-tppu-ditunda</t>
+        </is>
+      </c>
+      <c r="H1037" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/07/24/nikita-mirzani-jalani-sidang-ttpu-1753328999013_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>Pihak Sekolah di Jaksel Klarifikasi, Bunker Sudah Diperiksa Polisi</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:33:46 +0700</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>Pihak sekolah swasta di Jakarta memastikan bunker yang diduga menyimpan senjata telah diperiksa polisi. Ratusan senjata dan narkoba ditemukan di lokasi.</t>
+        </is>
+      </c>
+      <c r="F1038" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1038" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807182957-12-1389874/pihak-sekolah-di-jaksel-klarifikasi-bunker-sudah-diperiksa-polisi</t>
+        </is>
+      </c>
+      <c r="H1038" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/ratusan-senjata-di-yayasan-sekolah-jaksel-1786100090384_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>Kapolresta dan Kasat Narkoba Banda Aceh Masih Diperiksa di Mabes Polri</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:29:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>Kapolresta Banda Aceh dan Kasat Resnarkoba diperiksa Propam Mabes Polri. Proses dilakukan transparan dan profesional, menunggu hasil resmi untuk publik.</t>
+        </is>
+      </c>
+      <c r="F1039" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1039" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807191947-12-1389914/kapolresta-dan-kasat-narkoba-banda-aceh-masih-diperiksa-di-mabes-polri</t>
+        </is>
+      </c>
+      <c r="H1039" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/09/03/pengamanan-sidang-etik-penabrak-sopir-ojek-daring-di-tncc-polri-1756878770745_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>Polda Metro Tindak 28 Pegiat Medsos Sebar Provokasi-Hoaks, 9 Tersangka</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:08:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1040" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya menindak 28 pegiat medsos terkait penyebaran hoaks. Sembilan orang ditetapkan sebagai tersangka, sementara 30 konten telah diturunkan.</t>
+        </is>
+      </c>
+      <c r="F1040" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1040" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807185640-12-1389889/polda-metro-tindak-28-pegiat-medsos-sebar-provokasi-hoaks-9-tersangka</t>
+        </is>
+      </c>
+      <c r="H1040" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2022/09/12/ilustrasi-hacker-ilustrasi-serangan-siber-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>Penampakan Ruang Penyimpanan Ratusan Senjata di Yayasan Sekolah</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:56:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr">
+        <is>
+          <t>Penampakan dua ruangan yang ditemukan ratusan senjata dan narkoba di salah satu sekolah swasta di Pondok Pinang, Jaksel, Jumat (7/8).</t>
+        </is>
+      </c>
+      <c r="F1041" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1041" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807182953-16-1389873/penampakan-ruang-penyimpanan-ratusan-senjata-di-yayasan-sekolah</t>
+        </is>
+      </c>
+      <c r="H1041" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/penampakan-ruangan-penyimpanan-ratusan-senjata-di-sekolah-jaksel-1786102460839_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>Kebakaran di Alun-alun Suryakencana Gunung Gede Sudah Padam</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:45:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr">
+        <is>
+          <t>Kebakaran lahan di Alun-Alun Suryakencana, Taman Nasional Gunung Gede Pangrango, berhasil dikendalikan. Penyebab kebakaran masih dalam penyelidikan.</t>
+        </is>
+      </c>
+      <c r="F1042" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1042" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807173650-20-1389877/kebakaran-di-alun-alun-suryakencana-gunung-gede-sudah-padam</t>
+        </is>
+      </c>
+      <c r="H1042" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/bb-tnggp-tutup-jalur-pendakian-karena-kebakaran-alun-alun-suryakancana-1786099073263_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>30 Puisi Cinta Romantis yang Menyentuh Hati, Penuh Makna tentang Rindu dan Kesetiaan</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:33:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1043" t="inlineStr">
+        <is>
+          <t>Puisi cinta menjadi salah satu cara indah untuk mengungkapkan perasaan yang sulit disampaikan melalui kata-kata biasa, inilah 30 puisi cinta romantis.</t>
+        </is>
+      </c>
+      <c r="F1043" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1043" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865458/30-puisi-cinta-romantis-yang-menyentuh-hati-penuh-makna-tentang-rindu-dan-kesetiaan</t>
+        </is>
+      </c>
+      <c r="H1043" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/oex3nTadQ4mlr7fG6Zffxm4z76U=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Promo-Valentine-Day-di-Georgia-Florist-Semarang_20250131_152414.jpg</t>
+        </is>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>Susy Susanti Perluas Pembinaan Olahraga, Bisbol Jadi Program Baru ASNA Academy</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:29:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>Susy mengatakan Jepang dipilih karena memiliki sistem pembinaan bisbol yang matang dan pengalaman panjang dalam mencetak atlet berprestasi.</t>
+        </is>
+      </c>
+      <c r="F1044" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1044" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7865457/susy-susanti-perluas-pembinaan-olahraga-bisbol-jadi-program-baru-asna-academy</t>
+        </is>
+      </c>
+      <c r="H1044" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/tnYIWXvBd7AMdDkD6BtsjG5l6lI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Legenda-pebulutangkis-Indonesia-Susy-Susanti-dan-Alan-Budikusuma-2121.jpg</t>
+        </is>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>Wujud Kolaborasi JKN dan Pemda dari 0 KM Indonesia: Peresmian Taman Budaya Gotong Royong di Sabang</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:28:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1045" t="inlineStr">
+        <is>
+          <t>Taman Budaya Gotong Royong mencerminkan falsafah luhur Indonesia yang menjadi fondasi penyelenggaraan Program JKN.</t>
+        </is>
+      </c>
+      <c r="F1045" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1045" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865456/wujud-kolaborasi-jkn-dan-pemda-dari-0-km-indonesia-peresmian-taman-budaya-gotong-royong-di-sabang</t>
+        </is>
+      </c>
+      <c r="H1045" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/7TC5Iu6tiadTOpohRO-WVzndXEE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/eresmikan-Taman-Budaya-Gotong-Royong-dan-Prasasti-INISIATIF-BPJS-Kesehatan.jpg</t>
+        </is>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>SUV 7-Seater yang Wajib Anda Test Drive di GIIAS 2026, dari New XL7 Hybrid Sampai Eksion PHEV</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:28:13 +0700</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1046" t="inlineStr">
+        <is>
+          <t>Pameran otomotif GIIAS 2026 menawarkan puluhan kendaraan model terbaru dari berbagai kategori dan powertrain untuk di-test drive pengunjung</t>
+        </is>
+      </c>
+      <c r="F1046" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1046" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/otomotif/7865455/suv-7-seater-yang-wajib-anda-test-drive-di-giias-2026-dari-new-xl7-hybrid-sampai-eksion-phev</t>
+        </is>
+      </c>
+      <c r="H1046" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/oHHLc5CsdCHeaXW6QiTw-8hNplM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/XL7-Hybrid-di-pameran-GIIAS-2026-BSD-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>Susunan Pemain Timnas Indonesia vs Singapura: Cahya Gantikan Nadeo, Jordi Amat Diistirahatkan</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:28:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1047" t="inlineStr">
+        <is>
+          <t>Starting XI Timnas Indonesia vs Singapura resmi dirilis. John Herdman merotasi kiper dan lini belakang demi Garuda lolos ke semifinal Piala AFF 2026.</t>
+        </is>
+      </c>
+      <c r="F1047" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1047" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7865454/susunan-pemain-timnas-indonesia-vs-singapura-cahya-gantikan-nadeo-jordi-amat-diistirahatkan</t>
+        </is>
+      </c>
+      <c r="H1047" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/yNQRBwgJz2YPPsUobmy3fY0wL6Y=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Piala-AFF-2026-Timnas-Indonesia-Tekuk-Timor-Leste-3-0_20260731_231927.jpg</t>
+        </is>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>Misi Ussy Sulistiawaty di Event Lari 10K Bareng Suami: Harus Bisa Sejajar dan Happy</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:27:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1048" t="inlineStr">
+        <is>
+          <t>Sebagai pelari yang lebih terbiasa, Ussy harus menahan kecepatan larinya agar Andhika bisa berlari sejajar dengannya dan tidak ngos-ngosan.</t>
+        </is>
+      </c>
+      <c r="F1048" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1048" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865453/misi-ussy-sulistiawaty-di-event-lari-10k-bareng-suami-harus-bisa-sejajar-dan-happy</t>
+        </is>
+      </c>
+      <c r="H1048" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/5VzrzJf_FTWayAtjNEkYAwmZK70=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ussy-Sulistiawaty-1-07082026.jpg</t>
+        </is>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>Persaingan Memanas, 18 Atlet Berebut Super Tiket Audisi PB Djarum di Makassar</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:26:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1049" t="inlineStr">
+        <is>
+          <t>Hingga Jumat (7/8/2026), sebanyak 18 atlet tersisa dan akan memperebutkan tiket menuju tahap berikutnya di GOR Dafest Makassar</t>
+        </is>
+      </c>
+      <c r="F1049" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1049" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7865452/persaingan-memanas-18-atlet-berebut-super-tiket-audisi-pb-djarum-di-makassar</t>
+        </is>
+      </c>
+      <c r="H1049" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/QvZlTzRm1f76ec7JobnUNgsVr2s=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Super-Tiket-pada-Audisi-Umum-PB-Djarum-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I1049" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>Istana Tak Mau Komentari Soal Nobel MBG: Pemerintah Fokus Jalankan Program</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:21:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1050" t="inlineStr">
+        <is>
+          <t>Pras enggan mengomentari dugaan adanya pencatutan nama presiden dalam makalah MBG yang disebut untuk dinominasikan dalam Nobel Perdamaian 2026.</t>
+        </is>
+      </c>
+      <c r="F1050" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1050" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865451/istana-tak-mau-komentari-soal-nobel-mbg-pemerintah-fokus-jalankan-program</t>
+        </is>
+      </c>
+      <c r="H1050" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/hH7V60ix95CcR0SInm1prH87c_M=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Prasetyo-Hadi-di-Wisma-Negara-Komplek-Istana-07082026.jpg</t>
+        </is>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>Kepala BGN Sampaikan Permintaan Maaf Terbuka ke Keluarga Korban Keracunan MBG di Papua Hingga Jogja</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:21:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1051" t="inlineStr">
+        <is>
+          <t>Sudaryono menyampaikan permohonan maaf secara terbuka kepada seluruh korban dan pihak keluarga atas insiden keracunan Program MBG.</t>
+        </is>
+      </c>
+      <c r="F1051" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1051" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865450/kepala-bgn-sampaikan-permintaan-maaf-terbuka-ke-keluarga-korban-keracunan-mbg-di-papua-hingga-jogja</t>
+        </is>
+      </c>
+      <c r="H1051" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Y5lgDd3Odghq_xVmdEJ68vikNT0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Konferensi-Pers-Kepala-BGN-Sudaryono_20260727_165349.jpg</t>
+        </is>
+      </c>
+      <c r="I1051" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>Menpora Erick: Indonesia Makin Diminati sebagai Lokasi  Pramusim Internasional, Ini Sinyal Positif</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:20:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>Tren tersebut menjadi tanda bahwa atmosfer sepak bola dan industri olahraga Indonesia makin mendapat pengakuan dunia.</t>
+        </is>
+      </c>
+      <c r="F1052" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1052" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865449/menpora-erick-indonesia-makin-diminati-sebagai-lokasi-pramusim-internasional-ini-sinyal-positif</t>
+        </is>
+      </c>
+      <c r="H1052" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/gtfZaVm82NqrBbI30YP2j6YmRJk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Menpora-Erick-Thohir-087082026.jpg</t>
+        </is>
+      </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>Bertemu KBPBI, Kapolri Minta Pengawalan RUU Ketenagakerjaan Utamakan Dialog</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:19:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1053" t="inlineStr">
+        <is>
+          <t>Kapolri siap menjembatani komunikasi, sementara KBPBI menegaskan aksi tetap dapat digelar jika aspirasi buruh tidak diakomodasi.</t>
+        </is>
+      </c>
+      <c r="F1053" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1053" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865448/bertemu-kbpbi-kapolri-minta-pengawalan-ruu-ketenagakerjaan-utamakan-dialog</t>
+        </is>
+      </c>
+      <c r="H1053" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/GtD3aVR0q9O9I-gdav41_WOa_jg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/BURUH-KBPBI-kapolri-ruu-ketenagakerjaan.jpg</t>
+        </is>
+      </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>Hubungan Maverick Vinales dan KTM Memanas, Bos Tech3 Sebut Semua Berawal dari Cedera Bahu</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:17:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1054" t="inlineStr">
+        <is>
+          <t>Masa depan Maverick Vinales di MotoGP 2027 semakin tidak menentu setelah cedera bahunya belum pulih serta bos Tech3 belum ada kepastian.</t>
+        </is>
+      </c>
+      <c r="F1054" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1054" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7865447/hubungan-maverick-vinales-dan-ktm-memanas-bos-tech3-sebut-semua-berawal-dari-cedera-bahu</t>
+        </is>
+      </c>
+      <c r="H1054" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/M0XoOEGeMji8fIWColfmIdcSwHw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Vinales-vs-Marquez-di-Qatar.jpg</t>
+        </is>
+      </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>Pakar Dorong Pembenahan Tata Kelola agar Program MBG Lebih Efektif</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:14:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>Tata kelola transparan hingga pengawasan yang efektif dinilai akan menjadi faktor penentu agar manfaat program dapat dirasakan secara lebih luas</t>
+        </is>
+      </c>
+      <c r="F1055" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1055" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865446/pakar-dorong-pembenahan-tata-kelola-agar-program-mbg-lebih-efektif</t>
+        </is>
+      </c>
+      <c r="H1055" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Kxy0Y85qxTHxMbNcepFDroLjqqk=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/food-tray-mbg-2kf.jpg</t>
+        </is>
+      </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>Denda Parkir Ribuan Kendaraan Diplomatik di Jepang Kedaluwarsa, RI Catat 17 Pelanggaran</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:13:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>Ribuan denda parkir kendaraan diplomatik di Jepang kedaluwarsa dan tak tertagih. Pada 2025, kendaraan Kedubes RI tercatat 17 pelanggaran</t>
+        </is>
+      </c>
+      <c r="F1056" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1056" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7865445/denda-parkir-ribuan-kendaraan-diplomatik-di-jepang-kedaluwarsa-ri-catat-17-pelanggaran</t>
+        </is>
+      </c>
+      <c r="H1056" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/hTSTaO0V0mpADmjQriiCCQZuRMw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kedubesindonesidijepang1.jpg</t>
+        </is>
+      </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>30 Ucapan Hari Singa Sedunia 2026 Inspiratif, Penuh Makna tentang Konservasi dan Cinta Satwa Liar</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:13:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1057" t="inlineStr">
+        <is>
+          <t>Hari Singa Sedunia atau World Lion Day diperingati setiap tanggal 10 Agustus, inilah 30 ucapan Hari Singa Sedunia 2026 yang inspiratif, penuh makna.</t>
+        </is>
+      </c>
+      <c r="F1057" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1057" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865444/30-ucapan-hari-singa-sedunia-2026-inspiratif-penuh-makna-tentang-konservasi-dan-cinta-satwa-liar</t>
+        </is>
+      </c>
+      <c r="H1057" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/BAmz7J7p3S7BTrCYYvpJ6GyzyVQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/singa-mati-kepanasan-di-jepang.jpg</t>
+        </is>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>Kepala BGN Siapkan Sanksi Suspend Permanen Bagi Dapur MBG Penyebab Siswa Keracunan</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:12:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1058" t="inlineStr">
+        <is>
+          <t>BGN menerapkan kebijakan sanksi hingga penutupan permanen bagi fasilitas dapur penyedia MBG yang terbukti menjadi penyebab siswa keracunan.</t>
+        </is>
+      </c>
+      <c r="F1058" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1058" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865443/kepala-bgn-siapkan-sanksi-suspend-permanen-bagi-dapur-mbg-penyebab-siswa-keracunan</t>
+        </is>
+      </c>
+      <c r="H1058" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/4f0-zgr4hrnVHPQgVmsf_X-PPFM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Konferensi-Pers-Kepala-BGN-Sudaryono_20260727_163650.jpg</t>
+        </is>
+      </c>
+      <c r="I1058" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>BGN Bakal Aktivasi 114 Dapur MBG di Papua dan Wilayah 3T Pekan Depan</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:03:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1059" t="inlineStr">
+        <is>
+          <t>BGN bersiap mengaktivasi 114 fasilitas dapur penyedia Makan Bergizi Gratis (MBG) di wilayah Papua, Maluku, NTT, dan kawasan 3T pekan depan</t>
+        </is>
+      </c>
+      <c r="F1059" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1059" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865442/bgn-bakal-aktivasi-114-dapur-mbg-di-papua-dan-wilayah-3t-pekan-depan</t>
+        </is>
+      </c>
+      <c r="H1059" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/lTxA0XNqqRXLEstPwFl6NIDq18E=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/dapur-mbg2.jpg</t>
+        </is>
+      </c>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>Trofi Piala AFF 2026 Sudah di Indonesia, Mampukah Skuad Garuda Membawanya Pulang?</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:02:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1060" t="inlineStr">
+        <is>
+          <t>Di area pameran, trofi ASEAN Hyundai Cup 2026 ditempatkan bersama sejumlah atribut turnamen.</t>
+        </is>
+      </c>
+      <c r="F1060" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1060" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7865441/trofi-piala-aff-2026-sudah-di-indonesia-mampukah-skuad-garuda-membawanya-pulang</t>
+        </is>
+      </c>
+      <c r="H1060" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/htpzVdF_nAm8PPuQyKT3HfjGvgA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Trofi-ASEAN-Hyundai-Cup-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>Perang AS-Iran Diyakini Akan Berakhir, Trump Klaim Teheran Tak Mampu Bertahan karena Pasokan Senjata</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1061" t="inlineStr">
+        <is>
+          <t>Menurut Trump, Iran tidak akan mampu bertahan lebih lama lagi atas perangnya melawan AS.</t>
+        </is>
+      </c>
+      <c r="F1061" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1061" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7865440/perang-as-iran-diyakini-akan-berakhir-trump-klaim-teheran-tak-mampu-bertahan-karena-pasokan-senjata</t>
+        </is>
+      </c>
+      <c r="H1061" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/zAJrXAtbprOaJvloF4HTWYbFg8I=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/DONALD-TRUMP-SAAT-BERPIDATO-DI-MICHIGAN-27072026.jpg</t>
+        </is>
+      </c>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>Wamendagri Bima Arya Ajak Pemda jadikan Penghijauan sebagai Gerakan Berkelanjutan</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:59:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1062" t="inlineStr">
+        <is>
+          <t>Upaya rehabilitasi hutan dan lahan tidak berhenti pada penanaman pohon, tetapi perlu disertai perawatan serta kolaborasi berbagai pihak.</t>
+        </is>
+      </c>
+      <c r="F1062" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1062" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865439/wamendagri-bima-arya-ajak-pemda-jadikan-penghijauan-sebagai-gerakan-berkelanjutan</t>
+        </is>
+      </c>
+      <c r="H1062" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/7rBNuGGRJqMvbBXFZcThMh-3C10=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/peresmian-Pusat-Persemaian-Sriwijaya-Kemampo.jpg</t>
+        </is>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>BGN Pecat 66 Kepala Dapur MBG, Ada yang Terjerat Judi Online</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:23:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1063" t="inlineStr">
+        <is>
+          <t>BGN memproses pemecatan tidak hormat 66 kepala dapur MBG akibat berbagai pelanggaran disiplin.</t>
+        </is>
+      </c>
+      <c r="F1063" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1063" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264599/bgn-pecat-66-kepala-dapur-mbg-ada-yang-terjerat-judi-online</t>
+        </is>
+      </c>
+      <c r="H1063" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/ugc3f_O3CnjjEQV-fkElBMb_n8k=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318578/original/016581600_1786105434-IMG_20260807_163305_363.jpg</t>
+        </is>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>Akun X TMC Polda Metro Jaya Diretas</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:51:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1064" t="inlineStr">
+        <is>
+          <t>Upaya pemulihan masih terus dilakukan.</t>
+        </is>
+      </c>
+      <c r="F1064" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1064" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264565/akun-x-tmc-polda-metro-jaya-diretas</t>
+        </is>
+      </c>
+      <c r="H1064" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/KW2ZVGQIcI9JdIS1ziu4gBEJQnI=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318551/original/094695300_1786103501-Screenshot_2026-08-07_184037.jpg</t>
+        </is>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>Bola</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>John Herdman: Piala AFF 2026 Bagian dari Misi Menuju Piala Dunia 2030</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:42:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1065" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia punya dahaga gelar di Piala AFF 2026, mampukan tim asuhan John Herdman yang mematahkan kutukan tak pernah juara?</t>
+        </is>
+      </c>
+      <c r="F1065" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1065" t="inlineStr">
+        <is>
+          <t>https://bola.kompas.com/read/2026/08/07/19420528/john-herdman-piala-aff-2026-bagian-dari-misi-menuju-piala-dunia-2030</t>
+        </is>
+      </c>
+      <c r="H1065" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/DicUUyMV1n5ZSZ_B0wj7jj2KNk4=/0x0:2265x1510/1200x675/filters:watermark(data/photo/2026/01/30/697c8163c3944.png,0,-0,1)/data/photo/2026/07/18/6a5b175b0ade3.jpg</t>
+        </is>
+      </c>
+      <c r="I1065" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>Bola</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>Susunan Pemain Timnas Indonesia Vs Singapura: Herdman Mainkan Cahya dan Wahyu Prasetyo</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:42:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia wajib menang di laga ini jika ingin melangkahkan kakinya ke fase gugur Piala AFF 2026.</t>
+        </is>
+      </c>
+      <c r="F1066" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1066" t="inlineStr">
+        <is>
+          <t>https://bola.kompas.com/read/2026/08/07/19264738/susunan-pemain-timnas-indonesia-vs-singapura-herdman-mainkan-cahya-dan-wahyu</t>
+        </is>
+      </c>
+      <c r="H1066" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/BaeTjmZDOImSvWBkCx8pX6BsXB0=/2x65:1473x1046/1200x675/filters:watermark(data/photo/2026/01/30/697c8163c3944.png,0,-0,1)/data/photo/2026/07/31/6a6c926a79508.png</t>
+        </is>
+      </c>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>Di Balik Gang Sempit Cakung Jaktim, Ada Sawah dan Kebun Menghidupi Warga</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:42:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>Di tengah hiruk pikuk Jakarta, hamparan sawah hijau masih lestari di Cakung. Kisah sukses Kelompok Tani Baliku Lestari menjaga ruang hijau dan pangan kota.</t>
+        </is>
+      </c>
+      <c r="F1067" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1067" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/07/19082041/di-balik-gang-sempit-cakung-jaktim-ada-sawah-dan-kebun-menghidupi-warga</t>
+        </is>
+      </c>
+      <c r="H1067" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/wB7kW-1ZixJn0p5npsP0jfXwk7o=/266x513:4032x3024/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/07/6a75c9cda024b.jpeg</t>
+        </is>
+      </c>
+      <c r="I1067" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I987"/>
+  <autoFilter ref="A1:I1067"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-07.xlsx
+++ b/data/berita_2026-08-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1067</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1191</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1067"/>
+  <dimension ref="A1:I1191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -50582,8 +50582,5836 @@
         </is>
       </c>
     </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>Kemenkes ajak masyarakat deteksi dini katarak melalui CKG</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:01:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1068" t="inlineStr">
+        <is>
+          <t>ANTARA - Kementerian Kesehatan mengajak masyarakat melakukan deteksi dini kesehatan mata melalui program cek kesehatan ...</t>
+        </is>
+      </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1068" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5684868/kemenkes-ajak-masyarakat-deteksi-dini-katarak-melalui-ckg</t>
+        </is>
+      </c>
+      <c r="H1068" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/KEMENKES-AJAK-MASYARAKAT-DETEKSI-DINI-KATARAK-MELALUI-CKG.jpg</t>
+        </is>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>Indonesia imbang tanpa gol melawan Singapura pada babak pertama</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:01:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1069" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia bermain imbang tanpa gol melawan Singapura pada babak pertama pertandingan Grup A Piala AFF 2026 di ...</t>
+        </is>
+      </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1069" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684905/indonesia-imbang-tanpa-gol-melawan-singapura-pada-babak-pertama</t>
+        </is>
+      </c>
+      <c r="H1069" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/timnas-indonesia-dikalahkan-timnas-vietnam-2833607.jpg</t>
+        </is>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>Ombudsman soroti keterbatasan internet ganggu layanan publik digital</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:58:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1070" t="inlineStr">
+        <is>
+          <t>Ombudsman RI menyoroti keterbatasan akses internet di sejumlah daerah yang berdampak terhadap pemenuhan hak masyarakat ...</t>
+        </is>
+      </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1070" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684903/ombudsman-soroti-keterbatasan-internet-ganggu-layanan-publik-digital</t>
+        </is>
+      </c>
+      <c r="H1070" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000475159.jpg</t>
+        </is>
+      </c>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>Karhutla TNBTS mengarah ke Wisata B29 Lumajang</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:58:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan dan lahan (karhutla) di kawasan Taman Nasional Bromo Tengger Semeru (TNBTS) masih terus meluas hingga ...</t>
+        </is>
+      </c>
+      <c r="F1071" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1071" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684899/karhutla-tnbts-mengarah-ke-wisata-b29-lumajang</t>
+        </is>
+      </c>
+      <c r="H1071" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001170369.jpg</t>
+        </is>
+      </c>
+      <c r="I1071" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>Veda Ega tempati posisi keenam dalam FP1 GP Inggris</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:57:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr">
+        <is>
+          <t>Pembalap Indonesia Veda Ega Pratama menempati posisi keenam dalam latihan bebas 1 Moto3 Grand Prix Inggris yang ...</t>
+        </is>
+      </c>
+      <c r="F1072" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1072" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684892/veda-ega-tempati-posisi-keenam-dalam-fp1-gp-inggris</t>
+        </is>
+      </c>
+      <c r="H1072" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/21/Latihan-pembalap-nasional-Moto2-dan-Moto3-di-Mandalika-210726-AS-4.jpg</t>
+        </is>
+      </c>
+      <c r="I1072" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>Meta diperintahkan ganti rugi kesehatan mental anak 567 juta dolar AS</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:55:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1073" t="inlineStr">
+        <is>
+          <t>Pengadilan Negara Bagian New Mexico, Amerika Serikat (AS), pada Kamis (6/8) waktu setempat, memerintahkan raksasa media ...</t>
+        </is>
+      </c>
+      <c r="F1073" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1073" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684888/meta-diperintahkan-ganti-rugi-kesehatan-mental-anak-567-juta-dolar-as</t>
+        </is>
+      </c>
+      <c r="H1073" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/CjkinzN000024_20260807_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>Di acara peluncuran bukunya, Bahlil tuai ragam pujian dari Prabowo</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:54:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto memuji kemampuan kepemimpinan Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia ...</t>
+        </is>
+      </c>
+      <c r="F1074" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1074" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684887/di-acara-peluncuran-bukunya-bahlil-tuai-ragam-pujian-dari-prabowo</t>
+        </is>
+      </c>
+      <c r="H1074" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Peluncuran-10-buku-karya-nyata-untuk-negeri-Bahlil-Lahadalia-070826-Ada-6_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1074" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>Pacu sampan tradisional Padang simpan sejarah dan semangat kebersamaan</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:50:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1075" t="inlineStr">
+        <is>
+          <t>Dua tim adu cepat mengayuh dayungnya saat lomba selaju sampan tradisional di Batang Arau, Padang, Sumatera Barat, Jumat ...</t>
+        </is>
+      </c>
+      <c r="F1075" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1075" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5684883/pacu-sampan-tradisional-padang-simpan-sejarah-dan-semangat-kebersamaan</t>
+        </is>
+      </c>
+      <c r="H1075" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Selaju-sampan-tradisional-di-Padang-070826-Ief-3.jpg</t>
+        </is>
+      </c>
+      <c r="I1075" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>Basket putri Indonesia buka Asian Games 2026 lawan Thailand</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:50:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>Tim nasional bola basket 5x5 putri Indonesia akan mengawali perjuangan pada Asian Games Aichi-Nagoya 2026 dengan ...</t>
+        </is>
+      </c>
+      <c r="F1076" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1076" t="inlineStr">
+        <is>
+          <t>https://asiangames.antaranews.com/berita/5684879/basket-putri-indonesia-buka-asian-games-2026-lawan-thailand</t>
+        </is>
+      </c>
+      <c r="H1076" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/1001109495.jpg</t>
+        </is>
+      </c>
+      <c r="I1076" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>Moonton Games terapkan mekanisme “title defender” di MSC 2027</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:47:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>Moonton Games menerapkan mekanisme baru "Title Defender" pada ajang Mobile Legends: Bang Bang (MLBB) Mid ...</t>
+        </is>
+      </c>
+      <c r="F1077" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1077" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684875/moonton-games-terapkan-mekanisme-title-defender-di-msc-2027</t>
+        </is>
+      </c>
+      <c r="H1077" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/11/704127.jpg</t>
+        </is>
+      </c>
+      <c r="I1077" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>Balai Besar TNBTS duga kebakaran di Bromo karena aktivitas manusia</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:45:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1078" t="inlineStr">
+        <is>
+          <t>Balai Besar Taman Nasional Bromo Tengger Semeru (TNBTS) menduga kebakaran yang melanda kawasan Gunung Bromo bukan ...</t>
+        </is>
+      </c>
+      <c r="F1078" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1078" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684873/balai-besar-tnbts-duga-kebakaran-di-bromo-karena-aktivitas-manusia</t>
+        </is>
+      </c>
+      <c r="H1078" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001405775.jpg</t>
+        </is>
+      </c>
+      <c r="I1078" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>Paduan suara Unpatti wakili Indonesia pada ajang internasional Swedia</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:44:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr">
+        <is>
+          <t>Tim paduan suara mahasiswa Universitas Pattimura (Unpatti), Hotumese Choir Pattimura University, akan mewakili ...</t>
+        </is>
+      </c>
+      <c r="F1079" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1079" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684871/paduan-suara-unpatti-wakili-indonesia-pada-ajang-internasional-swedia</t>
+        </is>
+      </c>
+      <c r="H1079" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-22.27.28.jpeg</t>
+        </is>
+      </c>
+      <c r="I1079" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>WHO bersama mitra sepakati strategi bersama tangani Ebola di RD Kongo</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:44:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1080" t="inlineStr">
+        <is>
+          <t>Organisasi Kesehatan Dunia (WHO), Kamis (6/8), mengatakan bahwa mereka dengan mitra penanggulangan lainnya telah ...</t>
+        </is>
+      </c>
+      <c r="F1080" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1080" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684869/who-bersama-mitra-sepakati-strategi-bersama-tangani-ebola-di-rd-kongo</t>
+        </is>
+      </c>
+      <c r="H1080" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/17/thumbs_b_c_b3ea1b309945d5afbeeae7c304253618.jpg</t>
+        </is>
+      </c>
+      <c r="I1080" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>BI: Feskop Papua 2026 perkuat sektor kopi sebagai komoditas unggulan</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:43:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1081" t="inlineStr">
+        <is>
+          <t>Kantor Perwakilan (KPw) Bank Indonesia (BI) Provinsi Papua menyebutkan penyelenggaraan Festival Kopi Papua (Feskop) ...</t>
+        </is>
+      </c>
+      <c r="F1081" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1081" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684865/bi-feskop-papua-2026-perkuat-sektor-kopi-sebagai-komoditas-unggulan</t>
+        </is>
+      </c>
+      <c r="H1081" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1002075510.jpg</t>
+        </is>
+      </c>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>Bahlil: Saya tidak minder lahir dari rahim pembantu rumah tangga</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:43:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1082" t="inlineStr">
+        <is>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia mengatakan dirinya tidak pernah merasa menyesal, malu, ...</t>
+        </is>
+      </c>
+      <c r="F1082" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1082" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684861/bahlil-saya-tidak-minder-lahir-dari-rahim-pembantu-rumah-tangga</t>
+        </is>
+      </c>
+      <c r="H1082" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_7622.jpg</t>
+        </is>
+      </c>
+      <c r="I1082" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>"Pedas Level Up" raih dana produksi film dari Pemkot Semarang</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:42:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>Ide cerita "Pedas Level Up!" karya Segi Film terpilih sebagai penerima Lawang Sewu Film Fund pada ajang ...</t>
+        </is>
+      </c>
+      <c r="F1083" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1083" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684857/pedas-level-up-raih-dana-produksi-film-dari-pemkot-semarang</t>
+        </is>
+      </c>
+      <c r="H1083" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1002086879.jpg</t>
+        </is>
+      </c>
+      <c r="I1083" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>Xabi Alonso sebut laga di Jakarta dekatkan Chelsea dengan penggemar</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:41:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1084" t="inlineStr">
+        <is>
+          <t>Pelatih Chelsea Xabi Alonso menyebutkan laga pramusim yang akan dijalani di Jakarta menjadi menjadi momentum ...</t>
+        </is>
+      </c>
+      <c r="F1084" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1084" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684855/xabi-alonso-sebut-laga-di-jakarta-dekatkan-chelsea-dengan-penggemar</t>
+        </is>
+      </c>
+      <c r="H1084" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/ae243c06-7156-40d7-8f28-eccd40cee72c.jpeg</t>
+        </is>
+      </c>
+      <c r="I1084" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>NTB bagikan ribuan bendera Merah Putih sambut kemerdekaan</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:41:46 +0700</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi Nusa Tenggara Barat (NTB) bersama Pemerintah Kota Mataram membagikan ribuan bendera Merah Putih ...</t>
+        </is>
+      </c>
+      <c r="F1085" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1085" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684853/ntb-bagikan-ribuan-bendera-merah-putih-sambut-kemerdekaan</t>
+        </is>
+      </c>
+      <c r="H1085" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001791408.jpg</t>
+        </is>
+      </c>
+      <c r="I1085" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>Produksi garam meningkat, petani dorong hilirisasi saat harga anjlok</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:39:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1086" t="inlineStr">
+        <is>
+          <t>ANTARA - Musim kemarau mendorong peningkatan produksi garam di sejumlah sentra tambak di Jawa Tengah. Namun, ...</t>
+        </is>
+      </c>
+      <c r="F1086" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1086" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5684845/produksi-garam-meningkat-petani-dorong-hilirisasi-saat-harga-anjlok</t>
+        </is>
+      </c>
+      <c r="H1086" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SANS_PRODUKSI-GARAM-MENINGKAT-PETANI-DORONG-HILIRISASI-SAAT-HARGA-ANJLOK.jpg</t>
+        </is>
+      </c>
+      <c r="I1086" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>HIPPINDO: ISF 2026 berpotensi naikkan penjualan ritel hingga 20 persen</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:39:13 +0700</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>Ketua Umum Himpunan Peritel dan Penyewa Pusat Perbelanjaan Indonesia (Hippindo) Budihardjo Iduansjah mengatakan program ...</t>
+        </is>
+      </c>
+      <c r="F1087" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1087" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684851/hippindo-isf-2026-berpotensi-naikkan-penjualan-ritel-hingga-20-persen</t>
+        </is>
+      </c>
+      <c r="H1087" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000455497.jpg</t>
+        </is>
+      </c>
+      <c r="I1087" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>Brantas Abipraya: Kawasan DPR Paket I di IKN ditargetkan tuntas 2027</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:36:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1088" t="inlineStr">
+        <is>
+          <t>Badan Usaha Milik Negara (BUMN) bidang jasa konstruksi PT Brantas Abipraya (Persero) menyatakan pembangunan Bangunan ...</t>
+        </is>
+      </c>
+      <c r="F1088" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1088" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684844/brantas-abipraya-kawasan-dpr-paket-i-di-ikn-ditargetkan-tuntas-2027</t>
+        </is>
+      </c>
+      <c r="H1088" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000178454.jpg</t>
+        </is>
+      </c>
+      <c r="I1088" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>Tujuh pelaku penyalahgunaan solar subsidi diamankan di Sumbar</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:35:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1089" t="inlineStr">
+        <is>
+          <t>ANTARA - Polda Sumatera Barat mengamankan tujuh pelaku dalam pengungkapan kasus dugaan penimbunan dan penyalahgunaan ...</t>
+        </is>
+      </c>
+      <c r="F1089" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1089" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5684695/tujuh-pelaku-penyalahgunaan-solar-subsidi-diamankan-di-sumbar</t>
+        </is>
+      </c>
+      <c r="H1089" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/TUJUH-PELAKU-PENYALAHGUNAAN-SOLAR-SUBSIDI-DIAMANKAN-DI-SUMBAR.jpg</t>
+        </is>
+      </c>
+      <c r="I1089" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>Basket putra Indonesia kembali hadapi Jepang-Korea di Asian Games 2026</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:35:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1090" t="inlineStr">
+        <is>
+          <t>Tim nasional bola basket 5x5 putra Indonesia kembali menghadapi Jepang dan Korea Selatan setelah berada di Grup A ...</t>
+        </is>
+      </c>
+      <c r="F1090" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1090" t="inlineStr">
+        <is>
+          <t>https://asiangames.antaranews.com/berita/5684840/basket-putra-indonesia-kembali-hadapi-jepang-korea-di-asian-games-2026</t>
+        </is>
+      </c>
+      <c r="H1090" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/09/30/antarafoto-bola-basket-indonesia-kalah-dari-qatar-30092023-mrh-8_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1090" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>BNPB: Tim gabungan kendalikan karhutla di empat provinsi</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:34:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>Badan Nasional Penanggulangan Bencana (BNPB) memastikan tim gabungan berhasil mengendalikan dan memadamkan sejumlah ...</t>
+        </is>
+      </c>
+      <c r="F1091" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1091" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684839/bnpb-tim-gabungan-kendalikan-karhutla-di-empat-provinsi</t>
+        </is>
+      </c>
+      <c r="H1091" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/10/IMG_20260210_191724.jpg</t>
+        </is>
+      </c>
+      <c r="I1091" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>Eks ketua yayasan diduga lakukan penyalahgunaan keuangan Rp2 miliar</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:34:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>Mantan ketua pengurus yayasan sekolah swasta di Pondok Pinang, Kebayoran Lama, Jakarta Selatan berinisial ...</t>
+        </is>
+      </c>
+      <c r="F1092" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1092" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684835/eks-ketua-yayasan-diduga-lakukan-penyalahgunaan-keuangan-rp2-miliar</t>
+        </is>
+      </c>
+      <c r="H1092" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001016893.jpg</t>
+        </is>
+      </c>
+      <c r="I1092" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>Menkop buka pameran UMKM dan kopi Lembah Baliem Wamena Jayawijaya</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:34:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1093" t="inlineStr">
+        <is>
+          <t>Menteri Koperasi (Menkop) RI Ferry Juliantono membuka Pameran Usaha Mikro Kecil dan Menengah (UMKM), Kopi Lembah Baliem ...</t>
+        </is>
+      </c>
+      <c r="F1093" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1093" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684832/menkop-buka-pameran-umkm-dan-kopi-lembah-baliem-wamena-jayawijaya</t>
+        </is>
+      </c>
+      <c r="H1093" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-20.39.38.jpeg</t>
+        </is>
+      </c>
+      <c r="I1093" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>Turkiye, Saudi, Pakistan akan tingkatkan pertukaran intelijen</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:31:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1094" t="inlineStr">
+        <is>
+          <t>Turkiye, Arab Saudi, dan Pakistan diperkirakan akan menandatangani pakta pertahanan bersama di kota Jeddah, Arab Saudi, ...</t>
+        </is>
+      </c>
+      <c r="F1094" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1094" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684831/turkiye-saudi-pakistan-akan-tingkatkan-pertukaran-intelijen</t>
+        </is>
+      </c>
+      <c r="H1094" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/thumbs_b_c_8fe7e6db1fb161dba3498b23f6c0fb62.jpg</t>
+        </is>
+      </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>BNPB: 148 ribu liter air bersih untuk atasi kekeringan Bandung Barat</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:31:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>Badan Nasional Penanggulangan Bencana (BNPB) menyatakan sebanyak 148 ribu liter air bersih telah didistribusikan untuk ...</t>
+        </is>
+      </c>
+      <c r="F1095" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684829/bnpb-148-ribu-liter-air-bersih-untuk-atasi-kekeringan-bandung-barat</t>
+        </is>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/03/30/IMG-20260330-WA0008.jpg</t>
+        </is>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>Khofifah: BNPB kirim satu helikopter "water bombing" tambahan ke Bromo</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:30:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>Gubernur Jawa Timur Khofifah Indar Parawansa memastikan Badan Nasional Penanggulangan Bencana (BNPB) akan mengirimkan ...</t>
+        </is>
+      </c>
+      <c r="F1096" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684827/khofifah-bnpb-kirim-satu-helikopter-water-bombing-tambahan-ke-bromo</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001405726.jpg</t>
+        </is>
+      </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>APPBI nilai hub komersial perlu diintegrasikan dengan destinasi wisata</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:29:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>Asosiasi Pengelola Pusat Belanja Indonesia (APPBI) menyampaikan perlunya pengintegrasian hub-hub komersial dengan ...</t>
+        </is>
+      </c>
+      <c r="F1097" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684824/appbi-nilai-hub-komersial-perlu-diintegrasikan-dengan-destinasi-wisata</t>
+        </is>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/pusat-perbelanjaan-kek-kura-kura-2831260.jpg</t>
+        </is>
+      </c>
+      <c r="I1097" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>Istana: Destry masuk pertimbangan calon Gubernur BI</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:29:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>Menteri Sekretaris Negara Prasetyo Hadi mengatakan Presiden Prabowo Subianto mempertimbangkan sejumlah nama untuk ...</t>
+        </is>
+      </c>
+      <c r="F1098" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684823/istana-destry-masuk-pertimbangan-calon-gubernur-bi</t>
+        </is>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Image-07-08-26-at-19.53.jpeg</t>
+        </is>
+      </c>
+      <c r="I1098" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>Uenohara Challenger jadi penentu tiket World Tour Debrecen 2026</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:28:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>Federasi Bola Basket Internasional (FIBA) 3x3 Uenohara Challenger 2026 di Jepang pada 8-9 Agustus menjadi ajang penentu ...</t>
+        </is>
+      </c>
+      <c r="F1099" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684821/uenohara-challenger-jadi-penentu-tiket-world-tour-debrecen-2026</t>
+        </is>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/07/10/NBA.jpg</t>
+        </is>
+      </c>
+      <c r="I1099" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>Lestari dorong revisi UU TPPO hadapi modus kejahatan digital</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:27:44 +0700</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>Wakil Ketua MPR RI Lestari Moerdijat mendorong revisi Undang-Undang Nomor 21 Tahun 2007 tentang Pemberantasan TPPO ...</t>
+        </is>
+      </c>
+      <c r="F1100" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684820/lestari-dorong-revisi-uu-tppo-hadapi-modus-kejahatan-digital</t>
+        </is>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/06/17/1001130928.jpg</t>
+        </is>
+      </c>
+      <c r="I1100" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>Polisi masih cari potongan kaki korban mutilasi di Depok</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:25:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>Kepolisian masih mencari potongan kaki korban mutilasi yang sebagian tubuhnya ditemukan dalam karung di kawasan Tanah ...</t>
+        </is>
+      </c>
+      <c r="F1101" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684816/polisi-masih-cari-potongan-kaki-korban-mutilasi-di-depok</t>
+        </is>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/04/IMG_4065.jpeg</t>
+        </is>
+      </c>
+      <c r="I1101" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>Puan minta tenaga kesehatan berempati kepada pasien BPJS</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:23:53 +0700</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>Ketua DPR RI Puan Maharani meminta tenaga kesehatan mengedepankan empati dalam memberikan pelayanan kepada seluruh ...</t>
+        </is>
+      </c>
+      <c r="F1102" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684812/puan-minta-tenaga-kesehatan-berempati-kepada-pasien-bpjs</t>
+        </is>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/21/1001279828.jpg</t>
+        </is>
+      </c>
+      <c r="I1102" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>Soal demutualisasi BEI, ekonom usul porsi kepemilikan rendah per pihak</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:21:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>Kepala Ekonom PermataBank Josua Pardede merekomendasikan struktur kepemilikan yang sangat tersebar dengan batas ...</t>
+        </is>
+      </c>
+      <c r="F1103" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684809/soal-demutualisasi-bei-ekonom-usul-porsi-kepemilikan-rendah-per-pihak</t>
+        </is>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/02/07/WhatsApp-Image-2026-02-06-at-23.05.58-1.jpeg</t>
+        </is>
+      </c>
+      <c r="I1103" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>Legislator DKI minta Transjakarta perketat rekrutmen pramudi</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:19:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>Anggota DPRD DKI Jakarta Hardiyanto Kenneth meminta Dinas Perhubungan DKI Jakarta dan PT Transjakarta untuk ...</t>
+        </is>
+      </c>
+      <c r="F1104" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684807/legislator-dki-minta-transjakarta-perketat-rekrutmen-pramudi</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/11/19/rencana-pelatihan-ulang-pramudi-mikrotrans-2671713.jpg</t>
+        </is>
+      </c>
+      <c r="I1104" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>Ilmuwan AS perdana gunakan AI untuk rancang virus baru</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:19:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>Sejumlah ilmuwan asal Amerika Serikat pada Kamis (6/8) mengumumkan penelitian baru yang menggunakan kecerdasan buatan ...</t>
+        </is>
+      </c>
+      <c r="F1105" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684805/ilmuwan-as-perdana-gunakan-ai-untuk-rancang-virus-baru</t>
+        </is>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/09/10/penanganan-mpox.jpg</t>
+        </is>
+      </c>
+      <c r="I1105" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>Wamendagri minta penghijauan jadi gerakan berkelanjutan di daerah</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:17:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1106" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Dalam Negeri Bima Arya Sugiarto meminta pemerintah daerah menjadikan penghijauan sebagai gerakan ...</t>
+        </is>
+      </c>
+      <c r="F1106" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1106" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684804/wamendagri-minta-penghijauan-jadi-gerakan-berkelanjutan-di-daerah</t>
+        </is>
+      </c>
+      <c r="H1106" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000582177.jpg</t>
+        </is>
+      </c>
+      <c r="I1106" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>Alex Marquez ungguli Bezzecchi untuk jadi tercepat di FP1 GP Inggris</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:17:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1107" t="inlineStr">
+        <is>
+          <t>Pembalap Gresini Racing Alex Marquez mengungguli pembalap Aprilia Racing Marco Bezzecchi untuk menjadi yang tercepat ...</t>
+        </is>
+      </c>
+      <c r="F1107" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1107" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684803/alex-marquez-ungguli-bezzecchi-untuk-jadi-tercepat-di-fp1-gp-inggris</t>
+        </is>
+      </c>
+      <c r="H1107" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/10/05/race-motogp-indonesia-2025-2639153.jpg</t>
+        </is>
+      </c>
+      <c r="I1107" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>Galaxy S26 FE muncul di FCC, tampil dengan kejutan dari Qualcomm</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:14:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1108" t="inlineStr">
+        <is>
+          <t>Samsung dikabarkan tengah mempersiapkan model Galaxy S26 FE untuk melengkapi seri Galaxy S26 dan tampaknya kabar ...</t>
+        </is>
+      </c>
+      <c r="F1108" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1108" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684799/galaxy-s26-fe-muncul-di-fcc-tampil-dengan-kejutan-dari-qualcomm</t>
+        </is>
+      </c>
+      <c r="H1108" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/InShot_20260807_193645447.jpg</t>
+        </is>
+      </c>
+      <c r="I1108" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>Analis BEI nilai investor ritel topang aktivitas pasar modal</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:12:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>Analis Senior Divisi Riset Bursa Efek Indonesia (BEI) Fikrian Naufal Hardiatmojo menilai investor ritel semakin ...</t>
+        </is>
+      </c>
+      <c r="F1109" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1109" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684797/analis-bei-nilai-investor-ritel-topang-aktivitas-pasar-modal</t>
+        </is>
+      </c>
+      <c r="H1109" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000178309.jpg</t>
+        </is>
+      </c>
+      <c r="I1109" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>Wamenko Otto: Transformasi hukum penting wujudkan keadilan</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:11:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Koordinator Bidang Hukum, HAM, Imigrasi, dan Pemasyarakatan Otto Hasibuan menilai transformasi paradigma ...</t>
+        </is>
+      </c>
+      <c r="F1110" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1110" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684795/wamenko-otto-transformasi-hukum-penting-wujudkan-keadilan</t>
+        </is>
+      </c>
+      <c r="H1110" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000475100.jpg</t>
+        </is>
+      </c>
+      <c r="I1110" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>Yayasan sekolah bantah guru terlibat penyimpanan senjata</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:08:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>Yayasan sekolah swasta di kawasan Pondok Pinang, Kebayoran Lama, Jakarta Selatan membantah guru terlibat dalam ...</t>
+        </is>
+      </c>
+      <c r="F1111" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1111" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684793/yayasan-sekolah-bantah-guru-terlibat-penyimpanan-senjata</t>
+        </is>
+      </c>
+      <c r="H1111" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001016850.jpg</t>
+        </is>
+      </c>
+      <c r="I1111" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>Mendes: Keberadaan Kopdes tak akan bikin warung-warung di desa tutup</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:07:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1112" t="inlineStr">
+        <is>
+          <t>Menteri Desa dan Pembangunan Daerah Tertinggal (Mendes PDT) Yandri Susanto mengatakan Program Koperasi Desa Merah ...</t>
+        </is>
+      </c>
+      <c r="F1112" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1112" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684791/mendes-keberadaan-kopdes-tak-akan-bikin-warung-warung-di-desa-tutup</t>
+        </is>
+      </c>
+      <c r="H1112" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-19.24.01.jpeg</t>
+        </is>
+      </c>
+      <c r="I1112" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>PASI modifikasi uji tanding atlet jelang Asian Games 2026</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:07:05 +0700</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1113" t="inlineStr">
+        <is>
+          <t>Pengurus Besar Persatuan Atletik Seluruh Indonesia (PB PASI) memodifikasi program uji tanding atlet menjelang Asian ...</t>
+        </is>
+      </c>
+      <c r="F1113" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1113" t="inlineStr">
+        <is>
+          <t>https://asiangames.antaranews.com/berita/5684788/pasi-modifikasi-uji-tanding-atlet-jelang-asian-games-2026</t>
+        </is>
+      </c>
+      <c r="H1113" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/09/29/antarafoto-jalan-cepat-20km-pria-290923-hma-01.jpg</t>
+        </is>
+      </c>
+      <c r="I1113" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>Febrie Adriansyah dicecar puluhan pertanyaan saat di Kejagung</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:06:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr">
+        <is>
+          <t>Tersangka kasus dugaan tindak pidana pencucian uang (TPPU) yang juga mantan Jaksa Agung Muda Bidang Tindak Pidana ...</t>
+        </is>
+      </c>
+      <c r="F1114" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1114" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684785/febrie-adriansyah-dicecar-puluhan-pertanyaan-saat-di-kejagung</t>
+        </is>
+      </c>
+      <c r="H1114" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000087435.jpg</t>
+        </is>
+      </c>
+      <c r="I1114" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>Indonesia berpeluang tambahan ekspor garmen hingga 2 miliar dolar AS</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:04:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1115" t="inlineStr">
+        <is>
+          <t>Ketua Umum Asosiasi Garment dan Textile Indonesia (AGTI) Anne Patricia Sutanto mengatakan, berdasarkan laporan terbaru ...</t>
+        </is>
+      </c>
+      <c r="F1115" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1115" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684781/indonesia-berpeluang-tambahan-ekspor-garmen-hingga-2-miliar-dolar-as</t>
+        </is>
+      </c>
+      <c r="H1115" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_20260807_194407.jpg</t>
+        </is>
+      </c>
+      <c r="I1115" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>Polda Metro tahan sembilan tersangka penyebaran konten hoaks</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:04:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya menahan sembilan orang tersangka terkait kasus penyebaran konten provokatif, destruktif, dan berita ...</t>
+        </is>
+      </c>
+      <c r="F1116" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1116" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684779/polda-metro-tahan-sembilan-tersangka-penyebaran-konten-hoaks</t>
+        </is>
+      </c>
+      <c r="H1116" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_20260807_194634.jpg</t>
+        </is>
+      </c>
+      <c r="I1116" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>Pemprov Papua bagikan 2.000 Bendera Merah Putih bagi warga Jayapura</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:03:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1117" t="inlineStr">
+        <is>
+          <t>Pemerintah Provinsi (Pemprov) Papua membagikan sebanyak 2.000 Bendera Merah Putih kepada masyarakat Kota Jayapura dalam ...</t>
+        </is>
+      </c>
+      <c r="F1117" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1117" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684775/pemprov-papua-bagikan-2000-bendera-merah-putih-bagi-warga-jayapura</t>
+        </is>
+      </c>
+      <c r="H1117" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1002075390.jpg</t>
+        </is>
+      </c>
+      <c r="I1117" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>Eks Waka BGN Lodewyk Kembali Ajukan Praperadilan, Kejagung Bilang Begini</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:54:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr">
+        <is>
+          <t>Mantan Waka BGN Lodewyk Pusung kembali mengajukan praperadilan. Kali ini Lodewyk Pusung mengajukan praperadilan terkait penyitaan di PN Jakpus.</t>
+        </is>
+      </c>
+      <c r="F1118" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1118" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609155/eks-waka-bgn-lodewyk-kembali-ajukan-praperadilan-kejagung-bilang-begini</t>
+        </is>
+      </c>
+      <c r="H1118" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2019/12/13/9f4b19db-516f-42c9-8b04-4bb3a4965656_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1118" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>Kejagung Sudah Periksa Lebih dari 80 Saksi di Kasus Tata Kelola MBG</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:47:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr">
+        <is>
+          <t>Kejagung mengungkap perkembangan kasus korupsi MBG di BGN, memeriksa 80 saksi dan menetapkan tujuh tersangka. Proses hukum berlanjut.</t>
+        </is>
+      </c>
+      <c r="F1119" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1119" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609140/kejagung-sudah-periksa-lebih-dari-80-saksi-di-kasus-tata-kelola-mbg</t>
+        </is>
+      </c>
+      <c r="H1119" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/anang-supriatna-1786106599337_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1119" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>Mendes Tegaskan Keberadaan KDMP Tidak Akan Menutup Warung-warung di Desa</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:38:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>Hana Nushratu</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr">
+        <is>
+          <t>Mendes Yandri Susanto menegaskan program Koperasi Desa Merah Putih (KDMP) akan kolaborasi dengan warung desa, mempermudah akses barang subsidi untuk masyarakat</t>
+        </is>
+      </c>
+      <c r="F1120" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1120" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609126/mendes-tegaskan-keberadaan-kdmp-tidak-akan-menutup-warung-warung-di-desa</t>
+        </is>
+      </c>
+      <c r="H1120" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/menteri-desa-dan-pembangunan-daerah-tertinggal-ri-mendes-pdt-yandri-susanto-1786109851691.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1120" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>Kolonel Marinir Sri Utomo Resmi Jabat Komandan Brigif 1</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:35:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>Firda Cynthia Anggrainy</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr">
+        <is>
+          <t>Kolonel Marinir Sri Utomo resmi menjabat Danbrigif 1. Sertijab dipimpin Danpasmar 1, menekankan pentingnya profesionalisme dan semangat prajurit.</t>
+        </is>
+      </c>
+      <c r="F1121" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1121" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609120/kolonel-marinir-sri-utomo-resmi-jabat-komandan-brigif-1</t>
+        </is>
+      </c>
+      <c r="H1121" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/pengukuhan-jabatan-danbrigif-1-marinir-kolonel-mar-sri-utomo-1786109631657_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1121" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>Puan Soroti Kasus Pasien BPJS, Minta Sistem Layanan Kesehatan Dievaluasi</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:33:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr">
+        <is>
+          <t>Ketua DPR Puan Maharani menyoroti krisis empati nakes setelah keluhan pasien BPJS viral. Ia mendesak perbaikan sistem pelayanan kesehatan secara menyeluruh.</t>
+        </is>
+      </c>
+      <c r="F1122" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1122" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609114/puan-soroti-kasus-pasien-bpjs-minta-sistem-layanan-kesehatan-dievaluasi</t>
+        </is>
+      </c>
+      <c r="H1122" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/07/ketua-dpr-ri-puan-maharani-1783419345640_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1122" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>'Bunker' di Kasus Ratusan Senjata di Sekolah Jaksel Sudah Dicek, Apa Isinya?</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:33:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>Taufiq Syarifudin</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr">
+        <is>
+          <t>Pihak yayasan sekolah swasta di Jakarta memastikan ruangan mirip 'bunker' sudah dicek polisi. Hasilnya, tak ditemukan adanya senjata atau barang bahaya lainnya.</t>
+        </is>
+      </c>
+      <c r="F1123" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1123" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609113/bunker-di-kasus-ratusan-senjata-di-sekolah-jaksel-sudah-dicek-apa-isinya</t>
+        </is>
+      </c>
+      <c r="H1123" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/ruangan-mantan-kepala-yayasan-ditemukannya-senjata-di-sekolah-swasta-jaksel-taufiqdetikcom-1786104460813_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1123" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>Pemilik Senpi di Sekolah Swasta Jaksel Direktur Perusahaan Impor Airsoft Gun</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:32:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>Polisi ungkap DS sebagai pemilik senjata api di sekolah swasta Jaksel. DS sudah meninggal, sementara esk ketua yayasan diperiksa terkait temuan ratusan senjata.</t>
+        </is>
+      </c>
+      <c r="F1124" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1124" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609111/pemilik-senpi-di-sekolah-swasta-jaksel-direktur-perusahaan-impor-airsoft-gun</t>
+        </is>
+      </c>
+      <c r="H1124" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/temuan-sejumlah-senjata-api-di-salah-satu-ruangan-yayasan-sekolah-swasta-di-pondok-pinang-jakarta-selatan-1786002238709_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1124" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>Pemerintah Perbarui Kualitas Buku Ajar Nasional, Bandingkan Negara Tetangga</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:15:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>Pemerintah fokus memperbarui buku ajar nasional untuk meningkatkan kualitas pendidikan. Prabowo Subianto menekankan pentingnya aspek fisik dan konten buku.</t>
+        </is>
+      </c>
+      <c r="F1125" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1125" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609086/pemerintah-perbarui-kualitas-buku-ajar-nasional-bandingkan-negara-tetangga</t>
+        </is>
+      </c>
+      <c r="H1125" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/prasetyo-hadi-dan-teddy-indra-wijaya-1786108149413_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1125" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>JakLingko Kecelakaan, Kenneth DPRD DKI Desak Optimalisasi Akademi Transjakarta</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:01:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr">
+        <is>
+          <t>Mega Putra Ratya</t>
+        </is>
+      </c>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>Anggota DPRD DKI, Hardiyanto Kenneth, mendesak audit sistem rekrutmen dan pelatihan sopir JakLingko setelah kecelakaan yang melibatkan lansia.</t>
+        </is>
+      </c>
+      <c r="F1126" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1126" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609069/jaklingko-kecelakaan-kenneth-dprd-dki-desak-optimalisasi-akademi-transjakarta</t>
+        </is>
+      </c>
+      <c r="H1126" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/anggota-dprd-dki-jakarta-hardiyanto-kenneth-sedang-menyampaikan-pendapatnya-pada-saat-rapat-dengar-pendapat-di-kebon-sirih-jak-1786107626644.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1126" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>Kejagung Mulai Usut Asal-usul Barbuk Emas 74Kg-Duit Ratusan Miliar ke Febrie</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:00:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr">
+        <is>
+          <t>Kejaksaan Agung memeriksa mantan Jampidsus Febrie Adriansyah terkait kasus TPPU, menyelidiki asal barang bukti 74 kg emas dan ratusan miliar rupiah.</t>
+        </is>
+      </c>
+      <c r="F1127" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1127" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609068/kejagung-mulai-usut-asal-usul-barbuk-emas-74kg-duit-ratusan-miliar-ke-febrie</t>
+        </is>
+      </c>
+      <c r="H1127" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/03/kapuspenkum-kejagung-anang-supriatna-1770098880799_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1127" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>Lintasarta Bawa Solusi 4C Perkuat Infrastruktur Digital BPD</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:47:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr">
+        <is>
+          <t>Lintasarta hadirkan ekosistem Intelligent Core untuk BPD, integrasikan solusi 4C: Connectivity, Cloud, Cybersecurity, dan Collaboration-AI.</t>
+        </is>
+      </c>
+      <c r="F1128" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1128" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609061/lintasarta-bawa-solusi-4c-perkuat-infrastruktur-digital-bpd</t>
+        </is>
+      </c>
+      <c r="H1128" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/lintasarta-1786108005013_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1128" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>Tim 9 Kejagung Periksa Febrie sebagai Tersangka Sekaligus Saksi Kasus TPPU</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:43:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr">
+        <is>
+          <t>Kejagung memeriksa mantan Jampidsus Febrie Adriansyah sebagai tersangka dan saksi dalam kasus TPPU. Febrie terlibat dalam beberapa perkara korupsi.</t>
+        </is>
+      </c>
+      <c r="F1129" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1129" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609059/tim-9-kejagung-periksa-febrie-sebagai-tersangka-sekaligus-saksi-kasus-tppu</t>
+        </is>
+      </c>
+      <c r="H1129" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/febrie-adriansyah-dibawa-ke-kejagung-untuk-diperiksa-tim-9-1786087110132_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1129" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>Warga Desa Kawasi di Pulau Obi Kini Nikmati Air Bersih 24 Jam</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:35:39 +0700</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr">
+        <is>
+          <t>Warga Desa Kawasi merasakan manfaat air bersih 24 jam setelah relokasi. Program ini juga menyediakan infrastruktur dasar dan konektivitas yang lebih baik.</t>
+        </is>
+      </c>
+      <c r="F1130" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1130" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609053/warga-desa-kawasi-di-pulau-obi-kini-nikmati-air-bersih-24-jam</t>
+        </is>
+      </c>
+      <c r="H1130" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/harita-nickel-dukung-pemkab-halsel-sediakan-akses-air-bagi-warga-desa-kawasi-1786105965716.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1130" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>Teror Kera di Inhil Terjadi 18 Kali, Ada Korban 2 Kali Diserang</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:34:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>Mei Amelia R</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr">
+        <is>
+          <t>Kera ekor panjang menyerang warga di Inhil sebanyak 18 kali, melukai 17 orang. Setelah penangkapan, serangan dihentikan. Waspada tetap diperlukan.</t>
+        </is>
+      </c>
+      <c r="F1131" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1131" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609051/teror-kera-di-inhil-terjadi-18-kali-ada-korban-2-kali-diserang</t>
+        </is>
+      </c>
+      <c r="H1131" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kera-ekor-panjang-yang-diduga-pelaku-penyerangan-terhadap-belasan-warga-di-tembilahan-inhil-diamankan-setelah-masuk-jebakan-1786098478708_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1131" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>Polisi Dalami Pejabat Pakai Uang Negara untuk Sebar Hoax, Bakal Dijerat Korupsi</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:34:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya menelisik pejabat yang menggunakan uang negara untuk menyebarkan konten hoax. Praktik itu bisa dijerat dengan tipikor.</t>
+        </is>
+      </c>
+      <c r="F1132" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1132" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609050/polisi-dalami-pejabat-pakai-uang-negara-untuk-sebar-hoax-bakal-dijerat-korupsi</t>
+        </is>
+      </c>
+      <c r="H1132" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/dirkrimum-polda-metro-jaya-kombes-iman-imanuddin-1786096322096_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1132" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>BGN Akan Labeli Ompreng MBG, Harus Dimakan Sebelum Jam Tertentu</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:33:19 +0700</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E1133" t="inlineStr">
+        <is>
+          <t>BGN akan ketatkan aturan konsumsi MBG dengan label batas waktu. Edukasi di sekolah juga diperkuat untuk keamanan pangan.</t>
+        </is>
+      </c>
+      <c r="F1133" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1133" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609049/bgn-akan-labeli-ompreng-mbg-harus-dimakan-sebelum-jam-tertentu</t>
+        </is>
+      </c>
+      <c r="H1133" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kepala-bgn-sudaryono-brigittadetikcom-1786101809094_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1133" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>Prabowo Sebut Kecerdasan Bukan dari Sekolah, Singgung Kampusnya Bahlil</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:17:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menyatakan kecerdasan bukan dari sekolah, singgung kampusnya Menteri ESDM Bahlil Lahadalia</t>
+        </is>
+      </c>
+      <c r="F1134" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1134" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8609094/prabowo-sebut-kecerdasan-bukan-dari-sekolah-singgung-kampusnya-bahlil</t>
+        </is>
+      </c>
+      <c r="H1134" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/prabowo-hadiri-peluncuran-buku-berjudul-10-karya-nyata-untuk-negeri-setengah-abad-bahlil-lahadalia-evadetik-1786097755145_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1134" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>ISF 2026 Resmi Dibuka, Bidik Transaksi Belanja Rp38 Triliun</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:08:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr">
+        <is>
+          <t>Agung Pambudhy</t>
+        </is>
+      </c>
+      <c r="E1135" t="inlineStr">
+        <is>
+          <t>Indonesia Shopping Festival 2026 resmi dibuka di 407 mal se-Indonesia dengan target transaksi Rp38 triliun.</t>
+        </is>
+      </c>
+      <c r="F1135" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1135" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8609077/isf-2026-resmi-dibuka-bidik-transaksi-belanja-rp38-triliun</t>
+        </is>
+      </c>
+      <c r="H1135" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/indonesia-shopping-festival-2026-1786107515180_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1135" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>Bos BGN Siapkan CCTV buat Awasi Dapur MBG</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:00:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E1136" t="inlineStr">
+        <is>
+          <t>Badan Gizi Nasional (BGN) berencana mengintegrasikan kamera pengawas (CCTV) dari seluruh Satuan Pelayanan Pemenuhan Gizi (SPPG).</t>
+        </is>
+      </c>
+      <c r="F1136" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1136" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8609033/bos-bgn-siapkan-cctv-buat-awasi-dapur-mbg</t>
+        </is>
+      </c>
+      <c r="H1136" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kepala-bgn-sudaryono-brigittadetikcom-1786101809094_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1136" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>Investasi di Produsen Protein Global, Danantara Rogoh Rp 44,6 Triliun</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:45:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr">
+        <is>
+          <t>Andi Hidayat</t>
+        </is>
+      </c>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>Badan Pengelola Investasi (BPI) Danantara melalui Danantara Investment Management (DIM) menjalin kemitraan strategis dengan produsen protein global, JBS Group.</t>
+        </is>
+      </c>
+      <c r="F1137" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1137" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8609041/investasi-di-produsen-protein-global-danantara-rogoh-rp-44-6-triliun</t>
+        </is>
+      </c>
+      <c r="H1137" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/16/ilustrasi-kantor-danantara-1784212600266_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1137" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>Marshel Widianto Peluk Ibu Setelah Umur 30 Tahun, Perasaannya Dalam Banget</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:05:08 +0700</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr">
+        <is>
+          <t>Desi Puspasari</t>
+        </is>
+      </c>
+      <c r="E1138" t="inlineStr">
+        <is>
+          <t>Marshel Widianto menyingkirkan gengsi dan memberanikan diri untuk memeluk ibu pertama kali setelah berusia 30 tahun. Marshel mengaku momen itu terasa adem.</t>
+        </is>
+      </c>
+      <c r="F1138" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1138" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608681/marshel-widianto-peluk-ibu-setelah-umur-30-tahun-perasaannya-dalam-banget</t>
+        </is>
+      </c>
+      <c r="H1138" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/marshel-widianto-1786091036588_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1138" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>Situasi usai Penembakan di Sekolah Thailand yang Tewaskan 6 Orang</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:35:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1139" t="inlineStr">
+        <is>
+          <t>Sebanyak enam orang tewas dalam penembakan di sebuah sekolah ternama di Distrik Bang Kruai, Provinsi Nonthaburi, Thailand, Jumat (7/8).</t>
+        </is>
+      </c>
+      <c r="F1139" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1139" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807133125-110-1389698/situasi-usai-penembakan-di-sekolah-thailand-yang-tewaskan-6-orang</t>
+        </is>
+      </c>
+      <c r="H1139" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/thumbnail-video-1786084513510_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1139" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>Pelobi Israel Bersiap Jegal Calon Senator Muslim AS El Sayed</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:06:19 +0700</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>AIPAC mempertimbangkan untuk mengucurkan puluhan juta dolar AS untuk menjegal calon senator Muslim, Abdul El Sayed, dalam pemilihan paruh waktu.</t>
+        </is>
+      </c>
+      <c r="F1140" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1140" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807195428-134-1389929/pelobi-israel-bersiap-jegal-calon-senator-muslim-as-el-sayed</t>
+        </is>
+      </c>
+      <c r="H1140" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/politikus-demokrat-abdul-el-sayed-1785992947504_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1140" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>Pelaku Penembakan di Sekolah Thailand Diduga Belajar dari Internet</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:29:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>Pelaku penembakan di sekolah elite Debsirin, Thailand, diduga mempelajari seluk beluk aksi penembakan massal dari hasil pencarian di internet.</t>
+        </is>
+      </c>
+      <c r="F1141" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1141" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807192423-106-1389916/pelaku-penembakan-di-sekolah-thailand-diduga-belajar-dari-internet</t>
+        </is>
+      </c>
+      <c r="H1141" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/penembakan-sekolah-di-thailand-1786075379071_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1141" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>Tegang! Operasi Bedah di RS Berguncang Dahsyat saat Gempa Jepang</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:47:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>Sebuah rekaman CCTV di rumah sakit Jepang viral karena menangkap momen ketika gempa bumi mengguncang ruangan operasi di sebuah RS di Prefektur Kumamoto.</t>
+        </is>
+      </c>
+      <c r="F1142" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1142" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807183747-113-1389876/tegang-operasi-bedah-di-rs-berguncang-dahsyat-saat-gempa-jepang</t>
+        </is>
+      </c>
+      <c r="H1142" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/29/kerusakan-akibat-gempa-di-jepang-1785293352403_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1142" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>India Sukses Uji Tembak Rudal Hulu Ledak Nuklir Jangkauan 4.000 Km</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:05:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr">
+        <is>
+          <t>India telah merampungkan uji tembak senjata nuklir terbaru yang diberi nama Agni-4 pada Kamis (6/8).</t>
+        </is>
+      </c>
+      <c r="F1143" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1143" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807115259-113-1389660/india-sukses-uji-tembak-rudal-hulu-ledak-nuklir-jangkauan-4000-km</t>
+        </is>
+      </c>
+      <c r="H1143" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2021/10/28/rudal-balistik-agni-5-india_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1143" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>Filolog UNS dan Tim Temukan Mata Rantai Keilmuan Pesantren di Lereng Merapi, Sanadnya Misterius</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:47:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>Filolog UNS dan tim menemukan jejak sanad keilmuan pesantren di lereng Merapi melalui ratusan naskah Mbah Cipto yang penuh misteri.</t>
+        </is>
+      </c>
+      <c r="F1144" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1144" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865491/filolog-uns-dan-tim-temukan-mata-rantai-keilmuan-pesantren-di-lereng-merapi-sanadnya-misterius</t>
+        </is>
+      </c>
+      <c r="H1144" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/GDb0u3RBbumfe7qUvfBEiro97MA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Filolog-dan-tim-temukan-naskah-kuno-di-rumah-terlantar-di-Desa-Tumang-Cepogo-Boyolali.jpg</t>
+        </is>
+      </c>
+      <c r="I1144" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>Morowali Tak Masuk Daerah Pengolah Minerba, Menteri ESDM Bahlil: Akan Kami Cek</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:47:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>Morowali dan Morowali Utara tak masuk daftar daerah pengolah mineral dalam Kepmen ESDM 2026. Bahlil Lahadalia menyatakan akan mengecek</t>
+        </is>
+      </c>
+      <c r="F1145" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1145" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/bisnis/7865490/morowali-tak-masuk-daerah-pengolah-minerba-menteri-esdm-bahlil-akan-kami-cek</t>
+        </is>
+      </c>
+      <c r="H1145" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/c4JrnJ_-KyVcn76vqynMaMbNu2Y=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/bahlil-buka-suara-soal-morowali.jpg</t>
+        </is>
+      </c>
+      <c r="I1145" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>Kurangi Risiko Lantai Licin di Rumah, Platinum Super Stop Hadirkan Inovasi Lantai Anti-Slip Terbaru</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:39:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr">
+        <is>
+          <t>Platinum Super Stop menghadirkan keramik dengan teknologi anti-slip berstandar R12 untuk mengurangi risiko terpeleset pada area basah.</t>
+        </is>
+      </c>
+      <c r="F1146" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1146" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/lifestyle/7865489/kurangi-risiko-lantai-licin-di-rumah-platinum-super-stop-hadirkan-inovasi-lantai-anti-slip-terbaru</t>
+        </is>
+      </c>
+      <c r="H1146" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/FXTFC0viSdRcEcdw4_s9lMb-1Xw=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/LANTAI-ANTI-SLIP-PT-Platinum-Ceramics-Industry.jpg</t>
+        </is>
+      </c>
+      <c r="I1146" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>Beruang Madu Dilaporkan Serang Warga, BKSDA Riau Kirim Tim dan Pasang Kandang Jebak</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:38:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1147" t="inlineStr">
+        <is>
+          <t>BBKSDA Riau menurunkan Tim Wildlife Rescue Unit (WRU) usai menerima laporan serangan beruang madu terhadap seorang warga.</t>
+        </is>
+      </c>
+      <c r="F1147" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1147" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865488/beruang-madu-dilaporkan-serang-warga-bksda-riau-kirim-tim-dan-pasang-kandang-jebak</t>
+        </is>
+      </c>
+      <c r="H1147" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/7wyk_0JpIb0ho7_jpXcSVKyR3cg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kandang-beruang-madu1.jpg</t>
+        </is>
+      </c>
+      <c r="I1147" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>IPW: Sanksi Etik dan Pidana Tak Cukup Berantas Kasus Narkoba Oknum Polisi, Integritas Harus Ditegakkan</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:38:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr">
+        <is>
+          <t>Ketua IPW, Sugeng Teguh Santoso menegaskan sanksi etik dan pidana tidak cukup untuk memberantas tuntas keterlibatan oknum polisi dalam kasus narkoba.</t>
+        </is>
+      </c>
+      <c r="F1148" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1148" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865487/ipw-sanksi-etik-pidana-tak-cukup-berantas-kasus-narkoba-oknum-polisi-integritas-harus-ditegakkan</t>
+        </is>
+      </c>
+      <c r="H1148" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/D4UZ7vAeqc0NJq8c6hvDLc_ybII=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/wawancara-khusus-dengan-ketua-ipw-sugeng-teguh-santoso_20240710_213749.jpg</t>
+        </is>
+      </c>
+      <c r="I1148" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>Update Hasil Timnas Indonesia vs Singapura: Mitchell Baker Nyaris Nyekor, Garuda Tak Dapat Penalti</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:35:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia masih ditahan Singapura 0-0 hingga menit ke-31. Mitchell Baker nyaris mencetak gol, sementara Garuda tak mendapat penalti.</t>
+        </is>
+      </c>
+      <c r="F1149" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1149" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7865486/update-hasil-timnas-indonesia-vs-singapura-mitchell-baker-nyaris-nyekor-garuda-tak-dapat-penalti</t>
+        </is>
+      </c>
+      <c r="H1149" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/7e62AtI8Iz-kVGP2vP-7WxEOb1U=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Piala-AFF-2026-Timnas-Indonesia-Tekuk-Timor-Leste-3-0_20260731_232112.jpg</t>
+        </is>
+      </c>
+      <c r="I1149" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>50 Link Twibbon HUT ke-81 Republik Indonesia 2026, Lengkap Cara Mudah Unggah di Media Sosial</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:35:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1150" t="inlineStr">
+        <is>
+          <t>Berikut 50 twibbon HUT ke-81 Republik Indonesia 2026 yang dapat digunakan untuk update status di sosial media ataupun dikirimkan sebagai pesan.</t>
+        </is>
+      </c>
+      <c r="F1150" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1150" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865485/50-link-twibbon-hut-ke-81-republik-indonesia-2026-lengkap-cara-mudah-unggah-di-media-sosial</t>
+        </is>
+      </c>
+      <c r="H1150" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/DCuYEXOPEdEH8NAKZqaFmgDmrEQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/HUT-RI-2026-4.jpg</t>
+        </is>
+      </c>
+      <c r="I1150" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>Ketegangan Mereda? Iran Klaim Perjanjian Selat Hormuz dengan Oman Hampir Rampung</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:31:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1151" t="inlineStr">
+        <is>
+          <t>Juru Bicara Komisi Keamanan Nasional Parlemen Iran, Hassan Qashqavi, menyatakan kerangka umum perjanjian dengan Oman terkait Selat Hormuz</t>
+        </is>
+      </c>
+      <c r="F1151" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1151" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7865484/ketegangan-mereda-iran-klaim-perjanjian-selat-hormuz-dengan-oman-hampir-rampung</t>
+        </is>
+      </c>
+      <c r="H1151" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Bd1e1IxLZt15rzKTtafwMyww6zI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kapal-kapal-tanker-di-Selat-Hormuz.jpg</t>
+        </is>
+      </c>
+      <c r="I1151" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>Dorong Regenerasi Kepemimpinan PBNU, Anis Maftuhin Usul Dua Tokoh Ini Tak Maju Bursa Ketua Umum</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:29:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1152" t="inlineStr">
+        <is>
+          <t>Menurut Anis, persaingan yang hanya bertumpu pada dua figur berpotensi memperpanjang polarisasi di internal organisasi.</t>
+        </is>
+      </c>
+      <c r="F1152" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1152" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865483/dorong-regenerasi-kepemimpinan-pbnu-anis-maftuhin-usul-dua-tokoh-ini-tak-maju-bursa-ketua-umum</t>
+        </is>
+      </c>
+      <c r="H1152" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/XINpGhEhUkXdVpu5zdyEzpZccKg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/diskusi-jelangg-muktamarrrrr-nu.jpg</t>
+        </is>
+      </c>
+      <c r="I1152" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>Perluas Organisasi, Mighrul Lappung Bentuk DPW Jakarta, Septriana Tangkary Jabat Ketua</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:27:48 +0700</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>Dalam pengukuhan yang digelar di Manggala Wanabakti, Septriana Tangkary (Gelar Maharani) dipercaya memimpin DPW Mighrul Lappung DKI Jakarta</t>
+        </is>
+      </c>
+      <c r="F1153" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1153" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7865482/perluas-organisasi-mighrul-lappung-bentuk-dpw-jakarta-septriana-tangkary-jabat-ketua</t>
+        </is>
+      </c>
+      <c r="H1153" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/xLrcV-OCTkqugVNfVG74Le0pBtM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/perluas-organisasiiiiiiiiii.jpg</t>
+        </is>
+      </c>
+      <c r="I1153" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>4 Fakta Bunker di Sekolah Swasta Jaksel: Ada Narkoba dan Senjata Laras, Hanya IWD yang Punya Akses</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:23:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1154" t="inlineStr">
+        <is>
+          <t>Bunker di sekolah swasta di kawasan Kebayoran Lama, Jakarta Selatan, telah berhasil dibuka.</t>
+        </is>
+      </c>
+      <c r="F1154" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1154" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7865481/4-fakta-bunker-di-sekolah-swasta-jaksel-ada-narkoba-dan-senjata-laras-hanya-iwd-yang-punya-akses</t>
+        </is>
+      </c>
+      <c r="H1154" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/4GN1D3SMDsGS3xqRq2y20vH3An0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/bunker-sekolah-swasta-jaksel.jpg</t>
+        </is>
+      </c>
+      <c r="I1154" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>Ada Dugaan Pejabat Pakai Uang Negara Sebar Hoaks, Polisi Sebut Potensi Dijerat Pasal Tipikor</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:22:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1155" t="inlineStr">
+        <is>
+          <t>Polda Metro Jaya menyebut ada dugaan pejabat menggunakan uang negara untuk membuat dan menyebarkan hoaks. Ada potensi korupsi pada tindakan itu.</t>
+        </is>
+      </c>
+      <c r="F1155" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1155" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865480/ada-dugaan-pejabat-pakai-uang-negara-sebar-hoaks-polisi-sebut-potensi-dijerat-pasal-tipikor</t>
+        </is>
+      </c>
+      <c r="H1155" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/y5Dhakge7u48fgUcSMZn4ICWpAQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Potret-Kombes-Pol-Iman-Imanuddin.jpg</t>
+        </is>
+      </c>
+      <c r="I1155" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>Doa agar Diberi Sahabat yang Saleh/Salihah di Dunia dan Akhirat</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:20:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1156" t="inlineStr">
+        <is>
+          <t>Muslim dianjurkan untuk selektif dalam memilih sahabat karena mereka akan memberi dampak besar dalam hidup. Berikut doa agar diberi sahabat saleh.</t>
+        </is>
+      </c>
+      <c r="F1156" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1156" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/lifestyle/7865479/doa-agar-diberi-sahabat-yang-salehsalihah-di-dunia-dan-akhirat</t>
+        </is>
+      </c>
+      <c r="H1156" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/5YPdWLnxIcgguf1Epw921Bn6D08=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/DOA-SAHABAT-SALEH-4353454343.jpg</t>
+        </is>
+      </c>
+      <c r="I1156" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>Trump: Iran Ingin Buat Kesepakatan dengan AS, Singgung Harga BBM hingga Persaingan dengan China</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:15:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr">
+        <is>
+          <t>Donald Trump menyatakan Iran ingin mencapai kesepakatan dengan Washington karena tidak ingin kembali menghadapi serangan.</t>
+        </is>
+      </c>
+      <c r="F1157" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1157" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7865478/trump-iran-ingin-buat-kesepakatan-dengan-as-singgung-harga-bbm-hingga-persaingan-dengan-china</t>
+        </is>
+      </c>
+      <c r="H1157" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/pd58Lh0QZkuUPrM04LfPl7UxG4o=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/residen-AS-Donald-Trump-Senin-27-Juli-2026-Foto-Res.jpg</t>
+        </is>
+      </c>
+      <c r="I1157" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>Penguatan Kapasitas Local Hero, Upaya Pertamina Bangun Kemandirian Energi Desa</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:14:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr">
+        <is>
+          <t>PT Pertamina (Persero) tidak hanya membangun infrastruktur energi bersih, tetapi juga membangun kapasitas manusia yang mengelolanya.</t>
+        </is>
+      </c>
+      <c r="F1158" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1158" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pertamina/7865477/penguatan-kapasitas-local-hero-upaya-pertamina-bangun-kemandirian-energi-desa</t>
+        </is>
+      </c>
+      <c r="H1158" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/PHz5KKnCP5s48iUs4xSqlj37WZg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Peserta-mengikuti-kegiatan-ujian-Praktik-SERTIFIKASI-LOCAL-HERO.jpg</t>
+        </is>
+      </c>
+      <c r="I1158" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>Kuasa Gelap: Perjanjian Darah Tayang di IMAX, Jerome Kurnia Excited</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:13:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1159" t="inlineStr">
+        <is>
+          <t>Film horor garapan sutradara Rizal Mantovani, Kuasa Gelap: Perjanjian Darah dan dibintangi Jerome Kurnia hadir dalam format IMAX.</t>
+        </is>
+      </c>
+      <c r="F1159" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1159" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865476/kuasa-gelap-perjanjian-darah-tayang-di-imax-jerome-kurnia-excited</t>
+        </is>
+      </c>
+      <c r="H1159" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ki80OAaU5FqjqofJdSqIK0hzaQQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Jerome-Kurnia-1-07082026.jpg</t>
+        </is>
+      </c>
+      <c r="I1159" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>Merdeka Master 2026 Jadi Ajang Regenerasi Atlet Berkuda Indonesia Menuju Pentas Internasional</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:12:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>Kompetisi tahun ini dibagi dalam dua disiplin utama, yakni show jumping pada 6-9 Agustus 2026 dan dressage pada 14-16 Agustus 2026.</t>
+        </is>
+      </c>
+      <c r="F1160" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1160" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7865475/merdeka-master-2026-jadi-ajang-regenerasi-atlet-berkuda-indonesia-menuju-pentas-internasional</t>
+        </is>
+      </c>
+      <c r="H1160" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/XvB1BISLRRH4x0rI03pq1hhqs3A=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Turnamen-berkuda-Mandiri-Merdeka-Master-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I1160" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>Mahasiswi Korban Konten Pornografi Deepfake AI di Solo Depresi, Keluarga Pelaku Memohon Damai</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:07:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr">
+        <is>
+          <t>Mahasiswi Solo korban konten pornografi AI alami depresi, kasus dilaporkan ke Polda Jateng, tersangka mantan kekasih ditahan.</t>
+        </is>
+      </c>
+      <c r="F1161" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1161" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865474/mahasiswi-korban-konten-pornografi-deepfake-ai-di-solo-depresi-keluarga-pelaku-memohon-damai</t>
+        </is>
+      </c>
+      <c r="H1161" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/GIBC_E0D5q-3JLzPHyHY6i0Q_Z0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Kasus-konten-pornografi-berbasis-AI-di-Solo-menimpa-mahasiswi-E-yang-sempat-depresi.jpg</t>
+        </is>
+      </c>
+      <c r="I1161" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>Anggota Fraksi PDIP Minta Kenaikan Gaji Kepala Daerah Ditunda, Tunggu Fiskal Membaik</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:02:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr">
+        <is>
+          <t>Fraksi PDI Perjuangan (PDIP) DPR RI meminta wacana kenaikan gaji kepala daerah tidak dilakukan secara terburu-buru.</t>
+        </is>
+      </c>
+      <c r="F1162" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1162" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865473/anggota-fraksi-pdip-minta-kenaikan-gaji-kepala-daerah-ditunda-tunggu-fiskal-membaik</t>
+        </is>
+      </c>
+      <c r="H1162" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/LZRWwfA97lebPe-PeKLkaZM5gIA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Giri-Ramanda-Kiemas-4321.jpg</t>
+        </is>
+      </c>
+      <c r="I1162" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>Sempat Langka, Kini Pasokan Susu UHT di Solo Normal Lagi: Begini Cara Coffee Shop Bertahan</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:59:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr">
+        <is>
+          <t>Pasokan susu UHT di Solo kini kembali normal setelah sempat langka pada Februari hingga April 2026.</t>
+        </is>
+      </c>
+      <c r="F1163" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1163" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865472/sempat-langka-kini-pasokan-susu-uht-di-solo-normal-lagi-begini-cara-coffee-shop-bertahan</t>
+        </is>
+      </c>
+      <c r="H1163" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/nccIpsdzZFPG75gyydPZ_yBTQ28=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/White-Desk.jpg</t>
+        </is>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>Thailand Obral Insentif Pajak Demi Gaet Pabrik Mobil Baru</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1164" t="inlineStr">
+        <is>
+          <t>Pemerintah Thailand luncurkan kebijakan baru untuk industri otomotif, termasuk pemangkasan tarif cukai dan dukungan investasi.</t>
+        </is>
+      </c>
+      <c r="F1164" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1164" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807164652-4-757499/thailand-obral-insentif-pajak-demi-gaet-pabrik-mobil-baru</t>
+        </is>
+      </c>
+      <c r="H1164" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/10/27/perakitan-kendaraan-sebagai-salah-satu-bagian-dari-produksi-kendaraan-di-pabrik-daihatsu-kyoto-jepang-senin-27102025-1761553853531_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>SKK Migas, PHR dan Polda Riau Perkuat Sinergi Lindungi Aset Negara</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:57:08 +0700</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr">
+        <is>
+          <t>dpu</t>
+        </is>
+      </c>
+      <c r="E1165" t="inlineStr">
+        <is>
+          <t>PT Pertamina Hulu Rokan dan SKK Migas adakan FGD untuk sinergi lintas instansi dalam melindungi aset negara dan mendukung keberlanjutan operasi hulu migas.</t>
+        </is>
+      </c>
+      <c r="F1165" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1165" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807205354-4-757545/skk-migas-phr-dan-polda-riau-perkuat-sinergi-lindungi-aset-negara</t>
+        </is>
+      </c>
+      <c r="H1165" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/pertamina-hulu-rokan-1786111014470_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1165" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>Hambatan Ekspor Mineral Tuntas, 100 Lebih Kapal Kembali Beroperasi</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:50:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr">
+        <is>
+          <t>Verda Nano Setiawan</t>
+        </is>
+      </c>
+      <c r="E1166" t="inlineStr">
+        <is>
+          <t>KSP memastikan hambatan ekspor komoditas mineral akibat perbedaan interpretasi kandungan Logam Tanah Jarang (LTJ) telah diselesaikan</t>
+        </is>
+      </c>
+      <c r="F1166" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1166" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807191132-4-757533/hambatan-ekspor-mineral-tuntas-100-lebih-kapal-kembali-beroperasi</t>
+        </is>
+      </c>
+      <c r="H1166" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/03/kepala-staf-kepresidenan-dudung-abdurachman-saat-konferensi-pers-terkait-polemik-larangan-ekspor-mineral-yang-mengandung-logam-1785723409908_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1166" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>Perkuat Layanan, bank bjb Borong Lima Penghargaan di Ajang Ini!</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:48:24 +0700</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1167" t="inlineStr">
+        <is>
+          <t>Bank bjb meraih lima penghargaan Titanium Awards 2026, mengukuhkan komitmen inovasi layanan perbankan digital yang unggul dan berorientasi pada nasabah.</t>
+        </is>
+      </c>
+      <c r="F1167" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1167" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807204607-4-757544/perkuat-layanan-bank-bjb-borong-lima-penghargaan-di-ajang-ini</t>
+        </is>
+      </c>
+      <c r="H1167" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/bank-bjb-1786109016810_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1167" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>BGN Perketat Dapur MBG: CCTV Dipantau Pusat-Cek Kesehatan Rutin</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:30:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr">
+        <is>
+          <t>Zefanya Aprilia</t>
+        </is>
+      </c>
+      <c r="E1168" t="inlineStr">
+        <is>
+          <t>Badan Gizi Nasional (BGN) menyiapkan serangkaian langkah baru untuk memperketat pengawasan operasional dapur MBG</t>
+        </is>
+      </c>
+      <c r="F1168" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1168" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807184659-4-757532/bgn-perketat-dapur-mbg-cctv-dipantau-pusat-cek-kesehatan-rutin</t>
+        </is>
+      </c>
+      <c r="H1168" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/29/kepala-badan-gizi-nasional-bgn-sudaryono-saat-konferensi-pers-di-kantornya-jakarta-rabu-2972026-cnbc-indonesiamartyasari-rizki-1785315972564_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1168" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>Pemboran Masif dan Kolaborasi Teknologi Kunci Kemandirian Energi</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:21:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1169" t="inlineStr">
+        <is>
+          <t>Indonesia menetapkan kebijakan strategis untuk ketahanan energi. PHE fokus pada pengeboran masif dan eksplorasi untuk mendukung pertumbuhan ekonomi.</t>
+        </is>
+      </c>
+      <c r="F1169" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1169" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807201624-4-757543/pemboran-masif-kolaborasi-teknologi-kunci-kemandirian-energi</t>
+        </is>
+      </c>
+      <c r="H1169" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/pertamina-hulu-energi-1786108795692_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1169" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>Mobil China Bersiap Banjiri RI, Mau Buka 80 Diler Baru</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:10:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1170" t="inlineStr">
+        <is>
+          <t>Pabrikan mobil asal China terus mempercepat ekspansi bisnisnya di Indonesia</t>
+        </is>
+      </c>
+      <c r="F1170" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1170" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807183603-4-757531/mobil-china-bersiap-banjiri-ri-mau-buka-80-diler-baru</t>
+        </is>
+      </c>
+      <c r="H1170" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/29/jaecoo-indonesia-resmi-memperkenalkan-omoda-o4-ev-di-ajang-gaikindo-indonesia-international-auto-show-giias-2026-cnbc-indonesi-1785320118392_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1170" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>Perang AS-Iran Kembali Makan Korban Jepang</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1171" t="inlineStr">
+        <is>
+          <t>Pengeluaran rumah tangga Jepang merosot 3,3% pada Juni 2026, dipengaruhi cuaca buruk dan ketidakpastian akibat konflik AS-Iran. Daya beli masyarakat tertekan.</t>
+        </is>
+      </c>
+      <c r="F1171" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1171" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807163657-4-757496/perang-as-iran-kembali-makan-korban-jepang</t>
+        </is>
+      </c>
+      <c r="H1171" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/12/04/bendera-jepang-reutersissei-katofile-photo-1764827389770_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1171" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>Video:Wamenko Pangan Sidak TPST Bantar Gebang</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:50:46 +0700</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1172" t="inlineStr">
+        <is>
+          <t>Wamenko Pangan Sidak TPST Bantar Gebang, Pastikan Tranformasi Sistem Olah Sampah Sesuai Target</t>
+        </is>
+      </c>
+      <c r="F1172" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1172" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807154504-8-757468/videowamenko-pangan-sidak-tpst-bantar-gebang</t>
+        </is>
+      </c>
+      <c r="H1172" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/wamenko-pangan-sidak-tpst-bantar-gebang-pastikan-tranformasi-sistem-olah-sampah-sesuai-target-1786104896708_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1172" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>Fenomena Baru di Korea, Bayi Ramai-Ramai Punya Rekening Investasi</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr">
+        <is>
+          <t>Fenomena orang tua di Korea Selatan (Korsel) membuka rekening investasi untuk anak semakin meningkat.</t>
+        </is>
+      </c>
+      <c r="F1173" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1173" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807155452-4-757475/fenomena-baru-di-korea-bayi-ramai-ramai-punya-rekening-investasi</t>
+        </is>
+      </c>
+      <c r="H1173" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/ilustrasi-bendera-korea-selatan-1786094146060_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1173" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>Krisis 2026 Menggila, Perusahaan China Justru Dulang Cuan</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:30:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr">
+        <is>
+          <t>Novina Putri Bestari</t>
+        </is>
+      </c>
+      <c r="E1174" t="inlineStr">
+        <is>
+          <t>Krisis RAM masih terus berlanjut pada tahun ini. Di tengah masalah tersebut, chip buatan perusahaan China laku keras.</t>
+        </is>
+      </c>
+      <c r="F1174" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1174" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807180532-4-757528/krisis-2026-menggila-perusahaan-china-justru-dulang-cuan</t>
+        </is>
+      </c>
+      <c r="H1174" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/04/13/china-chipstariffs-1744522939332_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1174" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>Nasib 950 Dapur MBG Terancam, Sudaryono Ungkap Biang Masalahnya</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:20:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>Kepala BGN, Sudaryono, memperketat pengawasan dapur program Makan Bergizi Gratis. 950 dapur terancam.</t>
+        </is>
+      </c>
+      <c r="F1175" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1175" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807175109-4-757527/nasib-950-dapur-mbg-terancam-sudaryono-ungkap-biang-masalahnya</t>
+        </is>
+      </c>
+      <c r="H1175" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/24/sidak-perdana-kepala-badan-gizi-nasional-bgn-sudaryono-ke-sejumlah-dapur-sppg-di-bogor-jumat-2472026-dok-biro-humas-bgn-1784873744033_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1175" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>Video: Terminal LPG Tanjung Sekong Raih GTLC Bintang Dua</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:50:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1176" t="inlineStr">
+        <is>
+          <t>Pertama di Dunia! Terminal LPG Tanjung Sekong Raih Sertifikasi Berkelanjutan Bintang Dua</t>
+        </is>
+      </c>
+      <c r="F1176" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1176" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807165655-8-757510/video-terminal-lpg-tanjung-sekong-raih-gtlc-bintang-dua</t>
+        </is>
+      </c>
+      <c r="H1176" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/pertama-di-dunia-terminal-lpg-tanjung-sekong-raih-sertifikasi-berkelanjutan-bintang-dua-1786097227918_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1176" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>Geber Kepatuhan Pajak, DJP Teken MoU dengan GP Ansor di Jatim</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:50:08 +0700</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr">
+        <is>
+          <t>Arrijal Rachman</t>
+        </is>
+      </c>
+      <c r="E1177" t="inlineStr">
+        <is>
+          <t>Direktorat Jenderal Pajak (DJP) Jawa Timur bersama Pimpinan Wilayah (PW) Gerakan Pemuda (GP) Ansor Jawa Timur menandatangani kerja sama</t>
+        </is>
+      </c>
+      <c r="F1177" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1177" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807174012-4-757524/geber-kepatuhan-pajak-djp-teken-mou-dengan-gp-ansor-di-jatim</t>
+        </is>
+      </c>
+      <c r="H1177" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/dirjen-pajak-bimo-wijayanto-menyaksikan-penandatangan-kerja-sama-peningkatan-kepatuhan-pajak-djp-jawa-timur-dengan-gp-ansor-ja-1786100204847_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>RI Dikepung Mobil China, Bos Daihatsu Ungkap Hal Tak Terduga</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1178" t="inlineStr">
+        <is>
+          <t>Daihatsu buka suara soal makin banyak merek China masuk pasar Indonesia. Apa katanya?</t>
+        </is>
+      </c>
+      <c r="F1178" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1178" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807171434-4-757517/ri-dikepung-mobil-china-bos-daihatsu-ungkap-hal-tak-terduga</t>
+        </is>
+      </c>
+      <c r="H1178" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/29/suasana-press-day-saat-acara-gaikindo-indonesia-international-auto-show-giias-2026-di-ice-bsd-kabupaten-tangerang-banten-rabu--1785307480010_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>Pembangunan Kawasan DPR di IKN Ditargetkan Rampung Akhir 2027</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:31:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr">
+        <is>
+          <t>Satria K Yudha</t>
+        </is>
+      </c>
+      <c r="E1179" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, PENAJAM PASER UTARA – Pembangunan kawasan Dewan Perwakilan Rakyat (DPR) di Ibu Kota Nusantara (IKN) terus memasuki tahapan konstruksi untuk mengejar target penyelesaian pada akhir 2027. Selain percepatan pekerjaan,...</t>
+        </is>
+      </c>
+      <c r="F1179" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1179" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjeiou416/pembangunan-kawasan-dpr-di-ikn-ditargetkan-rampung-akhir-2027</t>
+        </is>
+      </c>
+      <c r="H1179" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/_260807203034-505.png</t>
+        </is>
+      </c>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>Presiden Sebut Bahlil Inspirasi Anak Muda</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:26:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E1180" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Presiden Prabowo Subianto mengaku belum lama mengenal Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia. Meski demikian, ia menilai perjalanan hidup dan kiprah Bahlil dapat menjadi...</t>
+        </is>
+      </c>
+      <c r="F1180" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1180" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjehzf423/presiden-sebut-bahlil-inspirasi-anak-muda</t>
+        </is>
+      </c>
+      <c r="H1180" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/011578400-1738845029-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>Energi</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>Bangun Kemandirian Energi Desa dengan Penguatan Kapasitas Local Hero</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:10:46 +0700</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr">
+        <is>
+          <t>Ferry kisihandi</t>
+        </is>
+      </c>
+      <c r="E1181" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, MAGELANG -- Setiap musim kemarau, Alfredo Nicholas Saputra Kolin, warga Kampung Posa, Distrik Klamono, Kabupaten Sorong, Papua Barat Daya, selalu dihantui kegelisahan akan ketersediaan air bersih untuk memenuhi...</t>
+        </is>
+      </c>
+      <c r="F1181" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1181" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjehxy472/bangun-kemandirian-energi-desa-dengan-penguatan-kapasitas-local-hero</t>
+        </is>
+      </c>
+      <c r="H1181" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/pertamina-terus-memperkuat-kapasitas-para-local-hero-agar-manfaat_260807200524-153.jpeg</t>
+        </is>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>Bisnis</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>BGN Temukan 950 Dapur MBG Diduga tak Layak Higiene dan Sanitasi</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:50:39 +0700</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr">
+        <is>
+          <t>Gita Amanda</t>
+        </is>
+      </c>
+      <c r="E1182" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Badan Gizi Nasional (BGN) menemukan sekitar 950 satuan pelayanan pemenuhan gizi (SPPG) yang diduga tidak layak higiene dan sanitasi di berbagai wilayah Indonesia. Ratusan dapur program Makan...</t>
+        </is>
+      </c>
+      <c r="F1182" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1182" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjeh0f423/bgn-temukan-950-dapur-mbg-diduga-tak-layak-higiene-dan-sanitasi</t>
+        </is>
+      </c>
+      <c r="H1182" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/009442800-1775755276-830-556.jpg</t>
+        </is>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>Kejagung Tak Gentar Hadapi Perlawanan Febrie</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:56:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1183" t="inlineStr">
+        <is>
+          <t>Kejagung sudah siapkan tim hadapi praperadilan Febrie.</t>
+        </is>
+      </c>
+      <c r="F1183" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1183" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264645/kejagung-tak-gentar-hadapi-perlawanan-febrie</t>
+        </is>
+      </c>
+      <c r="H1183" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/w_GeOd-UYoIvUQ2hdbIaeIz-tIY=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/5512712/original/018042200_1771992094-WhatsApp_Image_2026-02-25_at_10.59.24.jpeg</t>
+        </is>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>Kejagung Fokus Dalami Peran 3 Tersangka Kasus TPPU Eks Jampidsus Febrie</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:46:39 +0700</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1184" t="inlineStr">
+        <is>
+          <t>Kejagung masih mendalami peran tiga tersangka dan sejumlah barang bukti dalam penyidikan dugaan TPPU yang menjerat Febrie Adriansyah.</t>
+        </is>
+      </c>
+      <c r="F1184" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1184" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264642/kejagung-fokus-dalami-peran-3-tersangka-kasus-tppu-eks-jampidsus-febrie</t>
+        </is>
+      </c>
+      <c r="H1184" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/O9ygHu6SH_fJNl2Jr1f2FfozEX4=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318064/original/091991500_1786085263-IMG_20260807_131251_051.jpg</t>
+        </is>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>BGN Segera Coret Sekolah Swasta Elite dari Daftar Penerima MBG</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:39:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1185" t="inlineStr">
+        <is>
+          <t>Menurut Kepala BGN Sudaryono,  ada ratusan sekolah swasta yang menyatakan tak perlu MBG lagi.</t>
+        </is>
+      </c>
+      <c r="F1185" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1185" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264636/bgn-segera-coret-sekolah-swasta-elite-dari-daftar-penerima-mbg</t>
+        </is>
+      </c>
+      <c r="H1185" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/CSIKMS1zrLfH-SxfmCKYABQjZXw=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9295136/original/006741400_1783915651-mbg2.jpg</t>
+        </is>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>Kepala BGN Minta Maaf Marak Kasus Keracunan MBG</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:34:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1186" t="inlineStr">
+        <is>
+          <t>Kepala BGN Sudaryono minta maaf soal kasus keracunan MBG dan siapkan evaluasi serta sanksi.</t>
+        </is>
+      </c>
+      <c r="F1186" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1186" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264632/kepala-bgn-minta-maaf-marak-kasus-keracunan-mbg</t>
+        </is>
+      </c>
+      <c r="H1186" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/AEUfMbarOxgEuI-QjtVxgiBEenw=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318604/original/089170000_1786109673-IMG_20260807_161304_740.jpg</t>
+        </is>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>Kejagung Masih Tutup Rapat Hasil Penggeledahan Kasus Febrie Adriansyah</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:00:42 +0700</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>Sejumlah tempat di Jakarta, Depok, dan Bandung sempat digeledah terkait kasus Febrie.</t>
+        </is>
+      </c>
+      <c r="F1187" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1187" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264618/kejagung-masih-tutup-rapat-hasil-penggeledahan-kasus-febrie-adriansyah</t>
+        </is>
+      </c>
+      <c r="H1187" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/8OviIyZeymT8yDSWQW6PjdTfb54=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318587/original/009745600_1786107626-IMG_3025.jpg</t>
+        </is>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>950 Dapur MBG Diduga Tak Layak Sanitasi, BGN Ancam Tutup Permanen</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:56:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1188" t="inlineStr">
+        <is>
+          <t>BGN mengungkap 950 dapur MBG diduga tak memenuhi standar higiene sanitasi.</t>
+        </is>
+      </c>
+      <c r="F1188" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1188" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264617/950-dapur-mbg-diduga-tak-layak-sanitasi-bgn-ancam-tutup-permanen</t>
+        </is>
+      </c>
+      <c r="H1188" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/9F_7ivcn8DQxire7ZoZK4CYXkCU=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318586/original/083221800_1786107411-IMG_20260807_161335_949.jpg</t>
+        </is>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>Money</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>Luhut: Dulu Hilirisasi Nikel Dicibir, Kini Investor Asing Antre Temui Bahlil</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:12:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1189" t="inlineStr">
+        <is>
+          <t>Luhut Pandjaitan kenang awal larangan ekspor nikel dicibir dan digugat WTO. Kini, kebijakan hilirisasi berhasil menarik investor, dorong ekonomi daerah tumbuh dobel digit.</t>
+        </is>
+      </c>
+      <c r="F1189" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1189" t="inlineStr">
+        <is>
+          <t>https://money.kompas.com/read/2026/08/07/211050526/luhut-dulu-hilirisasi-nikel-dicibir-kini-investor-asing-antre-temui-bahlil</t>
+        </is>
+      </c>
+      <c r="H1189" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/5nmO6_gpJPPgt6dlo3_2jFQTHPQ=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815e7ef28.png,0,-0,1)/data/photo/2026/08/07/6a75e527e7399.jpg</t>
+        </is>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>Kebakaran Gunung Bromo Diduga akibat Aktivitas Manusia</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:12:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1190" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan Gunung Bromo diduga bukan disebabkan oleh faktor alam, melainkan akibat aktivitas manusia yang melintas di jalur trabasan</t>
+        </is>
+      </c>
+      <c r="F1190" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1190" t="inlineStr">
+        <is>
+          <t>https://surabaya.kompas.com/read/2026/08/07/205247678/kebakaran-gunung-bromo-diduga-akibat-aktivitas-manusia</t>
+        </is>
+      </c>
+      <c r="H1190" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/Z_WZJFDTuYNEd-9bJyrY0Z5kLaI=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/07/6a75da4f3b957.jpeg</t>
+        </is>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>Sungai Cihaur di Bandung Barat Berbusa dan Menghitam, Warga Sebut Pencemaran Sudah 25 Tahun</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:12:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1191" t="inlineStr">
+        <is>
+          <t>Aliran air Sungai Cihaur Bandung Barat berbusa dan menghitam selama 25 tahun terakhir.</t>
+        </is>
+      </c>
+      <c r="F1191" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1191" t="inlineStr">
+        <is>
+          <t>https://bandung.kompas.com/read/2026/08/07/203005978/sungai-cihaur-di-bandung-barat-berbusa-dan-menghitam-warga-sebut-pencemaran</t>
+        </is>
+      </c>
+      <c r="H1191" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/ILeZpW6fuih3WckevaU_twufKj0=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/07/6a75d8ba99dff.jpeg</t>
+        </is>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1067"/>
+  <autoFilter ref="A1:I1191"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-07.xlsx
+++ b/data/berita_2026-08-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1191</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1295</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1191"/>
+  <dimension ref="A1:I1295"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -56410,8 +56410,4896 @@
         </is>
       </c>
     </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>Suzuki ramaikan persaingan mobil irit BBM di segmen LSUV</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:37:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E1192" t="inlineStr">
+        <is>
+          <t>Persaingan di industri otomotif segmen Low Sport Utility Vehicle (LSUV) di Indonesia, semakin menunjukkan keseriusannya ...</t>
+        </is>
+      </c>
+      <c r="F1192" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1192" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5685115/suzuki-ramaikan-persaingan-mobil-irit-bbm-di-segmen-lsuv</t>
+        </is>
+      </c>
+      <c r="H1192" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-07-31-at-09.15.48.jpeg</t>
+        </is>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>Kongres MGBKGI di Unhas fokus perkuat riset berdampak</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:35:44 +0700</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1193" t="inlineStr">
+        <is>
+          <t>Universitas Hasanuddin (Unhas) menggelar kongres perdana Majelis Guru Besar Kedokteran Gigi Indonesia (MGBKGI) yang ...</t>
+        </is>
+      </c>
+      <c r="F1193" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1193" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685109/kongres-mgbkgi-di-unhas-fokus-perkuat-riset-berdampak</t>
+        </is>
+      </c>
+      <c r="H1193" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG-20260807-WA0064.jpg</t>
+        </is>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>Pemprov beri 20 hektare, minta Mensos tambah Sekolah Rakyat di Sulsel</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:35:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1194" t="inlineStr">
+        <is>
+          <t>Gubernur Sulawesi Selatan (Sulsel) Andi Sudirman Sulaiman meminta kepada Menteri Sosial Saifullah Yusuf (Gus Ipul) ...</t>
+        </is>
+      </c>
+      <c r="F1194" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1194" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685108/pemprov-beri-20-hektare-minta-mensos-tambah-sekolah-rakyat-di-sulsel</t>
+        </is>
+      </c>
+      <c r="H1194" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/download.jpg</t>
+        </is>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1195" t="inlineStr">
+        <is>
+          <t>RealCo: Hilirisasi sarang walet buka peluang nilai tambah ekspor RI</t>
+        </is>
+      </c>
+      <c r="C1195" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:34:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1195" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1195" t="inlineStr">
+        <is>
+          <t>CEO PT Abadi Lestari Indonesia Tbk (RealCo) Edwin Pranata menilai hilirisasi sarang burung walet (SBW) dapat ...</t>
+        </is>
+      </c>
+      <c r="F1195" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1195" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685104/realco-hilirisasi-sarang-walet-buka-peluang-nilai-tambah-ekspor-ri</t>
+        </is>
+      </c>
+      <c r="H1195" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000178490.jpg</t>
+        </is>
+      </c>
+      <c r="I1195" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1196" t="inlineStr">
+        <is>
+          <t>Muktamar XI Himi Persis tegaskan transformasi gerakan bangun peradaban</t>
+        </is>
+      </c>
+      <c r="C1196" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:27:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1196" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1196" t="inlineStr">
+        <is>
+          <t>Himpunan Mahasiswi Persatuan Islam (Himi Persis) menggelar Muktamar XI di Gedung PPSDM Kemendikdasmen, Depok, pada 7-9 ...</t>
+        </is>
+      </c>
+      <c r="F1196" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1196" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685100/muktamar-xi-himi-persis-tegaskan-transformasi-gerakan-bangun-peradaban</t>
+        </is>
+      </c>
+      <c r="H1196" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000177104.jpg</t>
+        </is>
+      </c>
+      <c r="I1196" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1197" t="inlineStr">
+        <is>
+          <t>Marco Palestra yakin Chelsea jalani musim hebat bersama Alonso</t>
+        </is>
+      </c>
+      <c r="C1197" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:25:46 +0700</t>
+        </is>
+      </c>
+      <c r="D1197" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1197" t="inlineStr">
+        <is>
+          <t>Pemain rekrutan baru Chelsea Marco Palestra meyakini Chelsea akan menjalani musim kompetisi yang hebat di bawah asuhan ...</t>
+        </is>
+      </c>
+      <c r="F1197" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1197" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685099/marco-palestra-yakin-chelsea-jalani-musim-hebat-bersama-alonso</t>
+        </is>
+      </c>
+      <c r="H1197" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_20260807_220403.jpg</t>
+        </is>
+      </c>
+      <c r="I1197" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1198" t="inlineStr">
+        <is>
+          <t>Berkat bantuan kewirausahaan Kemensos, Oneng stop mengemis</t>
+        </is>
+      </c>
+      <c r="C1198" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:25:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1198" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1198" t="inlineStr">
+        <is>
+          <t>Eks pengemis di Kota Bandung, Oneng, kini berhasil alih profesi menjadi penjual kopi dan aneka minuman di warung berkat ...</t>
+        </is>
+      </c>
+      <c r="F1198" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1198" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685096/berkat-bantuan-kewirausahaan-kemensos-oneng-stop-mengemis</t>
+        </is>
+      </c>
+      <c r="H1198" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-20.41.19.jpeg</t>
+        </is>
+      </c>
+      <c r="I1198" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1199" t="inlineStr">
+        <is>
+          <t>LPSK: Pembayaran restitusi korban TPKS baru Rp87,69 juta</t>
+        </is>
+      </c>
+      <c r="C1199" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:24:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1199" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1199" t="inlineStr">
+        <is>
+          <t>Lembaga Pelindungan Saksi dan Korban (LPSK) mencatat realisasi pembayaran restitusi oleh pelaku tindak pidana kekerasan ...</t>
+        </is>
+      </c>
+      <c r="F1199" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1199" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685092/lpsk-pembayaran-restitusi-korban-tpks-baru-rp8769-juta</t>
+        </is>
+      </c>
+      <c r="H1199" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001224422.jpg</t>
+        </is>
+      </c>
+      <c r="I1199" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1200" t="inlineStr">
+        <is>
+          <t>Indonesia bermain imbang 1-1 kontra Singapura</t>
+        </is>
+      </c>
+      <c r="C1200" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:24:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1200" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1200" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia bermain imbang dengan skor 1-1 kontra Timnas Singapura pada pertandingan Grup A Piala AFF 2026 di ...</t>
+        </is>
+      </c>
+      <c r="F1200" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1200" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685091/indonesia-bermain-imbang-1-1-kontra-singapura</t>
+        </is>
+      </c>
+      <c r="H1200" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/03/timnas-indonesia-lawan-vietnam-di-piala-aff-2833516.jpg</t>
+        </is>
+      </c>
+      <c r="I1200" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1201" t="inlineStr">
+        <is>
+          <t>LPM bentuk jaringan pengaman guna lawan 4 penyakit sosial di desa</t>
+        </is>
+      </c>
+      <c r="C1201" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:22:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1201" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1201" t="inlineStr">
+        <is>
+          <t>DPP Lembaga Pemberdayaan Masyarakat (LPM) menyatakan bakal membentuk jaringan posko sebagai katup pengaman di seluruh ...</t>
+        </is>
+      </c>
+      <c r="F1201" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1201" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685087/lpm-bentuk-jaringan-pengaman-guna-lawan-4-penyakit-sosial-di-desa</t>
+        </is>
+      </c>
+      <c r="H1201" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000036267.jpg</t>
+        </is>
+      </c>
+      <c r="I1201" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1202" t="inlineStr">
+        <is>
+          <t>Komisi VI DPR dan BRI Situbondo edukasi pencegahan kejahatan digital</t>
+        </is>
+      </c>
+      <c r="C1202" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:19:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1202" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1202" t="inlineStr">
+        <is>
+          <t>Komisi VI Dewan Perwakilan Rakyat Republik Indonesia bersama PT Bank Rakyat Indonesia (Persero) Tbk Cabang Situbondo, ...</t>
+        </is>
+      </c>
+      <c r="F1202" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1202" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685083/komisi-vi-dpr-dan-bri-situbondo-edukasi-pencegahan-kejahatan-digital</t>
+        </is>
+      </c>
+      <c r="H1202" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG-20260807-WA0154.jpg</t>
+        </is>
+      </c>
+      <c r="I1202" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1203" t="inlineStr">
+        <is>
+          <t>PM Spanyol perketat keamanan saat liburan di tengah krisis migrasi</t>
+        </is>
+      </c>
+      <c r="C1203" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:18:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1203" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1203" t="inlineStr">
+        <is>
+          <t>Perdana Menteri Spanyol Pedro Sanchez memperketat penjagaan keamanan selama melakukan liburan di Kepulauan Canary dan ...</t>
+        </is>
+      </c>
+      <c r="F1203" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1203" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685079/pm-spanyol-perketat-keamanan-saat-liburan-di-tengah-krisis-migrasi</t>
+        </is>
+      </c>
+      <c r="H1203" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/timnas-spanyol-juara-piala-dunia-2026-2824285.jpg</t>
+        </is>
+      </c>
+      <c r="I1203" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1204" t="inlineStr">
+        <is>
+          <t>Ratusan siswa Sekolah Rakyat Makassar sambut Mensos dengan "paper mob"</t>
+        </is>
+      </c>
+      <c r="C1204" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:17:46 +0700</t>
+        </is>
+      </c>
+      <c r="D1204" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1204" t="inlineStr">
+        <is>
+          <t>Ratusan siswa menyambut kedatangan Menteri Sosial Saifullah Yusuf (Gus Ipul) dengan penampilan paper mob di Sekolah ...</t>
+        </is>
+      </c>
+      <c r="F1204" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1204" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685075/ratusan-siswa-sekolah-rakyat-makassar-sambut-mensos-dengan-paper-mob</t>
+        </is>
+      </c>
+      <c r="H1204" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-20.24.11.jpeg</t>
+        </is>
+      </c>
+      <c r="I1204" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1205" t="inlineStr">
+        <is>
+          <t>Gempa magnitudo 5,0 guncang barat laut Jepara pada Jumat malam</t>
+        </is>
+      </c>
+      <c r="C1205" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:16:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1205" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1205" t="inlineStr">
+        <is>
+          <t>Gempa bumi magnitudo 5,0 mengguncang wilayah perairan Laut Jawa, tepatnya di 102 kilometer ke arah barat laut dari ...</t>
+        </is>
+      </c>
+      <c r="F1205" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1205" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685071/gempa-magnitudo-50-guncang-barat-laut-jepara-pada-jumat-malam</t>
+        </is>
+      </c>
+      <c r="H1205" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/18/ilustrasi-gempa-3_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1205" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1206" t="inlineStr">
+        <is>
+          <t>Pemerintah siapkan aturan PT Timah serap produksi tambang rakyat</t>
+        </is>
+      </c>
+      <c r="C1206" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:15:46 +0700</t>
+        </is>
+      </c>
+      <c r="D1206" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1206" t="inlineStr">
+        <is>
+          <t>Kementerian Energi dan Sumber Daya Mineral (ESDM) menyampaikan pemerintah sedang mempersiapkan peraturan presiden ...</t>
+        </is>
+      </c>
+      <c r="F1206" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1206" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685068/pemerintah-siapkan-aturan-pt-timah-serap-produksi-tambang-rakyat</t>
+        </is>
+      </c>
+      <c r="H1206" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/10/16/target-produksi-pt-timah-hingga-akhir-2025-2647369.jpg</t>
+        </is>
+      </c>
+      <c r="I1206" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1207" t="inlineStr">
+        <is>
+          <t>Satya Wacana lepas Hengky Lakay usai kebersamaan selama sembilan tahun</t>
+        </is>
+      </c>
+      <c r="C1207" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:13:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1207" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1207" t="inlineStr">
+        <is>
+          <t>Satya Wacana Salatiga memutuskan untuk melepas kapten tim Henry Cornelis Lakay atau kerap disapa Hengky Lakay, setelah ...</t>
+        </is>
+      </c>
+      <c r="F1207" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1207" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685065/satya-wacana-lepas-hengky-lakay-usai-kebersamaan-selama-sembilan-tahun</t>
+        </is>
+      </c>
+      <c r="H1207" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/09/02/IBla.jpeg</t>
+        </is>
+      </c>
+      <c r="I1207" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1208" t="inlineStr">
+        <is>
+          <t>Kubu Febrie Adriansyah siapkan saksi dan ahli meringankan</t>
+        </is>
+      </c>
+      <c r="C1208" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:10:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1208" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1208" t="inlineStr">
+        <is>
+          <t>Kubu mantan Jaksa Agung Muda Bidang Tindak Pidana Khusus (Jampidsus) Febrie Adriansyah akan menghadirkan saksi dan ahli ...</t>
+        </is>
+      </c>
+      <c r="F1208" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1208" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685063/kubu-febrie-adriansyah-siapkan-saksi-dan-ahli-meringankan</t>
+        </is>
+      </c>
+      <c r="H1208" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000087486.jpg</t>
+        </is>
+      </c>
+      <c r="I1208" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1209" t="inlineStr">
+        <is>
+          <t>Siap guncang GBK besok! Intip aksi memukau skuad AC Milan di Senayan sebelum jamu Chelsea</t>
+        </is>
+      </c>
+      <c r="C1209" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:10:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1209" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1209" t="inlineStr">
+        <is>
+          <t>Pesepak bola AC Milan mengikuti sesi latihan di Stadion Madya, Senayan, Jakarta, Jumat (7/8/2026). AC Milan melakukan ...</t>
+        </is>
+      </c>
+      <c r="F1209" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1209" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/foto/5685061/siap-guncang-gbk-besok-intip-aksi-memukau-skuad-ac-milan-di-senayan-sebelum-jamu-chelsea</t>
+        </is>
+      </c>
+      <c r="H1209" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Latihan-AC-Milan-jelang-melawan-Chelsea-070826-fzn-4.jpg</t>
+        </is>
+      </c>
+      <c r="I1209" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1210" t="inlineStr">
+        <is>
+          <t>Ekonom dorong pemisahan fungsi pengaturan BEI dalam demutualisasi</t>
+        </is>
+      </c>
+      <c r="C1210" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:07:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1210" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1210" t="inlineStr">
+        <is>
+          <t>Kepala Ekonom PermataBank Josua Pardede mendorong pemisahan fungsi pengaturan Bursa Efek Indonesia (BEI) dalam proses ...</t>
+        </is>
+      </c>
+      <c r="F1210" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1210" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685057/ekonom-dorong-pemisahan-fungsi-pengaturan-bei-dalam-demutualisasi</t>
+        </is>
+      </c>
+      <c r="H1210" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IHSG-ditutup-menguat-65-94-poin-070826-Fah-1.jpg</t>
+        </is>
+      </c>
+      <c r="I1210" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1211" t="inlineStr">
+        <is>
+          <t>LPSK luncurkan dana bantuan untuk penuhi restitusi korban TPKS</t>
+        </is>
+      </c>
+      <c r="C1211" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:07:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1211" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1211" t="inlineStr">
+        <is>
+          <t>Lembaga Pelindungan Saksi dan Korban (LPSK) meluncurkan Dana Bantuan Korban (DBK) untuk membantu memenuhi restitusi ...</t>
+        </is>
+      </c>
+      <c r="F1211" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1211" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685056/lpsk-luncurkan-dana-bantuan-untuk-penuhi-restitusi-korban-tpks</t>
+        </is>
+      </c>
+      <c r="H1211" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001224363.jpg</t>
+        </is>
+      </c>
+      <c r="I1211" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1212" t="inlineStr">
+        <is>
+          <t>Dedi Mulyadi sebut utang hajatan picu TKI ilegal dan TPPO di Jabar</t>
+        </is>
+      </c>
+      <c r="C1212" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:06:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1212" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1212" t="inlineStr">
+        <is>
+          <t>Gubernur Jawa Barat Dedi Mulyadi menyebut tradisi berutang untuk biaya hajatan dan pernikahan menjadi salah satu faktor ...</t>
+        </is>
+      </c>
+      <c r="F1212" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1212" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685055/dedi-mulyadi-sebut-utang-hajatan-picu-tki-ilegal-dan-tppo-di-jabar</t>
+        </is>
+      </c>
+      <c r="H1212" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000036265.jpg</t>
+        </is>
+      </c>
+      <c r="I1212" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1213" t="inlineStr">
+        <is>
+          <t>BGN sisir 13 ribu SPPG, prioritaskan operasional di 3T-rawan stunting</t>
+        </is>
+      </c>
+      <c r="C1213" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:06:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1213" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1213" t="inlineStr">
+        <is>
+          <t>Badan Gizi Nasional (BGN) menyisir pembangunan 13 ribu Satuan Pelayanan Pemenuhan Gizi (SPPG) dan memprioritaskan ...</t>
+        </is>
+      </c>
+      <c r="F1213" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1213" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685051/bgn-sisir-13-ribu-sppg-prioritaskan-operasional-di-3t-rawan-stunting</t>
+        </is>
+      </c>
+      <c r="H1213" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/BGN-berhentikan-66-kepala-dapur-MBG-070826-rn-01.jpg</t>
+        </is>
+      </c>
+      <c r="I1213" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1214" t="inlineStr">
+        <is>
+          <t>BGN pecat 66 kepala dapur MBG karena tindakan indisipliner</t>
+        </is>
+      </c>
+      <c r="C1214" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:03:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1214" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1214" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono mengatakan hingga Jumat (7/8), pihaknya telah memberhentikan 66 ...</t>
+        </is>
+      </c>
+      <c r="F1214" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1214" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5684984/bgn-pecat-66-kepala-dapur-mbg-karena-tindakan-indisipliner</t>
+        </is>
+      </c>
+      <c r="H1214" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BGN-PECAT-66-KEPALA-DAPUR-MBG-KARENA-TINDAKAN-INDISIPLINER.jpg</t>
+        </is>
+      </c>
+      <c r="I1214" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1215" t="inlineStr">
+        <is>
+          <t>Bappenas: Pembangunan Papua jadi ikhtiar untuk kemajuan kawasan</t>
+        </is>
+      </c>
+      <c r="C1215" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:01:13 +0700</t>
+        </is>
+      </c>
+      <c r="D1215" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1215" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Perencanaan Pembangunan Nasional (PPN)/Wakil Kepala Badan Perencanaan Pembangunan Nasional (Bappenas) ...</t>
+        </is>
+      </c>
+      <c r="F1215" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1215" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685043/bappenas-pembangunan-papua-jadi-ikhtiar-untuk-kemajuan-kawasan</t>
+        </is>
+      </c>
+      <c r="H1215" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Bappenas-Papua.jpg</t>
+        </is>
+      </c>
+      <c r="I1215" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1216" t="inlineStr">
+        <is>
+          <t>Tumpukan sampah Kedaung Kaliangke akibat transisi sistem pengelolaan</t>
+        </is>
+      </c>
+      <c r="C1216" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:59:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1216" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1216" t="inlineStr">
+        <is>
+          <t>Kepala Suku Dinas Lingkungan Hidup (Kasudin LH) Jakarta Barat, Aldi Jansen menyampaikan bahwa tumpukan sampah di RW 03 ...</t>
+        </is>
+      </c>
+      <c r="F1216" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1216" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685041/tumpukan-sampah-kedaung-kaliangke-akibat-transisi-sistem-pengelolaan</t>
+        </is>
+      </c>
+      <c r="H1216" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG-20260807-WA0013_3.jpg</t>
+        </is>
+      </c>
+      <c r="I1216" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1217" t="inlineStr">
+        <is>
+          <t>Prabowo terima laporan pendapatan Danantara naik 400 persen</t>
+        </is>
+      </c>
+      <c r="C1217" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:59:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1217" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1217" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto mengungkapkan menerima laporan bahwa pendapatan Danantara meningkat sekitar 400 persen dalam ...</t>
+        </is>
+      </c>
+      <c r="F1217" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1217" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685039/prabowo-terima-laporan-pendapatan-danantara-naik-400-persen</t>
+        </is>
+      </c>
+      <c r="H1217" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/19308ac9-e06c-4451-9835-757ab1cfb7d3.jpeg</t>
+        </is>
+      </c>
+      <c r="I1217" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1218" t="inlineStr">
+        <is>
+          <t>OpenAI dikabarkan pasarkan pengeras suara mulai dari Rp5,3 jutaan</t>
+        </is>
+      </c>
+      <c r="C1218" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:58:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1218" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1218" t="inlineStr">
+        <is>
+          <t>OpenAI dikabarkan memasarkan produk teknologi berupa perangkat keras speaker atau pengeras suara pintar mulai ...</t>
+        </is>
+      </c>
+      <c r="F1218" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1218" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685036/openai-dikabarkan-pasarkan-pengeras-suara-mulai-dari-rp53-jutaan</t>
+        </is>
+      </c>
+      <c r="H1218" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2024/10/09/Clipboard_10-09-2024_04.jpg</t>
+        </is>
+      </c>
+      <c r="I1218" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1219" t="inlineStr">
+        <is>
+          <t>KPK geledah rumah Sekretaris DPRD Kota Bengkulu</t>
+        </is>
+      </c>
+      <c r="C1219" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:57:53 +0700</t>
+        </is>
+      </c>
+      <c r="D1219" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1219" t="inlineStr">
+        <is>
+          <t>Penyidik Komisi Pemberantasan Korupsi (KPK) menggeledah rumah Sekretaris DPRD Kota Bengkulu Syofyan Tosoni di Kelurahan ...</t>
+        </is>
+      </c>
+      <c r="F1219" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1219" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685032/kpk-geledah-rumah-sekretaris-dprd-kota-bengkulu</t>
+        </is>
+      </c>
+      <c r="H1219" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_20260807_210151.jpg</t>
+        </is>
+      </c>
+      <c r="I1219" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1220" t="inlineStr">
+        <is>
+          <t>Sultra perkuat akses ekspor UMKM melalui program GETRA</t>
+        </is>
+      </c>
+      <c r="C1220" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:57:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1220" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1220" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah Provinsi Sulawesi Tenggara bersama Bank Indonesia memperkuat akses ekspor bagi pelaku usaha mikro, ...</t>
+        </is>
+      </c>
+      <c r="F1220" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1220" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5685000/sultra-perkuat-akses-ekspor-umkm-melalui-program-getra</t>
+        </is>
+      </c>
+      <c r="H1220" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SANS_SULTRA-PERKUAT-AKSES-EKSPOR-UMKM-MELALUI-PROGRAM-GATRA_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1220" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1221" t="inlineStr">
+        <is>
+          <t>Wagub Papua: Feskop 2026 lahirkan petani muda kopi</t>
+        </is>
+      </c>
+      <c r="C1221" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:56:13 +0700</t>
+        </is>
+      </c>
+      <c r="D1221" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1221" t="inlineStr">
+        <is>
+          <t>Wakil Gubernur Papua Aryoko Rumaropen mengatakan penyelenggaraan Festival Kopi Papua (Feskop) 2026 mampu melahirkan ...</t>
+        </is>
+      </c>
+      <c r="F1221" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1221" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685031/wagub-papua-feskop-2026-lahirkan-petani-muda-kopi</t>
+        </is>
+      </c>
+      <c r="H1221" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1002075495.jpg</t>
+        </is>
+      </c>
+      <c r="I1221" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1222" t="inlineStr">
+        <is>
+          <t>Kapolri siap jembatani dialog buruh-DPR soal RUU Ketenagakerjaan</t>
+        </is>
+      </c>
+      <c r="C1222" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:55:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1222" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1222" t="inlineStr">
+        <is>
+          <t>Kapolri Jenderal Pol. Listyo Sigit Prabowo menyatakan pihaknya siap menjembatani kalangan buruh dengan DPR RI dalam ...</t>
+        </is>
+      </c>
+      <c r="F1222" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1222" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685025/kapolri-siap-jembatani-dialog-buruh-dpr-soal-ruu-ketenagakerjaan</t>
+        </is>
+      </c>
+      <c r="H1222" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000087467.jpg</t>
+        </is>
+      </c>
+      <c r="I1222" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1223" t="inlineStr">
+        <is>
+          <t>Ekonom: Penundaan pajak marketplace beri ruang UMKM jaga arus kas</t>
+        </is>
+      </c>
+      <c r="C1223" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:53:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1223" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1223" t="inlineStr">
+        <is>
+          <t>Ekonom Center of Reform on Economics (CORE) Yusuf Rendy Manilet menilai ditundanya pungutan Pajak Penghasilan (PPh) ...</t>
+        </is>
+      </c>
+      <c r="F1223" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1223" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685021/ekonom-penundaan-pajak-marketplace-beri-ruang-umkm-jaga-arus-kas</t>
+        </is>
+      </c>
+      <c r="H1223" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2020/11/13/InShot_20200910_104834146.jpg</t>
+        </is>
+      </c>
+      <c r="I1223" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1224" t="inlineStr">
+        <is>
+          <t>RANS Simba Bogor dan Juan Laurent sepakat akhiri kerja sama</t>
+        </is>
+      </c>
+      <c r="C1224" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:47:48 +0700</t>
+        </is>
+      </c>
+      <c r="D1224" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1224" t="inlineStr">
+        <is>
+          <t>RANS Simba Bogor mengumumkan telah mengakhiri kerja sama dengan pebasket Juan Laurent Kokodiputra berdasarkan ...</t>
+        </is>
+      </c>
+      <c r="F1224" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1224" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685015/rans-simba-bogor-dan-juan-laurent-sepakat-akhiri-kerja-sama</t>
+        </is>
+      </c>
+      <c r="H1224" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/01/11/Tangerang-Hawks-dikalahkan-Satria-Muda-Pertamina-Bandung-11012026-gp-18.jpg</t>
+        </is>
+      </c>
+      <c r="I1224" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1225" t="inlineStr">
+        <is>
+          <t>Penguatan pendidikan melalui pembaruan buku ajar nasional</t>
+        </is>
+      </c>
+      <c r="C1225" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:45:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1225" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1225" t="inlineStr">
+        <is>
+          <t>ANTARA - Pemerintah terus mematangkan pembaruan buku ajar nasional sebagai bagian dari upaya memperkuat kualitas ...</t>
+        </is>
+      </c>
+      <c r="F1225" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1225" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5684957/penguatan-pendidikan-melalui-pembaruan-buku-ajar-nasional</t>
+        </is>
+      </c>
+      <c r="H1225" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PENGUATAN-PENDIDIKAN-MELALUI-PEMBARUAN-BUKU-AJAR-NASIONAL.jpg</t>
+        </is>
+      </c>
+      <c r="I1225" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1226" t="inlineStr">
+        <is>
+          <t>KY umumkan 14 calon lolos seleksi hakim agung dan ad hoc</t>
+        </is>
+      </c>
+      <c r="C1226" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:42:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1226" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1226" t="inlineStr">
+        <is>
+          <t>Komisi Yudisial (KY) mengumumkan 14 calon hakim agung dan hakim ad hoc yang dinyatakan lolos seleksi calon hakim agung, ...</t>
+        </is>
+      </c>
+      <c r="F1226" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1226" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685013/ky-umumkan-14-calon-lolos-seleksi-hakim-agung-dan-ad-hoc</t>
+        </is>
+      </c>
+      <c r="H1226" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1001849541.jpg</t>
+        </is>
+      </c>
+      <c r="I1226" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1227" t="inlineStr">
+        <is>
+          <t>Polsek Tambora kembalikan enam motor curian kepada pemilik</t>
+        </is>
+      </c>
+      <c r="C1227" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:40:34 +0700</t>
+        </is>
+      </c>
+      <c r="D1227" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1227" t="inlineStr">
+        <is>
+          <t>Kepolisian mengembalikan enam unit sepeda motor hasil curian kepada pemilknya di Polsek Tambora, Jakarta Barat, ...</t>
+        </is>
+      </c>
+      <c r="F1227" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1227" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685005/polsek-tambora-kembalikan-enam-motor-curian-kepada-pemilik</t>
+        </is>
+      </c>
+      <c r="H1227" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG-20260807-WA0040.jpg</t>
+        </is>
+      </c>
+      <c r="I1227" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1228" t="inlineStr">
+        <is>
+          <t>Bappenas: Kopi dan kakao sumber penghidupan jutaan keluarga Indonesia</t>
+        </is>
+      </c>
+      <c r="C1228" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:40:33 +0700</t>
+        </is>
+      </c>
+      <c r="D1228" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1228" t="inlineStr">
+        <is>
+          <t>Deputi Bidang Pangan, Sumber Daya Alam, dan Lingkungan Hidup Kementerian Perencanaan Pembangunan Nasional/Badan ...</t>
+        </is>
+      </c>
+      <c r="F1228" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1228" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685001/bappenas-kopi-dan-kakao-sumber-penghidupan-jutaan-keluarga-indonesia</t>
+        </is>
+      </c>
+      <c r="H1228" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Teguh-Pettani.jpg</t>
+        </is>
+      </c>
+      <c r="I1228" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1229" t="inlineStr">
+        <is>
+          <t>BGN buka PO box pengaduan MBG perkuat transparansi dan pengawasan</t>
+        </is>
+      </c>
+      <c r="C1229" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:36:45 +0700</t>
+        </is>
+      </c>
+      <c r="D1229" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1229" t="inlineStr">
+        <is>
+          <t>Badan Gizi Nasional (BGN) membuka jalur pengaduan melalui mekanisme PO box untuk memperkuat transparansi dan sistem ...</t>
+        </is>
+      </c>
+      <c r="F1229" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1229" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684992/bgn-buka-po-box-pengaduan-mbg-perkuat-transparansi-dan-pengawasan</t>
+        </is>
+      </c>
+      <c r="H1229" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/06/IMG-20260806-WA0015_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1229" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1230" t="inlineStr">
+        <is>
+          <t>Akun X TMC Polda Metro Jaya diretas pihak tak dikenal</t>
+        </is>
+      </c>
+      <c r="C1230" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:35:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1230" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1230" t="inlineStr">
+        <is>
+          <t>Akun X TMC Polda Metro Jaya diretas pihak tak dikenal, sehingga mengganggu publikasi informasi lalu lintas di wilayah ...</t>
+        </is>
+      </c>
+      <c r="F1230" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1230" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684988/akun-x-tmc-polda-metro-jaya-diretas-pihak-tak-dikenal</t>
+        </is>
+      </c>
+      <c r="H1230" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/29/IMG_20260630_094425.jpg</t>
+        </is>
+      </c>
+      <c r="I1230" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1231" t="inlineStr">
+        <is>
+          <t>Kekurangan staf picu penundaan dan pembatalan penerbangan di Sydney</t>
+        </is>
+      </c>
+      <c r="C1231" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:35:29 +0700</t>
+        </is>
+      </c>
+      <c r="D1231" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1231" t="inlineStr">
+        <is>
+          <t>Kekurangan staf layanan penerbangan dilaporkan menyebabkan penundaan penerbangan secara luas dan sejumlah pembatalan ...</t>
+        </is>
+      </c>
+      <c r="F1231" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1231" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684985/kekurangan-staf-picu-penundaan-dan-pembatalan-penerbangan-di-sydney</t>
+        </is>
+      </c>
+      <c r="H1231" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/CjkinzN000023_20260807_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I1231" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1232" t="inlineStr">
+        <is>
+          <t>Prabowo: "Kita bekerja beri harapan rakyat yang paling tak berdaya"</t>
+        </is>
+      </c>
+      <c r="C1232" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:34:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1232" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1232" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto saat memberikan sambutan dalam acara peluncuran 10 buku karya Menteri ESDM Bahlil Lahadalia ...</t>
+        </is>
+      </c>
+      <c r="F1232" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1232" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684980/prabowo-kita-bekerja-beri-harapan-rakyat-yang-paling-tak-berdaya</t>
+        </is>
+      </c>
+      <c r="H1232" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Peluncuran-10-buku-karya-nyata-untuk-negeri-Bahlil-Lahadalia-070826-Ada-4.jpg</t>
+        </is>
+      </c>
+      <c r="I1232" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1233" t="inlineStr">
+        <is>
+          <t>BGN tetapkan pembagian jajaran pejabat di daerah untuk awasi MBG</t>
+        </is>
+      </c>
+      <c r="C1233" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:32:32 +0700</t>
+        </is>
+      </c>
+      <c r="D1233" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1233" t="inlineStr">
+        <is>
+          <t>Badan Gizi Nasional (BGN) menetapkan pembagian wilayah tanggung jawab bagi jajaran pejabat eselon I dan II untuk ...</t>
+        </is>
+      </c>
+      <c r="F1233" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1233" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684979/bgn-tetapkan-pembagian-jajaran-pejabat-di-daerah-untuk-awasi-mbg</t>
+        </is>
+      </c>
+      <c r="H1233" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/BGN-berhentikan-66-kepala-dapur-MBG-070826-rn-01.jpg</t>
+        </is>
+      </c>
+      <c r="I1233" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1234" t="inlineStr">
+        <is>
+          <t>Grup musik D'MASIV agendakan Hong Kong dalam tur Asia Home Run 2026</t>
+        </is>
+      </c>
+      <c r="C1234" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:31:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1234" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1234" t="inlineStr">
+        <is>
+          <t>Grup band D'MASIV mengagendakan lawatan ke Hong Kong dalam tur Asia pada 2026 bertajuk "D'MASIV Asia Home ...</t>
+        </is>
+      </c>
+      <c r="F1234" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1234" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684976/grup-musik-dmasiv-agendakan-hong-kong-dalam-tur-asia-home-run-2026</t>
+        </is>
+      </c>
+      <c r="H1234" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG-20260807-WA0013-3.jpg</t>
+        </is>
+      </c>
+      <c r="I1234" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1235" t="inlineStr">
+        <is>
+          <t>Presiden Meksiko umumkan rencana keamanan untuk ekspor alpukat ke AS</t>
+        </is>
+      </c>
+      <c r="C1235" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:31:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1235" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1235" t="inlineStr">
+        <is>
+          <t>Presiden Meksiko Claudia Sheinbaum pada Kamis (6/8) mengatakan pemerintahannya sedang menyusun rencana aksi untuk ...</t>
+        </is>
+      </c>
+      <c r="F1235" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1235" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684973/presiden-meksiko-umumkan-rencana-keamanan-untuk-ekspor-alpukat-ke-as</t>
+        </is>
+      </c>
+      <c r="H1235" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/CjkinzN000025_20260807_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I1235" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1236" t="inlineStr">
+        <is>
+          <t>Wizards dan Davis tunda negosiasi kontrak hingga awal musim reguler</t>
+        </is>
+      </c>
+      <c r="C1236" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:31:11 +0700</t>
+        </is>
+      </c>
+      <c r="D1236" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1236" t="inlineStr">
+        <is>
+          <t>Washington Wizards dan Anthony Davis bersepakat untuk menunda pembahasan perpanjangan kontrak hingga awal musim reguler ...</t>
+        </is>
+      </c>
+      <c r="F1236" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1236" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684972/wizards-dan-davis-tunda-negosiasi-kontrak-hingga-awal-musim-reguler</t>
+        </is>
+      </c>
+      <c r="H1236" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2023/04/20/2023-04-20T000958Z_741082554_MT1USATODAY20498153_RTRMADP_3_NBA-PLAYOFFS-LOS-ANGELES-LAKERS-AT-MEMPHIS-GRIZZLIES.jpg</t>
+        </is>
+      </c>
+      <c r="I1236" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1237" t="inlineStr">
+        <is>
+          <t>Polda Jabar ungkap 352 kasus kejahatan jalanan dan siapkan pencegahan</t>
+        </is>
+      </c>
+      <c r="C1237" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:30:28 +0700</t>
+        </is>
+      </c>
+      <c r="D1237" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1237" t="inlineStr">
+        <is>
+          <t>ANTARA - Polda Jawa Barat mengungkap 352 kasus kejahatan jalanan dengan 413 pelaku sepanjang Juni hingga Agustus 2026. ...</t>
+        </is>
+      </c>
+      <c r="F1237" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1237" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5684943/polda-jabar-ungkap-352-kasus-kejahatan-jalanan-dan-siapkan-pencegahan</t>
+        </is>
+      </c>
+      <c r="H1237" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/POLDA-JABAR-UNGKAP-352-KASUS-KEJAHATAN-JALANAN-DAN-SIAPKAN-PENCEGAHAN.jpg</t>
+        </is>
+      </c>
+      <c r="I1237" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1238" t="inlineStr">
+        <is>
+          <t>Bursa saham Singapura catat rekor pendapatan dan laba bersih pada 2026</t>
+        </is>
+      </c>
+      <c r="C1238" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:27:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1238" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1238" t="inlineStr">
+        <is>
+          <t>Bursa Saham Singapura (Singapore Exchange/SGX Group) mencatatkan rekor pendapatan dan laba bersih untuk tahun keuangan ...</t>
+        </is>
+      </c>
+      <c r="F1238" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1238" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684969/bursa-saham-singapura-catat-rekor-pendapatan-dan-laba-bersih-pada-2026</t>
+        </is>
+      </c>
+      <c r="H1238" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/CjkinzN000027_20260807_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I1238" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1239" t="inlineStr">
+        <is>
+          <t>Chelsea jadikan laga pramusim di Jakarta bangun mentalitas pemenang</t>
+        </is>
+      </c>
+      <c r="C1239" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:27:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1239" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1239" t="inlineStr">
+        <is>
+          <t>Manajer Chelsea Xabi Alonso menjadikan laga tur pramusim di Jakarta menjadi bagian dari momentum membangun mentalitas ...</t>
+        </is>
+      </c>
+      <c r="F1239" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1239" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684968/chelsea-jadikan-laga-pramusim-di-jakarta-bangun-mentalitas-pemenang</t>
+        </is>
+      </c>
+      <c r="H1239" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_20260807_211305.jpg</t>
+        </is>
+      </c>
+      <c r="I1239" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1240" t="inlineStr">
+        <is>
+          <t>Menkum ungkap alasan pemerintah perketat naturalisasi WNA</t>
+        </is>
+      </c>
+      <c r="C1240" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:27:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1240" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1240" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Hukum Supratman Andi Agtas di Jakarta, Jumat (7/8), mengatakan pemerintah telah memperketat ...</t>
+        </is>
+      </c>
+      <c r="F1240" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1240" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5684923/menkum-ungkap-alasan-pemerintah-perketat-naturalisasi-wna</t>
+        </is>
+      </c>
+      <c r="H1240" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/MENKUM-UNGKAP-ALASAN-PEMERINTAH-PERKETAT-NATURALISASI-WNA.jpg</t>
+        </is>
+      </c>
+      <c r="I1240" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1241" t="inlineStr">
+        <is>
+          <t>China rilis peta bulan yang disempurnakan</t>
+        </is>
+      </c>
+      <c r="C1241" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:25:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1241" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1241" t="inlineStr">
+        <is>
+          <t>Sebuah tim peneliti China telah merampungkan peta geologis terbaru dari seluruh permukaan Bulan dengan skala ...</t>
+        </is>
+      </c>
+      <c r="F1241" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1241" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5684965/china-rilis-peta-bulan-yang-disempurnakan</t>
+        </is>
+      </c>
+      <c r="H1241" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/CjkinzN000021_20260807_CBMFN0A001.jpg</t>
+        </is>
+      </c>
+      <c r="I1241" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1242" t="inlineStr">
+        <is>
+          <t>Polri Pastikan Periksa Personel Polresta Banda Aceh Transparan</t>
+        </is>
+      </c>
+      <c r="C1242" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:08:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1242" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1242" t="inlineStr">
+        <is>
+          <t>Polri memastikan pemeriksaan Kapolresta Banda Aceh dan Kasat Narkoba dilakukan secara profesional dan transparan.</t>
+        </is>
+      </c>
+      <c r="F1242" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1242" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609267/polri-pastikan-periksa-personel-polresta-banda-aceh-transparan</t>
+        </is>
+      </c>
+      <c r="H1242" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/02/25/kadiv-humas-polri-johnny-eddizon-isir-1771994950407_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1242" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1243" t="inlineStr">
+        <is>
+          <t>Gaduh di Jakut Saat Ada Pencuri Kabel Tersengat Listik hingga Melepuh</t>
+        </is>
+      </c>
+      <c r="C1243" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:01:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1243" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E1243" t="inlineStr">
+        <is>
+          <t>Suasana di Sunter Agung, Jakarta Utara (Jakut), mendadak gaduh. Seorang pria ditarik paksa dari gardu PLN karena diduga hendak mencuri kabel listrik.</t>
+        </is>
+      </c>
+      <c r="F1243" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1243" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609235/gaduh-di-jakut-saat-ada-pencuri-kabel-tersengat-listik-hingga-melepuh</t>
+        </is>
+      </c>
+      <c r="H1243" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/maling-kabel-listrik-di-gardu-pln-sunter-agung-jakut-kesetrum-hingga-badan-melepuh-1786074935209_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1243" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1244" t="inlineStr">
+        <is>
+          <t>Kapolres Malang Gandeng Driver Ojol Jaga Keamanan Warga</t>
+        </is>
+      </c>
+      <c r="C1244" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:52:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1244" t="inlineStr">
+        <is>
+          <t>Firda Cynthia Anggrainy</t>
+        </is>
+      </c>
+      <c r="E1244" t="inlineStr">
+        <is>
+          <t>Kapolres Malang, AKBP Rulian Syauri, ajak pengemudi ojol jaga kamtibmas. Pertemuan ini bertujuan mempererat komunikasi dan sinergi dengan komunitas ojol.</t>
+        </is>
+      </c>
+      <c r="F1244" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1244" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609228/kapolres-malang-gandeng-driver-ojol-jaga-keamanan-warga</t>
+        </is>
+      </c>
+      <c r="H1244" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kapolres-malang-akbp-rulian-syauri-berdialog-dengan-perhimpunan-driver-ojek-indonesia-pdoi-malang-raya-1786114289613_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1244" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1245" t="inlineStr">
+        <is>
+          <t>Guyon Bahlil ke Cak Imin: Ketum Lama Belum Tentu Punya Buku Diteken Presiden</t>
+        </is>
+      </c>
+      <c r="C1245" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:51:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1245" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E1245" t="inlineStr">
+        <is>
+          <t>Ketum Golkar Bahlil Lahadalia bercanda tentang bukunya yang ditandatangani Prabowo, menyindir Cak Imin. Candaan ini mengundang tawa audiens di Jakarta.</t>
+        </is>
+      </c>
+      <c r="F1245" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1245" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609227/guyon-bahlil-ke-cak-imin-ketum-lama-belum-tentu-punya-buku-diteken-presiden</t>
+        </is>
+      </c>
+      <c r="H1245" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/bahlil-lahadalia-1786111824719_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1245" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1246" t="inlineStr">
+        <is>
+          <t>Pansus DPRD DKI Bakal Sidak 200 Vendor Pengelola Sampah, Cek Dibuang ke Mana</t>
+        </is>
+      </c>
+      <c r="C1246" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:36:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1246" t="inlineStr">
+        <is>
+          <t>Brigitta Belia Permata Sari</t>
+        </is>
+      </c>
+      <c r="E1246" t="inlineStr">
+        <is>
+          <t>DPRD DKI Jakarta akan sidak 200 vendor pengelola sampah untuk memastikan kepatuhan dalam pengolahan dan pembuangan sampah sesuai dengan aturan.</t>
+        </is>
+      </c>
+      <c r="F1246" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1246" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609216/pansus-dprd-dki-bakal-sidak-200-vendor-pengelola-sampah-cek-dibuang-ke-mana</t>
+        </is>
+      </c>
+      <c r="H1246" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/judistira-1786113237333_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1246" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1247" t="inlineStr">
+        <is>
+          <t>Terduga Pembunuh Bos Konter HP Ambarawa Ditangkap, Ternyata Teman Korban</t>
+        </is>
+      </c>
+      <c r="C1247" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:24:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1247" t="inlineStr">
+        <is>
+          <t>Ardian Dwi Kurnia</t>
+        </is>
+      </c>
+      <c r="E1247" t="inlineStr">
+        <is>
+          <t>Polres Semarang dan Polda Jateng menangkap terduga pelaku pencurian dengan kekerasan yang mengakibatkan kematian pemilik konter ponsel Royal Phone Ambarawa.</t>
+        </is>
+      </c>
+      <c r="F1247" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1247" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609199/terduga-pembunuh-bos-konter-hp-ambarawa-ditangkap-ternyata-teman-korban</t>
+        </is>
+      </c>
+      <c r="H1247" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/06/konter-hp-royal-phone-di-ambarawa-tkp-pencurian-dengan-kekerasan-kamis-682026-1786034565792_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1247" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1248" t="inlineStr">
+        <is>
+          <t>7 Jam Diperiksa Kejagung, Febrie Adriansyah Dibawa Lagi ke Rutan KPK</t>
+        </is>
+      </c>
+      <c r="C1248" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:22:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1248" t="inlineStr">
+        <is>
+          <t>Mulia Budi, Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1248" t="inlineStr">
+        <is>
+          <t>Febrie Adriansyah selesai diperiksa sebagai tersangka di kasus tindak pidana pencucian uang (TPPU). Usai 7 jam diperiksa, Febrie dikembalikan ke Rutan KPK.</t>
+        </is>
+      </c>
+      <c r="F1248" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1248" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609198/7-jam-diperiksa-kejagung-febrie-adriansyah-dibawa-lagi-ke-rutan-kpk</t>
+        </is>
+      </c>
+      <c r="H1248" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/febrie-adriansyah-selesai-diperiksa-kejagung-langsung-dibawa-lagi-ke-rutan-kpk-muliadetikcom-1786112429835_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1248" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1249" t="inlineStr">
+        <is>
+          <t>Bahlil Puji Luhut Mentornya: Ada Saat Dia Menekan, Ada Saat Dia Sayang-sayang Saya</t>
+        </is>
+      </c>
+      <c r="C1249" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:12:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1249" t="inlineStr">
+        <is>
+          <t>Eva Safitri</t>
+        </is>
+      </c>
+      <c r="E1249" t="inlineStr">
+        <is>
+          <t>Ketua Umum Golkar Bahlil Lahadalia menyebut Luhut sebagai mentornya. Ia mengaku dimentori Luhut tentang negosiasi investasi saat menjabat Menteri Investasi.</t>
+        </is>
+      </c>
+      <c r="F1249" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1249" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609192/bahlil-puji-luhut-mentornya-ada-saat-dia-menekan-ada-saat-dia-sayang-sayang-saya</t>
+        </is>
+      </c>
+      <c r="H1249" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/bahlil-lahadalia-1786111824719_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1249" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1250" t="inlineStr">
+        <is>
+          <t>Polisi Ungkap Kendala Pencarian Kaki Korban Mutilasi di Kali Licin Depok</t>
+        </is>
+      </c>
+      <c r="C1250" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:10:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1250" t="inlineStr">
+        <is>
+          <t>Wildan Noviansah</t>
+        </is>
+      </c>
+      <c r="E1250" t="inlineStr">
+        <is>
+          <t>Polisi masih mencari potongan kaki korban mutilasi K (51) di Kali Licin, Depok. Kendala pencarian akibat aliran sungai yang membawa potongan tersebut.</t>
+        </is>
+      </c>
+      <c r="F1250" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1250" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609186/polisi-ungkap-kendala-pencarian-kaki-korban-mutilasi-di-kali-licin-depok</t>
+        </is>
+      </c>
+      <c r="H1250" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/polisi-lanjut-cari-potongan-kaki-korban-mutilasi-di-kali-licin-depok-devidetikcom-1786074971703_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1250" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1251" t="inlineStr">
+        <is>
+          <t>Herman Deru Dorong Penguatan Sinergi untuk Jaga Kelestarian Hutan Sumsel</t>
+        </is>
+      </c>
+      <c r="C1251" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:00:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1251" t="inlineStr">
+        <is>
+          <t>Hana Nushratu Uzma</t>
+        </is>
+      </c>
+      <c r="E1251" t="inlineStr">
+        <is>
+          <t>Gubernur Sumsel Herman Deru dorong sinergi masyarakat dan pemerintah untuk jaga kelestarian hutan. Pentingnya kearifan lokal dan penambahan Polhut juga disorot.</t>
+        </is>
+      </c>
+      <c r="F1251" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1251" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609166/herman-deru-dorong-penguatan-sinergi-untuk-jaga-kelestarian-hutan-sumsel</t>
+        </is>
+      </c>
+      <c r="H1251" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/pemprov-sumsel-1786111204596_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1251" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1252" t="inlineStr">
+        <is>
+          <t>Api Cemburu Bikin Remaja Sayat Leher Warga Depok Pakai Cutter</t>
+        </is>
+      </c>
+      <c r="C1252" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:00:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1252" t="inlineStr">
+        <is>
+          <t>Tim detikcom</t>
+        </is>
+      </c>
+      <c r="E1252" t="inlineStr">
+        <is>
+          <t>Remaja RAN (19) ditangkap setelah menyerang MAN (16) di Depok karena cemburu. Pelaku menyayat leher korban dengan cutter.</t>
+        </is>
+      </c>
+      <c r="F1252" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1252" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609165/api-cemburu-bikin-remaja-sayat-leher-warga-depok-pakai-cutter</t>
+        </is>
+      </c>
+      <c r="H1252" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/polisi-tangkap-pelaku-penyerangan-terhadap-warga-di-depok-dokistimewa-1786087228399_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1252" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1253" t="inlineStr">
+        <is>
+          <t>Aturan Logam Tanah Jarang Lagi Disusun, Bakal Diolah di Dalam Negeri</t>
+        </is>
+      </c>
+      <c r="C1253" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1253" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E1253" t="inlineStr">
+        <is>
+          <t>Menteri ESDM Bahlil Lahadalia mengatakan pemerintah sedang menyusun aturan teknis terkait larangan ekspor rare earth atau Logam Tanah Jarang (LTJ).</t>
+        </is>
+      </c>
+      <c r="F1253" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1253" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8609275/aturan-logam-tanah-jarang-lagi-disusun-bakal-diolah-di-dalam-negeri</t>
+        </is>
+      </c>
+      <c r="H1253" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2021/10/09/logam-tanah-jarang-jadi-harta-karun-yang-diincar-dunia-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1253" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1254" t="inlineStr">
+        <is>
+          <t>Jawaban Bahlil Usai Dapat Rapor Memuaskan dari Prabowo</t>
+        </is>
+      </c>
+      <c r="C1254" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:03:16 +0700</t>
+        </is>
+      </c>
+      <c r="D1254" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E1254" t="inlineStr">
+        <is>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia merespons penilaian Presiden Prabowo Subianto yang menyebut kinerjanya memuaskan.</t>
+        </is>
+      </c>
+      <c r="F1254" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1254" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8609236/jawaban-bahlil-usai-dapat-rapor-memuaskan-dari-prabowo</t>
+        </is>
+      </c>
+      <c r="H1254" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/bahlil-lahadalia-1785840108228_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1254" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1255" t="inlineStr">
+        <is>
+          <t>Pasar Murah Ringankan Beban Belanja Warga</t>
+        </is>
+      </c>
+      <c r="C1255" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:40:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1255" t="inlineStr">
+        <is>
+          <t>Agung Pambudhy</t>
+        </is>
+      </c>
+      <c r="E1255" t="inlineStr">
+        <is>
+          <t>Pemprov Jatim bersama Perum Bulog menggelar pasar murah di Sidoarjo untuk menjaga stabilitas harga pangan, mengendalikan inflasi, dan membantu daya beli warga.</t>
+        </is>
+      </c>
+      <c r="F1255" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1255" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8609097/pasar-murah-ringankan-beban-belanja-warga</t>
+        </is>
+      </c>
+      <c r="H1255" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/pasar-murah-di-sidoarjo-1786108342125_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1255" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1256" t="inlineStr">
+        <is>
+          <t>BGN Sisir Sekolah Swasta Elite Tak Butuh MBG</t>
+        </is>
+      </c>
+      <c r="C1256" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:25:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1256" t="inlineStr">
+        <is>
+          <t>Retno Ayuningrum</t>
+        </is>
+      </c>
+      <c r="E1256" t="inlineStr">
+        <is>
+          <t>Kepala Badan Gizi Nasional (BGN) Sudaryono menyampaikan sekolah swasta elit tidak membutuhkan program makan bergizi gratis (MBG).</t>
+        </is>
+      </c>
+      <c r="F1256" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1256" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8609200/bgn-sisir-sekolah-swasta-elite-tak-butuh-mbg</t>
+        </is>
+      </c>
+      <c r="H1256" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kepala-badan-gizi-nasional-bgn-sudaryono-1786101835426_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1256" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1257" t="inlineStr">
+        <is>
+          <t>Prabowo Pastikan Harga BBM Subsidi Tidak Naik</t>
+        </is>
+      </c>
+      <c r="C1257" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:07:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1257" t="inlineStr">
+        <is>
+          <t>Ilyas Fadilah</t>
+        </is>
+      </c>
+      <c r="E1257" t="inlineStr">
+        <is>
+          <t>Presiden Prabowo Subianto menyebut Indonesia berhasil menjaga harga Bahan Bakar Minyak (BBM) bersubsidi tidak naik</t>
+        </is>
+      </c>
+      <c r="F1257" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1257" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8609174/prabowo-pastikan-harga-bbm-subsidi-tidak-naik</t>
+        </is>
+      </c>
+      <c r="H1257" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/31/presiden-prabowo-subianto-saat-memberikan-taklimat-di-depan-para-pimpinan-kamar-dagang-dan-industri-indonesia-kadin-di-istana--1785493704749_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1257" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1258" t="inlineStr">
+        <is>
+          <t>Larangan Ekspor Tembaga &amp;amp; Bauksit Mentah Tetap Berlaku!</t>
+        </is>
+      </c>
+      <c r="C1258" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:45:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1258" t="inlineStr">
+        <is>
+          <t>Ignacio Geordi Oswaldo</t>
+        </is>
+      </c>
+      <c r="E1258" t="inlineStr">
+        <is>
+          <t>Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia buka suara soal ekspor mineral. Bahlil memastikan pemerintah melarang ekspor mineral mentah.</t>
+        </is>
+      </c>
+      <c r="F1258" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1258" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/energi/d-8609135/larangan-ekspor-tembaga-bauksit-mentah-tetap-berlaku</t>
+        </is>
+      </c>
+      <c r="H1258" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/04/bahlil-lahadalia-1785840108228_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1258" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1259" t="inlineStr">
+        <is>
+          <t>Dari Lereng Arjuno Menembus Pasar Ekspor</t>
+        </is>
+      </c>
+      <c r="C1259" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1259" t="inlineStr">
+        <is>
+          <t>Agung Pambudhy</t>
+        </is>
+      </c>
+      <c r="E1259" t="inlineStr">
+        <is>
+          <t>Industri kopi rumahan di Malang mengolah hasil panen 207 petani mitra menjadi produk bernilai tambah yang dipasarkan ke dalam negeri hingga ekspor.</t>
+        </is>
+      </c>
+      <c r="F1259" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1259" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/foto-bisnis/d-8609121/dari-lereng-arjuno-menembus-pasar-ekspor</t>
+        </is>
+      </c>
+      <c r="H1259" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/industri-pengolahan-dan-pusat-studi-kopi-nusantara-di-malang-1786109312747_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1259" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1260" t="inlineStr">
+        <is>
+          <t>Kebakaran Gedung di Jalan Abdul Muis Jakpus, 20 Unit Damkar Dikerahkan</t>
+        </is>
+      </c>
+      <c r="C1260" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:29:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1260" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1260" t="inlineStr">
+        <is>
+          <t>Kebakaran terjadi di bangunan bertingkat yang berada di Jalan Abdul Muis, Jakarta Pusat. 20 unit damkar, 100 personel dikerahkan.</t>
+        </is>
+      </c>
+      <c r="F1260" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1260" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807221850-20-1389979/kebakaran-gedung-di-jalan-abdul-muis-jakpus-20-unit-damkar-dikerahkan</t>
+        </is>
+      </c>
+      <c r="H1260" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/03/30/ilustrasi-ledakan-1_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1260" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1261" t="inlineStr">
+        <is>
+          <t>Gempa M5,0 di Jepara Jateng, Tak Berpotensi Tsunami</t>
+        </is>
+      </c>
+      <c r="C1261" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:11:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1261" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1261" t="inlineStr">
+        <is>
+          <t>Gempa bumi tektonik M5.0 mengguncang Jepara, Jawa Tengah, Jumat (7/8). Tidak berpotensi tsunami.</t>
+        </is>
+      </c>
+      <c r="F1261" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1261" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807220347-20-1389976/gempa-m50-di-jepara-jateng-tak-berpotensi-tsunami</t>
+        </is>
+      </c>
+      <c r="H1261" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2016/11/21/f26faae5-d7b3-4ba6-b508-e53f4ff585e4_169.jpg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1261" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1262" t="inlineStr">
+        <is>
+          <t>Kebakaran Bromo Meluas 176 Hektare, Heli Dikerahkan Water Bombing</t>
+        </is>
+      </c>
+      <c r="C1262" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:59:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1262" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1262" t="inlineStr">
+        <is>
+          <t>Kebakaran hutan di Bromo meluas hingga 176,20 hektare. Upaya pemadaman melibatkan helikopter dan tim gabungan. Belum ada laporan korban jiwa.</t>
+        </is>
+      </c>
+      <c r="F1262" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1262" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807201108-12-1389942/kebakaran-bromo-meluas-176-hektare-heli-dikerahkan-water-bombing</t>
+        </is>
+      </c>
+      <c r="H1262" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/kebakaran-bromo-meluas-jadi-176-hektare-1786108419489_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1262" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1263">
+      <c r="A1263" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1263" t="inlineStr">
+        <is>
+          <t>KBPBI Apresiasi Komitmen Kapolri Kawal Pembahasan RUU Ketenagakerjaan</t>
+        </is>
+      </c>
+      <c r="C1263" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:42:53 +0700</t>
+        </is>
+      </c>
+      <c r="D1263" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1263" t="inlineStr">
+        <is>
+          <t>Kapolri Listyo menilai, dialog diperlukan dalam berbagai persoalan ketenagakerjaan, sehingga dapat menghasilkan regulasi yang berimbang.</t>
+        </is>
+      </c>
+      <c r="F1263" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1263" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807210753-25-1389970/kbpbi-apresiasi-komitmen-kapolri-kawal-pembahasan-ruu-ketenagakerjaan</t>
+        </is>
+      </c>
+      <c r="H1263" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/polri-1786111823262_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1263" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1264">
+      <c r="A1264" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1264" t="inlineStr">
+        <is>
+          <t>Pemprov DKI Sanksi Semua Pelaku Pembuangan Sampah Ilegal di Dukuh</t>
+        </is>
+      </c>
+      <c r="C1264" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:21:44 +0700</t>
+        </is>
+      </c>
+      <c r="D1264" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1264" t="inlineStr">
+        <is>
+          <t>Pemprov DKI menindak tegas pelaku pembuangan sampah ilegal di Kramat Jati. Tiga pelaku dijatuhi sanksi administratif untuk mencegah pencemaran lingkungan.</t>
+        </is>
+      </c>
+      <c r="F1264" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1264" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807205344-25-1389958/pemprov-dki-sanksi-semua-pelaku-pembuangan-sampah-ilegal-di-dukuh</t>
+        </is>
+      </c>
+      <c r="H1264" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/pemprov-dki-1786110503521_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1264" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1265">
+      <c r="A1265" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1265" t="inlineStr">
+        <is>
+          <t>Pihak Sekolah Minta Polisi Bongkar Bunker Usai Temuan Ratusan Senjata</t>
+        </is>
+      </c>
+      <c r="C1265" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:20:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1265" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1265" t="inlineStr">
+        <is>
+          <t>Sekolah swasta di Jakarta Selatan minta polisi bongkar bunker setelah ratusan senjata ditemukan. Kuasa hukum khawatir ada senjata lain di dalamnya.</t>
+        </is>
+      </c>
+      <c r="F1265" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1265" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807125001-12-1389679/pihak-sekolah-minta-polisi-bongkar-bunker-usai-temuan-ratusan-senjata</t>
+        </is>
+      </c>
+      <c r="H1265" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/995-senjata-yang-ditemukan-di-ruang-mantan-ketua-yayasan-sekolah-jaksel-1786011308099_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1265" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1266" t="inlineStr">
+        <is>
+          <t>Dokter PPDS UGM yang Cibir Pasien BPJS Dinonaktifkan 3 Bulan</t>
+        </is>
+      </c>
+      <c r="C1266" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:37:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1266" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1266" t="inlineStr">
+        <is>
+          <t>FK-KMK UGM menonaktifkan Elda Putri Rahardini selama 3 bulan akibat komentar nirempati terhadap pasien BPJS. Investigasi pelanggaran etik sedang berlangsung.</t>
+        </is>
+      </c>
+      <c r="F1266" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1266" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807201756-12-1389945/dokter-ppds-ugm-yang-cibir-pasien-bpjs-dinonaktifkan-3-bulan</t>
+        </is>
+      </c>
+      <c r="H1266" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/05/15/universitas-gadjah-mada-1747298810323_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1266" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1267" t="inlineStr">
+        <is>
+          <t>Polisi Tangkap 15 Pria Terduga Pemerkosa Anak di Mamuju Sulbar</t>
+        </is>
+      </c>
+      <c r="C1267" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:10:40 +0700</t>
+        </is>
+      </c>
+      <c r="D1267" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1267" t="inlineStr">
+        <is>
+          <t>Polisi Mamuju tangkap 15 pria terkait kasus pemerkosaan anak 15 tahun yang hamil 3 bulan. Kasus terungkap setelah laporan keluarga.</t>
+        </is>
+      </c>
+      <c r="F1267" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1267" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807192400-12-1389915/polisi-tangkap-15-pria-terduga-pemerkosa-anak-di-mamuju-sulbar</t>
+        </is>
+      </c>
+      <c r="H1267" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2022/11/25/ilustrasi-penjara_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1267" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1268" t="inlineStr">
+        <is>
+          <t>Wamendagri Bima Arya Dorong Penghijauan Jadi Gerakan Berkelanjutan</t>
+        </is>
+      </c>
+      <c r="C1268" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:47:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1268" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1268" t="inlineStr">
+        <is>
+          <t>Wamendagri Bima Arya mendorong Pemda untuk menjadikan penghijauan sebagai gerakan berkelanjutan, menekankan kolaborasi dan perawatan untuk dampak nyata.</t>
+        </is>
+      </c>
+      <c r="F1268" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1268" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807193943-20-1389924/wamendagri-bima-arya-dorong-penghijauan-jadi-gerakan-berkelanjutan</t>
+        </is>
+      </c>
+      <c r="H1268" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/wakil-menteri-dalam-negeri-wamendagri-bima-arya-sugiarto-1786106207706_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1268" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1269" t="inlineStr">
+        <is>
+          <t>FOTO: Jalintim Palembang Jambi Lumpuh Dua Pekan</t>
+        </is>
+      </c>
+      <c r="C1269" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:45:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1269" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1269" t="inlineStr">
+        <is>
+          <t>Sejumlah kendaraan terjebak kemacetan di Jalan Lintas Timur Palembang-Jambi di Air Batu, Kabupaten Banyuasin, Sumatera Selatan, Jumat (7/8).</t>
+        </is>
+      </c>
+      <c r="F1269" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1269" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807185911-22-1389890/foto-jalintim-palembang-jambi-lumpuh-dua-pekan</t>
+        </is>
+      </c>
+      <c r="H1269" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/jalintim-palembang-jambi-lumpuh-dua-pekan-1786102821694_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1269" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1270" t="inlineStr">
+        <is>
+          <t>Cegah Politik Uang, Pemilihan Ketua Umum PBNU Diusulkan Lewat AHWA</t>
+        </is>
+      </c>
+      <c r="C1270" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:34:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1270" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1270" t="inlineStr">
+        <is>
+          <t>TribunNews.com menyajikan berita dan video terkini dari regional, nasional dan internasional dengan sudut pandang dan nilai-nilai lokal</t>
+        </is>
+      </c>
+      <c r="F1270" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1270" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/</t>
+        </is>
+      </c>
+      <c r="H1270" t="inlineStr">
+        <is>
+          <t>https://asset-2.tribunnews.com/tribunnews/foto/bank/images/logo-tribunnews1_20160901_101844.jpg</t>
+        </is>
+      </c>
+      <c r="I1270" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1271" t="inlineStr">
+        <is>
+          <t>Malapetaka Menghantam Amerika, Ratusan Sudah Jadi Korban</t>
+        </is>
+      </c>
+      <c r="C1271" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1271" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1271" t="inlineStr">
+        <is>
+          <t>Serangan siber terus menghantam AS, dengan peretas menargetkan lembaga keuangan dan perusahaan besar. Simak!</t>
+        </is>
+      </c>
+      <c r="F1271" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1271" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807132653-37-757416/malapetaka-menghantam-amerika-ratusan-sudah-jadi-korban</t>
+        </is>
+      </c>
+      <c r="H1271" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2022/05/23/bendera-amerika-serikat-1_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1271" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1272" t="inlineStr">
+        <is>
+          <t>Penemuan Baru Bantah Teori Evolusi Manusia yang Sudah Lama Dipercaya</t>
+        </is>
+      </c>
+      <c r="C1272" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1272" t="inlineStr">
+        <is>
+          <t>Novina Putri Bestari</t>
+        </is>
+      </c>
+      <c r="E1272" t="inlineStr">
+        <is>
+          <t>Penelitian terbaru membantah teori evolusi manusia yang bertahap. Temuan menunjukkan perubahan fisik manusia purba dipengaruhi oleh budaya dan teknologi.</t>
+        </is>
+      </c>
+      <c r="F1272" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1272" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807131529-37-757405/penemuan-baru-bantah-teori-evolusi-manusia-yang-sudah-lama-dipercaya</t>
+        </is>
+      </c>
+      <c r="H1272" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/02/27/ilustrasi-manusia-purba-1772188117029_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1272" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1273" t="inlineStr">
+        <is>
+          <t>Pembeli Switch Minta Uang Kembali Karena Nintendo Untung Gede, Ditolak</t>
+        </is>
+      </c>
+      <c r="C1273" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1273" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1273" t="inlineStr">
+        <is>
+          <t>Nintendo mencatat lonjakan laba 53,5 persen berkat pengembalian tarif impor dari AS.</t>
+        </is>
+      </c>
+      <c r="F1273" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1273" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807134011-37-757434/pembeli-switch-minta-uang-kembali-karena-nintendo-untung-gede-ditolak</t>
+        </is>
+      </c>
+      <c r="H1273" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/04/05/nintendo-switch-2-ap-photorichard-drew-1743838124363_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1273" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1274" t="inlineStr">
+        <is>
+          <t>Amerika Buka-Bukaan Alasan Sebenarnya China Harus Diblokir Total</t>
+        </is>
+      </c>
+      <c r="C1274" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1274" t="inlineStr">
+        <is>
+          <t>Intan Rakhmayanti</t>
+        </is>
+      </c>
+      <c r="E1274" t="inlineStr">
+        <is>
+          <t>AS membatasi impor teknologi China untuk keamanan nasional. FCC mendorong investasi domestik dan menghindari ancaman di masa depan.</t>
+        </is>
+      </c>
+      <c r="F1274" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1274" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807145711-37-757463/amerika-buka-bukaan-alasan-sebenarnya-china-harus-diblokir-total</t>
+        </is>
+      </c>
+      <c r="H1274" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/12/02/bendera-amerikas-serikat-as-dan-china-reutersflorence-loillustrationfile_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1274" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1275" t="inlineStr">
+        <is>
+          <t>Ilmuwan Harvard Klaim Tahu Lokasi Tuhan, Segini Jaraknya dari Bumi</t>
+        </is>
+      </c>
+      <c r="C1275" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1275" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1275" t="inlineStr">
+        <is>
+          <t>Mantan fisikawan Harvard, Michael Guillén, klaim mengetahui lokasi Tuhan di alam semesta. Simak lokasinya!</t>
+        </is>
+      </c>
+      <c r="F1275" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1275" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807134408-37-757422/ilmuwan-harvard-klaim-tahu-lokasi-tuhan-segini-jaraknya-dari-bumi</t>
+        </is>
+      </c>
+      <c r="H1275" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/14/roket-diluncurkan-dari-pulau-hainan-di-selatan-tiongkok-pada-hari-jumat-1072026-pukul-1215-waktu-setempat-dari-pusat-peluncura-1783997825654_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1275" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1276" t="inlineStr">
+        <is>
+          <t>Penampakan Bulan Ditabrak Roket 4 Ton Elon Musk Sampai Bolong-Bolong</t>
+        </is>
+      </c>
+      <c r="C1276" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:45:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1276" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1276" t="inlineStr">
+        <is>
+          <t>Roket SpaceX menghantam Bulan, Danuri merekam perubahan medan. Temuan ini penting untuk studi dampak benda buatan manusia di permukaan Bulan.</t>
+        </is>
+      </c>
+      <c r="F1276" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1276" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807132841-37-757418/penampakan-bulan-ditabrak-roket-4-ton-elon-musk-sampai-bolong-bolong</t>
+        </is>
+      </c>
+      <c r="H1276" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/danuri-merekam-momen-saat-tingkat-atas-roket-spacex-falcon-9-menghantam-permukaan-bulan-pada-tanggal-5-agustus-pukul-1534-wakt-1786084126735_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1276" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1277" t="inlineStr">
+        <is>
+          <t>Demo Besar-Besaran Tolak Data Center Raksasa, Warga Sudah Muak</t>
+        </is>
+      </c>
+      <c r="C1277" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 17:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1277" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1277" t="inlineStr">
+        <is>
+          <t>Pembangunan pusat data Google di India ditentang aktivis lingkungan dan warga sekitar. Mereka menyoroti krisis air dan lingkungan.</t>
+        </is>
+      </c>
+      <c r="F1277" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1277" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807132141-37-757412/demo-besar-besaran-tolak-data-center-raksasa-warga-sudah-muak</t>
+        </is>
+      </c>
+      <c r="H1277" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/22/gedung-data-center-meta-di-mansfield-as-1779441817711_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1277" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1278" t="inlineStr">
+        <is>
+          <t>Erajaya Food dan Nourishment dan Oriental Kopi Jalin Kemitraan Strategis</t>
+        </is>
+      </c>
+      <c r="C1278" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:49:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1278" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1278" t="inlineStr">
+        <is>
+          <t>PT Era Boga Nusantara dan Oriental Coffee International membentuk joint venture PT Era Oriental Kopi untuk ekspansi restoran di Indonesia, fokus Jabodetabek.</t>
+        </is>
+      </c>
+      <c r="F1278" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1278" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807162246-37-757491/erajaya-food-nourishment-dan-oriental-kopi-jalin-kemitraan-strategis</t>
+        </is>
+      </c>
+      <c r="H1278" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/dok-erajaya-food-nourishment-1786096066750_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1278" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1279" t="inlineStr">
+        <is>
+          <t>700.000 Orang Tewas, Google Peringatkan Bencana Besar Lebih Cepat</t>
+        </is>
+      </c>
+      <c r="C1279" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1279" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1279" t="inlineStr">
+        <is>
+          <t>Google meluncurkan WeatherNext, AI yang memprediksi badai tropis dengan lebih cepat. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F1279" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1279" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807121851-37-757398/700000-orang-tewas-google-peringatkan-bencana-besar-lebih-cepat</t>
+        </is>
+      </c>
+      <c r="H1279" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/12/03/kondisi-setelah-siklon-ditwah-melanda-kawasan-niyamgamdora-sri-lanka-selasa-2122025-reutersakila-jayawardena-1764766482101_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1279" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1280" t="inlineStr">
+        <is>
+          <t>Krisis Menggila, HP Mahal Mendadak Laku Keras Diborong Warga</t>
+        </is>
+      </c>
+      <c r="C1280" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 16:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1280" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1280" t="inlineStr">
+        <is>
+          <t>Pasar smartphone premium global tumbuh 5% YoY pada H1 2026, dengan Apple dan Samsung tetap dominan. Simak selengkapnya!</t>
+        </is>
+      </c>
+      <c r="F1280" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1280" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807122415-37-757400/krisis-menggila-hp-mahal-mendadak-laku-keras-diborong-warga</t>
+        </is>
+      </c>
+      <c r="H1280" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/10/07/jasa-service-hp-cnbc-indonesianovina-1759823129283_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1280" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1281" t="inlineStr">
+        <is>
+          <t>Harga Naik, Ini Alasan Banyak Orang Ganti HP Samsung Galaxy Z Fold8</t>
+        </is>
+      </c>
+      <c r="C1281" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 15:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1281" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1281" t="inlineStr">
+        <is>
+          <t>Krisis chip memori global berdampak pada harga smartphone, termasuk Galaxy Z Fold8. Namun, HP ini tetap laku keras sampai cetak rekor.</t>
+        </is>
+      </c>
+      <c r="F1281" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1281" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807115948-37-757392/harga-naik-ini-alasan-banyak-orang-ganti-hp-samsung-galaxy-z-fold8</t>
+        </is>
+      </c>
+      <c r="H1281" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/07/18/samsung-galaxy-z-fold8-1784366205171_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1281" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1282" t="inlineStr">
+        <is>
+          <t>100 Spesies Terancam Punah, Leonardi DiCaprio Langsung Turun Tangan</t>
+        </is>
+      </c>
+      <c r="C1282" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1282" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1282" t="inlineStr">
+        <is>
+          <t>Leonardo DiCaprio dan Jeff Bezos luncurkan inisiatif dengan dana Rp3,5 triliun untuk menyelamatkan 100 spesies terancam punah.</t>
+        </is>
+      </c>
+      <c r="F1282" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1282" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807114627-37-757380/100-spesies-terancam-punah-leonardi-dicaprio-langsung-turun-tangan</t>
+        </is>
+      </c>
+      <c r="H1282" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/01/12/leonardo-dicaprio-berpose-di-karpet-merah-pada-acara-golden-globes-ke-83-di-beverly-hills-california-as-minggu-1112026-reuters-1768186303176_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1282" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1283" t="inlineStr">
+        <is>
+          <t>VinFast Indonesia dan Danamon Perkuat Ekosistem Kendaraan Listrik di RI</t>
+        </is>
+      </c>
+      <c r="C1283" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:40:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1283" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1283" t="inlineStr">
+        <is>
+          <t>VinFast Indonesia dan Bank Danamon tandatangani kerja sama pembiayaan dealer di GIIAS 2026. Kolaborasi ini dukung ekspansi dan ekosistem kendaraan listrik.</t>
+        </is>
+      </c>
+      <c r="F1283" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1283" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807143221-37-757449/vinfast-indonesia-danamon-perkuat-ekosistem-kendaraan-listrik-di-ri</t>
+        </is>
+      </c>
+      <c r="H1283" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/vinfast-1786088440435_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1283" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1284" t="inlineStr">
+        <is>
+          <t>267 Titik di Kaltim 'Gelap' Tak Ada Internet, Komdigi Buka Suara</t>
+        </is>
+      </c>
+      <c r="C1284" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 14:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1284" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1284" t="inlineStr">
+        <is>
+          <t>Meskipun konektivitas di Kalimantan Timur mencapai 95,5%, masih ada 269 titik blank spot. Simak penjelasan Wamenkomdigi!</t>
+        </is>
+      </c>
+      <c r="F1284" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1284" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807114120-37-757379/267-titik-di-kaltim-gelap-tak-ada-internet-komdigi-buka-suara</t>
+        </is>
+      </c>
+      <c r="H1284" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/05/22/wakil-menteri-komunikasi-dan-digital-nezar-patria-saat-menyampaikan-pemaparan-dalam-jogja-financial-festival-2026-di-jogja-exp-1779442550629_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1284" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1285" t="inlineStr">
+        <is>
+          <t>Video: Inovasi Fintech Lending Atasi Gap Kredit UMKM Sebesar Rp2.400 T</t>
+        </is>
+      </c>
+      <c r="C1285" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:53:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1285" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1285" t="inlineStr">
+        <is>
+          <t>Inovasi Fintech Lending Atasi Gap Kredit UMKM Yang Mencapai Rp 2.400 Triliun</t>
+        </is>
+      </c>
+      <c r="F1285" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1285" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807121240-39-757394/video-inovasi-fintech-lending-atasi-gap-kredit-umkm-sebesar-rp2400-t</t>
+        </is>
+      </c>
+      <c r="H1285" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/inovasi-fintech-lending-atasi-gap-kredit-umkm-yang-mencapai-rp-2400-triliun-1786085305978_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1285" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1286" t="inlineStr">
+        <is>
+          <t>Pencurian Terbesar Dalam Sejarah, Uang Rp 500 Miliar Lenyap Seketika</t>
+        </is>
+      </c>
+      <c r="C1286" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 13:20:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1286" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1286" t="inlineStr">
+        <is>
+          <t>Tahun 2026 tercatat sebagai pencurian kripto terburuk dalam sejarah. Kerugian lebih dari Rp500 miliar.</t>
+        </is>
+      </c>
+      <c r="F1286" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1286" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807113510-37-757377/pencurian-terbesar-dalam-sejarah-uang-rp-500-miliar-lenyap-seketika</t>
+        </is>
+      </c>
+      <c r="H1286" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2023/12/03/flexing-di-medsos-sasaran-empuk-penipu-online-kuras-rekening_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1286" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1287" t="inlineStr">
+        <is>
+          <t>Bulan Terus Menjauhi Bumi, Manusia Mulai Rasakan Dampaknya</t>
+        </is>
+      </c>
+      <c r="C1287" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1287" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1287" t="inlineStr">
+        <is>
+          <t>Jarak Bumi ke Bulan sekitar 384.400 km dan terus menjauh 3,8 cm per tahun. Ini berdampak pada frekuensi Gerhana Matahari Total.</t>
+        </is>
+      </c>
+      <c r="F1287" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1287" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807113304-37-757374/bulan-terus-menjauhi-bumi-manusia-mulai-rasakan-dampaknya</t>
+        </is>
+      </c>
+      <c r="H1287" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/04/08/pemandangan-bumi-yang-sebagian-tersembunyi-di-balik-bulan-yang-ditangkap-melalui-jendela-pesawat-ruang-angkasa-orion-pada-puku-1775628749897_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1287" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1288" t="inlineStr">
+        <is>
+          <t>Ledakan Gempa Langit Terdengar di Mana-Mana, Ilmuwan Buka Suara</t>
+        </is>
+      </c>
+      <c r="C1288" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 12:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1288" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1288" t="inlineStr">
+        <is>
+          <t>Fenomena "gempa langit" atau skyquake terus menjadi misteri. Penelitian terbaru menunjukkan asal-muasalnya.</t>
+        </is>
+      </c>
+      <c r="F1288" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1288" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807111947-37-757370/ledakan-gempa-langit-terdengar-di-mana-mana-ilmuwan-buka-suara</t>
+        </is>
+      </c>
+      <c r="H1288" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/08/26/badai-debu-menyelimuti-langit-di-paradise-valley-arizona-as-25-agustus-2025-abc-affiliate-knxv-via-reuters-1756193111443_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1288" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" t="inlineStr">
+        <is>
+          <t>Tech</t>
+        </is>
+      </c>
+      <c r="B1289" t="inlineStr">
+        <is>
+          <t>Samsung F70 Pro Baru Rilis, HP Baterai 6.000 mAh Harga Rp 4 Jutaan</t>
+        </is>
+      </c>
+      <c r="C1289" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 11:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1289" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1289" t="inlineStr">
+        <is>
+          <t>Samsung resmi luncurkan Galaxy F70 Pro di India. Ponsel ini hadir dengan baterai 6.000 mAh, layar AMOLED 6,7 inci, kamera 50 MP.</t>
+        </is>
+      </c>
+      <c r="F1289" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1289" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/tech/20260807110648-37-757368/samsung-f70-pro-baru-rilis-hp-baterai-6000-mah-harga-rp-4-jutaan</t>
+        </is>
+      </c>
+      <c r="H1289" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/galaxy-f70-pro-5g-1786076454500_169.png?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1289" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" t="inlineStr">
+        <is>
+          <t>Energi</t>
+        </is>
+      </c>
+      <c r="B1290" t="inlineStr">
+        <is>
+          <t>Konsumsi Listrik SPKLU Melonjak, PLN Perluas Infrastruktur Pengisian Kendaraan Listrik</t>
+        </is>
+      </c>
+      <c r="C1290" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:41:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1290" t="inlineStr">
+        <is>
+          <t>Erdy Nasrul</t>
+        </is>
+      </c>
+      <c r="E1290" t="inlineStr">
+        <is>
+          <t>REPUBLIKA.CO.ID, JAKARTA -- Penggunaan kendaraan listrik di Indonesia menunjukkan pertumbuhan yang semakin kuat. Hal itu tercermin dari konsumsi listrik pada Stasiun Pengisian Kendaraan Listrik Umum (SPKLU) yang mencapai 62,4 juta...</t>
+        </is>
+      </c>
+      <c r="F1290" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1290" t="inlineStr">
+        <is>
+          <t>https://ekonomi.republika.co.id/berita/tjem5d451/konsumsi-listrik-spklu-melonjak-pln-perluas-infrastruktur-pengisian-kendaraan-listrik</t>
+        </is>
+      </c>
+      <c r="H1290" t="inlineStr">
+        <is>
+          <t>https://static.republika.co.id/uploads/images/detailnews/petugas-spklu-mengisi-energi-listrik-ke-sebuah_260807214053-993.jpeg</t>
+        </is>
+      </c>
+      <c r="I1290" t="inlineStr">
+        <is>
+          <t>Republika</t>
+        </is>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1291" t="inlineStr">
+        <is>
+          <t>Gedung Bapenda DKI Jakarta Kebakaran</t>
+        </is>
+      </c>
+      <c r="C1291" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:29:03 +0700</t>
+        </is>
+      </c>
+      <c r="D1291" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1291" t="inlineStr">
+        <is>
+          <t>Gedung Bapenda DKI Jakarta di Gambir terbakar. Sebanyak 13 unit damkar dan 65 personel dikerahkan.</t>
+        </is>
+      </c>
+      <c r="F1291" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1291" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264699/gedung-bapenda-dki-jakarta-kebakaran</t>
+        </is>
+      </c>
+      <c r="H1291" t="inlineStr">
+        <is>
+          <t>https://cdn0-production-images-kly.akamaized.net/HYiZgk3x63v239p53K0KX2oQJvY=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318630/original/040776900_1786116540-Kebakaran.jpg</t>
+        </is>
+      </c>
+      <c r="I1291" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1292" t="inlineStr">
+        <is>
+          <t>Penampakan Febrie Adriansyah Usai 7 Jam Diperiksa Kejagung</t>
+        </is>
+      </c>
+      <c r="C1292" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:38:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1292" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1292" t="inlineStr">
+        <is>
+          <t>Febrie meninggalkan ruang pemeriksaan sekitar pukul 20.30 WIB. Ia langsung menuju mobil tahanan.</t>
+        </is>
+      </c>
+      <c r="F1292" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1292" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264672/penampakan-febrie-adriansyah-usai-7-jam-diperiksa-kejagung</t>
+        </is>
+      </c>
+      <c r="H1292" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/sp4SqvNV_83npEChYsHfHfViHdc=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318625/original/014147200_1786113402-IMG_3066.jpg</t>
+        </is>
+      </c>
+      <c r="I1292" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1293" t="inlineStr">
+        <is>
+          <t>Kuasa Hukum: Febrie Adriansyah Kooperatif Saat Diperiksa sebagai Tersangka</t>
+        </is>
+      </c>
+      <c r="C1293" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:47:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1293" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1293" t="inlineStr">
+        <is>
+          <t>Kuasa hukum mantan Jampidsus Febrie Adriansyah menyatakan bahwa kliennya bersikap kooperatif saat menjalani pemeriksaan sebagai tersangka.</t>
+        </is>
+      </c>
+      <c r="F1293" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1293" t="inlineStr">
+        <is>
+          <t>https://nasional.kompas.com/read/2026/08/07/22433161/kuasa-hukum-febrie-adriansyah-kooperatif-saat-diperiksa-sebagai-tersangka</t>
+        </is>
+      </c>
+      <c r="H1293" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/TjloeZKNzN-WVra0igWLvfg3HEc=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/07/6a75f51e10fa1.jpg</t>
+        </is>
+      </c>
+      <c r="I1293" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B1294" t="inlineStr">
+        <is>
+          <t>Dilema Warga Kuranji Padang: Antara Normalisasi Sungai dan Pilihan Berat Relokasi</t>
+        </is>
+      </c>
+      <c r="C1294" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:47:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1294" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1294" t="inlineStr">
+        <is>
+          <t>Warga Kuranji, Padang, Sumbar dilema dengan adanya aliran sungai Batang Guo yang jebol dan ancaman banjir susulan yang menghantui.</t>
+        </is>
+      </c>
+      <c r="F1294" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1294" t="inlineStr">
+        <is>
+          <t>https://regional.kompas.com/read/2026/08/07/221736278/dilema-warga-kuranji-padang-antara-normalisasi-sungai-dan-pilihan-berat</t>
+        </is>
+      </c>
+      <c r="H1294" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/tmaICnT04aLuV7IPK9dU1SnRQ_g=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/07/6a75eea4b05f1.jpeg</t>
+        </is>
+      </c>
+      <c r="I1294" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" t="inlineStr">
+        <is>
+          <t>Regional</t>
+        </is>
+      </c>
+      <c r="B1295" t="inlineStr">
+        <is>
+          <t>Keluarga Ungkap Kondisi Terkahir Kesehatan Yurizal saat Posting 8 Jam Menunggu di RS : Menahan Rasa Sakit</t>
+        </is>
+      </c>
+      <c r="C1295" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:47:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1295" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1295" t="inlineStr">
+        <is>
+          <t>Keluarga mengungkapkan kondisi kesehatan Yurizal, pasien BPJS, saat terakhirnya sebelum menghembuskan nafas terakhir.</t>
+        </is>
+      </c>
+      <c r="F1295" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1295" t="inlineStr">
+        <is>
+          <t>https://bandung.kompas.com/read/2026/08/07/214627678/keluarga-ungkap-kondisi-terkahir-kesehatan-yurizal-saat-posting-8-jam</t>
+        </is>
+      </c>
+      <c r="H1295" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/7lnn2eO2C64CMZyw4ySmKJcGGIg=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/06/6a7476b7ed27e.jpg</t>
+        </is>
+      </c>
+      <c r="I1295" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1191"/>
+  <autoFilter ref="A1:I1295"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-07.xlsx
+++ b/data/berita_2026-08-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1295</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1361</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1295"/>
+  <dimension ref="A1:I1361"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -61298,8 +61298,3110 @@
         </is>
       </c>
     </row>
+    <row r="1296">
+      <c r="A1296" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1296" t="inlineStr">
+        <is>
+          <t>Indonesia akhiri perlawanan sengit Vietnam 3-2</t>
+        </is>
+      </c>
+      <c r="C1296" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:38:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1296" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1296" t="inlineStr">
+        <is>
+          <t>Tim nasional voli putri Indonesia mengakhiri perlawanan sengit dari timnas Vietnam, 3-2 (20-25, 18-25, 25-22, 25-20, ...</t>
+        </is>
+      </c>
+      <c r="F1296" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1296" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685180/indonesia-akhiri-perlawanan-sengit-vietnam-3-2</t>
+        </is>
+      </c>
+      <c r="H1296" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/HPG0Fg1bIAAsUKg.jpg</t>
+        </is>
+      </c>
+      <c r="I1296" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1297" t="inlineStr">
+        <is>
+          <t>AI Cinefest 2026 himpun 1.111 film buatan AI dari seluruh Indonesia</t>
+        </is>
+      </c>
+      <c r="C1297" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:36:46 +0700</t>
+        </is>
+      </c>
+      <c r="D1297" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1297" t="inlineStr">
+        <is>
+          <t>Telkomsel bersama Huawei dan MiniMax menggelar kompetisi film pendek AI Cinefest 2026 yang menghimpun 1.111 karya film ...</t>
+        </is>
+      </c>
+      <c r="F1297" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1297" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685177/ai-cinefest-2026-himpun-1111-film-buatan-ai-dari-seluruh-indonesia</t>
+        </is>
+      </c>
+      <c r="H1297" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000142174.jpg</t>
+        </is>
+      </c>
+      <c r="I1297" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1298" t="inlineStr">
+        <is>
+          <t>RS Pusri putus kerja sama dengan Dokter Tamara buntut hina pasien BPJS</t>
+        </is>
+      </c>
+      <c r="C1298" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:36:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1298" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1298" t="inlineStr">
+        <is>
+          <t>ANTARA - Rumah Sakit Pusri Palembang mengakhiri kerja sama dengan dokter mitra yang diduga terlibat dalam polemik ...</t>
+        </is>
+      </c>
+      <c r="F1298" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1298" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5685175/rs-pusri-putus-kerja-sama-dengan-dokter-tamara-buntut-hina-pasien-bpjs</t>
+        </is>
+      </c>
+      <c r="H1298" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-07-232436.jpg</t>
+        </is>
+      </c>
+      <c r="I1298" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1299" t="inlineStr">
+        <is>
+          <t>Menkum minta penanganan laporan pelanggaran KI dipercepat</t>
+        </is>
+      </c>
+      <c r="C1299" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:28:43 +0700</t>
+        </is>
+      </c>
+      <c r="D1299" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1299" t="inlineStr">
+        <is>
+          <t>Menteri Hukum Supratman Andi Agtas meminta jajaran Kementerian Hukum mempercepat penanganan laporan dugaan pelanggaran ...</t>
+        </is>
+      </c>
+      <c r="F1299" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1299" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685171/menkum-minta-penanganan-laporan-pelanggaran-ki-dipercepat</t>
+        </is>
+      </c>
+      <c r="H1299" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000475284.jpg</t>
+        </is>
+      </c>
+      <c r="I1299" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1300" t="inlineStr">
+        <is>
+          <t>LPKA Klas I Kupang prioritaskan pendidikan bagi anak binaan</t>
+        </is>
+      </c>
+      <c r="C1300" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:25:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1300" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1300" t="inlineStr">
+        <is>
+          <t>ANTARA - Lembaga Pembinaan Khusus Anak (LPKA) Klas I Kupang memprioritaskan pendidikan bagi 37 anak binaan sebagai hak ...</t>
+        </is>
+      </c>
+      <c r="F1300" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1300" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5685161/lpka-klas-i-kupang-prioritaskan-pendidikan-bagi-anak-binaan</t>
+        </is>
+      </c>
+      <c r="H1300" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-07-230421.jpg</t>
+        </is>
+      </c>
+      <c r="I1300" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1301" t="inlineStr">
+        <is>
+          <t>Kepala Barantin pastikan layanan karantina optimal kawal ekspor udang</t>
+        </is>
+      </c>
+      <c r="C1301" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:23:42 +0700</t>
+        </is>
+      </c>
+      <c r="D1301" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1301" t="inlineStr">
+        <is>
+          <t>Kepala Badan Karantina Indonesia (Barantin) Abdul Kadir Karding memastikan layanan karantina berjalan optimal terhadap ...</t>
+        </is>
+      </c>
+      <c r="F1301" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1301" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685169/kepala-barantin-pastikan-layanan-karantina-optimal-kawal-ekspor-udang</t>
+        </is>
+      </c>
+      <c r="H1301" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1002919266.jpg</t>
+        </is>
+      </c>
+      <c r="I1301" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1302" t="inlineStr">
+        <is>
+          <t>KY ungkap beda pendapat komisioner soal tiga calon hakim agung</t>
+        </is>
+      </c>
+      <c r="C1302" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:18:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1302" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1302" t="inlineStr">
+        <is>
+          <t>Komisi Yudisial (KY) mengungkap adanya perbedaan pendapat di antara komisioner dalam penetapan kelulusan tiga calon ...</t>
+        </is>
+      </c>
+      <c r="F1302" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1302" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685165/ky-ungkap-beda-pendapat-komisioner-soal-tiga-calon-hakim-agung</t>
+        </is>
+      </c>
+      <c r="H1302" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_4555.jpeg</t>
+        </is>
+      </c>
+      <c r="I1302" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1303" t="inlineStr">
+        <is>
+          <t>Gerakan Langit Biru AHY di Pulau Madura berlanjut</t>
+        </is>
+      </c>
+      <c r="C1303" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:18:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1303" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1303" t="inlineStr">
+        <is>
+          <t>Gerakan Langit Biru Indonesia ASRI, yakni  pendistribusian bantuan air bersih ke desa-desa terdampak kekeringan di ...</t>
+        </is>
+      </c>
+      <c r="F1303" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1303" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685164/gerakan-langit-biru-ahy-di-pulau-madura-berlanjut</t>
+        </is>
+      </c>
+      <c r="H1303" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/Langit-Biru-Madura.jpg</t>
+        </is>
+      </c>
+      <c r="I1303" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1304" t="inlineStr">
+        <is>
+          <t>Aldila fokus adaptasi lapangan jelang laga pembuka WTA 1000 Toronto</t>
+        </is>
+      </c>
+      <c r="C1304" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:14:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1304" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1304" t="inlineStr">
+        <is>
+          <t>Petenis ganda putri Indonesia Aldila Sutjiadi memfokuskan persiapan pada adaptasi lapangan menjelang laga pembuka ...</t>
+        </is>
+      </c>
+      <c r="F1304" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1304" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685159/aldila-fokus-adaptasi-lapangan-jelang-laga-pembuka-wta-1000-toronto</t>
+        </is>
+      </c>
+      <c r="H1304" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2025/09/12/Aldila.jpg</t>
+        </is>
+      </c>
+      <c r="I1304" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1305" t="inlineStr">
+        <is>
+          <t>Bea Cukai-Polisi gagalkan penyelundupan 10,1 kg ganja di bandara Bali</t>
+        </is>
+      </c>
+      <c r="C1305" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:10:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1305" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1305" t="inlineStr">
+        <is>
+          <t>ANTARA - Kantor Pengawasan dan Pelayanan Bea Cukai (KPPBC) Ngurah Rai bersama Satuan Reserse Narkoba Polres Bandara I ...</t>
+        </is>
+      </c>
+      <c r="F1305" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1305" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5685020/bea-cukai-polisi-gagalkan-penyelundupan-101-kg-ganja-di-bandara-bali</t>
+        </is>
+      </c>
+      <c r="H1305" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BEA-CUKAI-POLISI-GAGALKAN-PENYELUNDUPAN-10-1-KG-GANJA-DI-BANDARA-BALI_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1305" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1306" t="inlineStr">
+        <is>
+          <t>PSSI akan lakukan evaluasi setelah Indonesia gagal tembus semifinal</t>
+        </is>
+      </c>
+      <c r="C1306" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:09:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1306" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1306" t="inlineStr">
+        <is>
+          <t>Ketua Umum PSSI Erick Thohir mengungkapkan pihaknya akan melakukan evaluasi terhadap hasil timnas Indonesia yang gagal ...</t>
+        </is>
+      </c>
+      <c r="F1306" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1306" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685155/pssi-akan-lakukan-evaluasi-setelah-indonesia-gagal-tembus-semifinal</t>
+        </is>
+      </c>
+      <c r="H1306" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/HPILtZ8aEAI6W61.jpg</t>
+        </is>
+      </c>
+      <c r="I1306" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1307" t="inlineStr">
+        <is>
+          <t>INDEF sebut PFII syariah bisa jadi daya tawar pembeda</t>
+        </is>
+      </c>
+      <c r="C1307" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:07:44 +0700</t>
+        </is>
+      </c>
+      <c r="D1307" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1307" t="inlineStr">
+        <is>
+          <t>Ketua Center for Sharia Economic Development (CSED) Institute for Development of Economics and Finance (INDEF) Nur ...</t>
+        </is>
+      </c>
+      <c r="F1307" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1307" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685152/indef-sebut-pfii-syariah-bisa-jadi-daya-tawar-pembeda</t>
+        </is>
+      </c>
+      <c r="H1307" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/IMG_20260807_225436.jpg</t>
+        </is>
+      </c>
+      <c r="I1307" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1308" t="inlineStr">
+        <is>
+          <t>OJK: Sektor jasa keuangan Sumbar tumbuh positif pada triwulan II 2026</t>
+        </is>
+      </c>
+      <c r="C1308" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:05:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1308" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1308" t="inlineStr">
+        <is>
+          <t>ANTARA - Otoritas Jasa Keuangan (OJK) mencatat kinerja sektor jasa keuangan di Sumatera Barat tetap tumbuh positif pada ...</t>
+        </is>
+      </c>
+      <c r="F1308" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1308" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5685116/ojk-sektor-jasa-keuangan-sumbar-tumbuh-positif-pada-triwulan-ii-2026</t>
+        </is>
+      </c>
+      <c r="H1308" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/OJK-SEKTOR-JASA-KEUANGAN-SUMBAR-TUMBUH-POSITIF-PADA-TRIWULAN-II-2026.jpg</t>
+        </is>
+      </c>
+      <c r="I1308" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1309" t="inlineStr">
+        <is>
+          <t>Kreativitas manusia jadi unsur penting dalam membuat film dengan AI</t>
+        </is>
+      </c>
+      <c r="C1309" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:04:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1309" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1309" t="inlineStr">
+        <is>
+          <t>Kreativitas dari buah pikiran manusia dinilai tetap menjadi unsur penting dalam membuat film menggunakan teknologi ...</t>
+        </is>
+      </c>
+      <c r="F1309" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1309" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685148/kreativitas-manusia-jadi-unsur-penting-dalam-membuat-film-dengan-ai</t>
+        </is>
+      </c>
+      <c r="H1309" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000142158.jpg</t>
+        </is>
+      </c>
+      <c r="I1309" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1310" t="inlineStr">
+        <is>
+          <t>TNBTS: kebakaran di Bromo diduga sisa perapian orang di Bantengan</t>
+        </is>
+      </c>
+      <c r="C1310" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:02:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1310" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1310" t="inlineStr">
+        <is>
+          <t>ANTARA - ‎Kebakaran yang melanda kawasan Gunung Bromo, Jawa Timur, pihak TNBTS menduga akibat dipicu aktivitas ...</t>
+        </is>
+      </c>
+      <c r="F1310" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1310" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5685145/tnbts-kebakaran-di-bromo-diduga-sisa-perapian-orang-di-bantengan</t>
+        </is>
+      </c>
+      <c r="H1310" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-07-225216.jpg</t>
+        </is>
+      </c>
+      <c r="I1310" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1311" t="inlineStr">
+        <is>
+          <t>Menghadap Wamensos, 4 bupati siap bangun Sekolah Rakyat permanen</t>
+        </is>
+      </c>
+      <c r="C1311" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:00:56 +0700</t>
+        </is>
+      </c>
+      <c r="D1311" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1311" t="inlineStr">
+        <is>
+          <t>Empat kepala daerah dari Agam, Buton Selatan, Kutai Kertanegara, dan Buru datang ke kantor Kemensos untuk menegaskan ...</t>
+        </is>
+      </c>
+      <c r="F1311" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1311" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685147/menghadap-wamensos-4-bupati-siap-bangun-sekolah-rakyat-permanen</t>
+        </is>
+      </c>
+      <c r="H1311" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-20.24.12-1.jpeg</t>
+        </is>
+      </c>
+      <c r="I1311" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1312" t="inlineStr">
+        <is>
+          <t>Prabowo sebut pendapatan Danantara dilaporkan naik hingga 400 persen</t>
+        </is>
+      </c>
+      <c r="C1312" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1312" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1312" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden Prabowo Subianto menyebut Badan Pengelola Investasi (BPI) Danantara mencatat peningkatan ...</t>
+        </is>
+      </c>
+      <c r="F1312" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1312" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5685047/prabowo-sebut-pendapatan-danantara-dilaporkan-naik-hingga-400-persen</t>
+        </is>
+      </c>
+      <c r="H1312" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/PRABOWO-SEBUT-PENDAPATAN-DANANTARA-DILAPORKAN-NAIK-HINGGA-400-PERSEN.jpg</t>
+        </is>
+      </c>
+      <c r="I1312" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1313" t="inlineStr">
+        <is>
+          <t>Setengah abad, Bahlil Rilis buku "10 Karya Nyata untuk Negeri"</t>
+        </is>
+      </c>
+      <c r="C1313" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:59:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1313" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1313" t="inlineStr">
+        <is>
+          <t>ANTARA - Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia meluncurkan Buku 10 Karya Nyata untuk Negeri: ...</t>
+        </is>
+      </c>
+      <c r="F1313" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1313" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5685113/setengah-abad-bahlil-rilis-buku-10-karya-nyata-untuk-negeri</t>
+        </is>
+      </c>
+      <c r="H1313" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/SETENGAH-ABAD-BAHLIL-RILIS-BUKU-10-KARYA-NYATA-UNTUK-NEGERI_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1313" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1314" t="inlineStr">
+        <is>
+          <t>BI: Sektor perumahan dan kawasan industri perkokoh investasi Banten</t>
+        </is>
+      </c>
+      <c r="C1314" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:55:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1314" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1314" t="inlineStr">
+        <is>
+          <t>Kantor Perwakilan Bank Indonesia (BI) Provinsi Banten mencatat bahwa realisasi investasi di wilayah tersebut didominasi ...</t>
+        </is>
+      </c>
+      <c r="F1314" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1314" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685141/bi-sektor-perumahan-dan-kawasan-industri-perkokoh-investasi-banten</t>
+        </is>
+      </c>
+      <c r="H1314" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000879852.jpg</t>
+        </is>
+      </c>
+      <c r="I1314" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1315" t="inlineStr">
+        <is>
+          <t>Wamen PKP usulkan Perumnas perkuat penyediaan hunian strategis</t>
+        </is>
+      </c>
+      <c r="C1315" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:55:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1315" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1315" t="inlineStr">
+        <is>
+          <t>ANTARA - Wakil Menteri Perumahan dan Kawasan Permukiman (PKP) Fahri Hamzah meminta Perum Perumnas menjadi off ...</t>
+        </is>
+      </c>
+      <c r="F1315" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1315" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5685016/wamen-pkp-usulkan-perumnas-perkuat-penyediaan-hunian-strategis</t>
+        </is>
+      </c>
+      <c r="H1315" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/WAMEN-PKP-USULKAN-PERUMNAS-PERKUAT-PENYEDIAAN-HUNIAN-STRATEGIS.jpg</t>
+        </is>
+      </c>
+      <c r="I1315" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1316" t="inlineStr">
+        <is>
+          <t>Nissan ramaikan GIIAS 2026 melalui Serena e-Power</t>
+        </is>
+      </c>
+      <c r="C1316" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:52:42 +0700</t>
+        </is>
+      </c>
+      <c r="D1316" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/antaranewsdotcom</t>
+        </is>
+      </c>
+      <c r="E1316" t="inlineStr">
+        <is>
+          <t>PT Nissan Motor Distributor Indonesia (NMDI) kembali ikut meramaikan pameran otomotif Gaikindo Indonesia Internaional ...</t>
+        </is>
+      </c>
+      <c r="F1316" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1316" t="inlineStr">
+        <is>
+          <t>https://otomotif.antaranews.com/berita/5685137/nissan-ramaikan-giias-2026-melalui-serena-e-power</t>
+        </is>
+      </c>
+      <c r="H1316" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-22.17.18.jpeg</t>
+        </is>
+      </c>
+      <c r="I1316" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1317" t="inlineStr">
+        <is>
+          <t>Khofifah tinjau kebakaran Bromo, area terbakar meluas capai 176 hektar</t>
+        </is>
+      </c>
+      <c r="C1317" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:50:10 +0700</t>
+        </is>
+      </c>
+      <c r="D1317" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1317" t="inlineStr">
+        <is>
+          <t>ANTARA - ‎‎Gubernur Jawa Timur Khofifah Indar Parawansa meninjau langsung penanganan kebakaran di kawasan ...</t>
+        </is>
+      </c>
+      <c r="F1317" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1317" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5685132/khofifah-tinjau-kebakaran-bromo-area-terbakar-meluas-capai-176-hektar</t>
+        </is>
+      </c>
+      <c r="H1317" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-07-224200.jpg</t>
+        </is>
+      </c>
+      <c r="I1317" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1318" t="inlineStr">
+        <is>
+          <t>Direktur STB: Kelola pengeluaran kunci agar tak bergantung "paylater"</t>
+        </is>
+      </c>
+      <c r="C1318" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:48:08 +0700</t>
+        </is>
+      </c>
+      <c r="D1318" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1318" t="inlineStr">
+        <is>
+          <t>Managing Director perusahaan induk investasi dan penyedia layanan finansial PT Samuel Tumbuh Bersama (STB) Tae Yong ...</t>
+        </is>
+      </c>
+      <c r="F1318" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1318" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685136/direktur-stb-kelola-pengeluaran-kunci-agar-tak-bergantung-paylater</t>
+        </is>
+      </c>
+      <c r="H1318" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000178486.jpg</t>
+        </is>
+      </c>
+      <c r="I1318" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1319" t="inlineStr">
+        <is>
+          <t>BGN: 950 dapur MBG diduga tak layak higienis dan sanitasi</t>
+        </is>
+      </c>
+      <c r="C1319" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:47:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1319" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1319" t="inlineStr">
+        <is>
+          <t>ANTARA - Kepala Badan Gizi Nasional (BGN) Sudaryono menyebut 950 Satuan Pelayanan Pemenuhan Gizi (SPPG) atau dapur ...</t>
+        </is>
+      </c>
+      <c r="F1319" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1319" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5685103/bgn-950-dapur-mbg-diduga-tak-layak-higienis-dan-sanitasi</t>
+        </is>
+      </c>
+      <c r="H1319" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/BGN-950-DAPUR-MBG-DIDUGA-TAK-LAYAK-HIGIENIS-DAN-SANITASI.jpg</t>
+        </is>
+      </c>
+      <c r="I1319" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1320" t="inlineStr">
+        <is>
+          <t>Prabowo sebut perjalanan hidup Bahlil jadi inspirasi generasi muda</t>
+        </is>
+      </c>
+      <c r="C1320" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:46:46 +0700</t>
+        </is>
+      </c>
+      <c r="D1320" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1320" t="inlineStr">
+        <is>
+          <t>ANTARA - Presiden RI Prabowo Subianto mengatakan Menteri Energi dan Sumber Daya Mineral (ESDM) Bahlil Lahadalia dapat ...</t>
+        </is>
+      </c>
+      <c r="F1320" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1320" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5685029/prabowo-sebut-perjalanan-hidup-bahlil-jadi-inspirasi-generasi-muda</t>
+        </is>
+      </c>
+      <c r="H1320" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/AB_PRABOWO-SEBUT-PERJALANAN-HIDUP-BAHLIL-JADI-INSPIRASI-GENERASI-MUDA.jpg</t>
+        </is>
+      </c>
+      <c r="I1320" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1321" t="inlineStr">
+        <is>
+          <t>Wamendikdasmen ajak Pemkab Bungo tingkatkan APK kurangi ATS lewat PJJ</t>
+        </is>
+      </c>
+      <c r="C1321" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:45:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1321" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1321" t="inlineStr">
+        <is>
+          <t>Wakil Menteri Pendidikan Dasar dan Menengah (Wamendikdasmen) Fajar Riza Ul Haq mengajak Pemerintah Kabupaten Bungo, ...</t>
+        </is>
+      </c>
+      <c r="F1321" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1321" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685128/wamendikdasmen-ajak-pemkab-bungo-tingkatkan-apk-kurangi-ats-lewat-pjj</t>
+        </is>
+      </c>
+      <c r="H1321" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000229856.jpg</t>
+        </is>
+      </c>
+      <c r="I1321" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1322" t="inlineStr">
+        <is>
+          <t>Perwira polisi terlibat kecelakaan tewaskan balita di Bone ditahan</t>
+        </is>
+      </c>
+      <c r="C1322" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:44:12 +0700</t>
+        </is>
+      </c>
+      <c r="D1322" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1322" t="inlineStr">
+        <is>
+          <t>Polres Bone menahan seorang perwira polisi berinisial MA berpangkat Inspektur Polisi Dua (Ipda) yang terlibat ...</t>
+        </is>
+      </c>
+      <c r="F1322" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1322" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685124/perwira-polisi-terlibat-kecelakaan-tewaskan-balita-di-bone-ditahan</t>
+        </is>
+      </c>
+      <c r="H1322" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/kasus-polisi-tabrak-bocah-di-bone-dok-polisi.jpeg</t>
+        </is>
+      </c>
+      <c r="I1322" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1323" t="inlineStr">
+        <is>
+          <t>Kemensos kebut pembangunan Sekolah Rakyat permanen lewat TP2SR</t>
+        </is>
+      </c>
+      <c r="C1323" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:42:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1323" t="inlineStr">
+        <is>
+          <t>antaranews.com</t>
+        </is>
+      </c>
+      <c r="E1323" t="inlineStr">
+        <is>
+          <t>Kementerian Sosial (Kemensos) membentuk Tim Percepatan Pembangunan Sekolah Rakyat (TP2SR) sebagai tim ad hoc untuk ...</t>
+        </is>
+      </c>
+      <c r="F1323" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1323" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685120/kemensos-kebut-pembangunan-sekolah-rakyat-permanen-lewat-tp2sr</t>
+        </is>
+      </c>
+      <c r="H1323" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-20.24.12.jpeg</t>
+        </is>
+      </c>
+      <c r="I1323" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1324" t="inlineStr">
+        <is>
+          <t>Kejagung: Febrio Adiono Pegawai, Bukan Jaksa</t>
+        </is>
+      </c>
+      <c r="C1324" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:04:07 +0700</t>
+        </is>
+      </c>
+      <c r="D1324" t="inlineStr">
+        <is>
+          <t>Kurniawan Fadilah</t>
+        </is>
+      </c>
+      <c r="E1324" t="inlineStr">
+        <is>
+          <t>Febrio Adiono, staf Kejagung, terlibat dalam kasus kematian misterius Sutrimo di depan klinik. Polisi selidiki penyebab kematian dan kumpulkan saksi.</t>
+        </is>
+      </c>
+      <c r="F1324" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1324" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609321/kejagung-febrio-adiono-pegawai-bukan-jaksa</t>
+        </is>
+      </c>
+      <c r="H1324" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/07/27/puslabfor-polri-menggelar-olah-tempat-kejadian-perkara-tkp-di-klinik-mordent-kawasan-kebayoran-baru-jakarta-selatan-1785134569014_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1324" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1325" t="inlineStr">
+        <is>
+          <t>100 Personel Damkar Dikerahkan Padamkan Kebakaran Hebat di Gedung Bapenda DKI</t>
+        </is>
+      </c>
+      <c r="C1325" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:54:25 +0700</t>
+        </is>
+      </c>
+      <c r="D1325" t="inlineStr">
+        <is>
+          <t>Rolando Fransiscus Sihombing</t>
+        </is>
+      </c>
+      <c r="E1325" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda gedung Bapenda DKI Jakarta, memicu pengerahan 20 unit pemadam. Asap membubung tinggi, penyebab dan korban masih belum diketahui.</t>
+        </is>
+      </c>
+      <c r="F1325" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1325" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609314/100-personel-damkar-dikerahkan-padamkan-kebakaran-hebat-di-gedung-bapenda-dki</t>
+        </is>
+      </c>
+      <c r="H1325" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2022/10/17/ilustrasi-kebakaran_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1325" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1326" t="inlineStr">
+        <is>
+          <t>Bahtra Banong Raih 'Legislator Aspiratif Bidang Keadilan Sosial-Agraria' detiktimur Awards 2026</t>
+        </is>
+      </c>
+      <c r="C1326" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:51:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1326" t="inlineStr">
+        <is>
+          <t>Tim detikSulsel</t>
+        </is>
+      </c>
+      <c r="E1326" t="inlineStr">
+        <is>
+          <t>Wakil Ketua Komisi II DPR RI, Bahtra Banong, raih detiktimur Awards 2026 sebagai Legislator Aspiratif. Ia fokus pada keadilan sosial dan agraria di Indonesia.</t>
+        </is>
+      </c>
+      <c r="F1326" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1326" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609313/bahtra-banong-raih-legislator-aspiratif-bidang-keadilan-sosial-agraria-detiktimur-awards-2026</t>
+        </is>
+      </c>
+      <c r="H1326" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/detiktimur-awards-bahtra-banong-1786111191099_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1326" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1327" t="inlineStr">
+        <is>
+          <t>Rudianto Lallo Dianugerahi detiktimur Awards 2026 'Legislator Pengawal Supremasi Hukum'</t>
+        </is>
+      </c>
+      <c r="C1327" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:46:46 +0700</t>
+        </is>
+      </c>
+      <c r="D1327" t="inlineStr">
+        <is>
+          <t>Syachrul Arsyad</t>
+        </is>
+      </c>
+      <c r="E1327" t="inlineStr">
+        <is>
+          <t>Anggota DPR Rudianto Lallo menerima detiktimur Awards 2026 sebagai Legislator Pengawal Supremasi Hukum atas dedikasinya memberikan bantuan hukum ke masyarakat.</t>
+        </is>
+      </c>
+      <c r="F1327" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1327" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609309/rudianto-lallo-dianugerahi-detiktimur-awards-2026-legislator-pengawal-supremasi-hukum</t>
+        </is>
+      </c>
+      <c r="H1327" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/detiktimur-awards-rudianto-lallo-1786110858616_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1327" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1328" t="inlineStr">
+        <is>
+          <t>Cerita Local Hero Pertamina Bangun Kemandirian Energi Desa</t>
+        </is>
+      </c>
+      <c r="C1328" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:34:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1328" t="inlineStr">
+        <is>
+          <t>Annisa Sekar Melati</t>
+        </is>
+      </c>
+      <c r="E1328" t="inlineStr">
+        <is>
+          <t>Alfredo dan Burhanudin, local hero Program Desa Energi Berdikari, membawa perubahan dengan akses air bersih dan energi terbarukan.</t>
+        </is>
+      </c>
+      <c r="F1328" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1328" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609294/cerita-local-hero-pertamina-bangun-kemandirian-energi-desa</t>
+        </is>
+      </c>
+      <c r="H1328" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/pertamina-1786116722039.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1328" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1329" t="inlineStr">
+        <is>
+          <t>Gedung Bapenda DKI di Gambir Jakpus Kebakaran</t>
+        </is>
+      </c>
+      <c r="C1329" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:33:38 +0700</t>
+        </is>
+      </c>
+      <c r="D1329" t="inlineStr">
+        <is>
+          <t>Rolando Fransiscus Sihombing</t>
+        </is>
+      </c>
+      <c r="E1329" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda gedung Bapenda DKI Jakarta. Personel damkar masih berupaya memadamkan api. Penyebab dan korban belum diketahui.</t>
+        </is>
+      </c>
+      <c r="F1329" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1329" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609292/gedung-bapenda-dki-di-gambir-jakpus-kebakaran</t>
+        </is>
+      </c>
+      <c r="H1329" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2024/11/13/ilustrasi-api_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1329" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="B1330" t="inlineStr">
+        <is>
+          <t>Danantara Gandeng JBS Perkuat Investasi Sektor Protein Indonesia</t>
+        </is>
+      </c>
+      <c r="C1330" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:46:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1330" t="inlineStr">
+        <is>
+          <t>Inkana Putri</t>
+        </is>
+      </c>
+      <c r="E1330" t="inlineStr">
+        <is>
+          <t>Danantara menjalin kemitraan dengan JBS Group, investasi US$ 2,5 miliar untuk 25% kepemilikan di JV Australia dan Selandia Baru, mendukung sektor protein.</t>
+        </is>
+      </c>
+      <c r="F1330" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1330" t="inlineStr">
+        <is>
+          <t>https://finance.detik.com/berita-ekonomi-bisnis/d-8609310/danantara-gandeng-jbs-perkuat-investasi-sektor-protein-indonesia</t>
+        </is>
+      </c>
+      <c r="H1330" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/06/30/wisma-danantara-indonesia-1751283332958_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1330" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1331" t="inlineStr">
+        <is>
+          <t>Marcos Tjung Garap Video Klip Warna Warni Indonesia Sehari: Luar Biasa</t>
+        </is>
+      </c>
+      <c r="C1331" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:30:48 +0700</t>
+        </is>
+      </c>
+      <c r="D1331" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E1331" t="inlineStr">
+        <is>
+          <t>Video klip Warna Warni Indonesia garapan Marcos Tjung melibatkan delapan penyanyi top. Lagu ini merayakan keberagaman dan semangat persatuan Indonesia.</t>
+        </is>
+      </c>
+      <c r="F1331" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1331" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/music/d-8609289/marcos-tjung-garap-video-klip-warna-warni-indonesia-sehari-luar-biasa</t>
+        </is>
+      </c>
+      <c r="H1331" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/marcos-tjung-1786116589482_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1331" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1332" t="inlineStr">
+        <is>
+          <t>Arafah Rianti Terus Ekspansi Usaha Warnet-Rental PS</t>
+        </is>
+      </c>
+      <c r="C1332" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:02:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1332" t="inlineStr">
+        <is>
+          <t>Mauludi Rismoyo</t>
+        </is>
+      </c>
+      <c r="E1332" t="inlineStr">
+        <is>
+          <t>Artis Arafah Rianti hadir dengan kabar baru. Ia mengekspansi usaha warnet dan rental PS-nya.</t>
+        </is>
+      </c>
+      <c r="F1332" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1332" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608180/arafah-rianti-terus-ekspansi-usaha-warnet-rental-ps</t>
+        </is>
+      </c>
+      <c r="H1332" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/arafah-rianti-1786075896543_43.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1332" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" t="inlineStr">
+        <is>
+          <t>Hot</t>
+        </is>
+      </c>
+      <c r="B1333" t="inlineStr">
+        <is>
+          <t>Pengacara Asisten Nikita Mirzani Ungkap Pemicu Kekecewaan di Sidang PK TPPU</t>
+        </is>
+      </c>
+      <c r="C1333" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:01:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1333" t="inlineStr">
+        <is>
+          <t>Febryantino Nur Pratama</t>
+        </is>
+      </c>
+      <c r="E1333" t="inlineStr">
+        <is>
+          <t>Asisten Nikita Mirzani, Mail Syahputra, ajukan PK atas kasus pemerasan dan TPPU. Kuasa hukum ungkap pemicu kekecewaan dalam sidang.</t>
+        </is>
+      </c>
+      <c r="F1333" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1333" t="inlineStr">
+        <is>
+          <t>https://hot.detik.com/celeb/d-8608870/pengacara-asisten-nikita-mirzani-ungkap-pemicu-kekecewaan-di-sidang-pk-tppu</t>
+        </is>
+      </c>
+      <c r="H1333" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2025/07/24/nikita-mirzani-jalani-sidang-ttpu-1753328999091_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1333" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1334" t="inlineStr">
+        <is>
+          <t>Momen Api Karhutla Membara di Alun-Alun Suryakencana Gede Pangrango</t>
+        </is>
+      </c>
+      <c r="C1334" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:16:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1334" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1334" t="inlineStr">
+        <is>
+          <t>Kebakaran lahan melanda kawasan Alun-alun Suryakencana di Taman Nasional Gunung Gede Pangrango (TNGGP), Cianjur, Jawa Barat, Kamis (6/8).</t>
+        </is>
+      </c>
+      <c r="F1334" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1334" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807192715-24-1389919/momen-api-karhutla-membara-di-alun-alun-suryakencana-gede-pangrango</t>
+        </is>
+      </c>
+      <c r="H1334" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/api-lahap-alun-alun-suryakencana-diduga-akibat-kemarau-1786107276515_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1334" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1335" t="inlineStr">
+        <is>
+          <t>Gempa Laut Jawa Malam Ini: Guncangan Terasa di Jepara, Demak, Batang</t>
+        </is>
+      </c>
+      <c r="C1335" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:02:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1335" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1335" t="inlineStr">
+        <is>
+          <t>Gempa magnitudo 5,0 terjadi di Laut Jawa malam ini, tidak berpotensi tsunami. Guncangan dirasakan di Jepara dan Demak, hingga Batang.</t>
+        </is>
+      </c>
+      <c r="F1335" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1335" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807221317-20-1389978/gempa-laut-jawa-malam-ini-guncangan-terasa-di-jepara-demak-batang</t>
+        </is>
+      </c>
+      <c r="H1335" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2018/08/17/1db060af-1933-4880-a245-a4ff9edc6a81_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1335" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1336" t="inlineStr">
+        <is>
+          <t>100 Personel Dikerahkan Atasi Kebakaran Gedung Dinas Teknis Abdul Muis</t>
+        </is>
+      </c>
+      <c r="C1336" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:45:21 +0700</t>
+        </is>
+      </c>
+      <c r="D1336" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1336" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda Gedung Dinas Teknis Abdul Muis di Jakarta Pusat, J umat malam. 21 unit pemadam/100 personel dikerahkan untuk memadamkan api.</t>
+        </is>
+      </c>
+      <c r="F1336" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1336" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807223646-20-1389980/100-personel-dikerahkan-atasi-kebakaran-gedung-dinas-teknis-abdul-muis</t>
+        </is>
+      </c>
+      <c r="H1336" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2023/05/30/ilustrasi-kebakaran-5_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1336" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1337" t="inlineStr">
+        <is>
+          <t>UPDATE Kebakaran Gedung Bapenda DKI: Api Membesar di Lantai Paling Atas, Puing Berjatuhan</t>
+        </is>
+      </c>
+      <c r="C1337" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:29:02 +0700</t>
+        </is>
+      </c>
+      <c r="D1337" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1337" t="inlineStr">
+        <is>
+          <t>Gedung Badan Pendapatan Daerah(Bapenda) DKI Jakarta dilalap api pada Jumat(7/8/2026) malam.</t>
+        </is>
+      </c>
+      <c r="F1337" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1337" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7865541/update-kebakaran-gedung-bapenda-dki-api-membesar-di-lantai-paling-atas-puing-berjatuhan</t>
+        </is>
+      </c>
+      <c r="H1337" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/vCWaggZXVG9j8HCC3w7rBy8DrbY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kebakaran-di-gedung-bapenda-dki-jakarta.jpg</t>
+        </is>
+      </c>
+      <c r="I1337" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1338" t="inlineStr">
+        <is>
+          <t>Golkar Usul Jabatan Wakil Kepala Daerah Dihapus, Klaim Bisa Tekan Konflik dan Biaya Politik</t>
+        </is>
+      </c>
+      <c r="C1338" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:23:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1338" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1338" t="inlineStr">
+        <is>
+          <t>Golkar mengusulkan jabatan wakil kepala daerah dihapus dari Pilkada karena dinilai memicu konflik dan membebani biaya politik.</t>
+        </is>
+      </c>
+      <c r="F1338" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1338" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865540/golkar-usul-jabatan-wakil-kepala-daerah-dihapus-klaim-bisa-tekan-konflik-dan-biaya-politik</t>
+        </is>
+      </c>
+      <c r="H1338" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/n4f-DiF2fXuszFf1sIRByQSzGHY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Wakil-Ketua-Badan-Legislasi-Baleg-DPR-RI-Ahmad-Doli-Kurnia.jpg</t>
+        </is>
+      </c>
+      <c r="I1338" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1339" t="inlineStr">
+        <is>
+          <t>1.155 Mahasiswa Indonesia Kuliah di Thailand, Pilihan Studi di Asean Makin Beragam</t>
+        </is>
+      </c>
+      <c r="C1339" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:13:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1339" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1339" t="inlineStr">
+        <is>
+          <t>Sebanyak 1.155 mahasiswa Indonesia tercatat menempuh pendidikan di Thailand hingga 2025, menunjukkan semakin terbukanya pilihan studi.</t>
+        </is>
+      </c>
+      <c r="F1339" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1339" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/pendidikan/7865539/1155-mahasiswa-indonesia-kuliah-di-thailand-pilihan-studi-di-asean-makin-beragam</t>
+        </is>
+      </c>
+      <c r="H1339" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/ncXvUod70I_NWVHp9nPvrNhuX5Y=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/ilustrasi-mahasiswa-kuliah-di-luar-negeri.jpg</t>
+        </is>
+      </c>
+      <c r="I1339" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1340" t="inlineStr">
+        <is>
+          <t>Jadwal Semifinal Korea Masters 2026: Yuta/Maya Incar Back to Back Final, Malaysia Bidik Derbi</t>
+        </is>
+      </c>
+      <c r="C1340" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:10:48 +0700</t>
+        </is>
+      </c>
+      <c r="D1340" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1340" t="inlineStr">
+        <is>
+          <t>Semifinal Korea Masters 2026 menghadirkan misi berbeda dari Jepang, Malaysia, dan Korea Selatan untuk sama-sama lolos ke final.</t>
+        </is>
+      </c>
+      <c r="F1340" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1340" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7865538/jadwal-semifinal-korea-masters-2026-yutamaya-incar-back-to-back-final-malaysia-bidik-derbi</t>
+        </is>
+      </c>
+      <c r="H1340" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/kCgeNAywY4bB7c1l4koRAi22PfE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/profil-maya-taguchi-tandem-anyar-yuta-watanabe-di-sektor-ganda-campuran-jepang.jpg</t>
+        </is>
+      </c>
+      <c r="I1340" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1341" t="inlineStr">
+        <is>
+          <t>Lika Liku Perjalanan Joanna di Modeling dan Mimpinya Mengangkat Identitas Indonesia ke Kancah Global</t>
+        </is>
+      </c>
+      <c r="C1341" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:08:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1341" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1341" t="inlineStr">
+        <is>
+          <t>Jejak modeling Indonesia dari pionir Non Kawilarang hingga generasi baru Joanna Adelaide yang membawa identitas lokal ke global.</t>
+        </is>
+      </c>
+      <c r="F1341" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1341" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865537/lika-liku-perjalanan-joanna-di-modeling-dan-mimpinya-mengangkat-identitas-indonesia-ke-kancah-global</t>
+        </is>
+      </c>
+      <c r="H1341" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/u1YW2Lk8dlDoOyAzBtxIln7NMOc=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/momen-menteri-dan-istri-pejabat-negara-catwalk-di-istana-berkebaya_20230806_210137.jpg</t>
+        </is>
+      </c>
+      <c r="I1341" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1342" t="inlineStr">
+        <is>
+          <t>Idrus Marham Nilai Kabinet Bayangan Bagian dari Dinamika Demokrasi</t>
+        </is>
+      </c>
+      <c r="C1342" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:07:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1342" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1342" t="inlineStr">
+        <is>
+          <t>Idrus Marham menilai pembentukan Kabinet Bayangan oleh koalisi masyarakat sipil merupakan bagian dari dinamika demokrasi dan hak warga.</t>
+        </is>
+      </c>
+      <c r="F1342" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1342" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865536/idrus-marham-nilai-kabinet-bayangan-bagian-dari-dinamika-demokrasi</t>
+        </is>
+      </c>
+      <c r="H1342" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/fEQ4y2P9_Tdpmm4P3Yndltf76PE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/wawancara-khusus-ketua-dewan-pembina-bappilu-golkar-idrus-marham_20240809_114219.jpg</t>
+        </is>
+      </c>
+      <c r="I1342" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1343" t="inlineStr">
+        <is>
+          <t>Pengamat Politik Unas: Publik Ingin Jangan Ada Pihak yang 'Dilindungi' dalam Kasus Eks Jampidsus</t>
+        </is>
+      </c>
+      <c r="C1343" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:01:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1343" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1343" t="inlineStr">
+        <is>
+          <t>publik ingin kasus dugaan korupsi dan TPPU eks Jampidsus Febrie Adriansyah diusut tuntas tanpa ada pihak yang dilindungi.</t>
+        </is>
+      </c>
+      <c r="F1343" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1343" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865535/pengamat-politik-unas-publik-ingin-jangan-ada-pihak-yang-dilindungi-dalam-kasus-eks-jampidsus</t>
+        </is>
+      </c>
+      <c r="H1343" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/7nYnvNOC8BdbFnfyWZMwIUfCcqI=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/diskusi-bertajuk-1.jpg</t>
+        </is>
+      </c>
+      <c r="I1343" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1344" t="inlineStr">
+        <is>
+          <t>Kronologi Pria Bunuh Mantan Istri di Pekanbaru, Pelaku Bacok Wajah Korban Setelah Terlibat Cekcok</t>
+        </is>
+      </c>
+      <c r="C1344" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:52:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1344" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1344" t="inlineStr">
+        <is>
+          <t>Marhalim (64) membacok wajah mantan istrinya Rosdiana (55) hingga tewas di Tuah Madani, Kota Pekanbaru, Riau, Jumat (7/8/2026) pagi.</t>
+        </is>
+      </c>
+      <c r="F1344" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1344" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865534/kronologi-pria-bunuh-mantan-istri-di-pekanbaru-pelaku-bacok-wajah-korban-setelah-terlibat-cekcok</t>
+        </is>
+      </c>
+      <c r="H1344" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/0vnfr07ygtSQr0kVzLyuJpOqNYY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Ilustrasi-pembunuhan-wae-lah.jpg</t>
+        </is>
+      </c>
+      <c r="I1344" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1345" t="inlineStr">
+        <is>
+          <t>Wacana Pilkada Tanpa Wakil Berpotensi Jadi Pintu Masuk Pemilihan Lewat DPRD</t>
+        </is>
+      </c>
+      <c r="C1345" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:51:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1345" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1345" t="inlineStr">
+        <is>
+          <t>Usulan Pilkada tanpa wakil dinilai bukan sekadar perubahan teknis, tetapi berpotensi mengubah arah demokrasi daerah secara bertahap.</t>
+        </is>
+      </c>
+      <c r="F1345" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1345" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865533/wacana-pilkada-tanpa-wakil-berpotensi-jadi-pintu-masuk-pemilihan-lewat-dprd</t>
+        </is>
+      </c>
+      <c r="H1345" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/GZLuQllSU5AIAGFRMXJDUPrXhnQ=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Simulasi-Pemungutan-Suara-Pilgub-Jakarta_20241117_160050.jpg</t>
+        </is>
+      </c>
+      <c r="I1345" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1346" t="inlineStr">
+        <is>
+          <t>Apa Kita Benar-Benar Butuh Tidur 8 Jam?</t>
+        </is>
+      </c>
+      <c r="C1346" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:47:09 +0700</t>
+        </is>
+      </c>
+      <c r="D1346" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1346" t="inlineStr">
+        <is>
+          <t>Politisi atau CEO sering mengeklaim hanya punya sedikit waktu untuk tidur, bahkan hanya sempat tidur 3 jam di malam hari. Jika mereka…</t>
+        </is>
+      </c>
+      <c r="F1346" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1346" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7865532/apa-kita-benar-benar-butuh-tidur-8-jam</t>
+        </is>
+      </c>
+      <c r="H1346" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/qPKMk6l8QMnnSYy7E7E28OXgKDo=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/BDeutsche-Welle76146878_403.jpg.jpg</t>
+        </is>
+      </c>
+      <c r="I1346" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1347">
+      <c r="A1347" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1347" t="inlineStr">
+        <is>
+          <t>Pemulihan Ekosistem Laut Bali Barat Diharapkan Dukung Pariwisata Pesisir</t>
+        </is>
+      </c>
+      <c r="C1347" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:46:37 +0700</t>
+        </is>
+      </c>
+      <c r="D1347" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1347" t="inlineStr">
+        <is>
+          <t>struktur fisik terumbu karang di laut Bali Barat yang mengalami kerusakan direhabilitasi guna mengembalikan habitat alami.</t>
+        </is>
+      </c>
+      <c r="F1347" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1347" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865531/pemulihan-ekosistem-laut-bali-barat-diharapkan-dukung-pariwisata-pesisir</t>
+        </is>
+      </c>
+      <c r="H1347" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/L1ie-WMdsyx4zIzhCDrtJEx2g_E=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/dca-bantu-ekosistem.jpg</t>
+        </is>
+      </c>
+      <c r="I1347" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1348">
+      <c r="A1348" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1348" t="inlineStr">
+        <is>
+          <t>BREAKING NEWS Gedung Bapenda DKI Jakarta Terbakar, Api dan Asap Hitam Membumbung Tinggi</t>
+        </is>
+      </c>
+      <c r="C1348" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:40:27 +0700</t>
+        </is>
+      </c>
+      <c r="D1348" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1348" t="inlineStr">
+        <is>
+          <t>Kebakaran melanda gedung Badan Pendapatan Daerah (Bapenda) DKI Jakarta di Jalan Abdul Muis, Petojo.</t>
+        </is>
+      </c>
+      <c r="F1348" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1348" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7865530/breaking-news-gedung-bapenda-dki-jakarta-terbakar-api-dan-asap-hitam-membumbung-tinggi</t>
+        </is>
+      </c>
+      <c r="H1348" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/3nU5duk4s3XXHJSRQYafr_rV9FE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kebakaran-di-gedung-bapenda-dki.jpg</t>
+        </is>
+      </c>
+      <c r="I1348" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1349">
+      <c r="A1349" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1349" t="inlineStr">
+        <is>
+          <t>Krisis Kemanusiaan Palestina Makin Dalam, 300 Anak Tewas di Gaza</t>
+        </is>
+      </c>
+      <c r="C1349" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:39:48 +0700</t>
+        </is>
+      </c>
+      <c r="D1349" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1349" t="inlineStr">
+        <is>
+          <t>UNICEF mencatat 300 anak tewas di Gaza dalam 300 hari. Di Tepi Barat, serangan pemukim dan penutupan akses terus menambah krisis</t>
+        </is>
+      </c>
+      <c r="F1349" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1349" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7865529/krisis-kemanusiaan-palestina-makin-dalam-300-anak-tewas-di-gaza</t>
+        </is>
+      </c>
+      <c r="H1349" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Ztk0o1a2h3t-EQaaVSlhpEUMm14=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/bocah-berusia-13-tahun-dari-Kota-Gaza-yang.jpg</t>
+        </is>
+      </c>
+      <c r="I1349" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1350">
+      <c r="A1350" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1350" t="inlineStr">
+        <is>
+          <t>Klasemen Akhir Grup A Piala AFF 2026: Kegagalan ke-6 Timnas Indonesia Melaju ke Semifinal</t>
+        </is>
+      </c>
+      <c r="C1350" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:38:55 +0700</t>
+        </is>
+      </c>
+      <c r="D1350" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1350" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia gagal ke semifinal Piala AFF 2026 setelah ditahan Singapura 1-1 dan finis di peringkat ketiga Grup A dengan 7 poin.</t>
+        </is>
+      </c>
+      <c r="F1350" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1350" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7865528/klasemen-akhir-grup-a-piala-aff-2026-kegagalan-ke-6-timnas-indonesia-melaju-ke-semifinal</t>
+        </is>
+      </c>
+      <c r="H1350" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/1a7ILPPDpySjbwe7SeQea4Z15Rg=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Timnas-Indonesia-Dicukur-Timnas-Vietnam-3-0_20260804_065849.jpg</t>
+        </is>
+      </c>
+      <c r="I1350" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1351">
+      <c r="A1351" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1351" t="inlineStr">
+        <is>
+          <t>Exam Concert Jadi Pelepas Penat usai Ujian, Yovie dan Nuno Hibur Mahasiswa Budi Luhur University</t>
+        </is>
+      </c>
+      <c r="C1351" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:25:04 +0700</t>
+        </is>
+      </c>
+      <c r="D1351" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1351" t="inlineStr">
+        <is>
+          <t>After Exam Concert dengan line up Yovie &amp; Nuno digelar untuk menjaga keseimbangan akademis dan kesehatan mental mahasiswa.</t>
+        </is>
+      </c>
+      <c r="F1351" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1351" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/seleb/7865527/exam-concert-jadi-pelepas-penat-usai-ujian-yovie-nuno-hibur-mahasiswa-budi-luhur-university</t>
+        </is>
+      </c>
+      <c r="H1351" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/1QPTDghBoKYDEzDSOlMPsaaK9b0=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Yovie-Nuno-1234.jpg</t>
+        </is>
+      </c>
+      <c r="I1351" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1352">
+      <c r="A1352" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1352" t="inlineStr">
+        <is>
+          <t>Klaim Kriminalisasi Febrie Adriansyah Dinilai Wajar, Pakar Hukum: Dulu Kerap Lakukan Hal Serupa</t>
+        </is>
+      </c>
+      <c r="C1352" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:13:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1352" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1352" t="inlineStr">
+        <is>
+          <t>Pakar Hukum UMJ Chairul Huda menilai pernyataan Febrie Adriansyah yang mengaku dikriminalisasi merupakan hal yang wajar disampaikan.</t>
+        </is>
+      </c>
+      <c r="F1352" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1352" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865526/klaim-kriminalisasi-febrie-adriansyah-dinilai-wajar-pakar-hukum-dulu-kerap-lakukan-hal-serupa</t>
+        </is>
+      </c>
+      <c r="H1352" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/Z8LfULQiAjAelAU76TuRVZDVlnY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Febrie-Adriansyah-Jalani-Pemeriksaan-Lanjutan-Kasus-TPPU_20260807_134518.jpg</t>
+        </is>
+      </c>
+      <c r="I1352" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1353">
+      <c r="A1353" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1353" t="inlineStr">
+        <is>
+          <t>Mobil Terjun ke Jurang 250 Meter di India, Lima Orang Tewas Termasuk Balita</t>
+        </is>
+      </c>
+      <c r="C1353" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:12:31 +0700</t>
+        </is>
+      </c>
+      <c r="D1353" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1353" t="inlineStr">
+        <is>
+          <t>Lima orang tewas setelah mobil Bolero terjun ke jurang sedalam hampir 250 meter di Uttarakhand India.</t>
+        </is>
+      </c>
+      <c r="F1353" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1353" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/internasional/7865525/mobil-terjun-ke-jurang-250-meter-di-india-lima-orang-tewas-termasuk-balita</t>
+        </is>
+      </c>
+      <c r="H1353" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/fye_UtxGjhYnqU3NPrNAQhorVCE=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/lakalatasindia22222.jpg</t>
+        </is>
+      </c>
+      <c r="I1353" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1354">
+      <c r="A1354" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1354" t="inlineStr">
+        <is>
+          <t>Eks Penyidik KPK Nilai Kasus Dugaan Korupsi dan TPPU Eks Jampidsus Perlu Dikembangkan ke Segala Arah</t>
+        </is>
+      </c>
+      <c r="C1354" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:04:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1354" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1354" t="inlineStr">
+        <is>
+          <t>Mantan Penyidik KPK Yudi Purnomo Harahap menilai kasus dugaan korupsi dan TPPU yang menjerat eks Jampidsus Febrie Adriansyah perlu dikembangkan.</t>
+        </is>
+      </c>
+      <c r="F1354" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1354" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865524/eks-penyidik-kpk-nilai-kasus-dugaan-korupsi-dan-tppu-eks-jampidsus-perlu-dikembangkan-ke-segala-arah</t>
+        </is>
+      </c>
+      <c r="H1354" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/8OfEROsNAENYYSUhKhNzr11IIxM=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/diskusi-mencari-aktor-di-balik.jpg</t>
+        </is>
+      </c>
+      <c r="I1354" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1355">
+      <c r="A1355" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1355" t="inlineStr">
+        <is>
+          <t>Niat Bayar COD Rp93 Ribu, Wanita di Palembang Salah Transfer Rp93 Juta, Uangnya Dihabiskan Kurir</t>
+        </is>
+      </c>
+      <c r="C1355" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:02:36 +0700</t>
+        </is>
+      </c>
+      <c r="D1355" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1355" t="inlineStr">
+        <is>
+          <t>NI seharusnya Rp93 ribu, namun justru mengirim uang sebesar Rp93 juta. Nahas, uang tersebut tidak dikembalikan oleh kurir paket.</t>
+        </is>
+      </c>
+      <c r="F1355" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1355" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865523/niat-bayar-cod-rp93-ribu-wanita-di-palembang-salah-transfer-rp93-juta-uangnya-dihabiskan-kurir</t>
+        </is>
+      </c>
+      <c r="H1355" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/jUb25Pvl71aBZZHrea6vweJM08g=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/DITAHAN-Kurir-paket.jpg</t>
+        </is>
+      </c>
+      <c r="I1355" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1356">
+      <c r="A1356" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1356" t="inlineStr">
+        <is>
+          <t>Hasil Akhir Timnas Indonesia vs Singapura 1-1: Wasit Kontroversi, Skuad Garuda Gagal ke Semifinal</t>
+        </is>
+      </c>
+      <c r="C1356" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:58:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1356" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1356" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia gagal ke semifinal Piala AFF 2026 seusai ditahan imbang Singapura 1-1 yang diwarnai kontroversi wasit asal Oman.</t>
+        </is>
+      </c>
+      <c r="F1356" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1356" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/superskor/7865522/hasil-akhir-timnas-indonesia-vs-singapura-1-1-wasit-kontroversi-skuad-garuda-gagal-ke-semifinal</t>
+        </is>
+      </c>
+      <c r="H1356" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/tZqFKgwVQ5eW_YBK_O5n7jSWMXA=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Timnas-Indonesia-Dicukur-Timnas-Vietnam-3-0_20260804_065938.jpg</t>
+        </is>
+      </c>
+      <c r="I1356" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1357">
+      <c r="A1357" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1357" t="inlineStr">
+        <is>
+          <t>Enam Jam Pemeriksaan Eks Jampidsus Febrie Adriansyah</t>
+        </is>
+      </c>
+      <c r="C1357" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:25:19 +0700</t>
+        </is>
+      </c>
+      <c r="D1357" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1357" t="inlineStr">
+        <is>
+          <t>Kuasa hukum menyebut Febrie Adriansyah kooperatif saat diperiksa dan akan menghadirkan saksi meringankan.</t>
+        </is>
+      </c>
+      <c r="F1357" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1357" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264718/enam-jam-pemeriksaan-eks-jampidsus-febrie-adriansyah</t>
+        </is>
+      </c>
+      <c r="H1357" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/2WEvQ2hmLFTijz9iyBipOx1Njqg=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318624/original/089072000_1786113401-IMG_3067.jpg</t>
+        </is>
+      </c>
+      <c r="I1357" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1358">
+      <c r="A1358" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1358" t="inlineStr">
+        <is>
+          <t>Penampakan Febrie Adriansyah Usai Diperiksa Tim 9 Kejagung</t>
+        </is>
+      </c>
+      <c r="C1358" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:11:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1358" t="inlineStr">
+        <is>
+          <t>Liputan6.com</t>
+        </is>
+      </c>
+      <c r="E1358" t="inlineStr">
+        <is>
+          <t>Febrie meninggalkan ruang pemeriksaan sekitar pukul 20.30 WIB. Ia langsung menuju mobil tahanan.</t>
+        </is>
+      </c>
+      <c r="F1358" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1358" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/news/read/8264672/penampakan-febrie-adriansyah-usai-diperiksa-tim-9-kejagung</t>
+        </is>
+      </c>
+      <c r="H1358" t="inlineStr">
+        <is>
+          <t>https://cdn1-production-images-kly.akamaized.net/sp4SqvNV_83npEChYsHfHfViHdc=/673x379/smart/filters:quality(75):strip_icc():format(webp)/kly-media-production/medias/9318625/original/014147200_1786113402-IMG_3066.jpg</t>
+        </is>
+      </c>
+      <c r="I1358" t="inlineStr">
+        <is>
+          <t>Liputan6</t>
+        </is>
+      </c>
+    </row>
+    <row r="1359">
+      <c r="A1359" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1359" t="inlineStr">
+        <is>
+          <t>Warga Dengar 2 Ledakan Saat Kebakaran Gedung Bapenda Jakarta, Sempat Dikira dari SPBU</t>
+        </is>
+      </c>
+      <c r="C1359" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:44:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1359" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1359" t="inlineStr">
+        <is>
+          <t>Warga sempat mendengar dua ledakan saat Gedung Bapenda kebakaran pada Jumat (7/8/2026) malam.</t>
+        </is>
+      </c>
+      <c r="F1359" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1359" t="inlineStr">
+        <is>
+          <t>https://megapolitan.kompas.com/read/2026/08/07/23404371/warga-dengar-2-ledakan-saat-kebakaran-gedung-bapenda-jakarta-sempat</t>
+        </is>
+      </c>
+      <c r="H1359" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/Xam7pd5ZbVyKKyx4Een4EDcC8v4=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c815a5f0b9.png,0,-0,1)/data/photo/2026/08/07/6a7608c1eab96.jpg</t>
+        </is>
+      </c>
+      <c r="I1359" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1360">
+      <c r="A1360" t="inlineStr">
+        <is>
+          <t>Hype</t>
+        </is>
+      </c>
+      <c r="B1360" t="inlineStr">
+        <is>
+          <t>Film Baby Udon: Sinopsis, Daftar Pemain, dan Jadwal Tayang</t>
+        </is>
+      </c>
+      <c r="C1360" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:44:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1360" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1360" t="inlineStr">
+        <is>
+          <t>Film Baby Udon, kisah nyata selebgram Fanny Kondoh dan mendiang suaminya Hajime, segera tayang. Mengangkat perjuangan IVF dan keteguhan hati Fanny.</t>
+        </is>
+      </c>
+      <c r="F1360" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1360" t="inlineStr">
+        <is>
+          <t>https://www.kompas.com/hype/read/2026/08/07/225112166/film-baby-udon-sinopsis-daftar-pemain-dan-jadwal-tayang</t>
+        </is>
+      </c>
+      <c r="H1360" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/SR2u2g8xxO6xNGB-48QQaa9Rqeo=/0x0:0x0/1200x675/filters:watermark(data/photo/2026/01/30/697c8191ee571.png,0,-0,1)/data/photo/2026/01/22/6971a80934093.jpg</t>
+        </is>
+      </c>
+      <c r="I1360" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
+    <row r="1361">
+      <c r="A1361" t="inlineStr">
+        <is>
+          <t>Bola</t>
+        </is>
+      </c>
+      <c r="B1361" t="inlineStr">
+        <is>
+          <t>Permintaan Maaf Rizky Ridho kepada Suporter Usai Timnas Indonesia Gagal Lolos dari Fase Grup Piala AFF</t>
+        </is>
+      </c>
+      <c r="C1361" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:44:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1361" t="inlineStr">
+        <is>
+          <t>Kompas Cyber Media</t>
+        </is>
+      </c>
+      <c r="E1361" t="inlineStr">
+        <is>
+          <t>Timnas Indonesia harus memupus mimpi untuk menyudahi dahaga gelar juara di Piala AFF.</t>
+        </is>
+      </c>
+      <c r="F1361" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1361" t="inlineStr">
+        <is>
+          <t>https://bola.kompas.com/read/2026/08/07/22212338/permintaan-maaf-rizky-ridho-kepada-suporter-usai-timnas-indonesia-gagal-lolos</t>
+        </is>
+      </c>
+      <c r="H1361" t="inlineStr">
+        <is>
+          <t>https://asset.kompas.com/crops/TEBkzl24l2b4Mn3aThNjri6hlKU=/500x334:4500x3000/1200x675/filters:watermark(data/photo/2026/01/30/697c8163c3944.png,0,-0,1)/data/photo/2026/07/27/6a678dab0ec5a.jpg</t>
+        </is>
+      </c>
+      <c r="I1361" t="inlineStr">
+        <is>
+          <t>Kompas</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1295"/>
+  <autoFilter ref="A1:I1361"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-07.xlsx
+++ b/data/berita_2026-08-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1361</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1373</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1361"/>
+  <dimension ref="A1:I1373"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -64400,8 +64400,572 @@
         </is>
       </c>
     </row>
+    <row r="1362">
+      <c r="A1362" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1362" t="inlineStr">
+        <is>
+          <t>Api Masih Berkobar di Gedung Bapenda DKI, Asap Hitam Membubung</t>
+        </is>
+      </c>
+      <c r="C1362" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:56:19 +0700</t>
+        </is>
+      </c>
+      <c r="D1362" t="inlineStr">
+        <is>
+          <t>Rolando Fransiscus Sihombing</t>
+        </is>
+      </c>
+      <c r="E1362" t="inlineStr">
+        <is>
+          <t>Gedung Bapenda DKI Jakarta di kawasan Gambir, Jakarta Pusat kebakaran. Hingga tengah malam ini api masih berkobar.</t>
+        </is>
+      </c>
+      <c r="F1362" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1362" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609350/api-masih-berkobar-di-gedung-bapenda-dki-asap-hitam-membubung</t>
+        </is>
+      </c>
+      <c r="H1362" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2026/08/07/kebakaran-gedung-bapenda-dki-jakarta-rolandodetikcom-1786121738496_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1362" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1363">
+      <c r="A1363" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1363" t="inlineStr">
+        <is>
+          <t>Daniel Johan Raih detiktimur Awards 2026 'Legislator Benteng Nelayan dan Petani'</t>
+        </is>
+      </c>
+      <c r="C1363" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:41:08 +0700</t>
+        </is>
+      </c>
+      <c r="D1363" t="inlineStr">
+        <is>
+          <t>Andi Sitti Nurfaisah</t>
+        </is>
+      </c>
+      <c r="E1363" t="inlineStr">
+        <is>
+          <t>Anggota DPR Daniel Johan meraih detiktimur Awards 2026 sebagai Legislator Benteng Nelayan dan Petani atas dedikasinya dalam memperjuangkan kesejahteraan petani.</t>
+        </is>
+      </c>
+      <c r="F1363" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1363" t="inlineStr">
+        <is>
+          <t>https://news.detik.com/berita/d-8609342/daniel-johan-raih-detiktimur-awards-2026-legislator-benteng-nelayan-dan-petani</t>
+        </is>
+      </c>
+      <c r="H1363" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/community/media/visual/2023/12/22/ketua-dpp-pkb-daniel-johan-tangkapan-layar_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1363" t="inlineStr">
+        <is>
+          <t>Detik</t>
+        </is>
+      </c>
+    </row>
+    <row r="1364">
+      <c r="A1364" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1364" t="inlineStr">
+        <is>
+          <t>Kecelakaan Maut di Lampu Merah, Mobil Polisi Bone Diklaim Rem Blong</t>
+        </is>
+      </c>
+      <c r="C1364" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:45:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1364" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1364" t="inlineStr">
+        <is>
+          <t>Kecelakaan tragis di Bone, mobil Ipda MA menabrak motor dan menewaskan balita usai menerobos lampu merah. Dari pemeriksaan Satlantas disebut rem mobil blong.</t>
+        </is>
+      </c>
+      <c r="F1364" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1364" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807160623-12-1389802/kecelakaan-maut-di-lampu-merah-mobil-polisi-bone-diklaim-rem-blong</t>
+        </is>
+      </c>
+      <c r="H1364" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2019/09/14/5cf965a3-c769-46ef-a4b8-ca0c095cfd58_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1364" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1365">
+      <c r="A1365" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1365" t="inlineStr">
+        <is>
+          <t>Gedung Bapenda DKI Kebakaran, 100 Personel Damkar Dikerahkan</t>
+        </is>
+      </c>
+      <c r="C1365" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:45:51 +0700</t>
+        </is>
+      </c>
+      <c r="D1365" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1365" t="inlineStr">
+        <is>
+          <t>Gedung Badan Pendapatan Daerah (Bapenda) DKI Jakarta mengalami kebakaran pada Jumat (7/8) malam. Dikutip dari Detik, sebanyak 100 personel Damkar dikerahkan.</t>
+        </is>
+      </c>
+      <c r="F1365" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1365" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807233808-20-1389985/gedung-bapenda-dki-kebakaran-100-personel-damkar-dikerahkan</t>
+        </is>
+      </c>
+      <c r="H1365" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/03/30/ilustrasi-ledakan-3_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1365" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1366">
+      <c r="A1366" t="inlineStr">
+        <is>
+          <t>Nasional</t>
+        </is>
+      </c>
+      <c r="B1366" t="inlineStr">
+        <is>
+          <t>Ada 995 Senjata di Sekolah, DPR Curiga Jaringan Manfaatkan Pendidikan</t>
+        </is>
+      </c>
+      <c r="C1366" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:40:06 +0700</t>
+        </is>
+      </c>
+      <c r="D1366" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1366" t="inlineStr">
+        <is>
+          <t>Anggota DPR Soedeson Tandra mendesak polisi usut tuntas temuan 995 senjata dan narkoba di sekolah swasta. Ia khawatir ada jaringan kejahatan di baliknya.</t>
+        </is>
+      </c>
+      <c r="F1366" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1366" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/nasional/20260807160119-12-1389800/ada-995-senjata-di-sekolah-dpr-curiga-jaringan-manfaatkan-pendidikan</t>
+        </is>
+      </c>
+      <c r="H1366" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/995-senjata-yang-ditemukan-di-ruang-mantan-ketua-yayasan-sekolah-jaksel-1786011308187_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1366" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1367">
+      <c r="A1367" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1367" t="inlineStr">
+        <is>
+          <t>Pria Berkostum Grim Reaper Manjat Atap RS Bikin Panik Pasien</t>
+        </is>
+      </c>
+      <c r="C1367" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:00:22 +0700</t>
+        </is>
+      </c>
+      <c r="D1367" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1367" t="inlineStr">
+        <is>
+          <t>Seorang pria dari Deganwy, Wales, ditangkap dan didenda usai membuat panik pasien rumah sakit karena mengenakan kostum Grim Reaper atau malaikat maut.</t>
+        </is>
+      </c>
+      <c r="F1367" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1367" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260806193238-134-1389472/pria-berkostum-grim-reaper-manjat-atap-rs-bikin-panik-pasien</t>
+        </is>
+      </c>
+      <c r="H1367" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/06/germany-economy-industry-automobile-layoffs-unions-protest-1786020097027_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1367" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1368">
+      <c r="A1368" t="inlineStr">
+        <is>
+          <t>Internasional</t>
+        </is>
+      </c>
+      <c r="B1368" t="inlineStr">
+        <is>
+          <t>Mau Dicaplok Trump, Belgia Ikut Kirim Pasukan ke Greenland</t>
+        </is>
+      </c>
+      <c r="C1368" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:05:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1368" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1368" t="inlineStr">
+        <is>
+          <t>Belgia ikut mengirim pasukan mereka ke Pulau Greenland sebagai bagian dari misi Pakta Pertahanan Atlantik Utara (NATO).</t>
+        </is>
+      </c>
+      <c r="F1368" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1368" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/internasional/20260807200752-134-1389937/mau-dicaplok-trump-belgia-ikut-kirim-pasukan-ke-greenland</t>
+        </is>
+      </c>
+      <c r="H1368" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/01/20/trump-kirim-pesawat-militer-ke-greenland-tentara-denmark-siaga-invasi-1768879805860_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1368" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1369">
+      <c r="A1369" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1369" t="inlineStr">
+        <is>
+          <t>Tak Lagi Sekadar Busana, Kebaya Kini Bisa Jadi Pesan Pelestarian Alam dan Budaya</t>
+        </is>
+      </c>
+      <c r="C1369" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:59:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1369" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1369" t="inlineStr">
+        <is>
+          <t>Kebaya Adhikari hadir di IFW 2026, memadukan identitas budaya, Bundengan, dan konservasi gajah dalam narasi pelestarian.</t>
+        </is>
+      </c>
+      <c r="F1369" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1369" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/regional/7865546/tak-lagi-sekadar-busana-kebaya-kini-bisa-jadi-pesan-pelestarian-alam-dan-budaya</t>
+        </is>
+      </c>
+      <c r="H1369" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/fVPdaKLg4RsCBRsIJP77MhxGv3k=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Tren-kebaya-tak-hanya-sekedar-busana.jpg</t>
+        </is>
+      </c>
+      <c r="I1369" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1370">
+      <c r="A1370" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1370" t="inlineStr">
+        <is>
+          <t>Bukan Cuma Lari, Pancasakti Run 2026 Suntik Rp18 Miliar ke Ekonomi Banten</t>
+        </is>
+      </c>
+      <c r="C1370" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:52:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1370" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1370" t="inlineStr">
+        <is>
+          <t>Perhelatan olahraga berbasis sport tourism makin terbukti ampuh menggerakkan roda ekonomi daerah.</t>
+        </is>
+      </c>
+      <c r="F1370" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1370" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/sport/7865545/bukan-cuma-lari-pancasakti-run-2026-suntik-rp18-miliar-ke-ekonomi-banten</t>
+        </is>
+      </c>
+      <c r="H1370" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/v3Dn2RmgA5zl6T6FhI0HV_ZARMU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Mantan-Gubernur-DKI-Basuki-Tjahaja-Purnama-alias-Ahok.jpg</t>
+        </is>
+      </c>
+      <c r="I1370" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1371">
+      <c r="A1371" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1371" t="inlineStr">
+        <is>
+          <t>Klarifikasi Kepala BGN soal Ucapan Makan Telur Bikin Bisulan: Memang Saya Sengaja</t>
+        </is>
+      </c>
+      <c r="C1371" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:50:14 +0700</t>
+        </is>
+      </c>
+      <c r="D1371" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1371" t="inlineStr">
+        <is>
+          <t>Kepala BGN Sudaryono ungkap alasan di balik ucapan telur bikin bisul yang menuai kritik dan sebut sengaja memancing edukasi gizi.</t>
+        </is>
+      </c>
+      <c r="F1371" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1371" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865544/klarifikasi-kepala-bgn-soal-ucapan-makan-telur-bikin-bisulan-memang-saya-sengaja</t>
+        </is>
+      </c>
+      <c r="H1371" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/fupn177hoCNSBh0082fDnbmrJfs=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Sudaryono-MBG-Kepala-BGN.jpg</t>
+        </is>
+      </c>
+      <c r="I1371" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1372">
+      <c r="A1372" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1372" t="inlineStr">
+        <is>
+          <t>Gedung Bapenda DKI Terbakar, Api Diduga Berasal dari Lantai 11</t>
+        </is>
+      </c>
+      <c r="C1372" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:48:13 +0700</t>
+        </is>
+      </c>
+      <c r="D1372" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1372" t="inlineStr">
+        <is>
+          <t>Informasi yang diterima Tribun api pertama kali muncul dari lantai 11 gedung Bapenda DKI Jakarta.</t>
+        </is>
+      </c>
+      <c r="F1372" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1372" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/metropolitan/7865543/gedung-bapenda-dki-terbakar-api-diduga-berasal-dari-lantai-11</t>
+        </is>
+      </c>
+      <c r="H1372" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/RHt7QpX6GbddeeJDO8EDZujKiDY=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/kebakaran-gedung-bapenda-dki-jakarta.jpg</t>
+        </is>
+      </c>
+      <c r="I1372" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
+    <row r="1373">
+      <c r="A1373" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1373" t="inlineStr">
+        <is>
+          <t>Dua Dekade Dinamika BLBI, Verifikasi Data Objektif Dinilai Jadi Kunci Optimalisasi Aset</t>
+        </is>
+      </c>
+      <c r="C1373" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:35:41 +0700</t>
+        </is>
+      </c>
+      <c r="D1373" t="inlineStr">
+        <is>
+          <t>Redaksi Tribunnews</t>
+        </is>
+      </c>
+      <c r="E1373" t="inlineStr">
+        <is>
+          <t>Kasus BLBI yang bergulir lebih dari dua dekade tetap menjadi sorotan karena menyangkut pemulihan aset keuangan negara.</t>
+        </is>
+      </c>
+      <c r="F1373" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1373" t="inlineStr">
+        <is>
+          <t>https://www.tribunnews.com/nasional/7865542/dua-dekade-dinamika-blbi-verifikasi-data-objektif-dinilai-jadi-kunci-optimalisasi-aset</t>
+        </is>
+      </c>
+      <c r="H1373" t="inlineStr">
+        <is>
+          <t>https://asset.tribunnews.com/1iVKAATZm8TQbSOeeRvmwqrYkvU=/148x99/filters:quality(30):format(webp):focal(0.5x0.5:0.5x0.5)/tribunnews/foto/bank/originals/Menteri-Purbaya-bahas-perekonomian-RI-OK.jpg</t>
+        </is>
+      </c>
+      <c r="I1373" t="inlineStr">
+        <is>
+          <t>Tribunnews</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1361"/>
+  <autoFilter ref="A1:I1373"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-07.xlsx
+++ b/data/berita_2026-08-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1373</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1395</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1373"/>
+  <dimension ref="A1:I1395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -64964,8 +64964,1042 @@
         </is>
       </c>
     </row>
+    <row r="1374">
+      <c r="A1374" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1374" t="inlineStr">
+        <is>
+          <t>Aceh tunggu pasokan semen dari Jawa-Sumbar rekonstruksi pascabencana</t>
+        </is>
+      </c>
+      <c r="C1374" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:57:49 +0700</t>
+        </is>
+      </c>
+      <c r="D1374" t="inlineStr">
+        <is>
+          <t>Redaksi Antara</t>
+        </is>
+      </c>
+      <c r="E1374" t="inlineStr">
+        <is>
+          <t>ANTARA - Meningkatnya kebutuhan material untuk pembangunan rehabilitasi dan rekonstruksi pascabencana, memicu ...</t>
+        </is>
+      </c>
+      <c r="F1374" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1374" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/video/5685192/aceh-tunggu-pasokan-semen-dari-jawa-sumbar-rekonstruksi-pascabencana</t>
+        </is>
+      </c>
+      <c r="H1374" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/Screenshot-2026-08-07-233819_1.jpg</t>
+        </is>
+      </c>
+      <c r="I1374" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1375">
+      <c r="A1375" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1375" t="inlineStr">
+        <is>
+          <t>Trump perketat aturan kewarganegaraan berdasarkan tempat kelahiran</t>
+        </is>
+      </c>
+      <c r="C1375" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:53:13 +0700</t>
+        </is>
+      </c>
+      <c r="D1375" t="inlineStr">
+        <is>
+          <t>Redaksi Antara</t>
+        </is>
+      </c>
+      <c r="E1375" t="inlineStr">
+        <is>
+          <t>Presiden AS Donald Trump, Kamis (6/8), menandatangani dua perintah eksekutif yang bertujuan untuk semakin membatasi ...</t>
+        </is>
+      </c>
+      <c r="F1375" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1375" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685204/trump-perketat-aturan-kewarganegaraan-berdasarkan-tempat-kelahiran</t>
+        </is>
+      </c>
+      <c r="H1375" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/30/thumbs_b_c_7585b7a40076b45ff76a5da72d4e66da.jpg</t>
+        </is>
+      </c>
+      <c r="I1375" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1376">
+      <c r="A1376" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1376" t="inlineStr">
+        <is>
+          <t>Jepang tetapkan pedoman hak suara, targetkan penggunaan AI tanpa izin</t>
+        </is>
+      </c>
+      <c r="C1376" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:50:52 +0700</t>
+        </is>
+      </c>
+      <c r="D1376" t="inlineStr">
+        <is>
+          <t>Redaksi Antara</t>
+        </is>
+      </c>
+      <c r="E1376" t="inlineStr">
+        <is>
+          <t>Suara para selebriti dan pengisi suara Jepang harus dilindungi di bawah hak publisitas yang diperluas karena merupakan ...</t>
+        </is>
+      </c>
+      <c r="F1376" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1376" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685203/jepang-tetapkan-pedoman-hak-suara-targetkan-penggunaan-ai-tanpa-izin</t>
+        </is>
+      </c>
+      <c r="H1376" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/01/JepangBenderaAnadolu_as.jpg</t>
+        </is>
+      </c>
+      <c r="I1376" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1377">
+      <c r="A1377" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1377" t="inlineStr">
+        <is>
+          <t>Ombudsman perkuat pengawasan tiga program prioritas nasional</t>
+        </is>
+      </c>
+      <c r="C1377" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:49:44 +0700</t>
+        </is>
+      </c>
+      <c r="D1377" t="inlineStr">
+        <is>
+          <t>Redaksi Antara</t>
+        </is>
+      </c>
+      <c r="E1377" t="inlineStr">
+        <is>
+          <t>Ombudsman RI memperkuat pengawasan terhadap tiga program prioritas nasional, yakni Makan Bergizi Gratis (MBG), Sekolah ...</t>
+        </is>
+      </c>
+      <c r="F1377" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1377" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685199/ombudsman-perkuat-pengawasan-tiga-program-prioritas-nasional</t>
+        </is>
+      </c>
+      <c r="H1377" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/1000475325.jpg</t>
+        </is>
+      </c>
+      <c r="I1377" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1378">
+      <c r="A1378" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1378" t="inlineStr">
+        <is>
+          <t>Tim Pengawalan Streamlining BUMN perkuat regulasi transformasi BUMN</t>
+        </is>
+      </c>
+      <c r="C1378" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:48:54 +0700</t>
+        </is>
+      </c>
+      <c r="D1378" t="inlineStr">
+        <is>
+          <t>Redaksi Antara</t>
+        </is>
+      </c>
+      <c r="E1378" t="inlineStr">
+        <is>
+          <t>Tim Pengawalan Streamlining BUMN yang terdiri atas BP BUMN, Danantara, Kementerian Hukum, dan Kejaksaan RI terus ...</t>
+        </is>
+      </c>
+      <c r="F1378" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1378" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685196/tim-pengawalan-streamlining-bumn-perkuat-regulasi-transformasi-bumn</t>
+        </is>
+      </c>
+      <c r="H1378" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/WhatsApp-Image-2026-08-07-at-10.05.33.jpeg</t>
+        </is>
+      </c>
+      <c r="I1378" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1379">
+      <c r="A1379" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1379" t="inlineStr">
+        <is>
+          <t>BP BUMN catat 274 BUMN telah ditata dalam rangka transformasi</t>
+        </is>
+      </c>
+      <c r="C1379" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:44:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1379" t="inlineStr">
+        <is>
+          <t>Redaksi Antara</t>
+        </is>
+      </c>
+      <c r="E1379" t="inlineStr">
+        <is>
+          <t>Kepala Badan Pengaturan Badan Usaha Milik Negara (BP BUMN) Dony Oskaria mencatat sebanyak 274 perusahaan pelat ...</t>
+        </is>
+      </c>
+      <c r="F1379" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1379" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685188/bp-bumn-catat-274-bumn-telah-ditata-dalam-rangka-transformasi</t>
+        </is>
+      </c>
+      <c r="H1379" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/07/31/IMG_3638.jpeg</t>
+        </is>
+      </c>
+      <c r="I1379" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1380">
+      <c r="A1380" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1380" t="inlineStr">
+        <is>
+          <t>Eks penyidik KPK: Kasus eks Jampidsus perlu terus diawasi publik</t>
+        </is>
+      </c>
+      <c r="C1380" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:44:47 +0700</t>
+        </is>
+      </c>
+      <c r="D1380" t="inlineStr">
+        <is>
+          <t>Redaksi Antara</t>
+        </is>
+      </c>
+      <c r="E1380" t="inlineStr">
+        <is>
+          <t>Mantan penyidik Komisi Pemberantasan Korupsi (KPK) Yudi Purnomo Harahap menilai penanganan kasus dugaan tindak pidana ...</t>
+        </is>
+      </c>
+      <c r="F1380" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1380" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685184/eks-penyidik-kpk-kasus-eks-jampidsus-perlu-terus-diawasi-publik</t>
+        </is>
+      </c>
+      <c r="H1380" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2021/08/16/IMG-20191206-WA0012_1610529146924.jpg</t>
+        </is>
+      </c>
+      <c r="I1380" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1381">
+      <c r="A1381" t="inlineStr">
+        <is>
+          <t>Terkini</t>
+        </is>
+      </c>
+      <c r="B1381" t="inlineStr">
+        <is>
+          <t>Klasemen Grup A Piala AFF 2026: Vietnam dan Singapura ke semifinal</t>
+        </is>
+      </c>
+      <c r="C1381" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 23:42:30 +0700</t>
+        </is>
+      </c>
+      <c r="D1381" t="inlineStr">
+        <is>
+          <t>Redaksi Antara</t>
+        </is>
+      </c>
+      <c r="E1381" t="inlineStr">
+        <is>
+          <t>Timnas Vietnam dan Timnas Singapura melaju ke semifinal Piala AFF 2026 setelah menempati peringkat kedua teratas ...</t>
+        </is>
+      </c>
+      <c r="F1381" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1381" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/5685181/klasemen-grup-a-piala-aff-2026-vietnam-dan-singapura-ke-semifinal</t>
+        </is>
+      </c>
+      <c r="H1381" t="inlineStr">
+        <is>
+          <t>https://cdn.antaranews.com/cache/800x533/2026/08/07/aff.jpg</t>
+        </is>
+      </c>
+      <c r="I1381" t="inlineStr">
+        <is>
+          <t>Antara</t>
+        </is>
+      </c>
+    </row>
+    <row r="1382">
+      <c r="A1382" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1382" t="inlineStr">
+        <is>
+          <t>Freeport Pastikan Smelter Manyar Gresik Produksi Lagi Mulai September</t>
+        </is>
+      </c>
+      <c r="C1382" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:30:15 +0700</t>
+        </is>
+      </c>
+      <c r="D1382" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1382" t="inlineStr">
+        <is>
+          <t>PT Freeport Indonesia (PTFI) memastikan smelter Manyar di JIIPE, Gresik, Jawa Timur, mulai memproduksi katoda tembaga pada September 2026.</t>
+        </is>
+      </c>
+      <c r="F1382" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1382" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807204055-85-1389951/freeport-pastikan-smelter-manyar-gresik-produksi-lagi-mulai-september</t>
+        </is>
+      </c>
+      <c r="H1382" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/29/tony-wenas-presiden-direktur-pt-freeport-indonesia-1785306971048_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1382" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1383">
+      <c r="A1383" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1383" t="inlineStr">
+        <is>
+          <t>Pertamina Perkuat SDM Local Hero, Bangun Kemandirian Energi Desa</t>
+        </is>
+      </c>
+      <c r="C1383" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:01:18 +0700</t>
+        </is>
+      </c>
+      <c r="D1383" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1383" t="inlineStr">
+        <is>
+          <t>Melalui Program Desa Energi Berdikari, Pertamina membina para local hero melalui edukasi, pelatihan, hingga sertifikasi kompetensi.</t>
+        </is>
+      </c>
+      <c r="F1383" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1383" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807205732-625-1389962/pertamina-perkuat-sdm-local-hero-bangun-kemandirian-energi-desa</t>
+        </is>
+      </c>
+      <c r="H1383" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/pertamina-1786111216109_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1383" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1384">
+      <c r="A1384" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1384" t="inlineStr">
+        <is>
+          <t>ASDP Terapkan Standar Baru Keselamatan Nasional di 6 Pelabuhan Utama</t>
+        </is>
+      </c>
+      <c r="C1384" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:30:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1384" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1384" t="inlineStr">
+        <is>
+          <t>PT ASDP Indonesia Ferry (Persero) resmi menerapkan program sterilisasi pelabuhan secara penuh di enam pelabuhan utama mulai Rabu (5/8).</t>
+        </is>
+      </c>
+      <c r="F1384" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1384" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807135157-92-1389713/asdp-terapkan-standar-baru-keselamatan-nasional-di-6-pelabuhan-utama</t>
+        </is>
+      </c>
+      <c r="H1384" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/asdp-resmi-terapkan-standar-baru-keselamatan-nasional-di-6-pelabuhan-utama-1786074467002_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1384" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1385">
+      <c r="A1385" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1385" t="inlineStr">
+        <is>
+          <t>BGN Bakal Pasang CCTV yang Terhubung ke Kantor Pusat Buat Awasi SPPG</t>
+        </is>
+      </c>
+      <c r="C1385" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:23:17 +0700</t>
+        </is>
+      </c>
+      <c r="D1385" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1385" t="inlineStr">
+        <is>
+          <t>BGN tengah menyiapkan sistem pengawasan baru berupa CCTV terintegrasi di seluruh SPPG. CCTV tersebut akan terhubung langsung ke kantor pusat.</t>
+        </is>
+      </c>
+      <c r="F1385" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1385" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807195839-92-1389933/bgn-bakal-pasang-cctv-yang-terhubung-ke-kantor-pusat-buat-awasi-sppg</t>
+        </is>
+      </c>
+      <c r="H1385" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/05/20/pemerintah-pangkas-anggaran-mbg-1779256675949_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1385" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1386">
+      <c r="A1386" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1386" t="inlineStr">
+        <is>
+          <t>Bank Mandiri Konsisten Perluas Manfaat Lewat Program Sosial Lingkungan</t>
+        </is>
+      </c>
+      <c r="C1386" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:21:57 +0700</t>
+        </is>
+      </c>
+      <c r="D1386" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1386" t="inlineStr">
+        <is>
+          <t>Implementasi tanggung jawab sosial itu diwujudkan lewat tiga pilar utama, yakni Sustainable Banking, Sustainable Operation, dan Sustainability Beyond Banking.</t>
+        </is>
+      </c>
+      <c r="F1386" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1386" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807200857-625-1389938/bank-mandiri-konsisten-perluas-manfaat-lewat-program-sosial-lingkungan</t>
+        </is>
+      </c>
+      <c r="H1386" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2025/09/30/bank-mandiri-1759222272580_169.png?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1386" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1387">
+      <c r="A1387" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1387" t="inlineStr">
+        <is>
+          <t>Semangat Koperasi Berhembus di Festival Lembah Baliem</t>
+        </is>
+      </c>
+      <c r="C1387" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 20:01:13 +0700</t>
+        </is>
+      </c>
+      <c r="D1387" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1387" t="inlineStr">
+        <is>
+          <t>Festival Budaya Lembah Baliem yang mempromosikan produk unggulan seperti kopi dan budaya ini dinilai Menkop sebagai momentum membangun kekuatan ekonomi lokal.</t>
+        </is>
+      </c>
+      <c r="F1387" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1387" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807181301-97-1389932/semangat-koperasi-berhembus-di-festival-lembah-baliem</t>
+        </is>
+      </c>
+      <c r="H1387" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/kemenkop-1786107655627_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1387" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1388">
+      <c r="A1388" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1388" t="inlineStr">
+        <is>
+          <t>Digitalisasi Jadi Motor Dongkrak Produktivitas Bank Mandiri</t>
+        </is>
+      </c>
+      <c r="C1388" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:59:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1388" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1388" t="inlineStr">
+        <is>
+          <t>Bank Mandiri terus tingkatkan kapabilitas digital, memperluas layanan dan efisiensi. Aplikasi Livin' dan Kopra tumbuh pesat, mendukung inklusi ekonomi.</t>
+        </is>
+      </c>
+      <c r="F1388" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1388" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807194135-625-1389925/digitalisasi-jadi-motor-dongkrak-produktivitas-bank-mandiri</t>
+        </is>
+      </c>
+      <c r="H1388" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2022/06/23/livin-bank-mandiri-5_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1388" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1389">
+      <c r="A1389" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1389" t="inlineStr">
+        <is>
+          <t>BGN Bakal Pasang Label Batas Konsumsi Maksimal 4 Jam di Ompreng MBG</t>
+        </is>
+      </c>
+      <c r="C1389" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:47:59 +0700</t>
+        </is>
+      </c>
+      <c r="D1389" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1389" t="inlineStr">
+        <is>
+          <t>BGN akan memperketat standar operasional prosedur (SOP) program MBG dengan mewajibkan makanan dikonsumsi maksimal empat jam setelah selesai dimasak.</t>
+        </is>
+      </c>
+      <c r="F1389" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1389" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807193427-92-1389921/bgn-bakal-pasang-label-batas-konsumsi-maksimal-4-jam-di-ompreng-mbg</t>
+        </is>
+      </c>
+      <c r="H1389" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/05/20/pemerintah-pangkas-anggaran-mbg-1779256686908_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1389" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1390">
+      <c r="A1390" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1390" t="inlineStr">
+        <is>
+          <t>Swasembada Beras, Fondasi Pemerintah Jaga Kedaulatan Pangan Nasional</t>
+        </is>
+      </c>
+      <c r="C1390" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:38:26 +0700</t>
+        </is>
+      </c>
+      <c r="D1390" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1390" t="inlineStr">
+        <is>
+          <t>Momentum Hari Kemerdekaan RI menekankan pentingnya swasembada beras. Kementan targetkan 2025, dengan stok beras mencapai 26 juta ton untuk stabilitas pangan.</t>
+        </is>
+      </c>
+      <c r="F1390" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1390" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807193251-97-1389920/swasembada-beras-fondasi-pemerintah-jaga-kedaulatan-pangan-nasional</t>
+        </is>
+      </c>
+      <c r="H1390" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2024/02/17/bulog-guyur-beras-ke-pasar-induk-cipinang-8_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1390" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1391">
+      <c r="A1391" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1391" t="inlineStr">
+        <is>
+          <t>Bos BGN Pecat 66 Kepala SPPG, Ada yang Terlibat Judol hingga Minta Fee</t>
+        </is>
+      </c>
+      <c r="C1391" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:25:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1391" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1391" t="inlineStr">
+        <is>
+          <t>Kepala BGN Sudaryono menyebut 66 kepala SPPG dipecat karena berbagai pelanggaran, mulai dari indisipliner, judi online, hingga diduga meminta fee kepada mitra.</t>
+        </is>
+      </c>
+      <c r="F1391" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1391" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807191247-92-1389912/bos-bgn-pecat-66-kepala-sppg-ada-yang-terlibat-judol-hingga-minta-fee</t>
+        </is>
+      </c>
+      <c r="H1391" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/05/bos-bgn-ultimatum-dapur-mbg-1785936867455_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1391" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1392">
+      <c r="A1392" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1392" t="inlineStr">
+        <is>
+          <t>BGN Mulai Coret Sekolah Swasta Elite dari Daftar Penerima MBG</t>
+        </is>
+      </c>
+      <c r="C1392" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:12:20 +0700</t>
+        </is>
+      </c>
+      <c r="D1392" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1392" t="inlineStr">
+        <is>
+          <t>Sudaryono menegaskan tak akan memaksakan pemberian MBG kepada sekolah yang menyatakan tidak membutuhkan program tersebut.</t>
+        </is>
+      </c>
+      <c r="F1392" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1392" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807190126-92-1389897/bgn-mulai-coret-sekolah-swasta-elite-dari-daftar-penerima-mbg</t>
+        </is>
+      </c>
+      <c r="H1392" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/29/bgn-tutup-833-dapur-sppg-bermasalah-1785317578338_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1392" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1393">
+      <c r="A1393" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1393" t="inlineStr">
+        <is>
+          <t>Bos BGN: Guru Tak Seharusnya Urus Ompreng MBG</t>
+        </is>
+      </c>
+      <c r="C1393" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:58:23 +0700</t>
+        </is>
+      </c>
+      <c r="D1393" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1393" t="inlineStr">
+        <is>
+          <t>Kepala BGN Sudaryono merespons keluhan sejumlah guru yang mengaku terbebani pelaksanaan MBG, termasuk mengurus ompreng.</t>
+        </is>
+      </c>
+      <c r="F1393" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1393" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807184759-92-1389881/bos-bgn-guru-tak-seharusnya-urus-ompreng-mbg</t>
+        </is>
+      </c>
+      <c r="H1393" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/07/29/bgn-tutup-833-dapur-sppg-bermasalah-1785317578257_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1393" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1394">
+      <c r="A1394" t="inlineStr">
+        <is>
+          <t>Ekonomi</t>
+        </is>
+      </c>
+      <c r="B1394" t="inlineStr">
+        <is>
+          <t>Bahlil Kenang Didemo 1,5 Bulan Gara-gara Larangan Ekspor Bijih Nikel</t>
+        </is>
+      </c>
+      <c r="C1394" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 18:43:50 +0700</t>
+        </is>
+      </c>
+      <c r="D1394" t="inlineStr">
+        <is>
+          <t>Redaksi CNN Indonesia</t>
+        </is>
+      </c>
+      <c r="E1394" t="inlineStr">
+        <is>
+          <t>Bahlil membagikan kisah menghadapi gelombang demo selama 1,5 bulan terkait kebijakan larangan ekspor bijih nikel. Saat itu, ia baru 4 hari menjabat Kepala BKPM.</t>
+        </is>
+      </c>
+      <c r="F1394" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1394" t="inlineStr">
+        <is>
+          <t>https://www.cnnindonesia.com/ekonomi/20260807181838-85-1389861/bahlil-kenang-didemo-15-bulan-gara-gara-larangan-ekspor-bijih-nikel</t>
+        </is>
+      </c>
+      <c r="H1394" t="inlineStr">
+        <is>
+          <t>https://akcdn.detik.net.id/visual/2026/08/07/peluncuran-sepuluh-buku-karya-nyata-untuk-negeri-bahlil-lahadalia-1786099773487_169.jpeg?w=360&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1394" t="inlineStr">
+        <is>
+          <t>CNN Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1395">
+      <c r="A1395" t="inlineStr">
+        <is>
+          <t>Market</t>
+        </is>
+      </c>
+      <c r="B1395" t="inlineStr">
+        <is>
+          <t>Prabowo Mau Perbaiki Buku SD-SMA, Malaysia-Kamboja Jadi Pembanding</t>
+        </is>
+      </c>
+      <c r="C1395" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 19:54:58 +0700</t>
+        </is>
+      </c>
+      <c r="D1395" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1395" t="inlineStr">
+        <is>
+          <t>Pemerintah tengah menggelar program perbaikan kualitas buku pelajaran di sekolah SD-SMA.</t>
+        </is>
+      </c>
+      <c r="F1395" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1395" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/market/20260807194220-17-757542/prabowo-mau-perbaiki-buku-sd-sma-malaysia-kamboja-jadi-pembanding</t>
+        </is>
+      </c>
+      <c r="H1395" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/menteri-sekertaris-negera-dan-sekertaris-kabinet-di-depan-buku-buku-pelajaran-sd-sma-negara-negara-tetangga-ri-jumat-782026-1786106683018_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1395" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1373"/>
+  <autoFilter ref="A1:I1395"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/berita_2026-08-07.xlsx
+++ b/data/berita_2026-08-07.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Berita" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1395</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Berita'!$A$1:$I$1401</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1395"/>
+  <dimension ref="A1:I1401"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -65998,8 +65998,290 @@
         </is>
       </c>
     </row>
+    <row r="1396">
+      <c r="A1396" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1396" t="inlineStr">
+        <is>
+          <t>Presiden Ini Mendadak Dievakuasi Tengah Malam, Ada Apa?</t>
+        </is>
+      </c>
+      <c r="C1396" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 22:00:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1396" t="inlineStr">
+        <is>
+          <t>tfa</t>
+        </is>
+      </c>
+      <c r="E1396" t="inlineStr">
+        <is>
+          <t>Presiden Taiwan Lai Ching-te mendadak dievakuasi menggunakan kendaraan pengangkut personel lapis baja menuju pusat komando pada Rabu malam lalu.</t>
+        </is>
+      </c>
+      <c r="F1396" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1396" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807171848-4-757520/presiden-ini-mendadak-dievakuasi-tengah-malam-ada-apa</t>
+        </is>
+      </c>
+      <c r="H1396" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/10/25/tentara-berdiri-selama-latihan-militer-di-pulau-penghu-taiwan-kamis-24-oktober-2024_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1396" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1397">
+      <c r="A1397" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1397" t="inlineStr">
+        <is>
+          <t>Korut "Terpanggang", Kim Jong Un Dorong Warga Makan Daging Anjing</t>
+        </is>
+      </c>
+      <c r="C1397" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:50:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1397" t="inlineStr">
+        <is>
+          <t>tps</t>
+        </is>
+      </c>
+      <c r="E1397" t="inlineStr">
+        <is>
+          <t>Korea Utara menghadapi gelombang panas ekstrem, media pemerintah mendorong konsumsi sup daging anjing dan kaldu ayam.</t>
+        </is>
+      </c>
+      <c r="F1397" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1397" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807152252-4-757464/korut-terpanggang-kim-jong-un-dorong-warga-makan-daging-anjing</t>
+        </is>
+      </c>
+      <c r="H1397" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2024/08/10/pemimpin-korea-utara-kim-jong-un-menyapa-anak-anak-saat-berkunjung-ke-daerah-yang-terkena-banjir-di-kabupaten-uiju-provinsi-py_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1397" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1398">
+      <c r="A1398" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1398" t="inlineStr">
+        <is>
+          <t>Stres Belajar, Kronologi Siswa 14 Tahun Tembak Sekolah dan Bunuh Guru</t>
+        </is>
+      </c>
+      <c r="C1398" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:40:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1398" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1398" t="inlineStr">
+        <is>
+          <t>Seorang siswa 14 tahun melakukan penembakan di Sekolah Debsirin Nonthaburi, Thailand, menewaskan delapan orang.</t>
+        </is>
+      </c>
+      <c r="F1398" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1398" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807171445-4-757518/stres-belajar-kronologi-siswa-14-tahun-tembak-sekolah-bunuh-guru</t>
+        </is>
+      </c>
+      <c r="H1398" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/petugas-penyelamat-berdiri-di-dekat-ambulans-di-sekolah-debsirin-nonthaburilokasi-terjadinya-insiden-penembakandi-distrik-bang-1786084015199_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1398" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1399">
+      <c r="A1399" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1399" t="inlineStr">
+        <is>
+          <t>"Neraka Luber-Luber" di Eropa, Sungai Menghilang-Suhu Panas Mendidih</t>
+        </is>
+      </c>
+      <c r="C1399" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:30:00 +0700</t>
+        </is>
+      </c>
+      <c r="D1399" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1399" t="inlineStr">
+        <is>
+          <t>Eropa menghadapi gelombang panas ekstrem dengan suhu melebihi 40°C. Kebakaran hutan melanda, dan negara-negara mengambil langkah</t>
+        </is>
+      </c>
+      <c r="F1399" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1399" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807081855-4-757300/neraka-luber-luber-di-eropa-sungai-menghilang-suhu-panas-mendidih</t>
+        </is>
+      </c>
+      <c r="H1399" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/05/tampilan-dari-drone-memperlihatkan-gosong-pasir-yang-muncul-di-permukaan-sungai-vistula-dekat-jozefowdi-pinggiran-warsawa-pola-1785897303805_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1399" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1400">
+      <c r="A1400" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1400" t="inlineStr">
+        <is>
+          <t>Pertamina Bangun Kemandirian Energi Desa Lewat Local Hero</t>
+        </is>
+      </c>
+      <c r="C1400" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:17:01 +0700</t>
+        </is>
+      </c>
+      <c r="D1400" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1400" t="inlineStr">
+        <is>
+          <t>PPertamina mengubah kehidupan masyarakat dengan menyediakan akses air bersih dan energi terbarukan, meningkatkan kemandirian dan kesejahteraan desa.</t>
+        </is>
+      </c>
+      <c r="F1400" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1400" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807211326-4-757548/pertamina-bangun-kemandirian-energi-desa-lewat-local-hero</t>
+        </is>
+      </c>
+      <c r="H1400" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2026/08/07/pertamina-1786112206041_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1400" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
+    <row r="1401">
+      <c r="A1401" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B1401" t="inlineStr">
+        <is>
+          <t>Danantara dan JBS Group Kerja Sama Kembangkan Ekosistem Protein</t>
+        </is>
+      </c>
+      <c r="C1401" t="inlineStr">
+        <is>
+          <t>Fri, 07 Aug 2026 21:11:35 +0700</t>
+        </is>
+      </c>
+      <c r="D1401" t="inlineStr">
+        <is>
+          <t>Redaksi CNBC Indonesia</t>
+        </is>
+      </c>
+      <c r="E1401" t="inlineStr">
+        <is>
+          <t>Danantara Indonesia menjalin kemitraan strategis dengan JBS Group senilai USD 2,5 miliar untuk pengelolaan operasi di Australia dan Selandia Baru.</t>
+        </is>
+      </c>
+      <c r="F1401" t="inlineStr">
+        <is>
+          <t>Netral</t>
+        </is>
+      </c>
+      <c r="G1401" t="inlineStr">
+        <is>
+          <t>https://www.cnbcindonesia.com/news/20260807210838-4-757547/danantara-jbs-group-kerja-sama-kembangkan-ekosistem-protein</t>
+        </is>
+      </c>
+      <c r="H1401" t="inlineStr">
+        <is>
+          <t>https://awsimages.detik.net.id/visual/2025/03/05/kantor-danantara-pusat-di-jakarta-indonesia-28-februari-2025-1741144820212_169.jpeg?w=1200&amp;q=90</t>
+        </is>
+      </c>
+      <c r="I1401" t="inlineStr">
+        <is>
+          <t>CNBC Indonesia</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I1395"/>
+  <autoFilter ref="A1:I1401"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>